--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -28,12 +28,17 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,9 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,11 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B543"/>
+  <dimension ref="A1:D543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,6 +443,16 @@
           <t>price_00:00</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>price_00:15</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>change_00:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -444,6 +463,12 @@
       <c r="B2" s="1" t="n">
         <v>70282.60000000001</v>
       </c>
+      <c r="C2" s="1" t="n">
+        <v>70080.39999999999</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-0.002876956743205454</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -454,6 +479,12 @@
       <c r="B3" s="1" t="n">
         <v>2071.1</v>
       </c>
+      <c r="C3" s="1" t="n">
+        <v>2063.91</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.003471585147989018</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -464,6 +495,12 @@
       <c r="B4" s="1" t="n">
         <v>86.52</v>
       </c>
+      <c r="C4" s="1" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.005085529357373992</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -474,6 +511,12 @@
       <c r="B5" s="1" t="n">
         <v>0.010763</v>
       </c>
+      <c r="C5" s="1" t="n">
+        <v>0.011109</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.03214717086314232</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -484,6 +527,12 @@
       <c r="B6" s="1" t="n">
         <v>1.3785</v>
       </c>
+      <c r="C6" s="1" t="n">
+        <v>1.3725</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.0043525571273123</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -494,6 +543,12 @@
       <c r="B7" s="1" t="n">
         <v>0.09404999999999999</v>
       </c>
+      <c r="C7" s="1" t="n">
+        <v>0.09361999999999999</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.004572036150983518</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -504,6 +559,12 @@
       <c r="B8" s="1" t="n">
         <v>37.388</v>
       </c>
+      <c r="C8" s="1" t="n">
+        <v>37.317</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.001899005028351288</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -514,6 +575,12 @@
       <c r="B9" s="1" t="n">
         <v>0.04879</v>
       </c>
+      <c r="C9" s="1" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.0186513629842181</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -524,6 +591,12 @@
       <c r="B10" s="1" t="n">
         <v>18.011</v>
       </c>
+      <c r="C10" s="1" t="n">
+        <v>18.249</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.01321414691022151</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -534,6 +607,12 @@
       <c r="B11" s="1" t="n">
         <v>650.23</v>
       </c>
+      <c r="C11" s="1" t="n">
+        <v>649.88</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>-0.0005382710733125551</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -544,6 +623,12 @@
       <c r="B12" s="1" t="n">
         <v>0.9508</v>
       </c>
+      <c r="C12" s="1" t="n">
+        <v>0.9467</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-0.004312158182583081</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -554,6 +639,12 @@
       <c r="B13" s="1" t="n">
         <v>208.43</v>
       </c>
+      <c r="C13" s="1" t="n">
+        <v>208.75</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.001535287626541252</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -564,6 +655,12 @@
       <c r="B14" s="1" t="n">
         <v>0.0032957</v>
       </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0032803</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.004672755408562688</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -574,6 +671,12 @@
       <c r="B15" s="1" t="n">
         <v>0.23917</v>
       </c>
+      <c r="C15" s="1" t="n">
+        <v>0.25799</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.0786887987623866</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -584,6 +687,12 @@
       <c r="B16" s="1" t="n">
         <v>0.9695</v>
       </c>
+      <c r="C16" s="1" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.0005157297576070716</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -594,6 +703,12 @@
       <c r="B17" s="1" t="n">
         <v>0.0302</v>
       </c>
+      <c r="C17" s="1" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.00993377483443714</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,6 +719,12 @@
       <c r="B18" s="1" t="n">
         <v>211.93</v>
       </c>
+      <c r="C18" s="1" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.001179634785070542</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -614,6 +735,12 @@
       <c r="B19" s="1" t="n">
         <v>0.2618</v>
       </c>
+      <c r="C19" s="1" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>-0.002673796791443768</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -624,6 +751,12 @@
       <c r="B20" s="1" t="n">
         <v>0.016957</v>
       </c>
+      <c r="C20" s="1" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>-0.009848440172200299</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -634,6 +767,12 @@
       <c r="B21" s="1" t="n">
         <v>9.582000000000001</v>
       </c>
+      <c r="C21" s="1" t="n">
+        <v>9.569000000000001</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>-0.001356710498852004</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -644,6 +783,12 @@
       <c r="B22" s="1" t="n">
         <v>0.1697</v>
       </c>
+      <c r="C22" s="1" t="n">
+        <v>0.1676</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>-0.01237477902180313</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -654,6 +799,12 @@
       <c r="B23" s="1" t="n">
         <v>0.35024</v>
       </c>
+      <c r="C23" s="1" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>-0.00385449977158525</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -664,6 +815,12 @@
       <c r="B24" s="1" t="n">
         <v>0.859</v>
       </c>
+      <c r="C24" s="1" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>-0.001164144353899885</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -674,6 +831,12 @@
       <c r="B25" s="1" t="n">
         <v>9.029999999999999</v>
       </c>
+      <c r="C25" s="1" t="n">
+        <v>8.997999999999999</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>-0.003543743078626803</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -684,6 +847,12 @@
       <c r="B26" s="1" t="n">
         <v>1.321</v>
       </c>
+      <c r="C26" s="1" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-0.005299015897047612</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -694,6 +863,12 @@
       <c r="B27" s="1" t="n">
         <v>5132.26</v>
       </c>
+      <c r="C27" s="1" t="n">
+        <v>5128.73</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>-0.0006878061516759974</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -704,6 +879,12 @@
       <c r="B28" s="1" t="n">
         <v>0.3514</v>
       </c>
+      <c r="C28" s="1" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>-0.005976095617529854</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -714,6 +895,12 @@
       <c r="B29" s="1" t="n">
         <v>2.652</v>
       </c>
+      <c r="C29" s="1" t="n">
+        <v>2.649</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>-0.001131221719457056</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -724,6 +911,12 @@
       <c r="B30" s="1" t="n">
         <v>0.56787</v>
       </c>
+      <c r="C30" s="1" t="n">
+        <v>0.57131</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0.00605772447919418</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -734,6 +927,12 @@
       <c r="B31" s="1" t="n">
         <v>0.002078</v>
       </c>
+      <c r="C31" s="1" t="n">
+        <v>0.002068</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>-0.004812319538017337</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -744,6 +943,12 @@
       <c r="B32" s="1" t="n">
         <v>1.2404</v>
       </c>
+      <c r="C32" s="1" t="n">
+        <v>1.2513</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.008787487907126841</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -754,6 +959,12 @@
       <c r="B33" s="1" t="n">
         <v>0.3219</v>
       </c>
+      <c r="C33" s="1" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.002485243864554108</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -764,6 +975,12 @@
       <c r="B34" s="1" t="n">
         <v>1.502</v>
       </c>
+      <c r="C34" s="1" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>-0.0006657789613848948</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -774,6 +991,12 @@
       <c r="B35" s="1" t="n">
         <v>455.99</v>
       </c>
+      <c r="C35" s="1" t="n">
+        <v>455.49</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>-0.001096515274457773</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -784,6 +1007,12 @@
       <c r="B36" s="1" t="n">
         <v>0.04816</v>
       </c>
+      <c r="C36" s="1" t="n">
+        <v>0.04847</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.006436877076411914</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -794,6 +1023,12 @@
       <c r="B37" s="1" t="n">
         <v>0.705</v>
       </c>
+      <c r="C37" s="1" t="n">
+        <v>0.7049</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>-0.0001418439716311901</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -804,6 +1039,12 @@
       <c r="B38" s="1" t="n">
         <v>0.1051</v>
       </c>
+      <c r="C38" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -814,6 +1055,12 @@
       <c r="B39" s="1" t="n">
         <v>109.64</v>
       </c>
+      <c r="C39" s="1" t="n">
+        <v>108.93</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>-0.006475738781466561</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -824,6 +1071,12 @@
       <c r="B40" s="1" t="n">
         <v>0.03784</v>
       </c>
+      <c r="C40" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.0200845665961946</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -834,6 +1087,12 @@
       <c r="B41" s="1" t="n">
         <v>0.056</v>
       </c>
+      <c r="C41" s="1" t="n">
+        <v>0.05539</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>-0.01089285714285713</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -844,6 +1103,12 @@
       <c r="B42" s="1" t="n">
         <v>54.28</v>
       </c>
+      <c r="C42" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>-0.001473839351510654</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -854,6 +1119,12 @@
       <c r="B43" s="1" t="n">
         <v>0.1321</v>
       </c>
+      <c r="C43" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>-0.004542013626040798</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -864,6 +1135,12 @@
       <c r="B44" s="1" t="n">
         <v>0.005868</v>
       </c>
+      <c r="C44" s="1" t="n">
+        <v>0.005844</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>-0.004089979550102201</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -874,6 +1151,12 @@
       <c r="B45" s="1" t="n">
         <v>0.09798</v>
       </c>
+      <c r="C45" s="1" t="n">
+        <v>0.09919</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.01234945907328029</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -884,6 +1167,12 @@
       <c r="B46" s="1" t="n">
         <v>2.752</v>
       </c>
+      <c r="C46" s="1" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>-0.0007267441860464316</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -894,6 +1183,12 @@
       <c r="B47" s="1" t="n">
         <v>0.28946</v>
       </c>
+      <c r="C47" s="1" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>-0.0007254888412906377</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -904,6 +1199,12 @@
       <c r="B48" s="1" t="n">
         <v>0.1057</v>
       </c>
+      <c r="C48" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>-0.00283822138126782</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -914,6 +1215,12 @@
       <c r="B49" s="1" t="n">
         <v>0.25131</v>
       </c>
+      <c r="C49" s="1" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>-0.002467072539890788</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -924,6 +1231,12 @@
       <c r="B50" s="1" t="n">
         <v>0.04792</v>
       </c>
+      <c r="C50" s="1" t="n">
+        <v>0.04821</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.006051752921536009</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -934,6 +1247,12 @@
       <c r="B51" s="1" t="n">
         <v>3.894</v>
       </c>
+      <c r="C51" s="1" t="n">
+        <v>3.888</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>-0.001540832049306684</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -944,6 +1263,12 @@
       <c r="B52" s="1" t="n">
         <v>0.000238</v>
       </c>
+      <c r="C52" s="1" t="n">
+        <v>0.000238</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -954,6 +1279,12 @@
       <c r="B53" s="1" t="n">
         <v>0.1651</v>
       </c>
+      <c r="C53" s="1" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>-0.004845548152634737</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -964,6 +1295,12 @@
       <c r="B54" s="1" t="n">
         <v>0.04045</v>
       </c>
+      <c r="C54" s="1" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.009394313967861518</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -974,6 +1311,12 @@
       <c r="B55" s="1" t="n">
         <v>0.12028</v>
       </c>
+      <c r="C55" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.001829065513801114</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -984,6 +1327,12 @@
       <c r="B56" s="1" t="n">
         <v>0.3197</v>
       </c>
+      <c r="C56" s="1" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>-0.002502345949327393</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -994,6 +1343,12 @@
       <c r="B57" s="1" t="n">
         <v>0.01193</v>
       </c>
+      <c r="C57" s="1" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>-0.005867560771165036</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1004,6 +1359,12 @@
       <c r="B58" s="1" t="n">
         <v>0.0988</v>
       </c>
+      <c r="C58" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.001012145748987883</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1014,6 +1375,12 @@
       <c r="B59" s="1" t="n">
         <v>0.00335</v>
       </c>
+      <c r="C59" s="1" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1024,6 +1391,12 @@
       <c r="B60" s="1" t="n">
         <v>0.1519</v>
       </c>
+      <c r="C60" s="1" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>-0.0006583278472680497</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1034,6 +1407,12 @@
       <c r="B61" s="1" t="n">
         <v>0.15882</v>
       </c>
+      <c r="C61" s="1" t="n">
+        <v>0.15845</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>-0.002329681400327298</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1044,6 +1423,12 @@
       <c r="B62" s="1" t="n">
         <v>0.7089</v>
       </c>
+      <c r="C62" s="1" t="n">
+        <v>0.7054</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>-0.004937226689236772</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1054,6 +1439,12 @@
       <c r="B63" s="1" t="n">
         <v>5.703</v>
       </c>
+      <c r="C63" s="1" t="n">
+        <v>5.709</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.001052077853761063</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1064,6 +1455,12 @@
       <c r="B64" s="1" t="n">
         <v>0.007045</v>
       </c>
+      <c r="C64" s="1" t="n">
+        <v>0.007024</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>-0.002980837473385406</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1074,6 +1471,12 @@
       <c r="B65" s="1" t="n">
         <v>0.03039</v>
       </c>
+      <c r="C65" s="1" t="n">
+        <v>0.03086</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.01546561368871333</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1084,6 +1487,12 @@
       <c r="B66" s="1" t="n">
         <v>0.233</v>
       </c>
+      <c r="C66" s="1" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>-0.004291845493562235</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1094,6 +1503,12 @@
       <c r="B67" s="1" t="n">
         <v>1.598</v>
       </c>
+      <c r="C67" s="1" t="n">
+        <v>1.602</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.002503128911138926</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1104,6 +1519,12 @@
       <c r="B68" s="1" t="n">
         <v>2.0068</v>
       </c>
+      <c r="C68" s="1" t="n">
+        <v>1.9889</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>-0.008919673111421292</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1114,6 +1535,12 @@
       <c r="B69" s="1" t="n">
         <v>0.5736</v>
       </c>
+      <c r="C69" s="1" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.002440725244072449</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1124,6 +1551,12 @@
       <c r="B70" s="1" t="n">
         <v>0.106</v>
       </c>
+      <c r="C70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>-0.0188679245283019</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1134,6 +1567,12 @@
       <c r="B71" s="1" t="n">
         <v>0.9106</v>
       </c>
+      <c r="C71" s="1" t="n">
+        <v>0.9101</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>-0.0005490885130682462</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1144,6 +1583,12 @@
       <c r="B72" s="1" t="n">
         <v>0.4263</v>
       </c>
+      <c r="C72" s="1" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>-0.002814919071076787</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1154,6 +1599,12 @@
       <c r="B73" s="1" t="n">
         <v>0.09413000000000001</v>
       </c>
+      <c r="C73" s="1" t="n">
+        <v>0.09384000000000001</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>-0.003080845639009865</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1164,6 +1615,12 @@
       <c r="B74" s="1" t="n">
         <v>1.1566</v>
       </c>
+      <c r="C74" s="1" t="n">
+        <v>1.1542</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>-0.002075047553173249</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1174,6 +1631,12 @@
       <c r="B75" s="1" t="n">
         <v>0.01593</v>
       </c>
+      <c r="C75" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>-0.0100439422473321</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1184,6 +1647,12 @@
       <c r="B76" s="1" t="n">
         <v>0.12643</v>
       </c>
+      <c r="C76" s="1" t="n">
+        <v>0.12497</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>-0.01154789211421331</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1194,6 +1663,12 @@
       <c r="B77" s="1" t="n">
         <v>0.1173</v>
       </c>
+      <c r="C77" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0.00341005967604431</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1204,6 +1679,12 @@
       <c r="B78" s="1" t="n">
         <v>0.1008</v>
       </c>
+      <c r="C78" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1214,6 +1695,12 @@
       <c r="B79" s="1" t="n">
         <v>0.005935</v>
       </c>
+      <c r="C79" s="1" t="n">
+        <v>0.005927</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>-0.001347935973041313</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1224,6 +1711,12 @@
       <c r="B80" s="1" t="n">
         <v>0.008081</v>
       </c>
+      <c r="C80" s="1" t="n">
+        <v>0.008159</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.009652270758569477</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1234,6 +1727,12 @@
       <c r="B81" s="1" t="n">
         <v>17.73</v>
       </c>
+      <c r="C81" s="1" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1244,6 +1743,12 @@
       <c r="B82" s="1" t="n">
         <v>0.1602</v>
       </c>
+      <c r="C82" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0.0006242197253432521</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1254,6 +1759,12 @@
       <c r="B83" s="1" t="n">
         <v>8.178000000000001</v>
       </c>
+      <c r="C83" s="1" t="n">
+        <v>8.161</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>-0.002078747860112648</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1264,6 +1775,12 @@
       <c r="B84" s="1" t="n">
         <v>351.7</v>
       </c>
+      <c r="C84" s="1" t="n">
+        <v>351.76</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0.0001705999431333587</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1274,6 +1791,12 @@
       <c r="B85" s="1" t="n">
         <v>0.004151</v>
       </c>
+      <c r="C85" s="1" t="n">
+        <v>0.004155</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0.0009636232233196009</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1284,6 +1807,12 @@
       <c r="B86" s="1" t="n">
         <v>0.13368</v>
       </c>
+      <c r="C86" s="1" t="n">
+        <v>0.13416</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.003590664272890546</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1294,6 +1823,12 @@
       <c r="B87" s="1" t="n">
         <v>0.01895</v>
       </c>
+      <c r="C87" s="1" t="n">
+        <v>0.01966</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.03746701846965693</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1304,6 +1839,12 @@
       <c r="B88" s="1" t="n">
         <v>1.12</v>
       </c>
+      <c r="C88" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.001785714285714287</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1314,6 +1855,12 @@
       <c r="B89" s="1" t="n">
         <v>0.2956</v>
       </c>
+      <c r="C89" s="1" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>-0.001014884979702189</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1324,6 +1871,12 @@
       <c r="B90" s="1" t="n">
         <v>0.2557</v>
       </c>
+      <c r="C90" s="1" t="n">
+        <v>0.2551</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>-0.002346499804458308</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1334,6 +1887,12 @@
       <c r="B91" s="1" t="n">
         <v>0.05869</v>
       </c>
+      <c r="C91" s="1" t="n">
+        <v>0.05879</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0.001703867779860332</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1344,6 +1903,12 @@
       <c r="B92" s="1" t="n">
         <v>1.3107</v>
       </c>
+      <c r="C92" s="1" t="n">
+        <v>1.3087</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>-0.001525902189669643</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1354,6 +1919,12 @@
       <c r="B93" s="1" t="n">
         <v>0.06292</v>
       </c>
+      <c r="C93" s="1" t="n">
+        <v>0.06265999999999999</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>-0.00413223140495884</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1364,6 +1935,12 @@
       <c r="B94" s="1" t="n">
         <v>0.00891</v>
       </c>
+      <c r="C94" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>-0.008978675645342335</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1374,6 +1951,12 @@
       <c r="B95" s="1" t="n">
         <v>0.331</v>
       </c>
+      <c r="C95" s="1" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>-0.001208459214501545</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1384,6 +1967,12 @@
       <c r="B96" s="1" t="n">
         <v>0.02268</v>
       </c>
+      <c r="C96" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>-0.005291005291005228</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1394,6 +1983,12 @@
       <c r="B97" s="1" t="n">
         <v>32.66</v>
       </c>
+      <c r="C97" s="1" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>-0.003674219228413884</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1404,6 +1999,12 @@
       <c r="B98" s="1" t="n">
         <v>1.097</v>
       </c>
+      <c r="C98" s="1" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>-0.002734731084776565</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1414,6 +2015,12 @@
       <c r="B99" s="1" t="n">
         <v>2.99</v>
       </c>
+      <c r="C99" s="1" t="n">
+        <v>2.984</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>-0.002006688963210778</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1424,6 +2031,12 @@
       <c r="B100" s="1" t="n">
         <v>0.03479</v>
       </c>
+      <c r="C100" s="1" t="n">
+        <v>0.03449</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>-0.008623167576889959</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1434,6 +2047,12 @@
       <c r="B101" s="1" t="n">
         <v>1.812</v>
       </c>
+      <c r="C101" s="1" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.002207505518763799</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1444,6 +2063,12 @@
       <c r="B102" s="1" t="n">
         <v>0.00743</v>
       </c>
+      <c r="C102" s="1" t="n">
+        <v>0.007452</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0.002960969044414578</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1454,6 +2079,12 @@
       <c r="B103" s="1" t="n">
         <v>0.067</v>
       </c>
+      <c r="C103" s="1" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.004477611940298428</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1464,6 +2095,12 @@
       <c r="B104" s="1" t="n">
         <v>0.4118</v>
       </c>
+      <c r="C104" s="1" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.0004856726566293783</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1474,6 +2111,12 @@
       <c r="B105" s="1" t="n">
         <v>1.786</v>
       </c>
+      <c r="C105" s="1" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>-0.00615901455767084</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1484,6 +2127,12 @@
       <c r="B106" s="1" t="n">
         <v>0.00813</v>
       </c>
+      <c r="C106" s="1" t="n">
+        <v>0.008055</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>-0.009225092250922559</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1494,6 +2143,12 @@
       <c r="B107" s="1" t="n">
         <v>0.0182</v>
       </c>
+      <c r="C107" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.001098901098901054</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1504,6 +2159,12 @@
       <c r="B108" s="1" t="n">
         <v>0.02102</v>
       </c>
+      <c r="C108" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0.005233111322549904</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1514,6 +2175,12 @@
       <c r="B109" s="1" t="n">
         <v>0.05645</v>
       </c>
+      <c r="C109" s="1" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>-0.0008857395925598128</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1524,6 +2191,12 @@
       <c r="B110" s="1" t="n">
         <v>0.12094</v>
       </c>
+      <c r="C110" s="1" t="n">
+        <v>0.11873</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>-0.01827352406151814</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1534,6 +2207,12 @@
       <c r="B111" s="1" t="n">
         <v>0.09907000000000001</v>
       </c>
+      <c r="C111" s="1" t="n">
+        <v>0.09862</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>-0.004542242858584899</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1544,6 +2223,12 @@
       <c r="B112" s="1" t="n">
         <v>0.0372</v>
       </c>
+      <c r="C112" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1554,6 +2239,12 @@
       <c r="B113" s="1" t="n">
         <v>0.0979</v>
       </c>
+      <c r="C113" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>-0.002042900919305472</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1564,6 +2255,12 @@
       <c r="B114" s="1" t="n">
         <v>0.001719</v>
       </c>
+      <c r="C114" s="1" t="n">
+        <v>0.001736</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0.00988947062245484</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1574,6 +2271,12 @@
       <c r="B115" s="1" t="n">
         <v>1.2312</v>
       </c>
+      <c r="C115" s="1" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0.002274204028589923</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1584,6 +2287,12 @@
       <c r="B116" s="1" t="n">
         <v>0.239</v>
       </c>
+      <c r="C116" s="1" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0.005439330543933152</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1594,6 +2303,12 @@
       <c r="B117" s="1" t="n">
         <v>0.06034</v>
       </c>
+      <c r="C117" s="1" t="n">
+        <v>0.06034</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1604,6 +2319,12 @@
       <c r="B118" s="1" t="n">
         <v>0.04314</v>
       </c>
+      <c r="C118" s="1" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>-0.00718590635141395</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1614,6 +2335,12 @@
       <c r="B119" s="1" t="n">
         <v>0.003839</v>
       </c>
+      <c r="C119" s="1" t="n">
+        <v>0.003805</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>-0.008856473039854174</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1624,6 +2351,12 @@
       <c r="B120" s="1" t="n">
         <v>0.786</v>
       </c>
+      <c r="C120" s="1" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>-0.001272264631043258</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1634,6 +2367,12 @@
       <c r="B121" s="1" t="n">
         <v>0.2965</v>
       </c>
+      <c r="C121" s="1" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>-0.00337268128161889</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1644,6 +2383,12 @@
       <c r="B122" s="1" t="n">
         <v>0.5709</v>
       </c>
+      <c r="C122" s="1" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>-0.001401296198983906</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1654,6 +2399,12 @@
       <c r="B123" s="1" t="n">
         <v>0.028465</v>
       </c>
+      <c r="C123" s="1" t="n">
+        <v>0.028871</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0.01426313015984543</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1664,6 +2415,12 @@
       <c r="B124" s="1" t="n">
         <v>0.07978</v>
       </c>
+      <c r="C124" s="1" t="n">
+        <v>0.07951</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>-0.003384306843820586</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1674,6 +2431,12 @@
       <c r="B125" s="1" t="n">
         <v>0.10123</v>
       </c>
+      <c r="C125" s="1" t="n">
+        <v>0.10113</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>-0.0009878494517435825</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1684,6 +2447,12 @@
       <c r="B126" s="1" t="n">
         <v>0.02739</v>
       </c>
+      <c r="C126" s="1" t="n">
+        <v>0.02759</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0.007301935012778342</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1694,6 +2463,12 @@
       <c r="B127" s="1" t="n">
         <v>0.02203</v>
       </c>
+      <c r="C127" s="1" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>-0.0009078529278258127</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1704,6 +2479,12 @@
       <c r="B128" s="1" t="n">
         <v>0.1615</v>
       </c>
+      <c r="C128" s="1" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>-0.003715170278637877</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1714,6 +2495,12 @@
       <c r="B129" s="1" t="n">
         <v>0.13639</v>
       </c>
+      <c r="C129" s="1" t="n">
+        <v>0.13596</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>-0.003152723806730799</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1724,6 +2511,12 @@
       <c r="B130" s="1" t="n">
         <v>0.0549</v>
       </c>
+      <c r="C130" s="1" t="n">
+        <v>0.054612</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>-0.005245901639344201</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1734,6 +2527,12 @@
       <c r="B131" s="1" t="n">
         <v>0.08165</v>
       </c>
+      <c r="C131" s="1" t="n">
+        <v>0.08137999999999999</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>-0.003306797305572643</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1744,6 +2543,12 @@
       <c r="B132" s="1" t="n">
         <v>0.0866</v>
       </c>
+      <c r="C132" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>-0.002309468822170807</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1754,6 +2559,12 @@
       <c r="B133" s="1" t="n">
         <v>0.578</v>
       </c>
+      <c r="C133" s="1" t="n">
+        <v>0.5783</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.000519031141868647</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1764,6 +2575,12 @@
       <c r="B134" s="1" t="n">
         <v>0.03065</v>
       </c>
+      <c r="C134" s="1" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>-0.006851549755301855</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1774,6 +2591,12 @@
       <c r="B135" s="1" t="n">
         <v>0.01764</v>
       </c>
+      <c r="C135" s="1" t="n">
+        <v>0.01766</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0.001133786848072516</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1784,6 +2607,12 @@
       <c r="B136" s="1" t="n">
         <v>0.03707</v>
       </c>
+      <c r="C136" s="1" t="n">
+        <v>0.03702</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>-0.001348799568384177</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1794,6 +2623,12 @@
       <c r="B137" s="1" t="n">
         <v>0.02685</v>
       </c>
+      <c r="C137" s="1" t="n">
+        <v>0.02684</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>-0.0003724394785847148</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1804,6 +2639,12 @@
       <c r="B138" s="1" t="n">
         <v>2.484</v>
       </c>
+      <c r="C138" s="1" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>-0.002012882447665013</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1814,6 +2655,12 @@
       <c r="B139" s="1" t="n">
         <v>0.01184</v>
       </c>
+      <c r="C139" s="1" t="n">
+        <v>0.01191</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>0.005912162162162215</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1824,6 +2671,12 @@
       <c r="B140" s="1" t="n">
         <v>0.0156</v>
       </c>
+      <c r="C140" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>-0.005769230769230757</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1834,6 +2687,12 @@
       <c r="B141" s="1" t="n">
         <v>16.004</v>
       </c>
+      <c r="C141" s="1" t="n">
+        <v>16.005</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>6.248437890512805e-05</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1844,6 +2703,12 @@
       <c r="B142" s="1" t="n">
         <v>0.0124</v>
       </c>
+      <c r="C142" s="1" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>0.001612903225806526</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1854,6 +2719,12 @@
       <c r="B143" s="1" t="n">
         <v>0.02641</v>
       </c>
+      <c r="C143" s="1" t="n">
+        <v>0.02637</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>-0.001514577811435001</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1864,6 +2735,12 @@
       <c r="B144" s="1" t="n">
         <v>0.004639</v>
       </c>
+      <c r="C144" s="1" t="n">
+        <v>0.004646</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>0.001508945893511546</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1874,6 +2751,12 @@
       <c r="B145" s="1" t="n">
         <v>1.9819</v>
       </c>
+      <c r="C145" s="1" t="n">
+        <v>1.9788</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>-0.001564155608254757</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1884,6 +2767,12 @@
       <c r="B146" s="1" t="n">
         <v>0.02285</v>
       </c>
+      <c r="C146" s="1" t="n">
+        <v>0.02279</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>-0.002625820568927683</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1894,6 +2783,12 @@
       <c r="B147" s="1" t="n">
         <v>0.08923</v>
       </c>
+      <c r="C147" s="1" t="n">
+        <v>0.08959</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>0.004034517538944292</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1904,6 +2799,12 @@
       <c r="B148" s="1" t="n">
         <v>0.05838</v>
       </c>
+      <c r="C148" s="1" t="n">
+        <v>0.05976</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>0.02363823227132578</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1914,6 +2815,12 @@
       <c r="B149" s="1" t="n">
         <v>0.05915</v>
       </c>
+      <c r="C149" s="1" t="n">
+        <v>0.05905</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>-0.001690617075232508</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1924,6 +2831,12 @@
       <c r="B150" s="1" t="n">
         <v>0.24963</v>
       </c>
+      <c r="C150" s="1" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>-0.005568240996675088</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1934,6 +2847,12 @@
       <c r="B151" s="1" t="n">
         <v>6.698e-05</v>
       </c>
+      <c r="C151" s="1" t="n">
+        <v>6.685999999999999e-05</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>-0.001791579575992918</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1944,6 +2863,12 @@
       <c r="B152" s="1" t="n">
         <v>0.4442</v>
       </c>
+      <c r="C152" s="1" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>-0.004502476361999103</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1954,6 +2879,12 @@
       <c r="B153" s="1" t="n">
         <v>0.3037</v>
       </c>
+      <c r="C153" s="1" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0.007902535396772992</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1964,6 +2895,12 @@
       <c r="B154" s="1" t="n">
         <v>0.3735</v>
       </c>
+      <c r="C154" s="1" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>-0.01793842034805886</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1974,6 +2911,12 @@
       <c r="B155" s="1" t="n">
         <v>0.2302</v>
       </c>
+      <c r="C155" s="1" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>0.0004344048653345645</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1984,6 +2927,12 @@
       <c r="B156" s="1" t="n">
         <v>0.08166</v>
       </c>
+      <c r="C156" s="1" t="n">
+        <v>0.08087</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>-0.009674259123193718</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -1994,6 +2943,12 @@
       <c r="B157" s="1" t="n">
         <v>0.22045</v>
       </c>
+      <c r="C157" s="1" t="n">
+        <v>0.22249</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>0.009253799047402977</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2004,6 +2959,12 @@
       <c r="B158" s="1" t="n">
         <v>0.249</v>
       </c>
+      <c r="C158" s="1" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>-0.004417670682730883</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2014,6 +2975,12 @@
       <c r="B159" s="1" t="n">
         <v>2.947</v>
       </c>
+      <c r="C159" s="1" t="n">
+        <v>2.939</v>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>-0.002714625042416019</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2024,6 +2991,12 @@
       <c r="B160" s="1" t="n">
         <v>0.1002</v>
       </c>
+      <c r="C160" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>-0.003992015968063849</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2034,6 +3007,12 @@
       <c r="B161" s="1" t="n">
         <v>0.14612</v>
       </c>
+      <c r="C161" s="1" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>-0.003558718861209914</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2044,6 +3023,12 @@
       <c r="B162" s="1" t="n">
         <v>0.003246</v>
       </c>
+      <c r="C162" s="1" t="n">
+        <v>0.003252</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>0.001848428835489812</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2054,6 +3039,12 @@
       <c r="B163" s="1" t="n">
         <v>0.004981</v>
       </c>
+      <c r="C163" s="1" t="n">
+        <v>0.004966</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>-0.003011443485243978</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2064,6 +3055,12 @@
       <c r="B164" s="1" t="n">
         <v>0.09520000000000001</v>
       </c>
+      <c r="C164" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>0.005252100840335993</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2074,6 +3071,12 @@
       <c r="B165" s="1" t="n">
         <v>0.3062</v>
       </c>
+      <c r="C165" s="1" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>-0.005225342913128823</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2084,6 +3087,12 @@
       <c r="B166" s="1" t="n">
         <v>1.3884</v>
       </c>
+      <c r="C166" s="1" t="n">
+        <v>1.3865</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>-0.001368481705560366</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2094,6 +3103,12 @@
       <c r="B167" s="1" t="n">
         <v>0.2767</v>
       </c>
+      <c r="C167" s="1" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>0.000722804481387705</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2104,6 +3119,12 @@
       <c r="B168" s="1" t="n">
         <v>0.315</v>
       </c>
+      <c r="C168" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>-0.006349206349206354</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2114,6 +3135,12 @@
       <c r="B169" s="1" t="n">
         <v>0.02945</v>
       </c>
+      <c r="C169" s="1" t="n">
+        <v>0.02937</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>-0.002716468590831926</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2124,6 +3151,12 @@
       <c r="B170" s="1" t="n">
         <v>0.04512</v>
       </c>
+      <c r="C170" s="1" t="n">
+        <v>0.04482</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>-0.006648936170212802</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2134,6 +3167,12 @@
       <c r="B171" s="1" t="n">
         <v>0.0166</v>
       </c>
+      <c r="C171" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>-0.006024096385542133</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2144,6 +3183,12 @@
       <c r="B172" s="1" t="n">
         <v>1.23e-05</v>
       </c>
+      <c r="C172" s="1" t="n">
+        <v>1.22e-05</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>-0.008130081300813068</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2154,6 +3199,12 @@
       <c r="B173" s="1" t="n">
         <v>0.02095</v>
       </c>
+      <c r="C173" s="1" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>-0.0009546539379474551</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2164,6 +3215,12 @@
       <c r="B174" s="1" t="n">
         <v>0.0888</v>
       </c>
+      <c r="C174" s="1" t="n">
+        <v>0.08918</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>0.004279279279279183</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2174,6 +3231,12 @@
       <c r="B175" s="1" t="n">
         <v>0.3598</v>
       </c>
+      <c r="C175" s="1" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>-0.002501389660922768</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2184,6 +3247,12 @@
       <c r="B176" s="1" t="n">
         <v>0.02146</v>
       </c>
+      <c r="C176" s="1" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>0.0009319664492077905</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2194,6 +3263,12 @@
       <c r="B177" s="1" t="n">
         <v>0.00792</v>
       </c>
+      <c r="C177" s="1" t="n">
+        <v>0.007939999999999999</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>0.002525252525252422</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2204,6 +3279,12 @@
       <c r="B178" s="1" t="n">
         <v>0.0009879999999999999</v>
       </c>
+      <c r="C178" s="1" t="n">
+        <v>0.0009829999999999999</v>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>-0.005060728744939285</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2214,6 +3295,12 @@
       <c r="B179" s="1" t="n">
         <v>0.022884</v>
       </c>
+      <c r="C179" s="1" t="n">
+        <v>0.022905</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>0.0009176717357103966</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2224,6 +3311,12 @@
       <c r="B180" s="1" t="n">
         <v>4.612</v>
       </c>
+      <c r="C180" s="1" t="n">
+        <v>4.504</v>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>-0.02341717259323516</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2234,6 +3327,12 @@
       <c r="B181" s="1" t="n">
         <v>0.5854</v>
       </c>
+      <c r="C181" s="1" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>-0.006149641270925944</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2244,6 +3343,12 @@
       <c r="B182" s="1" t="n">
         <v>0.04903</v>
       </c>
+      <c r="C182" s="1" t="n">
+        <v>0.04888</v>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>-0.003059351417499437</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2254,6 +3359,12 @@
       <c r="B183" s="1" t="n">
         <v>5.449</v>
       </c>
+      <c r="C183" s="1" t="n">
+        <v>5.437</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>-0.002202238942925228</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2264,6 +3375,12 @@
       <c r="B184" s="1" t="n">
         <v>28.44</v>
       </c>
+      <c r="C184" s="1" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>-0.001758087201125201</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2274,6 +3391,12 @@
       <c r="B185" s="1" t="n">
         <v>0.01868</v>
       </c>
+      <c r="C185" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>-0.02194860813704482</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2284,6 +3407,12 @@
       <c r="B186" s="1" t="n">
         <v>3.13e-05</v>
       </c>
+      <c r="C186" s="1" t="n">
+        <v>3.12e-05</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>-0.003194888178913816</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2294,6 +3423,12 @@
       <c r="B187" s="1" t="n">
         <v>0.01605</v>
       </c>
+      <c r="C187" s="1" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>-0.002492211838006129</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2304,6 +3439,12 @@
       <c r="B188" s="1" t="n">
         <v>0.0402</v>
       </c>
+      <c r="C188" s="1" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>0.0002487562189055488</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2314,6 +3455,12 @@
       <c r="B189" s="1" t="n">
         <v>0.0004356</v>
       </c>
+      <c r="C189" s="1" t="n">
+        <v>0.0004332</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>-0.005509641873278246</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2324,6 +3471,12 @@
       <c r="B190" s="1" t="n">
         <v>0.02313</v>
       </c>
+      <c r="C190" s="1" t="n">
+        <v>0.02299</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>-0.0060527453523563</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2334,6 +3487,12 @@
       <c r="B191" s="1" t="n">
         <v>0.01572</v>
       </c>
+      <c r="C191" s="1" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>0.001272264631043205</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2344,6 +3503,12 @@
       <c r="B192" s="1" t="n">
         <v>0.05565</v>
       </c>
+      <c r="C192" s="1" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>-0.0008984725965858299</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2354,6 +3519,12 @@
       <c r="B193" s="1" t="n">
         <v>0.1864</v>
       </c>
+      <c r="C193" s="1" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>-0.002145922746781177</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2364,6 +3535,12 @@
       <c r="B194" s="1" t="n">
         <v>0.01895</v>
       </c>
+      <c r="C194" s="1" t="n">
+        <v>0.01893</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>-0.001055408970976393</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2374,6 +3551,12 @@
       <c r="B195" s="1" t="n">
         <v>0.4342</v>
       </c>
+      <c r="C195" s="1" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>0.01658222017503464</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2384,6 +3567,12 @@
       <c r="B196" s="1" t="n">
         <v>0.01243</v>
       </c>
+      <c r="C196" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>0.004827031375703885</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2394,6 +3583,12 @@
       <c r="B197" s="1" t="n">
         <v>0.04542</v>
       </c>
+      <c r="C197" s="1" t="n">
+        <v>0.04531</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>-0.002421840598855108</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2404,6 +3599,12 @@
       <c r="B198" s="1" t="n">
         <v>0.5094</v>
       </c>
+      <c r="C198" s="1" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>0.004711425206124988</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2414,6 +3615,12 @@
       <c r="B199" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
+      <c r="C199" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2424,6 +3631,12 @@
       <c r="B200" s="1" t="n">
         <v>14.75</v>
       </c>
+      <c r="C200" s="1" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>-0.001355932203389802</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2434,6 +3647,12 @@
       <c r="B201" s="1" t="n">
         <v>0.00565</v>
       </c>
+      <c r="C201" s="1" t="n">
+        <v>0.005635</v>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>-0.00265486725663706</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2444,6 +3663,12 @@
       <c r="B202" s="1" t="n">
         <v>0.022918</v>
       </c>
+      <c r="C202" s="1" t="n">
+        <v>0.022771</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>-0.006414172266340923</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2454,6 +3679,12 @@
       <c r="B203" s="1" t="n">
         <v>0.0273</v>
       </c>
+      <c r="C203" s="1" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>0.007326007326007281</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2464,6 +3695,12 @@
       <c r="B204" s="1" t="n">
         <v>0.03423</v>
       </c>
+      <c r="C204" s="1" t="n">
+        <v>0.03412</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>-0.003213555360794595</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2474,6 +3711,12 @@
       <c r="B205" s="1" t="n">
         <v>4.268</v>
       </c>
+      <c r="C205" s="1" t="n">
+        <v>4.263</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>-0.001171508903467641</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2484,6 +3727,12 @@
       <c r="B206" s="1" t="n">
         <v>0.36</v>
       </c>
+      <c r="C206" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2494,6 +3743,12 @@
       <c r="B207" s="1" t="n">
         <v>0.0009463</v>
       </c>
+      <c r="C207" s="1" t="n">
+        <v>0.0009578</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>0.01215259431469936</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2504,6 +3759,12 @@
       <c r="B208" s="1" t="n">
         <v>0.007335</v>
       </c>
+      <c r="C208" s="1" t="n">
+        <v>0.007318</v>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>-0.002317655078391346</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2514,6 +3775,12 @@
       <c r="B209" s="1" t="n">
         <v>0.06</v>
       </c>
+      <c r="C209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>-0.003333333333333313</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2524,6 +3791,12 @@
       <c r="B210" s="1" t="n">
         <v>0.1291</v>
       </c>
+      <c r="C210" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>-0.0007745933384972036</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2534,6 +3807,12 @@
       <c r="B211" s="1" t="n">
         <v>0.007074</v>
       </c>
+      <c r="C211" s="1" t="n">
+        <v>0.007055</v>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>-0.002685891998869209</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2544,6 +3823,12 @@
       <c r="B212" s="1" t="n">
         <v>0.275</v>
       </c>
+      <c r="C212" s="1" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>0.01418181818181803</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2554,6 +3839,12 @@
       <c r="B213" s="1" t="n">
         <v>0.05788</v>
       </c>
+      <c r="C213" s="1" t="n">
+        <v>0.05809</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>0.003628196268141013</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2564,6 +3855,12 @@
       <c r="B214" s="1" t="n">
         <v>0.1878</v>
       </c>
+      <c r="C214" s="1" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>0.00106496272630461</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2574,6 +3871,12 @@
       <c r="B215" s="1" t="n">
         <v>0.05231</v>
       </c>
+      <c r="C215" s="1" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>-0.003441024660676727</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2584,6 +3887,12 @@
       <c r="B216" s="1" t="n">
         <v>0.002098</v>
       </c>
+      <c r="C216" s="1" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>-0.003813155386082076</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2594,6 +3903,12 @@
       <c r="B217" s="1" t="n">
         <v>5.994</v>
       </c>
+      <c r="C217" s="1" t="n">
+        <v>5.987</v>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>-0.00116783450116778</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2604,6 +3919,12 @@
       <c r="B218" s="1" t="n">
         <v>4.47</v>
       </c>
+      <c r="C218" s="1" t="n">
+        <v>4.458</v>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>-0.002684563758389165</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2614,6 +3935,12 @@
       <c r="B219" s="1" t="n">
         <v>0.005335</v>
       </c>
+      <c r="C219" s="1" t="n">
+        <v>0.005347</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>0.002249297094657893</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2624,6 +3951,12 @@
       <c r="B220" s="1" t="n">
         <v>0.04097</v>
       </c>
+      <c r="C220" s="1" t="n">
+        <v>0.04106</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>0.002196729314132287</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2634,6 +3967,12 @@
       <c r="B221" s="1" t="n">
         <v>0.005747</v>
       </c>
+      <c r="C221" s="1" t="n">
+        <v>0.005739</v>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>-0.001392030624673777</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2644,6 +3983,12 @@
       <c r="B222" s="1" t="n">
         <v>0.0905</v>
       </c>
+      <c r="C222" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>-0.002209944751381125</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2654,6 +3999,12 @@
       <c r="B223" s="1" t="n">
         <v>0.3372</v>
       </c>
+      <c r="C223" s="1" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>-0.0008896797153025577</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2664,6 +4015,12 @@
       <c r="B224" s="1" t="n">
         <v>0.4325</v>
       </c>
+      <c r="C224" s="1" t="n">
+        <v>0.4309</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>-0.003699421965317897</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2674,6 +4031,12 @@
       <c r="B225" s="1" t="n">
         <v>0.08319</v>
       </c>
+      <c r="C225" s="1" t="n">
+        <v>0.08316</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>-0.0003606202668590245</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2684,6 +4047,12 @@
       <c r="B226" s="1" t="n">
         <v>0.01903</v>
       </c>
+      <c r="C226" s="1" t="n">
+        <v>0.01884</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>-0.009984235417761387</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2694,6 +4063,12 @@
       <c r="B227" s="1" t="n">
         <v>0.04648</v>
       </c>
+      <c r="C227" s="1" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="D227" s="2" t="n">
+        <v>-0.002796901893287396</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2704,6 +4079,12 @@
       <c r="B228" s="1" t="n">
         <v>0.02322</v>
       </c>
+      <c r="C228" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>-0.0008613264427219058</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2714,6 +4095,12 @@
       <c r="B229" s="1" t="n">
         <v>0.1067</v>
       </c>
+      <c r="C229" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2724,6 +4111,12 @@
       <c r="B230" s="1" t="n">
         <v>0.1662</v>
       </c>
+      <c r="C230" s="1" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>0.004211793020457318</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2734,6 +4127,12 @@
       <c r="B231" s="1" t="n">
         <v>0.03045</v>
       </c>
+      <c r="C231" s="1" t="n">
+        <v>0.03046</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>0.0003284072249589357</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2744,6 +4143,12 @@
       <c r="B232" s="1" t="n">
         <v>0.02313</v>
       </c>
+      <c r="C232" s="1" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>0.0008646779074794286</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2754,6 +4159,12 @@
       <c r="B233" s="1" t="n">
         <v>0.13281</v>
       </c>
+      <c r="C233" s="1" t="n">
+        <v>0.12351</v>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>-0.0700248475265418</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2764,6 +4175,12 @@
       <c r="B234" s="1" t="n">
         <v>0.2516</v>
       </c>
+      <c r="C234" s="1" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>-0.002384737678855284</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2774,6 +4191,12 @@
       <c r="B235" s="1" t="n">
         <v>0.06893000000000001</v>
       </c>
+      <c r="C235" s="1" t="n">
+        <v>0.06887</v>
+      </c>
+      <c r="D235" s="2" t="n">
+        <v>-0.0008704482808647104</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2784,6 +4207,12 @@
       <c r="B236" s="1" t="n">
         <v>0.12284</v>
       </c>
+      <c r="C236" s="1" t="n">
+        <v>0.12202</v>
+      </c>
+      <c r="D236" s="2" t="n">
+        <v>-0.006675350048844035</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2794,6 +4223,12 @@
       <c r="B237" s="1" t="n">
         <v>0.03754</v>
       </c>
+      <c r="C237" s="1" t="n">
+        <v>0.03736</v>
+      </c>
+      <c r="D237" s="2" t="n">
+        <v>-0.004794885455514108</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2804,6 +4239,12 @@
       <c r="B238" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="C238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2814,6 +4255,12 @@
       <c r="B239" s="1" t="n">
         <v>0.004011</v>
       </c>
+      <c r="C239" s="1" t="n">
+        <v>0.003985</v>
+      </c>
+      <c r="D239" s="2" t="n">
+        <v>-0.006482174021441033</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2824,6 +4271,12 @@
       <c r="B240" s="1" t="n">
         <v>0.01369</v>
       </c>
+      <c r="C240" s="1" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>0.0007304601899196196</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2834,6 +4287,12 @@
       <c r="B241" s="1" t="n">
         <v>0.4283</v>
       </c>
+      <c r="C241" s="1" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="D241" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2844,6 +4303,12 @@
       <c r="B242" s="1" t="n">
         <v>0.00735</v>
       </c>
+      <c r="C242" s="1" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>-0.004081632653061176</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -2854,6 +4319,12 @@
       <c r="B243" s="1" t="n">
         <v>0.023</v>
       </c>
+      <c r="C243" s="1" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>-0.004347826086956496</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -2864,6 +4335,12 @@
       <c r="B244" s="1" t="n">
         <v>0.001661</v>
       </c>
+      <c r="C244" s="1" t="n">
+        <v>0.001667</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>0.00361228175797721</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -2874,6 +4351,12 @@
       <c r="B245" s="1" t="n">
         <v>0.1313</v>
       </c>
+      <c r="C245" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>-0.0007616146230006777</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -2884,6 +4367,12 @@
       <c r="B246" s="1" t="n">
         <v>0.03144</v>
       </c>
+      <c r="C246" s="1" t="n">
+        <v>0.03156</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>0.003816793893129615</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -2894,6 +4383,12 @@
       <c r="B247" s="1" t="n">
         <v>0.1787</v>
       </c>
+      <c r="C247" s="1" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>-0.00615556799104639</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -2904,6 +4399,12 @@
       <c r="B248" s="1" t="n">
         <v>0.03037</v>
       </c>
+      <c r="C248" s="1" t="n">
+        <v>0.03054</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>0.005597629239380968</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -2914,6 +4415,12 @@
       <c r="B249" s="1" t="n">
         <v>0.008632000000000001</v>
       </c>
+      <c r="C249" s="1" t="n">
+        <v>0.008571</v>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>-0.007066728452270654</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -2924,6 +4431,12 @@
       <c r="B250" s="1" t="n">
         <v>0.02071</v>
       </c>
+      <c r="C250" s="1" t="n">
+        <v>0.02072</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>0.0004828585224529017</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -2934,6 +4447,12 @@
       <c r="B251" s="1" t="n">
         <v>0.04687</v>
       </c>
+      <c r="C251" s="1" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>-0.001066780456582066</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -2944,6 +4463,12 @@
       <c r="B252" s="1" t="n">
         <v>0.008345999999999999</v>
       </c>
+      <c r="C252" s="1" t="n">
+        <v>0.00831</v>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>-0.004313443565779964</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -2954,6 +4479,12 @@
       <c r="B253" s="1" t="n">
         <v>0.03979</v>
       </c>
+      <c r="C253" s="1" t="n">
+        <v>0.03946</v>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>-0.008293541090726237</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -2964,6 +4495,12 @@
       <c r="B254" s="1" t="n">
         <v>0.06082</v>
       </c>
+      <c r="C254" s="1" t="n">
+        <v>0.06089</v>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>0.001150937191713262</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -2974,6 +4511,12 @@
       <c r="B255" s="1" t="n">
         <v>0.003509</v>
       </c>
+      <c r="C255" s="1" t="n">
+        <v>0.003557</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>0.0136791108577942</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -2984,6 +4527,12 @@
       <c r="B256" s="1" t="n">
         <v>0.012985</v>
       </c>
+      <c r="C256" s="1" t="n">
+        <v>0.013126</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>0.0108586830958799</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -2994,6 +4543,12 @@
       <c r="B257" s="1" t="n">
         <v>0.999374</v>
       </c>
+      <c r="C257" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="D257" s="2" t="n">
+        <v>-1.000626392150242e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3004,6 +4559,12 @@
       <c r="B258" s="1" t="n">
         <v>0.08649999999999999</v>
       </c>
+      <c r="C258" s="1" t="n">
+        <v>0.08643000000000001</v>
+      </c>
+      <c r="D258" s="2" t="n">
+        <v>-0.0008092485549131415</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3014,6 +4575,12 @@
       <c r="B259" s="1" t="n">
         <v>0.08862</v>
       </c>
+      <c r="C259" s="1" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>0.0009027307605506289</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3024,6 +4591,12 @@
       <c r="B260" s="1" t="n">
         <v>0.08114</v>
       </c>
+      <c r="C260" s="1" t="n">
+        <v>0.08132</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>0.002218387971407439</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3034,6 +4607,12 @@
       <c r="B261" s="1" t="n">
         <v>1.116</v>
       </c>
+      <c r="C261" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>0.005376344086021509</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3044,6 +4623,12 @@
       <c r="B262" s="1" t="n">
         <v>0.003655</v>
       </c>
+      <c r="C262" s="1" t="n">
+        <v>0.003638</v>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>-0.00465116279069758</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3054,6 +4639,12 @@
       <c r="B263" s="1" t="n">
         <v>0.1155</v>
       </c>
+      <c r="C263" s="1" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>0.009523809523809436</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3064,6 +4655,12 @@
       <c r="B264" s="1" t="n">
         <v>0.0005728</v>
       </c>
+      <c r="C264" s="1" t="n">
+        <v>0.0005705</v>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>-0.004015363128491623</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3074,6 +4671,12 @@
       <c r="B265" s="1" t="n">
         <v>0.01496</v>
       </c>
+      <c r="C265" s="1" t="n">
+        <v>0.01496</v>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3084,6 +4687,12 @@
       <c r="B266" s="1" t="n">
         <v>0.0635</v>
       </c>
+      <c r="C266" s="1" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>-0.001574803149606344</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3094,6 +4703,12 @@
       <c r="B267" s="1" t="n">
         <v>0.01648</v>
       </c>
+      <c r="C267" s="1" t="n">
+        <v>0.01648</v>
+      </c>
+      <c r="D267" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3104,6 +4719,12 @@
       <c r="B268" s="1" t="n">
         <v>0.0004267</v>
       </c>
+      <c r="C268" s="1" t="n">
+        <v>0.0004266</v>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>-0.0002343566908835304</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3114,6 +4735,12 @@
       <c r="B269" s="1" t="n">
         <v>0.02086</v>
       </c>
+      <c r="C269" s="1" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>-0.00479386385426651</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3124,6 +4751,12 @@
       <c r="B270" s="1" t="n">
         <v>0.18</v>
       </c>
+      <c r="C270" s="1" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="D270" s="2" t="n">
+        <v>-0.00277777777777778</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3134,6 +4767,12 @@
       <c r="B271" s="1" t="n">
         <v>0.1471</v>
       </c>
+      <c r="C271" s="1" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>-0.003399048266485387</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3144,6 +4783,12 @@
       <c r="B272" s="1" t="n">
         <v>0.03946</v>
       </c>
+      <c r="C272" s="1" t="n">
+        <v>0.03943</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>-0.0007602635580335085</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3154,6 +4799,12 @@
       <c r="B273" s="1" t="n">
         <v>0.925</v>
       </c>
+      <c r="C273" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>0.001081081081081082</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3164,6 +4815,12 @@
       <c r="B274" s="1" t="n">
         <v>63.02</v>
       </c>
+      <c r="C274" s="1" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>-0.0007933989209775351</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3174,6 +4831,12 @@
       <c r="B275" s="1" t="n">
         <v>0.01153</v>
       </c>
+      <c r="C275" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="D275" s="2" t="n">
+        <v>-0.001734605377276749</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3184,6 +4847,12 @@
       <c r="B276" s="1" t="n">
         <v>2.584</v>
       </c>
+      <c r="C276" s="1" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="D276" s="2" t="n">
+        <v>-0.0003869969040247252</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3194,6 +4863,12 @@
       <c r="B277" s="1" t="n">
         <v>0.04171</v>
       </c>
+      <c r="C277" s="1" t="n">
+        <v>0.04177</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>0.001438503955885987</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3204,6 +4879,12 @@
       <c r="B278" s="1" t="n">
         <v>0.01888</v>
       </c>
+      <c r="C278" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="D278" s="2" t="n">
+        <v>-0.003177966101694969</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3214,6 +4895,12 @@
       <c r="B279" s="1" t="n">
         <v>0.005704</v>
       </c>
+      <c r="C279" s="1" t="n">
+        <v>0.005605</v>
+      </c>
+      <c r="D279" s="2" t="n">
+        <v>-0.01735624123422162</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3224,6 +4911,12 @@
       <c r="B280" s="1" t="n">
         <v>0.03765</v>
       </c>
+      <c r="C280" s="1" t="n">
+        <v>0.03778</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>0.003452855245683882</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3234,6 +4927,12 @@
       <c r="B281" s="1" t="n">
         <v>0.901</v>
       </c>
+      <c r="C281" s="1" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>0.001109877913429524</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3244,6 +4943,12 @@
       <c r="B282" s="1" t="n">
         <v>0.0003985</v>
       </c>
+      <c r="C282" s="1" t="n">
+        <v>0.000399</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>0.001254705144291122</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3254,6 +4959,12 @@
       <c r="B283" s="1" t="n">
         <v>0.03898</v>
       </c>
+      <c r="C283" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>0.02616726526423807</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3264,6 +4975,12 @@
       <c r="B284" s="1" t="n">
         <v>0.0418</v>
       </c>
+      <c r="C284" s="1" t="n">
+        <v>0.04163</v>
+      </c>
+      <c r="D284" s="2" t="n">
+        <v>-0.004066985645932932</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3274,6 +4991,12 @@
       <c r="B285" s="1" t="n">
         <v>0.10711</v>
       </c>
+      <c r="C285" s="1" t="n">
+        <v>0.10749</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>0.003547754644757776</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3284,6 +5007,12 @@
       <c r="B286" s="1" t="n">
         <v>0.00415</v>
       </c>
+      <c r="C286" s="1" t="n">
+        <v>0.00415</v>
+      </c>
+      <c r="D286" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3294,6 +5023,12 @@
       <c r="B287" s="1" t="n">
         <v>0.15199</v>
       </c>
+      <c r="C287" s="1" t="n">
+        <v>0.15094</v>
+      </c>
+      <c r="D287" s="2" t="n">
+        <v>-0.006908349233502174</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3304,6 +5039,12 @@
       <c r="B288" s="1" t="n">
         <v>0.182</v>
       </c>
+      <c r="C288" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>0.004395604395604369</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3314,6 +5055,12 @@
       <c r="B289" s="1" t="n">
         <v>4.102</v>
       </c>
+      <c r="C289" s="1" t="n">
+        <v>4.103</v>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>0.0002437835202338971</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3324,6 +5071,12 @@
       <c r="B290" s="1" t="n">
         <v>0.08495999999999999</v>
       </c>
+      <c r="C290" s="1" t="n">
+        <v>0.08464000000000001</v>
+      </c>
+      <c r="D290" s="2" t="n">
+        <v>-0.003766478342749376</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3334,6 +5087,12 @@
       <c r="B291" s="1" t="n">
         <v>0.03522</v>
       </c>
+      <c r="C291" s="1" t="n">
+        <v>0.03528</v>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>0.001703577512776762</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3344,6 +5103,12 @@
       <c r="B292" s="1" t="n">
         <v>1.464</v>
       </c>
+      <c r="C292" s="1" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>0.003415300546448166</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3354,6 +5119,12 @@
       <c r="B293" s="1" t="n">
         <v>0.005822</v>
       </c>
+      <c r="C293" s="1" t="n">
+        <v>0.005825</v>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>0.0005152868430093435</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3364,6 +5135,12 @@
       <c r="B294" s="1" t="n">
         <v>0.003435</v>
       </c>
+      <c r="C294" s="1" t="n">
+        <v>0.003433</v>
+      </c>
+      <c r="D294" s="2" t="n">
+        <v>-0.000582241630276642</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3374,6 +5151,12 @@
       <c r="B295" s="1" t="n">
         <v>0.5381</v>
       </c>
+      <c r="C295" s="1" t="n">
+        <v>0.5357</v>
+      </c>
+      <c r="D295" s="2" t="n">
+        <v>-0.004460137520907022</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3384,6 +5167,12 @@
       <c r="B296" s="1" t="n">
         <v>2.245</v>
       </c>
+      <c r="C296" s="1" t="n">
+        <v>2.239</v>
+      </c>
+      <c r="D296" s="2" t="n">
+        <v>-0.002672605790645981</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3394,6 +5183,12 @@
       <c r="B297" s="1" t="n">
         <v>0.01707</v>
       </c>
+      <c r="C297" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="D297" s="2" t="n">
+        <v>-0.004100761570005692</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3404,6 +5199,12 @@
       <c r="B298" s="1" t="n">
         <v>0.3601</v>
       </c>
+      <c r="C298" s="1" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>0.007220216606498325</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3414,6 +5215,12 @@
       <c r="B299" s="1" t="n">
         <v>0.01103</v>
       </c>
+      <c r="C299" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>0.0009066183136898996</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -3424,6 +5231,12 @@
       <c r="B300" s="1" t="n">
         <v>0.02076</v>
       </c>
+      <c r="C300" s="1" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>-0.002890173410404674</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -3434,6 +5247,12 @@
       <c r="B301" s="1" t="n">
         <v>0.2991</v>
       </c>
+      <c r="C301" s="1" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>0.009695753928452068</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -3444,6 +5263,12 @@
       <c r="B302" s="1" t="n">
         <v>0.01355</v>
       </c>
+      <c r="C302" s="1" t="n">
+        <v>0.01352</v>
+      </c>
+      <c r="D302" s="2" t="n">
+        <v>-0.002214022140221312</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -3454,6 +5279,12 @@
       <c r="B303" s="1" t="n">
         <v>0.07377</v>
       </c>
+      <c r="C303" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>0.003117798563101452</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -3464,6 +5295,12 @@
       <c r="B304" s="1" t="n">
         <v>0.01591</v>
       </c>
+      <c r="C304" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="D304" s="2" t="n">
+        <v>-0.001885606536769469</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -3474,6 +5311,12 @@
       <c r="B305" s="1" t="n">
         <v>0.06525</v>
       </c>
+      <c r="C305" s="1" t="n">
+        <v>0.06517000000000001</v>
+      </c>
+      <c r="D305" s="2" t="n">
+        <v>-0.001226053639846693</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -3484,6 +5327,12 @@
       <c r="B306" s="1" t="n">
         <v>0.04982</v>
       </c>
+      <c r="C306" s="1" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>0.001204335608189433</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -3494,6 +5343,12 @@
       <c r="B307" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
+      <c r="C307" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D307" s="2" t="n">
+        <v>-0.005347593582887705</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -3504,6 +5359,12 @@
       <c r="B308" s="1" t="n">
         <v>0.03937</v>
       </c>
+      <c r="C308" s="1" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>0.0005080010160020112</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -3514,6 +5375,12 @@
       <c r="B309" s="1" t="n">
         <v>0.01584</v>
       </c>
+      <c r="C309" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>0.007575757575757486</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -3524,6 +5391,12 @@
       <c r="B310" s="1" t="n">
         <v>0.05401</v>
       </c>
+      <c r="C310" s="1" t="n">
+        <v>0.05397</v>
+      </c>
+      <c r="D310" s="2" t="n">
+        <v>-0.0007406035919275191</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -3534,6 +5407,12 @@
       <c r="B311" s="1" t="n">
         <v>0.004451</v>
       </c>
+      <c r="C311" s="1" t="n">
+        <v>0.004473</v>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>0.004942709503482435</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -3544,6 +5423,12 @@
       <c r="B312" s="1" t="n">
         <v>0.08425000000000001</v>
       </c>
+      <c r="C312" s="1" t="n">
+        <v>0.08394</v>
+      </c>
+      <c r="D312" s="2" t="n">
+        <v>-0.003679525222551985</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -3554,6 +5439,12 @@
       <c r="B313" s="1" t="n">
         <v>0.07431</v>
       </c>
+      <c r="C313" s="1" t="n">
+        <v>0.07436</v>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>0.0006728569506122258</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -3564,6 +5455,12 @@
       <c r="B314" s="1" t="n">
         <v>0.1527</v>
       </c>
+      <c r="C314" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -3574,6 +5471,12 @@
       <c r="B315" s="1" t="n">
         <v>0.1598</v>
       </c>
+      <c r="C315" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="D315" s="2" t="n">
+        <v>-0.003128911138923658</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -3584,6 +5487,12 @@
       <c r="B316" s="1" t="n">
         <v>0.1797</v>
       </c>
+      <c r="C316" s="1" t="n">
+        <v>0.1797</v>
+      </c>
+      <c r="D316" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -3594,6 +5503,12 @@
       <c r="B317" s="1" t="n">
         <v>0.007524</v>
       </c>
+      <c r="C317" s="1" t="n">
+        <v>0.007512</v>
+      </c>
+      <c r="D317" s="2" t="n">
+        <v>-0.001594896331738533</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -3604,6 +5519,12 @@
       <c r="B318" s="1" t="n">
         <v>0.04988</v>
       </c>
+      <c r="C318" s="1" t="n">
+        <v>0.04996</v>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>0.001603849238171547</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -3614,6 +5535,12 @@
       <c r="B319" s="1" t="n">
         <v>0.28018</v>
       </c>
+      <c r="C319" s="1" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>0.001284888286101888</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -3624,6 +5551,12 @@
       <c r="B320" s="1" t="n">
         <v>0.4381</v>
       </c>
+      <c r="C320" s="1" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="D320" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -3634,6 +5567,12 @@
       <c r="B321" s="1" t="n">
         <v>0.07686999999999999</v>
       </c>
+      <c r="C321" s="1" t="n">
+        <v>0.07659000000000001</v>
+      </c>
+      <c r="D321" s="2" t="n">
+        <v>-0.00364251333420045</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -3644,6 +5583,12 @@
       <c r="B322" s="1" t="n">
         <v>0.1615</v>
       </c>
+      <c r="C322" s="1" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="D322" s="3" t="n">
+        <v>0.003095975232198145</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -3654,6 +5599,12 @@
       <c r="B323" s="1" t="n">
         <v>1.987</v>
       </c>
+      <c r="C323" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D323" s="2" t="n">
+        <v>-0.003522898842476154</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -3664,6 +5615,12 @@
       <c r="B324" s="1" t="n">
         <v>0.052698</v>
       </c>
+      <c r="C324" s="1" t="n">
+        <v>0.052768</v>
+      </c>
+      <c r="D324" s="3" t="n">
+        <v>0.001328323655546712</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -3674,6 +5631,12 @@
       <c r="B325" s="1" t="n">
         <v>0.15275</v>
       </c>
+      <c r="C325" s="1" t="n">
+        <v>0.15292</v>
+      </c>
+      <c r="D325" s="3" t="n">
+        <v>0.001112929623567944</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -3684,6 +5647,12 @@
       <c r="B326" s="1" t="n">
         <v>0.006546</v>
       </c>
+      <c r="C326" s="1" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="D326" s="2" t="n">
+        <v>-0.0009165902841429773</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -3694,6 +5663,12 @@
       <c r="B327" s="1" t="n">
         <v>0.01512</v>
       </c>
+      <c r="C327" s="1" t="n">
+        <v>0.015105</v>
+      </c>
+      <c r="D327" s="2" t="n">
+        <v>-0.0009920634920634517</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -3704,6 +5679,12 @@
       <c r="B328" s="1" t="n">
         <v>0.09379999999999999</v>
       </c>
+      <c r="C328" s="1" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="D328" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -3714,6 +5695,12 @@
       <c r="B329" s="1" t="n">
         <v>0.0044</v>
       </c>
+      <c r="C329" s="1" t="n">
+        <v>0.004381</v>
+      </c>
+      <c r="D329" s="2" t="n">
+        <v>-0.0043181818181818</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -3724,6 +5711,12 @@
       <c r="B330" s="1" t="n">
         <v>0.05152</v>
       </c>
+      <c r="C330" s="1" t="n">
+        <v>0.05132</v>
+      </c>
+      <c r="D330" s="2" t="n">
+        <v>-0.003881987577639863</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -3734,6 +5727,12 @@
       <c r="B331" s="1" t="n">
         <v>0.03621</v>
       </c>
+      <c r="C331" s="1" t="n">
+        <v>0.03621</v>
+      </c>
+      <c r="D331" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -3744,6 +5743,12 @@
       <c r="B332" s="1" t="n">
         <v>0.1482</v>
       </c>
+      <c r="C332" s="1" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="D332" s="2" t="n">
+        <v>-0.007422402159244197</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -3754,6 +5759,12 @@
       <c r="B333" s="1" t="n">
         <v>0.0963</v>
       </c>
+      <c r="C333" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>-0.004153686396677026</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -3764,6 +5775,12 @@
       <c r="B334" s="1" t="n">
         <v>0.04349</v>
       </c>
+      <c r="C334" s="1" t="n">
+        <v>0.04316</v>
+      </c>
+      <c r="D334" s="2" t="n">
+        <v>-0.007587951253161736</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -3774,6 +5791,12 @@
       <c r="B335" s="1" t="n">
         <v>0.08083</v>
       </c>
+      <c r="C335" s="1" t="n">
+        <v>0.08092000000000001</v>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>0.001113447977236258</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -3784,6 +5807,12 @@
       <c r="B336" s="1" t="n">
         <v>0.2038</v>
       </c>
+      <c r="C336" s="1" t="n">
+        <v>0.2034</v>
+      </c>
+      <c r="D336" s="2" t="n">
+        <v>-0.001962708537782196</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -3794,6 +5823,12 @@
       <c r="B337" s="1" t="n">
         <v>0.01013</v>
       </c>
+      <c r="C337" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>0.001974333662388863</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -3804,6 +5839,12 @@
       <c r="B338" s="1" t="n">
         <v>0.1129</v>
       </c>
+      <c r="C338" s="1" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="D338" s="2" t="n">
+        <v>-0.001771479185119626</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -3814,6 +5855,12 @@
       <c r="B339" s="1" t="n">
         <v>0.01842</v>
       </c>
+      <c r="C339" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="D339" s="2" t="n">
+        <v>-0.005428881650379989</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -3824,6 +5871,12 @@
       <c r="B340" s="1" t="n">
         <v>0.28667</v>
       </c>
+      <c r="C340" s="1" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="D340" s="2" t="n">
+        <v>-0.004918547458750365</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -3834,6 +5887,12 @@
       <c r="B341" s="1" t="n">
         <v>0.0434</v>
       </c>
+      <c r="C341" s="1" t="n">
+        <v>0.04422</v>
+      </c>
+      <c r="D341" s="3" t="n">
+        <v>0.01889400921658989</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -3844,6 +5903,12 @@
       <c r="B342" s="1" t="n">
         <v>0.07842</v>
       </c>
+      <c r="C342" s="1" t="n">
+        <v>0.07846</v>
+      </c>
+      <c r="D342" s="3" t="n">
+        <v>0.0005100739607242842</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -3854,6 +5919,12 @@
       <c r="B343" s="1" t="n">
         <v>7.629</v>
       </c>
+      <c r="C343" s="1" t="n">
+        <v>7.616</v>
+      </c>
+      <c r="D343" s="2" t="n">
+        <v>-0.001704024118495203</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -3864,6 +5935,12 @@
       <c r="B344" s="1" t="n">
         <v>0.6036</v>
       </c>
+      <c r="C344" s="1" t="n">
+        <v>0.6016</v>
+      </c>
+      <c r="D344" s="2" t="n">
+        <v>-0.003313452617627571</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -3874,6 +5951,12 @@
       <c r="B345" s="1" t="n">
         <v>0.0369</v>
       </c>
+      <c r="C345" s="1" t="n">
+        <v>0.03676</v>
+      </c>
+      <c r="D345" s="2" t="n">
+        <v>-0.003794037940379437</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -3884,6 +5967,12 @@
       <c r="B346" s="1" t="n">
         <v>0.0412</v>
       </c>
+      <c r="C346" s="1" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="D346" s="2" t="n">
+        <v>-0.002427184466019487</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -3894,6 +5983,12 @@
       <c r="B347" s="1" t="n">
         <v>0.173</v>
       </c>
+      <c r="C347" s="1" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="D347" s="2" t="n">
+        <v>-0.001156069364161722</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -3904,6 +5999,12 @@
       <c r="B348" s="1" t="n">
         <v>5187.6</v>
       </c>
+      <c r="C348" s="1" t="n">
+        <v>5190.6</v>
+      </c>
+      <c r="D348" s="3" t="n">
+        <v>0.0005783021050196623</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -3914,6 +6015,12 @@
       <c r="B349" s="1" t="n">
         <v>0.0135</v>
       </c>
+      <c r="C349" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="D349" s="2" t="n">
+        <v>-0.006666666666666652</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -3924,6 +6031,12 @@
       <c r="B350" s="1" t="n">
         <v>0.01492</v>
       </c>
+      <c r="C350" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="D350" s="2" t="n">
+        <v>-0.00201072386058973</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -3934,6 +6047,12 @@
       <c r="B351" s="1" t="n">
         <v>0.0006058</v>
       </c>
+      <c r="C351" s="1" t="n">
+        <v>0.0006022</v>
+      </c>
+      <c r="D351" s="2" t="n">
+        <v>-0.005942555298778441</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -3944,6 +6063,12 @@
       <c r="B352" s="1" t="n">
         <v>0.01966</v>
       </c>
+      <c r="C352" s="1" t="n">
+        <v>0.01964</v>
+      </c>
+      <c r="D352" s="2" t="n">
+        <v>-0.001017293997965371</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -3954,6 +6079,12 @@
       <c r="B353" s="1" t="n">
         <v>0.09320000000000001</v>
       </c>
+      <c r="C353" s="1" t="n">
+        <v>0.09368</v>
+      </c>
+      <c r="D353" s="3" t="n">
+        <v>0.005150214592274617</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -3964,6 +6095,12 @@
       <c r="B354" s="1" t="n">
         <v>0.0902</v>
       </c>
+      <c r="C354" s="1" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="D354" s="3" t="n">
+        <v>0.002217294900221639</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -3974,6 +6111,12 @@
       <c r="B355" s="1" t="n">
         <v>0.0005999999999999999</v>
       </c>
+      <c r="C355" s="1" t="n">
+        <v>0.0005997</v>
+      </c>
+      <c r="D355" s="2" t="n">
+        <v>-0.0004999999999999218</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -3984,6 +6127,12 @@
       <c r="B356" s="1" t="n">
         <v>2.085</v>
       </c>
+      <c r="C356" s="1" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="D356" s="2" t="n">
+        <v>-0.002877697841726515</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -3994,6 +6143,12 @@
       <c r="B357" s="1" t="n">
         <v>0.02328</v>
       </c>
+      <c r="C357" s="1" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="D357" s="3" t="n">
+        <v>0.00257731958762891</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4004,6 +6159,12 @@
       <c r="B358" s="1" t="n">
         <v>0.000406</v>
       </c>
+      <c r="C358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="D358" s="2" t="n">
+        <v>-0.002463054187192178</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4014,6 +6175,12 @@
       <c r="B359" s="1" t="n">
         <v>0.01459</v>
       </c>
+      <c r="C359" s="1" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="D359" s="2" t="n">
+        <v>-0.00137080191912275</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4024,6 +6191,12 @@
       <c r="B360" s="1" t="n">
         <v>0.003368</v>
       </c>
+      <c r="C360" s="1" t="n">
+        <v>0.003372</v>
+      </c>
+      <c r="D360" s="3" t="n">
+        <v>0.001187648456057036</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -4034,6 +6207,12 @@
       <c r="B361" s="1" t="n">
         <v>0.6392</v>
       </c>
+      <c r="C361" s="1" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="D361" s="3" t="n">
+        <v>0.00797872340425531</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -4044,6 +6223,12 @@
       <c r="B362" s="1" t="n">
         <v>0.02324</v>
       </c>
+      <c r="C362" s="1" t="n">
+        <v>0.02339</v>
+      </c>
+      <c r="D362" s="3" t="n">
+        <v>0.006454388984509502</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -4054,6 +6239,12 @@
       <c r="B363" s="1" t="n">
         <v>0.06532</v>
       </c>
+      <c r="C363" s="1" t="n">
+        <v>0.06542000000000001</v>
+      </c>
+      <c r="D363" s="3" t="n">
+        <v>0.001530924678505861</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -4064,6 +6255,12 @@
       <c r="B364" s="1" t="n">
         <v>4.691</v>
       </c>
+      <c r="C364" s="1" t="n">
+        <v>4.702</v>
+      </c>
+      <c r="D364" s="3" t="n">
+        <v>0.002344915796205526</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -4074,6 +6271,12 @@
       <c r="B365" s="1" t="n">
         <v>0.07095</v>
       </c>
+      <c r="C365" s="1" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="D365" s="3" t="n">
+        <v>0.003523608174770969</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -4084,6 +6287,12 @@
       <c r="B366" s="1" t="n">
         <v>0.05494</v>
       </c>
+      <c r="C366" s="1" t="n">
+        <v>0.05492</v>
+      </c>
+      <c r="D366" s="2" t="n">
+        <v>-0.0003640334910812909</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -4094,6 +6303,12 @@
       <c r="B367" s="1" t="n">
         <v>0.05855</v>
       </c>
+      <c r="C367" s="1" t="n">
+        <v>0.05843</v>
+      </c>
+      <c r="D367" s="2" t="n">
+        <v>-0.002049530315969173</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -4104,6 +6319,12 @@
       <c r="B368" s="1" t="n">
         <v>0.057</v>
       </c>
+      <c r="C368" s="1" t="n">
+        <v>0.05668</v>
+      </c>
+      <c r="D368" s="2" t="n">
+        <v>-0.005614035087719313</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -4114,6 +6335,12 @@
       <c r="B369" s="1" t="n">
         <v>0.03085</v>
       </c>
+      <c r="C369" s="1" t="n">
+        <v>0.03079</v>
+      </c>
+      <c r="D369" s="2" t="n">
+        <v>-0.001944894651539629</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -4124,6 +6351,12 @@
       <c r="B370" s="1" t="n">
         <v>0.0001619</v>
       </c>
+      <c r="C370" s="1" t="n">
+        <v>0.0001621</v>
+      </c>
+      <c r="D370" s="3" t="n">
+        <v>0.001235330450895645</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -4134,6 +6367,12 @@
       <c r="B371" s="1" t="n">
         <v>0.006788</v>
       </c>
+      <c r="C371" s="1" t="n">
+        <v>0.00677</v>
+      </c>
+      <c r="D371" s="2" t="n">
+        <v>-0.002651738361814936</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -4144,6 +6383,12 @@
       <c r="B372" s="1" t="n">
         <v>0.006974</v>
       </c>
+      <c r="C372" s="1" t="n">
+        <v>0.006928</v>
+      </c>
+      <c r="D372" s="2" t="n">
+        <v>-0.006595927731574424</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -4154,6 +6399,12 @@
       <c r="B373" s="1" t="n">
         <v>3.787</v>
       </c>
+      <c r="C373" s="1" t="n">
+        <v>3.793</v>
+      </c>
+      <c r="D373" s="3" t="n">
+        <v>0.00158436757327706</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -4164,6 +6415,12 @@
       <c r="B374" s="1" t="n">
         <v>0.07008</v>
       </c>
+      <c r="C374" s="1" t="n">
+        <v>0.07037</v>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>0.004138127853881258</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -4174,6 +6431,12 @@
       <c r="B375" s="1" t="n">
         <v>0.07727000000000001</v>
       </c>
+      <c r="C375" s="1" t="n">
+        <v>0.07743999999999999</v>
+      </c>
+      <c r="D375" s="3" t="n">
+        <v>0.00220007764979927</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -4184,6 +6447,12 @@
       <c r="B376" s="1" t="n">
         <v>0.06278</v>
       </c>
+      <c r="C376" s="1" t="n">
+        <v>0.06290999999999999</v>
+      </c>
+      <c r="D376" s="3" t="n">
+        <v>0.002070723160241976</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -4194,6 +6463,12 @@
       <c r="B377" s="1" t="n">
         <v>0.07625</v>
       </c>
+      <c r="C377" s="1" t="n">
+        <v>0.07599</v>
+      </c>
+      <c r="D377" s="2" t="n">
+        <v>-0.003409836065573723</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -4204,6 +6479,12 @@
       <c r="B378" s="1" t="n">
         <v>0.0004029</v>
       </c>
+      <c r="C378" s="1" t="n">
+        <v>0.0004048</v>
+      </c>
+      <c r="D378" s="3" t="n">
+        <v>0.004715810374782805</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -4214,6 +6495,12 @@
       <c r="B379" s="1" t="n">
         <v>0.07436</v>
       </c>
+      <c r="C379" s="1" t="n">
+        <v>0.07443</v>
+      </c>
+      <c r="D379" s="3" t="n">
+        <v>0.000941366325981719</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -4224,6 +6511,12 @@
       <c r="B380" s="1" t="n">
         <v>0.001342</v>
       </c>
+      <c r="C380" s="1" t="n">
+        <v>0.001356</v>
+      </c>
+      <c r="D380" s="3" t="n">
+        <v>0.01043219076005954</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -4234,6 +6527,12 @@
       <c r="B381" s="1" t="n">
         <v>6.52</v>
       </c>
+      <c r="C381" s="1" t="n">
+        <v>6.504</v>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>-0.002453987730061352</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -4244,6 +6543,12 @@
       <c r="B382" s="1" t="n">
         <v>0.01323</v>
       </c>
+      <c r="C382" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="D382" s="3" t="n">
+        <v>0.003023431594860174</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -4254,6 +6559,12 @@
       <c r="B383" s="1" t="n">
         <v>0.01746</v>
       </c>
+      <c r="C383" s="1" t="n">
+        <v>0.01751</v>
+      </c>
+      <c r="D383" s="3" t="n">
+        <v>0.002863688430698822</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -4264,6 +6575,12 @@
       <c r="B384" s="1" t="n">
         <v>0.1013</v>
       </c>
+      <c r="C384" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="D384" s="3" t="n">
+        <v>0.006910167818361227</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -4274,6 +6591,12 @@
       <c r="B385" s="1" t="n">
         <v>4.481</v>
       </c>
+      <c r="C385" s="1" t="n">
+        <v>4.463</v>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>-0.004016960499888372</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -4284,6 +6607,12 @@
       <c r="B386" s="1" t="n">
         <v>0.001291</v>
       </c>
+      <c r="C386" s="1" t="n">
+        <v>0.001288</v>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>-0.002323780015491839</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -4294,6 +6623,12 @@
       <c r="B387" s="1" t="n">
         <v>0.0005897</v>
       </c>
+      <c r="C387" s="1" t="n">
+        <v>0.0005894</v>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>-0.0005087332541969698</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -4304,6 +6639,12 @@
       <c r="B388" s="1" t="n">
         <v>0.01131</v>
       </c>
+      <c r="C388" s="1" t="n">
+        <v>0.01127</v>
+      </c>
+      <c r="D388" s="2" t="n">
+        <v>-0.003536693191865615</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -4314,6 +6655,12 @@
       <c r="B389" s="1" t="n">
         <v>0.00908</v>
       </c>
+      <c r="C389" s="1" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="D389" s="3" t="n">
+        <v>0.002202643171806269</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -4324,6 +6671,12 @@
       <c r="B390" s="1" t="n">
         <v>0.07844</v>
       </c>
+      <c r="C390" s="1" t="n">
+        <v>0.07834000000000001</v>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>-0.001274859765425663</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -4334,6 +6687,12 @@
       <c r="B391" s="1" t="n">
         <v>0.05095</v>
       </c>
+      <c r="C391" s="1" t="n">
+        <v>0.05086</v>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>-0.001766437684003921</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -4344,6 +6703,12 @@
       <c r="B392" s="1" t="n">
         <v>0.00237</v>
       </c>
+      <c r="C392" s="1" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D392" s="3" t="n">
+        <v>0.004219409282700433</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -4354,6 +6719,12 @@
       <c r="B393" s="1" t="n">
         <v>0.02123</v>
       </c>
+      <c r="C393" s="1" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="D393" s="3" t="n">
+        <v>0.006594441827602508</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -4364,6 +6735,12 @@
       <c r="B394" s="1" t="n">
         <v>0.2057</v>
       </c>
+      <c r="C394" s="1" t="n">
+        <v>0.2059</v>
+      </c>
+      <c r="D394" s="3" t="n">
+        <v>0.0009722897423432461</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -4374,6 +6751,12 @@
       <c r="B395" s="1" t="n">
         <v>0.0969</v>
       </c>
+      <c r="C395" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="D395" s="2" t="n">
+        <v>-0.001031991744066077</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -4384,6 +6767,12 @@
       <c r="B396" s="1" t="n">
         <v>2.701</v>
       </c>
+      <c r="C396" s="1" t="n">
+        <v>2.697</v>
+      </c>
+      <c r="D396" s="2" t="n">
+        <v>-0.001480932987782304</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -4394,6 +6783,12 @@
       <c r="B397" s="1" t="n">
         <v>1.265</v>
       </c>
+      <c r="C397" s="1" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="D397" s="2" t="n">
+        <v>-0.001581027667984191</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -4404,6 +6799,12 @@
       <c r="B398" s="1" t="n">
         <v>0.007262</v>
       </c>
+      <c r="C398" s="1" t="n">
+        <v>0.007253</v>
+      </c>
+      <c r="D398" s="2" t="n">
+        <v>-0.001239328008813044</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -4414,6 +6815,12 @@
       <c r="B399" s="1" t="n">
         <v>0.2591</v>
       </c>
+      <c r="C399" s="1" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="D399" s="2" t="n">
+        <v>-0.0003859513701273215</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -4424,6 +6831,12 @@
       <c r="B400" s="1" t="n">
         <v>0.3185</v>
       </c>
+      <c r="C400" s="1" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>-0.00219780219780213</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -4434,6 +6847,12 @@
       <c r="B401" s="1" t="n">
         <v>0.007057</v>
       </c>
+      <c r="C401" s="1" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="D401" s="3" t="n">
+        <v>0.003259175286949192</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -4444,6 +6863,12 @@
       <c r="B402" s="1" t="n">
         <v>0.004563</v>
       </c>
+      <c r="C402" s="1" t="n">
+        <v>0.004555</v>
+      </c>
+      <c r="D402" s="2" t="n">
+        <v>-0.001753232522463334</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -4454,6 +6879,12 @@
       <c r="B403" s="1" t="n">
         <v>0.2637</v>
       </c>
+      <c r="C403" s="1" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>-0.0007584376185057944</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -4464,6 +6895,12 @@
       <c r="B404" s="1" t="n">
         <v>0.2405</v>
       </c>
+      <c r="C404" s="1" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>-0.002910602910602821</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -4474,6 +6911,12 @@
       <c r="B405" s="1" t="n">
         <v>0.0008704</v>
       </c>
+      <c r="C405" s="1" t="n">
+        <v>0.0008703</v>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>-0.000114889705882418</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -4484,6 +6927,12 @@
       <c r="B406" s="1" t="n">
         <v>0.005095</v>
       </c>
+      <c r="C406" s="1" t="n">
+        <v>0.005088</v>
+      </c>
+      <c r="D406" s="2" t="n">
+        <v>-0.00137389597644751</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -4494,6 +6943,12 @@
       <c r="B407" s="1" t="n">
         <v>0.0121</v>
       </c>
+      <c r="C407" s="1" t="n">
+        <v>0.01209</v>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>-0.0008264462809917019</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -4504,6 +6959,12 @@
       <c r="B408" s="1" t="n">
         <v>0.001444</v>
       </c>
+      <c r="C408" s="1" t="n">
+        <v>0.001453</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>0.006232686980609495</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -4514,6 +6975,12 @@
       <c r="B409" s="1" t="n">
         <v>0.03627</v>
       </c>
+      <c r="C409" s="1" t="n">
+        <v>0.03631</v>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>0.001102839812517378</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -4524,6 +6991,12 @@
       <c r="B410" s="1" t="n">
         <v>0.01632</v>
       </c>
+      <c r="C410" s="1" t="n">
+        <v>0.01626</v>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>-0.003676470588235357</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -4534,6 +7007,12 @@
       <c r="B411" s="1" t="n">
         <v>0.1908</v>
       </c>
+      <c r="C411" s="1" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="D411" s="3" t="n">
+        <v>0.00157232704402513</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -4544,6 +7023,12 @@
       <c r="B412" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
+      <c r="C412" s="1" t="n">
+        <v>0.06773</v>
+      </c>
+      <c r="D412" s="3" t="n">
+        <v>0.002367914755068721</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -4554,6 +7039,12 @@
       <c r="B413" s="1" t="n">
         <v>2525</v>
       </c>
+      <c r="C413" s="1" t="n">
+        <v>2522</v>
+      </c>
+      <c r="D413" s="2" t="n">
+        <v>-0.001188118811881188</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -4564,6 +7055,12 @@
       <c r="B414" s="1" t="n">
         <v>0.05216</v>
       </c>
+      <c r="C414" s="1" t="n">
+        <v>0.05189</v>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>-0.005176380368098149</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -4574,6 +7071,12 @@
       <c r="B415" s="1" t="n">
         <v>1.756</v>
       </c>
+      <c r="C415" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>-0.003416856492027338</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -4584,6 +7087,12 @@
       <c r="B416" s="1" t="n">
         <v>0.06865</v>
       </c>
+      <c r="C416" s="1" t="n">
+        <v>0.06848</v>
+      </c>
+      <c r="D416" s="2" t="n">
+        <v>-0.00247632920611804</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -4594,6 +7103,12 @@
       <c r="B417" s="1" t="n">
         <v>0.074</v>
       </c>
+      <c r="C417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -4604,6 +7119,12 @@
       <c r="B418" s="1" t="n">
         <v>0.1536</v>
       </c>
+      <c r="C418" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>-0.005208333333333303</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -4614,6 +7135,12 @@
       <c r="B419" s="1" t="n">
         <v>0.0123</v>
       </c>
+      <c r="C419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -4624,6 +7151,12 @@
       <c r="B420" s="1" t="n">
         <v>0.01913</v>
       </c>
+      <c r="C420" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>-0.002090956612650384</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -4634,6 +7167,12 @@
       <c r="B421" s="1" t="n">
         <v>0.19122</v>
       </c>
+      <c r="C421" s="1" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="D421" s="3" t="n">
+        <v>0.005647944775651071</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -4644,6 +7183,12 @@
       <c r="B422" s="1" t="n">
         <v>0.03421</v>
       </c>
+      <c r="C422" s="1" t="n">
+        <v>0.03437</v>
+      </c>
+      <c r="D422" s="3" t="n">
+        <v>0.004676995030692793</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -4654,6 +7199,12 @@
       <c r="B423" s="1" t="n">
         <v>0.1421</v>
       </c>
+      <c r="C423" s="1" t="n">
+        <v>0.1421</v>
+      </c>
+      <c r="D423" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -4664,6 +7215,12 @@
       <c r="B424" s="1" t="n">
         <v>0.00528</v>
       </c>
+      <c r="C424" s="1" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>-0.005681818181818114</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -4674,6 +7231,12 @@
       <c r="B425" s="1" t="n">
         <v>0.105</v>
       </c>
+      <c r="C425" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>-0.003809523809523787</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -4684,6 +7247,12 @@
       <c r="B426" s="1" t="n">
         <v>0.007108</v>
       </c>
+      <c r="C426" s="1" t="n">
+        <v>0.007087</v>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>-0.00295441755768139</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -4694,6 +7263,12 @@
       <c r="B427" s="1" t="n">
         <v>0.02574</v>
       </c>
+      <c r="C427" s="1" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>-0.0007770007770007453</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -4704,6 +7279,12 @@
       <c r="B428" s="1" t="n">
         <v>0.008059</v>
       </c>
+      <c r="C428" s="1" t="n">
+        <v>0.00808</v>
+      </c>
+      <c r="D428" s="3" t="n">
+        <v>0.002605782355130933</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -4714,6 +7295,12 @@
       <c r="B429" s="1" t="n">
         <v>0.01211</v>
       </c>
+      <c r="C429" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="D429" s="3" t="n">
+        <v>0.00412881915772101</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -4724,6 +7311,12 @@
       <c r="B430" s="1" t="n">
         <v>0.06679</v>
       </c>
+      <c r="C430" s="1" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>-0.0002994460248541117</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -4734,6 +7327,12 @@
       <c r="B431" s="1" t="n">
         <v>0.00541</v>
       </c>
+      <c r="C431" s="1" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="D431" s="3" t="n">
+        <v>0.001848428835489919</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -4744,6 +7343,12 @@
       <c r="B432" s="1" t="n">
         <v>0.009523999999999999</v>
       </c>
+      <c r="C432" s="1" t="n">
+        <v>0.009534000000000001</v>
+      </c>
+      <c r="D432" s="3" t="n">
+        <v>0.001049979000420131</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -4754,6 +7359,12 @@
       <c r="B433" s="1" t="n">
         <v>0.04145</v>
       </c>
+      <c r="C433" s="1" t="n">
+        <v>0.04126</v>
+      </c>
+      <c r="D433" s="2" t="n">
+        <v>-0.004583835946924069</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -4764,6 +7375,12 @@
       <c r="B434" s="1" t="n">
         <v>0.04188</v>
       </c>
+      <c r="C434" s="1" t="n">
+        <v>0.04172</v>
+      </c>
+      <c r="D434" s="2" t="n">
+        <v>-0.00382043935052532</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -4774,6 +7391,12 @@
       <c r="B435" s="1" t="n">
         <v>0.001527</v>
       </c>
+      <c r="C435" s="1" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="D435" s="3" t="n">
+        <v>0.001964636542239663</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -4784,6 +7407,12 @@
       <c r="B436" s="1" t="n">
         <v>0.0274</v>
       </c>
+      <c r="C436" s="1" t="n">
+        <v>0.02741</v>
+      </c>
+      <c r="D436" s="3" t="n">
+        <v>0.0003649635036496202</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -4794,6 +7423,12 @@
       <c r="B437" s="1" t="n">
         <v>0.08346000000000001</v>
       </c>
+      <c r="C437" s="1" t="n">
+        <v>0.08287</v>
+      </c>
+      <c r="D437" s="2" t="n">
+        <v>-0.00706925473280622</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -4804,6 +7439,12 @@
       <c r="B438" s="1" t="n">
         <v>0.115</v>
       </c>
+      <c r="C438" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="D438" s="2" t="n">
+        <v>-0.002608695652173988</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -4814,6 +7455,12 @@
       <c r="B439" s="1" t="n">
         <v>1.541</v>
       </c>
+      <c r="C439" s="1" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="D439" s="3" t="n">
+        <v>0.0006489292667100012</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -4824,6 +7471,12 @@
       <c r="B440" s="1" t="n">
         <v>0.001786</v>
       </c>
+      <c r="C440" s="1" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="D440" s="2" t="n">
+        <v>-0.0005599104143337809</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -4834,6 +7487,12 @@
       <c r="B441" s="1" t="n">
         <v>0.037</v>
       </c>
+      <c r="C441" s="1" t="n">
+        <v>0.03683</v>
+      </c>
+      <c r="D441" s="2" t="n">
+        <v>-0.004594594594594502</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -4844,6 +7503,12 @@
       <c r="B442" s="1" t="n">
         <v>0.01844</v>
       </c>
+      <c r="C442" s="1" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="D442" s="2" t="n">
+        <v>-0.001084598698481706</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -4854,6 +7519,12 @@
       <c r="B443" s="1" t="n">
         <v>0.12765</v>
       </c>
+      <c r="C443" s="1" t="n">
+        <v>0.12744</v>
+      </c>
+      <c r="D443" s="2" t="n">
+        <v>-0.001645123384253942</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -4864,6 +7535,12 @@
       <c r="B444" s="1" t="n">
         <v>0.011083</v>
       </c>
+      <c r="C444" s="1" t="n">
+        <v>0.011162</v>
+      </c>
+      <c r="D444" s="3" t="n">
+        <v>0.007128033925832284</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -4874,6 +7551,12 @@
       <c r="B445" s="1" t="n">
         <v>0.08008</v>
       </c>
+      <c r="C445" s="1" t="n">
+        <v>0.08008999999999999</v>
+      </c>
+      <c r="D445" s="3" t="n">
+        <v>0.0001248751248750765</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -4884,6 +7567,12 @@
       <c r="B446" s="1" t="n">
         <v>0.0002111</v>
       </c>
+      <c r="C446" s="1" t="n">
+        <v>0.0002094</v>
+      </c>
+      <c r="D446" s="2" t="n">
+        <v>-0.00805305542396975</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -4894,6 +7583,12 @@
       <c r="B447" s="1" t="n">
         <v>0.00651</v>
       </c>
+      <c r="C447" s="1" t="n">
+        <v>0.00649</v>
+      </c>
+      <c r="D447" s="2" t="n">
+        <v>-0.003072196620583725</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -4904,6 +7599,12 @@
       <c r="B448" s="1" t="n">
         <v>0.11187</v>
       </c>
+      <c r="C448" s="1" t="n">
+        <v>0.11118</v>
+      </c>
+      <c r="D448" s="2" t="n">
+        <v>-0.006167873424510559</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -4914,6 +7615,12 @@
       <c r="B449" s="1" t="n">
         <v>0.00169</v>
       </c>
+      <c r="C449" s="1" t="n">
+        <v>0.001689</v>
+      </c>
+      <c r="D449" s="2" t="n">
+        <v>-0.0005917159763314395</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -4924,6 +7631,12 @@
       <c r="B450" s="1" t="n">
         <v>0.0002065</v>
       </c>
+      <c r="C450" s="1" t="n">
+        <v>0.0002061</v>
+      </c>
+      <c r="D450" s="2" t="n">
+        <v>-0.001937046004842662</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -4934,6 +7647,12 @@
       <c r="B451" s="1" t="n">
         <v>26.41</v>
       </c>
+      <c r="C451" s="1" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="D451" s="2" t="n">
+        <v>-0.004543733434305225</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -4944,6 +7663,12 @@
       <c r="B452" s="1" t="n">
         <v>0.1329</v>
       </c>
+      <c r="C452" s="1" t="n">
+        <v>0.1332</v>
+      </c>
+      <c r="D452" s="3" t="n">
+        <v>0.002257336343115294</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -4954,6 +7679,12 @@
       <c r="B453" s="1" t="n">
         <v>0.0001746</v>
       </c>
+      <c r="C453" s="1" t="n">
+        <v>0.000174</v>
+      </c>
+      <c r="D453" s="2" t="n">
+        <v>-0.003436426116838416</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -4964,6 +7695,12 @@
       <c r="B454" s="1" t="n">
         <v>0.1083</v>
       </c>
+      <c r="C454" s="1" t="n">
+        <v>0.10909</v>
+      </c>
+      <c r="D454" s="3" t="n">
+        <v>0.00729455216989855</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -4974,6 +7711,12 @@
       <c r="B455" s="1" t="n">
         <v>0.4984</v>
       </c>
+      <c r="C455" s="1" t="n">
+        <v>0.4982</v>
+      </c>
+      <c r="D455" s="2" t="n">
+        <v>-0.0004012841091493449</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -4984,6 +7727,12 @@
       <c r="B456" s="1" t="n">
         <v>0.015953</v>
       </c>
+      <c r="C456" s="1" t="n">
+        <v>0.015944</v>
+      </c>
+      <c r="D456" s="2" t="n">
+        <v>-0.0005641572118096028</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -4994,6 +7743,12 @@
       <c r="B457" s="1" t="n">
         <v>0.00664</v>
       </c>
+      <c r="C457" s="1" t="n">
+        <v>0.006642</v>
+      </c>
+      <c r="D457" s="3" t="n">
+        <v>0.0003012048192771484</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -5004,6 +7759,12 @@
       <c r="B458" s="1" t="n">
         <v>0.4815</v>
       </c>
+      <c r="C458" s="1" t="n">
+        <v>0.4797</v>
+      </c>
+      <c r="D458" s="2" t="n">
+        <v>-0.00373831775700928</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -5014,6 +7775,12 @@
       <c r="B459" s="1" t="n">
         <v>0.00636</v>
       </c>
+      <c r="C459" s="1" t="n">
+        <v>0.006365</v>
+      </c>
+      <c r="D459" s="3" t="n">
+        <v>0.0007861635220125466</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -5024,6 +7791,12 @@
       <c r="B460" s="1" t="n">
         <v>0.1373</v>
       </c>
+      <c r="C460" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="D460" s="2" t="n">
+        <v>-0.002184996358339364</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -5034,6 +7807,12 @@
       <c r="B461" s="1" t="n">
         <v>0.08902</v>
       </c>
+      <c r="C461" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="D461" s="3" t="n">
+        <v>0.0008986744551785749</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -5044,6 +7823,12 @@
       <c r="B462" s="1" t="n">
         <v>0.04488</v>
       </c>
+      <c r="C462" s="1" t="n">
+        <v>0.04525</v>
+      </c>
+      <c r="D462" s="3" t="n">
+        <v>0.008244206773618434</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -5054,6 +7839,12 @@
       <c r="B463" s="1" t="n">
         <v>0.00697</v>
       </c>
+      <c r="C463" s="1" t="n">
+        <v>0.00696</v>
+      </c>
+      <c r="D463" s="2" t="n">
+        <v>-0.001434720229555178</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -5064,6 +7855,12 @@
       <c r="B464" s="1" t="n">
         <v>1.303</v>
       </c>
+      <c r="C464" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="D464" s="3" t="n">
+        <v>0.0007674597083653968</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -5074,6 +7871,12 @@
       <c r="B465" s="1" t="n">
         <v>0.2817</v>
       </c>
+      <c r="C465" s="1" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="D465" s="2" t="n">
+        <v>-0.002839900603478959</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -5084,6 +7887,12 @@
       <c r="B466" s="1" t="n">
         <v>1.418</v>
       </c>
+      <c r="C466" s="1" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="D466" s="2" t="n">
+        <v>-0.00141043723554302</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -5094,6 +7903,12 @@
       <c r="B467" s="1" t="n">
         <v>0.01916</v>
       </c>
+      <c r="C467" s="1" t="n">
+        <v>0.01911</v>
+      </c>
+      <c r="D467" s="2" t="n">
+        <v>-0.00260960334029235</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -5104,6 +7919,12 @@
       <c r="B468" s="1" t="n">
         <v>0.009900000000000001</v>
       </c>
+      <c r="C468" s="1" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="D468" s="2" t="n">
+        <v>-0.005050505050505195</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -5114,6 +7935,12 @@
       <c r="B469" s="1" t="n">
         <v>0.3985</v>
       </c>
+      <c r="C469" s="1" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="D469" s="2" t="n">
+        <v>-0.001505646173149423</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -5124,6 +7951,12 @@
       <c r="B470" s="1" t="n">
         <v>0.881</v>
       </c>
+      <c r="C470" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D470" s="2" t="n">
+        <v>-0.001135073779795688</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -5134,6 +7967,12 @@
       <c r="B471" s="1" t="n">
         <v>3.234</v>
       </c>
+      <c r="C471" s="1" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="D471" s="2" t="n">
+        <v>-0.003401360544217724</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -5144,6 +7983,12 @@
       <c r="B472" s="1" t="n">
         <v>0.04095</v>
       </c>
+      <c r="C472" s="1" t="n">
+        <v>0.04063</v>
+      </c>
+      <c r="D472" s="2" t="n">
+        <v>-0.007814407814407835</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -5154,6 +7999,12 @@
       <c r="B473" s="1" t="n">
         <v>1.238</v>
       </c>
+      <c r="C473" s="1" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="D473" s="2" t="n">
+        <v>-0.002423263327948216</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -5164,6 +8015,12 @@
       <c r="B474" s="1" t="n">
         <v>0.00852</v>
       </c>
+      <c r="C474" s="1" t="n">
+        <v>0.008534999999999999</v>
+      </c>
+      <c r="D474" s="3" t="n">
+        <v>0.001760563380281618</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -5174,6 +8031,12 @@
       <c r="B475" s="1" t="n">
         <v>0.04119</v>
       </c>
+      <c r="C475" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="D475" s="3" t="n">
+        <v>0.000971109492595419</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -5184,6 +8047,12 @@
       <c r="B476" s="1" t="n">
         <v>0.07928</v>
       </c>
+      <c r="C476" s="1" t="n">
+        <v>0.07911</v>
+      </c>
+      <c r="D476" s="2" t="n">
+        <v>-0.002144298688193787</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -5194,6 +8063,12 @@
       <c r="B477" s="1" t="n">
         <v>0.13776</v>
       </c>
+      <c r="C477" s="1" t="n">
+        <v>0.13738</v>
+      </c>
+      <c r="D477" s="2" t="n">
+        <v>-0.002758420441347209</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -5204,6 +8079,12 @@
       <c r="B478" s="1" t="n">
         <v>0.04747</v>
       </c>
+      <c r="C478" s="1" t="n">
+        <v>0.04742</v>
+      </c>
+      <c r="D478" s="2" t="n">
+        <v>-0.001053296819043637</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -5214,6 +8095,12 @@
       <c r="B479" s="1" t="n">
         <v>0.005268</v>
       </c>
+      <c r="C479" s="1" t="n">
+        <v>0.005267</v>
+      </c>
+      <c r="D479" s="2" t="n">
+        <v>-0.0001898253606682105</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -5224,6 +8111,12 @@
       <c r="B480" s="1" t="n">
         <v>0.2792</v>
       </c>
+      <c r="C480" s="1" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="D480" s="3" t="n">
+        <v>0.001074498567335324</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -5234,6 +8127,12 @@
       <c r="B481" s="1" t="n">
         <v>0.07611999999999999</v>
       </c>
+      <c r="C481" s="1" t="n">
+        <v>0.07602</v>
+      </c>
+      <c r="D481" s="2" t="n">
+        <v>-0.001313715186547412</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -5244,6 +8143,12 @@
       <c r="B482" s="1" t="n">
         <v>0.0149</v>
       </c>
+      <c r="C482" s="1" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="D482" s="2" t="n">
+        <v>-0.006040268456375826</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -5254,6 +8159,12 @@
       <c r="B483" s="1" t="n">
         <v>0.025</v>
       </c>
+      <c r="C483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="D483" s="3" t="n">
+        <v>0.003999999999999976</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -5264,6 +8175,12 @@
       <c r="B484" s="1" t="n">
         <v>0.02169</v>
       </c>
+      <c r="C484" s="1" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="D484" s="2" t="n">
+        <v>-0.001844167819271638</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -5274,6 +8191,12 @@
       <c r="B485" s="1" t="n">
         <v>0.008264000000000001</v>
       </c>
+      <c r="C485" s="1" t="n">
+        <v>0.008303</v>
+      </c>
+      <c r="D485" s="3" t="n">
+        <v>0.004719264278799504</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -5284,6 +8207,12 @@
       <c r="B486" s="1" t="n">
         <v>0.00747</v>
       </c>
+      <c r="C486" s="1" t="n">
+        <v>0.007432</v>
+      </c>
+      <c r="D486" s="2" t="n">
+        <v>-0.005087014725568921</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -5294,6 +8223,12 @@
       <c r="B487" s="1" t="n">
         <v>0.1099</v>
       </c>
+      <c r="C487" s="1" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="D487" s="3" t="n">
+        <v>0.002729754322111088</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -5304,6 +8239,12 @@
       <c r="B488" s="1" t="n">
         <v>0.009435000000000001</v>
       </c>
+      <c r="C488" s="1" t="n">
+        <v>0.009387</v>
+      </c>
+      <c r="D488" s="2" t="n">
+        <v>-0.005087440381558152</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -5314,6 +8255,12 @@
       <c r="B489" s="1" t="n">
         <v>0.03895</v>
       </c>
+      <c r="C489" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="D489" s="2" t="n">
+        <v>-0.0005134788189986954</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -5324,6 +8271,12 @@
       <c r="B490" s="1" t="n">
         <v>0.05805</v>
       </c>
+      <c r="C490" s="1" t="n">
+        <v>0.05798</v>
+      </c>
+      <c r="D490" s="2" t="n">
+        <v>-0.001205857019810519</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -5334,6 +8287,12 @@
       <c r="B491" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
+      <c r="C491" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="D491" s="2" t="n">
+        <v>-0.00207039337474126</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -5344,6 +8303,12 @@
       <c r="B492" s="1" t="n">
         <v>1.336</v>
       </c>
+      <c r="C492" s="1" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="D492" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -5354,6 +8319,12 @@
       <c r="B493" s="1" t="n">
         <v>0.03525</v>
       </c>
+      <c r="C493" s="1" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="D493" s="2" t="n">
+        <v>-0.001418439716311901</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -5364,6 +8335,12 @@
       <c r="B494" s="1" t="n">
         <v>0.01697</v>
       </c>
+      <c r="C494" s="1" t="n">
+        <v>0.01699</v>
+      </c>
+      <c r="D494" s="3" t="n">
+        <v>0.001178550383029031</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -5374,6 +8351,12 @@
       <c r="B495" s="1" t="n">
         <v>0.04739</v>
       </c>
+      <c r="C495" s="1" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="D495" s="2" t="n">
+        <v>-0.000633044946191227</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -5384,6 +8367,12 @@
       <c r="B496" s="1" t="n">
         <v>0.04822</v>
       </c>
+      <c r="C496" s="1" t="n">
+        <v>0.04816</v>
+      </c>
+      <c r="D496" s="2" t="n">
+        <v>-0.00124429697221065</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -5394,6 +8383,12 @@
       <c r="B497" s="1" t="n">
         <v>0.05004</v>
       </c>
+      <c r="C497" s="1" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="D497" s="2" t="n">
+        <v>-0.001398880895283785</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -5404,6 +8399,12 @@
       <c r="B498" s="1" t="n">
         <v>0.2883</v>
       </c>
+      <c r="C498" s="1" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="D498" s="2" t="n">
+        <v>-0.003468609087755813</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -5414,6 +8415,12 @@
       <c r="B499" s="1" t="n">
         <v>0.2734</v>
       </c>
+      <c r="C499" s="1" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="D499" s="2" t="n">
+        <v>-0.002560351133869709</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -5424,6 +8431,12 @@
       <c r="B500" s="1" t="n">
         <v>0.00266</v>
       </c>
+      <c r="C500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="D500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -5434,6 +8447,12 @@
       <c r="B501" s="1" t="n">
         <v>0.03606</v>
       </c>
+      <c r="C501" s="1" t="n">
+        <v>0.03613</v>
+      </c>
+      <c r="D501" s="3" t="n">
+        <v>0.001941209095951209</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -5444,6 +8463,12 @@
       <c r="B502" s="1" t="n">
         <v>0.03179</v>
       </c>
+      <c r="C502" s="1" t="n">
+        <v>0.03184</v>
+      </c>
+      <c r="D502" s="3" t="n">
+        <v>0.001572821642025839</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -5454,6 +8479,12 @@
       <c r="B503" s="1" t="n">
         <v>0.00774</v>
       </c>
+      <c r="C503" s="1" t="n">
+        <v>0.007785</v>
+      </c>
+      <c r="D503" s="3" t="n">
+        <v>0.00581395348837208</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -5464,6 +8495,12 @@
       <c r="B504" s="1" t="n">
         <v>3.051</v>
       </c>
+      <c r="C504" s="1" t="n">
+        <v>3.053</v>
+      </c>
+      <c r="D504" s="3" t="n">
+        <v>0.0006555227794165125</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -5474,6 +8511,12 @@
       <c r="B505" s="1" t="n">
         <v>0.0007344</v>
       </c>
+      <c r="C505" s="1" t="n">
+        <v>0.0007346</v>
+      </c>
+      <c r="D505" s="3" t="n">
+        <v>0.0002723311546841025</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -5484,6 +8527,12 @@
       <c r="B506" s="1" t="n">
         <v>0.2961</v>
       </c>
+      <c r="C506" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="D506" s="3" t="n">
+        <v>0.001688618709895307</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -5494,6 +8543,12 @@
       <c r="B507" s="1" t="n">
         <v>0.002844</v>
       </c>
+      <c r="C507" s="1" t="n">
+        <v>0.00283</v>
+      </c>
+      <c r="D507" s="2" t="n">
+        <v>-0.004922644163150535</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -5504,6 +8559,12 @@
       <c r="B508" s="1" t="n">
         <v>0.06326</v>
       </c>
+      <c r="C508" s="1" t="n">
+        <v>0.06326</v>
+      </c>
+      <c r="D508" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -5514,6 +8575,12 @@
       <c r="B509" s="1" t="n">
         <v>2.238</v>
       </c>
+      <c r="C509" s="1" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="D509" s="3" t="n">
+        <v>0.0008936550491511278</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -5524,6 +8591,12 @@
       <c r="B510" s="1" t="n">
         <v>0.0007292000000000001</v>
       </c>
+      <c r="C510" s="1" t="n">
+        <v>0.0007292000000000001</v>
+      </c>
+      <c r="D510" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -5534,6 +8607,12 @@
       <c r="B511" s="1" t="n">
         <v>0.2746</v>
       </c>
+      <c r="C511" s="1" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="D511" s="2" t="n">
+        <v>-0.002184996358339364</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -5544,6 +8623,12 @@
       <c r="B512" s="1" t="n">
         <v>0.0004802</v>
       </c>
+      <c r="C512" s="1" t="n">
+        <v>0.0004767</v>
+      </c>
+      <c r="D512" s="2" t="n">
+        <v>-0.007288629737609393</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -5554,6 +8639,12 @@
       <c r="B513" s="1" t="n">
         <v>0.05509</v>
       </c>
+      <c r="C513" s="1" t="n">
+        <v>0.05491</v>
+      </c>
+      <c r="D513" s="2" t="n">
+        <v>-0.0032673806498457</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -5564,6 +8655,12 @@
       <c r="B514" s="1" t="n">
         <v>0.03033</v>
       </c>
+      <c r="C514" s="1" t="n">
+        <v>0.03035</v>
+      </c>
+      <c r="D514" s="3" t="n">
+        <v>0.0006594131223211073</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -5574,6 +8671,12 @@
       <c r="B515" s="1" t="n">
         <v>0.001141</v>
       </c>
+      <c r="C515" s="1" t="n">
+        <v>0.001141</v>
+      </c>
+      <c r="D515" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -5584,6 +8687,12 @@
       <c r="B516" s="1" t="n">
         <v>0.006596</v>
       </c>
+      <c r="C516" s="1" t="n">
+        <v>0.006594</v>
+      </c>
+      <c r="D516" s="2" t="n">
+        <v>-0.000303214069132848</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -5594,6 +8703,12 @@
       <c r="B517" s="1" t="n">
         <v>0.03982</v>
       </c>
+      <c r="C517" s="1" t="n">
+        <v>0.03976</v>
+      </c>
+      <c r="D517" s="2" t="n">
+        <v>-0.001506780512305487</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -5604,6 +8719,12 @@
       <c r="B518" s="1" t="n">
         <v>0.1028</v>
       </c>
+      <c r="C518" s="1" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="D518" s="2" t="n">
+        <v>-0.00194552529182885</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -5614,6 +8735,12 @@
       <c r="B519" s="1" t="n">
         <v>0.008789999999999999</v>
       </c>
+      <c r="C519" s="1" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="D519" s="2" t="n">
+        <v>-0.004550625711035082</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -5624,6 +8751,12 @@
       <c r="B520" s="1" t="n">
         <v>0.1607</v>
       </c>
+      <c r="C520" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="D520" s="2" t="n">
+        <v>-0.004978220286247809</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -5634,6 +8767,12 @@
       <c r="B521" s="1" t="n">
         <v>0.01784</v>
       </c>
+      <c r="C521" s="1" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="D521" s="3" t="n">
+        <v>0.003923766816143337</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -5644,6 +8783,12 @@
       <c r="B522" s="1" t="n">
         <v>0.01654</v>
       </c>
+      <c r="C522" s="1" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="D522" s="3" t="n">
+        <v>0.0006045949214026356</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -5654,6 +8799,12 @@
       <c r="B523" s="1" t="n">
         <v>0.004194</v>
       </c>
+      <c r="C523" s="1" t="n">
+        <v>0.004192</v>
+      </c>
+      <c r="D523" s="2" t="n">
+        <v>-0.0004768717215067711</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -5664,6 +8815,12 @@
       <c r="B524" s="1" t="n">
         <v>0.01418</v>
       </c>
+      <c r="C524" s="1" t="n">
+        <v>0.01415</v>
+      </c>
+      <c r="D524" s="2" t="n">
+        <v>-0.002115655853314564</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -5674,6 +8831,12 @@
       <c r="B525" s="1" t="n">
         <v>0.0249</v>
       </c>
+      <c r="C525" s="1" t="n">
+        <v>0.02495</v>
+      </c>
+      <c r="D525" s="3" t="n">
+        <v>0.002008032128514114</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -5684,6 +8847,12 @@
       <c r="B526" s="1" t="n">
         <v>0.1205</v>
       </c>
+      <c r="C526" s="1" t="n">
+        <v>0.1201</v>
+      </c>
+      <c r="D526" s="2" t="n">
+        <v>-0.003319502074688777</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -5694,6 +8863,12 @@
       <c r="B527" s="1" t="n">
         <v>0.0716</v>
       </c>
+      <c r="C527" s="1" t="n">
+        <v>0.07149</v>
+      </c>
+      <c r="D527" s="2" t="n">
+        <v>-0.001536312849161997</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -5704,6 +8879,12 @@
       <c r="B528" s="1" t="n">
         <v>0.04311</v>
       </c>
+      <c r="C528" s="1" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="D528" s="2" t="n">
+        <v>-0.004639294827186401</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -5714,6 +8895,12 @@
       <c r="B529" s="1" t="n">
         <v>0.06326</v>
       </c>
+      <c r="C529" s="1" t="n">
+        <v>0.06312</v>
+      </c>
+      <c r="D529" s="2" t="n">
+        <v>-0.002213088839709157</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -5724,6 +8911,12 @@
       <c r="B530" s="1" t="n">
         <v>0.004992</v>
       </c>
+      <c r="C530" s="1" t="n">
+        <v>0.005003</v>
+      </c>
+      <c r="D530" s="3" t="n">
+        <v>0.002203525641025586</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -5734,6 +8927,12 @@
       <c r="B531" s="1" t="n">
         <v>0.1305</v>
       </c>
+      <c r="C531" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="D531" s="2" t="n">
+        <v>-0.001532567049808473</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -5744,6 +8943,12 @@
       <c r="B532" s="1" t="n">
         <v>0.0534</v>
       </c>
+      <c r="C532" s="1" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="D532" s="2" t="n">
+        <v>-0.004868913857677964</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -5754,6 +8959,12 @@
       <c r="B533" s="1" t="n">
         <v>0.003761</v>
       </c>
+      <c r="C533" s="1" t="n">
+        <v>0.003811</v>
+      </c>
+      <c r="D533" s="3" t="n">
+        <v>0.01329433661260307</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -5764,6 +8975,12 @@
       <c r="B534" s="1" t="n">
         <v>0.1714</v>
       </c>
+      <c r="C534" s="1" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="D534" s="3" t="n">
+        <v>0.000583430571762058</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -5774,6 +8991,12 @@
       <c r="B535" s="1" t="n">
         <v>1.12e-05</v>
       </c>
+      <c r="C535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="D535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -5784,6 +9007,12 @@
       <c r="B536" s="1" t="n">
         <v>0.0004462</v>
       </c>
+      <c r="C536" s="1" t="n">
+        <v>0.0004482</v>
+      </c>
+      <c r="D536" s="3" t="n">
+        <v>0.00448229493500671</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -5794,6 +9023,12 @@
       <c r="B537" s="1" t="n">
         <v>0.009679999999999999</v>
       </c>
+      <c r="C537" s="1" t="n">
+        <v>0.009639999999999999</v>
+      </c>
+      <c r="D537" s="2" t="n">
+        <v>-0.004132231404958689</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -5804,6 +9039,12 @@
       <c r="B538" s="1" t="n">
         <v>0.05439</v>
       </c>
+      <c r="C538" s="1" t="n">
+        <v>0.05443</v>
+      </c>
+      <c r="D538" s="3" t="n">
+        <v>0.0007354293068578483</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -5814,6 +9055,12 @@
       <c r="B539" s="1" t="n">
         <v>0.6838</v>
       </c>
+      <c r="C539" s="1" t="n">
+        <v>0.6846</v>
+      </c>
+      <c r="D539" s="3" t="n">
+        <v>0.001169932728868124</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -5824,6 +9071,12 @@
       <c r="B540" s="1" t="n">
         <v>0.1508</v>
       </c>
+      <c r="C540" s="1" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="D540" s="3" t="n">
+        <v>0.0006631299734749122</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -5834,6 +9087,12 @@
       <c r="B541" s="1" t="n">
         <v>0.01314</v>
       </c>
+      <c r="C541" s="1" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="D541" s="2" t="n">
+        <v>-0.005327245053272497</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -5844,6 +9103,12 @@
       <c r="B542" s="1" t="n">
         <v>0.0135</v>
       </c>
+      <c r="C542" s="1" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="D542" s="3" t="n">
+        <v>0.02444444444444448</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -5853,6 +9118,12 @@
       </c>
       <c r="B543" s="1" t="n">
         <v>0.05711</v>
+      </c>
+      <c r="C543" s="1" t="n">
+        <v>0.05697</v>
+      </c>
+      <c r="D543" s="2" t="n">
+        <v>-0.002451409560497307</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:J543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -434,6 +434,8 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +479,16 @@
           <t>change_00:45</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>price_01:00</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>change_01:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -505,6 +517,12 @@
       <c r="H2" s="3" t="n">
         <v>0.004715094587568574</v>
       </c>
+      <c r="I2" s="1" t="n">
+        <v>70332.8</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>-9.240922215603511e-05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,6 +551,12 @@
       <c r="H3" s="3" t="n">
         <v>0.003708983011403349</v>
       </c>
+      <c r="I3" s="1" t="n">
+        <v>2068.44</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>-0.0008549857260857506</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -561,6 +585,12 @@
       <c r="H4" s="3" t="n">
         <v>0.007662835249042271</v>
       </c>
+      <c r="I4" s="1" t="n">
+        <v>86.76000000000001</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>-0.0003456619426201306</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -589,6 +619,12 @@
       <c r="H5" s="2" t="n">
         <v>-0.03154714298409323</v>
       </c>
+      <c r="I5" s="1" t="n">
+        <v>0.011114</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.01982015048632785</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -617,6 +653,12 @@
       <c r="H6" s="3" t="n">
         <v>0.004938988959906971</v>
       </c>
+      <c r="I6" s="1" t="n">
+        <v>1.3812</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.001734605377276639</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -645,6 +687,12 @@
       <c r="H7" s="3" t="n">
         <v>0.008635394456290035</v>
       </c>
+      <c r="I7" s="1" t="n">
+        <v>0.09469</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.000845576577528768</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -673,6 +721,12 @@
       <c r="H8" s="3" t="n">
         <v>0.004983655752639192</v>
       </c>
+      <c r="I8" s="1" t="n">
+        <v>37.558</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.001333048949557352</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -701,6 +755,12 @@
       <c r="H9" s="3" t="n">
         <v>0.003389154704944109</v>
       </c>
+      <c r="I9" s="1" t="n">
+        <v>0.05008</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.004967216371945166</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -729,6 +789,12 @@
       <c r="H10" s="2" t="n">
         <v>-0.002452182442373612</v>
       </c>
+      <c r="I10" s="1" t="n">
+        <v>18.466</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.00874030372555447</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -757,6 +823,12 @@
       <c r="H11" s="3" t="n">
         <v>0.003556143969949729</v>
       </c>
+      <c r="I11" s="1" t="n">
+        <v>651.7</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>-0.0002914602156804689</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -785,6 +857,12 @@
       <c r="H12" s="2" t="n">
         <v>-0.04220987390468046</v>
       </c>
+      <c r="I12" s="1" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>-0.06482204618989182</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -813,6 +891,12 @@
       <c r="H13" s="3" t="n">
         <v>0.00209234866137238</v>
       </c>
+      <c r="I13" s="1" t="n">
+        <v>210.35</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>-0.00180325535044842</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +925,12 @@
       <c r="H14" s="3" t="n">
         <v>0.008689575547655988</v>
       </c>
+      <c r="I14" s="1" t="n">
+        <v>0.0033128</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>-0.002138618633091459</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -869,6 +959,12 @@
       <c r="H15" s="3" t="n">
         <v>0.010812723626784</v>
       </c>
+      <c r="I15" s="1" t="n">
+        <v>0.25434</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>-0.01065816088377145</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -897,6 +993,12 @@
       <c r="H16" s="3" t="n">
         <v>0.008045384218669332</v>
       </c>
+      <c r="I16" s="1" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>-0.0003069681776322183</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -925,6 +1027,12 @@
       <c r="H17" s="3" t="n">
         <v>0.003344481605351151</v>
       </c>
+      <c r="I17" s="1" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>-0.01333333333333325</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -953,6 +1061,12 @@
       <c r="H18" s="3" t="n">
         <v>0.01264577771532957</v>
       </c>
+      <c r="I18" s="1" t="n">
+        <v>215.95</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>-0.001202534572869059</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -981,6 +1095,12 @@
       <c r="H19" s="3" t="n">
         <v>0.006118546845124246</v>
       </c>
+      <c r="I19" s="1" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>-0.0003800836183960053</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1009,6 +1129,12 @@
       <c r="H20" s="3" t="n">
         <v>0.007482031342052675</v>
       </c>
+      <c r="I20" s="1" t="n">
+        <v>0.016927</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>-0.01017484357639907</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1037,6 +1163,12 @@
       <c r="H21" s="3" t="n">
         <v>0.004916317991631675</v>
       </c>
+      <c r="I21" s="1" t="n">
+        <v>9.593999999999999</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>-0.00135317997293639</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1065,6 +1197,12 @@
       <c r="H22" s="3" t="n">
         <v>0.002969121140142521</v>
       </c>
+      <c r="I22" s="1" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>-0.009473060982830021</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1093,6 +1231,12 @@
       <c r="H23" s="2" t="n">
         <v>-0.002148012372551347</v>
       </c>
+      <c r="I23" s="1" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.004534887058350868</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1121,6 +1265,12 @@
       <c r="H24" s="3" t="n">
         <v>0.003492433061699654</v>
       </c>
+      <c r="I24" s="1" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>-0.001160092807424595</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1149,6 +1299,12 @@
       <c r="H25" s="3" t="n">
         <v>0.005106005106005037</v>
       </c>
+      <c r="I25" s="1" t="n">
+        <v>9.045</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>-0.001104362230811683</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1177,6 +1333,12 @@
       <c r="H26" s="3" t="n">
         <v>0.003793626707131937</v>
       </c>
+      <c r="I26" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>-0.002267573696145043</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1205,6 +1367,12 @@
       <c r="H27" s="3" t="n">
         <v>0.0009449438683859509</v>
       </c>
+      <c r="I27" s="1" t="n">
+        <v>5126.18</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>-0.002189810858736761</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1233,6 +1401,12 @@
       <c r="H28" s="3" t="n">
         <v>0.009129814550642044</v>
       </c>
+      <c r="I28" s="1" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>-0.003109980209216822</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1261,6 +1435,12 @@
       <c r="H29" s="2" t="n">
         <v>-0.001130369253956335</v>
       </c>
+      <c r="I29" s="1" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>-0.007167106752168874</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1289,6 +1469,12 @@
       <c r="H30" s="3" t="n">
         <v>0.0141509433962265</v>
       </c>
+      <c r="I30" s="1" t="n">
+        <v>0.57691</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.001232211037834065</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1317,6 +1503,12 @@
       <c r="H31" s="3" t="n">
         <v>0.007736943907156651</v>
       </c>
+      <c r="I31" s="1" t="n">
+        <v>0.002084</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1345,6 +1537,12 @@
       <c r="H32" s="2" t="n">
         <v>-0.004443386495278941</v>
       </c>
+      <c r="I32" s="1" t="n">
+        <v>1.2705</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.01259265162987171</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1373,6 +1571,12 @@
       <c r="H33" s="2" t="n">
         <v>-0.006155740227762394</v>
       </c>
+      <c r="I33" s="1" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.006193868070610101</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1401,6 +1605,12 @@
       <c r="H34" s="3" t="n">
         <v>0.004666666666666597</v>
       </c>
+      <c r="I34" s="1" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>-0.003981420039814204</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1429,6 +1639,12 @@
       <c r="H35" s="3" t="n">
         <v>0.003661317197228834</v>
       </c>
+      <c r="I35" s="1" t="n">
+        <v>456.68</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>-0.002424692544616557</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1457,6 +1673,12 @@
       <c r="H36" s="2" t="n">
         <v>-0.007244876837093689</v>
       </c>
+      <c r="I36" s="1" t="n">
+        <v>0.04874</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.01626355296080058</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1485,6 +1707,12 @@
       <c r="H37" s="3" t="n">
         <v>0.0007068136839128426</v>
       </c>
+      <c r="I37" s="1" t="n">
+        <v>0.7088</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.001271366012148625</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1513,6 +1741,12 @@
       <c r="H38" s="3" t="n">
         <v>0.006641366223908977</v>
       </c>
+      <c r="I38" s="1" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>-0.003770028275212041</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1541,6 +1775,12 @@
       <c r="H39" s="3" t="n">
         <v>0.006764168190127924</v>
       </c>
+      <c r="I39" s="1" t="n">
+        <v>109.94</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>-0.001815870710005473</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1569,6 +1809,12 @@
       <c r="H40" s="2" t="n">
         <v>-0.000262191924488806</v>
       </c>
+      <c r="I40" s="1" t="n">
+        <v>0.03854</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.01075268817204303</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1597,6 +1843,12 @@
       <c r="H41" s="3" t="n">
         <v>0.005975013579576262</v>
       </c>
+      <c r="I41" s="1" t="n">
+        <v>0.05563</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0.001259899208063366</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1625,6 +1877,12 @@
       <c r="H42" s="3" t="n">
         <v>0.003506181952389829</v>
       </c>
+      <c r="I42" s="1" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1653,6 +1911,12 @@
       <c r="H43" s="3" t="n">
         <v>0.003044140030441488</v>
       </c>
+      <c r="I43" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1681,6 +1945,12 @@
       <c r="H44" s="3" t="n">
         <v>0.003580562659846431</v>
       </c>
+      <c r="I44" s="1" t="n">
+        <v>0.005878</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>-0.001359157322459961</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1709,6 +1979,12 @@
       <c r="H45" s="3" t="n">
         <v>0.002134146341463433</v>
       </c>
+      <c r="I45" s="1" t="n">
+        <v>0.09841999999999999</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>-0.00192678227360318</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1737,6 +2013,12 @@
       <c r="H46" s="3" t="n">
         <v>0.006161652772743713</v>
       </c>
+      <c r="I46" s="1" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>-0.0007204610951007853</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1765,6 +2047,12 @@
       <c r="H47" s="3" t="n">
         <v>0.0003459489379367224</v>
       </c>
+      <c r="I47" s="1" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>-0.0006916585973162885</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1793,6 +2081,12 @@
       <c r="H48" s="3" t="n">
         <v>0.01597744360902262</v>
       </c>
+      <c r="I48" s="1" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.003700277520814039</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1821,6 +2115,12 @@
       <c r="H49" s="3" t="n">
         <v>0.005080440304826351</v>
       </c>
+      <c r="I49" s="1" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>-0.005736751313836349</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1849,6 +2149,12 @@
       <c r="H50" s="2" t="n">
         <v>-0.01064495929868511</v>
       </c>
+      <c r="I50" s="1" t="n">
+        <v>0.04722</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>-0.003797468354430372</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1877,6 +2183,12 @@
       <c r="H51" s="3" t="n">
         <v>0.007196093549216146</v>
       </c>
+      <c r="I51" s="1" t="n">
+        <v>3.914</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>-0.001275835672365372</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1905,6 +2217,12 @@
       <c r="H52" s="2" t="n">
         <v>-0.004237288135593209</v>
       </c>
+      <c r="I52" s="1" t="n">
+        <v>0.000234</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>-0.004255319148936158</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1933,6 +2251,12 @@
       <c r="H53" s="3" t="n">
         <v>0.006064281382656161</v>
       </c>
+      <c r="I53" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>-0.0006027727546714225</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1961,6 +2285,12 @@
       <c r="H54" s="3" t="n">
         <v>0.0009678199854826608</v>
       </c>
+      <c r="I54" s="1" t="n">
+        <v>0.04154</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.004109257916364599</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1989,6 +2319,12 @@
       <c r="H55" s="2" t="n">
         <v>-0.001071723000824444</v>
       </c>
+      <c r="I55" s="1" t="n">
+        <v>0.12115</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>-0.000165057357431758</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2017,6 +2353,12 @@
       <c r="H56" s="3" t="n">
         <v>0.02064435408195181</v>
       </c>
+      <c r="I56" s="1" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>-0.01348452344468268</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2045,6 +2387,12 @@
       <c r="H57" s="2" t="n">
         <v>-0.001692047377326643</v>
       </c>
+      <c r="I57" s="1" t="n">
+        <v>0.01167</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>-0.01101694915254237</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2073,6 +2421,12 @@
       <c r="H58" s="3" t="n">
         <v>0.006054490413723545</v>
       </c>
+      <c r="I58" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>-0.002006018054162406</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2101,6 +2455,12 @@
       <c r="H59" s="3" t="n">
         <v>0.005970149253731359</v>
       </c>
+      <c r="I59" s="1" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>-0.002967359050445111</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2129,6 +2489,12 @@
       <c r="H60" s="3" t="n">
         <v>0.01180327868852456</v>
       </c>
+      <c r="I60" s="1" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>-0.003888528839922161</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2157,6 +2523,12 @@
       <c r="H61" s="3" t="n">
         <v>0.006545820745216598</v>
       </c>
+      <c r="I61" s="1" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.0004377188594296319</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2185,6 +2557,12 @@
       <c r="H62" s="3" t="n">
         <v>0.008907111550968431</v>
       </c>
+      <c r="I62" s="1" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>-0.002242152466367777</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2213,6 +2591,12 @@
       <c r="H63" s="3" t="n">
         <v>0.01306066334421715</v>
       </c>
+      <c r="I63" s="1" t="n">
+        <v>5.917</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.003731976251060262</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2241,6 +2625,12 @@
       <c r="H64" s="3" t="n">
         <v>0.01134912753582071</v>
       </c>
+      <c r="I64" s="1" t="n">
+        <v>0.007113</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>-0.002244354046850824</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2269,6 +2659,12 @@
       <c r="H65" s="2" t="n">
         <v>-0.0006589785831960193</v>
       </c>
+      <c r="I65" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>-0.007583250906693078</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2297,6 +2693,12 @@
       <c r="H66" s="3" t="n">
         <v>0.01716738197424882</v>
       </c>
+      <c r="I66" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>-0.008438818565400852</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2325,6 +2727,12 @@
       <c r="H67" s="3" t="n">
         <v>0.009293680297397709</v>
       </c>
+      <c r="I67" s="1" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>-0.003683241252302029</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2353,6 +2761,12 @@
       <c r="H68" s="3" t="n">
         <v>0.009708249496981828</v>
       </c>
+      <c r="I68" s="1" t="n">
+        <v>2.0142</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0.003437453295471704</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2381,6 +2795,12 @@
       <c r="H69" s="3" t="n">
         <v>0.00559930008748903</v>
       </c>
+      <c r="I69" s="1" t="n">
+        <v>0.5735</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>-0.002088045937010577</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2409,6 +2829,12 @@
       <c r="H70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>-0.009615384615384625</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2437,6 +2863,12 @@
       <c r="H71" s="3" t="n">
         <v>0.003943044906900259</v>
       </c>
+      <c r="I71" s="1" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>-0.000654593061313478</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2465,6 +2897,12 @@
       <c r="H72" s="2" t="n">
         <v>-0.01250000000000004</v>
       </c>
+      <c r="I72" s="1" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>-0.006094702297233923</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2493,6 +2931,12 @@
       <c r="H73" s="3" t="n">
         <v>0.005536037474715283</v>
       </c>
+      <c r="I73" s="1" t="n">
+        <v>0.09426</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>-0.002011646373742822</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2521,6 +2965,12 @@
       <c r="H74" s="2" t="n">
         <v>-0.003132886606909797</v>
       </c>
+      <c r="I74" s="1" t="n">
+        <v>1.1494</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.003404626800523802</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2549,6 +2999,12 @@
       <c r="H75" s="3" t="n">
         <v>0.005703422053231927</v>
       </c>
+      <c r="I75" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2577,6 +3033,12 @@
       <c r="H76" s="3" t="n">
         <v>0.005225080385852073</v>
       </c>
+      <c r="I76" s="1" t="n">
+        <v>0.12413</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>-0.007357057177129071</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2605,6 +3067,12 @@
       <c r="H77" s="3" t="n">
         <v>0.004244482173174876</v>
       </c>
+      <c r="I77" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>-0.004226542688081153</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2633,6 +3101,12 @@
       <c r="H78" s="3" t="n">
         <v>0.003968253968253945</v>
       </c>
+      <c r="I78" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>-0.0009881422924901469</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2661,6 +3135,12 @@
       <c r="H79" s="3" t="n">
         <v>0.008587304259976399</v>
       </c>
+      <c r="I79" s="1" t="n">
+        <v>0.005984</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>-0.001001669449081791</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2689,6 +3169,12 @@
       <c r="H80" s="3" t="n">
         <v>0.003186665032479468</v>
       </c>
+      <c r="I80" s="1" t="n">
+        <v>0.008206</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.00256566890653637</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2717,6 +3203,12 @@
       <c r="H81" s="3" t="n">
         <v>0.003939223410241997</v>
       </c>
+      <c r="I81" s="1" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>-0.0005605381165920158</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2745,6 +3237,12 @@
       <c r="H82" s="3" t="n">
         <v>0.009357454772301942</v>
       </c>
+      <c r="I82" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>-0.003090234857849199</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2773,6 +3271,12 @@
       <c r="H83" s="3" t="n">
         <v>0.004647181117769385</v>
       </c>
+      <c r="I83" s="1" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>-0.002434570906877611</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2801,6 +3305,12 @@
       <c r="H84" s="3" t="n">
         <v>0.001026313538786138</v>
       </c>
+      <c r="I84" s="1" t="n">
+        <v>351.65</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.001480932987782251</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2829,6 +3339,12 @@
       <c r="H85" s="3" t="n">
         <v>0.004786979415988523</v>
       </c>
+      <c r="I85" s="1" t="n">
+        <v>0.004165</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>-0.007860886136255369</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2857,6 +3373,12 @@
       <c r="H86" s="2" t="n">
         <v>-0.005997900734742804</v>
       </c>
+      <c r="I86" s="1" t="n">
+        <v>0.13299</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.003092472469452359</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2885,6 +3407,12 @@
       <c r="H87" s="2" t="n">
         <v>-0.004119464469618961</v>
       </c>
+      <c r="I87" s="1" t="n">
+        <v>0.02031</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.0501551189245089</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2913,6 +3441,12 @@
       <c r="H88" s="3" t="n">
         <v>0.005347593582887507</v>
       </c>
+      <c r="I88" s="1" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>-0.0008865248226949379</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2941,6 +3475,12 @@
       <c r="H89" s="3" t="n">
         <v>0.00270270270270278</v>
       </c>
+      <c r="I89" s="1" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>-0.001684636118598384</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2969,6 +3509,12 @@
       <c r="H90" s="3" t="n">
         <v>0.005870841487279848</v>
       </c>
+      <c r="I90" s="1" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.0003891050583657159</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2997,6 +3543,12 @@
       <c r="H91" s="2" t="n">
         <v>-0.00189786059351275</v>
       </c>
+      <c r="I91" s="1" t="n">
+        <v>0.05753</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>-0.005531547104580827</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3025,6 +3577,12 @@
       <c r="H92" s="3" t="n">
         <v>0.003441156228492734</v>
       </c>
+      <c r="I92" s="1" t="n">
+        <v>1.3105</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>-0.001295534217344943</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3053,6 +3611,12 @@
       <c r="H93" s="3" t="n">
         <v>0.004140786749482344</v>
       </c>
+      <c r="I93" s="1" t="n">
+        <v>0.06306</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0.0001586042823157811</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3081,6 +3645,12 @@
       <c r="H94" s="2" t="n">
         <v>-0.001122334455667743</v>
       </c>
+      <c r="I94" s="1" t="n">
+        <v>0.00889</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>-0.001123595505617932</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3109,6 +3679,12 @@
       <c r="H95" s="3" t="n">
         <v>0.007235453723243935</v>
       </c>
+      <c r="I95" s="1" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>-0.003891050583657657</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3137,6 +3713,12 @@
       <c r="H96" s="3" t="n">
         <v>0.005747126436781528</v>
       </c>
+      <c r="I96" s="1" t="n">
+        <v>0.02273</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>-0.0008791208791208433</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3165,6 +3747,12 @@
       <c r="H97" s="3" t="n">
         <v>0.003364943407769943</v>
       </c>
+      <c r="I97" s="1" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>-0.002439024390243851</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3193,6 +3781,12 @@
       <c r="H98" s="3" t="n">
         <v>0.01004566210045673</v>
       </c>
+      <c r="I98" s="1" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>-0.003616636528028936</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3221,6 +3815,12 @@
       <c r="H99" s="3" t="n">
         <v>0.006026113157013657</v>
       </c>
+      <c r="I99" s="1" t="n">
+        <v>3.001</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>-0.001331114808652248</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3249,6 +3849,12 @@
       <c r="H100" s="3" t="n">
         <v>0.005229517722254492</v>
       </c>
+      <c r="I100" s="1" t="n">
+        <v>0.03448</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>-0.003468208092485609</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3277,6 +3883,12 @@
       <c r="H101" s="3" t="n">
         <v>0.002751788662630773</v>
       </c>
+      <c r="I101" s="1" t="n">
+        <v>1.817</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>-0.002744237102085683</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3305,6 +3917,12 @@
       <c r="H102" s="3" t="n">
         <v>0.005590310129109593</v>
       </c>
+      <c r="I102" s="1" t="n">
+        <v>0.007437</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>-0.0156187954996691</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3333,6 +3951,12 @@
       <c r="H103" s="2" t="n">
         <v>-0.001913453046806081</v>
       </c>
+      <c r="I103" s="1" t="n">
+        <v>0.06791</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0.0014747087450229</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3361,6 +3985,12 @@
       <c r="H104" s="2" t="n">
         <v>-0.003135552339604494</v>
       </c>
+      <c r="I104" s="1" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0.002903459956448049</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3389,6 +4019,12 @@
       <c r="H105" s="3" t="n">
         <v>0.00224466891133558</v>
       </c>
+      <c r="I105" s="1" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>-0.00615901455767084</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3417,6 +4053,12 @@
       <c r="H106" s="2" t="n">
         <v>-0.0004945598417409163</v>
       </c>
+      <c r="I106" s="1" t="n">
+        <v>0.008106</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>0.002721425037110488</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3445,6 +4087,12 @@
       <c r="H107" s="3" t="n">
         <v>0.001097694840834203</v>
       </c>
+      <c r="I107" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>-0.004385964912280714</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3473,6 +4121,12 @@
       <c r="H108" s="3" t="n">
         <v>0.00751526538280885</v>
       </c>
+      <c r="I108" s="1" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0.003263403263403292</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3501,6 +4155,12 @@
       <c r="H109" s="2" t="n">
         <v>-0.001066856330014181</v>
       </c>
+      <c r="I109" s="1" t="n">
+        <v>0.05598</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>-0.003559985760056938</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3529,6 +4189,12 @@
       <c r="H110" s="3" t="n">
         <v>0.005004587538577057</v>
       </c>
+      <c r="I110" s="1" t="n">
+        <v>0.11593</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>-0.03784546435388825</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3557,6 +4223,12 @@
       <c r="H111" s="2" t="n">
         <v>-0.003934624697336577</v>
       </c>
+      <c r="I111" s="1" t="n">
+        <v>0.09854</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>-0.001924440392990942</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3585,6 +4257,12 @@
       <c r="H112" s="3" t="n">
         <v>0.00268817204301083</v>
       </c>
+      <c r="I112" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>-0.005361930294906134</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3613,6 +4291,12 @@
       <c r="H113" s="3" t="n">
         <v>0.004907975460122783</v>
       </c>
+      <c r="I113" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>-0.000814000814000922</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3641,6 +4325,12 @@
       <c r="H114" s="2" t="n">
         <v>-0.01100811123986103</v>
       </c>
+      <c r="I114" s="1" t="n">
+        <v>0.001602</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>-0.06151142355008791</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3669,6 +4359,12 @@
       <c r="H115" s="3" t="n">
         <v>0.006957365908906998</v>
       </c>
+      <c r="I115" s="1" t="n">
+        <v>1.2484</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0.002972603840282829</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3697,6 +4393,12 @@
       <c r="H116" s="3" t="n">
         <v>0.00167574361122753</v>
       </c>
+      <c r="I116" s="1" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>-0.003764115432873325</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3725,6 +4427,12 @@
       <c r="H117" s="3" t="n">
         <v>0.005910359546872422</v>
       </c>
+      <c r="I117" s="1" t="n">
+        <v>0.06074</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>-0.008650236657417917</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3753,6 +4461,12 @@
       <c r="H118" s="3" t="n">
         <v>0.01923968474733436</v>
       </c>
+      <c r="I118" s="1" t="n">
+        <v>0.04435</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0.00864225608369339</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3781,6 +4495,12 @@
       <c r="H119" s="2" t="n">
         <v>-0.007099658164606919</v>
       </c>
+      <c r="I119" s="1" t="n">
+        <v>0.003756</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>-0.00529661016949154</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3809,6 +4529,12 @@
       <c r="H120" s="3" t="n">
         <v>0.00253807106598985</v>
       </c>
+      <c r="I120" s="1" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>-0.003797468354430383</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3837,6 +4563,12 @@
       <c r="H121" s="3" t="n">
         <v>0.005067567567567572</v>
       </c>
+      <c r="I121" s="1" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0.00201680672268904</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3865,6 +4597,12 @@
       <c r="H122" s="3" t="n">
         <v>0.004915730337078695</v>
       </c>
+      <c r="I122" s="1" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0.003144654088050356</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3893,6 +4631,12 @@
       <c r="H123" s="2" t="n">
         <v>-0.008113520232012122</v>
       </c>
+      <c r="I123" s="1" t="n">
+        <v>0.028693</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>-0.001253089212990404</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3921,6 +4665,12 @@
       <c r="H124" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I124" s="1" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>-0.006823351023502638</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3949,6 +4699,12 @@
       <c r="H125" s="3" t="n">
         <v>0.008268530367162059</v>
       </c>
+      <c r="I125" s="1" t="n">
+        <v>0.10227</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>-0.001562042370399233</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3977,6 +4733,12 @@
       <c r="H126" s="3" t="n">
         <v>0.001830831197363529</v>
       </c>
+      <c r="I126" s="1" t="n">
+        <v>0.02742</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0.002192982456140388</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4005,6 +4767,12 @@
       <c r="H127" s="3" t="n">
         <v>0.003160270880361202</v>
       </c>
+      <c r="I127" s="1" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>-0.008550855085508515</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4033,6 +4801,12 @@
       <c r="H128" s="3" t="n">
         <v>0.004975124378109422</v>
       </c>
+      <c r="I128" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4061,6 +4835,12 @@
       <c r="H129" s="2" t="n">
         <v>-0.009615384615384583</v>
       </c>
+      <c r="I129" s="1" t="n">
+        <v>0.13823</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>0.03233756534727409</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4089,6 +4869,12 @@
       <c r="H130" s="2" t="n">
         <v>-0.001050943083135157</v>
       </c>
+      <c r="I130" s="1" t="n">
+        <v>0.054199</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.0003506829088224102</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4117,6 +4903,12 @@
       <c r="H131" s="3" t="n">
         <v>0.007241929544617568</v>
       </c>
+      <c r="I131" s="1" t="n">
+        <v>0.08184</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>-0.002680965147453058</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4145,6 +4937,12 @@
       <c r="H132" s="3" t="n">
         <v>0.008101851851851763</v>
       </c>
+      <c r="I132" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>-0.001148105625717599</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4173,6 +4971,12 @@
       <c r="H133" s="3" t="n">
         <v>0.001380977041256537</v>
       </c>
+      <c r="I133" s="1" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>0.000517152215135456</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4201,6 +5005,12 @@
       <c r="H134" s="3" t="n">
         <v>0.005595786701777485</v>
       </c>
+      <c r="I134" s="1" t="n">
+        <v>0.03038</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>-0.005564648117839607</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4229,6 +5039,12 @@
       <c r="H135" s="3" t="n">
         <v>0.007932011331444829</v>
       </c>
+      <c r="I135" s="1" t="n">
+        <v>0.01771</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>-0.004496908375491861</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4257,6 +5073,12 @@
       <c r="H136" s="3" t="n">
         <v>0.002430461787739665</v>
       </c>
+      <c r="I136" s="1" t="n">
+        <v>0.03695</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>-0.004579741379310439</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4285,6 +5107,12 @@
       <c r="H137" s="3" t="n">
         <v>0.007060572277963553</v>
       </c>
+      <c r="I137" s="1" t="n">
+        <v>0.02696</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>-0.005166051660516523</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4313,6 +5141,12 @@
       <c r="H138" s="3" t="n">
         <v>0.006846556584776441</v>
       </c>
+      <c r="I138" s="1" t="n">
+        <v>2.496</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>-0.001600000000000001</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4341,6 +5175,12 @@
       <c r="H139" s="3" t="n">
         <v>0.003358522250209916</v>
       </c>
+      <c r="I139" s="1" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>-0.004184100418410016</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4369,6 +5209,12 @@
       <c r="H140" s="3" t="n">
         <v>0.005294506949040385</v>
       </c>
+      <c r="I140" s="1" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4397,6 +5243,12 @@
       <c r="H141" s="3" t="n">
         <v>0.004986909362922222</v>
       </c>
+      <c r="I141" s="1" t="n">
+        <v>16.101</v>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>-0.001302567919613001</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4425,6 +5277,12 @@
       <c r="H142" s="3" t="n">
         <v>0.0008038585209002888</v>
       </c>
+      <c r="I142" s="1" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="J142" s="3" t="n">
+        <v>0.0008032128514057291</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4453,6 +5311,12 @@
       <c r="H143" s="3" t="n">
         <v>0.009844755774327899</v>
       </c>
+      <c r="I143" s="1" t="n">
+        <v>0.02667</v>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4481,6 +5345,12 @@
       <c r="H144" s="2" t="n">
         <v>-0.003003003003003029</v>
       </c>
+      <c r="I144" s="1" t="n">
+        <v>0.004656</v>
+      </c>
+      <c r="J144" s="3" t="n">
+        <v>0.001721170395869233</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4509,6 +5379,12 @@
       <c r="H145" s="3" t="n">
         <v>0.003624100266774095</v>
       </c>
+      <c r="I145" s="1" t="n">
+        <v>1.9902</v>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>-0.001855659762274957</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4537,6 +5413,12 @@
       <c r="H146" s="3" t="n">
         <v>0.005235602094240927</v>
       </c>
+      <c r="I146" s="1" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>0.00260416666666656</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4565,6 +5447,12 @@
       <c r="H147" s="2" t="n">
         <v>-0.0026637069922309</v>
       </c>
+      <c r="I147" s="1" t="n">
+        <v>0.09021</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>0.003894947696416683</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4593,6 +5481,12 @@
       <c r="H148" s="3" t="n">
         <v>0.009602649006622469</v>
       </c>
+      <c r="I148" s="1" t="n">
+        <v>0.05995</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>-0.01689078386356176</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4621,6 +5515,12 @@
       <c r="H149" s="3" t="n">
         <v>0.00304981362250084</v>
       </c>
+      <c r="I149" s="1" t="n">
+        <v>0.05914</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>-0.001013513513513589</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4649,6 +5549,12 @@
       <c r="H150" s="2" t="n">
         <v>-0.0002805161497155345</v>
       </c>
+      <c r="I150" s="1" t="n">
+        <v>0.24788</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>-0.006373511845111669</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4677,6 +5583,12 @@
       <c r="H151" s="3" t="n">
         <v>0.008944543828264774</v>
       </c>
+      <c r="I151" s="1" t="n">
+        <v>6.749000000000001e-05</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>-0.002807328605200894</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4705,6 +5617,12 @@
       <c r="H152" s="3" t="n">
         <v>0.005215419501133842</v>
       </c>
+      <c r="I152" s="1" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>0.001127904353710681</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4733,6 +5651,12 @@
       <c r="H153" s="2" t="n">
         <v>-0.001952489424015766</v>
       </c>
+      <c r="I153" s="1" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>-0.00228236061297678</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4761,6 +5685,12 @@
       <c r="H154" s="2" t="n">
         <v>-0.007850568489442376</v>
       </c>
+      <c r="I154" s="1" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>0.002455661664392938</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4789,6 +5719,12 @@
       <c r="H155" s="3" t="n">
         <v>0.004342162396873647</v>
       </c>
+      <c r="I155" s="1" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>0.005188067444876812</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4817,6 +5753,12 @@
       <c r="H156" s="2" t="n">
         <v>-0.005042430205386714</v>
       </c>
+      <c r="I156" s="1" t="n">
+        <v>0.08085000000000001</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>-0.0006180469715697713</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4845,6 +5787,12 @@
       <c r="H157" s="2" t="n">
         <v>-0.005351316075701583</v>
       </c>
+      <c r="I157" s="1" t="n">
+        <v>0.22765</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>-0.004242848394716117</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4873,6 +5821,12 @@
       <c r="H158" s="3" t="n">
         <v>0.003615910004017614</v>
       </c>
+      <c r="I158" s="1" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>-0.001601281024819791</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4901,6 +5855,12 @@
       <c r="H159" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I159" s="1" t="n">
+        <v>2.927</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>-0.003065395095367812</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4929,6 +5889,12 @@
       <c r="H160" s="3" t="n">
         <v>0.00100100100100103</v>
       </c>
+      <c r="I160" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>0.01399999999999998</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4957,6 +5923,12 @@
       <c r="H161" s="3" t="n">
         <v>0.0002052966536645606</v>
       </c>
+      <c r="I161" s="1" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>0.001642036124794678</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4985,6 +5957,12 @@
       <c r="H162" s="3" t="n">
         <v>0.003066544004906478</v>
       </c>
+      <c r="I162" s="1" t="n">
+        <v>0.003265</v>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>-0.001834301436869437</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5013,6 +5991,12 @@
       <c r="H163" s="3" t="n">
         <v>0.004224502112251094</v>
       </c>
+      <c r="I163" s="1" t="n">
+        <v>0.004978</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>-0.002804487179487204</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5041,6 +6025,12 @@
       <c r="H164" s="3" t="n">
         <v>0.007314524555903932</v>
       </c>
+      <c r="I164" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>-0.006224066390041528</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5069,6 +6059,12 @@
       <c r="H165" s="3" t="n">
         <v>0.01151315789473685</v>
       </c>
+      <c r="I165" s="1" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>-0.002276422764227572</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5097,6 +6093,12 @@
       <c r="H166" s="3" t="n">
         <v>0.004978714192943307</v>
       </c>
+      <c r="I166" s="1" t="n">
+        <v>1.3919</v>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>-0.0006461803561172623</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5125,6 +6127,12 @@
       <c r="H167" s="3" t="n">
         <v>0.004338394793926171</v>
       </c>
+      <c r="I167" s="1" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>-0.001439884809215304</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5153,6 +6161,12 @@
       <c r="H168" s="3" t="n">
         <v>0.003184713375796181</v>
       </c>
+      <c r="I168" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>-0.003174603174603177</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5181,6 +6195,12 @@
       <c r="H169" s="3" t="n">
         <v>0.007817811012916301</v>
       </c>
+      <c r="I169" s="1" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>-0.001686340640809375</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5209,6 +6229,12 @@
       <c r="H170" s="2" t="n">
         <v>-0.008614826569938909</v>
       </c>
+      <c r="I170" s="1" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="J170" s="3" t="n">
+        <v>0.0006860278984679224</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5237,6 +6263,12 @@
       <c r="H171" s="3" t="n">
         <v>0.006060606060606023</v>
       </c>
+      <c r="I171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5265,6 +6297,12 @@
       <c r="H172" s="3" t="n">
         <v>0.008264462809917416</v>
       </c>
+      <c r="I172" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="J172" s="3" t="n">
+        <v>0.02459016393442627</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5293,6 +6331,12 @@
       <c r="H173" s="3" t="n">
         <v>0.007166746297181119</v>
       </c>
+      <c r="I173" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>-0.0004743833017079251</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5321,6 +6365,12 @@
       <c r="H174" s="3" t="n">
         <v>0.002551303383250227</v>
       </c>
+      <c r="I174" s="1" t="n">
+        <v>0.09019000000000001</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>-0.002102235007745029</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5349,6 +6399,12 @@
       <c r="H175" s="3" t="n">
         <v>0.008368200836820092</v>
       </c>
+      <c r="I175" s="1" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>-0.001106500691562964</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5377,6 +6433,12 @@
       <c r="H176" s="3" t="n">
         <v>0.001864801864801789</v>
       </c>
+      <c r="I176" s="1" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>-0.0004653327128896972</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5405,6 +6467,12 @@
       <c r="H177" s="3" t="n">
         <v>0.005025125628140717</v>
       </c>
+      <c r="I177" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5433,6 +6501,12 @@
       <c r="H178" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I178" s="1" t="n">
+        <v>0.000977</v>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>-0.003061224489795882</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5461,6 +6535,12 @@
       <c r="H179" s="3" t="n">
         <v>0.001876827724673646</v>
       </c>
+      <c r="I179" s="1" t="n">
+        <v>0.022971</v>
+      </c>
+      <c r="J179" s="3" t="n">
+        <v>0.0007406116580987912</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5489,6 +6569,12 @@
       <c r="H180" s="2" t="n">
         <v>-0.01278538812785389</v>
       </c>
+      <c r="I180" s="1" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>-0.01665124884366329</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5517,6 +6603,12 @@
       <c r="H181" s="3" t="n">
         <v>0.005207429265752479</v>
       </c>
+      <c r="I181" s="1" t="n">
+        <v>0.5852000000000001</v>
+      </c>
+      <c r="J181" s="3" t="n">
+        <v>0.01053358659989657</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5545,6 +6637,12 @@
       <c r="H182" s="3" t="n">
         <v>0.01161605869166485</v>
       </c>
+      <c r="I182" s="1" t="n">
+        <v>0.04949</v>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>-0.003021756647864572</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5573,6 +6671,12 @@
       <c r="H183" s="3" t="n">
         <v>0.004406095098219207</v>
       </c>
+      <c r="I183" s="1" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>-0.000182781941144276</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5601,6 +6705,12 @@
       <c r="H184" s="3" t="n">
         <v>0.008104298801973235</v>
       </c>
+      <c r="I184" s="1" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>0.003844809507165307</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5629,6 +6739,12 @@
       <c r="H185" s="3" t="n">
         <v>0.01037117903930127</v>
       </c>
+      <c r="I185" s="1" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>-0.0005402485143165636</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5657,6 +6773,12 @@
       <c r="H186" s="3" t="n">
         <v>0.006369426751592512</v>
       </c>
+      <c r="I186" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>-0.006329113924050786</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5685,6 +6807,12 @@
       <c r="H187" s="3" t="n">
         <v>0.003717472118958956</v>
       </c>
+      <c r="I187" s="1" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>-0.005555555555555544</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5713,6 +6841,12 @@
       <c r="H188" s="3" t="n">
         <v>0.005468555804126223</v>
       </c>
+      <c r="I188" s="1" t="n">
+        <v>0.04037</v>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>-0.001977750309023405</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5741,6 +6875,12 @@
       <c r="H189" s="3" t="n">
         <v>0.006904487917146188</v>
       </c>
+      <c r="I189" s="1" t="n">
+        <v>0.0004366</v>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>-0.002057142857142907</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5769,6 +6909,12 @@
       <c r="H190" s="2" t="n">
         <v>-0.001742160278745725</v>
       </c>
+      <c r="I190" s="1" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>0.001745200698080359</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5797,6 +6943,12 @@
       <c r="H191" s="3" t="n">
         <v>0.004458598726114689</v>
       </c>
+      <c r="I191" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>-0.000634115409004413</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5825,6 +6977,12 @@
       <c r="H192" s="3" t="n">
         <v>0.002697356590541222</v>
       </c>
+      <c r="I192" s="1" t="n">
+        <v>0.05582</v>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>0.001076040172166508</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5853,6 +7011,12 @@
       <c r="H193" s="3" t="n">
         <v>0.005904455179817593</v>
       </c>
+      <c r="I193" s="1" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>-0.003735325506937066</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5881,6 +7045,12 @@
       <c r="H194" s="3" t="n">
         <v>0.008928571428571428</v>
       </c>
+      <c r="I194" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>-0.002602811035918867</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5909,6 +7079,12 @@
       <c r="H195" s="2" t="n">
         <v>-0.02163624070317782</v>
       </c>
+      <c r="I195" s="1" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>-0.00598940336328033</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5937,6 +7113,12 @@
       <c r="H196" s="3" t="n">
         <v>0.003984063745019896</v>
       </c>
+      <c r="I196" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>-0.0007936507936507613</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5965,6 +7147,12 @@
       <c r="H197" s="3" t="n">
         <v>0.007920792079207904</v>
       </c>
+      <c r="I197" s="1" t="n">
+        <v>0.04573</v>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>-0.001746343593101872</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5993,6 +7181,12 @@
       <c r="H198" s="2" t="n">
         <v>-0.004306126443530984</v>
       </c>
+      <c r="I198" s="1" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>0.0007863180656574718</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6021,6 +7215,12 @@
       <c r="H199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I199" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>0.0116279069767442</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6049,6 +7249,12 @@
       <c r="H200" s="3" t="n">
         <v>0.0006752194463200396</v>
       </c>
+      <c r="I200" s="1" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>-0.002024291497975785</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6077,6 +7283,12 @@
       <c r="H201" s="3" t="n">
         <v>0.0060240963855422</v>
       </c>
+      <c r="I201" s="1" t="n">
+        <v>0.005667</v>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>-0.001937301866854478</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6105,6 +7317,12 @@
       <c r="H202" s="3" t="n">
         <v>0.0009284230072063391</v>
       </c>
+      <c r="I202" s="1" t="n">
+        <v>0.022637</v>
+      </c>
+      <c r="J202" s="2" t="n">
+        <v>-0.0001325088339222408</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6133,6 +7351,12 @@
       <c r="H203" s="3" t="n">
         <v>0.01465201465201456</v>
       </c>
+      <c r="I203" s="1" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="J203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6161,6 +7385,12 @@
       <c r="H204" s="2" t="n">
         <v>-0.001171303074670523</v>
       </c>
+      <c r="I204" s="1" t="n">
+        <v>0.03393</v>
+      </c>
+      <c r="J204" s="2" t="n">
+        <v>-0.005277044854881255</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6189,6 +7419,12 @@
       <c r="H205" s="3" t="n">
         <v>0.005621925509487005</v>
       </c>
+      <c r="I205" s="1" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="J205" s="2" t="n">
+        <v>-0.000698812019566763</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6217,6 +7453,12 @@
       <c r="H206" s="3" t="n">
         <v>0.008356545961002793</v>
       </c>
+      <c r="I206" s="1" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6245,6 +7487,12 @@
       <c r="H207" s="3" t="n">
         <v>0.008743056984159572</v>
       </c>
+      <c r="I207" s="1" t="n">
+        <v>0.0009858</v>
+      </c>
+      <c r="J207" s="3" t="n">
+        <v>0.005200367084735464</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6273,6 +7521,12 @@
       <c r="H208" s="3" t="n">
         <v>0.0004110715264456561</v>
       </c>
+      <c r="I208" s="1" t="n">
+        <v>0.007295</v>
+      </c>
+      <c r="J208" s="2" t="n">
+        <v>-0.0008218052321599683</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6301,6 +7555,12 @@
       <c r="H209" s="3" t="n">
         <v>0.003344481605351151</v>
       </c>
+      <c r="I209" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6329,6 +7589,12 @@
       <c r="H210" s="3" t="n">
         <v>0.003872966692486448</v>
       </c>
+      <c r="I210" s="1" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="J210" s="2" t="n">
+        <v>-0.001543209876543254</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6357,6 +7623,12 @@
       <c r="H211" s="3" t="n">
         <v>0.007928642220019893</v>
       </c>
+      <c r="I211" s="1" t="n">
+        <v>0.007108</v>
+      </c>
+      <c r="J211" s="2" t="n">
+        <v>-0.001545160837196319</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6385,6 +7657,12 @@
       <c r="H212" s="3" t="n">
         <v>0.03285058283292114</v>
       </c>
+      <c r="I212" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="J212" s="2" t="n">
+        <v>-0.01162790697674423</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6413,6 +7691,12 @@
       <c r="H213" s="2" t="n">
         <v>-0.003129890453834109</v>
       </c>
+      <c r="I213" s="1" t="n">
+        <v>0.05715</v>
+      </c>
+      <c r="J213" s="2" t="n">
+        <v>-0.003139717425431704</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6441,6 +7725,12 @@
       <c r="H214" s="3" t="n">
         <v>0.001595744680851036</v>
       </c>
+      <c r="I214" s="1" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="J214" s="2" t="n">
+        <v>-0.001062134891131204</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6469,6 +7759,12 @@
       <c r="H215" s="3" t="n">
         <v>0.006892590465249842</v>
       </c>
+      <c r="I215" s="1" t="n">
+        <v>0.05244</v>
+      </c>
+      <c r="J215" s="2" t="n">
+        <v>-0.002852253280091222</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6497,6 +7793,12 @@
       <c r="H216" s="3" t="n">
         <v>0.005260640841702611</v>
       </c>
+      <c r="I216" s="1" t="n">
+        <v>0.002091</v>
+      </c>
+      <c r="J216" s="2" t="n">
+        <v>-0.005233111322550028</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6525,6 +7827,12 @@
       <c r="H217" s="3" t="n">
         <v>0.005168389463154333</v>
       </c>
+      <c r="I217" s="1" t="n">
+        <v>6.022</v>
+      </c>
+      <c r="J217" s="2" t="n">
+        <v>-0.001161054901310279</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6553,6 +7861,12 @@
       <c r="H218" s="2" t="n">
         <v>-0.003831417624521151</v>
       </c>
+      <c r="I218" s="1" t="n">
+        <v>4.414</v>
+      </c>
+      <c r="J218" s="2" t="n">
+        <v>-0.001357466063348468</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6581,6 +7895,12 @@
       <c r="H219" s="3" t="n">
         <v>0.005417522884363817</v>
       </c>
+      <c r="I219" s="1" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="J219" s="2" t="n">
+        <v>-0.004087699739873552</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6609,6 +7929,12 @@
       <c r="H220" s="3" t="n">
         <v>0.002186588921282794</v>
       </c>
+      <c r="I220" s="1" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="J220" s="2" t="n">
+        <v>-0.002181818181818177</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6637,6 +7963,12 @@
       <c r="H221" s="3" t="n">
         <v>0.003990284524635597</v>
       </c>
+      <c r="I221" s="1" t="n">
+        <v>0.005784</v>
+      </c>
+      <c r="J221" s="2" t="n">
+        <v>-0.0005184033177811528</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6665,6 +7997,12 @@
       <c r="H222" s="3" t="n">
         <v>0.005537098560354379</v>
       </c>
+      <c r="I222" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>-0.00220264317180623</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6693,6 +8031,12 @@
       <c r="H223" s="3" t="n">
         <v>0.005050505050504988</v>
       </c>
+      <c r="I223" s="1" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="J223" s="2" t="n">
+        <v>-0.001477978125923738</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6721,6 +8065,12 @@
       <c r="H224" s="3" t="n">
         <v>0.005331478905887734</v>
       </c>
+      <c r="I224" s="1" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="J224" s="2" t="n">
+        <v>-0.0009222965183305418</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6749,6 +8099,12 @@
       <c r="H225" s="3" t="n">
         <v>0.001681277771106055</v>
       </c>
+      <c r="I225" s="1" t="n">
+        <v>0.08346000000000001</v>
+      </c>
+      <c r="J225" s="3" t="n">
+        <v>0.000599448507373317</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6777,6 +8133,12 @@
       <c r="H226" s="2" t="n">
         <v>-0.002660989888238501</v>
       </c>
+      <c r="I226" s="1" t="n">
+        <v>0.01872</v>
+      </c>
+      <c r="J226" s="2" t="n">
+        <v>-0.001067235859124823</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6805,6 +8167,12 @@
       <c r="H227" s="3" t="n">
         <v>0.005370569280343721</v>
       </c>
+      <c r="I227" s="1" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="J227" s="2" t="n">
+        <v>-0.004273504273504248</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6833,6 +8201,12 @@
       <c r="H228" s="3" t="n">
         <v>0.001289767841788575</v>
       </c>
+      <c r="I228" s="1" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="J228" s="2" t="n">
+        <v>-0.003434950622584809</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6861,6 +8235,12 @@
       <c r="H229" s="3" t="n">
         <v>0.006535947712418358</v>
       </c>
+      <c r="I229" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="J229" s="2" t="n">
+        <v>-0.003710575139146674</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6889,6 +8269,12 @@
       <c r="H230" s="3" t="n">
         <v>0.007198560287942452</v>
       </c>
+      <c r="I230" s="1" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="J230" s="2" t="n">
+        <v>-0.004764740917212597</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6917,6 +8303,12 @@
       <c r="H231" s="3" t="n">
         <v>0.004599211563731972</v>
       </c>
+      <c r="I231" s="1" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="J231" s="2" t="n">
+        <v>-0.004578155657292388</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6945,6 +8337,12 @@
       <c r="H232" s="3" t="n">
         <v>0.005201560468140381</v>
       </c>
+      <c r="I232" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="J232" s="2" t="n">
+        <v>-0.003018542475204707</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6973,6 +8371,12 @@
       <c r="H233" s="2" t="n">
         <v>-0.05950982695168739</v>
       </c>
+      <c r="I233" s="1" t="n">
+        <v>0.12563</v>
+      </c>
+      <c r="J233" s="3" t="n">
+        <v>0.04595787195071183</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7001,6 +8405,12 @@
       <c r="H234" s="3" t="n">
         <v>0.008386581469648526</v>
       </c>
+      <c r="I234" s="1" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="J234" s="3" t="n">
+        <v>0.0003960396039603524</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7029,6 +8439,12 @@
       <c r="H235" s="3" t="n">
         <v>0.004480416245122195</v>
       </c>
+      <c r="I235" s="1" t="n">
+        <v>0.06948</v>
+      </c>
+      <c r="J235" s="2" t="n">
+        <v>-0.00028776978417275</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7057,6 +8473,12 @@
       <c r="H236" s="2" t="n">
         <v>-0.0004907975460123067</v>
       </c>
+      <c r="I236" s="1" t="n">
+        <v>0.12211</v>
+      </c>
+      <c r="J236" s="2" t="n">
+        <v>-0.0006547180620345098</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7085,6 +8507,12 @@
       <c r="H237" s="3" t="n">
         <v>0.01160337552742605</v>
       </c>
+      <c r="I237" s="1" t="n">
+        <v>0.03858</v>
+      </c>
+      <c r="J237" s="3" t="n">
+        <v>0.00573514077163725</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7113,6 +8541,12 @@
       <c r="H238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7141,6 +8575,12 @@
       <c r="H239" s="3" t="n">
         <v>0.01123595505617975</v>
       </c>
+      <c r="I239" s="1" t="n">
+        <v>0.004002</v>
+      </c>
+      <c r="J239" s="2" t="n">
+        <v>-0.01185185185185171</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7169,6 +8609,12 @@
       <c r="H240" s="3" t="n">
         <v>0.003652300949598225</v>
       </c>
+      <c r="I240" s="1" t="n">
+        <v>0.01372</v>
+      </c>
+      <c r="J240" s="2" t="n">
+        <v>-0.001455604075691479</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7197,6 +8643,12 @@
       <c r="H241" s="3" t="n">
         <v>0.005151018496839231</v>
       </c>
+      <c r="I241" s="1" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="J241" s="3" t="n">
+        <v>0.0006988120195666595</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7225,6 +8677,12 @@
       <c r="H242" s="3" t="n">
         <v>0.005449591280653966</v>
       </c>
+      <c r="I242" s="1" t="n">
+        <v>0.00738</v>
+      </c>
+      <c r="J242" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7253,6 +8711,12 @@
       <c r="H243" s="3" t="n">
         <v>0.003042155584528493</v>
       </c>
+      <c r="I243" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="J243" s="2" t="n">
+        <v>-0.001733102253032858</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7281,6 +8745,12 @@
       <c r="H244" s="3" t="n">
         <v>0.006555423122765162</v>
       </c>
+      <c r="I244" s="1" t="n">
+        <v>0.001684</v>
+      </c>
+      <c r="J244" s="2" t="n">
+        <v>-0.002960331557134407</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7309,6 +8779,12 @@
       <c r="H245" s="3" t="n">
         <v>0.004562737642585471</v>
       </c>
+      <c r="I245" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="J245" s="2" t="n">
+        <v>-0.001514004542013669</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7337,6 +8813,12 @@
       <c r="H246" s="2" t="n">
         <v>-0.002544529262086631</v>
       </c>
+      <c r="I246" s="1" t="n">
+        <v>0.03175</v>
+      </c>
+      <c r="J246" s="3" t="n">
+        <v>0.01243622448979597</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7365,6 +8847,12 @@
       <c r="H247" s="3" t="n">
         <v>0.003939223410242016</v>
       </c>
+      <c r="I247" s="1" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="J247" s="2" t="n">
+        <v>-0.004484304932735399</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7393,6 +8881,12 @@
       <c r="H248" s="3" t="n">
         <v>0.01085526315789475</v>
       </c>
+      <c r="I248" s="1" t="n">
+        <v>0.03071</v>
+      </c>
+      <c r="J248" s="2" t="n">
+        <v>-0.0006508298080051801</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7421,6 +8915,12 @@
       <c r="H249" s="3" t="n">
         <v>0.01240201240201222</v>
       </c>
+      <c r="I249" s="1" t="n">
+        <v>0.008697999999999999</v>
+      </c>
+      <c r="J249" s="3" t="n">
+        <v>0.005200508494163863</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7449,6 +8949,12 @@
       <c r="H250" s="3" t="n">
         <v>0.00815347721822542</v>
       </c>
+      <c r="I250" s="1" t="n">
+        <v>0.02077</v>
+      </c>
+      <c r="J250" s="2" t="n">
+        <v>-0.01189343482397717</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7477,6 +8983,12 @@
       <c r="H251" s="3" t="n">
         <v>0.002138579982891273</v>
       </c>
+      <c r="I251" s="1" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="J251" s="2" t="n">
+        <v>-0.001707212974818539</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7505,6 +9017,12 @@
       <c r="H252" s="3" t="n">
         <v>0.01104044161766471</v>
       </c>
+      <c r="I252" s="1" t="n">
+        <v>0.008397999999999999</v>
+      </c>
+      <c r="J252" s="2" t="n">
+        <v>-0.003204747774480828</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7533,6 +9051,12 @@
       <c r="H253" s="3" t="n">
         <v>0.005836082212636413</v>
       </c>
+      <c r="I253" s="1" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="J253" s="2" t="n">
+        <v>-0.03380423814328963</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7561,6 +9085,12 @@
       <c r="H254" s="3" t="n">
         <v>0.003444316877152614</v>
       </c>
+      <c r="I254" s="1" t="n">
+        <v>0.06117</v>
+      </c>
+      <c r="J254" s="2" t="n">
+        <v>-0.0001634521085321367</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7589,6 +9119,12 @@
       <c r="H255" s="2" t="n">
         <v>-0.01359223300970874</v>
       </c>
+      <c r="I255" s="1" t="n">
+        <v>0.003578</v>
+      </c>
+      <c r="J255" s="3" t="n">
+        <v>0.006186726659167571</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7617,6 +9153,12 @@
       <c r="H256" s="3" t="n">
         <v>0.004729575101075563</v>
       </c>
+      <c r="I256" s="1" t="n">
+        <v>0.01324</v>
+      </c>
+      <c r="J256" s="3" t="n">
+        <v>0.005238782172955707</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7645,6 +9187,12 @@
       <c r="H257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I257" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="J257" s="2" t="n">
+        <v>-1.000626392150242e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7673,6 +9221,12 @@
       <c r="H258" s="2" t="n">
         <v>-0.001513211500407463</v>
       </c>
+      <c r="I258" s="1" t="n">
+        <v>0.08629000000000001</v>
+      </c>
+      <c r="J258" s="3" t="n">
+        <v>0.005945441827932041</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7701,6 +9255,12 @@
       <c r="H259" s="2" t="n">
         <v>-0.001340931947703599</v>
       </c>
+      <c r="I259" s="1" t="n">
+        <v>0.08921</v>
+      </c>
+      <c r="J259" s="2" t="n">
+        <v>-0.001790309947409728</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7729,6 +9289,12 @@
       <c r="H260" s="3" t="n">
         <v>0.01407059985188845</v>
       </c>
+      <c r="I260" s="1" t="n">
+        <v>0.08144999999999999</v>
+      </c>
+      <c r="J260" s="2" t="n">
+        <v>-0.008641674780915315</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7757,6 +9323,12 @@
       <c r="H261" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I261" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="J261" s="3" t="n">
+        <v>0.002680965147453185</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7785,6 +9357,12 @@
       <c r="H262" s="3" t="n">
         <v>0.008509470216854298</v>
       </c>
+      <c r="I262" s="1" t="n">
+        <v>0.003692</v>
+      </c>
+      <c r="J262" s="3" t="n">
+        <v>0.004899292324441967</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7813,6 +9391,12 @@
       <c r="H263" s="2" t="n">
         <v>-0.0008488964346349988</v>
       </c>
+      <c r="I263" s="1" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="J263" s="2" t="n">
+        <v>-0.001699235344095206</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7841,6 +9425,12 @@
       <c r="H264" s="3" t="n">
         <v>0.007004027315706702</v>
       </c>
+      <c r="I264" s="1" t="n">
+        <v>0.000575</v>
+      </c>
+      <c r="J264" s="2" t="n">
+        <v>-0.0001738828029908827</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7869,6 +9459,12 @@
       <c r="H265" s="3" t="n">
         <v>0.001329787234042614</v>
       </c>
+      <c r="I265" s="1" t="n">
+        <v>0.01498</v>
+      </c>
+      <c r="J265" s="2" t="n">
+        <v>-0.005312084993359907</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7897,6 +9493,12 @@
       <c r="H266" s="3" t="n">
         <v>0.003149606299212689</v>
       </c>
+      <c r="I266" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="J266" s="2" t="n">
+        <v>-0.0015698587127159</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7925,6 +9527,12 @@
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I267" s="1" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="J267" s="2" t="n">
+        <v>-0.0006086427267193909</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7953,6 +9561,12 @@
       <c r="H268" s="3" t="n">
         <v>0.006572769953051676</v>
       </c>
+      <c r="I268" s="1" t="n">
+        <v>0.0004275</v>
+      </c>
+      <c r="J268" s="2" t="n">
+        <v>-0.003031716417910522</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7981,6 +9595,12 @@
       <c r="H269" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I269" s="1" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="J269" s="3" t="n">
+        <v>0.0004803073967338901</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8009,6 +9629,12 @@
       <c r="H270" s="3" t="n">
         <v>0.007812500000000069</v>
       </c>
+      <c r="I270" s="1" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="J270" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8037,6 +9663,12 @@
       <c r="H271" s="3" t="n">
         <v>0.003419972640218881</v>
       </c>
+      <c r="I271" s="1" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="J271" s="2" t="n">
+        <v>-0.0006816632583502998</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8065,6 +9697,12 @@
       <c r="H272" s="3" t="n">
         <v>0.002783400809716573</v>
       </c>
+      <c r="I272" s="1" t="n">
+        <v>0.03967</v>
+      </c>
+      <c r="J272" s="3" t="n">
+        <v>0.001009336361342376</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8093,6 +9731,12 @@
       <c r="H273" s="3" t="n">
         <v>0.006479481641468688</v>
       </c>
+      <c r="I273" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="J273" s="3" t="n">
+        <v>0.001072961373390559</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8121,6 +9765,12 @@
       <c r="H274" s="3" t="n">
         <v>0.002536461636017814</v>
       </c>
+      <c r="I274" s="1" t="n">
+        <v>63.28</v>
+      </c>
+      <c r="J274" s="3" t="n">
+        <v>0.000632511068943693</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8149,6 +9799,12 @@
       <c r="H275" s="3" t="n">
         <v>0.005217391304347915</v>
       </c>
+      <c r="I275" s="1" t="n">
+        <v>0.01152</v>
+      </c>
+      <c r="J275" s="2" t="n">
+        <v>-0.003460207612456756</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8177,6 +9833,12 @@
       <c r="H276" s="3" t="n">
         <v>0.004642166344294008</v>
       </c>
+      <c r="I276" s="1" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J276" s="2" t="n">
+        <v>-0.002695417789757458</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8205,6 +9867,12 @@
       <c r="H277" s="3" t="n">
         <v>0.006217120994739271</v>
       </c>
+      <c r="I277" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J277" s="2" t="n">
+        <v>-0.001901140684410569</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8233,6 +9901,12 @@
       <c r="H278" s="3" t="n">
         <v>0.01054852320675099</v>
       </c>
+      <c r="I278" s="1" t="n">
+        <v>0.01913</v>
+      </c>
+      <c r="J278" s="2" t="n">
+        <v>-0.001565762004175302</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8261,6 +9935,12 @@
       <c r="H279" s="2" t="n">
         <v>-0.01114846929746942</v>
       </c>
+      <c r="I279" s="1" t="n">
+        <v>0.005611</v>
+      </c>
+      <c r="J279" s="3" t="n">
+        <v>0.004115962777380026</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8289,6 +9969,12 @@
       <c r="H280" s="3" t="n">
         <v>0.006051039200210498</v>
       </c>
+      <c r="I280" s="1" t="n">
+        <v>0.03839</v>
+      </c>
+      <c r="J280" s="3" t="n">
+        <v>0.003922594142259345</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8317,6 +10003,12 @@
       <c r="H281" s="3" t="n">
         <v>0.003333333333333336</v>
       </c>
+      <c r="I281" s="1" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="J281" s="2" t="n">
+        <v>-0.001107419712070876</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8345,6 +10037,12 @@
       <c r="H282" s="3" t="n">
         <v>0.003998000999500212</v>
       </c>
+      <c r="I282" s="1" t="n">
+        <v>0.0004006</v>
+      </c>
+      <c r="J282" s="2" t="n">
+        <v>-0.002986560477849749</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8373,6 +10071,12 @@
       <c r="H283" s="3" t="n">
         <v>0.004071246819338433</v>
       </c>
+      <c r="I283" s="1" t="n">
+        <v>0.03952</v>
+      </c>
+      <c r="J283" s="3" t="n">
+        <v>0.001520527116066841</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8401,6 +10105,12 @@
       <c r="H284" s="3" t="n">
         <v>0.007208073041806864</v>
       </c>
+      <c r="I284" s="1" t="n">
+        <v>0.04181</v>
+      </c>
+      <c r="J284" s="2" t="n">
+        <v>-0.002624045801526693</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8429,6 +10139,12 @@
       <c r="H285" s="2" t="n">
         <v>-0.001955671447196888</v>
       </c>
+      <c r="I285" s="1" t="n">
+        <v>0.10778</v>
+      </c>
+      <c r="J285" s="3" t="n">
+        <v>0.005691891387515157</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -8457,6 +10173,12 @@
       <c r="H286" s="3" t="n">
         <v>0.009661835748792296</v>
       </c>
+      <c r="I286" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="J286" s="2" t="n">
+        <v>-0.002392344497607558</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -8485,6 +10207,12 @@
       <c r="H287" s="2" t="n">
         <v>-0.0001980459466596399</v>
       </c>
+      <c r="I287" s="1" t="n">
+        <v>0.15114</v>
+      </c>
+      <c r="J287" s="2" t="n">
+        <v>-0.002046880158468172</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8513,6 +10241,12 @@
       <c r="H288" s="2" t="n">
         <v>-0.001642036124794717</v>
       </c>
+      <c r="I288" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="J288" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8541,6 +10275,12 @@
       <c r="H289" s="3" t="n">
         <v>0.003637245392822641</v>
       </c>
+      <c r="I289" s="1" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="J289" s="2" t="n">
+        <v>-0.002174438270113636</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8569,6 +10309,12 @@
       <c r="H290" s="3" t="n">
         <v>0.00519051551256336</v>
       </c>
+      <c r="I290" s="1" t="n">
+        <v>0.08501</v>
+      </c>
+      <c r="J290" s="2" t="n">
+        <v>-0.002347142354183686</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8597,6 +10343,12 @@
       <c r="H291" s="3" t="n">
         <v>0.00255102040816326</v>
       </c>
+      <c r="I291" s="1" t="n">
+        <v>0.03544</v>
+      </c>
+      <c r="J291" s="3" t="n">
+        <v>0.001979078314956195</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8625,6 +10377,12 @@
       <c r="H292" s="2" t="n">
         <v>-0.002252098546372811</v>
       </c>
+      <c r="I292" s="1" t="n">
+        <v>1.4554</v>
+      </c>
+      <c r="J292" s="2" t="n">
+        <v>-0.004514363885088878</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8653,6 +10411,12 @@
       <c r="H293" s="3" t="n">
         <v>0.00651019359259891</v>
       </c>
+      <c r="I293" s="1" t="n">
+        <v>0.005863</v>
+      </c>
+      <c r="J293" s="2" t="n">
+        <v>-0.002042553191489337</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8681,6 +10445,12 @@
       <c r="H294" s="3" t="n">
         <v>0.0002911208151381948</v>
       </c>
+      <c r="I294" s="1" t="n">
+        <v>0.003427</v>
+      </c>
+      <c r="J294" s="2" t="n">
+        <v>-0.002619324796274707</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8709,6 +10479,12 @@
       <c r="H295" s="3" t="n">
         <v>0.003914259086672863</v>
       </c>
+      <c r="I295" s="1" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="J295" s="2" t="n">
+        <v>-0.001485332343111814</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8737,6 +10513,12 @@
       <c r="H296" s="3" t="n">
         <v>0.004017857142857096</v>
       </c>
+      <c r="I296" s="1" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="J296" s="2" t="n">
+        <v>-0.000444642063139124</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -8765,6 +10547,12 @@
       <c r="H297" s="3" t="n">
         <v>0.002359882005899813</v>
       </c>
+      <c r="I297" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J297" s="3" t="n">
+        <v>0.0005885815185402938</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -8793,6 +10581,12 @@
       <c r="H298" s="2" t="n">
         <v>-0.005505092210294527</v>
       </c>
+      <c r="I298" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="J298" s="2" t="n">
+        <v>-0.000276778300581204</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -8821,6 +10615,12 @@
       <c r="H299" s="3" t="n">
         <v>0.003613369467028013</v>
       </c>
+      <c r="I299" s="1" t="n">
+        <v>0.01107</v>
+      </c>
+      <c r="J299" s="2" t="n">
+        <v>-0.00360036003600361</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -8849,6 +10649,12 @@
       <c r="H300" s="3" t="n">
         <v>0.003861003861003872</v>
       </c>
+      <c r="I300" s="1" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="J300" s="2" t="n">
+        <v>-0.002403846153846056</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -8877,6 +10683,12 @@
       <c r="H301" s="2" t="n">
         <v>-0.000331235508446469</v>
       </c>
+      <c r="I301" s="1" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="J301" s="2" t="n">
+        <v>-0.0006626905235256245</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -8905,6 +10717,12 @@
       <c r="H302" s="3" t="n">
         <v>0.004441154700222134</v>
       </c>
+      <c r="I302" s="1" t="n">
+        <v>0.01356</v>
+      </c>
+      <c r="J302" s="2" t="n">
+        <v>-0.0007369196757554405</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -8933,6 +10751,12 @@
       <c r="H303" s="3" t="n">
         <v>0.0008123476848091592</v>
       </c>
+      <c r="I303" s="1" t="n">
+        <v>0.07388</v>
+      </c>
+      <c r="J303" s="2" t="n">
+        <v>-0.0005411255411255191</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -8961,6 +10785,12 @@
       <c r="H304" s="3" t="n">
         <v>0.003771213073538719</v>
       </c>
+      <c r="I304" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="J304" s="2" t="n">
+        <v>-0.001878522229179852</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -8989,6 +10819,12 @@
       <c r="H305" s="2" t="n">
         <v>-0.002753556677374937</v>
       </c>
+      <c r="I305" s="1" t="n">
+        <v>0.06501999999999999</v>
+      </c>
+      <c r="J305" s="2" t="n">
+        <v>-0.002607761926675924</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9017,6 +10853,12 @@
       <c r="H306" s="3" t="n">
         <v>0.00579768092762892</v>
       </c>
+      <c r="I306" s="1" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="J306" s="2" t="n">
+        <v>-0.005366726296958843</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9045,6 +10887,12 @@
       <c r="H307" s="2" t="n">
         <v>-0.00107181136120043</v>
       </c>
+      <c r="I307" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J307" s="2" t="n">
+        <v>-0.002145922746781118</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -9073,6 +10921,12 @@
       <c r="H308" s="3" t="n">
         <v>0.0005036514731805385</v>
       </c>
+      <c r="I308" s="1" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="J308" s="2" t="n">
+        <v>-0.003523785552479266</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -9101,6 +10955,12 @@
       <c r="H309" s="3" t="n">
         <v>0.01074589127686473</v>
       </c>
+      <c r="I309" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="J309" s="2" t="n">
+        <v>-0.001250781738586566</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -9129,6 +10989,12 @@
       <c r="H310" s="3" t="n">
         <v>0.004629629629629634</v>
       </c>
+      <c r="I310" s="1" t="n">
+        <v>0.05411</v>
+      </c>
+      <c r="J310" s="2" t="n">
+        <v>-0.002580645161290346</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -9157,6 +11023,12 @@
       <c r="H311" s="2" t="n">
         <v>-0.0004458314757022437</v>
       </c>
+      <c r="I311" s="1" t="n">
+        <v>0.004461</v>
+      </c>
+      <c r="J311" s="2" t="n">
+        <v>-0.005129348795718209</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -9185,6 +11057,12 @@
       <c r="H312" s="3" t="n">
         <v>0.00249169435215949</v>
       </c>
+      <c r="I312" s="1" t="n">
+        <v>0.08438</v>
+      </c>
+      <c r="J312" s="2" t="n">
+        <v>-0.001301929222393171</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -9213,6 +11091,12 @@
       <c r="H313" s="3" t="n">
         <v>0.004156053090226449</v>
       </c>
+      <c r="I313" s="1" t="n">
+        <v>0.07493</v>
+      </c>
+      <c r="J313" s="3" t="n">
+        <v>0.0004005340453938885</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -9241,6 +11125,12 @@
       <c r="H314" s="3" t="n">
         <v>0.003926701570680741</v>
       </c>
+      <c r="I314" s="1" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="J314" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -9269,6 +11159,12 @@
       <c r="H315" s="3" t="n">
         <v>0.00502828409805151</v>
       </c>
+      <c r="I315" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="J315" s="2" t="n">
+        <v>-0.0006253908692932395</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -9297,6 +11193,12 @@
       <c r="H316" s="3" t="n">
         <v>0.007234279354479664</v>
       </c>
+      <c r="I316" s="1" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="J316" s="2" t="n">
+        <v>-0.003314917127071765</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -9325,6 +11227,12 @@
       <c r="H317" s="3" t="n">
         <v>0.004249667994687903</v>
       </c>
+      <c r="I317" s="1" t="n">
+        <v>0.007541</v>
+      </c>
+      <c r="J317" s="2" t="n">
+        <v>-0.002777043110288308</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -9353,6 +11261,12 @@
       <c r="H318" s="2" t="n">
         <v>-0.003401360544217618</v>
       </c>
+      <c r="I318" s="1" t="n">
+        <v>0.04965</v>
+      </c>
+      <c r="J318" s="2" t="n">
+        <v>-0.003212206384260197</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -9381,6 +11295,12 @@
       <c r="H319" s="2" t="n">
         <v>-0.002948176038077638</v>
       </c>
+      <c r="I319" s="1" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="J319" s="2" t="n">
+        <v>-0.01036693979337379</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -9409,6 +11329,12 @@
       <c r="H320" s="3" t="n">
         <v>0.004567252797442342</v>
       </c>
+      <c r="I320" s="1" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="J320" s="3" t="n">
+        <v>0.0006819731757216798</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -9437,6 +11363,12 @@
       <c r="H321" s="3" t="n">
         <v>0.01555352241537068</v>
       </c>
+      <c r="I321" s="1" t="n">
+        <v>0.07783</v>
+      </c>
+      <c r="J321" s="3" t="n">
+        <v>0.00167310167310156</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -9465,6 +11397,12 @@
       <c r="H322" s="3" t="n">
         <v>0.005548705302096079</v>
       </c>
+      <c r="I322" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="J322" s="2" t="n">
+        <v>-0.002452483139178318</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -9493,6 +11431,12 @@
       <c r="H323" s="3" t="n">
         <v>0.004529441368897784</v>
       </c>
+      <c r="I323" s="1" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="J323" s="2" t="n">
+        <v>-0.006513026052104159</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -9521,6 +11465,12 @@
       <c r="H324" s="3" t="n">
         <v>0.0003393281303019489</v>
       </c>
+      <c r="I324" s="1" t="n">
+        <v>0.053124</v>
+      </c>
+      <c r="J324" s="3" t="n">
+        <v>0.00113071008593392</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -9549,6 +11499,12 @@
       <c r="H325" s="3" t="n">
         <v>0.006670154329060902</v>
       </c>
+      <c r="I325" s="1" t="n">
+        <v>0.15376</v>
+      </c>
+      <c r="J325" s="2" t="n">
+        <v>-0.001169286735091501</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -9577,6 +11533,12 @@
       <c r="H326" s="2" t="n">
         <v>-0.0004615384615383894</v>
       </c>
+      <c r="I326" s="1" t="n">
+        <v>0.006471</v>
+      </c>
+      <c r="J326" s="2" t="n">
+        <v>-0.004001847006310602</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -9605,6 +11567,12 @@
       <c r="H327" s="3" t="n">
         <v>0.0015286454871727</v>
       </c>
+      <c r="I327" s="1" t="n">
+        <v>0.015033</v>
+      </c>
+      <c r="J327" s="2" t="n">
+        <v>-0.002389010551463356</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -9633,6 +11601,12 @@
       <c r="H328" s="3" t="n">
         <v>0.004259850905218292</v>
       </c>
+      <c r="I328" s="1" t="n">
+        <v>0.0944</v>
+      </c>
+      <c r="J328" s="3" t="n">
+        <v>0.001060445387062597</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -9661,6 +11635,12 @@
       <c r="H329" s="3" t="n">
         <v>0.004778156996587074</v>
       </c>
+      <c r="I329" s="1" t="n">
+        <v>0.004409</v>
+      </c>
+      <c r="J329" s="2" t="n">
+        <v>-0.001585144927536246</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -9689,6 +11669,12 @@
       <c r="H330" s="2" t="n">
         <v>-0.003319016009371407</v>
       </c>
+      <c r="I330" s="1" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="J330" s="3" t="n">
+        <v>0.001175318315377169</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -9717,6 +11703,12 @@
       <c r="H331" s="3" t="n">
         <v>0.007440066133921173</v>
       </c>
+      <c r="I331" s="1" t="n">
+        <v>0.03657</v>
+      </c>
+      <c r="J331" s="3" t="n">
+        <v>0.0002735229759298721</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -9745,6 +11737,12 @@
       <c r="H332" s="3" t="n">
         <v>0.000677506775067676</v>
       </c>
+      <c r="I332" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="J332" s="2" t="n">
+        <v>-0.002708192281652075</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -9773,6 +11771,12 @@
       <c r="H333" s="3" t="n">
         <v>0.007299270072992766</v>
       </c>
+      <c r="I333" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="J333" s="2" t="n">
+        <v>-0.00103519668737063</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -9801,6 +11805,12 @@
       <c r="H334" s="2" t="n">
         <v>-0.004107713372889083</v>
       </c>
+      <c r="I334" s="1" t="n">
+        <v>0.04377</v>
+      </c>
+      <c r="J334" s="3" t="n">
+        <v>0.002978918423464828</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -9829,6 +11839,12 @@
       <c r="H335" s="3" t="n">
         <v>0.003824799506477541</v>
       </c>
+      <c r="I335" s="1" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="J335" s="2" t="n">
+        <v>-0.000983284169124837</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -9857,6 +11873,12 @@
       <c r="H336" s="3" t="n">
         <v>0.006872852233677037</v>
       </c>
+      <c r="I336" s="1" t="n">
+        <v>0.2046</v>
+      </c>
+      <c r="J336" s="2" t="n">
+        <v>-0.002437835202340324</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -9885,6 +11907,12 @@
       <c r="H337" s="2" t="n">
         <v>-0.00683593750000006</v>
       </c>
+      <c r="I337" s="1" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="J337" s="3" t="n">
+        <v>0.002949852507374682</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -9913,6 +11941,12 @@
       <c r="H338" s="3" t="n">
         <v>0.005323868677905974</v>
       </c>
+      <c r="I338" s="1" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="J338" s="2" t="n">
+        <v>-0.0008826125330979953</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -9941,6 +11975,12 @@
       <c r="H339" s="3" t="n">
         <v>0.003831417624520916</v>
       </c>
+      <c r="I339" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="J339" s="3" t="n">
+        <v>0.0005452562704472771</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -9969,6 +12009,12 @@
       <c r="H340" s="3" t="n">
         <v>0.002955561028816746</v>
       </c>
+      <c r="I340" s="1" t="n">
+        <v>0.28516</v>
+      </c>
+      <c r="J340" s="3" t="n">
+        <v>0.0003858972110156077</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -9997,6 +12043,12 @@
       <c r="H341" s="3" t="n">
         <v>0.006662072134160317</v>
       </c>
+      <c r="I341" s="1" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="J341" s="2" t="n">
+        <v>-0.01346417161113647</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -10025,6 +12077,12 @@
       <c r="H342" s="2" t="n">
         <v>-0.0006388959877331267</v>
       </c>
+      <c r="I342" s="1" t="n">
+        <v>0.07832</v>
+      </c>
+      <c r="J342" s="3" t="n">
+        <v>0.001406469760900128</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -10053,6 +12111,12 @@
       <c r="H343" s="3" t="n">
         <v>0.002756629036492506</v>
       </c>
+      <c r="I343" s="1" t="n">
+        <v>7.617</v>
+      </c>
+      <c r="J343" s="2" t="n">
+        <v>-0.002879958109700254</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -10081,6 +12145,12 @@
       <c r="H344" s="3" t="n">
         <v>0.006819693945442437</v>
       </c>
+      <c r="I344" s="1" t="n">
+        <v>0.6036</v>
+      </c>
+      <c r="J344" s="2" t="n">
+        <v>-0.002808524698496487</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -10109,6 +12179,12 @@
       <c r="H345" s="3" t="n">
         <v>0.008686210640608058</v>
       </c>
+      <c r="I345" s="1" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="J345" s="2" t="n">
+        <v>-0.002152852529601634</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -10137,6 +12213,12 @@
       <c r="H346" s="3" t="n">
         <v>0.009756097560975551</v>
       </c>
+      <c r="I346" s="1" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="J346" s="2" t="n">
+        <v>-0.002415458937197969</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -10165,6 +12247,12 @@
       <c r="H347" s="3" t="n">
         <v>0.002886836027713629</v>
       </c>
+      <c r="I347" s="1" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="J347" s="2" t="n">
+        <v>-0.004029936672423755</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -10193,6 +12281,12 @@
       <c r="H348" s="2" t="n">
         <v>-0.0007715602877919873</v>
       </c>
+      <c r="I348" s="1" t="n">
+        <v>5183.7</v>
+      </c>
+      <c r="J348" s="3" t="n">
+        <v>0.0006563326448274494</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -10221,6 +12315,12 @@
       <c r="H349" s="3" t="n">
         <v>0.004460966542750877</v>
       </c>
+      <c r="I349" s="1" t="n">
+        <v>0.01355</v>
+      </c>
+      <c r="J349" s="3" t="n">
+        <v>0.002960769800148047</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -10249,6 +12349,12 @@
       <c r="H350" s="3" t="n">
         <v>0.00736771600803744</v>
       </c>
+      <c r="I350" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="J350" s="2" t="n">
+        <v>-0.001994680851063749</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -10277,6 +12383,12 @@
       <c r="H351" s="3" t="n">
         <v>0.008946322067594291</v>
       </c>
+      <c r="I351" s="1" t="n">
+        <v>0.0006081</v>
+      </c>
+      <c r="J351" s="2" t="n">
+        <v>-0.001477832512315218</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -10305,6 +12417,12 @@
       <c r="H352" s="3" t="n">
         <v>0.003556910569105723</v>
       </c>
+      <c r="I352" s="1" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="J352" s="2" t="n">
+        <v>-0.002025316455696295</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -10333,6 +12451,12 @@
       <c r="H353" s="3" t="n">
         <v>0.008230892570817818</v>
       </c>
+      <c r="I353" s="1" t="n">
+        <v>0.09402000000000001</v>
+      </c>
+      <c r="J353" s="2" t="n">
+        <v>-0.003180661577608086</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -10361,6 +12485,12 @@
       <c r="H354" s="3" t="n">
         <v>0.006615214994487357</v>
       </c>
+      <c r="I354" s="1" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="J354" s="2" t="n">
+        <v>-0.002190580503833578</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -10389,6 +12519,12 @@
       <c r="H355" s="3" t="n">
         <v>0.008497167610796517</v>
       </c>
+      <c r="I355" s="1" t="n">
+        <v>0.0006103</v>
+      </c>
+      <c r="J355" s="3" t="n">
+        <v>0.008260366760284178</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -10417,6 +12553,12 @@
       <c r="H356" s="3" t="n">
         <v>0.003840614498319734</v>
       </c>
+      <c r="I356" s="1" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="J356" s="2" t="n">
+        <v>-0.003347680535628941</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -10445,6 +12587,12 @@
       <c r="H357" s="2" t="n">
         <v>-0.002595155709342605</v>
       </c>
+      <c r="I357" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="J357" s="3" t="n">
+        <v>0.004770164787510797</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -10473,6 +12621,12 @@
       <c r="H358" s="2" t="n">
         <v>-0.002457002457002516</v>
       </c>
+      <c r="I358" s="1" t="n">
+        <v>0.000406</v>
+      </c>
+      <c r="J358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -10501,6 +12655,12 @@
       <c r="H359" s="3" t="n">
         <v>0.009615384615384581</v>
       </c>
+      <c r="I359" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="J359" s="2" t="n">
+        <v>-0.001360544217687019</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -10529,6 +12689,12 @@
       <c r="H360" s="3" t="n">
         <v>0.00147754137115846</v>
       </c>
+      <c r="I360" s="1" t="n">
+        <v>0.003365</v>
+      </c>
+      <c r="J360" s="2" t="n">
+        <v>-0.007081735025081188</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -10557,6 +12723,12 @@
       <c r="H361" s="2" t="n">
         <v>-0.004348501320080796</v>
       </c>
+      <c r="I361" s="1" t="n">
+        <v>0.6422</v>
+      </c>
+      <c r="J361" s="3" t="n">
+        <v>0.001715800967087802</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -10585,6 +12757,12 @@
       <c r="H362" s="3" t="n">
         <v>0.006437768240343234</v>
       </c>
+      <c r="I362" s="1" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="J362" s="3" t="n">
+        <v>0.0008528784648188766</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -10613,6 +12791,12 @@
       <c r="H363" s="3" t="n">
         <v>0.002602173580284762</v>
       </c>
+      <c r="I363" s="1" t="n">
+        <v>0.06535000000000001</v>
+      </c>
+      <c r="J363" s="2" t="n">
+        <v>-0.002290076335877822</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -10641,6 +12825,12 @@
       <c r="H364" s="2" t="n">
         <v>-0.0004241781548249798</v>
       </c>
+      <c r="I364" s="1" t="n">
+        <v>4.707</v>
+      </c>
+      <c r="J364" s="2" t="n">
+        <v>-0.001273074474856827</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -10669,6 +12859,12 @@
       <c r="H365" s="2" t="n">
         <v>-0.005343833497398471</v>
       </c>
+      <c r="I365" s="1" t="n">
+        <v>0.07112</v>
+      </c>
+      <c r="J365" s="3" t="n">
+        <v>0.005513926198218598</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -10697,6 +12893,12 @@
       <c r="H366" s="3" t="n">
         <v>0.006359011627907033</v>
       </c>
+      <c r="I366" s="1" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="J366" s="3" t="n">
+        <v>0.001444304025997414</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -10725,6 +12927,12 @@
       <c r="H367" s="3" t="n">
         <v>0.003248418533082624</v>
       </c>
+      <c r="I367" s="1" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="J367" s="2" t="n">
+        <v>-0.0001704158145876459</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -10753,6 +12961,12 @@
       <c r="H368" s="3" t="n">
         <v>0.005104735081851762</v>
       </c>
+      <c r="I368" s="1" t="n">
+        <v>0.05717</v>
+      </c>
+      <c r="J368" s="3" t="n">
+        <v>0.001225919439579696</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -10781,6 +12995,12 @@
       <c r="H369" s="3" t="n">
         <v>0.007462686567164213</v>
       </c>
+      <c r="I369" s="1" t="n">
+        <v>0.03103</v>
+      </c>
+      <c r="J369" s="2" t="n">
+        <v>-0.0006441223832529035</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -10809,6 +13029,12 @@
       <c r="H370" s="3" t="n">
         <v>0.005555555555555523</v>
       </c>
+      <c r="I370" s="1" t="n">
+        <v>0.0001622</v>
+      </c>
+      <c r="J370" s="2" t="n">
+        <v>-0.004297114794352301</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -10837,6 +13063,12 @@
       <c r="H371" s="3" t="n">
         <v>0.003692762186115192</v>
       </c>
+      <c r="I371" s="1" t="n">
+        <v>0.006786</v>
+      </c>
+      <c r="J371" s="2" t="n">
+        <v>-0.001324503311258199</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -10865,6 +13097,12 @@
       <c r="H372" s="2" t="n">
         <v>-0.002896032435563286</v>
       </c>
+      <c r="I372" s="1" t="n">
+        <v>0.006898</v>
+      </c>
+      <c r="J372" s="3" t="n">
+        <v>0.001742666279407473</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -10893,6 +13131,12 @@
       <c r="H373" s="3" t="n">
         <v>0.006342494714587744</v>
       </c>
+      <c r="I373" s="1" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="J373" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -10921,6 +13165,12 @@
       <c r="H374" s="3" t="n">
         <v>0.003821115199547217</v>
       </c>
+      <c r="I374" s="1" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="J374" s="2" t="n">
+        <v>-0.001832792894403004</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -10949,6 +13199,12 @@
       <c r="H375" s="3" t="n">
         <v>0.009304729904368033</v>
       </c>
+      <c r="I375" s="1" t="n">
+        <v>0.07868</v>
+      </c>
+      <c r="J375" s="3" t="n">
+        <v>0.007426376440460911</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -10977,6 +13233,12 @@
       <c r="H376" s="3" t="n">
         <v>0.001754106203157375</v>
       </c>
+      <c r="I376" s="1" t="n">
+        <v>0.06272</v>
+      </c>
+      <c r="J376" s="2" t="n">
+        <v>-0.001591849729385592</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -11005,6 +13267,12 @@
       <c r="H377" s="3" t="n">
         <v>0.00393597480976133</v>
       </c>
+      <c r="I377" s="1" t="n">
+        <v>0.07633</v>
+      </c>
+      <c r="J377" s="2" t="n">
+        <v>-0.002483010977522342</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -11033,6 +13301,12 @@
       <c r="H378" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I378" s="1" t="n">
+        <v>0.0004027</v>
+      </c>
+      <c r="J378" s="2" t="n">
+        <v>-0.001240079365079395</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -11061,6 +13335,12 @@
       <c r="H379" s="3" t="n">
         <v>0.003640285829850429</v>
       </c>
+      <c r="I379" s="1" t="n">
+        <v>0.07437000000000001</v>
+      </c>
+      <c r="J379" s="2" t="n">
+        <v>-0.000940354648038697</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -11089,6 +13369,12 @@
       <c r="H380" s="2" t="n">
         <v>-0.001477104874446122</v>
       </c>
+      <c r="I380" s="1" t="n">
+        <v>0.001346</v>
+      </c>
+      <c r="J380" s="2" t="n">
+        <v>-0.004437869822485155</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -11117,6 +13403,12 @@
       <c r="H381" s="3" t="n">
         <v>0.004635352286773696</v>
       </c>
+      <c r="I381" s="1" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="J381" s="2" t="n">
+        <v>-0.001845585973546534</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -11145,6 +13437,12 @@
       <c r="H382" s="3" t="n">
         <v>0.004521477015825116</v>
       </c>
+      <c r="I382" s="1" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="J382" s="3" t="n">
+        <v>0.0007501875468866911</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -11173,6 +13471,12 @@
       <c r="H383" s="3" t="n">
         <v>0.005698005698005664</v>
       </c>
+      <c r="I383" s="1" t="n">
+        <v>0.01768</v>
+      </c>
+      <c r="J383" s="3" t="n">
+        <v>0.001699716713881147</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -11201,6 +13505,12 @@
       <c r="H384" s="3" t="n">
         <v>0.001964636542239606</v>
       </c>
+      <c r="I384" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="J384" s="2" t="n">
+        <v>-0.0009803921568626371</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -11229,6 +13539,12 @@
       <c r="H385" s="3" t="n">
         <v>0.005812653699977599</v>
       </c>
+      <c r="I385" s="1" t="n">
+        <v>4.487</v>
+      </c>
+      <c r="J385" s="2" t="n">
+        <v>-0.002667259390975676</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -11257,6 +13573,12 @@
       <c r="H386" s="3" t="n">
         <v>0.00311041990668731</v>
       </c>
+      <c r="I386" s="1" t="n">
+        <v>0.001285</v>
+      </c>
+      <c r="J386" s="2" t="n">
+        <v>-0.003875968992248072</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -11285,6 +13607,12 @@
       <c r="H387" s="3" t="n">
         <v>0.003564154786150707</v>
       </c>
+      <c r="I387" s="1" t="n">
+        <v>0.0005921</v>
+      </c>
+      <c r="J387" s="3" t="n">
+        <v>0.001352951124640655</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -11313,6 +13641,12 @@
       <c r="H388" s="3" t="n">
         <v>0.005333333333333424</v>
       </c>
+      <c r="I388" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="J388" s="2" t="n">
+        <v>-0.0008841732979665187</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -11341,6 +13675,12 @@
       <c r="H389" s="3" t="n">
         <v>0.001097694840834203</v>
       </c>
+      <c r="I389" s="1" t="n">
+        <v>0.00912</v>
+      </c>
+      <c r="J389" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -11369,6 +13709,12 @@
       <c r="H390" s="3" t="n">
         <v>0.006234096692111837</v>
       </c>
+      <c r="I390" s="1" t="n">
+        <v>0.07895000000000001</v>
+      </c>
+      <c r="J390" s="2" t="n">
+        <v>-0.001770135288911207</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -11397,6 +13743,12 @@
       <c r="H391" s="3" t="n">
         <v>0.009049773755656149</v>
       </c>
+      <c r="I391" s="1" t="n">
+        <v>0.05123</v>
+      </c>
+      <c r="J391" s="2" t="n">
+        <v>-0.001169818678104981</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -11425,6 +13777,12 @@
       <c r="H392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I392" s="1" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="J392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -11453,6 +13811,12 @@
       <c r="H393" s="3" t="n">
         <v>0.002843601895734646</v>
       </c>
+      <c r="I393" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="J393" s="2" t="n">
+        <v>-0.004253308128544578</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -11481,6 +13845,12 @@
       <c r="H394" s="3" t="n">
         <v>0.006819288845591741</v>
       </c>
+      <c r="I394" s="1" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="J394" s="3" t="n">
+        <v>0.001935171746492557</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -11509,6 +13879,12 @@
       <c r="H395" s="3" t="n">
         <v>0.006185567010309312</v>
       </c>
+      <c r="I395" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="J395" s="2" t="n">
+        <v>-0.001024590163934456</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -11537,6 +13913,12 @@
       <c r="H396" s="3" t="n">
         <v>0.008531157270029557</v>
       </c>
+      <c r="I396" s="1" t="n">
+        <v>2.711</v>
+      </c>
+      <c r="J396" s="2" t="n">
+        <v>-0.002942258183155575</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -11565,6 +13947,12 @@
       <c r="H397" s="2" t="n">
         <v>-0.0007905138339920079</v>
       </c>
+      <c r="I397" s="1" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="J397" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -11593,6 +13981,12 @@
       <c r="H398" s="3" t="n">
         <v>0.0117581961543782</v>
       </c>
+      <c r="I398" s="1" t="n">
+        <v>0.007306</v>
+      </c>
+      <c r="J398" s="2" t="n">
+        <v>-0.001093792726278397</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -11621,6 +14015,12 @@
       <c r="H399" s="3" t="n">
         <v>0.003086419753086508</v>
       </c>
+      <c r="I399" s="1" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="J399" s="2" t="n">
+        <v>-0.0003846153846153422</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -11649,6 +14049,12 @@
       <c r="H400" s="3" t="n">
         <v>0.001572821642025796</v>
       </c>
+      <c r="I400" s="1" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="J400" s="2" t="n">
+        <v>-0.0009422110552764525</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -11677,6 +14083,12 @@
       <c r="H401" s="3" t="n">
         <v>0.005013550135501315</v>
       </c>
+      <c r="I401" s="1" t="n">
+        <v>0.007404</v>
+      </c>
+      <c r="J401" s="2" t="n">
+        <v>-0.001752730214372386</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -11705,6 +14117,12 @@
       <c r="H402" s="3" t="n">
         <v>0.004170324846356435</v>
       </c>
+      <c r="I402" s="1" t="n">
+        <v>0.004567</v>
+      </c>
+      <c r="J402" s="2" t="n">
+        <v>-0.001748633879781463</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -11733,6 +14151,12 @@
       <c r="H403" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I403" s="1" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="J403" s="2" t="n">
+        <v>-0.001512859304084763</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -11761,6 +14185,12 @@
       <c r="H404" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I404" s="1" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="J404" s="2" t="n">
+        <v>-0.0008340283569641606</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -11789,6 +14219,12 @@
       <c r="H405" s="3" t="n">
         <v>0.003220982399631841</v>
       </c>
+      <c r="I405" s="1" t="n">
+        <v>0.000871</v>
+      </c>
+      <c r="J405" s="2" t="n">
+        <v>-0.00126132324274736</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -11817,6 +14253,12 @@
       <c r="H406" s="3" t="n">
         <v>0.0009807767752059232</v>
       </c>
+      <c r="I406" s="1" t="n">
+        <v>0.005093</v>
+      </c>
+      <c r="J406" s="2" t="n">
+        <v>-0.001959631589261139</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -11845,6 +14287,12 @@
       <c r="H407" s="3" t="n">
         <v>0.001650165016501583</v>
       </c>
+      <c r="I407" s="1" t="n">
+        <v>0.01213</v>
+      </c>
+      <c r="J407" s="2" t="n">
+        <v>-0.0008237232289950241</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -11873,6 +14321,12 @@
       <c r="H408" s="3" t="n">
         <v>0.001388888888888772</v>
       </c>
+      <c r="I408" s="1" t="n">
+        <v>0.001444</v>
+      </c>
+      <c r="J408" s="3" t="n">
+        <v>0.00138696255201113</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -11901,6 +14355,12 @@
       <c r="H409" s="3" t="n">
         <v>0.01701894043370855</v>
       </c>
+      <c r="I409" s="1" t="n">
+        <v>0.03727</v>
+      </c>
+      <c r="J409" s="3" t="n">
+        <v>0.005937921727395357</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -11929,6 +14389,12 @@
       <c r="H410" s="3" t="n">
         <v>0.003678724708767477</v>
       </c>
+      <c r="I410" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="J410" s="2" t="n">
+        <v>-0.0006108735491752959</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -11957,6 +14423,12 @@
       <c r="H411" s="2" t="n">
         <v>-0.004682622268470405</v>
       </c>
+      <c r="I411" s="1" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="J411" s="2" t="n">
+        <v>-0.001568217459487688</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -11985,6 +14457,12 @@
       <c r="H412" s="2" t="n">
         <v>-0.00650310375406438</v>
       </c>
+      <c r="I412" s="1" t="n">
+        <v>0.06718</v>
+      </c>
+      <c r="J412" s="2" t="n">
+        <v>-0.0005950609937518353</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -12013,6 +14491,12 @@
       <c r="H413" s="3" t="n">
         <v>0.005533596837944664</v>
       </c>
+      <c r="I413" s="1" t="n">
+        <v>2545</v>
+      </c>
+      <c r="J413" s="3" t="n">
+        <v>0.0003930817610062893</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -12041,6 +14525,12 @@
       <c r="H414" s="3" t="n">
         <v>0.002497118709181678</v>
       </c>
+      <c r="I414" s="1" t="n">
+        <v>0.05214</v>
+      </c>
+      <c r="J414" s="2" t="n">
+        <v>-0.0009580379383023842</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -12069,6 +14559,12 @@
       <c r="H415" s="2" t="n">
         <v>-0.004043905257076902</v>
       </c>
+      <c r="I415" s="1" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="J415" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -12097,6 +14593,12 @@
       <c r="H416" s="3" t="n">
         <v>0.007439824945295354</v>
       </c>
+      <c r="I416" s="1" t="n">
+        <v>0.06881</v>
+      </c>
+      <c r="J416" s="2" t="n">
+        <v>-0.003620040544454101</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -12125,6 +14627,12 @@
       <c r="H417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="J417" s="2" t="n">
+        <v>-0.01333333333333335</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -12153,6 +14661,12 @@
       <c r="H418" s="3" t="n">
         <v>0.003916449086161811</v>
       </c>
+      <c r="I418" s="1" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="J418" s="2" t="n">
+        <v>-0.002600780234070115</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -12181,6 +14695,12 @@
       <c r="H419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="J419" s="3" t="n">
+        <v>0.008130081300812959</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -12209,6 +14729,12 @@
       <c r="H420" s="3" t="n">
         <v>0.005753138075313754</v>
       </c>
+      <c r="I420" s="1" t="n">
+        <v>0.01915</v>
+      </c>
+      <c r="J420" s="2" t="n">
+        <v>-0.004160166406656277</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -12237,6 +14763,12 @@
       <c r="H421" s="3" t="n">
         <v>0.005486542443064066</v>
       </c>
+      <c r="I421" s="1" t="n">
+        <v>0.19272</v>
+      </c>
+      <c r="J421" s="2" t="n">
+        <v>-0.007927519818799475</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -12265,6 +14797,12 @@
       <c r="H422" s="3" t="n">
         <v>0.002343978904189767</v>
       </c>
+      <c r="I422" s="1" t="n">
+        <v>0.03423</v>
+      </c>
+      <c r="J422" s="3" t="n">
+        <v>0.0005846243788365737</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -12293,6 +14831,12 @@
       <c r="H423" s="3" t="n">
         <v>0.001405481377371595</v>
       </c>
+      <c r="I423" s="1" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="J423" s="2" t="n">
+        <v>-0.0021052631578947</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -12321,6 +14865,12 @@
       <c r="H424" s="3" t="n">
         <v>0.001890359168241889</v>
       </c>
+      <c r="I424" s="1" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="J424" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -12349,6 +14899,12 @@
       <c r="H425" s="3" t="n">
         <v>0.003813155386082092</v>
       </c>
+      <c r="I425" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="J425" s="2" t="n">
+        <v>-0.00189933523266862</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -12377,6 +14933,12 @@
       <c r="H426" s="3" t="n">
         <v>0.003262411347517795</v>
       </c>
+      <c r="I426" s="1" t="n">
+        <v>0.007063</v>
+      </c>
+      <c r="J426" s="2" t="n">
+        <v>-0.001413827230312521</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -12405,6 +14967,12 @@
       <c r="H427" s="3" t="n">
         <v>0.00195312499999992</v>
       </c>
+      <c r="I427" s="1" t="n">
+        <v>0.02557</v>
+      </c>
+      <c r="J427" s="2" t="n">
+        <v>-0.003118908382066285</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -12433,6 +15001,12 @@
       <c r="H428" s="3" t="n">
         <v>0.004949882440292056</v>
       </c>
+      <c r="I428" s="1" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="J428" s="2" t="n">
+        <v>-0.00381726388375813</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -12461,6 +15035,12 @@
       <c r="H429" s="3" t="n">
         <v>0.001632653061224423</v>
       </c>
+      <c r="I429" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="J429" s="3" t="n">
+        <v>0.004889975550122333</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -12489,6 +15069,12 @@
       <c r="H430" s="3" t="n">
         <v>0.003290457672748997</v>
       </c>
+      <c r="I430" s="1" t="n">
+        <v>0.06711</v>
+      </c>
+      <c r="J430" s="3" t="n">
+        <v>0.0004472271914132714</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -12517,6 +15103,12 @@
       <c r="H431" s="3" t="n">
         <v>0.001845018450184427</v>
       </c>
+      <c r="I431" s="1" t="n">
+        <v>0.00543</v>
+      </c>
+      <c r="J431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -12545,6 +15137,12 @@
       <c r="H432" s="3" t="n">
         <v>0.005123379339188669</v>
       </c>
+      <c r="I432" s="1" t="n">
+        <v>0.009664000000000001</v>
+      </c>
+      <c r="J432" s="3" t="n">
+        <v>0.005305315718298211</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -12573,6 +15171,12 @@
       <c r="H433" s="3" t="n">
         <v>0.005073689296931503</v>
       </c>
+      <c r="I433" s="1" t="n">
+        <v>0.04156</v>
+      </c>
+      <c r="J433" s="2" t="n">
+        <v>-0.0009615384615384225</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -12601,6 +15205,12 @@
       <c r="H434" s="3" t="n">
         <v>0.0004775549188156443</v>
       </c>
+      <c r="I434" s="1" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="J434" s="2" t="n">
+        <v>-0.0002386634844869466</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -12629,6 +15239,12 @@
       <c r="H435" s="3" t="n">
         <v>0.005882352941176543</v>
       </c>
+      <c r="I435" s="1" t="n">
+        <v>0.001537</v>
+      </c>
+      <c r="J435" s="2" t="n">
+        <v>-0.001299545159194314</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -12657,6 +15273,12 @@
       <c r="H436" s="3" t="n">
         <v>0.003999999999999963</v>
       </c>
+      <c r="I436" s="1" t="n">
+        <v>0.02752</v>
+      </c>
+      <c r="J436" s="2" t="n">
+        <v>-0.003259688518652655</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -12685,6 +15307,12 @@
       <c r="H437" s="2" t="n">
         <v>-0.01053261520047882</v>
       </c>
+      <c r="I437" s="1" t="n">
+        <v>0.08298999999999999</v>
+      </c>
+      <c r="J437" s="3" t="n">
+        <v>0.003870811660820139</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -12713,6 +15341,12 @@
       <c r="H438" s="3" t="n">
         <v>0.002615518744551078</v>
       </c>
+      <c r="I438" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="J438" s="2" t="n">
+        <v>-0.0008695652173913292</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -12741,6 +15375,12 @@
       <c r="H439" s="3" t="n">
         <v>0.003893575600259575</v>
       </c>
+      <c r="I439" s="1" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="J439" s="2" t="n">
+        <v>-0.001292824822236588</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -12769,6 +15409,12 @@
       <c r="H440" s="3" t="n">
         <v>0.003921568627451015</v>
       </c>
+      <c r="I440" s="1" t="n">
+        <v>0.001792</v>
+      </c>
+      <c r="J440" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -12797,6 +15443,12 @@
       <c r="H441" s="3" t="n">
         <v>0.003805381897254533</v>
       </c>
+      <c r="I441" s="1" t="n">
+        <v>0.03676</v>
+      </c>
+      <c r="J441" s="2" t="n">
+        <v>-0.004603303547251463</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -12825,6 +15477,12 @@
       <c r="H442" s="3" t="n">
         <v>0.004347826086956533</v>
       </c>
+      <c r="I442" s="1" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="J442" s="3" t="n">
+        <v>0.001082251082251038</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -12853,6 +15511,12 @@
       <c r="H443" s="3" t="n">
         <v>0.002509016779049826</v>
       </c>
+      <c r="I443" s="1" t="n">
+        <v>0.12785</v>
+      </c>
+      <c r="J443" s="2" t="n">
+        <v>-7.821054278124512e-05</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -12881,6 +15545,12 @@
       <c r="H444" s="2" t="n">
         <v>-0.002144963803735787</v>
       </c>
+      <c r="I444" s="1" t="n">
+        <v>0.011279</v>
+      </c>
+      <c r="J444" s="3" t="n">
+        <v>0.01021047917599653</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -12909,6 +15579,12 @@
       <c r="H445" s="3" t="n">
         <v>0.006482982171798936</v>
       </c>
+      <c r="I445" s="1" t="n">
+        <v>0.08087</v>
+      </c>
+      <c r="J445" s="3" t="n">
+        <v>0.001734175647219141</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -12937,6 +15613,12 @@
       <c r="H446" s="3" t="n">
         <v>0.007593735168486055</v>
       </c>
+      <c r="I446" s="1" t="n">
+        <v>0.0002107</v>
+      </c>
+      <c r="J446" s="2" t="n">
+        <v>-0.007536504945831426</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -12965,6 +15647,12 @@
       <c r="H447" s="3" t="n">
         <v>0.001536098310291796</v>
       </c>
+      <c r="I447" s="1" t="n">
+        <v>0.00651</v>
+      </c>
+      <c r="J447" s="2" t="n">
+        <v>-0.001533742331288281</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -12993,6 +15681,12 @@
       <c r="H448" s="3" t="n">
         <v>0.002060193479039718</v>
       </c>
+      <c r="I448" s="1" t="n">
+        <v>0.11197</v>
+      </c>
+      <c r="J448" s="3" t="n">
+        <v>0.0008938946992044593</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -13021,6 +15715,12 @@
       <c r="H449" s="3" t="n">
         <v>0.001779359430604961</v>
       </c>
+      <c r="I449" s="1" t="n">
+        <v>0.001686</v>
+      </c>
+      <c r="J449" s="2" t="n">
+        <v>-0.001776198934280618</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -13049,6 +15749,12 @@
       <c r="H450" s="3" t="n">
         <v>0.002906976744185986</v>
       </c>
+      <c r="I450" s="1" t="n">
+        <v>0.0002068</v>
+      </c>
+      <c r="J450" s="2" t="n">
+        <v>-0.0009661835748791197</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -13077,6 +15783,12 @@
       <c r="H451" s="3" t="n">
         <v>0.003783579265985676</v>
       </c>
+      <c r="I451" s="1" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="J451" s="2" t="n">
+        <v>-0.006407840180927316</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -13105,6 +15817,12 @@
       <c r="H452" s="3" t="n">
         <v>0.002998500749625274</v>
       </c>
+      <c r="I452" s="1" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="J452" s="2" t="n">
+        <v>-0.000747384155455822</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -13133,6 +15851,12 @@
       <c r="H453" s="3" t="n">
         <v>0.002870264064293829</v>
       </c>
+      <c r="I453" s="1" t="n">
+        <v>0.0001746</v>
+      </c>
+      <c r="J453" s="2" t="n">
+        <v>-0.0005724098454493557</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -13161,6 +15885,12 @@
       <c r="H454" s="3" t="n">
         <v>0.007326678267240673</v>
       </c>
+      <c r="I454" s="1" t="n">
+        <v>0.10981</v>
+      </c>
+      <c r="J454" s="2" t="n">
+        <v>-0.001636512410219107</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -13189,6 +15919,12 @@
       <c r="H455" s="3" t="n">
         <v>0.006019261637239059</v>
       </c>
+      <c r="I455" s="1" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="J455" s="2" t="n">
+        <v>-0.0007977662544873474</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -13217,6 +15953,12 @@
       <c r="H456" s="3" t="n">
         <v>0.001629481072950504</v>
       </c>
+      <c r="I456" s="1" t="n">
+        <v>0.015985</v>
+      </c>
+      <c r="J456" s="3" t="n">
+        <v>0.0001877111750719266</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -13245,6 +15987,12 @@
       <c r="H457" s="3" t="n">
         <v>0.001503533303262736</v>
       </c>
+      <c r="I457" s="1" t="n">
+        <v>0.006673</v>
+      </c>
+      <c r="J457" s="3" t="n">
+        <v>0.001801531301606344</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -13273,6 +16021,12 @@
       <c r="H458" s="3" t="n">
         <v>0.003333333333333313</v>
       </c>
+      <c r="I458" s="1" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="J458" s="2" t="n">
+        <v>-0.001453488372092979</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -13301,6 +16055,12 @@
       <c r="H459" s="3" t="n">
         <v>0.00219918316054039</v>
       </c>
+      <c r="I459" s="1" t="n">
+        <v>0.006372</v>
+      </c>
+      <c r="J459" s="2" t="n">
+        <v>-0.001253918495297836</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -13329,6 +16089,12 @@
       <c r="H460" s="3" t="n">
         <v>0.005098324836125318</v>
       </c>
+      <c r="I460" s="1" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="J460" s="3" t="n">
+        <v>0.001449275362318681</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -13357,6 +16123,12 @@
       <c r="H461" s="3" t="n">
         <v>0.0005609783462357735</v>
       </c>
+      <c r="I461" s="1" t="n">
+        <v>0.08902</v>
+      </c>
+      <c r="J461" s="2" t="n">
+        <v>-0.001794124243103762</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -13385,6 +16157,12 @@
       <c r="H462" s="2" t="n">
         <v>-0.0008812513769552406</v>
       </c>
+      <c r="I462" s="1" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="J462" s="2" t="n">
+        <v>-0.0006615214994487816</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -13413,6 +16191,12 @@
       <c r="H463" s="3" t="n">
         <v>0.004310344827586156</v>
       </c>
+      <c r="I463" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="J463" s="2" t="n">
+        <v>-0.001430615164520686</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -13441,6 +16225,12 @@
       <c r="H464" s="3" t="n">
         <v>0.003065134099616861</v>
       </c>
+      <c r="I464" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="J464" s="3" t="n">
+        <v>0.002291825821237673</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -13469,6 +16259,12 @@
       <c r="H465" s="3" t="n">
         <v>0.005366726296958859</v>
       </c>
+      <c r="I465" s="1" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="J465" s="2" t="n">
+        <v>-0.002491103202847096</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -13497,6 +16293,12 @@
       <c r="H466" s="3" t="n">
         <v>0.001409443269908387</v>
       </c>
+      <c r="I466" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="J466" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -13525,6 +16327,12 @@
       <c r="H467" s="3" t="n">
         <v>0.00521920668058452</v>
       </c>
+      <c r="I467" s="1" t="n">
+        <v>0.01919</v>
+      </c>
+      <c r="J467" s="2" t="n">
+        <v>-0.003634475597092452</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -13553,6 +16361,12 @@
       <c r="H468" s="3" t="n">
         <v>0.006072874493927054</v>
       </c>
+      <c r="I468" s="1" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="J468" s="2" t="n">
+        <v>-0.002012072434607564</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -13581,6 +16395,12 @@
       <c r="H469" s="3" t="n">
         <v>0.001498875843117635</v>
       </c>
+      <c r="I469" s="1" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="J469" s="3" t="n">
+        <v>0.0007483162883512659</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -13609,6 +16429,12 @@
       <c r="H470" s="3" t="n">
         <v>0.002270147559591376</v>
       </c>
+      <c r="I470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="J470" s="2" t="n">
+        <v>-0.002265005662514158</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -13637,6 +16463,12 @@
       <c r="H471" s="3" t="n">
         <v>0.00557275541795673</v>
       </c>
+      <c r="I471" s="1" t="n">
+        <v>3.233</v>
+      </c>
+      <c r="J471" s="2" t="n">
+        <v>-0.004618226600985259</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -13665,6 +16497,12 @@
       <c r="H472" s="3" t="n">
         <v>0.001230314960629786</v>
       </c>
+      <c r="I472" s="1" t="n">
+        <v>0.04141</v>
+      </c>
+      <c r="J472" s="3" t="n">
+        <v>0.0176947652985993</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -13693,6 +16531,12 @@
       <c r="H473" s="3" t="n">
         <v>0.003220611916264093</v>
       </c>
+      <c r="I473" s="1" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="J473" s="2" t="n">
+        <v>-0.001605136436597112</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -13721,6 +16565,12 @@
       <c r="H474" s="3" t="n">
         <v>0.002934961258511472</v>
       </c>
+      <c r="I474" s="1" t="n">
+        <v>0.008524</v>
+      </c>
+      <c r="J474" s="2" t="n">
+        <v>-0.00222404307620273</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -13749,6 +16599,12 @@
       <c r="H475" s="3" t="n">
         <v>0.02717258261933904</v>
       </c>
+      <c r="I475" s="1" t="n">
+        <v>0.04171</v>
+      </c>
+      <c r="J475" s="2" t="n">
+        <v>-0.005958055290753104</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -13777,6 +16633,12 @@
       <c r="H476" s="3" t="n">
         <v>0.003670421465637243</v>
       </c>
+      <c r="I476" s="1" t="n">
+        <v>0.07926</v>
+      </c>
+      <c r="J476" s="2" t="n">
+        <v>-0.000504413619167697</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -13805,6 +16667,12 @@
       <c r="H477" s="2" t="n">
         <v>-0.005386911261556313</v>
       </c>
+      <c r="I477" s="1" t="n">
+        <v>0.13664</v>
+      </c>
+      <c r="J477" s="3" t="n">
+        <v>7.319036814762498e-05</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -13833,6 +16701,12 @@
       <c r="H478" s="3" t="n">
         <v>0.003581209184748336</v>
       </c>
+      <c r="I478" s="1" t="n">
+        <v>0.04756</v>
+      </c>
+      <c r="J478" s="2" t="n">
+        <v>-0.001679261125105031</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -13861,6 +16735,12 @@
       <c r="H479" s="3" t="n">
         <v>0.005312084993359941</v>
       </c>
+      <c r="I479" s="1" t="n">
+        <v>0.005296</v>
+      </c>
+      <c r="J479" s="2" t="n">
+        <v>-0.0005661445555764353</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -13889,6 +16769,12 @@
       <c r="H480" s="3" t="n">
         <v>0.002516175413371598</v>
       </c>
+      <c r="I480" s="1" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="J480" s="2" t="n">
+        <v>-0.001075654356400025</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -13917,6 +16803,12 @@
       <c r="H481" s="3" t="n">
         <v>0.001314924391847324</v>
       </c>
+      <c r="I481" s="1" t="n">
+        <v>0.07602</v>
+      </c>
+      <c r="J481" s="2" t="n">
+        <v>-0.001707156927117416</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -13945,6 +16837,12 @@
       <c r="H482" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I482" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="J482" s="3" t="n">
+        <v>0.002027027027026944</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -13973,6 +16871,12 @@
       <c r="H483" s="3" t="n">
         <v>0.003999999999999976</v>
       </c>
+      <c r="I483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="J483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -14001,6 +16905,12 @@
       <c r="H484" s="3" t="n">
         <v>0.00138376383763832</v>
       </c>
+      <c r="I484" s="1" t="n">
+        <v>0.02168</v>
+      </c>
+      <c r="J484" s="2" t="n">
+        <v>-0.001381851681252823</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -14029,6 +16939,12 @@
       <c r="H485" s="3" t="n">
         <v>0.003117505995203835</v>
       </c>
+      <c r="I485" s="1" t="n">
+        <v>0.008363000000000001</v>
+      </c>
+      <c r="J485" s="2" t="n">
+        <v>-0.0003585943103035537</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -14057,6 +16973,12 @@
       <c r="H486" s="3" t="n">
         <v>0.002822580645161199</v>
       </c>
+      <c r="I486" s="1" t="n">
+        <v>0.007463</v>
+      </c>
+      <c r="J486" s="3" t="n">
+        <v>0.0002680605816914978</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -14085,6 +17007,12 @@
       <c r="H487" s="3" t="n">
         <v>0.003623188405797079</v>
       </c>
+      <c r="I487" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J487" s="3" t="n">
+        <v>0.0018050541516246</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -14113,6 +17041,12 @@
       <c r="H488" s="2" t="n">
         <v>-0.001490789053348964</v>
       </c>
+      <c r="I488" s="1" t="n">
+        <v>0.009363</v>
+      </c>
+      <c r="J488" s="2" t="n">
+        <v>-0.001493014823504332</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -14141,6 +17075,12 @@
       <c r="H489" s="3" t="n">
         <v>0.0007753941586972165</v>
       </c>
+      <c r="I489" s="1" t="n">
+        <v>0.03861</v>
+      </c>
+      <c r="J489" s="2" t="n">
+        <v>-0.002840909090909065</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -14169,6 +17109,12 @@
       <c r="H490" s="3" t="n">
         <v>0.005137866072957727</v>
       </c>
+      <c r="I490" s="1" t="n">
+        <v>0.05864</v>
+      </c>
+      <c r="J490" s="2" t="n">
+        <v>-0.0008519338899301658</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -14197,6 +17143,12 @@
       <c r="H491" s="3" t="n">
         <v>0.003124999999999945</v>
       </c>
+      <c r="I491" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="J491" s="3" t="n">
+        <v>0.001038421599169292</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -14225,6 +17177,12 @@
       <c r="H492" s="3" t="n">
         <v>0.003016591251885372</v>
       </c>
+      <c r="I492" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J492" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -14253,6 +17211,12 @@
       <c r="H493" s="3" t="n">
         <v>0.00567375886524839</v>
       </c>
+      <c r="I493" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="J493" s="2" t="n">
+        <v>-0.006770098730606603</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -14281,6 +17245,12 @@
       <c r="H494" s="3" t="n">
         <v>0.008849557522123942</v>
       </c>
+      <c r="I494" s="1" t="n">
+        <v>0.01705</v>
+      </c>
+      <c r="J494" s="2" t="n">
+        <v>-0.002923976608187218</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -14309,6 +17279,12 @@
       <c r="H495" s="3" t="n">
         <v>0.00273684210526312</v>
       </c>
+      <c r="I495" s="1" t="n">
+        <v>0.04752</v>
+      </c>
+      <c r="J495" s="2" t="n">
+        <v>-0.002309468822170879</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -14337,6 +17313,12 @@
       <c r="H496" s="3" t="n">
         <v>0.0006208609271522208</v>
       </c>
+      <c r="I496" s="1" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="J496" s="2" t="n">
+        <v>-0.003102378490175747</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -14365,6 +17347,12 @@
       <c r="H497" s="3" t="n">
         <v>0.001198561725928836</v>
       </c>
+      <c r="I497" s="1" t="n">
+        <v>0.05001</v>
+      </c>
+      <c r="J497" s="2" t="n">
+        <v>-0.002194732641659996</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -14393,6 +17381,12 @@
       <c r="H498" s="3" t="n">
         <v>0.006263048016701544</v>
       </c>
+      <c r="I498" s="1" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="J498" s="2" t="n">
+        <v>-0.002420470262794031</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -14421,6 +17415,12 @@
       <c r="H499" s="3" t="n">
         <v>0.002565042139978138</v>
       </c>
+      <c r="I499" s="1" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="J499" s="2" t="n">
+        <v>-0.001827485380116961</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -14449,6 +17449,12 @@
       <c r="H500" s="3" t="n">
         <v>0.007547169811320775</v>
       </c>
+      <c r="I500" s="1" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="J500" s="2" t="n">
+        <v>-0.007490636704119869</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -14477,6 +17483,12 @@
       <c r="H501" s="2" t="n">
         <v>-0.006651884700665302</v>
       </c>
+      <c r="I501" s="1" t="n">
+        <v>0.03591</v>
+      </c>
+      <c r="J501" s="3" t="n">
+        <v>0.001953125000000017</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -14505,6 +17517,12 @@
       <c r="H502" s="3" t="n">
         <v>0.0006269592476488773</v>
       </c>
+      <c r="I502" s="1" t="n">
+        <v>0.03182</v>
+      </c>
+      <c r="J502" s="2" t="n">
+        <v>-0.003132832080200374</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -14533,6 +17551,12 @@
       <c r="H503" s="3" t="n">
         <v>0.003859017236943724</v>
       </c>
+      <c r="I503" s="1" t="n">
+        <v>0.007755</v>
+      </c>
+      <c r="J503" s="2" t="n">
+        <v>-0.006278831368529015</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -14561,6 +17585,12 @@
       <c r="H504" s="3" t="n">
         <v>0.002951787471302033</v>
       </c>
+      <c r="I504" s="1" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="J504" s="2" t="n">
+        <v>-0.00294310006540219</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -14589,6 +17619,12 @@
       <c r="H505" s="3" t="n">
         <v>0.005162342073088021</v>
       </c>
+      <c r="I505" s="1" t="n">
+        <v>0.0007418</v>
+      </c>
+      <c r="J505" s="3" t="n">
+        <v>0.002567914583051753</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -14617,6 +17653,12 @@
       <c r="H506" s="3" t="n">
         <v>0.004729729729729772</v>
       </c>
+      <c r="I506" s="1" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="J506" s="2" t="n">
+        <v>-0.003698722259583019</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -14645,6 +17687,12 @@
       <c r="H507" s="3" t="n">
         <v>0.005285412262156538</v>
       </c>
+      <c r="I507" s="1" t="n">
+        <v>0.002849</v>
+      </c>
+      <c r="J507" s="2" t="n">
+        <v>-0.001402032947774307</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -14673,6 +17721,12 @@
       <c r="H508" s="3" t="n">
         <v>0.001577784790154449</v>
       </c>
+      <c r="I508" s="1" t="n">
+        <v>0.06340999999999999</v>
+      </c>
+      <c r="J508" s="2" t="n">
+        <v>-0.001102709514807823</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -14701,6 +17755,12 @@
       <c r="H509" s="3" t="n">
         <v>0.005795809184128356</v>
       </c>
+      <c r="I509" s="1" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="J509" s="2" t="n">
+        <v>-0.002216312056737542</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -14729,6 +17789,12 @@
       <c r="H510" s="3" t="n">
         <v>0.004673539518900457</v>
       </c>
+      <c r="I510" s="1" t="n">
+        <v>0.00073</v>
+      </c>
+      <c r="J510" s="2" t="n">
+        <v>-0.001231358598987654</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -14757,6 +17823,12 @@
       <c r="H511" s="3" t="n">
         <v>0.003272727272727114</v>
       </c>
+      <c r="I511" s="1" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="J511" s="2" t="n">
+        <v>-0.003262051467923003</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -14785,6 +17857,12 @@
       <c r="H512" s="3" t="n">
         <v>0.01028331584470097</v>
       </c>
+      <c r="I512" s="1" t="n">
+        <v>0.0004816</v>
+      </c>
+      <c r="J512" s="3" t="n">
+        <v>0.0004154549231408493</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -14813,6 +17891,12 @@
       <c r="H513" s="3" t="n">
         <v>0.001997820559389739</v>
       </c>
+      <c r="I513" s="1" t="n">
+        <v>0.05523</v>
+      </c>
+      <c r="J513" s="3" t="n">
+        <v>0.001087547580206715</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -14841,6 +17925,12 @@
       <c r="H514" s="3" t="n">
         <v>0.002304906157392069</v>
       </c>
+      <c r="I514" s="1" t="n">
+        <v>0.03042</v>
+      </c>
+      <c r="J514" s="2" t="n">
+        <v>-0.0006570302233902492</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -14869,6 +17959,12 @@
       <c r="H515" s="2" t="n">
         <v>-0.001746724890829737</v>
       </c>
+      <c r="I515" s="1" t="n">
+        <v>0.001142</v>
+      </c>
+      <c r="J515" s="2" t="n">
+        <v>-0.0008748906386700927</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -14897,6 +17993,12 @@
       <c r="H516" s="3" t="n">
         <v>0.004994702588164075</v>
       </c>
+      <c r="I516" s="1" t="n">
+        <v>0.006627</v>
+      </c>
+      <c r="J516" s="2" t="n">
+        <v>-0.001957831325301203</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -14925,6 +18027,12 @@
       <c r="H517" s="3" t="n">
         <v>0.002010555415933744</v>
       </c>
+      <c r="I517" s="1" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="J517" s="2" t="n">
+        <v>-0.0005016302984701812</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -14953,6 +18061,12 @@
       <c r="H518" s="3" t="n">
         <v>0.0009727626459144248</v>
       </c>
+      <c r="I518" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="J518" s="3" t="n">
+        <v>0.0009718172983478035</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -14981,6 +18095,12 @@
       <c r="H519" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="I519" s="1" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="J519" s="2" t="n">
+        <v>-0.007927519818799422</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -15009,6 +18129,12 @@
       <c r="H520" s="3" t="n">
         <v>0.006913890634820979</v>
       </c>
+      <c r="I520" s="1" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="J520" s="3" t="n">
+        <v>0.001872659176029929</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -15037,6 +18163,12 @@
       <c r="H521" s="3" t="n">
         <v>0.002240896358543326</v>
       </c>
+      <c r="I521" s="1" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="J521" s="2" t="n">
+        <v>-0.005030743432084953</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -15065,6 +18197,12 @@
       <c r="H522" s="3" t="n">
         <v>0.005438066465256786</v>
       </c>
+      <c r="I522" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="J522" s="2" t="n">
+        <v>-0.002403846153846056</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -15093,6 +18231,12 @@
       <c r="H523" s="3" t="n">
         <v>0.0007153075822604669</v>
       </c>
+      <c r="I523" s="1" t="n">
+        <v>0.004187</v>
+      </c>
+      <c r="J523" s="2" t="n">
+        <v>-0.002382654276864537</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -15121,6 +18265,12 @@
       <c r="H524" s="3" t="n">
         <v>0.004936530324400608</v>
       </c>
+      <c r="I524" s="1" t="n">
+        <v>0.01424</v>
+      </c>
+      <c r="J524" s="2" t="n">
+        <v>-0.0007017543859650054</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -15149,6 +18299,12 @@
       <c r="H525" s="3" t="n">
         <v>0.0007999999999999674</v>
       </c>
+      <c r="I525" s="1" t="n">
+        <v>0.02502</v>
+      </c>
+      <c r="J525" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -15177,6 +18333,12 @@
       <c r="H526" s="3" t="n">
         <v>0.002495840266222918</v>
       </c>
+      <c r="I526" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="J526" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -15205,6 +18367,12 @@
       <c r="H527" s="3" t="n">
         <v>0.0008390434904207889</v>
       </c>
+      <c r="I527" s="1" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="J527" s="3" t="n">
+        <v>0.001816403521028435</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -15233,6 +18401,12 @@
       <c r="H528" s="3" t="n">
         <v>0.006039488966318311</v>
       </c>
+      <c r="I528" s="1" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="J528" s="2" t="n">
+        <v>-0.001616254906488123</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -15261,6 +18435,12 @@
       <c r="H529" s="3" t="n">
         <v>0.001428118057759328</v>
       </c>
+      <c r="I529" s="1" t="n">
+        <v>0.06306</v>
+      </c>
+      <c r="J529" s="2" t="n">
+        <v>-0.0007922674694976152</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -15289,6 +18469,12 @@
       <c r="H530" s="3" t="n">
         <v>0.004195804195804233</v>
       </c>
+      <c r="I530" s="1" t="n">
+        <v>0.005022</v>
+      </c>
+      <c r="J530" s="2" t="n">
+        <v>-0.0007958615200954365</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -15317,6 +18503,12 @@
       <c r="H531" s="3" t="n">
         <v>0.002302379125095892</v>
       </c>
+      <c r="I531" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="J531" s="2" t="n">
+        <v>-0.001531393568147058</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -15345,6 +18537,12 @@
       <c r="H532" s="3" t="n">
         <v>0.001874765654293267</v>
       </c>
+      <c r="I532" s="1" t="n">
+        <v>0.05336</v>
+      </c>
+      <c r="J532" s="2" t="n">
+        <v>-0.001497005988024021</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -15373,6 +18571,12 @@
       <c r="H533" s="2" t="n">
         <v>-0.0007951232441028265</v>
       </c>
+      <c r="I533" s="1" t="n">
+        <v>0.003767</v>
+      </c>
+      <c r="J533" s="2" t="n">
+        <v>-0.0007957559681697518</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -15401,6 +18605,12 @@
       <c r="H534" s="3" t="n">
         <v>0.001748251748251717</v>
       </c>
+      <c r="I534" s="1" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="J534" s="2" t="n">
+        <v>-0.001745200698080248</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -15429,6 +18639,12 @@
       <c r="H535" s="3" t="n">
         <v>0.008928571428571494</v>
       </c>
+      <c r="I535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="J535" s="2" t="n">
+        <v>-0.00884955752212396</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -15457,6 +18673,12 @@
       <c r="H536" s="2" t="n">
         <v>-0.003792103502119088</v>
       </c>
+      <c r="I536" s="1" t="n">
+        <v>0.000446</v>
+      </c>
+      <c r="J536" s="2" t="n">
+        <v>-0.001343484102104824</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -15485,6 +18707,12 @@
       <c r="H537" s="3" t="n">
         <v>0.002066115702479434</v>
       </c>
+      <c r="I537" s="1" t="n">
+        <v>0.00971</v>
+      </c>
+      <c r="J537" s="3" t="n">
+        <v>0.001030927835051504</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -15513,6 +18741,12 @@
       <c r="H538" s="3" t="n">
         <v>0.00478556966685066</v>
       </c>
+      <c r="I538" s="1" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="J538" s="3" t="n">
+        <v>0.001648653599560355</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -15541,6 +18775,12 @@
       <c r="H539" s="3" t="n">
         <v>0.001902531830820969</v>
       </c>
+      <c r="I539" s="1" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="J539" s="2" t="n">
+        <v>-0.002191060473268983</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -15569,6 +18809,12 @@
       <c r="H540" s="3" t="n">
         <v>0.00462962962962967</v>
       </c>
+      <c r="I540" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="J540" s="2" t="n">
+        <v>-0.001316655694535917</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -15597,6 +18843,12 @@
       <c r="H541" s="3" t="n">
         <v>0.00458365164247525</v>
       </c>
+      <c r="I541" s="1" t="n">
+        <v>0.01311</v>
+      </c>
+      <c r="J541" s="2" t="n">
+        <v>-0.003041825095057042</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -15625,6 +18877,12 @@
       <c r="H542" s="2" t="n">
         <v>-0.01475755446240338</v>
       </c>
+      <c r="I542" s="1" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="J542" s="3" t="n">
+        <v>0.007132667617689097</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -15652,6 +18910,12 @@
       </c>
       <c r="H543" s="3" t="n">
         <v>0.00279769190417906</v>
+      </c>
+      <c r="I543" s="1" t="n">
+        <v>0.05739</v>
+      </c>
+      <c r="J543" s="3" t="n">
+        <v>0.0006974716652135723</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L543"/>
+  <dimension ref="A1:N543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,8 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,6 +503,16 @@
           <t>change_01:15</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_01:30</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>change_01:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -541,6 +553,12 @@
       <c r="L2" s="3" t="n">
         <v>0.0006995313708539556</v>
       </c>
+      <c r="M2" s="1" t="n">
+        <v>70251.89999999999</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>-0.00184848398738322</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,6 +599,12 @@
       <c r="L3" s="3" t="n">
         <v>0.0001595405232928812</v>
       </c>
+      <c r="M3" s="1" t="n">
+        <v>2060.49</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>-0.004002378224742335</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -621,6 +645,12 @@
       <c r="L4" s="2" t="n">
         <v>-0.0003457814661134294</v>
       </c>
+      <c r="M4" s="1" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>-0.003459010722933208</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -661,6 +691,12 @@
       <c r="L5" s="2" t="n">
         <v>-0.0107072161238079</v>
       </c>
+      <c r="M5" s="1" t="n">
+        <v>0.010823</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>-0.01564347430650298</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -701,6 +737,12 @@
       <c r="L6" s="3" t="n">
         <v>0.0005068056762235179</v>
       </c>
+      <c r="M6" s="1" t="n">
+        <v>1.3782</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>-0.002677473044359082</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -741,6 +783,12 @@
       <c r="L7" s="2" t="n">
         <v>-0.0007392544091245181</v>
       </c>
+      <c r="M7" s="1" t="n">
+        <v>0.09422</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>-0.004227436060029567</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -781,6 +829,12 @@
       <c r="L8" s="3" t="n">
         <v>0.001650780126737249</v>
       </c>
+      <c r="M8" s="1" t="n">
+        <v>37.451</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.004492291334396516</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -821,6 +875,12 @@
       <c r="L9" s="3" t="n">
         <v>0.002396166134185345</v>
       </c>
+      <c r="M9" s="1" t="n">
+        <v>0.04967</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>-0.01055776892430284</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -861,6 +921,12 @@
       <c r="L10" s="2" t="n">
         <v>-0.004278132784577094</v>
       </c>
+      <c r="M10" s="1" t="n">
+        <v>18.527</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.007614075161799128</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -901,6 +967,12 @@
       <c r="L11" s="2" t="n">
         <v>-0.0004756789934019627</v>
       </c>
+      <c r="M11" s="1" t="n">
+        <v>650.5</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-0.001366308970048644</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -941,6 +1013,12 @@
       <c r="L12" s="2" t="n">
         <v>-0.004294917680744377</v>
       </c>
+      <c r="M12" s="1" t="n">
+        <v>0.9196</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0.1018451953031392</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -981,6 +1059,12 @@
       <c r="L13" s="2" t="n">
         <v>-0.00194913239838363</v>
       </c>
+      <c r="M13" s="1" t="n">
+        <v>209.64</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>-0.001428979708488194</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1021,6 +1105,12 @@
       <c r="L14" s="2" t="n">
         <v>-0.0004527891813570893</v>
       </c>
+      <c r="M14" s="1" t="n">
+        <v>0.0033116</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>9.059885845436931e-05</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1061,6 +1151,12 @@
       <c r="L15" s="2" t="n">
         <v>-0.001729967759691735</v>
       </c>
+      <c r="M15" s="1" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0.04135486411973222</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1101,6 +1197,12 @@
       <c r="L16" s="2" t="n">
         <v>-0.00153531218014324</v>
       </c>
+      <c r="M16" s="1" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>-0.003382880574064665</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1141,6 +1243,12 @@
       <c r="L17" s="2" t="n">
         <v>-0.03378378378378381</v>
       </c>
+      <c r="M17" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0.01398601398601402</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1181,6 +1289,12 @@
       <c r="L18" s="2" t="n">
         <v>-0.001759666589488287</v>
       </c>
+      <c r="M18" s="1" t="n">
+        <v>214.56</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>-0.004685253050053305</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1221,6 +1335,12 @@
       <c r="L19" s="2" t="n">
         <v>-0.0007604562737643858</v>
       </c>
+      <c r="M19" s="1" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>-0.002663622526636143</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1261,6 +1381,12 @@
       <c r="L20" s="2" t="n">
         <v>-0.01104743900277661</v>
       </c>
+      <c r="M20" s="1" t="n">
+        <v>0.016925</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.01105137395459962</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1301,6 +1427,12 @@
       <c r="L21" s="2" t="n">
         <v>-0.0005211590577443199</v>
       </c>
+      <c r="M21" s="1" t="n">
+        <v>9.557</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>-0.003337157159244971</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1341,6 +1473,12 @@
       <c r="L22" s="2" t="n">
         <v>-0.00358637178720871</v>
       </c>
+      <c r="M22" s="1" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0.002999400119976008</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1381,6 +1519,12 @@
       <c r="L23" s="2" t="n">
         <v>-0.0003142946941341152</v>
       </c>
+      <c r="M23" s="1" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0.001314736481079114</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1421,6 +1565,12 @@
       <c r="L24" s="2" t="n">
         <v>-0.001161440185830431</v>
       </c>
+      <c r="M24" s="1" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>-0.002325581395348839</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1461,6 +1611,12 @@
       <c r="L25" s="2" t="n">
         <v>-0.00110558319513541</v>
       </c>
+      <c r="M25" s="1" t="n">
+        <v>9.006</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>-0.003209739900387373</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1501,6 +1657,12 @@
       <c r="L26" s="3" t="n">
         <v>0.008333333333333257</v>
       </c>
+      <c r="M26" s="1" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0.002253944402704819</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1541,6 +1703,12 @@
       <c r="L27" s="2" t="n">
         <v>-0.0003804002200470385</v>
       </c>
+      <c r="M27" s="1" t="n">
+        <v>5120.29</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>-0.0007688960097418735</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1581,6 +1749,12 @@
       <c r="L28" s="2" t="n">
         <v>-0.0005672149744754211</v>
       </c>
+      <c r="M28" s="1" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0.0005675368898979384</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1621,6 +1795,12 @@
       <c r="L29" s="2" t="n">
         <v>-0.0007598784194529725</v>
       </c>
+      <c r="M29" s="1" t="n">
+        <v>2.617</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>-0.004942965779467643</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1661,6 +1841,12 @@
       <c r="L30" s="2" t="n">
         <v>-0.004056091938083945</v>
       </c>
+      <c r="M30" s="1" t="n">
+        <v>0.57712</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0.004438101536801332</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1701,6 +1887,12 @@
       <c r="L31" s="3" t="n">
         <v>0.0004798464491363401</v>
       </c>
+      <c r="M31" s="1" t="n">
+        <v>0.002081</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>-0.001918465227817792</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1741,6 +1933,12 @@
       <c r="L32" s="3" t="n">
         <v>0.01031090121999222</v>
       </c>
+      <c r="M32" s="1" t="n">
+        <v>1.2895</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0.004596447491430364</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1781,6 +1979,12 @@
       <c r="L33" s="2" t="n">
         <v>-0.001538935056940598</v>
       </c>
+      <c r="M33" s="1" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0.0009247842170159277</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1821,6 +2025,12 @@
       <c r="L34" s="2" t="n">
         <v>-0.001332445036642092</v>
       </c>
+      <c r="M34" s="1" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>-0.003335557038025427</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1861,6 +2071,12 @@
       <c r="L35" s="2" t="n">
         <v>-0.0004598405885959086</v>
       </c>
+      <c r="M35" s="1" t="n">
+        <v>455.04</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-0.003132735995793824</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1901,6 +2117,12 @@
       <c r="L36" s="2" t="n">
         <v>-0.008617152236356109</v>
       </c>
+      <c r="M36" s="1" t="n">
+        <v>0.04873</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0.008485099337748356</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1941,6 +2163,12 @@
       <c r="L37" s="3" t="n">
         <v>0.0005643340857788755</v>
       </c>
+      <c r="M37" s="1" t="n">
+        <v>0.7059</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>-0.004653130287648168</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1981,6 +2209,12 @@
       <c r="L38" s="2" t="n">
         <v>-0.0009460737937559401</v>
       </c>
+      <c r="M38" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>-0.002840909090909041</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2021,6 +2255,12 @@
       <c r="L39" s="2" t="n">
         <v>-0.0001819174094960526</v>
       </c>
+      <c r="M39" s="1" t="n">
+        <v>109.74</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>-0.0016375545851529</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2061,6 +2301,12 @@
       <c r="L40" s="2" t="n">
         <v>-0.02439024390243893</v>
       </c>
+      <c r="M40" s="1" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0.001329787234042591</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2101,6 +2347,12 @@
       <c r="L41" s="3" t="n">
         <v>0.001617832104979324</v>
       </c>
+      <c r="M41" s="1" t="n">
+        <v>0.05554</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-0.003230437903804731</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2141,6 +2393,12 @@
       <c r="L42" s="2" t="n">
         <v>-0.0007355645457888773</v>
       </c>
+      <c r="M42" s="1" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-0.002392344497607702</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2181,6 +2439,12 @@
       <c r="L43" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M43" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2221,6 +2485,12 @@
       <c r="L44" s="2" t="n">
         <v>-0.00102075535896577</v>
       </c>
+      <c r="M44" s="1" t="n">
+        <v>0.005866</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-0.001021798365122604</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2261,6 +2531,12 @@
       <c r="L45" s="3" t="n">
         <v>0.01737451737451741</v>
       </c>
+      <c r="M45" s="1" t="n">
+        <v>0.10038</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0.002496754219514633</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2301,6 +2577,12 @@
       <c r="L46" s="2" t="n">
         <v>-0.002162941600576866</v>
       </c>
+      <c r="M46" s="1" t="n">
+        <v>2.776</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>0.002890173410404627</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2341,6 +2623,12 @@
       <c r="L47" s="3" t="n">
         <v>0.0002076411960133046</v>
       </c>
+      <c r="M47" s="1" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0.0003459968168292471</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2381,6 +2669,12 @@
       <c r="L48" s="3" t="n">
         <v>0.003686635944700439</v>
       </c>
+      <c r="M48" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>-0.0137741046831956</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2421,6 +2715,12 @@
       <c r="L49" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M49" s="1" t="n">
+        <v>0.24763</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-0.000847320852162749</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2461,6 +2761,12 @@
       <c r="L50" s="3" t="n">
         <v>0.003176620076238973</v>
       </c>
+      <c r="M50" s="1" t="n">
+        <v>0.04715</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>-0.004644289634790055</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2501,6 +2807,12 @@
       <c r="L51" s="3" t="n">
         <v>0.0002554931016862263</v>
       </c>
+      <c r="M51" s="1" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-0.002554278416347441</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2541,6 +2853,12 @@
       <c r="L52" s="3" t="n">
         <v>0.004273504273504262</v>
       </c>
+      <c r="M52" s="1" t="n">
+        <v>0.000234</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>-0.004255319148936158</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2581,6 +2899,12 @@
       <c r="L53" s="3" t="n">
         <v>0.001809408926417338</v>
       </c>
+      <c r="M53" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>-0.002408187838651484</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2621,6 +2945,12 @@
       <c r="L54" s="2" t="n">
         <v>-0.006018295618680795</v>
       </c>
+      <c r="M54" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0.01719544683942849</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2661,6 +2991,12 @@
       <c r="L55" s="3" t="n">
         <v>0.01155592241023535</v>
       </c>
+      <c r="M55" s="1" t="n">
+        <v>0.12291</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0.002937576499387998</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2701,6 +3037,12 @@
       <c r="L56" s="2" t="n">
         <v>-0.01988195091643373</v>
       </c>
+      <c r="M56" s="1" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>0.01299524564183833</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2741,6 +3083,12 @@
       <c r="L57" s="3" t="n">
         <v>0.002570694087403643</v>
       </c>
+      <c r="M57" s="1" t="n">
+        <v>0.01169</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>-0.0008547008547008199</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2781,6 +3129,12 @@
       <c r="L58" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M58" s="1" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>-0.003015075376884508</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2821,6 +3175,12 @@
       <c r="L59" s="2" t="n">
         <v>-0.002976190476190484</v>
       </c>
+      <c r="M59" s="1" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>0.002985074626865679</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2861,6 +3221,12 @@
       <c r="L60" s="3" t="n">
         <v>0.002602472348731189</v>
       </c>
+      <c r="M60" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>-0.001946787800129752</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2901,6 +3267,12 @@
       <c r="L61" s="2" t="n">
         <v>-0.002875179698731097</v>
       </c>
+      <c r="M61" s="1" t="n">
+        <v>0.15912</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>-0.00257004952046633</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2941,6 +3313,12 @@
       <c r="L62" s="2" t="n">
         <v>-0.001685393258426937</v>
       </c>
+      <c r="M62" s="1" t="n">
+        <v>0.7083</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>-0.003517163759144551</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2981,6 +3359,12 @@
       <c r="L63" s="2" t="n">
         <v>-0.001183031941862375</v>
       </c>
+      <c r="M63" s="1" t="n">
+        <v>5.843</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>-0.01133671742808801</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3021,6 +3405,12 @@
       <c r="L64" s="2" t="n">
         <v>-0.002389990158864125</v>
       </c>
+      <c r="M64" s="1" t="n">
+        <v>0.007086</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-0.001409244644870292</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3061,6 +3451,12 @@
       <c r="L65" s="3" t="n">
         <v>0.01860465116279075</v>
       </c>
+      <c r="M65" s="1" t="n">
+        <v>0.03136</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>0.02283105022831048</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3101,6 +3497,12 @@
       <c r="L66" s="3" t="n">
         <v>0.004255319148936175</v>
       </c>
+      <c r="M66" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>-0.008474576271186331</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3141,6 +3543,12 @@
       <c r="L67" s="3" t="n">
         <v>0.003696857670979671</v>
       </c>
+      <c r="M67" s="1" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>-0.003683241252302029</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3181,6 +3589,12 @@
       <c r="L68" s="2" t="n">
         <v>-0.001489425081918436</v>
       </c>
+      <c r="M68" s="1" t="n">
+        <v>1.9929</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>-0.009099045346062155</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3221,6 +3635,12 @@
       <c r="L69" s="3" t="n">
         <v>0.0003487358326067619</v>
       </c>
+      <c r="M69" s="1" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-0.002440299808262083</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3261,6 +3681,12 @@
       <c r="L70" s="3" t="n">
         <v>0.01941747572815536</v>
       </c>
+      <c r="M70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>-0.009523809523809533</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3301,6 +3727,12 @@
       <c r="L71" s="2" t="n">
         <v>-0.003165938864628836</v>
       </c>
+      <c r="M71" s="1" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>-0.003066476837148203</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3341,6 +3773,12 @@
       <c r="L72" s="3" t="n">
         <v>0.006132075471698093</v>
       </c>
+      <c r="M72" s="1" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>-0.005860290670417258</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3381,6 +3819,12 @@
       <c r="L73" s="3" t="n">
         <v>0.001909611712285165</v>
       </c>
+      <c r="M73" s="1" t="n">
+        <v>0.09404999999999999</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-0.004129606099110562</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3421,6 +3865,12 @@
       <c r="L74" s="3" t="n">
         <v>0.004611101444231845</v>
       </c>
+      <c r="M74" s="1" t="n">
+        <v>1.1618</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>0.006148783233740265</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3461,6 +3911,12 @@
       <c r="L75" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M75" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>0.0031505986137367</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3501,6 +3957,12 @@
       <c r="L76" s="2" t="n">
         <v>-0.003947474421976994</v>
       </c>
+      <c r="M76" s="1" t="n">
+        <v>0.12391</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>0.002183759301197075</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3541,6 +4003,12 @@
       <c r="L77" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M77" s="1" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>-0.002546689303904997</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3581,6 +4049,12 @@
       <c r="L78" s="3" t="n">
         <v>0.0009891196834817297</v>
       </c>
+      <c r="M78" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3621,6 +4095,12 @@
       <c r="L79" s="2" t="n">
         <v>-0.001336898395721813</v>
       </c>
+      <c r="M79" s="1" t="n">
+        <v>0.005955</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-0.003514056224899629</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3661,6 +4141,12 @@
       <c r="L80" s="2" t="n">
         <v>-0.004387033877650448</v>
       </c>
+      <c r="M80" s="1" t="n">
+        <v>0.008069</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-0.01236230110159123</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3701,6 +4187,12 @@
       <c r="L81" s="3" t="n">
         <v>0.001682557487380883</v>
       </c>
+      <c r="M81" s="1" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-0.0005599104143335953</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3741,6 +4233,12 @@
       <c r="L82" s="2" t="n">
         <v>-0.0006199628022317979</v>
       </c>
+      <c r="M82" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-0.003101736972704717</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3781,6 +4279,12 @@
       <c r="L83" s="3" t="n">
         <v>0.0009762050030505331</v>
       </c>
+      <c r="M83" s="1" t="n">
+        <v>8.194000000000001</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-0.001097159575764789</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3821,6 +4325,12 @@
       <c r="L84" s="2" t="n">
         <v>-0.001393430968292201</v>
       </c>
+      <c r="M84" s="1" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-0.001879485134981276</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3861,6 +4371,12 @@
       <c r="L85" s="3" t="n">
         <v>0.001920768307322767</v>
       </c>
+      <c r="M85" s="1" t="n">
+        <v>0.004156</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-0.004073807812125486</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3901,6 +4417,12 @@
       <c r="L86" s="3" t="n">
         <v>0.001353485224453068</v>
       </c>
+      <c r="M86" s="1" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-0.000525643913794507</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3941,6 +4463,12 @@
       <c r="L87" s="2" t="n">
         <v>-0.04480551452486465</v>
       </c>
+      <c r="M87" s="1" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>-0.007216494845360888</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3981,6 +4509,12 @@
       <c r="L88" s="3" t="n">
         <v>0.002661934338952877</v>
       </c>
+      <c r="M88" s="1" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>-0.00176991150442478</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4021,6 +4555,12 @@
       <c r="L89" s="2" t="n">
         <v>-0.00843739453256835</v>
       </c>
+      <c r="M89" s="1" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-0.001021102791014372</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4061,6 +4601,12 @@
       <c r="L90" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M90" s="1" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-0.003889537145079739</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4101,6 +4647,12 @@
       <c r="L91" s="2" t="n">
         <v>-0.01025551885972537</v>
       </c>
+      <c r="M91" s="1" t="n">
+        <v>0.05668</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-0.004566210045662037</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4141,6 +4693,12 @@
       <c r="L92" s="2" t="n">
         <v>-0.002441816100724984</v>
       </c>
+      <c r="M92" s="1" t="n">
+        <v>1.3055</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.001376883653331142</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4181,6 +4739,12 @@
       <c r="L93" s="3" t="n">
         <v>0.001744370440849968</v>
       </c>
+      <c r="M93" s="1" t="n">
+        <v>0.06286</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.004907392749723044</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4221,6 +4785,12 @@
       <c r="L94" s="2" t="n">
         <v>-0.005624296962879606</v>
       </c>
+      <c r="M94" s="1" t="n">
+        <v>0.00886</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>0.002262443438913935</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4261,6 +4831,12 @@
       <c r="L95" s="3" t="n">
         <v>0.0006009615384616391</v>
       </c>
+      <c r="M95" s="1" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-0.001501501501501503</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4301,6 +4877,12 @@
       <c r="L96" s="2" t="n">
         <v>-0.0008798944126704437</v>
       </c>
+      <c r="M96" s="1" t="n">
+        <v>0.02273</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>0.0008806693086745568</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4341,6 +4923,12 @@
       <c r="L97" s="3" t="n">
         <v>0.002750611246943869</v>
       </c>
+      <c r="M97" s="1" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-0.005486132276744886</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4381,6 +4969,12 @@
       <c r="L98" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M98" s="1" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-0.006352087114337674</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4421,6 +5015,12 @@
       <c r="L99" s="2" t="n">
         <v>-0.0009996667777406431</v>
       </c>
+      <c r="M99" s="1" t="n">
+        <v>2.993</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-0.001667778519012788</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4461,6 +5061,12 @@
       <c r="L100" s="2" t="n">
         <v>-0.003770301624129878</v>
       </c>
+      <c r="M100" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>0.002037845705967995</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4501,6 +5107,12 @@
       <c r="L101" s="3" t="n">
         <v>0.0005503577325262036</v>
       </c>
+      <c r="M101" s="1" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.001100110011001101</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4541,6 +5153,12 @@
       <c r="L102" s="3" t="n">
         <v>0.00336157052574961</v>
       </c>
+      <c r="M102" s="1" t="n">
+        <v>0.007282</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.02412221924417041</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4581,6 +5199,12 @@
       <c r="L103" s="2" t="n">
         <v>-0.0005890148726255098</v>
       </c>
+      <c r="M103" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-0.005598939148371966</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4621,6 +5245,12 @@
       <c r="L104" s="2" t="n">
         <v>-0.005307599517490904</v>
       </c>
+      <c r="M104" s="1" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="N104" s="3" t="n">
+        <v>0.0007276255154014613</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4661,6 +5291,12 @@
       <c r="L105" s="3" t="n">
         <v>0.004507042253521131</v>
       </c>
+      <c r="M105" s="1" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-0.003365114974761641</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4701,6 +5337,12 @@
       <c r="L106" s="3" t="n">
         <v>0.003207500616827039</v>
       </c>
+      <c r="M106" s="1" t="n">
+        <v>0.008161</v>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>0.003566158386620698</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4741,6 +5383,12 @@
       <c r="L107" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M107" s="1" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.002753303964757597</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4781,6 +5429,12 @@
       <c r="L108" s="2" t="n">
         <v>-0.003717472118959118</v>
       </c>
+      <c r="M108" s="1" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.008861940298507424</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4821,6 +5475,12 @@
       <c r="L109" s="2" t="n">
         <v>-0.001429081814933971</v>
       </c>
+      <c r="M109" s="1" t="n">
+        <v>0.05622</v>
+      </c>
+      <c r="N109" s="3" t="n">
+        <v>0.005724508050089461</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4861,6 +5521,12 @@
       <c r="L110" s="3" t="n">
         <v>0.002932804278443829</v>
       </c>
+      <c r="M110" s="1" t="n">
+        <v>0.11697</v>
+      </c>
+      <c r="N110" s="3" t="n">
+        <v>0.00602046959662859</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4901,6 +5567,12 @@
       <c r="L111" s="3" t="n">
         <v>0.001014816318246426</v>
       </c>
+      <c r="M111" s="1" t="n">
+        <v>0.09823</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-0.004156528791565365</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4941,6 +5613,12 @@
       <c r="L112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M112" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.00269541778975749</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4981,6 +5659,12 @@
       <c r="L113" s="2" t="n">
         <v>-0.0006109979633400266</v>
       </c>
+      <c r="M113" s="1" t="n">
+        <v>0.09794</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-0.002037905033625491</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5021,6 +5705,12 @@
       <c r="L114" s="3" t="n">
         <v>0.07490636704119857</v>
       </c>
+      <c r="M114" s="1" t="n">
+        <v>0.001743</v>
+      </c>
+      <c r="N114" s="3" t="n">
+        <v>0.01219512195121949</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5061,6 +5751,12 @@
       <c r="L115" s="3" t="n">
         <v>0.002643383530919642</v>
       </c>
+      <c r="M115" s="1" t="n">
+        <v>1.2511</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0004793480866021682</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5101,6 +5797,12 @@
       <c r="L116" s="2" t="n">
         <v>-0.005457598656591082</v>
       </c>
+      <c r="M116" s="1" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.002954833262980186</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5141,6 +5843,12 @@
       <c r="L117" s="2" t="n">
         <v>-0.002634178465591051</v>
       </c>
+      <c r="M117" s="1" t="n">
+        <v>0.06055</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.00049521294156491</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5181,6 +5889,12 @@
       <c r="L118" s="2" t="n">
         <v>-0.01082299887260431</v>
       </c>
+      <c r="M118" s="1" t="n">
+        <v>0.04397</v>
+      </c>
+      <c r="N118" s="3" t="n">
+        <v>0.002279462046956983</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5221,6 +5935,12 @@
       <c r="L119" s="2" t="n">
         <v>-0.007720979765708186</v>
       </c>
+      <c r="M119" s="1" t="n">
+        <v>0.003711</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-0.004292997048564518</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5261,6 +5981,12 @@
       <c r="L120" s="3" t="n">
         <v>0.001270648030495554</v>
       </c>
+      <c r="M120" s="1" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-0.003807106598984775</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5301,6 +6027,12 @@
       <c r="L121" s="2" t="n">
         <v>-0.001677289500167731</v>
       </c>
+      <c r="M121" s="1" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.003696236559139751</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5341,6 +6073,12 @@
       <c r="L122" s="2" t="n">
         <v>-0.002089864158829832</v>
       </c>
+      <c r="M122" s="1" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.003839441535776579</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5381,6 +6119,12 @@
       <c r="L123" s="2" t="n">
         <v>-0.001847140417523471</v>
       </c>
+      <c r="M123" s="1" t="n">
+        <v>0.028671</v>
+      </c>
+      <c r="N123" s="3" t="n">
+        <v>0.001082402234636864</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5421,6 +6165,12 @@
       <c r="L124" s="2" t="n">
         <v>-0.001781170483460575</v>
       </c>
+      <c r="M124" s="1" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-0.004588325261279623</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5461,6 +6211,12 @@
       <c r="L125" s="2" t="n">
         <v>-0.004204556565952868</v>
       </c>
+      <c r="M125" s="1" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>0.004516889238020445</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5501,6 +6257,12 @@
       <c r="L126" s="2" t="n">
         <v>-0.001094091903719868</v>
       </c>
+      <c r="M126" s="1" t="n">
+        <v>0.02704</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.01277838627236216</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5541,6 +6303,12 @@
       <c r="L127" s="2" t="n">
         <v>-0.0009078529278258127</v>
       </c>
+      <c r="M127" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.001363016810540608</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5581,6 +6349,12 @@
       <c r="L128" s="3" t="n">
         <v>0.001237623762376273</v>
       </c>
+      <c r="M128" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.003090234857849199</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5621,6 +6395,12 @@
       <c r="L129" s="3" t="n">
         <v>0.01873688779570288</v>
       </c>
+      <c r="M129" s="1" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>0.009799744354495045</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5661,6 +6441,12 @@
       <c r="L130" s="2" t="n">
         <v>-0.007878374139744218</v>
       </c>
+      <c r="M130" s="1" t="n">
+        <v>0.053708</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-0.001190210518485486</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5701,6 +6487,12 @@
       <c r="L131" s="2" t="n">
         <v>-0.0003665689149560392</v>
       </c>
+      <c r="M131" s="1" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>-0.002077985576335284</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5741,6 +6533,12 @@
       <c r="L132" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M132" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5781,6 +6579,12 @@
       <c r="L133" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M133" s="1" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>-0.003273604410751228</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5821,6 +6625,12 @@
       <c r="L134" s="2" t="n">
         <v>-0.006254114549045398</v>
       </c>
+      <c r="M134" s="1" t="n">
+        <v>0.03019</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5861,6 +6671,12 @@
       <c r="L135" s="3" t="n">
         <v>0.006775832862789304</v>
       </c>
+      <c r="M135" s="1" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>-0.01570386988222092</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5901,6 +6717,12 @@
       <c r="L136" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M136" s="1" t="n">
+        <v>0.03706</v>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>0.002976995940460242</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5941,6 +6763,12 @@
       <c r="L137" s="2" t="n">
         <v>-0.004451038575667731</v>
       </c>
+      <c r="M137" s="1" t="n">
+        <v>0.02675</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>-0.003353204172876297</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5981,6 +6809,12 @@
       <c r="L138" s="3" t="n">
         <v>0.01041666666666659</v>
       </c>
+      <c r="M138" s="1" t="n">
+        <v>2.534</v>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>0.00475812846946868</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6021,6 +6855,12 @@
       <c r="L139" s="2" t="n">
         <v>-0.003361344537815134</v>
       </c>
+      <c r="M139" s="1" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>-0.0008431703204048336</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6061,6 +6901,12 @@
       <c r="L140" s="2" t="n">
         <v>-0.003291639236339677</v>
       </c>
+      <c r="M140" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>-0.003963011889035735</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6101,6 +6947,12 @@
       <c r="L141" s="3" t="n">
         <v>0.0007452953232718747</v>
       </c>
+      <c r="M141" s="1" t="n">
+        <v>16.191</v>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>0.004840811766896258</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6141,6 +6993,12 @@
       <c r="L142" s="3" t="n">
         <v>0.001605136436597045</v>
       </c>
+      <c r="M142" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>-0.0008012820512820186</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6181,6 +7039,12 @@
       <c r="L143" s="2" t="n">
         <v>-0.00149981252343451</v>
       </c>
+      <c r="M143" s="1" t="n">
+        <v>0.02654</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>-0.00337964701464513</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6221,6 +7085,12 @@
       <c r="L144" s="3" t="n">
         <v>0.01374570446735391</v>
       </c>
+      <c r="M144" s="1" t="n">
+        <v>0.004525</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>-0.04131355932203386</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6261,6 +7131,12 @@
       <c r="L145" s="2" t="n">
         <v>-0.005476836498844292</v>
       </c>
+      <c r="M145" s="1" t="n">
+        <v>1.9748</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>-0.002273531046329484</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6301,6 +7177,12 @@
       <c r="L146" s="2" t="n">
         <v>-0.003896103896103888</v>
       </c>
+      <c r="M146" s="1" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="N146" s="3" t="n">
+        <v>0.0008691873098652406</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6341,6 +7223,12 @@
       <c r="L147" s="2" t="n">
         <v>-0.006761999778295083</v>
       </c>
+      <c r="M147" s="1" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>-0.002232142857142921</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6381,6 +7269,12 @@
       <c r="L148" s="3" t="n">
         <v>0.02685571309424509</v>
       </c>
+      <c r="M148" s="1" t="n">
+        <v>0.06106</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>-0.008122157244964158</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6421,6 +7315,12 @@
       <c r="L149" s="3" t="n">
         <v>0.0001690902942171637</v>
       </c>
+      <c r="M149" s="1" t="n">
+        <v>0.05951</v>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>0.006086221470836842</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6461,6 +7361,12 @@
       <c r="L150" s="2" t="n">
         <v>-0.01323220913345158</v>
       </c>
+      <c r="M150" s="1" t="n">
+        <v>0.24549</v>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>0.0036385936222404</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6501,6 +7407,12 @@
       <c r="L151" s="3" t="n">
         <v>0.0001481700992738898</v>
       </c>
+      <c r="M151" s="1" t="n">
+        <v>6.76e-05</v>
+      </c>
+      <c r="N151" s="3" t="n">
+        <v>0.001481481481481517</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6541,6 +7453,12 @@
       <c r="L152" s="3" t="n">
         <v>0.002253267237494369</v>
       </c>
+      <c r="M152" s="1" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>0.0008992805755395942</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6581,6 +7499,12 @@
       <c r="L153" s="3" t="n">
         <v>0.005228758169934609</v>
       </c>
+      <c r="M153" s="1" t="n">
+        <v>0.3059</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>-0.005526657997399153</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6621,6 +7545,12 @@
       <c r="L154" s="2" t="n">
         <v>-0.0002721829069134158</v>
       </c>
+      <c r="M154" s="1" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>-0.007895453307922715</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6661,6 +7591,12 @@
       <c r="L155" s="2" t="n">
         <v>-0.007311827956989278</v>
       </c>
+      <c r="M155" s="1" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6701,6 +7637,12 @@
       <c r="L156" s="2" t="n">
         <v>-0.002473716759431116</v>
       </c>
+      <c r="M156" s="1" t="n">
+        <v>0.08054</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>-0.001363918164910093</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6741,6 +7683,12 @@
       <c r="L157" s="2" t="n">
         <v>-0.00685262464309237</v>
       </c>
+      <c r="M157" s="1" t="n">
+        <v>0.22748</v>
+      </c>
+      <c r="N157" s="3" t="n">
+        <v>0.006147994161616942</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6781,6 +7729,12 @@
       <c r="L158" s="3" t="n">
         <v>0.006415396952686408</v>
       </c>
+      <c r="M158" s="1" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>-0.004382470119521872</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6821,6 +7775,12 @@
       <c r="L159" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M159" s="1" t="n">
+        <v>2.923</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>-0.001366586949094637</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6861,6 +7821,12 @@
       <c r="L160" s="2" t="n">
         <v>-0.00197238658777126</v>
       </c>
+      <c r="M160" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>-0.009881422924901195</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6901,6 +7867,12 @@
       <c r="L161" s="2" t="n">
         <v>-0.001707650273224045</v>
       </c>
+      <c r="M161" s="1" t="n">
+        <v>0.14592</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>-0.00157372562435859</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6941,6 +7913,12 @@
       <c r="L162" s="3" t="n">
         <v>0.0009188361408881974</v>
       </c>
+      <c r="M162" s="1" t="n">
+        <v>0.003259</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>-0.002753977968176222</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6981,6 +7959,12 @@
       <c r="L163" s="3" t="n">
         <v>0.004218561671353995</v>
       </c>
+      <c r="M163" s="1" t="n">
+        <v>0.00498</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>-0.00380076015203039</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7021,6 +8005,12 @@
       <c r="L164" s="3" t="n">
         <v>0.00104384133611694</v>
       </c>
+      <c r="M164" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>-0.005213764337851934</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7061,6 +8051,12 @@
       <c r="L165" s="3" t="n">
         <v>0.00130378096479777</v>
       </c>
+      <c r="M165" s="1" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>-0.003580729166666634</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7101,6 +8097,12 @@
       <c r="L166" s="2" t="n">
         <v>-0.0002155327250520634</v>
       </c>
+      <c r="M166" s="1" t="n">
+        <v>1.3905</v>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>-0.0007904570278814882</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7141,6 +8143,12 @@
       <c r="L167" s="2" t="n">
         <v>-0.001441961067051031</v>
       </c>
+      <c r="M167" s="1" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>-0.00180505415162455</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7181,6 +8189,12 @@
       <c r="L168" s="2" t="n">
         <v>-0.003184713375796181</v>
       </c>
+      <c r="M168" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>-0.003194888178913741</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7221,6 +8235,12 @@
       <c r="L169" s="3" t="n">
         <v>0.000337837837837824</v>
       </c>
+      <c r="M169" s="1" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>-0.001350894967916307</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7261,6 +8281,12 @@
       <c r="L170" s="2" t="n">
         <v>-0.007084095063985324</v>
       </c>
+      <c r="M170" s="1" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="N170" s="3" t="n">
+        <v>0.0004602991944763909</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7301,6 +8327,12 @@
       <c r="L171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M171" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="N171" s="3" t="n">
+        <v>0.006024096385542133</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7341,6 +8373,12 @@
       <c r="L172" s="3" t="n">
         <v>0.1199999999999999</v>
       </c>
+      <c r="M172" s="1" t="n">
+        <v>1.4e-05</v>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7381,6 +8419,12 @@
       <c r="L173" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M173" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>-0.001898433792121423</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7421,6 +8465,12 @@
       <c r="L174" s="2" t="n">
         <v>-0.003215434083601424</v>
       </c>
+      <c r="M174" s="1" t="n">
+        <v>0.09014</v>
+      </c>
+      <c r="N174" s="3" t="n">
+        <v>0.002669632925472793</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7461,6 +8511,12 @@
       <c r="L175" s="3" t="n">
         <v>0.002769315978953201</v>
       </c>
+      <c r="M175" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>-0.002485501242750501</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7501,6 +8557,12 @@
       <c r="L176" s="2" t="n">
         <v>-0.002793296089385361</v>
       </c>
+      <c r="M176" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>-0.0018674136321196</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7541,6 +8603,12 @@
       <c r="L177" s="2" t="n">
         <v>-0.006249999999999962</v>
       </c>
+      <c r="M177" s="1" t="n">
+        <v>0.00791</v>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>-0.005031446540880516</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7581,6 +8649,12 @@
       <c r="L178" s="2" t="n">
         <v>-0.004094165813715444</v>
       </c>
+      <c r="M178" s="1" t="n">
+        <v>0.000973</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7621,6 +8695,12 @@
       <c r="L179" s="2" t="n">
         <v>-0.001523660267293407</v>
       </c>
+      <c r="M179" s="1" t="n">
+        <v>0.022884</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>-0.002267178235088941</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7661,6 +8741,12 @@
       <c r="L180" s="2" t="n">
         <v>-0.005644402634054568</v>
       </c>
+      <c r="M180" s="1" t="n">
+        <v>4.261</v>
+      </c>
+      <c r="N180" s="3" t="n">
+        <v>0.007805108798486368</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7701,6 +8787,12 @@
       <c r="L181" s="2" t="n">
         <v>-0.01196172248803829</v>
       </c>
+      <c r="M181" s="1" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="N181" s="3" t="n">
+        <v>0.007782774126599703</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7741,6 +8833,12 @@
       <c r="L182" s="2" t="n">
         <v>-0.0008082440897150611</v>
       </c>
+      <c r="M182" s="1" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="N182" s="3" t="n">
+        <v>0.001011122345803871</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7781,6 +8879,12 @@
       <c r="L183" s="2" t="n">
         <v>-0.0005484460694698563</v>
       </c>
+      <c r="M183" s="1" t="n">
+        <v>5.454</v>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>-0.002377903786354473</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7821,6 +8925,12 @@
       <c r="L184" s="2" t="n">
         <v>-0.005571030640668529</v>
       </c>
+      <c r="M184" s="1" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>-0.0003501400560223393</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7861,6 +8971,12 @@
       <c r="L185" s="3" t="n">
         <v>0.005945945945946079</v>
       </c>
+      <c r="M185" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="N185" s="3" t="n">
+        <v>0.01128425577646418</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7901,6 +9017,12 @@
       <c r="L186" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M186" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="N186" s="3" t="n">
+        <v>0.003184713375796256</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7941,6 +9063,12 @@
       <c r="L187" s="2" t="n">
         <v>-0.000620732464307858</v>
       </c>
+      <c r="M187" s="1" t="n">
+        <v>0.01603</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>-0.00434782608695656</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7981,6 +9109,12 @@
       <c r="L188" s="2" t="n">
         <v>-0.0002477086945752554</v>
       </c>
+      <c r="M188" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>-0.0002477700693756953</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8021,6 +9155,12 @@
       <c r="L189" s="3" t="n">
         <v>0.0002290426019239634</v>
       </c>
+      <c r="M189" s="1" t="n">
+        <v>0.000436</v>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>-0.001602931073963734</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8061,6 +9201,12 @@
       <c r="L190" s="3" t="n">
         <v>0.007839721254355383</v>
       </c>
+      <c r="M190" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="N190" s="3" t="n">
+        <v>0.001728608470181433</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8101,6 +9247,12 @@
       <c r="L191" s="2" t="n">
         <v>-0.003172588832487401</v>
       </c>
+      <c r="M191" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="N191" s="3" t="n">
+        <v>0.001273074474856948</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8141,6 +9293,12 @@
       <c r="L192" s="3" t="n">
         <v>0.002328914367610143</v>
       </c>
+      <c r="M192" s="1" t="n">
+        <v>0.05601</v>
+      </c>
+      <c r="N192" s="3" t="n">
+        <v>0.00107238605898119</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8181,6 +9339,12 @@
       <c r="L193" s="2" t="n">
         <v>-0.001606855918585938</v>
       </c>
+      <c r="M193" s="1" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="N193" s="2" t="n">
+        <v>-0.003755364806866986</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8221,6 +9385,12 @@
       <c r="L194" s="2" t="n">
         <v>-0.002087682672233735</v>
       </c>
+      <c r="M194" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="N194" s="2" t="n">
+        <v>-0.001569037656903883</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8261,6 +9431,12 @@
       <c r="L195" s="3" t="n">
         <v>0.005330243337195885</v>
       </c>
+      <c r="M195" s="1" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="N195" s="2" t="n">
+        <v>-0.009451360073766695</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8301,6 +9477,12 @@
       <c r="L196" s="2" t="n">
         <v>-0.00476568705321692</v>
       </c>
+      <c r="M196" s="1" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="N196" s="2" t="n">
+        <v>-0.003990422984836368</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8341,6 +9523,12 @@
       <c r="L197" s="2" t="n">
         <v>-0.0006560244915810681</v>
       </c>
+      <c r="M197" s="1" t="n">
+        <v>0.04571</v>
+      </c>
+      <c r="N197" s="3" t="n">
+        <v>0.0002188183807440495</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8381,6 +9569,12 @@
       <c r="L198" s="3" t="n">
         <v>0.00648202710665875</v>
       </c>
+      <c r="M198" s="1" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>-0.001366120218579085</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8421,6 +9615,12 @@
       <c r="L199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M199" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="N199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8461,6 +9661,12 @@
       <c r="L200" s="3" t="n">
         <v>0.0006761325219744127</v>
       </c>
+      <c r="M200" s="1" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="N200" s="3" t="n">
+        <v>0.003378378378378306</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8501,6 +9707,12 @@
       <c r="L201" s="2" t="n">
         <v>-0.001764602082230538</v>
       </c>
+      <c r="M201" s="1" t="n">
+        <v>0.005669</v>
+      </c>
+      <c r="N201" s="3" t="n">
+        <v>0.002121265688527616</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8541,6 +9753,12 @@
       <c r="L202" s="3" t="n">
         <v>0.02487078676503059</v>
       </c>
+      <c r="M202" s="1" t="n">
+        <v>0.023088</v>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>-0.004827586206896445</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8581,6 +9799,12 @@
       <c r="L203" s="2" t="n">
         <v>-0.003610108303249076</v>
       </c>
+      <c r="M203" s="1" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="N203" s="2" t="n">
+        <v>-0.007246376811594159</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8621,6 +9845,12 @@
       <c r="L204" s="2" t="n">
         <v>-0.001473622163277378</v>
       </c>
+      <c r="M204" s="1" t="n">
+        <v>0.03399</v>
+      </c>
+      <c r="N204" s="3" t="n">
+        <v>0.003246753246753217</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8661,6 +9891,12 @@
       <c r="L205" s="2" t="n">
         <v>-0.007692307692307777</v>
       </c>
+      <c r="M205" s="1" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>-0.001644350481559707</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8701,6 +9937,12 @@
       <c r="L206" s="2" t="n">
         <v>-0.002762430939226522</v>
       </c>
+      <c r="M206" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N206" s="2" t="n">
+        <v>-0.002770083102493077</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8741,6 +9983,12 @@
       <c r="L207" s="2" t="n">
         <v>-0.01237573544329476</v>
       </c>
+      <c r="M207" s="1" t="n">
+        <v>0.0009954</v>
+      </c>
+      <c r="N207" s="3" t="n">
+        <v>0.02239112571898109</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8781,6 +10029,12 @@
       <c r="L208" s="3" t="n">
         <v>0.002193283070596233</v>
       </c>
+      <c r="M208" s="1" t="n">
+        <v>0.007283</v>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>-0.003829845438380438</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8821,6 +10075,12 @@
       <c r="L209" s="2" t="n">
         <v>-0.001666666666666599</v>
       </c>
+      <c r="M209" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N209" s="3" t="n">
+        <v>0.001669449081802937</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8861,6 +10121,12 @@
       <c r="L210" s="3" t="n">
         <v>0.002318392581143914</v>
       </c>
+      <c r="M210" s="1" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="N210" s="2" t="n">
+        <v>-0.002313030069391075</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8901,6 +10167,12 @@
       <c r="L211" s="3" t="n">
         <v>0.0001406865503658037</v>
       </c>
+      <c r="M211" s="1" t="n">
+        <v>0.007097</v>
+      </c>
+      <c r="N211" s="2" t="n">
+        <v>-0.001688001125334064</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8941,6 +10213,12 @@
       <c r="L212" s="2" t="n">
         <v>-0.009342560553633149</v>
       </c>
+      <c r="M212" s="1" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="N212" s="3" t="n">
+        <v>0.000698567935731673</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8981,6 +10259,12 @@
       <c r="L213" s="3" t="n">
         <v>0.0001749781277340868</v>
       </c>
+      <c r="M213" s="1" t="n">
+        <v>0.05669</v>
+      </c>
+      <c r="N213" s="2" t="n">
+        <v>-0.008222533240028081</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9021,6 +10305,12 @@
       <c r="L214" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M214" s="1" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="N214" s="2" t="n">
+        <v>-0.001063264221158841</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9061,6 +10351,12 @@
       <c r="L215" s="2" t="n">
         <v>-0.0003813882532417846</v>
       </c>
+      <c r="M215" s="1" t="n">
+        <v>0.05239</v>
+      </c>
+      <c r="N215" s="2" t="n">
+        <v>-0.0005723006486074446</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9101,6 +10397,12 @@
       <c r="L216" s="2" t="n">
         <v>-0.002391200382591964</v>
       </c>
+      <c r="M216" s="1" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>0.001917545541706454</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9141,6 +10443,12 @@
       <c r="L217" s="2" t="n">
         <v>-0.0001660577881103178</v>
       </c>
+      <c r="M217" s="1" t="n">
+        <v>6.007</v>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>-0.002325195150307297</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9181,6 +10489,12 @@
       <c r="L218" s="3" t="n">
         <v>0.0006796556411418473</v>
       </c>
+      <c r="M218" s="1" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="N218" s="2" t="n">
+        <v>-0.0004527960153950147</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9221,6 +10535,12 @@
       <c r="L219" s="2" t="n">
         <v>-0.001119402985074613</v>
       </c>
+      <c r="M219" s="1" t="n">
+        <v>0.005354</v>
+      </c>
+      <c r="N219" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9261,6 +10581,12 @@
       <c r="L220" s="2" t="n">
         <v>-0.0004859086491739355</v>
       </c>
+      <c r="M220" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="N220" s="3" t="n">
+        <v>0.002187651920272236</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9301,6 +10627,12 @@
       <c r="L221" s="2" t="n">
         <v>-0.001037344398340237</v>
       </c>
+      <c r="M221" s="1" t="n">
+        <v>0.005776</v>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>-0.0003461405330564668</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9341,6 +10673,12 @@
       <c r="L222" s="3" t="n">
         <v>0.003311258278145637</v>
       </c>
+      <c r="M222" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>-0.003300330033003242</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9381,6 +10719,12 @@
       <c r="L223" s="2" t="n">
         <v>-0.001480165778567201</v>
       </c>
+      <c r="M223" s="1" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>-0.002075303883782919</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9421,6 +10765,12 @@
       <c r="L224" s="2" t="n">
         <v>-0.0002307869836142268</v>
       </c>
+      <c r="M224" s="1" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>-0.003231763619575155</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9461,6 +10811,12 @@
       <c r="L225" s="3" t="n">
         <v>0.0008387251377903994</v>
       </c>
+      <c r="M225" s="1" t="n">
+        <v>0.08352999999999999</v>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9501,6 +10857,12 @@
       <c r="L226" s="3" t="n">
         <v>0.004807692307692297</v>
       </c>
+      <c r="M226" s="1" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="N226" s="2" t="n">
+        <v>-0.0005316321105794574</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9541,6 +10903,12 @@
       <c r="L227" s="3" t="n">
         <v>0.001502145922746794</v>
       </c>
+      <c r="M227" s="1" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="N227" s="2" t="n">
+        <v>-0.002785515320334371</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9581,6 +10949,12 @@
       <c r="L228" s="2" t="n">
         <v>-0.0008616975441621135</v>
       </c>
+      <c r="M228" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="N228" s="3" t="n">
+        <v>0.0004312203536006724</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9621,6 +10995,12 @@
       <c r="L229" s="3" t="n">
         <v>0.001862197392923703</v>
       </c>
+      <c r="M229" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>-0.001858736059479607</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9661,6 +11041,12 @@
       <c r="L230" s="2" t="n">
         <v>-0.0005984440454816815</v>
       </c>
+      <c r="M230" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="N230" s="2" t="n">
+        <v>-0.005988023952095813</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9701,6 +11087,12 @@
       <c r="L231" s="3" t="n">
         <v>0.0003285151116952386</v>
       </c>
+      <c r="M231" s="1" t="n">
+        <v>0.03047</v>
+      </c>
+      <c r="N231" s="3" t="n">
+        <v>0.0006568144499178714</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9741,6 +11133,12 @@
       <c r="L232" s="3" t="n">
         <v>0.0008650519031141515</v>
       </c>
+      <c r="M232" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>-0.0025929127052723</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9781,6 +11179,12 @@
       <c r="L233" s="3" t="n">
         <v>0.02467563480060511</v>
       </c>
+      <c r="M233" s="1" t="n">
+        <v>0.12016</v>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>-0.06657344830264901</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9821,6 +11225,12 @@
       <c r="L234" s="3" t="n">
         <v>0.001979414093428347</v>
       </c>
+      <c r="M234" s="1" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="N234" s="2" t="n">
+        <v>-0.00158040300276575</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9861,6 +11271,12 @@
       <c r="L235" s="2" t="n">
         <v>-0.001583189407023589</v>
       </c>
+      <c r="M235" s="1" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>-0.002450627072221471</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9901,6 +11317,12 @@
       <c r="L236" s="3" t="n">
         <v>0.024568012447793</v>
       </c>
+      <c r="M236" s="1" t="n">
+        <v>0.12452</v>
+      </c>
+      <c r="N236" s="2" t="n">
+        <v>-0.004715850051954227</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9941,6 +11363,12 @@
       <c r="L237" s="3" t="n">
         <v>0.002073613271124851</v>
       </c>
+      <c r="M237" s="1" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>-0.005949301603724807</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9981,6 +11409,12 @@
       <c r="L238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10021,6 +11455,12 @@
       <c r="L239" s="2" t="n">
         <v>-0.0009995002498751951</v>
       </c>
+      <c r="M239" s="1" t="n">
+        <v>0.003931</v>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>-0.01675837918959485</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10061,6 +11501,12 @@
       <c r="L240" s="3" t="n">
         <v>0.00291545189504374</v>
       </c>
+      <c r="M240" s="1" t="n">
+        <v>0.01372</v>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>-0.002906976744186054</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10101,6 +11547,12 @@
       <c r="L241" s="3" t="n">
         <v>0.001629422718808273</v>
       </c>
+      <c r="M241" s="1" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="N241" s="3" t="n">
+        <v>0.004880316058563771</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10141,6 +11593,12 @@
       <c r="L242" s="3" t="n">
         <v>0.001355013550135446</v>
       </c>
+      <c r="M242" s="1" t="n">
+        <v>0.00739</v>
+      </c>
+      <c r="N242" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10181,6 +11639,12 @@
       <c r="L243" s="2" t="n">
         <v>-0.001302083333333431</v>
       </c>
+      <c r="M243" s="1" t="n">
+        <v>0.02292</v>
+      </c>
+      <c r="N243" s="2" t="n">
+        <v>-0.003911342894393733</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10221,6 +11685,12 @@
       <c r="L244" s="2" t="n">
         <v>-0.004750593824228016</v>
       </c>
+      <c r="M244" s="1" t="n">
+        <v>0.00167</v>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>-0.00357995226730306</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10261,6 +11731,12 @@
       <c r="L245" s="2" t="n">
         <v>-0.0007581501137224336</v>
       </c>
+      <c r="M245" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>-0.002276176024279171</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10301,6 +11777,12 @@
       <c r="L246" s="3" t="n">
         <v>0.003779527559055183</v>
       </c>
+      <c r="M246" s="1" t="n">
+        <v>0.03147</v>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>-0.01255098839033588</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10341,6 +11823,12 @@
       <c r="L247" s="2" t="n">
         <v>-0.002252252252252317</v>
       </c>
+      <c r="M247" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="N247" s="2" t="n">
+        <v>-0.001128668171557595</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10381,6 +11869,12 @@
       <c r="L248" s="3" t="n">
         <v>0.004884402474763835</v>
       </c>
+      <c r="M248" s="1" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>-0.01490602721970184</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10421,6 +11915,12 @@
       <c r="L249" s="2" t="n">
         <v>-0.02575304667739693</v>
       </c>
+      <c r="M249" s="1" t="n">
+        <v>0.008553</v>
+      </c>
+      <c r="N249" s="3" t="n">
+        <v>0.009322633939107766</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10461,6 +11961,12 @@
       <c r="L250" s="2" t="n">
         <v>-0.006740491092922543</v>
       </c>
+      <c r="M250" s="1" t="n">
+        <v>0.02049</v>
+      </c>
+      <c r="N250" s="2" t="n">
+        <v>-0.006786233640329509</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10501,6 +12007,12 @@
       <c r="L251" s="3" t="n">
         <v>0.001710132535271414</v>
       </c>
+      <c r="M251" s="1" t="n">
+        <v>0.04663</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>-0.004908237302603522</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10541,6 +12053,12 @@
       <c r="L252" s="3" t="n">
         <v>0.005001190759704737</v>
       </c>
+      <c r="M252" s="1" t="n">
+        <v>0.008449</v>
+      </c>
+      <c r="N252" s="3" t="n">
+        <v>0.001066350710900513</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10581,6 +12099,12 @@
       <c r="L253" s="3" t="n">
         <v>0.009399477806788492</v>
       </c>
+      <c r="M253" s="1" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>-0.005949301603724807</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10621,6 +12145,12 @@
       <c r="L254" s="2" t="n">
         <v>-0.0009808729769495584</v>
       </c>
+      <c r="M254" s="1" t="n">
+        <v>0.06109</v>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>-0.0003272786777941284</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10661,6 +12191,12 @@
       <c r="L255" s="2" t="n">
         <v>-0.001676914477361635</v>
       </c>
+      <c r="M255" s="1" t="n">
+        <v>0.003578</v>
+      </c>
+      <c r="N255" s="3" t="n">
+        <v>0.0016797312430011</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10701,6 +12237,12 @@
       <c r="L256" s="3" t="n">
         <v>0.003323262839879202</v>
       </c>
+      <c r="M256" s="1" t="n">
+        <v>0.013102</v>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>-0.01370069256248117</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10741,6 +12283,12 @@
       <c r="L257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M257" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10781,6 +12329,12 @@
       <c r="L258" s="3" t="n">
         <v>0.01089349866728469</v>
       </c>
+      <c r="M258" s="1" t="n">
+        <v>0.08694</v>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>-0.003324544308150849</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10821,6 +12375,12 @@
       <c r="L259" s="3" t="n">
         <v>0.000784665396256032</v>
       </c>
+      <c r="M259" s="1" t="n">
+        <v>0.08933000000000001</v>
+      </c>
+      <c r="N259" s="3" t="n">
+        <v>0.0005600358422940006</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -10861,6 +12421,12 @@
       <c r="L260" s="3" t="n">
         <v>0.0009821976672806706</v>
       </c>
+      <c r="M260" s="1" t="n">
+        <v>0.08141</v>
+      </c>
+      <c r="N260" s="2" t="n">
+        <v>-0.001471850852447062</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10901,6 +12467,12 @@
       <c r="L261" s="3" t="n">
         <v>0.004456327985739655</v>
       </c>
+      <c r="M261" s="1" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="N261" s="3" t="n">
+        <v>0.007985803016858826</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10941,6 +12513,12 @@
       <c r="L262" s="2" t="n">
         <v>-0.009479956663055221</v>
       </c>
+      <c r="M262" s="1" t="n">
+        <v>0.003691</v>
+      </c>
+      <c r="N262" s="3" t="n">
+        <v>0.009297238173366076</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -10981,6 +12559,12 @@
       <c r="L263" s="2" t="n">
         <v>-0.00765957446808509</v>
       </c>
+      <c r="M263" s="1" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>-0.002572898799313848</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11021,6 +12605,12 @@
       <c r="L264" s="3" t="n">
         <v>0.002956521739130412</v>
       </c>
+      <c r="M264" s="1" t="n">
+        <v>0.0005777</v>
+      </c>
+      <c r="N264" s="3" t="n">
+        <v>0.001734003814808435</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11061,6 +12651,12 @@
       <c r="L265" s="2" t="n">
         <v>-0.002670226969292397</v>
       </c>
+      <c r="M265" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>-0.005354752342704164</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11101,6 +12697,12 @@
       <c r="L266" s="2" t="n">
         <v>-0.001572327044025202</v>
       </c>
+      <c r="M266" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="N266" s="3" t="n">
+        <v>0.001574803149606344</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11141,6 +12743,12 @@
       <c r="L267" s="2" t="n">
         <v>-0.004872107186358113</v>
       </c>
+      <c r="M267" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="N267" s="2" t="n">
+        <v>-0.001223990208078285</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11181,6 +12789,12 @@
       <c r="L268" s="3" t="n">
         <v>0.009824561403508757</v>
       </c>
+      <c r="M268" s="1" t="n">
+        <v>0.0004305</v>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>-0.002779708130646224</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11221,6 +12835,12 @@
       <c r="L269" s="2" t="n">
         <v>-0.003840614498319741</v>
       </c>
+      <c r="M269" s="1" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>-0.0004819277108433538</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11261,6 +12881,12 @@
       <c r="L270" s="3" t="n">
         <v>0.0005537098560353764</v>
       </c>
+      <c r="M270" s="1" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>-0.006087437742113945</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11301,6 +12927,12 @@
       <c r="L271" s="3" t="n">
         <v>0.00136425648021832</v>
       </c>
+      <c r="M271" s="1" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>-0.0006811989100818579</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11341,6 +12973,12 @@
       <c r="L272" s="3" t="n">
         <v>0.003024955886060047</v>
       </c>
+      <c r="M272" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11381,6 +13019,12 @@
       <c r="L273" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M273" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>-0.005359056806002148</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11421,6 +13065,12 @@
       <c r="L274" s="2" t="n">
         <v>-0.002370417193426021</v>
       </c>
+      <c r="M274" s="1" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>-0.0007920164739427255</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11461,6 +13111,12 @@
       <c r="L275" s="2" t="n">
         <v>-0.006076388888888942</v>
       </c>
+      <c r="M275" s="1" t="n">
+        <v>0.01137</v>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>-0.006986899563318796</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11501,6 +13157,12 @@
       <c r="L276" s="2" t="n">
         <v>-0.001158301158301031</v>
       </c>
+      <c r="M276" s="1" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>-0.0007730962504832716</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -11541,6 +13203,12 @@
       <c r="L277" s="3" t="n">
         <v>0.0004761904761904568</v>
       </c>
+      <c r="M277" s="1" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>-0.001903855306996756</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11581,6 +13249,12 @@
       <c r="L278" s="3" t="n">
         <v>0.009409304756926272</v>
       </c>
+      <c r="M278" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>-0.007767995857068919</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -11621,6 +13295,12 @@
       <c r="L279" s="2" t="n">
         <v>-0.003029762965603218</v>
       </c>
+      <c r="M279" s="1" t="n">
+        <v>0.005587</v>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>-0.001251340722202371</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11661,6 +13341,12 @@
       <c r="L280" s="2" t="n">
         <v>-0.002865329512893956</v>
       </c>
+      <c r="M280" s="1" t="n">
+        <v>0.03834</v>
+      </c>
+      <c r="N280" s="3" t="n">
+        <v>0.001567398119122193</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11701,6 +13387,12 @@
       <c r="L281" s="3" t="n">
         <v>0.001108647450110866</v>
       </c>
+      <c r="M281" s="1" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="N281" s="2" t="n">
+        <v>-0.001107419712070876</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11741,6 +13433,12 @@
       <c r="L282" s="3" t="n">
         <v>0.0009985022466300793</v>
       </c>
+      <c r="M282" s="1" t="n">
+        <v>0.0004019</v>
+      </c>
+      <c r="N282" s="3" t="n">
+        <v>0.002244389027431476</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -11781,6 +13479,12 @@
       <c r="L283" s="3" t="n">
         <v>0.01265182186234819</v>
       </c>
+      <c r="M283" s="1" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="N283" s="3" t="n">
+        <v>0.001749125437281375</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11821,6 +13525,12 @@
       <c r="L284" s="2" t="n">
         <v>-0.0004783544606553261</v>
       </c>
+      <c r="M284" s="1" t="n">
+        <v>0.04166</v>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>-0.00311079205551563</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -11861,6 +13571,12 @@
       <c r="L285" s="3" t="n">
         <v>0.001020597513453321</v>
       </c>
+      <c r="M285" s="1" t="n">
+        <v>0.10787</v>
+      </c>
+      <c r="N285" s="2" t="n">
+        <v>-0.0001853739920289751</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -11901,6 +13617,12 @@
       <c r="L286" s="3" t="n">
         <v>0.002398081534772085</v>
       </c>
+      <c r="M286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="N286" s="3" t="n">
+        <v>0.002392344497607766</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11941,6 +13663,12 @@
       <c r="L287" s="2" t="n">
         <v>-0.000264655286489245</v>
       </c>
+      <c r="M287" s="1" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>-0.002051621442753175</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -11981,6 +13709,12 @@
       <c r="L288" s="2" t="n">
         <v>-0.00328947368421062</v>
       </c>
+      <c r="M288" s="1" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="N288" s="2" t="n">
+        <v>-0.01100110011001101</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12021,6 +13755,12 @@
       <c r="L289" s="3" t="n">
         <v>0.0004842615012106004</v>
       </c>
+      <c r="M289" s="1" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="N289" s="2" t="n">
+        <v>-0.001694094869312603</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12061,6 +13801,12 @@
       <c r="L290" s="3" t="n">
         <v>0.0004705328784848649</v>
       </c>
+      <c r="M290" s="1" t="n">
+        <v>0.08527999999999999</v>
+      </c>
+      <c r="N290" s="3" t="n">
+        <v>0.002704291593180413</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12101,6 +13847,12 @@
       <c r="L291" s="2" t="n">
         <v>-0.000846501128668235</v>
       </c>
+      <c r="M291" s="1" t="n">
+        <v>0.03535</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>-0.001694436599830487</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12141,6 +13893,12 @@
       <c r="L292" s="3" t="n">
         <v>0.002404837158169616</v>
       </c>
+      <c r="M292" s="1" t="n">
+        <v>1.4608</v>
+      </c>
+      <c r="N292" s="3" t="n">
+        <v>0.001302351086434994</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12181,6 +13939,12 @@
       <c r="L293" s="2" t="n">
         <v>-0.001876172607879878</v>
       </c>
+      <c r="M293" s="1" t="n">
+        <v>0.005844</v>
+      </c>
+      <c r="N293" s="2" t="n">
+        <v>-0.001367053998632979</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12221,6 +13985,12 @@
       <c r="L294" s="2" t="n">
         <v>-0.005836008170411454</v>
       </c>
+      <c r="M294" s="1" t="n">
+        <v>0.003404</v>
+      </c>
+      <c r="N294" s="2" t="n">
+        <v>-0.0008805400645729277</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12261,6 +14031,12 @@
       <c r="L295" s="3" t="n">
         <v>0.00223131275567142</v>
       </c>
+      <c r="M295" s="1" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="N295" s="2" t="n">
+        <v>-0.003153988868274647</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12301,6 +14077,12 @@
       <c r="L296" s="3" t="n">
         <v>0.0004448398576511965</v>
       </c>
+      <c r="M296" s="1" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="N296" s="2" t="n">
+        <v>-0.002223210315695817</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12341,6 +14123,12 @@
       <c r="L297" s="3" t="n">
         <v>0.004117647058823361</v>
       </c>
+      <c r="M297" s="1" t="n">
+        <v>0.01697</v>
+      </c>
+      <c r="N297" s="2" t="n">
+        <v>-0.005858230814294049</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12381,6 +14169,12 @@
       <c r="L298" s="2" t="n">
         <v>-0.004152823920265785</v>
       </c>
+      <c r="M298" s="1" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="N298" s="2" t="n">
+        <v>-0.003614122880177991</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12421,6 +14215,12 @@
       <c r="L299" s="2" t="n">
         <v>-0.0009033423667569641</v>
       </c>
+      <c r="M299" s="1" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="N299" s="2" t="n">
+        <v>-0.0009041591320071964</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -12461,6 +14261,12 @@
       <c r="L300" s="2" t="n">
         <v>-0.003373493975903644</v>
       </c>
+      <c r="M300" s="1" t="n">
+        <v>0.02064</v>
+      </c>
+      <c r="N300" s="2" t="n">
+        <v>-0.001934235976789257</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -12501,6 +14307,12 @@
       <c r="L301" s="2" t="n">
         <v>-0.000331564986737364</v>
       </c>
+      <c r="M301" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="N301" s="2" t="n">
+        <v>-0.001658374792703152</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -12541,6 +14353,12 @@
       <c r="L302" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M302" s="1" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="N302" s="2" t="n">
+        <v>-0.002212389380530884</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -12581,6 +14399,12 @@
       <c r="L303" s="3" t="n">
         <v>0.001218191662154749</v>
       </c>
+      <c r="M303" s="1" t="n">
+        <v>0.07396999999999999</v>
+      </c>
+      <c r="N303" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -12621,6 +14445,12 @@
       <c r="L304" s="2" t="n">
         <v>-0.003136762860727601</v>
       </c>
+      <c r="M304" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="N304" s="2" t="n">
+        <v>-0.0006293266205162404</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -12661,6 +14491,12 @@
       <c r="L305" s="3" t="n">
         <v>0.0009227929867733697</v>
       </c>
+      <c r="M305" s="1" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="N305" s="2" t="n">
+        <v>-0.002765826674861703</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -12701,6 +14537,12 @@
       <c r="L306" s="2" t="n">
         <v>-0.002797761790567571</v>
       </c>
+      <c r="M306" s="1" t="n">
+        <v>0.04986</v>
+      </c>
+      <c r="N306" s="2" t="n">
+        <v>-0.000801603206412793</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -12741,6 +14583,12 @@
       <c r="L307" s="2" t="n">
         <v>-0.003225806451612906</v>
       </c>
+      <c r="M307" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="N307" s="2" t="n">
+        <v>-0.002157497303128373</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -12781,6 +14629,12 @@
       <c r="L308" s="3" t="n">
         <v>0.005051780752715301</v>
       </c>
+      <c r="M308" s="1" t="n">
+        <v>0.03973</v>
+      </c>
+      <c r="N308" s="2" t="n">
+        <v>-0.001507916561950177</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -12821,6 +14675,12 @@
       <c r="L309" s="2" t="n">
         <v>-0.01001878522229182</v>
       </c>
+      <c r="M309" s="1" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="N309" s="2" t="n">
+        <v>-0.001265022137887581</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -12861,6 +14721,12 @@
       <c r="L310" s="3" t="n">
         <v>0.002956939567547596</v>
       </c>
+      <c r="M310" s="1" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="N310" s="2" t="n">
+        <v>-0.001289847060991351</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -12901,6 +14767,12 @@
       <c r="L311" s="3" t="n">
         <v>0.0008966599417172228</v>
       </c>
+      <c r="M311" s="1" t="n">
+        <v>0.004456</v>
+      </c>
+      <c r="N311" s="2" t="n">
+        <v>-0.002015677491601417</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12941,6 +14813,12 @@
       <c r="L312" s="3" t="n">
         <v>0.002251718416686533</v>
       </c>
+      <c r="M312" s="1" t="n">
+        <v>0.08445</v>
+      </c>
+      <c r="N312" s="2" t="n">
+        <v>-0.001418942887548882</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -12981,6 +14859,12 @@
       <c r="L313" s="2" t="n">
         <v>-0.0008007473642064676</v>
       </c>
+      <c r="M313" s="1" t="n">
+        <v>0.07478</v>
+      </c>
+      <c r="N313" s="2" t="n">
+        <v>-0.001202083611593519</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13021,6 +14905,12 @@
       <c r="L314" s="2" t="n">
         <v>-0.001955671447196836</v>
       </c>
+      <c r="M314" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="N314" s="3" t="n">
+        <v>0.0006531678641410123</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13061,6 +14951,12 @@
       <c r="L315" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M315" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="N315" s="2" t="n">
+        <v>-0.001251564455569498</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -13101,6 +14997,12 @@
       <c r="L316" s="3" t="n">
         <v>0.001108647450110896</v>
       </c>
+      <c r="M316" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="N316" s="3" t="n">
+        <v>0.0005537098560353764</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -13141,6 +15043,12 @@
       <c r="L317" s="2" t="n">
         <v>-0.0009282588516112003</v>
       </c>
+      <c r="M317" s="1" t="n">
+        <v>0.007502</v>
+      </c>
+      <c r="N317" s="2" t="n">
+        <v>-0.004247411733474902</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -13181,6 +15089,12 @@
       <c r="L318" s="3" t="n">
         <v>0.01268882175226583</v>
       </c>
+      <c r="M318" s="1" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="N318" s="3" t="n">
+        <v>0.001789976133651547</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13221,6 +15135,12 @@
       <c r="L319" s="3" t="n">
         <v>0.003095863781993691</v>
       </c>
+      <c r="M319" s="1" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="N319" s="2" t="n">
+        <v>-0.004091153777139888</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13261,6 +15181,12 @@
       <c r="L320" s="3" t="n">
         <v>0.0006815084052703827</v>
       </c>
+      <c r="M320" s="1" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="N320" s="2" t="n">
+        <v>-0.002270147559591376</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13301,6 +15227,12 @@
       <c r="L321" s="2" t="n">
         <v>-0.001798792239496354</v>
       </c>
+      <c r="M321" s="1" t="n">
+        <v>0.07741000000000001</v>
+      </c>
+      <c r="N321" s="2" t="n">
+        <v>-0.0036040674475478</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13341,6 +15273,12 @@
       <c r="L322" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M322" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="N322" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13381,6 +15319,12 @@
       <c r="L323" s="3" t="n">
         <v>0.0005042864346948511</v>
       </c>
+      <c r="M323" s="1" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="N323" s="2" t="n">
+        <v>-0.004032258064516132</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -13421,6 +15365,12 @@
       <c r="L324" s="3" t="n">
         <v>0.00515774414577222</v>
       </c>
+      <c r="M324" s="1" t="n">
+        <v>0.053284</v>
+      </c>
+      <c r="N324" s="2" t="n">
+        <v>-0.002134911419903423</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -13461,6 +15411,12 @@
       <c r="L325" s="2" t="n">
         <v>-0.0008454734651406022</v>
       </c>
+      <c r="M325" s="1" t="n">
+        <v>0.15323</v>
+      </c>
+      <c r="N325" s="2" t="n">
+        <v>-0.002603658139686153</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -13501,6 +15457,12 @@
       <c r="L326" s="2" t="n">
         <v>-0.007108638541183748</v>
       </c>
+      <c r="M326" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="N326" s="3" t="n">
+        <v>0.003891050583657564</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -13541,6 +15503,12 @@
       <c r="L327" s="3" t="n">
         <v>0.004390341249251652</v>
       </c>
+      <c r="M327" s="1" t="n">
+        <v>0.015133</v>
+      </c>
+      <c r="N327" s="3" t="n">
+        <v>0.002251804755281876</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -13581,6 +15549,12 @@
       <c r="L328" s="3" t="n">
         <v>0.002118644067796671</v>
       </c>
+      <c r="M328" s="1" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="N328" s="3" t="n">
+        <v>0.00105708245243132</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -13621,6 +15595,12 @@
       <c r="L329" s="3" t="n">
         <v>0.002268088001814575</v>
       </c>
+      <c r="M329" s="1" t="n">
+        <v>0.004412</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>-0.001584068793844775</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -13661,6 +15641,12 @@
       <c r="L330" s="2" t="n">
         <v>-0.0005869692819409557</v>
       </c>
+      <c r="M330" s="1" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="N330" s="3" t="n">
+        <v>0.009984338292873856</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -13701,6 +15687,12 @@
       <c r="L331" s="3" t="n">
         <v>0.002734481815696004</v>
       </c>
+      <c r="M331" s="1" t="n">
+        <v>0.03653</v>
+      </c>
+      <c r="N331" s="2" t="n">
+        <v>-0.003817834742296188</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -13741,6 +15733,12 @@
       <c r="L332" s="2" t="n">
         <v>-0.005431093007467721</v>
       </c>
+      <c r="M332" s="1" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="N332" s="2" t="n">
+        <v>-0.002047781569965834</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -13781,6 +15779,12 @@
       <c r="L333" s="3" t="n">
         <v>0.001036269430051843</v>
       </c>
+      <c r="M333" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="N333" s="2" t="n">
+        <v>-0.00207039337474126</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -13821,6 +15825,12 @@
       <c r="L334" s="2" t="n">
         <v>-0.0004569339730410355</v>
       </c>
+      <c r="M334" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="N334" s="2" t="n">
+        <v>-0.001142857142857017</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -13861,6 +15871,12 @@
       <c r="L335" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M335" s="1" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="N335" s="2" t="n">
+        <v>-0.000369094488189004</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -13901,6 +15917,12 @@
       <c r="L336" s="3" t="n">
         <v>0.002443792766373414</v>
       </c>
+      <c r="M336" s="1" t="n">
+        <v>0.2045</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>-0.00292540224280847</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -13941,6 +15963,12 @@
       <c r="L337" s="2" t="n">
         <v>-0.0009803921568628752</v>
       </c>
+      <c r="M337" s="1" t="n">
+        <v>0.01018</v>
+      </c>
+      <c r="N337" s="2" t="n">
+        <v>-0.0009813542688910297</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -13981,6 +16009,12 @@
       <c r="L338" s="2" t="n">
         <v>-0.002650176678445183</v>
       </c>
+      <c r="M338" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="N338" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -14021,6 +16055,12 @@
       <c r="L339" s="2" t="n">
         <v>-0.001634877384196308</v>
       </c>
+      <c r="M339" s="1" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>-0.0005458515283842572</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -14061,6 +16101,12 @@
       <c r="L340" s="2" t="n">
         <v>-0.01002945714686502</v>
       </c>
+      <c r="M340" s="1" t="n">
+        <v>0.28065</v>
+      </c>
+      <c r="N340" s="2" t="n">
+        <v>-0.00584484590860781</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -14101,6 +16147,12 @@
       <c r="L341" s="2" t="n">
         <v>-0.0002313208420077752</v>
       </c>
+      <c r="M341" s="1" t="n">
+        <v>0.04303</v>
+      </c>
+      <c r="N341" s="2" t="n">
+        <v>-0.004396112910689557</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -14141,6 +16193,12 @@
       <c r="L342" s="3" t="n">
         <v>0.0005107252298263326</v>
       </c>
+      <c r="M342" s="1" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="N342" s="3" t="n">
+        <v>0.001786625829504865</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -14181,6 +16239,12 @@
       <c r="L343" s="3" t="n">
         <v>0.001312852829197819</v>
       </c>
+      <c r="M343" s="1" t="n">
+        <v>7.635</v>
+      </c>
+      <c r="N343" s="3" t="n">
+        <v>0.001048905205192082</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14221,6 +16285,12 @@
       <c r="L344" s="2" t="n">
         <v>-0.001325381047051065</v>
       </c>
+      <c r="M344" s="1" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="N344" s="2" t="n">
+        <v>-0.003151957531519597</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14261,6 +16331,12 @@
       <c r="L345" s="3" t="n">
         <v>0.001887810140237341</v>
       </c>
+      <c r="M345" s="1" t="n">
+        <v>0.03703</v>
+      </c>
+      <c r="N345" s="2" t="n">
+        <v>-0.003230148048452276</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -14301,6 +16377,12 @@
       <c r="L346" s="3" t="n">
         <v>0.004842615012106507</v>
       </c>
+      <c r="M346" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="N346" s="2" t="n">
+        <v>-0.002409638554216936</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14341,6 +16423,12 @@
       <c r="L347" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M347" s="1" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="N347" s="2" t="n">
+        <v>-0.002312138728323605</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -14381,6 +16469,12 @@
       <c r="L348" s="3" t="n">
         <v>0.0006751933946794761</v>
       </c>
+      <c r="M348" s="1" t="n">
+        <v>5193.8</v>
+      </c>
+      <c r="N348" s="3" t="n">
+        <v>0.001272362739050039</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -14421,6 +16515,12 @@
       <c r="L349" s="3" t="n">
         <v>0.00221402214022144</v>
       </c>
+      <c r="M349" s="1" t="n">
+        <v>0.01358</v>
+      </c>
+      <c r="N349" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -14461,6 +16561,12 @@
       <c r="L350" s="2" t="n">
         <v>-0.002664890073284484</v>
       </c>
+      <c r="M350" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="N350" s="2" t="n">
+        <v>-0.003340013360053536</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -14501,6 +16607,12 @@
       <c r="L351" s="3" t="n">
         <v>0.0009866798223976559</v>
       </c>
+      <c r="M351" s="1" t="n">
+        <v>0.0006077</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>-0.001642845408247124</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -14541,6 +16653,12 @@
       <c r="L352" s="3" t="n">
         <v>0.002029426686961027</v>
       </c>
+      <c r="M352" s="1" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="N352" s="2" t="n">
+        <v>-0.002531645569620326</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -14581,6 +16699,12 @@
       <c r="L353" s="2" t="n">
         <v>-0.001276324186343427</v>
       </c>
+      <c r="M353" s="1" t="n">
+        <v>0.09309000000000001</v>
+      </c>
+      <c r="N353" s="2" t="n">
+        <v>-0.008626198083066999</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -14621,6 +16745,12 @@
       <c r="L354" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M354" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="N354" s="2" t="n">
+        <v>-0.006586169045005525</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -14661,6 +16791,12 @@
       <c r="L355" s="3" t="n">
         <v>0.005243322955923266</v>
       </c>
+      <c r="M355" s="1" t="n">
+        <v>0.0006129</v>
+      </c>
+      <c r="N355" s="2" t="n">
+        <v>-0.0009779951100244736</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -14701,6 +16837,12 @@
       <c r="L356" s="2" t="n">
         <v>-0.004798464491362875</v>
       </c>
+      <c r="M356" s="1" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="N356" s="2" t="n">
+        <v>-0.008678881388620923</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -14741,6 +16883,12 @@
       <c r="L357" s="2" t="n">
         <v>-0.0008631851532153296</v>
       </c>
+      <c r="M357" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="N357" s="2" t="n">
+        <v>-0.0004319654427645612</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -14781,6 +16929,12 @@
       <c r="L358" s="2" t="n">
         <v>-0.002463054187192178</v>
       </c>
+      <c r="M358" s="1" t="n">
+        <v>0.000404</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>-0.002469135802469062</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -14821,6 +16975,12 @@
       <c r="L359" s="3" t="n">
         <v>0.0006811989100817161</v>
       </c>
+      <c r="M359" s="1" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="N359" s="2" t="n">
+        <v>-0.002722940776038128</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -14861,6 +17021,12 @@
       <c r="L360" s="2" t="n">
         <v>-0.002377414561664119</v>
       </c>
+      <c r="M360" s="1" t="n">
+        <v>0.003346</v>
+      </c>
+      <c r="N360" s="2" t="n">
+        <v>-0.003276735180220482</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14901,6 +17067,12 @@
       <c r="L361" s="2" t="n">
         <v>-0.0001557147306134989</v>
       </c>
+      <c r="M361" s="1" t="n">
+        <v>0.6401</v>
+      </c>
+      <c r="N361" s="2" t="n">
+        <v>-0.003114779629341227</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -14941,6 +17113,12 @@
       <c r="L362" s="2" t="n">
         <v>-0.001278227524499457</v>
       </c>
+      <c r="M362" s="1" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="N362" s="2" t="n">
+        <v>-0.005972696245733693</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -14981,6 +17159,12 @@
       <c r="L363" s="3" t="n">
         <v>0.0006120887528691411</v>
       </c>
+      <c r="M363" s="1" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="N363" s="3" t="n">
+        <v>0.001682214405872442</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -15021,6 +17205,12 @@
       <c r="L364" s="2" t="n">
         <v>-0.0006373486297004703</v>
       </c>
+      <c r="M364" s="1" t="n">
+        <v>4.704</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -15061,6 +17251,12 @@
       <c r="L365" s="3" t="n">
         <v>0.0005624296962879411</v>
       </c>
+      <c r="M365" s="1" t="n">
+        <v>0.07124999999999999</v>
+      </c>
+      <c r="N365" s="3" t="n">
+        <v>0.001264755480606982</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -15101,6 +17297,12 @@
       <c r="L366" s="3" t="n">
         <v>0.002343609158103447</v>
       </c>
+      <c r="M366" s="1" t="n">
+        <v>0.05557</v>
+      </c>
+      <c r="N366" s="2" t="n">
+        <v>-0.0005395683453236566</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -15141,6 +17343,12 @@
       <c r="L367" s="2" t="n">
         <v>-0.002556672916311528</v>
       </c>
+      <c r="M367" s="1" t="n">
+        <v>0.05843</v>
+      </c>
+      <c r="N367" s="2" t="n">
+        <v>-0.001537935748462061</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -15181,6 +17389,12 @@
       <c r="L368" s="3" t="n">
         <v>0.0006996676578624868</v>
       </c>
+      <c r="M368" s="1" t="n">
+        <v>0.05709</v>
+      </c>
+      <c r="N368" s="2" t="n">
+        <v>-0.002097535395909721</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -15221,6 +17435,12 @@
       <c r="L369" s="3" t="n">
         <v>0.0009668063164680067</v>
       </c>
+      <c r="M369" s="1" t="n">
+        <v>0.03098</v>
+      </c>
+      <c r="N369" s="2" t="n">
+        <v>-0.002575660012878307</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -15261,6 +17481,12 @@
       <c r="L370" s="3" t="n">
         <v>0.001849568434031937</v>
       </c>
+      <c r="M370" s="1" t="n">
+        <v>0.0001624</v>
+      </c>
+      <c r="N370" s="2" t="n">
+        <v>-0.0006153846153846304</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -15301,6 +17527,12 @@
       <c r="L371" s="3" t="n">
         <v>0.0001473622163276253</v>
       </c>
+      <c r="M371" s="1" t="n">
+        <v>0.006788</v>
+      </c>
+      <c r="N371" s="3" t="n">
+        <v>0.0001473405039045429</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -15341,6 +17573,12 @@
       <c r="L372" s="3" t="n">
         <v>0.006668599594085247</v>
       </c>
+      <c r="M372" s="1" t="n">
+        <v>0.006928</v>
+      </c>
+      <c r="N372" s="2" t="n">
+        <v>-0.002304147465437719</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -15381,6 +17619,12 @@
       <c r="L373" s="3" t="n">
         <v>0.01444327731092441</v>
       </c>
+      <c r="M373" s="1" t="n">
+        <v>3.817</v>
+      </c>
+      <c r="N373" s="2" t="n">
+        <v>-0.01190784364483557</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -15421,6 +17665,12 @@
       <c r="L374" s="3" t="n">
         <v>0.0008474576271187075</v>
       </c>
+      <c r="M374" s="1" t="n">
+        <v>0.07063999999999999</v>
+      </c>
+      <c r="N374" s="2" t="n">
+        <v>-0.003104713519616312</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -15461,6 +17711,12 @@
       <c r="L375" s="2" t="n">
         <v>-0.005719369598373233</v>
       </c>
+      <c r="M375" s="1" t="n">
+        <v>0.07803</v>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>-0.002556563978013446</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -15501,6 +17757,12 @@
       <c r="L376" s="2" t="n">
         <v>-0.0007971938775509326</v>
       </c>
+      <c r="M376" s="1" t="n">
+        <v>0.06269</v>
+      </c>
+      <c r="N376" s="3" t="n">
+        <v>0.000319131961065777</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -15541,6 +17803,12 @@
       <c r="L377" s="3" t="n">
         <v>0.00183414122887464</v>
       </c>
+      <c r="M377" s="1" t="n">
+        <v>0.07622</v>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>-0.003269255917353213</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -15581,6 +17849,12 @@
       <c r="L378" s="2" t="n">
         <v>-0.002979885771045381</v>
       </c>
+      <c r="M378" s="1" t="n">
+        <v>0.0004018</v>
+      </c>
+      <c r="N378" s="3" t="n">
+        <v>0.0007471980074719982</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -15621,6 +17895,12 @@
       <c r="L379" s="3" t="n">
         <v>0.002016942315449743</v>
       </c>
+      <c r="M379" s="1" t="n">
+        <v>0.07431</v>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>-0.002818035426731104</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -15661,6 +17941,12 @@
       <c r="L380" s="3" t="n">
         <v>0.00297176820208031</v>
       </c>
+      <c r="M380" s="1" t="n">
+        <v>0.001343</v>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>-0.005185185185185231</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -15701,6 +17987,12 @@
       <c r="L381" s="2" t="n">
         <v>-0.0006163328197227192</v>
       </c>
+      <c r="M381" s="1" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>-0.01156336725254397</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -15741,6 +18033,12 @@
       <c r="L382" s="3" t="n">
         <v>0.0007496251874063964</v>
       </c>
+      <c r="M382" s="1" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>-0.0007490636704120844</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -15781,6 +18079,12 @@
       <c r="L383" s="3" t="n">
         <v>0.0005656108597284837</v>
       </c>
+      <c r="M383" s="1" t="n">
+        <v>0.01764</v>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>-0.002826455624646774</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -15821,6 +18125,12 @@
       <c r="L384" s="2" t="n">
         <v>-0.001962708537782196</v>
       </c>
+      <c r="M384" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>-0.0009832841691249053</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -15861,6 +18171,12 @@
       <c r="L385" s="2" t="n">
         <v>-0.001337196344996708</v>
       </c>
+      <c r="M385" s="1" t="n">
+        <v>4.478</v>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>-0.000669493416648095</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -15901,6 +18217,12 @@
       <c r="L386" s="3" t="n">
         <v>0.0007782101167316209</v>
       </c>
+      <c r="M386" s="1" t="n">
+        <v>0.001279</v>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>-0.005443234836703003</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -15941,6 +18263,12 @@
       <c r="L387" s="3" t="n">
         <v>0.0006755615605472212</v>
       </c>
+      <c r="M387" s="1" t="n">
+        <v>0.0005928</v>
+      </c>
+      <c r="N387" s="3" t="n">
+        <v>0.0005063291139239714</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -15981,6 +18309,12 @@
       <c r="L388" s="2" t="n">
         <v>-0.001769911504424707</v>
       </c>
+      <c r="M388" s="1" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>-0.002659574468085152</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -16021,6 +18355,12 @@
       <c r="L389" s="2" t="n">
         <v>-0.003289473684210393</v>
       </c>
+      <c r="M389" s="1" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>-0.001100110011001246</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -16061,6 +18401,12 @@
       <c r="L390" s="2" t="n">
         <v>-0.003419886003799953</v>
       </c>
+      <c r="M390" s="1" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>-0.00101677681748852</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -16101,6 +18447,12 @@
       <c r="L391" s="2" t="n">
         <v>-0.0005855943782938768</v>
       </c>
+      <c r="M391" s="1" t="n">
+        <v>0.05114</v>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>-0.001171875000000088</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -16141,6 +18493,12 @@
       <c r="L392" s="3" t="n">
         <v>0.004201680672268919</v>
       </c>
+      <c r="M392" s="1" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -16181,6 +18539,12 @@
       <c r="L393" s="3" t="n">
         <v>0.004746084480303885</v>
       </c>
+      <c r="M393" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="N393" s="3" t="n">
+        <v>0.007557864903164711</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -16221,6 +18585,12 @@
       <c r="L394" s="2" t="n">
         <v>-0.006760019314340958</v>
       </c>
+      <c r="M394" s="1" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>-0.0009722897423432461</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -16261,6 +18631,12 @@
       <c r="L395" s="2" t="n">
         <v>-0.001025641025641055</v>
       </c>
+      <c r="M395" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>-0.00308008213552356</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -16301,6 +18677,12 @@
       <c r="L396" s="2" t="n">
         <v>-0.00147547030616009</v>
       </c>
+      <c r="M396" s="1" t="n">
+        <v>2.709</v>
+      </c>
+      <c r="N396" s="3" t="n">
+        <v>0.0007388252678242423</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -16341,6 +18723,12 @@
       <c r="L397" s="2" t="n">
         <v>-0.00158227848101266</v>
       </c>
+      <c r="M397" s="1" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="N397" s="3" t="n">
+        <v>0.0007923930269412757</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -16381,6 +18769,12 @@
       <c r="L398" s="3" t="n">
         <v>0.001779359430604981</v>
       </c>
+      <c r="M398" s="1" t="n">
+        <v>0.007306</v>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>-0.001776198934280638</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -16421,6 +18815,12 @@
       <c r="L399" s="3" t="n">
         <v>0.0003847633705270834</v>
       </c>
+      <c r="M399" s="1" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="N399" s="3" t="n">
+        <v>0.002692307692307609</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -16461,6 +18861,12 @@
       <c r="L400" s="2" t="n">
         <v>-0.003458032065388211</v>
       </c>
+      <c r="M400" s="1" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>-0.001577287066246058</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -16501,6 +18907,12 @@
       <c r="L401" s="2" t="n">
         <v>-0.01242571582928148</v>
       </c>
+      <c r="M401" s="1" t="n">
+        <v>0.007289</v>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>-0.003145514223194691</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -16541,6 +18953,12 @@
       <c r="L402" s="3" t="n">
         <v>0.001094810597766542</v>
       </c>
+      <c r="M402" s="1" t="n">
+        <v>0.004569</v>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>-0.0006561679790025221</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -16581,6 +18999,12 @@
       <c r="L403" s="3" t="n">
         <v>0.001893939393939396</v>
       </c>
+      <c r="M403" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -16621,6 +19045,12 @@
       <c r="L404" s="2" t="n">
         <v>-0.0008347245409015264</v>
       </c>
+      <c r="M404" s="1" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="N404" s="3" t="n">
+        <v>0.001253132832080178</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -16661,6 +19091,12 @@
       <c r="L405" s="2" t="n">
         <v>-0.002525832376578707</v>
       </c>
+      <c r="M405" s="1" t="n">
+        <v>0.0008666</v>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>-0.002532228360957579</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -16701,6 +19137,12 @@
       <c r="L406" s="2" t="n">
         <v>-0.00176713135676425</v>
       </c>
+      <c r="M406" s="1" t="n">
+        <v>0.005063</v>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>-0.00413060582218729</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -16741,6 +19183,12 @@
       <c r="L407" s="2" t="n">
         <v>-0.0008244023083264297</v>
       </c>
+      <c r="M407" s="1" t="n">
+        <v>0.01212</v>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -16781,6 +19229,12 @@
       <c r="L408" s="3" t="n">
         <v>0.002077562326869781</v>
       </c>
+      <c r="M408" s="1" t="n">
+        <v>0.001446</v>
+      </c>
+      <c r="N408" s="2" t="n">
+        <v>-0.0006910850034553669</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -16821,6 +19275,12 @@
       <c r="L409" s="3" t="n">
         <v>0.002414810839817543</v>
       </c>
+      <c r="M409" s="1" t="n">
+        <v>0.03742</v>
+      </c>
+      <c r="N409" s="3" t="n">
+        <v>0.001605995717344874</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -16861,6 +19321,12 @@
       <c r="L410" s="2" t="n">
         <v>-0.002444987775061025</v>
       </c>
+      <c r="M410" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -16901,6 +19367,12 @@
       <c r="L411" s="2" t="n">
         <v>-0.004188481675392645</v>
       </c>
+      <c r="M411" s="1" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>-0.003154574132492204</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -16941,6 +19413,12 @@
       <c r="L412" s="3" t="n">
         <v>0.002083953557606449</v>
       </c>
+      <c r="M412" s="1" t="n">
+        <v>0.06705999999999999</v>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>-0.003862150920974602</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -16981,6 +19459,12 @@
       <c r="L413" s="2" t="n">
         <v>-0.00275049115913556</v>
       </c>
+      <c r="M413" s="1" t="n">
+        <v>2535</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>-0.001182033096926714</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -17021,6 +19505,12 @@
       <c r="L414" s="3" t="n">
         <v>0.0007671653241273182</v>
       </c>
+      <c r="M414" s="1" t="n">
+        <v>0.05225</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>0.001341510157148345</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -17061,6 +19551,12 @@
       <c r="L415" s="3" t="n">
         <v>0.01218097447795831</v>
       </c>
+      <c r="M415" s="1" t="n">
+        <v>1.749</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>0.002292263610315188</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -17101,6 +19597,12 @@
       <c r="L416" s="3" t="n">
         <v>0.001307949425955628</v>
       </c>
+      <c r="M416" s="1" t="n">
+        <v>0.06893000000000001</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>0.0004354136429608454</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -17141,6 +19643,12 @@
       <c r="L417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N417" s="3" t="n">
+        <v>0.01351351351351353</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -17181,6 +19689,12 @@
       <c r="L418" s="2" t="n">
         <v>-0.002607561929595902</v>
       </c>
+      <c r="M418" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>-0.001960784313725456</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -17221,6 +19735,12 @@
       <c r="L419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -17261,6 +19781,12 @@
       <c r="L420" s="2" t="n">
         <v>-0.001566579634464688</v>
       </c>
+      <c r="M420" s="1" t="n">
+        <v>0.01913</v>
+      </c>
+      <c r="N420" s="3" t="n">
+        <v>0.0005230125523012338</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -17301,6 +19827,12 @@
       <c r="L421" s="2" t="n">
         <v>-0.003580323785803218</v>
       </c>
+      <c r="M421" s="1" t="n">
+        <v>0.19303</v>
+      </c>
+      <c r="N421" s="3" t="n">
+        <v>0.005207519658386715</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -17341,6 +19873,12 @@
       <c r="L422" s="2" t="n">
         <v>-0.00204498977505094</v>
       </c>
+      <c r="M422" s="1" t="n">
+        <v>0.03424</v>
+      </c>
+      <c r="N422" s="3" t="n">
+        <v>0.002341920374707165</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -17381,6 +19919,12 @@
       <c r="L423" s="2" t="n">
         <v>-0.002109704641350174</v>
       </c>
+      <c r="M423" s="1" t="n">
+        <v>0.1414</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>-0.003523608174770969</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -17421,6 +19965,12 @@
       <c r="L424" s="2" t="n">
         <v>-0.003773584905660387</v>
       </c>
+      <c r="M424" s="1" t="n">
+        <v>0.00526</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>-0.003787878787878798</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -17461,6 +20011,12 @@
       <c r="L425" s="2" t="n">
         <v>-0.001902949571836401</v>
       </c>
+      <c r="M425" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>-0.0009532888465203907</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -17501,6 +20057,12 @@
       <c r="L426" s="2" t="n">
         <v>-0.00212374345179106</v>
       </c>
+      <c r="M426" s="1" t="n">
+        <v>0.007048</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -17541,6 +20103,12 @@
       <c r="L427" s="3" t="n">
         <v>0.0007821666014862204</v>
       </c>
+      <c r="M427" s="1" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>-0.004298554122704277</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -17581,6 +20149,12 @@
       <c r="L428" s="2" t="n">
         <v>-0.003955500618047067</v>
       </c>
+      <c r="M428" s="1" t="n">
+        <v>0.008043</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>-0.001861504095308934</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -17621,6 +20195,12 @@
       <c r="L429" s="3" t="n">
         <v>0.001622060016220534</v>
       </c>
+      <c r="M429" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>-0.004858299595141643</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -17661,6 +20241,12 @@
       <c r="L430" s="2" t="n">
         <v>-0.000596036358217827</v>
       </c>
+      <c r="M430" s="1" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>-0.001490979573579884</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -17701,6 +20287,12 @@
       <c r="L431" s="2" t="n">
         <v>-0.001841620626150938</v>
       </c>
+      <c r="M431" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>-0.003690036900369013</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -17741,6 +20333,12 @@
       <c r="L432" s="3" t="n">
         <v>0.003725165562913863</v>
       </c>
+      <c r="M432" s="1" t="n">
+        <v>0.009705</v>
+      </c>
+      <c r="N432" s="3" t="n">
+        <v>0.0005154639175257522</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -17781,6 +20379,12 @@
       <c r="L433" s="2" t="n">
         <v>-0.002646775745909504</v>
       </c>
+      <c r="M433" s="1" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>-0.001930036188178617</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -17821,6 +20425,12 @@
       <c r="L434" s="2" t="n">
         <v>-0.003819527333492325</v>
       </c>
+      <c r="M434" s="1" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="N434" s="3" t="n">
+        <v>0.003115264797507744</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -17861,6 +20471,12 @@
       <c r="L435" s="3" t="n">
         <v>0.00065061808718291</v>
       </c>
+      <c r="M435" s="1" t="n">
+        <v>0.001533</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>-0.003250975292587785</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -17901,6 +20517,12 @@
       <c r="L436" s="2" t="n">
         <v>-0.002180232558139572</v>
       </c>
+      <c r="M436" s="1" t="n">
+        <v>0.02743</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>-0.001092498179169657</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -17941,6 +20563,12 @@
       <c r="L437" s="2" t="n">
         <v>-0.008434751174840251</v>
       </c>
+      <c r="M437" s="1" t="n">
+        <v>0.08248999999999999</v>
+      </c>
+      <c r="N437" s="3" t="n">
+        <v>0.002430428970713232</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -17981,6 +20609,12 @@
       <c r="L438" s="3" t="n">
         <v>0.0008703220191471093</v>
       </c>
+      <c r="M438" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>-0.002608695652173988</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -18021,6 +20655,12 @@
       <c r="L439" s="3" t="n">
         <v>0.001294498381877024</v>
       </c>
+      <c r="M439" s="1" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>-0.002585649644473176</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -18061,6 +20701,12 @@
       <c r="L440" s="2" t="n">
         <v>-0.001116071428571456</v>
       </c>
+      <c r="M440" s="1" t="n">
+        <v>0.001788</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>-0.001117318435754096</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -18101,6 +20747,12 @@
       <c r="L441" s="3" t="n">
         <v>0.002448313384113161</v>
       </c>
+      <c r="M441" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>-0.001356852103120799</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -18141,6 +20793,12 @@
       <c r="L442" s="3" t="n">
         <v>0.003783783783783817</v>
       </c>
+      <c r="M442" s="1" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>-0.001615508885298803</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -18181,6 +20839,12 @@
       <c r="L443" s="3" t="n">
         <v>0.001173249902229263</v>
       </c>
+      <c r="M443" s="1" t="n">
+        <v>0.12781</v>
+      </c>
+      <c r="N443" s="2" t="n">
+        <v>-0.001484374999999967</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -18221,6 +20885,12 @@
       <c r="L444" s="3" t="n">
         <v>0.01613618228566361</v>
       </c>
+      <c r="M444" s="1" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="N444" s="2" t="n">
+        <v>-0.004449873483989241</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -18261,6 +20931,12 @@
       <c r="L445" s="2" t="n">
         <v>-0.004080623222455755</v>
       </c>
+      <c r="M445" s="1" t="n">
+        <v>0.08051999999999999</v>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>-0.000248323814253863</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -18301,6 +20977,12 @@
       <c r="L446" s="2" t="n">
         <v>-0.000949216896060773</v>
       </c>
+      <c r="M446" s="1" t="n">
+        <v>0.0002109</v>
+      </c>
+      <c r="N446" s="3" t="n">
+        <v>0.001900237529691258</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -18341,6 +21023,12 @@
       <c r="L447" s="3" t="n">
         <v>0.003072196620583725</v>
       </c>
+      <c r="M447" s="1" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>-0.00459418070444112</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -18381,6 +21069,12 @@
       <c r="L448" s="2" t="n">
         <v>-0.00169688309368577</v>
       </c>
+      <c r="M448" s="1" t="n">
+        <v>0.11224</v>
+      </c>
+      <c r="N448" s="3" t="n">
+        <v>0.004115226337448578</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -18421,6 +21115,12 @@
       <c r="L449" s="2" t="n">
         <v>-0.0005931198102016108</v>
       </c>
+      <c r="M449" s="1" t="n">
+        <v>0.001683</v>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>-0.00118694362017807</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -18461,6 +21161,12 @@
       <c r="L450" s="2" t="n">
         <v>-0.0004835589941973038</v>
       </c>
+      <c r="M450" s="1" t="n">
+        <v>0.0002065</v>
+      </c>
+      <c r="N450" s="2" t="n">
+        <v>-0.0009675858732462741</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -18501,6 +21207,12 @@
       <c r="L451" s="3" t="n">
         <v>0.0007587253414263875</v>
       </c>
+      <c r="M451" s="1" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -18541,6 +21253,12 @@
       <c r="L452" s="3" t="n">
         <v>0.0007479431563200373</v>
       </c>
+      <c r="M452" s="1" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="N452" s="3" t="n">
+        <v>0.002242152466367674</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -18581,6 +21299,12 @@
       <c r="L453" s="2" t="n">
         <v>-0.001145475372279369</v>
       </c>
+      <c r="M453" s="1" t="n">
+        <v>0.0001743</v>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>-0.0005733944954128579</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -18621,6 +21345,12 @@
       <c r="L454" s="2" t="n">
         <v>-0.005646116018577629</v>
       </c>
+      <c r="M454" s="1" t="n">
+        <v>0.10846</v>
+      </c>
+      <c r="N454" s="2" t="n">
+        <v>-0.006685593918856989</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -18661,6 +21391,12 @@
       <c r="L455" s="2" t="n">
         <v>-0.0005988023952095149</v>
       </c>
+      <c r="M455" s="1" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="N455" s="3" t="n">
+        <v>0.0001997203914519452</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -18701,6 +21437,12 @@
       <c r="L456" s="2" t="n">
         <v>-0.000750703784798131</v>
       </c>
+      <c r="M456" s="1" t="n">
+        <v>0.015984</v>
+      </c>
+      <c r="N456" s="3" t="n">
+        <v>0.0006886621173230196</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -18741,6 +21483,12 @@
       <c r="L457" s="3" t="n">
         <v>0.002247864528697776</v>
       </c>
+      <c r="M457" s="1" t="n">
+        <v>0.006685</v>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>-0.0004485645933014949</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -18781,6 +21529,12 @@
       <c r="L458" s="3" t="n">
         <v>0.0002079434393844645</v>
       </c>
+      <c r="M458" s="1" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>-0.000623700623700555</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -18821,6 +21575,12 @@
       <c r="L459" s="3" t="n">
         <v>0.0006277463904582021</v>
       </c>
+      <c r="M459" s="1" t="n">
+        <v>0.006373</v>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>-0.0004705144291090858</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -18861,6 +21621,12 @@
       <c r="L460" s="2" t="n">
         <v>-0.0007235890014470984</v>
       </c>
+      <c r="M460" s="1" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="N460" s="2" t="n">
+        <v>-0.001448225923244068</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -18901,6 +21667,12 @@
       <c r="L461" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M461" s="1" t="n">
+        <v>0.08928999999999999</v>
+      </c>
+      <c r="N461" s="3" t="n">
+        <v>0.003033026286227729</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -18941,6 +21713,12 @@
       <c r="L462" s="3" t="n">
         <v>0.006178287731685845</v>
       </c>
+      <c r="M462" s="1" t="n">
+        <v>0.04582</v>
+      </c>
+      <c r="N462" s="3" t="n">
+        <v>0.004824561403508727</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -18981,6 +21759,12 @@
       <c r="L463" s="3" t="n">
         <v>0.00286532951289399</v>
       </c>
+      <c r="M463" s="1" t="n">
+        <v>0.00697</v>
+      </c>
+      <c r="N463" s="2" t="n">
+        <v>-0.004285714285714359</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -19021,6 +21805,12 @@
       <c r="L464" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M464" s="1" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="N464" s="2" t="n">
+        <v>-0.002286585365853745</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -19061,6 +21851,12 @@
       <c r="L465" s="3" t="n">
         <v>0.001070281840884847</v>
       </c>
+      <c r="M465" s="1" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="N465" s="3" t="n">
+        <v>0.002494654312188091</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -19101,6 +21897,12 @@
       <c r="L466" s="3" t="n">
         <v>0.0007037297677690991</v>
       </c>
+      <c r="M466" s="1" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="N466" s="2" t="n">
+        <v>-0.002812939521800284</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -19141,6 +21943,12 @@
       <c r="L467" s="2" t="n">
         <v>-0.002084418968212526</v>
       </c>
+      <c r="M467" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="N467" s="2" t="n">
+        <v>-0.003133159268929557</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -19181,6 +21989,12 @@
       <c r="L468" s="2" t="n">
         <v>-0.002016129032257982</v>
       </c>
+      <c r="M468" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="N468" s="2" t="n">
+        <v>-0.002020202020202113</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -19221,6 +22035,12 @@
       <c r="L469" s="2" t="n">
         <v>-0.0009970089730807863</v>
       </c>
+      <c r="M469" s="1" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="N469" s="3" t="n">
+        <v>0.001746506986028029</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -19261,6 +22081,12 @@
       <c r="L470" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -19301,6 +22127,12 @@
       <c r="L471" s="2" t="n">
         <v>-0.00433034333436444</v>
       </c>
+      <c r="M471" s="1" t="n">
+        <v>3.224</v>
+      </c>
+      <c r="N471" s="3" t="n">
+        <v>0.001553277415346486</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -19341,6 +22173,12 @@
       <c r="L472" s="2" t="n">
         <v>-0.008935039845448014</v>
       </c>
+      <c r="M472" s="1" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="N472" s="2" t="n">
+        <v>-0.001218323586744674</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -19381,6 +22219,12 @@
       <c r="L473" s="3" t="n">
         <v>0.0008038585209004115</v>
       </c>
+      <c r="M473" s="1" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="N473" s="2" t="n">
+        <v>-0.002409638554216959</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -19421,6 +22265,12 @@
       <c r="L474" s="3" t="n">
         <v>0.0009385265133739238</v>
       </c>
+      <c r="M474" s="1" t="n">
+        <v>0.008503</v>
+      </c>
+      <c r="N474" s="2" t="n">
+        <v>-0.00339896858884195</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -19461,6 +22311,12 @@
       <c r="L475" s="3" t="n">
         <v>0.005993766482857834</v>
       </c>
+      <c r="M475" s="1" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="N475" s="2" t="n">
+        <v>-0.00691134413727356</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -19501,6 +22357,12 @@
       <c r="L476" s="2" t="n">
         <v>-0.003154176129195057</v>
       </c>
+      <c r="M476" s="1" t="n">
+        <v>0.07861</v>
+      </c>
+      <c r="N476" s="2" t="n">
+        <v>-0.005062650297430675</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -19541,6 +22403,12 @@
       <c r="L477" s="3" t="n">
         <v>0.000658665105386263</v>
       </c>
+      <c r="M477" s="1" t="n">
+        <v>0.13709</v>
+      </c>
+      <c r="N477" s="3" t="n">
+        <v>0.002632926204929417</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -19581,6 +22449,12 @@
       <c r="L478" s="2" t="n">
         <v>-0.0006307821698905658</v>
       </c>
+      <c r="M478" s="1" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="N478" s="2" t="n">
+        <v>-0.002103934357248114</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -19621,6 +22495,12 @@
       <c r="L479" s="2" t="n">
         <v>-0.0007552870090635443</v>
       </c>
+      <c r="M479" s="1" t="n">
+        <v>0.005287</v>
+      </c>
+      <c r="N479" s="2" t="n">
+        <v>-0.0009448223733937635</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -19661,6 +22541,12 @@
       <c r="L480" s="3" t="n">
         <v>0.0007178750897343071</v>
       </c>
+      <c r="M480" s="1" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="N480" s="2" t="n">
+        <v>-0.001793400286944048</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -19701,6 +22587,12 @@
       <c r="L481" s="2" t="n">
         <v>-0.001710076295711722</v>
       </c>
+      <c r="M481" s="1" t="n">
+        <v>0.07573000000000001</v>
+      </c>
+      <c r="N481" s="2" t="n">
+        <v>-0.002108314665963809</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -19741,6 +22633,12 @@
       <c r="L482" s="2" t="n">
         <v>-0.002022926500337072</v>
       </c>
+      <c r="M482" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="N482" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -19781,6 +22679,12 @@
       <c r="L483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="N483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -19821,6 +22725,12 @@
       <c r="L484" s="2" t="n">
         <v>-0.001845018450184587</v>
       </c>
+      <c r="M484" s="1" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="N484" s="2" t="n">
+        <v>-0.003696857670979677</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -19861,6 +22771,12 @@
       <c r="L485" s="2" t="n">
         <v>-0.002869783570489232</v>
       </c>
+      <c r="M485" s="1" t="n">
+        <v>0.008305999999999999</v>
+      </c>
+      <c r="N485" s="2" t="n">
+        <v>-0.003957309029859701</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -19901,6 +22817,12 @@
       <c r="L486" s="2" t="n">
         <v>-0.0002679887444727677</v>
       </c>
+      <c r="M486" s="1" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="N486" s="2" t="n">
+        <v>-0.002814636107760263</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -19941,6 +22863,12 @@
       <c r="L487" s="3" t="n">
         <v>0.0009009009009009267</v>
       </c>
+      <c r="M487" s="1" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="N487" s="2" t="n">
+        <v>-0.002700270027002777</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -19981,6 +22909,12 @@
       <c r="L488" s="2" t="n">
         <v>-0.0002136067499733275</v>
       </c>
+      <c r="M488" s="1" t="n">
+        <v>0.009363</v>
+      </c>
+      <c r="N488" s="3" t="n">
+        <v>0.0002136523875654594</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -20021,6 +22955,12 @@
       <c r="L489" s="2" t="n">
         <v>-0.001554001554001491</v>
       </c>
+      <c r="M489" s="1" t="n">
+        <v>0.03848</v>
+      </c>
+      <c r="N489" s="2" t="n">
+        <v>-0.00181582360570689</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -20061,6 +23001,12 @@
       <c r="L490" s="3" t="n">
         <v>0.0001705320600273374</v>
       </c>
+      <c r="M490" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="N490" s="2" t="n">
+        <v>-0.0008525149190111071</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -20101,6 +23047,12 @@
       <c r="L491" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M491" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="N491" s="2" t="n">
+        <v>-0.003112033195020692</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -20141,6 +23093,12 @@
       <c r="L492" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M492" s="1" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="N492" s="2" t="n">
+        <v>-0.002255639097744446</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -20181,6 +23139,12 @@
       <c r="L493" s="3" t="n">
         <v>0.0008520306731042956</v>
       </c>
+      <c r="M493" s="1" t="n">
+        <v>0.03525</v>
+      </c>
+      <c r="N493" s="3" t="n">
+        <v>0.0002837684449488117</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -20221,6 +23185,12 @@
       <c r="L494" s="2" t="n">
         <v>-0.00117302052785919</v>
       </c>
+      <c r="M494" s="1" t="n">
+        <v>0.01705</v>
+      </c>
+      <c r="N494" s="3" t="n">
+        <v>0.001174398120962959</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -20261,6 +23231,12 @@
       <c r="L495" s="2" t="n">
         <v>-0.0006313131313131786</v>
       </c>
+      <c r="M495" s="1" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="N495" s="2" t="n">
+        <v>-0.002526847757422512</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -20301,6 +23277,12 @@
       <c r="L496" s="3" t="n">
         <v>0.002074688796680557</v>
       </c>
+      <c r="M496" s="1" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="N496" s="2" t="n">
+        <v>-0.00207039337474126</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -20341,6 +23323,12 @@
       <c r="L497" s="2" t="n">
         <v>-0.002999400119975952</v>
       </c>
+      <c r="M497" s="1" t="n">
+        <v>0.04964</v>
+      </c>
+      <c r="N497" s="2" t="n">
+        <v>-0.004412354592860107</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -20381,6 +23369,12 @@
       <c r="L498" s="3" t="n">
         <v>0.0006932409012132877</v>
       </c>
+      <c r="M498" s="1" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="N498" s="2" t="n">
+        <v>-0.002771042604780128</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -20421,6 +23415,12 @@
       <c r="L499" s="3" t="n">
         <v>0.0003661662394726803</v>
       </c>
+      <c r="M499" s="1" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="N499" s="2" t="n">
+        <v>-0.003294289897511024</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -20461,6 +23461,12 @@
       <c r="L500" s="3" t="n">
         <v>0.007547169811320775</v>
       </c>
+      <c r="M500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="N500" s="2" t="n">
+        <v>-0.003745318352059935</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -20501,6 +23507,12 @@
       <c r="L501" s="3" t="n">
         <v>0.006961849067112232</v>
       </c>
+      <c r="M501" s="1" t="n">
+        <v>0.03592</v>
+      </c>
+      <c r="N501" s="2" t="n">
+        <v>-0.006637168141592842</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -20541,6 +23553,12 @@
       <c r="L502" s="3" t="n">
         <v>0.001885606536769251</v>
       </c>
+      <c r="M502" s="1" t="n">
+        <v>0.03183</v>
+      </c>
+      <c r="N502" s="2" t="n">
+        <v>-0.001568381430363909</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -20581,6 +23599,12 @@
       <c r="L503" s="2" t="n">
         <v>-0.003352675693101223</v>
       </c>
+      <c r="M503" s="1" t="n">
+        <v>0.007729</v>
+      </c>
+      <c r="N503" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -20621,6 +23645,12 @@
       <c r="L504" s="3" t="n">
         <v>0.004591669399803291</v>
       </c>
+      <c r="M504" s="1" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N504" s="2" t="n">
+        <v>-0.0009794319294809382</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -20661,6 +23691,12 @@
       <c r="L505" s="2" t="n">
         <v>-0.0004044216770019702</v>
       </c>
+      <c r="M505" s="1" t="n">
+        <v>0.0007406</v>
+      </c>
+      <c r="N505" s="2" t="n">
+        <v>-0.001213755900202249</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -20701,6 +23737,12 @@
       <c r="L506" s="3" t="n">
         <v>0.003712453594330037</v>
       </c>
+      <c r="M506" s="1" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="N506" s="2" t="n">
+        <v>-0.005379959650302591</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -20741,6 +23783,12 @@
       <c r="L507" s="2" t="n">
         <v>-0.000702000702000643</v>
       </c>
+      <c r="M507" s="1" t="n">
+        <v>0.002845</v>
+      </c>
+      <c r="N507" s="2" t="n">
+        <v>-0.0007024938531788779</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -20781,6 +23829,12 @@
       <c r="L508" s="3" t="n">
         <v>0.001892445986437612</v>
       </c>
+      <c r="M508" s="1" t="n">
+        <v>0.06337</v>
+      </c>
+      <c r="N508" s="2" t="n">
+        <v>-0.002518495199118643</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -20821,6 +23875,12 @@
       <c r="L509" s="2" t="n">
         <v>-0.002221235006663658</v>
       </c>
+      <c r="M509" s="1" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="N509" s="2" t="n">
+        <v>-0.0004452359750667364</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -20861,6 +23921,12 @@
       <c r="L510" s="3" t="n">
         <v>0.001780821917808337</v>
       </c>
+      <c r="M510" s="1" t="n">
+        <v>0.0007283</v>
+      </c>
+      <c r="N510" s="2" t="n">
+        <v>-0.00410228360453996</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -20901,6 +23967,12 @@
       <c r="L511" s="3" t="n">
         <v>0.003636363636363639</v>
       </c>
+      <c r="M511" s="1" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="N511" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -20941,6 +24013,12 @@
       <c r="L512" s="2" t="n">
         <v>-0.001661129568106353</v>
       </c>
+      <c r="M512" s="1" t="n">
+        <v>0.0004802</v>
+      </c>
+      <c r="N512" s="2" t="n">
+        <v>-0.001247920133111398</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -20981,6 +24059,12 @@
       <c r="L513" s="2" t="n">
         <v>-0.001086366105377594</v>
       </c>
+      <c r="M513" s="1" t="n">
+        <v>0.05524</v>
+      </c>
+      <c r="N513" s="3" t="n">
+        <v>0.001268805510241084</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -21021,6 +24105,12 @@
       <c r="L514" s="2" t="n">
         <v>-0.003287310979618652</v>
       </c>
+      <c r="M514" s="1" t="n">
+        <v>0.03036</v>
+      </c>
+      <c r="N514" s="3" t="n">
+        <v>0.001319261213720377</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -21061,6 +24151,12 @@
       <c r="L515" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M515" s="1" t="n">
+        <v>0.001141</v>
+      </c>
+      <c r="N515" s="2" t="n">
+        <v>-0.0008756567425568441</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -21101,6 +24197,12 @@
       <c r="L516" s="3" t="n">
         <v>0.001961671948091141</v>
       </c>
+      <c r="M516" s="1" t="n">
+        <v>0.006638</v>
+      </c>
+      <c r="N516" s="2" t="n">
+        <v>-0.0003012048192771484</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -21141,6 +24243,12 @@
       <c r="L517" s="3" t="n">
         <v>0.0005018820577165903</v>
       </c>
+      <c r="M517" s="1" t="n">
+        <v>0.03981</v>
+      </c>
+      <c r="N517" s="2" t="n">
+        <v>-0.001504890895410195</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -21181,6 +24289,12 @@
       <c r="L518" s="2" t="n">
         <v>-0.00291262135922325</v>
       </c>
+      <c r="M518" s="1" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="N518" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -21221,6 +24335,12 @@
       <c r="L519" s="3" t="n">
         <v>0.003424657534246436</v>
       </c>
+      <c r="M519" s="1" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="N519" s="2" t="n">
+        <v>-0.002275312855517541</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -21261,6 +24381,12 @@
       <c r="L520" s="2" t="n">
         <v>-0.000623052959501662</v>
       </c>
+      <c r="M520" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="N520" s="2" t="n">
+        <v>-0.004987531172069796</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -21301,6 +24427,12 @@
       <c r="L521" s="3" t="n">
         <v>0.007303370786516946</v>
       </c>
+      <c r="M521" s="1" t="n">
+        <v>0.01794</v>
+      </c>
+      <c r="N521" s="3" t="n">
+        <v>0.0005577244841048295</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -21341,6 +24473,12 @@
       <c r="L522" s="2" t="n">
         <v>-0.00542168674698794</v>
       </c>
+      <c r="M522" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="N522" s="2" t="n">
+        <v>-0.004239854633555458</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -21381,6 +24519,12 @@
       <c r="L523" s="3" t="n">
         <v>0.001671841413900182</v>
       </c>
+      <c r="M523" s="1" t="n">
+        <v>0.004185</v>
+      </c>
+      <c r="N523" s="2" t="n">
+        <v>-0.002145922746780987</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -21421,6 +24565,12 @@
       <c r="L524" s="2" t="n">
         <v>-0.001404494382022415</v>
       </c>
+      <c r="M524" s="1" t="n">
+        <v>0.01419</v>
+      </c>
+      <c r="N524" s="2" t="n">
+        <v>-0.002109704641350247</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -21461,6 +24611,12 @@
       <c r="L525" s="2" t="n">
         <v>-0.002797761790567571</v>
       </c>
+      <c r="M525" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="N525" s="2" t="n">
+        <v>-0.004008016032064104</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -21501,6 +24657,12 @@
       <c r="L526" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M526" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="N526" s="2" t="n">
+        <v>-0.001659751037344331</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -21541,6 +24703,12 @@
       <c r="L527" s="2" t="n">
         <v>-0.0002789400278940882</v>
       </c>
+      <c r="M527" s="1" t="n">
+        <v>0.07155</v>
+      </c>
+      <c r="N527" s="2" t="n">
+        <v>-0.001813616071428449</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -21581,6 +24749,12 @@
       <c r="L528" s="2" t="n">
         <v>-0.001387604070305216</v>
       </c>
+      <c r="M528" s="1" t="n">
+        <v>0.04327</v>
+      </c>
+      <c r="N528" s="3" t="n">
+        <v>0.002084298286243627</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -21621,6 +24795,12 @@
       <c r="L529" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M529" s="1" t="n">
+        <v>0.06297</v>
+      </c>
+      <c r="N529" s="2" t="n">
+        <v>-0.001427212178877366</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -21661,6 +24841,12 @@
       <c r="L530" s="3" t="n">
         <v>0.001194743130226987</v>
       </c>
+      <c r="M530" s="1" t="n">
+        <v>0.005017</v>
+      </c>
+      <c r="N530" s="2" t="n">
+        <v>-0.002187748607796458</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -21701,6 +24887,12 @@
       <c r="L531" s="3" t="n">
         <v>0.0007668711656443003</v>
       </c>
+      <c r="M531" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="N531" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -21741,6 +24933,12 @@
       <c r="L532" s="3" t="n">
         <v>0.0005622188905547648</v>
       </c>
+      <c r="M532" s="1" t="n">
+        <v>0.05331</v>
+      </c>
+      <c r="N532" s="2" t="n">
+        <v>-0.001498407941562029</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -21781,6 +24979,12 @@
       <c r="L533" s="3" t="n">
         <v>0.001327316166710972</v>
       </c>
+      <c r="M533" s="1" t="n">
+        <v>0.00374</v>
+      </c>
+      <c r="N533" s="2" t="n">
+        <v>-0.008483563096500621</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -21821,6 +25025,12 @@
       <c r="L534" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M534" s="1" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="N534" s="3" t="n">
+        <v>0.0005827505827505186</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -21861,6 +25071,12 @@
       <c r="L535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="M535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="N535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -21901,6 +25117,12 @@
       <c r="L536" s="3" t="n">
         <v>0.001345291479820661</v>
       </c>
+      <c r="M536" s="1" t="n">
+        <v>0.0004453</v>
+      </c>
+      <c r="N536" s="2" t="n">
+        <v>-0.00291088222122712</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -21941,6 +25163,12 @@
       <c r="L537" s="2" t="n">
         <v>-0.001029866117404695</v>
       </c>
+      <c r="M537" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="N537" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -21981,6 +25209,12 @@
       <c r="L538" s="2" t="n">
         <v>-0.001463057790782676</v>
       </c>
+      <c r="M538" s="1" t="n">
+        <v>0.05461</v>
+      </c>
+      <c r="N538" s="3" t="n">
+        <v>0.0001831501831501121</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -22021,6 +25255,12 @@
       <c r="L539" s="3" t="n">
         <v>0.001317523056653509</v>
       </c>
+      <c r="M539" s="1" t="n">
+        <v>0.6816</v>
+      </c>
+      <c r="N539" s="2" t="n">
+        <v>-0.003508771929824662</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -22061,6 +25301,12 @@
       <c r="L540" s="3" t="n">
         <v>0.0006591957811469281</v>
       </c>
+      <c r="M540" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="N540" s="2" t="n">
+        <v>-0.003952569169960405</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -22101,6 +25347,12 @@
       <c r="L541" s="2" t="n">
         <v>-0.001525553012967271</v>
       </c>
+      <c r="M541" s="1" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="N541" s="3" t="n">
+        <v>0.0007639419404126301</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -22141,6 +25393,12 @@
       <c r="L542" s="2" t="n">
         <v>-0.01416430594900854</v>
       </c>
+      <c r="M542" s="1" t="n">
+        <v>0.01408</v>
+      </c>
+      <c r="N542" s="3" t="n">
+        <v>0.01149425287356325</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -22180,6 +25438,12 @@
       </c>
       <c r="L543" s="2" t="n">
         <v>-0.0008712319219375239</v>
+      </c>
+      <c r="M543" s="1" t="n">
+        <v>0.05729</v>
+      </c>
+      <c r="N543" s="2" t="n">
+        <v>-0.0008719916288803877</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N543"/>
+  <dimension ref="A1:P543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,8 @@
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +515,16 @@
           <t>change_01:30</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>price_01:45</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>change_01:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +571,12 @@
       <c r="N2" s="2" t="n">
         <v>-0.00184848398738322</v>
       </c>
+      <c r="O2" s="1" t="n">
+        <v>70324.5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.001033424007037615</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,6 +623,12 @@
       <c r="N3" s="2" t="n">
         <v>-0.004002378224742335</v>
       </c>
+      <c r="O3" s="1" t="n">
+        <v>2064.5</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.001946139025183436</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,6 +675,12 @@
       <c r="N4" s="2" t="n">
         <v>-0.003459010722933208</v>
       </c>
+      <c r="O4" s="1" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.00439662154344551</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -697,6 +727,12 @@
       <c r="N5" s="2" t="n">
         <v>-0.01564347430650298</v>
       </c>
+      <c r="O5" s="1" t="n">
+        <v>0.010755</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>-0.006282916012196121</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -743,6 +779,12 @@
       <c r="N6" s="2" t="n">
         <v>-0.002677473044359082</v>
       </c>
+      <c r="O6" s="1" t="n">
+        <v>1.3808</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.0018865186475112</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -789,6 +831,12 @@
       <c r="N7" s="2" t="n">
         <v>-0.004227436060029567</v>
       </c>
+      <c r="O7" s="1" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.004033113988537522</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,6 +883,12 @@
       <c r="N8" s="2" t="n">
         <v>-0.004492291334396516</v>
       </c>
+      <c r="O8" s="1" t="n">
+        <v>37.643</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.00512669888654509</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -881,6 +935,12 @@
       <c r="N9" s="2" t="n">
         <v>-0.01055776892430284</v>
       </c>
+      <c r="O9" s="1" t="n">
+        <v>0.04941</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>-0.005234548016911543</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -927,6 +987,12 @@
       <c r="N10" s="3" t="n">
         <v>0.007614075161799128</v>
       </c>
+      <c r="O10" s="1" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.0007016786311868151</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -973,6 +1039,12 @@
       <c r="N11" s="2" t="n">
         <v>-0.001366308970048644</v>
       </c>
+      <c r="O11" s="1" t="n">
+        <v>652.0700000000001</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0.002413528055342121</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1019,6 +1091,12 @@
       <c r="N12" s="3" t="n">
         <v>0.1018451953031392</v>
       </c>
+      <c r="O12" s="1" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>-0.02196607220530665</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1065,6 +1143,12 @@
       <c r="N13" s="2" t="n">
         <v>-0.001428979708488194</v>
       </c>
+      <c r="O13" s="1" t="n">
+        <v>210.69</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.005008586147681795</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1111,6 +1195,12 @@
       <c r="N14" s="3" t="n">
         <v>9.059885845436931e-05</v>
       </c>
+      <c r="O14" s="1" t="n">
+        <v>0.003328</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.004952288923782989</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1157,6 +1247,12 @@
       <c r="N15" s="3" t="n">
         <v>0.04135486411973222</v>
       </c>
+      <c r="O15" s="1" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.04084720121028735</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1203,6 +1299,12 @@
       <c r="N16" s="2" t="n">
         <v>-0.003382880574064665</v>
       </c>
+      <c r="O16" s="1" t="n">
+        <v>0.9752</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.003085784817938699</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1249,6 +1351,12 @@
       <c r="N17" s="3" t="n">
         <v>0.01398601398601402</v>
       </c>
+      <c r="O17" s="1" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>-0.03103448275862074</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1295,6 +1403,12 @@
       <c r="N18" s="2" t="n">
         <v>-0.004685253050053305</v>
       </c>
+      <c r="O18" s="1" t="n">
+        <v>214.87</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.001444817300522009</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1341,6 +1455,12 @@
       <c r="N19" s="2" t="n">
         <v>-0.002663622526636143</v>
       </c>
+      <c r="O19" s="1" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.002289202594429566</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1387,6 +1507,12 @@
       <c r="N20" s="3" t="n">
         <v>0.01105137395459962</v>
       </c>
+      <c r="O20" s="1" t="n">
+        <v>0.016794</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>-0.007740029542097441</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1433,6 +1559,12 @@
       <c r="N21" s="2" t="n">
         <v>-0.003337157159244971</v>
       </c>
+      <c r="O21" s="1" t="n">
+        <v>9.564</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.0007324474207386913</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1479,6 +1611,12 @@
       <c r="N22" s="3" t="n">
         <v>0.002999400119976008</v>
       </c>
+      <c r="O22" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.005980861244019145</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1525,6 +1663,12 @@
       <c r="N23" s="3" t="n">
         <v>0.001314736481079114</v>
       </c>
+      <c r="O23" s="1" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>-0.004081749157960801</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1571,6 +1715,12 @@
       <c r="N24" s="2" t="n">
         <v>-0.002325581395348839</v>
       </c>
+      <c r="O24" s="1" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.009324009324009333</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1617,6 +1767,12 @@
       <c r="N25" s="2" t="n">
         <v>-0.003209739900387373</v>
       </c>
+      <c r="O25" s="1" t="n">
+        <v>9.019</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.001443482123029081</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1663,6 +1819,12 @@
       <c r="N26" s="3" t="n">
         <v>0.002253944402704819</v>
       </c>
+      <c r="O26" s="1" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.002248875562218809</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1709,6 +1871,12 @@
       <c r="N27" s="2" t="n">
         <v>-0.0007688960097418735</v>
       </c>
+      <c r="O27" s="1" t="n">
+        <v>5113.42</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>-0.001341720879090811</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1755,6 +1923,12 @@
       <c r="N28" s="3" t="n">
         <v>0.0005675368898979384</v>
       </c>
+      <c r="O28" s="1" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>0.004821327283040213</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1801,6 +1975,12 @@
       <c r="N29" s="2" t="n">
         <v>-0.004942965779467643</v>
       </c>
+      <c r="O29" s="1" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>0.003056935422239208</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1847,6 +2027,12 @@
       <c r="N30" s="3" t="n">
         <v>0.004438101536801332</v>
       </c>
+      <c r="O30" s="1" t="n">
+        <v>0.5757</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>-0.002460493484890451</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1893,6 +2079,12 @@
       <c r="N31" s="2" t="n">
         <v>-0.001918465227817792</v>
       </c>
+      <c r="O31" s="1" t="n">
+        <v>0.002101</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.009610764055742457</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1939,6 +2131,12 @@
       <c r="N32" s="3" t="n">
         <v>0.004596447491430364</v>
       </c>
+      <c r="O32" s="1" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>-0.004265219077161737</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1985,6 +2183,12 @@
       <c r="N33" s="3" t="n">
         <v>0.0009247842170159277</v>
       </c>
+      <c r="O33" s="1" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.009239297813366193</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2031,6 +2235,12 @@
       <c r="N34" s="2" t="n">
         <v>-0.003335557038025427</v>
       </c>
+      <c r="O34" s="1" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0.002008032128514132</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2077,6 +2287,12 @@
       <c r="N35" s="2" t="n">
         <v>-0.003132735995793824</v>
       </c>
+      <c r="O35" s="1" t="n">
+        <v>455.22</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.0003955696202531795</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2123,6 +2339,12 @@
       <c r="N36" s="3" t="n">
         <v>0.008485099337748356</v>
       </c>
+      <c r="O36" s="1" t="n">
+        <v>0.04816</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>-0.01169710650523294</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2169,6 +2391,12 @@
       <c r="N37" s="2" t="n">
         <v>-0.004653130287648168</v>
       </c>
+      <c r="O37" s="1" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.001983283751239648</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2215,6 +2443,12 @@
       <c r="N38" s="2" t="n">
         <v>-0.002840909090909041</v>
       </c>
+      <c r="O38" s="1" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>0.003798670465337109</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2261,6 +2495,12 @@
       <c r="N39" s="2" t="n">
         <v>-0.0016375545851529</v>
       </c>
+      <c r="O39" s="1" t="n">
+        <v>110.13</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0.003553854565336255</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2307,6 +2547,12 @@
       <c r="N40" s="3" t="n">
         <v>0.001329787234042591</v>
       </c>
+      <c r="O40" s="1" t="n">
+        <v>0.03706</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>-0.01567065073041169</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2353,6 +2599,12 @@
       <c r="N41" s="2" t="n">
         <v>-0.003230437903804731</v>
       </c>
+      <c r="O41" s="1" t="n">
+        <v>0.05515</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>-0.007021966150522172</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2399,6 +2651,12 @@
       <c r="N42" s="2" t="n">
         <v>-0.002392344497607702</v>
       </c>
+      <c r="O42" s="1" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>0.00202914591403799</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2445,6 +2703,12 @@
       <c r="N43" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O43" s="1" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>-0.005311077389984873</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2491,6 +2755,12 @@
       <c r="N44" s="2" t="n">
         <v>-0.001021798365122604</v>
       </c>
+      <c r="O44" s="1" t="n">
+        <v>0.005896</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.005114217524718806</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2537,6 +2807,12 @@
       <c r="N45" s="3" t="n">
         <v>0.002496754219514633</v>
       </c>
+      <c r="O45" s="1" t="n">
+        <v>0.10109</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0.007073122135883665</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2583,6 +2859,12 @@
       <c r="N46" s="3" t="n">
         <v>0.002890173410404627</v>
       </c>
+      <c r="O46" s="1" t="n">
+        <v>2.793</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.006123919308357474</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2629,6 +2911,12 @@
       <c r="N47" s="3" t="n">
         <v>0.0003459968168292471</v>
       </c>
+      <c r="O47" s="1" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.0004496402877698498</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2675,6 +2963,12 @@
       <c r="N48" s="2" t="n">
         <v>-0.0137741046831956</v>
       </c>
+      <c r="O48" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>-0.001862197392923574</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2721,6 +3015,12 @@
       <c r="N49" s="2" t="n">
         <v>-0.000847320852162749</v>
       </c>
+      <c r="O49" s="1" t="n">
+        <v>0.24772</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.0003634454629891643</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2767,6 +3067,12 @@
       <c r="N50" s="2" t="n">
         <v>-0.004644289634790055</v>
       </c>
+      <c r="O50" s="1" t="n">
+        <v>0.04742</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.005726405090137845</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2813,6 +3119,12 @@
       <c r="N51" s="2" t="n">
         <v>-0.002554278416347441</v>
       </c>
+      <c r="O51" s="1" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0.001280409731114043</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2859,6 +3171,12 @@
       <c r="N52" s="2" t="n">
         <v>-0.004255319148936158</v>
       </c>
+      <c r="O52" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>-0.01282051282051279</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2905,6 +3223,12 @@
       <c r="N53" s="2" t="n">
         <v>-0.002408187838651484</v>
       </c>
+      <c r="O53" s="1" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0.009052504526252272</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2951,6 +3275,12 @@
       <c r="N54" s="3" t="n">
         <v>0.01719544683942849</v>
       </c>
+      <c r="O54" s="1" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>-0.007142857142857182</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2997,6 +3327,12 @@
       <c r="N55" s="3" t="n">
         <v>0.002937576499387998</v>
       </c>
+      <c r="O55" s="1" t="n">
+        <v>0.12412</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0.009844601741111292</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3043,6 +3379,12 @@
       <c r="N56" s="3" t="n">
         <v>0.01299524564183833</v>
       </c>
+      <c r="O56" s="1" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>-0.007509386733416812</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3089,6 +3431,12 @@
       <c r="N57" s="2" t="n">
         <v>-0.0008547008547008199</v>
       </c>
+      <c r="O57" s="1" t="n">
+        <v>0.01156</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>-0.01112061591103506</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3135,6 +3483,12 @@
       <c r="N58" s="2" t="n">
         <v>-0.003015075376884508</v>
       </c>
+      <c r="O58" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>0.003024193548387183</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3181,6 +3535,12 @@
       <c r="N59" s="3" t="n">
         <v>0.002985074626865679</v>
       </c>
+      <c r="O59" s="1" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3227,6 +3587,12 @@
       <c r="N60" s="2" t="n">
         <v>-0.001946787800129752</v>
       </c>
+      <c r="O60" s="1" t="n">
+        <v>0.1549</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>0.007152145643693223</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3273,6 +3639,12 @@
       <c r="N61" s="2" t="n">
         <v>-0.00257004952046633</v>
       </c>
+      <c r="O61" s="1" t="n">
+        <v>0.15954</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>0.002639517345399547</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3319,6 +3691,12 @@
       <c r="N62" s="2" t="n">
         <v>-0.003517163759144551</v>
       </c>
+      <c r="O62" s="1" t="n">
+        <v>0.7113</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>0.00423549343498518</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3365,6 +3743,12 @@
       <c r="N63" s="2" t="n">
         <v>-0.01133671742808801</v>
       </c>
+      <c r="O63" s="1" t="n">
+        <v>5.864</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>0.003594044155399607</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3411,6 +3795,12 @@
       <c r="N64" s="2" t="n">
         <v>-0.001409244644870292</v>
       </c>
+      <c r="O64" s="1" t="n">
+        <v>0.007165</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>0.01114874400225798</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3457,6 +3847,12 @@
       <c r="N65" s="3" t="n">
         <v>0.02283105022831048</v>
       </c>
+      <c r="O65" s="1" t="n">
+        <v>0.03122</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>-0.004464285714285643</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3503,6 +3899,12 @@
       <c r="N66" s="2" t="n">
         <v>-0.008474576271186331</v>
       </c>
+      <c r="O66" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3549,6 +3951,12 @@
       <c r="N67" s="2" t="n">
         <v>-0.003683241252302029</v>
       </c>
+      <c r="O67" s="1" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>0.001232285890326557</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3595,6 +4003,12 @@
       <c r="N68" s="2" t="n">
         <v>-0.009099045346062155</v>
       </c>
+      <c r="O68" s="1" t="n">
+        <v>2.0071</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>0.007125294796527668</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3641,6 +4055,12 @@
       <c r="N69" s="2" t="n">
         <v>-0.002440299808262083</v>
       </c>
+      <c r="O69" s="1" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>0.004543071815481278</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3687,6 +4107,12 @@
       <c r="N70" s="2" t="n">
         <v>-0.009523809523809533</v>
       </c>
+      <c r="O70" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>0.009615384615384625</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3733,6 +4159,12 @@
       <c r="N71" s="2" t="n">
         <v>-0.003066476837148203</v>
       </c>
+      <c r="O71" s="1" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>0.0005492694716028298</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3779,6 +4211,12 @@
       <c r="N72" s="2" t="n">
         <v>-0.005860290670417258</v>
       </c>
+      <c r="O72" s="1" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>0.00589483612355577</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3825,6 +4263,12 @@
       <c r="N73" s="2" t="n">
         <v>-0.004129606099110562</v>
       </c>
+      <c r="O73" s="1" t="n">
+        <v>0.09435</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>0.003189792663476966</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3871,6 +4315,12 @@
       <c r="N74" s="3" t="n">
         <v>0.006148783233740265</v>
       </c>
+      <c r="O74" s="1" t="n">
+        <v>1.1401</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>-0.01867791358237223</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3917,6 +4367,12 @@
       <c r="N75" s="3" t="n">
         <v>0.0031505986137367</v>
       </c>
+      <c r="O75" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>0.00314070351758803</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3963,6 +4419,12 @@
       <c r="N76" s="3" t="n">
         <v>0.002183759301197075</v>
       </c>
+      <c r="O76" s="1" t="n">
+        <v>0.12333</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>-0.004680816721814309</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4009,6 +4471,12 @@
       <c r="N77" s="2" t="n">
         <v>-0.002546689303904997</v>
       </c>
+      <c r="O77" s="1" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>-0.001702127659574399</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4055,6 +4523,12 @@
       <c r="N78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O78" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>0.001976284584980294</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4101,6 +4575,12 @@
       <c r="N79" s="2" t="n">
         <v>-0.003514056224899629</v>
       </c>
+      <c r="O79" s="1" t="n">
+        <v>0.006012</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>0.009571788413098196</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4147,6 +4627,12 @@
       <c r="N80" s="2" t="n">
         <v>-0.01236230110159123</v>
       </c>
+      <c r="O80" s="1" t="n">
+        <v>0.008021</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>-0.005948692526954943</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4193,6 +4679,12 @@
       <c r="N81" s="2" t="n">
         <v>-0.0005599104143335953</v>
       </c>
+      <c r="O81" s="1" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>0.00224089635854337</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4239,6 +4731,12 @@
       <c r="N82" s="2" t="n">
         <v>-0.003101736972704717</v>
       </c>
+      <c r="O82" s="1" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>0.003111387678904794</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4285,6 +4783,12 @@
       <c r="N83" s="2" t="n">
         <v>-0.001097159575764789</v>
       </c>
+      <c r="O83" s="1" t="n">
+        <v>8.211</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>0.002074688796680432</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4331,6 +4835,12 @@
       <c r="N84" s="2" t="n">
         <v>-0.001879485134981276</v>
       </c>
+      <c r="O84" s="1" t="n">
+        <v>351.71</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>0.003452211126961425</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4377,6 +4887,12 @@
       <c r="N85" s="2" t="n">
         <v>-0.004073807812125486</v>
       </c>
+      <c r="O85" s="1" t="n">
+        <v>0.004112</v>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>-0.01058710298363806</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4423,6 +4939,12 @@
       <c r="N86" s="2" t="n">
         <v>-0.000525643913794507</v>
       </c>
+      <c r="O86" s="1" t="n">
+        <v>0.13247</v>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>-0.004733283245679878</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4469,6 +4991,12 @@
       <c r="N87" s="2" t="n">
         <v>-0.007216494845360888</v>
       </c>
+      <c r="O87" s="1" t="n">
+        <v>0.01899</v>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>-0.01401869158878502</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4515,6 +5043,12 @@
       <c r="N88" s="2" t="n">
         <v>-0.00176991150442478</v>
       </c>
+      <c r="O88" s="1" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>0.00443262411347528</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4561,6 +5095,12 @@
       <c r="N89" s="2" t="n">
         <v>-0.001021102791014372</v>
       </c>
+      <c r="O89" s="1" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>0.001022146507666175</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4607,6 +5147,12 @@
       <c r="N90" s="2" t="n">
         <v>-0.003889537145079739</v>
       </c>
+      <c r="O90" s="1" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>0.004685669660288867</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4653,6 +5199,12 @@
       <c r="N91" s="2" t="n">
         <v>-0.004566210045662037</v>
       </c>
+      <c r="O91" s="1" t="n">
+        <v>0.05599</v>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>-0.01217360621030351</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4699,6 +5251,12 @@
       <c r="N92" s="2" t="n">
         <v>-0.001376883653331142</v>
       </c>
+      <c r="O92" s="1" t="n">
+        <v>1.3036</v>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>-0.001455381080045969</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4745,6 +5303,12 @@
       <c r="N93" s="2" t="n">
         <v>-0.004907392749723044</v>
       </c>
+      <c r="O93" s="1" t="n">
+        <v>0.06307</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>0.003340757238307379</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4791,6 +5355,12 @@
       <c r="N94" s="3" t="n">
         <v>0.002262443438913935</v>
       </c>
+      <c r="O94" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>-0.003386004514672744</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4837,6 +5407,12 @@
       <c r="N95" s="2" t="n">
         <v>-0.001501501501501503</v>
       </c>
+      <c r="O95" s="1" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>0.002706766917293102</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4883,6 +5459,12 @@
       <c r="N96" s="3" t="n">
         <v>0.0008806693086745568</v>
       </c>
+      <c r="O96" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>-0.003519577650681927</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4929,6 +5511,12 @@
       <c r="N97" s="2" t="n">
         <v>-0.005486132276744886</v>
       </c>
+      <c r="O97" s="1" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>0.003064664419245918</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4975,6 +5563,12 @@
       <c r="N98" s="2" t="n">
         <v>-0.006352087114337674</v>
       </c>
+      <c r="O98" s="1" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>0.005479452054794526</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5021,6 +5615,12 @@
       <c r="N99" s="2" t="n">
         <v>-0.001667778519012788</v>
       </c>
+      <c r="O99" s="1" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>0.004009355162044775</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5067,6 +5667,12 @@
       <c r="N100" s="3" t="n">
         <v>0.002037845705967995</v>
       </c>
+      <c r="O100" s="1" t="n">
+        <v>0.03459</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>0.004938988959907132</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5113,6 +5719,12 @@
       <c r="N101" s="2" t="n">
         <v>-0.001100110011001101</v>
       </c>
+      <c r="O101" s="1" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5159,6 +5771,12 @@
       <c r="N102" s="2" t="n">
         <v>-0.02412221924417041</v>
       </c>
+      <c r="O102" s="1" t="n">
+        <v>0.007066</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>-0.02966218071958254</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5205,6 +5823,12 @@
       <c r="N103" s="2" t="n">
         <v>-0.005598939148371966</v>
       </c>
+      <c r="O103" s="1" t="n">
+        <v>0.06734</v>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>-0.002222551489109459</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5251,6 +5875,12 @@
       <c r="N104" s="3" t="n">
         <v>0.0007276255154014613</v>
       </c>
+      <c r="O104" s="1" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>-0.004362578768783383</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5297,6 +5927,12 @@
       <c r="N105" s="2" t="n">
         <v>-0.003365114974761641</v>
       </c>
+      <c r="O105" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="P105" s="3" t="n">
+        <v>0.003376477208778844</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5343,6 +5979,12 @@
       <c r="N106" s="3" t="n">
         <v>0.003566158386620698</v>
       </c>
+      <c r="O106" s="1" t="n">
+        <v>0.008238000000000001</v>
+      </c>
+      <c r="P106" s="3" t="n">
+        <v>0.009435118245313158</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5389,6 +6031,12 @@
       <c r="N107" s="2" t="n">
         <v>-0.002753303964757597</v>
       </c>
+      <c r="O107" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="P107" s="3" t="n">
+        <v>0.002760905577029153</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5435,6 +6083,12 @@
       <c r="N108" s="2" t="n">
         <v>-0.008861940298507424</v>
       </c>
+      <c r="O108" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>0.004705882352941147</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5481,6 +6135,12 @@
       <c r="N109" s="3" t="n">
         <v>0.005724508050089461</v>
       </c>
+      <c r="O109" s="1" t="n">
+        <v>0.05643</v>
+      </c>
+      <c r="P109" s="3" t="n">
+        <v>0.003735325506937066</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5527,6 +6187,12 @@
       <c r="N110" s="3" t="n">
         <v>0.00602046959662859</v>
       </c>
+      <c r="O110" s="1" t="n">
+        <v>0.11644</v>
+      </c>
+      <c r="P110" s="2" t="n">
+        <v>-0.004531076344361825</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5573,6 +6239,12 @@
       <c r="N111" s="2" t="n">
         <v>-0.004156528791565365</v>
       </c>
+      <c r="O111" s="1" t="n">
+        <v>0.09838</v>
+      </c>
+      <c r="P111" s="3" t="n">
+        <v>0.001527028402728264</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5619,6 +6291,12 @@
       <c r="N112" s="2" t="n">
         <v>-0.00269541778975749</v>
       </c>
+      <c r="O112" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="P112" s="3" t="n">
+        <v>0.00270270270270278</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5665,6 +6343,12 @@
       <c r="N113" s="2" t="n">
         <v>-0.002037905033625491</v>
       </c>
+      <c r="O113" s="1" t="n">
+        <v>0.09821000000000001</v>
+      </c>
+      <c r="P113" s="3" t="n">
+        <v>0.002756789871349871</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5711,6 +6395,12 @@
       <c r="N114" s="3" t="n">
         <v>0.01219512195121949</v>
       </c>
+      <c r="O114" s="1" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="P114" s="3" t="n">
+        <v>0.01376936316695349</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5757,6 +6447,12 @@
       <c r="N115" s="2" t="n">
         <v>-0.0004793480866021682</v>
       </c>
+      <c r="O115" s="1" t="n">
+        <v>1.2552</v>
+      </c>
+      <c r="P115" s="3" t="n">
+        <v>0.003277116137798731</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5803,6 +6499,12 @@
       <c r="N116" s="2" t="n">
         <v>-0.002954833262980186</v>
       </c>
+      <c r="O116" s="1" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="P116" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5849,6 +6551,12 @@
       <c r="N117" s="2" t="n">
         <v>-0.00049521294156491</v>
       </c>
+      <c r="O117" s="1" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="P117" s="3" t="n">
+        <v>0.004128819157720895</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5895,6 +6603,12 @@
       <c r="N118" s="3" t="n">
         <v>0.002279462046956983</v>
       </c>
+      <c r="O118" s="1" t="n">
+        <v>0.04386</v>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>-0.002501705708437548</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5941,6 +6655,12 @@
       <c r="N119" s="2" t="n">
         <v>-0.004292997048564518</v>
       </c>
+      <c r="O119" s="1" t="n">
+        <v>0.003725</v>
+      </c>
+      <c r="P119" s="3" t="n">
+        <v>0.003772568040959344</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5987,6 +6707,12 @@
       <c r="N120" s="2" t="n">
         <v>-0.003807106598984775</v>
       </c>
+      <c r="O120" s="1" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="P120" s="2" t="n">
+        <v>-0.001273885350318472</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6033,6 +6759,12 @@
       <c r="N121" s="2" t="n">
         <v>-0.003696236559139751</v>
       </c>
+      <c r="O121" s="1" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="P121" s="3" t="n">
+        <v>0.005059021922428335</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6079,6 +6811,12 @@
       <c r="N122" s="2" t="n">
         <v>-0.003839441535776579</v>
       </c>
+      <c r="O122" s="1" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="P122" s="2" t="n">
+        <v>-0.0008759635599158111</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6125,6 +6863,12 @@
       <c r="N123" s="3" t="n">
         <v>0.001082402234636864</v>
       </c>
+      <c r="O123" s="1" t="n">
+        <v>0.028977</v>
+      </c>
+      <c r="P123" s="3" t="n">
+        <v>0.01067280527362145</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6171,6 +6915,12 @@
       <c r="N124" s="2" t="n">
         <v>-0.004588325261279623</v>
       </c>
+      <c r="O124" s="1" t="n">
+        <v>0.07814</v>
+      </c>
+      <c r="P124" s="3" t="n">
+        <v>0.0005121638924455617</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6217,6 +6967,12 @@
       <c r="N125" s="3" t="n">
         <v>0.004516889238020445</v>
       </c>
+      <c r="O125" s="1" t="n">
+        <v>0.10262</v>
+      </c>
+      <c r="P125" s="3" t="n">
+        <v>0.003128054740957975</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6263,6 +7019,12 @@
       <c r="N126" s="2" t="n">
         <v>-0.01277838627236216</v>
       </c>
+      <c r="O126" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>-0.009985207100591822</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6309,6 +7071,12 @@
       <c r="N127" s="2" t="n">
         <v>-0.001363016810540608</v>
       </c>
+      <c r="O127" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="P127" s="2" t="n">
+        <v>-0.003184713375796207</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6355,6 +7123,12 @@
       <c r="N128" s="2" t="n">
         <v>-0.003090234857849199</v>
       </c>
+      <c r="O128" s="1" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="P128" s="3" t="n">
+        <v>0.005579665220086869</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6401,6 +7175,12 @@
       <c r="N129" s="3" t="n">
         <v>0.009799744354495045</v>
       </c>
+      <c r="O129" s="1" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="P129" s="3" t="n">
+        <v>0.003586497890295432</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6447,6 +7227,12 @@
       <c r="N130" s="2" t="n">
         <v>-0.001190210518485486</v>
       </c>
+      <c r="O130" s="1" t="n">
+        <v>0.053035</v>
+      </c>
+      <c r="P130" s="2" t="n">
+        <v>-0.01253072168019662</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6493,6 +7279,12 @@
       <c r="N131" s="2" t="n">
         <v>-0.002077985576335284</v>
       </c>
+      <c r="O131" s="1" t="n">
+        <v>0.08191</v>
+      </c>
+      <c r="P131" s="3" t="n">
+        <v>0.003307202351788247</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6539,6 +7331,12 @@
       <c r="N132" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O132" s="1" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="P132" s="3" t="n">
+        <v>0.00689655172413797</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6585,6 +7383,12 @@
       <c r="N133" s="2" t="n">
         <v>-0.003273604410751228</v>
       </c>
+      <c r="O133" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>0.002592912705272162</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6631,6 +7435,12 @@
       <c r="N134" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O134" s="1" t="n">
+        <v>0.03009</v>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>-0.003312355084465149</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6677,6 +7487,12 @@
       <c r="N135" s="2" t="n">
         <v>-0.01570386988222092</v>
       </c>
+      <c r="O135" s="1" t="n">
+        <v>0.01753</v>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>-0.001139601139601093</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6723,6 +7539,12 @@
       <c r="N136" s="3" t="n">
         <v>0.002976995940460242</v>
       </c>
+      <c r="O136" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="P136" s="3" t="n">
+        <v>0.003777657852131524</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6769,6 +7591,12 @@
       <c r="N137" s="2" t="n">
         <v>-0.003353204172876297</v>
       </c>
+      <c r="O137" s="1" t="n">
+        <v>0.02724</v>
+      </c>
+      <c r="P137" s="3" t="n">
+        <v>0.01831775700934583</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6815,6 +7643,12 @@
       <c r="N138" s="3" t="n">
         <v>0.00475812846946868</v>
       </c>
+      <c r="O138" s="1" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>-0.0007892659826360615</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6861,6 +7695,12 @@
       <c r="N139" s="2" t="n">
         <v>-0.0008431703204048336</v>
       </c>
+      <c r="O139" s="1" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="P139" s="3" t="n">
+        <v>0.0008438818565401964</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6907,6 +7747,12 @@
       <c r="N140" s="2" t="n">
         <v>-0.003963011889035735</v>
       </c>
+      <c r="O140" s="1" t="n">
+        <v>0.01503</v>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>-0.003315649867373986</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6953,6 +7799,12 @@
       <c r="N141" s="3" t="n">
         <v>0.004840811766896258</v>
       </c>
+      <c r="O141" s="1" t="n">
+        <v>16.192</v>
+      </c>
+      <c r="P141" s="3" t="n">
+        <v>6.176270767718005e-05</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6999,6 +7851,12 @@
       <c r="N142" s="2" t="n">
         <v>-0.0008012820512820186</v>
       </c>
+      <c r="O142" s="1" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="P142" s="3" t="n">
+        <v>0.0008019246190857733</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7045,6 +7903,12 @@
       <c r="N143" s="2" t="n">
         <v>-0.00337964701464513</v>
       </c>
+      <c r="O143" s="1" t="n">
+        <v>0.02649</v>
+      </c>
+      <c r="P143" s="2" t="n">
+        <v>-0.001883948756593874</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7091,6 +7955,12 @@
       <c r="N144" s="2" t="n">
         <v>-0.04131355932203386</v>
       </c>
+      <c r="O144" s="1" t="n">
+        <v>0.004527</v>
+      </c>
+      <c r="P144" s="3" t="n">
+        <v>0.0004419889502761101</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7137,6 +8007,12 @@
       <c r="N145" s="2" t="n">
         <v>-0.002273531046329484</v>
       </c>
+      <c r="O145" s="1" t="n">
+        <v>1.9772</v>
+      </c>
+      <c r="P145" s="3" t="n">
+        <v>0.001215312943082822</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7183,6 +8059,12 @@
       <c r="N146" s="3" t="n">
         <v>0.0008691873098652406</v>
       </c>
+      <c r="O146" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="P146" s="3" t="n">
+        <v>0.002171081198436884</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7229,6 +8111,12 @@
       <c r="N147" s="2" t="n">
         <v>-0.002232142857142921</v>
       </c>
+      <c r="O147" s="1" t="n">
+        <v>0.08949</v>
+      </c>
+      <c r="P147" s="3" t="n">
+        <v>0.001006711409396049</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7275,6 +8163,12 @@
       <c r="N148" s="2" t="n">
         <v>-0.008122157244964158</v>
       </c>
+      <c r="O148" s="1" t="n">
+        <v>0.06185</v>
+      </c>
+      <c r="P148" s="3" t="n">
+        <v>0.01293809367834915</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7321,6 +8215,12 @@
       <c r="N149" s="3" t="n">
         <v>0.006086221470836842</v>
       </c>
+      <c r="O149" s="1" t="n">
+        <v>0.05947</v>
+      </c>
+      <c r="P149" s="2" t="n">
+        <v>-0.0006721559401780939</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7367,6 +8267,12 @@
       <c r="N150" s="3" t="n">
         <v>0.0036385936222404</v>
       </c>
+      <c r="O150" s="1" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="P150" s="3" t="n">
+        <v>0.001670129129496084</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7413,6 +8319,12 @@
       <c r="N151" s="3" t="n">
         <v>0.001481481481481517</v>
       </c>
+      <c r="O151" s="1" t="n">
+        <v>6.925e-05</v>
+      </c>
+      <c r="P151" s="3" t="n">
+        <v>0.02440828402366863</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7459,6 +8371,12 @@
       <c r="N152" s="3" t="n">
         <v>0.0008992805755395942</v>
       </c>
+      <c r="O152" s="1" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>-0.004267744833782474</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7505,6 +8423,12 @@
       <c r="N153" s="2" t="n">
         <v>-0.005526657997399153</v>
       </c>
+      <c r="O153" s="1" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="P153" s="2" t="n">
+        <v>-0.0003269042170643641</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7551,6 +8475,12 @@
       <c r="N154" s="2" t="n">
         <v>-0.007895453307922715</v>
       </c>
+      <c r="O154" s="1" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="P154" s="2" t="n">
+        <v>-0.001646542261251343</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7597,6 +8527,12 @@
       <c r="N155" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O155" s="1" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="P155" s="3" t="n">
+        <v>0.001733102253032858</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7643,6 +8579,12 @@
       <c r="N156" s="2" t="n">
         <v>-0.001363918164910093</v>
       </c>
+      <c r="O156" s="1" t="n">
+        <v>0.08004</v>
+      </c>
+      <c r="P156" s="2" t="n">
+        <v>-0.006208095356344679</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7689,6 +8631,12 @@
       <c r="N157" s="3" t="n">
         <v>0.006147994161616942</v>
       </c>
+      <c r="O157" s="1" t="n">
+        <v>0.22868</v>
+      </c>
+      <c r="P157" s="3" t="n">
+        <v>0.005275189027606852</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7735,6 +8683,12 @@
       <c r="N158" s="2" t="n">
         <v>-0.004382470119521872</v>
       </c>
+      <c r="O158" s="1" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="P158" s="2" t="n">
+        <v>-0.0008003201280512434</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7781,6 +8735,12 @@
       <c r="N159" s="2" t="n">
         <v>-0.001366586949094637</v>
       </c>
+      <c r="O159" s="1" t="n">
+        <v>2.928</v>
+      </c>
+      <c r="P159" s="3" t="n">
+        <v>0.001710571330824459</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7827,6 +8787,12 @@
       <c r="N160" s="2" t="n">
         <v>-0.009881422924901195</v>
       </c>
+      <c r="O160" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="P160" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7873,6 +8839,12 @@
       <c r="N161" s="2" t="n">
         <v>-0.00157372562435859</v>
       </c>
+      <c r="O161" s="1" t="n">
+        <v>0.14608</v>
+      </c>
+      <c r="P161" s="3" t="n">
+        <v>0.001096491228070131</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7919,6 +8891,12 @@
       <c r="N162" s="2" t="n">
         <v>-0.002753977968176222</v>
       </c>
+      <c r="O162" s="1" t="n">
+        <v>0.00328</v>
+      </c>
+      <c r="P162" s="3" t="n">
+        <v>0.006443694384780531</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7965,6 +8943,12 @@
       <c r="N163" s="2" t="n">
         <v>-0.00380076015203039</v>
       </c>
+      <c r="O163" s="1" t="n">
+        <v>0.004991</v>
+      </c>
+      <c r="P163" s="3" t="n">
+        <v>0.002208835341365407</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8011,6 +8995,12 @@
       <c r="N164" s="2" t="n">
         <v>-0.005213764337851934</v>
       </c>
+      <c r="O164" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="P164" s="3" t="n">
+        <v>0.00209643605870027</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8057,6 +9047,12 @@
       <c r="N165" s="2" t="n">
         <v>-0.003580729166666634</v>
       </c>
+      <c r="O165" s="1" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="P165" s="3" t="n">
+        <v>0.005553740607644675</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8103,6 +9099,12 @@
       <c r="N166" s="2" t="n">
         <v>-0.0007904570278814882</v>
       </c>
+      <c r="O166" s="1" t="n">
+        <v>1.3943</v>
+      </c>
+      <c r="P166" s="3" t="n">
+        <v>0.002732829917295955</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8149,6 +9151,12 @@
       <c r="N167" s="2" t="n">
         <v>-0.00180505415162455</v>
       </c>
+      <c r="O167" s="1" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="P167" s="3" t="n">
+        <v>0.001446654611211414</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8195,6 +9203,12 @@
       <c r="N168" s="2" t="n">
         <v>-0.003194888178913741</v>
       </c>
+      <c r="O168" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="P168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8241,6 +9255,12 @@
       <c r="N169" s="2" t="n">
         <v>-0.001350894967916307</v>
       </c>
+      <c r="O169" s="1" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="P169" s="3" t="n">
+        <v>0.0111599594183294</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8287,6 +9307,12 @@
       <c r="N170" s="3" t="n">
         <v>0.0004602991944763909</v>
       </c>
+      <c r="O170" s="1" t="n">
+        <v>0.04366</v>
+      </c>
+      <c r="P170" s="3" t="n">
+        <v>0.004370830457786881</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8333,6 +9359,12 @@
       <c r="N171" s="3" t="n">
         <v>0.006024096385542133</v>
       </c>
+      <c r="O171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="P171" s="2" t="n">
+        <v>-0.005988023952095772</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8379,6 +9411,12 @@
       <c r="N172" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O172" s="1" t="n">
+        <v>1.34e-05</v>
+      </c>
+      <c r="P172" s="2" t="n">
+        <v>-0.04285714285714281</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8425,6 +9463,12 @@
       <c r="N173" s="2" t="n">
         <v>-0.001898433792121423</v>
       </c>
+      <c r="O173" s="1" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="P173" s="3" t="n">
+        <v>0.003328578221588236</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8471,6 +9515,12 @@
       <c r="N174" s="3" t="n">
         <v>0.002669632925472793</v>
       </c>
+      <c r="O174" s="1" t="n">
+        <v>0.09024</v>
+      </c>
+      <c r="P174" s="3" t="n">
+        <v>0.001109385400488161</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8517,6 +9567,12 @@
       <c r="N175" s="2" t="n">
         <v>-0.002485501242750501</v>
       </c>
+      <c r="O175" s="1" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="P175" s="3" t="n">
+        <v>0.001661129568106283</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8563,6 +9619,12 @@
       <c r="N176" s="2" t="n">
         <v>-0.0018674136321196</v>
       </c>
+      <c r="O176" s="1" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="P176" s="3" t="n">
+        <v>0.003741814780168392</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8609,6 +9671,12 @@
       <c r="N177" s="2" t="n">
         <v>-0.005031446540880516</v>
       </c>
+      <c r="O177" s="1" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="P177" s="2" t="n">
+        <v>-0.001264222503160505</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8655,6 +9723,12 @@
       <c r="N178" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O178" s="1" t="n">
+        <v>0.000974</v>
+      </c>
+      <c r="P178" s="3" t="n">
+        <v>0.001027749229188103</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8701,6 +9775,12 @@
       <c r="N179" s="2" t="n">
         <v>-0.002267178235088941</v>
       </c>
+      <c r="O179" s="1" t="n">
+        <v>0.022902</v>
+      </c>
+      <c r="P179" s="3" t="n">
+        <v>0.0007865757734660542</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8747,6 +9827,12 @@
       <c r="N180" s="3" t="n">
         <v>0.007805108798486368</v>
       </c>
+      <c r="O180" s="1" t="n">
+        <v>4.203</v>
+      </c>
+      <c r="P180" s="2" t="n">
+        <v>-0.01361182820934049</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8793,6 +9879,12 @@
       <c r="N181" s="3" t="n">
         <v>0.007782774126599703</v>
       </c>
+      <c r="O181" s="1" t="n">
+        <v>0.5848</v>
+      </c>
+      <c r="P181" s="3" t="n">
+        <v>0.003603912819632728</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8839,6 +9931,12 @@
       <c r="N182" s="3" t="n">
         <v>0.001011122345803871</v>
       </c>
+      <c r="O182" s="1" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="P182" s="3" t="n">
+        <v>0.01535353535353529</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8885,6 +9983,12 @@
       <c r="N183" s="2" t="n">
         <v>-0.002377903786354473</v>
       </c>
+      <c r="O183" s="1" t="n">
+        <v>5.481</v>
+      </c>
+      <c r="P183" s="3" t="n">
+        <v>0.004950495049504976</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8931,6 +10035,12 @@
       <c r="N184" s="2" t="n">
         <v>-0.0003501400560223393</v>
       </c>
+      <c r="O184" s="1" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="P184" s="3" t="n">
+        <v>0.00420315236427324</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8977,6 +10087,12 @@
       <c r="N185" s="3" t="n">
         <v>0.01128425577646418</v>
       </c>
+      <c r="O185" s="1" t="n">
+        <v>0.01867</v>
+      </c>
+      <c r="P185" s="2" t="n">
+        <v>-0.007970244420828949</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9023,6 +10139,12 @@
       <c r="N186" s="3" t="n">
         <v>0.003184713375796256</v>
       </c>
+      <c r="O186" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="P186" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9069,6 +10191,12 @@
       <c r="N187" s="2" t="n">
         <v>-0.00434782608695656</v>
       </c>
+      <c r="O187" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="P187" s="2" t="n">
+        <v>-0.0006238303181534369</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9115,6 +10243,12 @@
       <c r="N188" s="2" t="n">
         <v>-0.0002477700693756953</v>
       </c>
+      <c r="O188" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="P188" s="3" t="n">
+        <v>0.003717472118959215</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9161,6 +10295,12 @@
       <c r="N189" s="2" t="n">
         <v>-0.001602931073963734</v>
       </c>
+      <c r="O189" s="1" t="n">
+        <v>0.0004427</v>
+      </c>
+      <c r="P189" s="3" t="n">
+        <v>0.01536697247706422</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9207,6 +10347,12 @@
       <c r="N190" s="3" t="n">
         <v>0.001728608470181433</v>
       </c>
+      <c r="O190" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="P190" s="3" t="n">
+        <v>0.00560828300258851</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9253,6 +10399,12 @@
       <c r="N191" s="3" t="n">
         <v>0.001273074474856948</v>
       </c>
+      <c r="O191" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="P191" s="3" t="n">
+        <v>0.001907183725365466</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9299,6 +10451,12 @@
       <c r="N192" s="3" t="n">
         <v>0.00107238605898119</v>
       </c>
+      <c r="O192" s="1" t="n">
+        <v>0.05614</v>
+      </c>
+      <c r="P192" s="3" t="n">
+        <v>0.002321014104624266</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9345,6 +10503,12 @@
       <c r="N193" s="2" t="n">
         <v>-0.003755364806866986</v>
       </c>
+      <c r="O193" s="1" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="P193" s="3" t="n">
+        <v>0.009693053311793194</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9391,6 +10555,12 @@
       <c r="N194" s="2" t="n">
         <v>-0.001569037656903883</v>
       </c>
+      <c r="O194" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="P194" s="3" t="n">
+        <v>0.005762179151388109</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9437,6 +10607,12 @@
       <c r="N195" s="2" t="n">
         <v>-0.009451360073766695</v>
       </c>
+      <c r="O195" s="1" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="P195" s="3" t="n">
+        <v>0.0009308820107050405</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9483,6 +10659,12 @@
       <c r="N196" s="2" t="n">
         <v>-0.003990422984836368</v>
       </c>
+      <c r="O196" s="1" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="P196" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9529,6 +10711,12 @@
       <c r="N197" s="3" t="n">
         <v>0.0002188183807440495</v>
       </c>
+      <c r="O197" s="1" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="P197" s="3" t="n">
+        <v>0.01509516517173477</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9575,6 +10763,12 @@
       <c r="N198" s="2" t="n">
         <v>-0.001366120218579085</v>
       </c>
+      <c r="O198" s="1" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="P198" s="2" t="n">
+        <v>-0.001367989056087617</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9621,6 +10815,12 @@
       <c r="N199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="P199" s="3" t="n">
+        <v>0.01149425287356323</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9667,6 +10867,12 @@
       <c r="N200" s="3" t="n">
         <v>0.003378378378378306</v>
       </c>
+      <c r="O200" s="1" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="P200" s="3" t="n">
+        <v>0.002020202020202097</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9713,6 +10919,12 @@
       <c r="N201" s="3" t="n">
         <v>0.002121265688527616</v>
       </c>
+      <c r="O201" s="1" t="n">
+        <v>0.005699</v>
+      </c>
+      <c r="P201" s="3" t="n">
+        <v>0.00529193861351202</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9759,6 +10971,12 @@
       <c r="N202" s="2" t="n">
         <v>-0.004827586206896445</v>
       </c>
+      <c r="O202" s="1" t="n">
+        <v>0.023197</v>
+      </c>
+      <c r="P202" s="3" t="n">
+        <v>0.004721067221067134</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9805,6 +11023,12 @@
       <c r="N203" s="2" t="n">
         <v>-0.007246376811594159</v>
       </c>
+      <c r="O203" s="1" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P203" s="3" t="n">
+        <v>0.003649635036496328</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9851,6 +11075,12 @@
       <c r="N204" s="3" t="n">
         <v>0.003246753246753217</v>
       </c>
+      <c r="O204" s="1" t="n">
+        <v>0.03407</v>
+      </c>
+      <c r="P204" s="3" t="n">
+        <v>0.002353633421594695</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9897,6 +11127,12 @@
       <c r="N205" s="2" t="n">
         <v>-0.001644350481559707</v>
       </c>
+      <c r="O205" s="1" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="P205" s="2" t="n">
+        <v>-0.007294117647058751</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9943,6 +11179,12 @@
       <c r="N206" s="2" t="n">
         <v>-0.002770083102493077</v>
       </c>
+      <c r="O206" s="1" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="P206" s="3" t="n">
+        <v>0.005555555555555561</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9989,6 +11231,12 @@
       <c r="N207" s="3" t="n">
         <v>0.02239112571898109</v>
       </c>
+      <c r="O207" s="1" t="n">
+        <v>0.0011403</v>
+      </c>
+      <c r="P207" s="3" t="n">
+        <v>0.1455696202531644</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10035,6 +11283,12 @@
       <c r="N208" s="2" t="n">
         <v>-0.003829845438380438</v>
       </c>
+      <c r="O208" s="1" t="n">
+        <v>0.007289</v>
+      </c>
+      <c r="P208" s="3" t="n">
+        <v>0.0008238363311821954</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10081,6 +11335,12 @@
       <c r="N209" s="3" t="n">
         <v>0.001669449081802937</v>
       </c>
+      <c r="O209" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10127,6 +11387,12 @@
       <c r="N210" s="2" t="n">
         <v>-0.002313030069391075</v>
       </c>
+      <c r="O210" s="1" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="P210" s="3" t="n">
+        <v>0.002318392581143914</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10173,6 +11439,12 @@
       <c r="N211" s="2" t="n">
         <v>-0.001688001125334064</v>
       </c>
+      <c r="O211" s="1" t="n">
+        <v>0.007124</v>
+      </c>
+      <c r="P211" s="3" t="n">
+        <v>0.003804424404678049</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10219,6 +11491,12 @@
       <c r="N212" s="3" t="n">
         <v>0.000698567935731673</v>
       </c>
+      <c r="O212" s="1" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="P212" s="3" t="n">
+        <v>0.01815008726003504</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10265,6 +11543,12 @@
       <c r="N213" s="2" t="n">
         <v>-0.008222533240028081</v>
       </c>
+      <c r="O213" s="1" t="n">
+        <v>0.05668</v>
+      </c>
+      <c r="P213" s="2" t="n">
+        <v>-0.0001763979537836677</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10311,6 +11595,12 @@
       <c r="N214" s="2" t="n">
         <v>-0.001063264221158841</v>
       </c>
+      <c r="O214" s="1" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="P214" s="3" t="n">
+        <v>0.003725385843533679</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10357,6 +11647,12 @@
       <c r="N215" s="2" t="n">
         <v>-0.0005723006486074446</v>
       </c>
+      <c r="O215" s="1" t="n">
+        <v>0.05259</v>
+      </c>
+      <c r="P215" s="3" t="n">
+        <v>0.003817522427944241</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10403,6 +11699,12 @@
       <c r="N216" s="3" t="n">
         <v>0.001917545541706454</v>
       </c>
+      <c r="O216" s="1" t="n">
+        <v>0.002088</v>
+      </c>
+      <c r="P216" s="2" t="n">
+        <v>-0.0009569377990429818</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10449,6 +11751,12 @@
       <c r="N217" s="2" t="n">
         <v>-0.002325195150307297</v>
       </c>
+      <c r="O217" s="1" t="n">
+        <v>6.025</v>
+      </c>
+      <c r="P217" s="3" t="n">
+        <v>0.00299650407857511</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10495,6 +11803,12 @@
       <c r="N218" s="2" t="n">
         <v>-0.0004527960153950147</v>
       </c>
+      <c r="O218" s="1" t="n">
+        <v>4.425</v>
+      </c>
+      <c r="P218" s="3" t="n">
+        <v>0.002265005662514108</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10541,6 +11855,12 @@
       <c r="N219" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O219" s="1" t="n">
+        <v>0.005372</v>
+      </c>
+      <c r="P219" s="3" t="n">
+        <v>0.003361972357116135</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10587,6 +11907,12 @@
       <c r="N220" s="3" t="n">
         <v>0.002187651920272236</v>
       </c>
+      <c r="O220" s="1" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="P220" s="2" t="n">
+        <v>-0.0002425418384672098</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10633,6 +11959,12 @@
       <c r="N221" s="2" t="n">
         <v>-0.0003461405330564668</v>
       </c>
+      <c r="O221" s="1" t="n">
+        <v>0.005804</v>
+      </c>
+      <c r="P221" s="3" t="n">
+        <v>0.004847645429362924</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10679,6 +12011,12 @@
       <c r="N222" s="2" t="n">
         <v>-0.003300330033003242</v>
       </c>
+      <c r="O222" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="P222" s="3" t="n">
+        <v>0.003311258278145637</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10725,6 +12063,12 @@
       <c r="N223" s="2" t="n">
         <v>-0.002075303883782919</v>
       </c>
+      <c r="O223" s="1" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="P223" s="3" t="n">
+        <v>0.0005941770647652346</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10771,6 +12115,12 @@
       <c r="N224" s="2" t="n">
         <v>-0.003231763619575155</v>
       </c>
+      <c r="O224" s="1" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="P224" s="3" t="n">
+        <v>0.003010653080129615</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10817,6 +12167,12 @@
       <c r="N225" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O225" s="1" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="P225" s="3" t="n">
+        <v>0.0008380222674488283</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10863,6 +12219,12 @@
       <c r="N226" s="2" t="n">
         <v>-0.0005316321105794574</v>
       </c>
+      <c r="O226" s="1" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="P226" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10909,6 +12271,12 @@
       <c r="N227" s="2" t="n">
         <v>-0.002785515320334371</v>
       </c>
+      <c r="O227" s="1" t="n">
+        <v>0.04685</v>
+      </c>
+      <c r="P227" s="3" t="n">
+        <v>0.006660936828534696</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10955,6 +12323,12 @@
       <c r="N228" s="3" t="n">
         <v>0.0004312203536006724</v>
       </c>
+      <c r="O228" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="P228" s="3" t="n">
+        <v>0.003879310344827728</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11001,6 +12375,12 @@
       <c r="N229" s="2" t="n">
         <v>-0.001858736059479607</v>
       </c>
+      <c r="O229" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="P229" s="3" t="n">
+        <v>0.003724394785847406</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11047,6 +12427,12 @@
       <c r="N230" s="2" t="n">
         <v>-0.005988023952095813</v>
       </c>
+      <c r="O230" s="1" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="P230" s="3" t="n">
+        <v>0.006626506024096324</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11093,6 +12479,12 @@
       <c r="N231" s="3" t="n">
         <v>0.0006568144499178714</v>
       </c>
+      <c r="O231" s="1" t="n">
+        <v>0.03056</v>
+      </c>
+      <c r="P231" s="3" t="n">
+        <v>0.002953724975385619</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11139,6 +12531,12 @@
       <c r="N232" s="2" t="n">
         <v>-0.0025929127052723</v>
       </c>
+      <c r="O232" s="1" t="n">
+        <v>0.02289</v>
+      </c>
+      <c r="P232" s="2" t="n">
+        <v>-0.008232235701906378</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11185,6 +12583,12 @@
       <c r="N233" s="2" t="n">
         <v>-0.06657344830264901</v>
       </c>
+      <c r="O233" s="1" t="n">
+        <v>0.11998</v>
+      </c>
+      <c r="P233" s="2" t="n">
+        <v>-0.001498002663115842</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11231,6 +12635,12 @@
       <c r="N234" s="2" t="n">
         <v>-0.00158040300276575</v>
       </c>
+      <c r="O234" s="1" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="P234" s="3" t="n">
+        <v>0.004748713889988264</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11277,6 +12687,12 @@
       <c r="N235" s="2" t="n">
         <v>-0.002450627072221471</v>
       </c>
+      <c r="O235" s="1" t="n">
+        <v>0.06917</v>
+      </c>
+      <c r="P235" s="2" t="n">
+        <v>-0.0004335260115607261</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11323,6 +12739,12 @@
       <c r="N236" s="2" t="n">
         <v>-0.004715850051954227</v>
       </c>
+      <c r="O236" s="1" t="n">
+        <v>0.12554</v>
+      </c>
+      <c r="P236" s="3" t="n">
+        <v>0.008191455187921675</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11369,6 +12791,12 @@
       <c r="N237" s="2" t="n">
         <v>-0.005949301603724807</v>
       </c>
+      <c r="O237" s="1" t="n">
+        <v>0.03891</v>
+      </c>
+      <c r="P237" s="3" t="n">
+        <v>0.01249024199843875</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11415,6 +12843,12 @@
       <c r="N238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11461,6 +12895,12 @@
       <c r="N239" s="2" t="n">
         <v>-0.01675837918959485</v>
       </c>
+      <c r="O239" s="1" t="n">
+        <v>0.004021</v>
+      </c>
+      <c r="P239" s="3" t="n">
+        <v>0.02289493767489206</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11507,6 +12947,12 @@
       <c r="N240" s="2" t="n">
         <v>-0.002906976744186054</v>
       </c>
+      <c r="O240" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="P240" s="3" t="n">
+        <v>0.001457725947521933</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11553,6 +12999,12 @@
       <c r="N241" s="3" t="n">
         <v>0.004880316058563771</v>
       </c>
+      <c r="O241" s="1" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="P241" s="3" t="n">
+        <v>0.0002312673450508533</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11599,6 +13051,12 @@
       <c r="N242" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O242" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="P242" s="3" t="n">
+        <v>0.008119079837618426</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11645,6 +13103,12 @@
       <c r="N243" s="2" t="n">
         <v>-0.003911342894393733</v>
       </c>
+      <c r="O243" s="1" t="n">
+        <v>0.02297</v>
+      </c>
+      <c r="P243" s="3" t="n">
+        <v>0.002181500872600411</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11691,6 +13155,12 @@
       <c r="N244" s="2" t="n">
         <v>-0.00357995226730306</v>
       </c>
+      <c r="O244" s="1" t="n">
+        <v>0.001679</v>
+      </c>
+      <c r="P244" s="3" t="n">
+        <v>0.005389221556886164</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11737,6 +13207,12 @@
       <c r="N245" s="2" t="n">
         <v>-0.002276176024279171</v>
       </c>
+      <c r="O245" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="P245" s="3" t="n">
+        <v>0.0007604562737641748</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11783,6 +13259,12 @@
       <c r="N246" s="2" t="n">
         <v>-0.01255098839033588</v>
       </c>
+      <c r="O246" s="1" t="n">
+        <v>0.03173</v>
+      </c>
+      <c r="P246" s="3" t="n">
+        <v>0.0082618366698444</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11829,6 +13311,12 @@
       <c r="N247" s="2" t="n">
         <v>-0.001128668171557595</v>
       </c>
+      <c r="O247" s="1" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="P247" s="3" t="n">
+        <v>0.003954802259887041</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11875,6 +13363,12 @@
       <c r="N248" s="2" t="n">
         <v>-0.01490602721970184</v>
       </c>
+      <c r="O248" s="1" t="n">
+        <v>0.03053</v>
+      </c>
+      <c r="P248" s="3" t="n">
+        <v>0.004276315789473738</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11921,6 +13415,12 @@
       <c r="N249" s="3" t="n">
         <v>0.009322633939107766</v>
       </c>
+      <c r="O249" s="1" t="n">
+        <v>0.008501</v>
+      </c>
+      <c r="P249" s="2" t="n">
+        <v>-0.00607973810358938</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11967,6 +13467,12 @@
       <c r="N250" s="2" t="n">
         <v>-0.006786233640329509</v>
       </c>
+      <c r="O250" s="1" t="n">
+        <v>0.02043</v>
+      </c>
+      <c r="P250" s="2" t="n">
+        <v>-0.002928257686676477</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12013,6 +13519,12 @@
       <c r="N251" s="2" t="n">
         <v>-0.004908237302603522</v>
       </c>
+      <c r="O251" s="1" t="n">
+        <v>0.04664</v>
+      </c>
+      <c r="P251" s="3" t="n">
+        <v>0.0002144542140253713</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12059,6 +13571,12 @@
       <c r="N252" s="3" t="n">
         <v>0.001066350710900513</v>
       </c>
+      <c r="O252" s="1" t="n">
+        <v>0.008484999999999999</v>
+      </c>
+      <c r="P252" s="3" t="n">
+        <v>0.004260859273286729</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12105,6 +13623,12 @@
       <c r="N253" s="2" t="n">
         <v>-0.005949301603724807</v>
       </c>
+      <c r="O253" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="P253" s="3" t="n">
+        <v>0.004423627374447138</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12151,6 +13675,12 @@
       <c r="N254" s="2" t="n">
         <v>-0.0003272786777941284</v>
       </c>
+      <c r="O254" s="1" t="n">
+        <v>0.06113</v>
+      </c>
+      <c r="P254" s="3" t="n">
+        <v>0.0006547716483875981</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12197,6 +13727,12 @@
       <c r="N255" s="3" t="n">
         <v>0.0016797312430011</v>
       </c>
+      <c r="O255" s="1" t="n">
+        <v>0.003574</v>
+      </c>
+      <c r="P255" s="2" t="n">
+        <v>-0.001117942984907797</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12243,6 +13779,12 @@
       <c r="N256" s="2" t="n">
         <v>-0.01370069256248117</v>
       </c>
+      <c r="O256" s="1" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="P256" s="2" t="n">
+        <v>-0.002442375209891679</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12289,6 +13831,12 @@
       <c r="N257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O257" s="1" t="n">
+        <v>0.999426</v>
+      </c>
+      <c r="P257" s="3" t="n">
+        <v>5.303325184899008e-05</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12335,6 +13883,12 @@
       <c r="N258" s="2" t="n">
         <v>-0.003324544308150849</v>
       </c>
+      <c r="O258" s="1" t="n">
+        <v>0.08724999999999999</v>
+      </c>
+      <c r="P258" s="3" t="n">
+        <v>0.003565677478720851</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12381,6 +13935,12 @@
       <c r="N259" s="3" t="n">
         <v>0.0005600358422940006</v>
       </c>
+      <c r="O259" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="P259" s="3" t="n">
+        <v>0.01645583790439941</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12427,6 +13987,12 @@
       <c r="N260" s="2" t="n">
         <v>-0.001471850852447062</v>
       </c>
+      <c r="O260" s="1" t="n">
+        <v>0.08162999999999999</v>
+      </c>
+      <c r="P260" s="3" t="n">
+        <v>0.002702370716128215</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12473,6 +14039,12 @@
       <c r="N261" s="3" t="n">
         <v>0.007985803016858826</v>
       </c>
+      <c r="O261" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P261" s="3" t="n">
+        <v>0.01232394366197184</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12519,6 +14091,12 @@
       <c r="N262" s="3" t="n">
         <v>0.009297238173366076</v>
       </c>
+      <c r="O262" s="1" t="n">
+        <v>0.003753</v>
+      </c>
+      <c r="P262" s="3" t="n">
+        <v>0.01679761582227039</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12565,6 +14143,12 @@
       <c r="N263" s="2" t="n">
         <v>-0.002572898799313848</v>
       </c>
+      <c r="O263" s="1" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="P263" s="3" t="n">
+        <v>0.01117798796216677</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12611,6 +14195,12 @@
       <c r="N264" s="3" t="n">
         <v>0.001734003814808435</v>
       </c>
+      <c r="O264" s="1" t="n">
+        <v>0.0005839</v>
+      </c>
+      <c r="P264" s="3" t="n">
+        <v>0.01073221395187821</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12657,6 +14247,12 @@
       <c r="N265" s="2" t="n">
         <v>-0.005354752342704164</v>
       </c>
+      <c r="O265" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="P265" s="2" t="n">
+        <v>-0.002691790040376858</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12703,6 +14299,12 @@
       <c r="N266" s="3" t="n">
         <v>0.001574803149606344</v>
       </c>
+      <c r="O266" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="P266" s="3" t="n">
+        <v>0.001572327044025202</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12749,6 +14351,12 @@
       <c r="N267" s="2" t="n">
         <v>-0.001223990208078285</v>
       </c>
+      <c r="O267" s="1" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="P267" s="2" t="n">
+        <v>-0.004289215686274547</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12795,6 +14403,12 @@
       <c r="N268" s="2" t="n">
         <v>-0.002779708130646224</v>
       </c>
+      <c r="O268" s="1" t="n">
+        <v>0.0004441</v>
+      </c>
+      <c r="P268" s="3" t="n">
+        <v>0.0315911730545877</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12841,6 +14455,12 @@
       <c r="N269" s="2" t="n">
         <v>-0.0004819277108433538</v>
       </c>
+      <c r="O269" s="1" t="n">
+        <v>0.02072</v>
+      </c>
+      <c r="P269" s="2" t="n">
+        <v>-0.0009643201542913527</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12887,6 +14507,12 @@
       <c r="N270" s="2" t="n">
         <v>-0.006087437742113945</v>
       </c>
+      <c r="O270" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="P270" s="3" t="n">
+        <v>0.006124721603563418</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12933,6 +14559,12 @@
       <c r="N271" s="2" t="n">
         <v>-0.0006811989100818579</v>
       </c>
+      <c r="O271" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="P271" s="3" t="n">
+        <v>0.002044989775051089</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12979,6 +14611,12 @@
       <c r="N272" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O272" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="P272" s="3" t="n">
+        <v>0.007790902236742845</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13025,6 +14663,12 @@
       <c r="N273" s="2" t="n">
         <v>-0.005359056806002148</v>
       </c>
+      <c r="O273" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="P273" s="3" t="n">
+        <v>0.003232758620689658</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13071,6 +14715,12 @@
       <c r="N274" s="2" t="n">
         <v>-0.0007920164739427255</v>
       </c>
+      <c r="O274" s="1" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="P274" s="3" t="n">
+        <v>0.001109701965757772</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13117,6 +14767,12 @@
       <c r="N275" s="2" t="n">
         <v>-0.006986899563318796</v>
       </c>
+      <c r="O275" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="P275" s="3" t="n">
+        <v>0.006156552330694866</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13163,6 +14819,12 @@
       <c r="N276" s="2" t="n">
         <v>-0.0007730962504832716</v>
       </c>
+      <c r="O276" s="1" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="P276" s="3" t="n">
+        <v>0.003481624758220463</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13209,6 +14871,12 @@
       <c r="N277" s="2" t="n">
         <v>-0.001903855306996756</v>
       </c>
+      <c r="O277" s="1" t="n">
+        <v>0.04207</v>
+      </c>
+      <c r="P277" s="3" t="n">
+        <v>0.003099666189795067</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13255,6 +14923,12 @@
       <c r="N278" s="2" t="n">
         <v>-0.007767995857068919</v>
       </c>
+      <c r="O278" s="1" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="P278" s="3" t="n">
+        <v>0.02296450939457199</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -13301,6 +14975,12 @@
       <c r="N279" s="2" t="n">
         <v>-0.001251340722202371</v>
       </c>
+      <c r="O279" s="1" t="n">
+        <v>0.005578</v>
+      </c>
+      <c r="P279" s="2" t="n">
+        <v>-0.001610882405584451</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -13347,6 +15027,12 @@
       <c r="N280" s="3" t="n">
         <v>0.001567398119122193</v>
       </c>
+      <c r="O280" s="1" t="n">
+        <v>0.03859</v>
+      </c>
+      <c r="P280" s="3" t="n">
+        <v>0.006520605112154414</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -13393,6 +15079,12 @@
       <c r="N281" s="2" t="n">
         <v>-0.001107419712070876</v>
       </c>
+      <c r="O281" s="1" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="P281" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13439,6 +15131,12 @@
       <c r="N282" s="3" t="n">
         <v>0.002244389027431476</v>
       </c>
+      <c r="O282" s="1" t="n">
+        <v>0.0004052</v>
+      </c>
+      <c r="P282" s="3" t="n">
+        <v>0.008210997760636904</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13485,6 +15183,12 @@
       <c r="N283" s="3" t="n">
         <v>0.001749125437281375</v>
       </c>
+      <c r="O283" s="1" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="P283" s="2" t="n">
+        <v>-0.00324270391618853</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13531,6 +15235,12 @@
       <c r="N284" s="2" t="n">
         <v>-0.00311079205551563</v>
       </c>
+      <c r="O284" s="1" t="n">
+        <v>0.04192</v>
+      </c>
+      <c r="P284" s="3" t="n">
+        <v>0.006240998559769475</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13577,6 +15287,12 @@
       <c r="N285" s="2" t="n">
         <v>-0.0001853739920289751</v>
       </c>
+      <c r="O285" s="1" t="n">
+        <v>0.10776</v>
+      </c>
+      <c r="P285" s="2" t="n">
+        <v>-0.001019745990544164</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13623,6 +15339,12 @@
       <c r="N286" s="3" t="n">
         <v>0.002392344497607766</v>
       </c>
+      <c r="O286" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="P286" s="3" t="n">
+        <v>0.002386634844868638</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13669,6 +15391,12 @@
       <c r="N287" s="2" t="n">
         <v>-0.002051621442753175</v>
       </c>
+      <c r="O287" s="1" t="n">
+        <v>0.15207</v>
+      </c>
+      <c r="P287" s="3" t="n">
+        <v>0.008488626566748481</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13715,6 +15443,12 @@
       <c r="N288" s="2" t="n">
         <v>-0.01100110011001101</v>
       </c>
+      <c r="O288" s="1" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="P288" s="3" t="n">
+        <v>0.003893214682981125</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13761,6 +15495,12 @@
       <c r="N289" s="2" t="n">
         <v>-0.001694094869312603</v>
       </c>
+      <c r="O289" s="1" t="n">
+        <v>4.149</v>
+      </c>
+      <c r="P289" s="3" t="n">
+        <v>0.005818181818181823</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13807,6 +15547,12 @@
       <c r="N290" s="3" t="n">
         <v>0.002704291593180413</v>
       </c>
+      <c r="O290" s="1" t="n">
+        <v>0.08525000000000001</v>
+      </c>
+      <c r="P290" s="2" t="n">
+        <v>-0.0003517823639773496</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13853,6 +15599,12 @@
       <c r="N291" s="2" t="n">
         <v>-0.001694436599830487</v>
       </c>
+      <c r="O291" s="1" t="n">
+        <v>0.03547</v>
+      </c>
+      <c r="P291" s="3" t="n">
+        <v>0.003394625176803453</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13899,6 +15651,12 @@
       <c r="N292" s="3" t="n">
         <v>0.001302351086434994</v>
       </c>
+      <c r="O292" s="1" t="n">
+        <v>1.4624</v>
+      </c>
+      <c r="P292" s="3" t="n">
+        <v>0.001095290251916637</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13945,6 +15703,12 @@
       <c r="N293" s="2" t="n">
         <v>-0.001367053998632979</v>
       </c>
+      <c r="O293" s="1" t="n">
+        <v>0.005856</v>
+      </c>
+      <c r="P293" s="3" t="n">
+        <v>0.002053388090349052</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13991,6 +15755,12 @@
       <c r="N294" s="2" t="n">
         <v>-0.0008805400645729277</v>
       </c>
+      <c r="O294" s="1" t="n">
+        <v>0.003405</v>
+      </c>
+      <c r="P294" s="3" t="n">
+        <v>0.0002937720329025067</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14037,6 +15807,12 @@
       <c r="N295" s="2" t="n">
         <v>-0.003153988868274647</v>
       </c>
+      <c r="O295" s="1" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="P295" s="3" t="n">
+        <v>0.003163967988088656</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14083,6 +15859,12 @@
       <c r="N296" s="2" t="n">
         <v>-0.002223210315695817</v>
       </c>
+      <c r="O296" s="1" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="P296" s="3" t="n">
+        <v>0.003119429590017679</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14129,6 +15911,12 @@
       <c r="N297" s="2" t="n">
         <v>-0.005858230814294049</v>
       </c>
+      <c r="O297" s="1" t="n">
+        <v>0.01701</v>
+      </c>
+      <c r="P297" s="3" t="n">
+        <v>0.002357100766057857</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14175,6 +15963,12 @@
       <c r="N298" s="2" t="n">
         <v>-0.003614122880177991</v>
       </c>
+      <c r="O298" s="1" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="P298" s="3" t="n">
+        <v>0.0005580357142856528</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14221,6 +16015,12 @@
       <c r="N299" s="2" t="n">
         <v>-0.0009041591320071964</v>
       </c>
+      <c r="O299" s="1" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="P299" s="3" t="n">
+        <v>0.002714932126696722</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14267,6 +16067,12 @@
       <c r="N300" s="2" t="n">
         <v>-0.001934235976789257</v>
       </c>
+      <c r="O300" s="1" t="n">
+        <v>0.02069</v>
+      </c>
+      <c r="P300" s="3" t="n">
+        <v>0.002422480620155108</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14313,6 +16119,12 @@
       <c r="N301" s="2" t="n">
         <v>-0.001658374792703152</v>
       </c>
+      <c r="O301" s="1" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="P301" s="3" t="n">
+        <v>0.0116279069767442</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14359,6 +16171,12 @@
       <c r="N302" s="2" t="n">
         <v>-0.002212389380530884</v>
       </c>
+      <c r="O302" s="1" t="n">
+        <v>0.01373</v>
+      </c>
+      <c r="P302" s="3" t="n">
+        <v>0.01478196600147811</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14405,6 +16223,12 @@
       <c r="N303" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O303" s="1" t="n">
+        <v>0.07396999999999999</v>
+      </c>
+      <c r="P303" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14451,6 +16275,12 @@
       <c r="N304" s="2" t="n">
         <v>-0.0006293266205162404</v>
       </c>
+      <c r="O304" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="P304" s="3" t="n">
+        <v>0.001259445843828883</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14497,6 +16327,12 @@
       <c r="N305" s="2" t="n">
         <v>-0.002765826674861703</v>
       </c>
+      <c r="O305" s="1" t="n">
+        <v>0.06482</v>
+      </c>
+      <c r="P305" s="2" t="n">
+        <v>-0.00123266563944525</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14543,6 +16379,12 @@
       <c r="N306" s="2" t="n">
         <v>-0.000801603206412793</v>
       </c>
+      <c r="O306" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P306" s="3" t="n">
+        <v>0.002807862013638212</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14589,6 +16431,12 @@
       <c r="N307" s="2" t="n">
         <v>-0.002157497303128373</v>
       </c>
+      <c r="O307" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="P307" s="3" t="n">
+        <v>0.006486486486486492</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14635,6 +16483,12 @@
       <c r="N308" s="2" t="n">
         <v>-0.001507916561950177</v>
       </c>
+      <c r="O308" s="1" t="n">
+        <v>0.03969</v>
+      </c>
+      <c r="P308" s="2" t="n">
+        <v>-0.001006795872136883</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14681,6 +16535,12 @@
       <c r="N309" s="2" t="n">
         <v>-0.001265022137887581</v>
       </c>
+      <c r="O309" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="P309" s="2" t="n">
+        <v>-0.004433185560481137</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14727,6 +16587,12 @@
       <c r="N310" s="2" t="n">
         <v>-0.001289847060991351</v>
       </c>
+      <c r="O310" s="1" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="P310" s="3" t="n">
+        <v>0.001845018450184555</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14773,6 +16639,12 @@
       <c r="N311" s="2" t="n">
         <v>-0.002015677491601417</v>
       </c>
+      <c r="O311" s="1" t="n">
+        <v>0.004459</v>
+      </c>
+      <c r="P311" s="3" t="n">
+        <v>0.0006732495511670553</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14819,6 +16691,12 @@
       <c r="N312" s="2" t="n">
         <v>-0.001418942887548882</v>
       </c>
+      <c r="O312" s="1" t="n">
+        <v>0.08459999999999999</v>
+      </c>
+      <c r="P312" s="3" t="n">
+        <v>0.001776198934280608</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14865,6 +16743,12 @@
       <c r="N313" s="2" t="n">
         <v>-0.001202083611593519</v>
       </c>
+      <c r="O313" s="1" t="n">
+        <v>0.07502</v>
+      </c>
+      <c r="P313" s="3" t="n">
+        <v>0.003209414281893609</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14911,6 +16795,12 @@
       <c r="N314" s="3" t="n">
         <v>0.0006531678641410123</v>
       </c>
+      <c r="O314" s="1" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="P314" s="3" t="n">
+        <v>0.001958224543080905</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14957,6 +16847,12 @@
       <c r="N315" s="2" t="n">
         <v>-0.001251564455569498</v>
       </c>
+      <c r="O315" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="P315" s="3" t="n">
+        <v>0.001879699248120268</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15003,6 +16899,12 @@
       <c r="N316" s="3" t="n">
         <v>0.0005537098560353764</v>
       </c>
+      <c r="O316" s="1" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="P316" s="3" t="n">
+        <v>0.003873824017708944</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15049,6 +16951,12 @@
       <c r="N317" s="2" t="n">
         <v>-0.004247411733474902</v>
       </c>
+      <c r="O317" s="1" t="n">
+        <v>0.007502</v>
+      </c>
+      <c r="P317" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15095,6 +17003,12 @@
       <c r="N318" s="3" t="n">
         <v>0.001789976133651547</v>
       </c>
+      <c r="O318" s="1" t="n">
+        <v>0.04993</v>
+      </c>
+      <c r="P318" s="2" t="n">
+        <v>-0.008735358348223069</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15141,6 +17055,12 @@
       <c r="N319" s="2" t="n">
         <v>-0.004091153777139888</v>
       </c>
+      <c r="O319" s="1" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="P319" s="3" t="n">
+        <v>0.002234153724190154</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15187,6 +17107,12 @@
       <c r="N320" s="2" t="n">
         <v>-0.002270147559591376</v>
       </c>
+      <c r="O320" s="1" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="P320" s="3" t="n">
+        <v>0.00386803185437993</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15233,6 +17159,12 @@
       <c r="N321" s="2" t="n">
         <v>-0.0036040674475478</v>
       </c>
+      <c r="O321" s="1" t="n">
+        <v>0.07743999999999999</v>
+      </c>
+      <c r="P321" s="3" t="n">
+        <v>0.0003875468285749692</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -15279,6 +17211,12 @@
       <c r="N322" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O322" s="1" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="P322" s="3" t="n">
+        <v>0.0006146281499692009</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -15325,6 +17263,12 @@
       <c r="N323" s="2" t="n">
         <v>-0.004032258064516132</v>
       </c>
+      <c r="O323" s="1" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="P323" s="3" t="n">
+        <v>0.001012145748987855</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15371,6 +17315,12 @@
       <c r="N324" s="2" t="n">
         <v>-0.002134911419903423</v>
       </c>
+      <c r="O324" s="1" t="n">
+        <v>0.053327</v>
+      </c>
+      <c r="P324" s="3" t="n">
+        <v>0.0008069964717363819</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15417,6 +17367,12 @@
       <c r="N325" s="2" t="n">
         <v>-0.002603658139686153</v>
       </c>
+      <c r="O325" s="1" t="n">
+        <v>0.15358</v>
+      </c>
+      <c r="P325" s="3" t="n">
+        <v>0.002284148012791158</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15463,6 +17419,12 @@
       <c r="N326" s="3" t="n">
         <v>0.003891050583657564</v>
       </c>
+      <c r="O326" s="1" t="n">
+        <v>0.006493</v>
+      </c>
+      <c r="P326" s="3" t="n">
+        <v>0.00666666666666661</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15509,6 +17471,12 @@
       <c r="N327" s="3" t="n">
         <v>0.002251804755281876</v>
       </c>
+      <c r="O327" s="1" t="n">
+        <v>0.015155</v>
+      </c>
+      <c r="P327" s="3" t="n">
+        <v>0.001453776514901173</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15555,6 +17523,12 @@
       <c r="N328" s="3" t="n">
         <v>0.00105708245243132</v>
       </c>
+      <c r="O328" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="P328" s="3" t="n">
+        <v>0.004223864836325212</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15601,6 +17575,12 @@
       <c r="N329" s="2" t="n">
         <v>-0.001584068793844775</v>
       </c>
+      <c r="O329" s="1" t="n">
+        <v>0.004426</v>
+      </c>
+      <c r="P329" s="3" t="n">
+        <v>0.003173164097914806</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15647,6 +17627,12 @@
       <c r="N330" s="3" t="n">
         <v>0.009984338292873856</v>
       </c>
+      <c r="O330" s="1" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="P330" s="3" t="n">
+        <v>0.002519868191510082</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15693,6 +17679,12 @@
       <c r="N331" s="2" t="n">
         <v>-0.003817834742296188</v>
       </c>
+      <c r="O331" s="1" t="n">
+        <v>0.03621</v>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>-0.008759923350670705</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15739,6 +17731,12 @@
       <c r="N332" s="2" t="n">
         <v>-0.002047781569965834</v>
       </c>
+      <c r="O332" s="1" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="P332" s="3" t="n">
+        <v>0.0006839945280438901</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15785,6 +17783,12 @@
       <c r="N333" s="2" t="n">
         <v>-0.00207039337474126</v>
       </c>
+      <c r="O333" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="P333" s="3" t="n">
+        <v>0.003112033195020692</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15831,6 +17835,12 @@
       <c r="N334" s="2" t="n">
         <v>-0.001142857142857017</v>
       </c>
+      <c r="O334" s="1" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="P334" s="2" t="n">
+        <v>-0.0004576659038903003</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15877,6 +17887,12 @@
       <c r="N335" s="2" t="n">
         <v>-0.000369094488189004</v>
       </c>
+      <c r="O335" s="1" t="n">
+        <v>0.08123</v>
+      </c>
+      <c r="P335" s="2" t="n">
+        <v>-0.0002461538461539215</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15923,6 +17939,12 @@
       <c r="N336" s="2" t="n">
         <v>-0.00292540224280847</v>
       </c>
+      <c r="O336" s="1" t="n">
+        <v>0.2048</v>
+      </c>
+      <c r="P336" s="3" t="n">
+        <v>0.001466992665036785</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15969,6 +17991,12 @@
       <c r="N337" s="2" t="n">
         <v>-0.0009813542688910297</v>
       </c>
+      <c r="O337" s="1" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="P337" s="3" t="n">
+        <v>0.002946954813359579</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -16015,6 +18043,12 @@
       <c r="N338" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O338" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="P338" s="3" t="n">
+        <v>0.003542958370239128</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -16061,6 +18095,12 @@
       <c r="N339" s="2" t="n">
         <v>-0.0005458515283842572</v>
       </c>
+      <c r="O339" s="1" t="n">
+        <v>0.01834</v>
+      </c>
+      <c r="P339" s="3" t="n">
+        <v>0.001638448935008125</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -16107,6 +18147,12 @@
       <c r="N340" s="2" t="n">
         <v>-0.00584484590860781</v>
       </c>
+      <c r="O340" s="1" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="P340" s="2" t="n">
+        <v>-0.003670051665775987</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -16153,6 +18199,12 @@
       <c r="N341" s="2" t="n">
         <v>-0.004396112910689557</v>
       </c>
+      <c r="O341" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="P341" s="3" t="n">
+        <v>0.0002323960027888232</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16199,6 +18251,12 @@
       <c r="N342" s="3" t="n">
         <v>0.001786625829504865</v>
       </c>
+      <c r="O342" s="1" t="n">
+        <v>0.07824</v>
+      </c>
+      <c r="P342" s="2" t="n">
+        <v>-0.003312101910827979</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16245,6 +18303,12 @@
       <c r="N343" s="3" t="n">
         <v>0.001048905205192082</v>
       </c>
+      <c r="O343" s="1" t="n">
+        <v>7.647</v>
+      </c>
+      <c r="P343" s="3" t="n">
+        <v>0.001571709233791808</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -16291,6 +18355,12 @@
       <c r="N344" s="2" t="n">
         <v>-0.003151957531519597</v>
       </c>
+      <c r="O344" s="1" t="n">
+        <v>0.6034</v>
+      </c>
+      <c r="P344" s="3" t="n">
+        <v>0.004160426027625325</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -16337,6 +18407,12 @@
       <c r="N345" s="2" t="n">
         <v>-0.003230148048452276</v>
       </c>
+      <c r="O345" s="1" t="n">
+        <v>0.03729</v>
+      </c>
+      <c r="P345" s="3" t="n">
+        <v>0.007021334053470061</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16383,6 +18459,12 @@
       <c r="N346" s="2" t="n">
         <v>-0.002409638554216936</v>
       </c>
+      <c r="O346" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="P346" s="3" t="n">
+        <v>0.002415458937198137</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -16429,6 +18511,12 @@
       <c r="N347" s="2" t="n">
         <v>-0.002312138728323605</v>
       </c>
+      <c r="O347" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="P347" s="3" t="n">
+        <v>0.008111239860950085</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -16475,6 +18563,12 @@
       <c r="N348" s="3" t="n">
         <v>0.001272362739050039</v>
       </c>
+      <c r="O348" s="1" t="n">
+        <v>5190.3</v>
+      </c>
+      <c r="P348" s="2" t="n">
+        <v>-0.0006738803958565982</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16521,6 +18615,12 @@
       <c r="N349" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O349" s="1" t="n">
+        <v>0.01362</v>
+      </c>
+      <c r="P349" s="3" t="n">
+        <v>0.002945508100147283</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16567,6 +18667,12 @@
       <c r="N350" s="2" t="n">
         <v>-0.003340013360053536</v>
       </c>
+      <c r="O350" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="P350" s="3" t="n">
+        <v>0.01005361930294912</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16613,6 +18719,12 @@
       <c r="N351" s="2" t="n">
         <v>-0.001642845408247124</v>
       </c>
+      <c r="O351" s="1" t="n">
+        <v>0.0006122</v>
+      </c>
+      <c r="P351" s="3" t="n">
+        <v>0.007404969557347467</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16659,6 +18771,12 @@
       <c r="N352" s="2" t="n">
         <v>-0.002531645569620326</v>
       </c>
+      <c r="O352" s="1" t="n">
+        <v>0.01976</v>
+      </c>
+      <c r="P352" s="3" t="n">
+        <v>0.00304568527918787</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16705,6 +18823,12 @@
       <c r="N353" s="2" t="n">
         <v>-0.008626198083066999</v>
       </c>
+      <c r="O353" s="1" t="n">
+        <v>0.09336999999999999</v>
+      </c>
+      <c r="P353" s="3" t="n">
+        <v>0.003007841873455673</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16751,6 +18875,12 @@
       <c r="N354" s="2" t="n">
         <v>-0.006586169045005525</v>
       </c>
+      <c r="O354" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="P354" s="3" t="n">
+        <v>0.004419889502762404</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16797,6 +18927,12 @@
       <c r="N355" s="2" t="n">
         <v>-0.0009779951100244736</v>
       </c>
+      <c r="O355" s="1" t="n">
+        <v>0.0006181</v>
+      </c>
+      <c r="P355" s="3" t="n">
+        <v>0.008484255180290452</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16843,6 +18979,12 @@
       <c r="N356" s="2" t="n">
         <v>-0.008678881388620923</v>
       </c>
+      <c r="O356" s="1" t="n">
+        <v>2.061</v>
+      </c>
+      <c r="P356" s="3" t="n">
+        <v>0.00243190661478594</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16889,6 +19031,12 @@
       <c r="N357" s="2" t="n">
         <v>-0.0004319654427645612</v>
       </c>
+      <c r="O357" s="1" t="n">
+        <v>0.02294</v>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>-0.008643042350907617</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16935,6 +19083,12 @@
       <c r="N358" s="2" t="n">
         <v>-0.002469135802469062</v>
       </c>
+      <c r="O358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="P358" s="3" t="n">
+        <v>0.002475247524752401</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16981,6 +19135,12 @@
       <c r="N359" s="2" t="n">
         <v>-0.002722940776038128</v>
       </c>
+      <c r="O359" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="P359" s="3" t="n">
+        <v>0.002730375426621168</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -17027,6 +19187,12 @@
       <c r="N360" s="2" t="n">
         <v>-0.003276735180220482</v>
       </c>
+      <c r="O360" s="1" t="n">
+        <v>0.003343</v>
+      </c>
+      <c r="P360" s="2" t="n">
+        <v>-0.0008965929468021412</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -17073,6 +19239,12 @@
       <c r="N361" s="2" t="n">
         <v>-0.003114779629341227</v>
       </c>
+      <c r="O361" s="1" t="n">
+        <v>0.6398</v>
+      </c>
+      <c r="P361" s="2" t="n">
+        <v>-0.0004686767692547523</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -17119,6 +19291,12 @@
       <c r="N362" s="2" t="n">
         <v>-0.005972696245733693</v>
       </c>
+      <c r="O362" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="P362" s="3" t="n">
+        <v>0.002575107296137234</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -17165,6 +19343,12 @@
       <c r="N363" s="3" t="n">
         <v>0.001682214405872442</v>
       </c>
+      <c r="O363" s="1" t="n">
+        <v>0.06555</v>
+      </c>
+      <c r="P363" s="3" t="n">
+        <v>0.0007633587786258701</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -17211,6 +19395,12 @@
       <c r="N364" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O364" s="1" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="P364" s="3" t="n">
+        <v>0.0002125850340136764</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -17257,6 +19447,12 @@
       <c r="N365" s="3" t="n">
         <v>0.001264755480606982</v>
       </c>
+      <c r="O365" s="1" t="n">
+        <v>0.07137</v>
+      </c>
+      <c r="P365" s="3" t="n">
+        <v>0.001684210526315916</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -17303,6 +19499,12 @@
       <c r="N366" s="2" t="n">
         <v>-0.0005395683453236566</v>
       </c>
+      <c r="O366" s="1" t="n">
+        <v>0.05606</v>
+      </c>
+      <c r="P366" s="3" t="n">
+        <v>0.008817707396076973</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -17349,6 +19551,12 @@
       <c r="N367" s="2" t="n">
         <v>-0.001537935748462061</v>
       </c>
+      <c r="O367" s="1" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="P367" s="3" t="n">
+        <v>0.000513434879342723</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -17395,6 +19603,12 @@
       <c r="N368" s="2" t="n">
         <v>-0.002097535395909721</v>
       </c>
+      <c r="O368" s="1" t="n">
+        <v>0.05745</v>
+      </c>
+      <c r="P368" s="3" t="n">
+        <v>0.006305832895428258</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -17441,6 +19655,12 @@
       <c r="N369" s="2" t="n">
         <v>-0.002575660012878307</v>
       </c>
+      <c r="O369" s="1" t="n">
+        <v>0.03094</v>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>-0.001291155584247961</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -17487,6 +19707,12 @@
       <c r="N370" s="2" t="n">
         <v>-0.0006153846153846304</v>
       </c>
+      <c r="O370" s="1" t="n">
+        <v>0.0001627</v>
+      </c>
+      <c r="P370" s="3" t="n">
+        <v>0.001847290640394134</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -17533,6 +19759,12 @@
       <c r="N371" s="3" t="n">
         <v>0.0001473405039045429</v>
       </c>
+      <c r="O371" s="1" t="n">
+        <v>0.006811</v>
+      </c>
+      <c r="P371" s="3" t="n">
+        <v>0.003388332351208081</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -17579,6 +19811,12 @@
       <c r="N372" s="2" t="n">
         <v>-0.002304147465437719</v>
       </c>
+      <c r="O372" s="1" t="n">
+        <v>0.006982</v>
+      </c>
+      <c r="P372" s="3" t="n">
+        <v>0.007794457274826823</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -17625,6 +19863,12 @@
       <c r="N373" s="2" t="n">
         <v>-0.01190784364483557</v>
       </c>
+      <c r="O373" s="1" t="n">
+        <v>3.805</v>
+      </c>
+      <c r="P373" s="2" t="n">
+        <v>-0.003143830233167411</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -17671,6 +19915,12 @@
       <c r="N374" s="2" t="n">
         <v>-0.003104713519616312</v>
       </c>
+      <c r="O374" s="1" t="n">
+        <v>0.07065</v>
+      </c>
+      <c r="P374" s="3" t="n">
+        <v>0.0001415628539072763</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17717,6 +19967,12 @@
       <c r="N375" s="2" t="n">
         <v>-0.002556563978013446</v>
       </c>
+      <c r="O375" s="1" t="n">
+        <v>0.07852000000000001</v>
+      </c>
+      <c r="P375" s="3" t="n">
+        <v>0.00627963603742156</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -17763,6 +20019,12 @@
       <c r="N376" s="3" t="n">
         <v>0.000319131961065777</v>
       </c>
+      <c r="O376" s="1" t="n">
+        <v>0.06272999999999999</v>
+      </c>
+      <c r="P376" s="3" t="n">
+        <v>0.0006380602966980121</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -17809,6 +20071,12 @@
       <c r="N377" s="2" t="n">
         <v>-0.003269255917353213</v>
       </c>
+      <c r="O377" s="1" t="n">
+        <v>0.07642</v>
+      </c>
+      <c r="P377" s="3" t="n">
+        <v>0.002623983206507554</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -17855,6 +20123,12 @@
       <c r="N378" s="3" t="n">
         <v>0.0007471980074719982</v>
       </c>
+      <c r="O378" s="1" t="n">
+        <v>0.0004013</v>
+      </c>
+      <c r="P378" s="2" t="n">
+        <v>-0.001244400199104062</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17901,6 +20175,12 @@
       <c r="N379" s="2" t="n">
         <v>-0.002818035426731104</v>
       </c>
+      <c r="O379" s="1" t="n">
+        <v>0.07451000000000001</v>
+      </c>
+      <c r="P379" s="3" t="n">
+        <v>0.002691427802449276</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -17947,6 +20227,12 @@
       <c r="N380" s="2" t="n">
         <v>-0.005185185185185231</v>
       </c>
+      <c r="O380" s="1" t="n">
+        <v>0.001353</v>
+      </c>
+      <c r="P380" s="3" t="n">
+        <v>0.007446016381236058</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -17993,6 +20279,12 @@
       <c r="N381" s="2" t="n">
         <v>-0.01156336725254397</v>
       </c>
+      <c r="O381" s="1" t="n">
+        <v>6.441</v>
+      </c>
+      <c r="P381" s="3" t="n">
+        <v>0.004679457182966815</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -18039,6 +20331,12 @@
       <c r="N382" s="2" t="n">
         <v>-0.0007490636704120844</v>
       </c>
+      <c r="O382" s="1" t="n">
+        <v>0.01373</v>
+      </c>
+      <c r="P382" s="3" t="n">
+        <v>0.02923538230884556</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -18085,6 +20383,12 @@
       <c r="N383" s="2" t="n">
         <v>-0.002826455624646774</v>
       </c>
+      <c r="O383" s="1" t="n">
+        <v>0.01757</v>
+      </c>
+      <c r="P383" s="2" t="n">
+        <v>-0.003968253968254004</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -18131,6 +20435,12 @@
       <c r="N384" s="2" t="n">
         <v>-0.0009832841691249053</v>
       </c>
+      <c r="O384" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="P384" s="3" t="n">
+        <v>0.0009842519685039652</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -18177,6 +20487,12 @@
       <c r="N385" s="2" t="n">
         <v>-0.000669493416648095</v>
       </c>
+      <c r="O385" s="1" t="n">
+        <v>4.493</v>
+      </c>
+      <c r="P385" s="3" t="n">
+        <v>0.003349709691826836</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -18223,6 +20539,12 @@
       <c r="N386" s="2" t="n">
         <v>-0.005443234836703003</v>
       </c>
+      <c r="O386" s="1" t="n">
+        <v>0.001292</v>
+      </c>
+      <c r="P386" s="3" t="n">
+        <v>0.01016419077404221</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -18269,6 +20591,12 @@
       <c r="N387" s="3" t="n">
         <v>0.0005063291139239714</v>
       </c>
+      <c r="O387" s="1" t="n">
+        <v>0.0005931000000000001</v>
+      </c>
+      <c r="P387" s="3" t="n">
+        <v>0.0005060728744940309</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -18315,6 +20643,12 @@
       <c r="N388" s="2" t="n">
         <v>-0.002659574468085152</v>
       </c>
+      <c r="O388" s="1" t="n">
+        <v>0.01139</v>
+      </c>
+      <c r="P388" s="3" t="n">
+        <v>0.01244444444444455</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -18361,6 +20695,12 @@
       <c r="N389" s="2" t="n">
         <v>-0.001100110011001246</v>
       </c>
+      <c r="O389" s="1" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="P389" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -18407,6 +20747,12 @@
       <c r="N390" s="2" t="n">
         <v>-0.00101677681748852</v>
       </c>
+      <c r="O390" s="1" t="n">
+        <v>0.07899</v>
+      </c>
+      <c r="P390" s="3" t="n">
+        <v>0.004961832061068721</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -18453,6 +20799,12 @@
       <c r="N391" s="2" t="n">
         <v>-0.001171875000000088</v>
       </c>
+      <c r="O391" s="1" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="P391" s="3" t="n">
+        <v>0.01095033242080573</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -18499,6 +20851,12 @@
       <c r="N392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O392" s="1" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="P392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -18545,6 +20903,12 @@
       <c r="N393" s="3" t="n">
         <v>0.007557864903164711</v>
       </c>
+      <c r="O393" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="P393" s="2" t="n">
+        <v>-0.001406469760900083</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -18591,6 +20955,12 @@
       <c r="N394" s="2" t="n">
         <v>-0.0009722897423432461</v>
       </c>
+      <c r="O394" s="1" t="n">
+        <v>0.2057</v>
+      </c>
+      <c r="P394" s="3" t="n">
+        <v>0.000973236009732388</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -18637,6 +21007,12 @@
       <c r="N395" s="2" t="n">
         <v>-0.00308008213552356</v>
       </c>
+      <c r="O395" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="P395" s="3" t="n">
+        <v>0.003089598352214157</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -18683,6 +21059,12 @@
       <c r="N396" s="3" t="n">
         <v>0.0007388252678242423</v>
       </c>
+      <c r="O396" s="1" t="n">
+        <v>2.721</v>
+      </c>
+      <c r="P396" s="3" t="n">
+        <v>0.004429678848283504</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -18729,6 +21111,12 @@
       <c r="N397" s="3" t="n">
         <v>0.0007923930269412757</v>
       </c>
+      <c r="O397" s="1" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="P397" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -18775,6 +21163,12 @@
       <c r="N398" s="2" t="n">
         <v>-0.001776198934280638</v>
       </c>
+      <c r="O398" s="1" t="n">
+        <v>0.007393</v>
+      </c>
+      <c r="P398" s="3" t="n">
+        <v>0.011908020804818</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -18821,6 +21215,12 @@
       <c r="N399" s="3" t="n">
         <v>0.002692307692307609</v>
       </c>
+      <c r="O399" s="1" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="P399" s="3" t="n">
+        <v>0.002301495972382008</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18867,6 +21267,12 @@
       <c r="N400" s="2" t="n">
         <v>-0.001577287066246058</v>
       </c>
+      <c r="O400" s="1" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="P400" s="3" t="n">
+        <v>0.004107424960505603</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -18913,6 +21319,12 @@
       <c r="N401" s="2" t="n">
         <v>-0.003145514223194691</v>
       </c>
+      <c r="O401" s="1" t="n">
+        <v>0.007294</v>
+      </c>
+      <c r="P401" s="3" t="n">
+        <v>0.0006859651529702011</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -18959,6 +21371,12 @@
       <c r="N402" s="2" t="n">
         <v>-0.0006561679790025221</v>
       </c>
+      <c r="O402" s="1" t="n">
+        <v>0.00459</v>
+      </c>
+      <c r="P402" s="3" t="n">
+        <v>0.004596191726854932</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -19005,6 +21423,12 @@
       <c r="N403" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O403" s="1" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="P403" s="3" t="n">
+        <v>0.001890359168241968</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -19051,6 +21475,12 @@
       <c r="N404" s="3" t="n">
         <v>0.001253132832080178</v>
       </c>
+      <c r="O404" s="1" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="P404" s="3" t="n">
+        <v>0.003754693366708435</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -19097,6 +21527,12 @@
       <c r="N405" s="2" t="n">
         <v>-0.002532228360957579</v>
       </c>
+      <c r="O405" s="1" t="n">
+        <v>0.0008736</v>
+      </c>
+      <c r="P405" s="3" t="n">
+        <v>0.008077544426494292</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -19143,6 +21579,12 @@
       <c r="N406" s="2" t="n">
         <v>-0.00413060582218729</v>
       </c>
+      <c r="O406" s="1" t="n">
+        <v>0.005074</v>
+      </c>
+      <c r="P406" s="3" t="n">
+        <v>0.002172624925933358</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -19189,6 +21631,12 @@
       <c r="N407" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O407" s="1" t="n">
+        <v>0.01212</v>
+      </c>
+      <c r="P407" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -19235,6 +21683,12 @@
       <c r="N408" s="2" t="n">
         <v>-0.0006910850034553669</v>
       </c>
+      <c r="O408" s="1" t="n">
+        <v>0.001446</v>
+      </c>
+      <c r="P408" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -19281,6 +21735,12 @@
       <c r="N409" s="3" t="n">
         <v>0.001605995717344874</v>
       </c>
+      <c r="O409" s="1" t="n">
+        <v>0.03734</v>
+      </c>
+      <c r="P409" s="2" t="n">
+        <v>-0.002137894174238473</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -19327,6 +21787,12 @@
       <c r="N410" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O410" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="P410" s="3" t="n">
+        <v>0.0006127450980391906</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -19373,6 +21839,12 @@
       <c r="N411" s="2" t="n">
         <v>-0.003154574132492204</v>
       </c>
+      <c r="O411" s="1" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="P411" s="3" t="n">
+        <v>0.004219409282700543</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -19419,6 +21891,12 @@
       <c r="N412" s="2" t="n">
         <v>-0.003862150920974602</v>
       </c>
+      <c r="O412" s="1" t="n">
+        <v>0.06721000000000001</v>
+      </c>
+      <c r="P412" s="3" t="n">
+        <v>0.002236802863107833</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -19465,6 +21943,12 @@
       <c r="N413" s="2" t="n">
         <v>-0.001182033096926714</v>
       </c>
+      <c r="O413" s="1" t="n">
+        <v>2543</v>
+      </c>
+      <c r="P413" s="3" t="n">
+        <v>0.003155818540433925</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -19511,6 +21995,12 @@
       <c r="N414" s="3" t="n">
         <v>0.001341510157148345</v>
       </c>
+      <c r="O414" s="1" t="n">
+        <v>0.05229</v>
+      </c>
+      <c r="P414" s="3" t="n">
+        <v>0.0007655502392345514</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -19557,6 +22047,12 @@
       <c r="N415" s="3" t="n">
         <v>0.002292263610315188</v>
       </c>
+      <c r="O415" s="1" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="P415" s="3" t="n">
+        <v>0.0017152658662092</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -19603,6 +22099,12 @@
       <c r="N416" s="3" t="n">
         <v>0.0004354136429608454</v>
       </c>
+      <c r="O416" s="1" t="n">
+        <v>0.06904</v>
+      </c>
+      <c r="P416" s="3" t="n">
+        <v>0.001595821848251835</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -19649,6 +22151,12 @@
       <c r="N417" s="3" t="n">
         <v>0.01351351351351353</v>
       </c>
+      <c r="O417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="P417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -19695,6 +22203,12 @@
       <c r="N418" s="2" t="n">
         <v>-0.001960784313725456</v>
       </c>
+      <c r="O418" s="1" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="P418" s="3" t="n">
+        <v>0.00458415193189264</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -19741,6 +22255,12 @@
       <c r="N419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="P419" s="2" t="n">
+        <v>-0.008064516129032209</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -19787,6 +22307,12 @@
       <c r="N420" s="3" t="n">
         <v>0.0005230125523012338</v>
       </c>
+      <c r="O420" s="1" t="n">
+        <v>0.01933</v>
+      </c>
+      <c r="P420" s="3" t="n">
+        <v>0.01045478306325137</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -19833,6 +22359,12 @@
       <c r="N421" s="3" t="n">
         <v>0.005207519658386715</v>
       </c>
+      <c r="O421" s="1" t="n">
+        <v>0.19376</v>
+      </c>
+      <c r="P421" s="3" t="n">
+        <v>0.00378179557581713</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -19879,6 +22411,12 @@
       <c r="N422" s="3" t="n">
         <v>0.002341920374707165</v>
       </c>
+      <c r="O422" s="1" t="n">
+        <v>0.03422</v>
+      </c>
+      <c r="P422" s="2" t="n">
+        <v>-0.0005841121495326865</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -19925,6 +22463,12 @@
       <c r="N423" s="2" t="n">
         <v>-0.003523608174770969</v>
       </c>
+      <c r="O423" s="1" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="P423" s="3" t="n">
+        <v>0.00282885431400291</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -19971,6 +22515,12 @@
       <c r="N424" s="2" t="n">
         <v>-0.003787878787878798</v>
       </c>
+      <c r="O424" s="1" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="P424" s="3" t="n">
+        <v>0.003802281368821303</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -20017,6 +22567,12 @@
       <c r="N425" s="2" t="n">
         <v>-0.0009532888465203907</v>
       </c>
+      <c r="O425" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="P425" s="3" t="n">
+        <v>0.001908396946564808</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -20063,6 +22619,12 @@
       <c r="N426" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O426" s="1" t="n">
+        <v>0.007031</v>
+      </c>
+      <c r="P426" s="2" t="n">
+        <v>-0.002412031782065785</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -20109,6 +22671,12 @@
       <c r="N427" s="2" t="n">
         <v>-0.004298554122704277</v>
       </c>
+      <c r="O427" s="1" t="n">
+        <v>0.02551</v>
+      </c>
+      <c r="P427" s="3" t="n">
+        <v>0.00117739403453698</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -20155,6 +22723,12 @@
       <c r="N428" s="2" t="n">
         <v>-0.001861504095308934</v>
       </c>
+      <c r="O428" s="1" t="n">
+        <v>0.008062</v>
+      </c>
+      <c r="P428" s="3" t="n">
+        <v>0.002362302623399219</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -20201,6 +22775,12 @@
       <c r="N429" s="2" t="n">
         <v>-0.004858299595141643</v>
       </c>
+      <c r="O429" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="P429" s="3" t="n">
+        <v>0.006509357200976421</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -20247,6 +22827,12 @@
       <c r="N430" s="2" t="n">
         <v>-0.001490979573579884</v>
       </c>
+      <c r="O430" s="1" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="P430" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20293,6 +22879,12 @@
       <c r="N431" s="2" t="n">
         <v>-0.003690036900369013</v>
       </c>
+      <c r="O431" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="P431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -20339,6 +22931,12 @@
       <c r="N432" s="3" t="n">
         <v>0.0005154639175257522</v>
       </c>
+      <c r="O432" s="1" t="n">
+        <v>0.009712999999999999</v>
+      </c>
+      <c r="P432" s="3" t="n">
+        <v>0.0008243173621843717</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -20385,6 +22983,12 @@
       <c r="N433" s="2" t="n">
         <v>-0.001930036188178617</v>
       </c>
+      <c r="O433" s="1" t="n">
+        <v>0.04143</v>
+      </c>
+      <c r="P433" s="3" t="n">
+        <v>0.001450326323422879</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -20431,6 +23035,12 @@
       <c r="N434" s="3" t="n">
         <v>0.003115264797507744</v>
       </c>
+      <c r="O434" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="P434" s="2" t="n">
+        <v>-0.002627806975633038</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -20477,6 +23087,12 @@
       <c r="N435" s="2" t="n">
         <v>-0.003250975292587785</v>
       </c>
+      <c r="O435" s="1" t="n">
+        <v>0.001541</v>
+      </c>
+      <c r="P435" s="3" t="n">
+        <v>0.005218525766470957</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -20523,6 +23139,12 @@
       <c r="N436" s="2" t="n">
         <v>-0.001092498179169657</v>
       </c>
+      <c r="O436" s="1" t="n">
+        <v>0.02751</v>
+      </c>
+      <c r="P436" s="3" t="n">
+        <v>0.002916514764856005</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -20569,6 +23191,12 @@
       <c r="N437" s="3" t="n">
         <v>0.002430428970713232</v>
       </c>
+      <c r="O437" s="1" t="n">
+        <v>0.08186</v>
+      </c>
+      <c r="P437" s="2" t="n">
+        <v>-0.007637289368408191</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -20615,6 +23243,12 @@
       <c r="N438" s="2" t="n">
         <v>-0.002608695652173988</v>
       </c>
+      <c r="O438" s="1" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="P438" s="3" t="n">
+        <v>0.006974716652136086</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -20661,6 +23295,12 @@
       <c r="N439" s="2" t="n">
         <v>-0.002585649644473176</v>
       </c>
+      <c r="O439" s="1" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="P439" s="3" t="n">
+        <v>0.001296176279974078</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -20707,6 +23347,12 @@
       <c r="N440" s="2" t="n">
         <v>-0.001117318435754096</v>
       </c>
+      <c r="O440" s="1" t="n">
+        <v>0.001803</v>
+      </c>
+      <c r="P440" s="3" t="n">
+        <v>0.008389261744966344</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -20753,6 +23399,12 @@
       <c r="N441" s="2" t="n">
         <v>-0.001356852103120799</v>
       </c>
+      <c r="O441" s="1" t="n">
+        <v>0.03677</v>
+      </c>
+      <c r="P441" s="2" t="n">
+        <v>-0.0008152173913044089</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -20799,6 +23451,12 @@
       <c r="N442" s="2" t="n">
         <v>-0.001615508885298803</v>
       </c>
+      <c r="O442" s="1" t="n">
+        <v>0.01857</v>
+      </c>
+      <c r="P442" s="3" t="n">
+        <v>0.001618122977346212</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -20845,6 +23503,12 @@
       <c r="N443" s="2" t="n">
         <v>-0.001484374999999967</v>
       </c>
+      <c r="O443" s="1" t="n">
+        <v>0.12804</v>
+      </c>
+      <c r="P443" s="3" t="n">
+        <v>0.001799546201392537</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -20891,6 +23555,12 @@
       <c r="N444" s="2" t="n">
         <v>-0.004449873483989241</v>
       </c>
+      <c r="O444" s="1" t="n">
+        <v>0.011442</v>
+      </c>
+      <c r="P444" s="3" t="n">
+        <v>0.002804557405784468</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -20937,6 +23607,12 @@
       <c r="N445" s="2" t="n">
         <v>-0.000248323814253863</v>
       </c>
+      <c r="O445" s="1" t="n">
+        <v>0.08087999999999999</v>
+      </c>
+      <c r="P445" s="3" t="n">
+        <v>0.004470938897168396</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -20983,6 +23659,12 @@
       <c r="N446" s="3" t="n">
         <v>0.001900237529691258</v>
       </c>
+      <c r="O446" s="1" t="n">
+        <v>0.0002115</v>
+      </c>
+      <c r="P446" s="3" t="n">
+        <v>0.002844950213371207</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -21029,6 +23711,12 @@
       <c r="N447" s="2" t="n">
         <v>-0.00459418070444112</v>
       </c>
+      <c r="O447" s="1" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="P447" s="3" t="n">
+        <v>0.004615384615384695</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -21075,6 +23763,12 @@
       <c r="N448" s="3" t="n">
         <v>0.004115226337448578</v>
       </c>
+      <c r="O448" s="1" t="n">
+        <v>0.11159</v>
+      </c>
+      <c r="P448" s="2" t="n">
+        <v>-0.005791161796151209</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -21121,6 +23815,12 @@
       <c r="N449" s="2" t="n">
         <v>-0.00118694362017807</v>
       </c>
+      <c r="O449" s="1" t="n">
+        <v>0.001685</v>
+      </c>
+      <c r="P449" s="3" t="n">
+        <v>0.001188354129530629</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -21167,6 +23867,12 @@
       <c r="N450" s="2" t="n">
         <v>-0.0009675858732462741</v>
       </c>
+      <c r="O450" s="1" t="n">
+        <v>0.0002067</v>
+      </c>
+      <c r="P450" s="3" t="n">
+        <v>0.000968523002421331</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -21213,6 +23919,12 @@
       <c r="N451" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O451" s="1" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="P451" s="3" t="n">
+        <v>0.005686125852918959</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -21259,6 +23971,12 @@
       <c r="N452" s="3" t="n">
         <v>0.002242152466367674</v>
       </c>
+      <c r="O452" s="1" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="P452" s="3" t="n">
+        <v>0.004474272930648691</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -21305,6 +24023,12 @@
       <c r="N453" s="2" t="n">
         <v>-0.0005733944954128579</v>
       </c>
+      <c r="O453" s="1" t="n">
+        <v>0.0001751</v>
+      </c>
+      <c r="P453" s="3" t="n">
+        <v>0.004589787722317799</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -21351,6 +24075,12 @@
       <c r="N454" s="2" t="n">
         <v>-0.006685593918856989</v>
       </c>
+      <c r="O454" s="1" t="n">
+        <v>0.10943</v>
+      </c>
+      <c r="P454" s="3" t="n">
+        <v>0.008943389267932866</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -21397,6 +24127,12 @@
       <c r="N455" s="3" t="n">
         <v>0.0001997203914519452</v>
       </c>
+      <c r="O455" s="1" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="P455" s="3" t="n">
+        <v>0.0009984025559104332</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -21443,6 +24179,12 @@
       <c r="N456" s="3" t="n">
         <v>0.0006886621173230196</v>
       </c>
+      <c r="O456" s="1" t="n">
+        <v>0.015973</v>
+      </c>
+      <c r="P456" s="2" t="n">
+        <v>-0.0006881881881882252</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -21489,6 +24231,12 @@
       <c r="N457" s="2" t="n">
         <v>-0.0004485645933014949</v>
       </c>
+      <c r="O457" s="1" t="n">
+        <v>0.006707</v>
+      </c>
+      <c r="P457" s="3" t="n">
+        <v>0.003290949887808574</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -21535,6 +24283,12 @@
       <c r="N458" s="2" t="n">
         <v>-0.000623700623700555</v>
       </c>
+      <c r="O458" s="1" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="P458" s="3" t="n">
+        <v>0.001872269606823292</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -21581,6 +24335,12 @@
       <c r="N459" s="2" t="n">
         <v>-0.0004705144291090858</v>
       </c>
+      <c r="O459" s="1" t="n">
+        <v>0.006375</v>
+      </c>
+      <c r="P459" s="3" t="n">
+        <v>0.0003138239447668913</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -21627,6 +24387,12 @@
       <c r="N460" s="2" t="n">
         <v>-0.001448225923244068</v>
       </c>
+      <c r="O460" s="1" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="P460" s="3" t="n">
+        <v>0.002175489485134117</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -21673,6 +24439,12 @@
       <c r="N461" s="3" t="n">
         <v>0.003033026286227729</v>
       </c>
+      <c r="O461" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="P461" s="3" t="n">
+        <v>0.003471833351999157</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -21719,6 +24491,12 @@
       <c r="N462" s="3" t="n">
         <v>0.004824561403508727</v>
       </c>
+      <c r="O462" s="1" t="n">
+        <v>0.04593</v>
+      </c>
+      <c r="P462" s="3" t="n">
+        <v>0.002400698384984701</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -21765,6 +24543,12 @@
       <c r="N463" s="2" t="n">
         <v>-0.004285714285714359</v>
       </c>
+      <c r="O463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="P463" s="3" t="n">
+        <v>0.002869440459110481</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -21811,6 +24595,12 @@
       <c r="N464" s="2" t="n">
         <v>-0.002286585365853745</v>
       </c>
+      <c r="O464" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="P464" s="3" t="n">
+        <v>0.002291825821237673</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -21857,6 +24647,12 @@
       <c r="N465" s="3" t="n">
         <v>0.002494654312188091</v>
       </c>
+      <c r="O465" s="1" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="P465" s="3" t="n">
+        <v>0.006043370067543474</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -21903,6 +24699,12 @@
       <c r="N466" s="2" t="n">
         <v>-0.002812939521800284</v>
       </c>
+      <c r="O466" s="1" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="P466" s="3" t="n">
+        <v>0.002820874471086039</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -21949,6 +24751,12 @@
       <c r="N467" s="2" t="n">
         <v>-0.003133159268929557</v>
       </c>
+      <c r="O467" s="1" t="n">
+        <v>0.01914</v>
+      </c>
+      <c r="P467" s="3" t="n">
+        <v>0.002619172341540148</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -21995,6 +24803,12 @@
       <c r="N468" s="2" t="n">
         <v>-0.002020202020202113</v>
       </c>
+      <c r="O468" s="1" t="n">
+        <v>0.009979999999999999</v>
+      </c>
+      <c r="P468" s="3" t="n">
+        <v>0.01012145748987848</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -22041,6 +24855,12 @@
       <c r="N469" s="3" t="n">
         <v>0.001746506986028029</v>
       </c>
+      <c r="O469" s="1" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="P469" s="3" t="n">
+        <v>0.002490660024906602</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -22087,6 +24907,12 @@
       <c r="N470" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O470" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="P470" s="3" t="n">
+        <v>0.002270147559591376</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -22133,6 +24959,12 @@
       <c r="N471" s="3" t="n">
         <v>0.001553277415346486</v>
       </c>
+      <c r="O471" s="1" t="n">
+        <v>3.234</v>
+      </c>
+      <c r="P471" s="3" t="n">
+        <v>0.003101736972704649</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -22179,6 +25011,12 @@
       <c r="N472" s="2" t="n">
         <v>-0.001218323586744674</v>
       </c>
+      <c r="O472" s="1" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="P472" s="3" t="n">
+        <v>0.009514515735545291</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -22225,6 +25063,12 @@
       <c r="N473" s="2" t="n">
         <v>-0.002409638554216959</v>
       </c>
+      <c r="O473" s="1" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="P473" s="3" t="n">
+        <v>0.008051529790660233</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -22271,6 +25115,12 @@
       <c r="N474" s="2" t="n">
         <v>-0.00339896858884195</v>
       </c>
+      <c r="O474" s="1" t="n">
+        <v>0.008540000000000001</v>
+      </c>
+      <c r="P474" s="3" t="n">
+        <v>0.004351405386334302</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -22317,6 +25167,12 @@
       <c r="N475" s="2" t="n">
         <v>-0.00691134413727356</v>
       </c>
+      <c r="O475" s="1" t="n">
+        <v>0.04176</v>
+      </c>
+      <c r="P475" s="3" t="n">
+        <v>0.00215982721382289</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -22363,6 +25219,12 @@
       <c r="N476" s="2" t="n">
         <v>-0.005062650297430675</v>
       </c>
+      <c r="O476" s="1" t="n">
+        <v>0.07888000000000001</v>
+      </c>
+      <c r="P476" s="3" t="n">
+        <v>0.003434677521943854</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -22409,6 +25271,12 @@
       <c r="N477" s="3" t="n">
         <v>0.002632926204929417</v>
       </c>
+      <c r="O477" s="1" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="P477" s="2" t="n">
+        <v>-0.002844846451236425</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -22455,6 +25323,12 @@
       <c r="N478" s="2" t="n">
         <v>-0.002103934357248114</v>
       </c>
+      <c r="O478" s="1" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="P478" s="3" t="n">
+        <v>0.002530044275774869</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -22501,6 +25375,12 @@
       <c r="N479" s="2" t="n">
         <v>-0.0009448223733937635</v>
       </c>
+      <c r="O479" s="1" t="n">
+        <v>0.005307</v>
+      </c>
+      <c r="P479" s="3" t="n">
+        <v>0.003782863627766229</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -22547,6 +25427,12 @@
       <c r="N480" s="2" t="n">
         <v>-0.001793400286944048</v>
       </c>
+      <c r="O480" s="1" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="P480" s="3" t="n">
+        <v>0.001077973409989301</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -22593,6 +25479,12 @@
       <c r="N481" s="2" t="n">
         <v>-0.002108314665963809</v>
       </c>
+      <c r="O481" s="1" t="n">
+        <v>0.07586</v>
+      </c>
+      <c r="P481" s="3" t="n">
+        <v>0.00171662485144581</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -22639,6 +25531,12 @@
       <c r="N482" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O482" s="1" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="P482" s="3" t="n">
+        <v>0.0006756756756756481</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -22685,6 +25583,12 @@
       <c r="N483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="P483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -22731,6 +25635,12 @@
       <c r="N484" s="2" t="n">
         <v>-0.003696857670979677</v>
       </c>
+      <c r="O484" s="1" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="P484" s="3" t="n">
+        <v>0.002319109461966671</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -22777,6 +25687,12 @@
       <c r="N485" s="2" t="n">
         <v>-0.003957309029859701</v>
       </c>
+      <c r="O485" s="1" t="n">
+        <v>0.008319</v>
+      </c>
+      <c r="P485" s="3" t="n">
+        <v>0.001565133638333838</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -22823,6 +25739,12 @@
       <c r="N486" s="2" t="n">
         <v>-0.002814636107760263</v>
       </c>
+      <c r="O486" s="1" t="n">
+        <v>0.007461</v>
+      </c>
+      <c r="P486" s="3" t="n">
+        <v>0.002822580645161199</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -22869,6 +25791,12 @@
       <c r="N487" s="2" t="n">
         <v>-0.002700270027002777</v>
       </c>
+      <c r="O487" s="1" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="P487" s="3" t="n">
+        <v>0.005415162454873676</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -22915,6 +25843,12 @@
       <c r="N488" s="3" t="n">
         <v>0.0002136523875654594</v>
       </c>
+      <c r="O488" s="1" t="n">
+        <v>0.009365</v>
+      </c>
+      <c r="P488" s="3" t="n">
+        <v>0.0002136067499733275</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -22961,6 +25895,12 @@
       <c r="N489" s="2" t="n">
         <v>-0.00181582360570689</v>
       </c>
+      <c r="O489" s="1" t="n">
+        <v>0.03854</v>
+      </c>
+      <c r="P489" s="3" t="n">
+        <v>0.001559251559251496</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -23007,6 +25947,12 @@
       <c r="N490" s="2" t="n">
         <v>-0.0008525149190111071</v>
       </c>
+      <c r="O490" s="1" t="n">
+        <v>0.05861</v>
+      </c>
+      <c r="P490" s="3" t="n">
+        <v>0.0001706484641638748</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -23053,6 +25999,12 @@
       <c r="N491" s="2" t="n">
         <v>-0.003112033195020692</v>
       </c>
+      <c r="O491" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="P491" s="3" t="n">
+        <v>0.002081165452653401</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -23099,6 +26051,12 @@
       <c r="N492" s="2" t="n">
         <v>-0.002255639097744446</v>
       </c>
+      <c r="O492" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P492" s="3" t="n">
+        <v>0.002260738507912671</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -23145,6 +26103,12 @@
       <c r="N493" s="3" t="n">
         <v>0.0002837684449488117</v>
       </c>
+      <c r="O493" s="1" t="n">
+        <v>0.03531</v>
+      </c>
+      <c r="P493" s="3" t="n">
+        <v>0.001702127659574596</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -23191,6 +26155,12 @@
       <c r="N494" s="3" t="n">
         <v>0.001174398120962959</v>
       </c>
+      <c r="O494" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="P494" s="3" t="n">
+        <v>0.00645161290322595</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -23237,6 +26207,12 @@
       <c r="N495" s="2" t="n">
         <v>-0.002526847757422512</v>
       </c>
+      <c r="O495" s="1" t="n">
+        <v>0.04741</v>
+      </c>
+      <c r="P495" s="3" t="n">
+        <v>0.0008444162972345022</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -23283,6 +26259,12 @@
       <c r="N496" s="2" t="n">
         <v>-0.00207039337474126</v>
       </c>
+      <c r="O496" s="1" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="P496" s="3" t="n">
+        <v>0.002074688796680557</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -23329,6 +26311,12 @@
       <c r="N497" s="2" t="n">
         <v>-0.004412354592860107</v>
       </c>
+      <c r="O497" s="1" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="P497" s="3" t="n">
+        <v>0.001208702659145941</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -23375,6 +26363,12 @@
       <c r="N498" s="2" t="n">
         <v>-0.002771042604780128</v>
       </c>
+      <c r="O498" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="P498" s="3" t="n">
+        <v>0.003820771101076728</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -23421,6 +26415,12 @@
       <c r="N499" s="2" t="n">
         <v>-0.003294289897511024</v>
       </c>
+      <c r="O499" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="P499" s="3" t="n">
+        <v>0.002570694087403724</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -23467,6 +26467,12 @@
       <c r="N500" s="2" t="n">
         <v>-0.003745318352059935</v>
       </c>
+      <c r="O500" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="P500" s="3" t="n">
+        <v>0.003759398496240611</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -23513,6 +26519,12 @@
       <c r="N501" s="2" t="n">
         <v>-0.006637168141592842</v>
       </c>
+      <c r="O501" s="1" t="n">
+        <v>0.03592</v>
+      </c>
+      <c r="P501" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -23559,6 +26571,12 @@
       <c r="N502" s="2" t="n">
         <v>-0.001568381430363909</v>
       </c>
+      <c r="O502" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="P502" s="3" t="n">
+        <v>0.001256676091737522</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -23605,6 +26623,12 @@
       <c r="N503" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O503" s="1" t="n">
+        <v>0.007737</v>
+      </c>
+      <c r="P503" s="3" t="n">
+        <v>0.001035062750679285</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -23651,6 +26675,12 @@
       <c r="N504" s="2" t="n">
         <v>-0.0009794319294809382</v>
       </c>
+      <c r="O504" s="1" t="n">
+        <v>3.082</v>
+      </c>
+      <c r="P504" s="3" t="n">
+        <v>0.007189542483660064</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -23697,6 +26727,12 @@
       <c r="N505" s="2" t="n">
         <v>-0.001213755900202249</v>
       </c>
+      <c r="O505" s="1" t="n">
+        <v>0.0007412</v>
+      </c>
+      <c r="P505" s="3" t="n">
+        <v>0.0008101539292465766</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -23743,6 +26779,12 @@
       <c r="N506" s="2" t="n">
         <v>-0.005379959650302591</v>
       </c>
+      <c r="O506" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="P506" s="3" t="n">
+        <v>0.002704530087897118</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -23789,6 +26831,12 @@
       <c r="N507" s="2" t="n">
         <v>-0.0007024938531788779</v>
       </c>
+      <c r="O507" s="1" t="n">
+        <v>0.002852</v>
+      </c>
+      <c r="P507" s="3" t="n">
+        <v>0.002460456942003537</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -23835,6 +26883,12 @@
       <c r="N508" s="2" t="n">
         <v>-0.002518495199118643</v>
       </c>
+      <c r="O508" s="1" t="n">
+        <v>0.06339</v>
+      </c>
+      <c r="P508" s="3" t="n">
+        <v>0.0003156067539846319</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -23881,6 +26935,12 @@
       <c r="N509" s="2" t="n">
         <v>-0.0004452359750667364</v>
       </c>
+      <c r="O509" s="1" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="P509" s="3" t="n">
+        <v>0.001781737193763921</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -23927,6 +26987,12 @@
       <c r="N510" s="2" t="n">
         <v>-0.00410228360453996</v>
       </c>
+      <c r="O510" s="1" t="n">
+        <v>0.0007327</v>
+      </c>
+      <c r="P510" s="3" t="n">
+        <v>0.006041466428669502</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -23973,6 +27039,12 @@
       <c r="N511" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O511" s="1" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="P511" s="3" t="n">
+        <v>0.001811594202898552</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -24019,6 +27091,12 @@
       <c r="N512" s="2" t="n">
         <v>-0.001247920133111398</v>
       </c>
+      <c r="O512" s="1" t="n">
+        <v>0.0004834</v>
+      </c>
+      <c r="P512" s="3" t="n">
+        <v>0.00666389004581418</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -24065,6 +27143,12 @@
       <c r="N513" s="3" t="n">
         <v>0.001268805510241084</v>
       </c>
+      <c r="O513" s="1" t="n">
+        <v>0.05542</v>
+      </c>
+      <c r="P513" s="3" t="n">
+        <v>0.003258508327299052</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -24111,6 +27195,12 @@
       <c r="N514" s="3" t="n">
         <v>0.001319261213720377</v>
       </c>
+      <c r="O514" s="1" t="n">
+        <v>0.03036</v>
+      </c>
+      <c r="P514" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -24157,6 +27247,12 @@
       <c r="N515" s="2" t="n">
         <v>-0.0008756567425568441</v>
       </c>
+      <c r="O515" s="1" t="n">
+        <v>0.001144</v>
+      </c>
+      <c r="P515" s="3" t="n">
+        <v>0.002629272567922844</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -24203,6 +27299,12 @@
       <c r="N516" s="2" t="n">
         <v>-0.0003012048192771484</v>
       </c>
+      <c r="O516" s="1" t="n">
+        <v>0.006629</v>
+      </c>
+      <c r="P516" s="2" t="n">
+        <v>-0.0013558300692979</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -24249,6 +27351,12 @@
       <c r="N517" s="2" t="n">
         <v>-0.001504890895410195</v>
       </c>
+      <c r="O517" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="P517" s="3" t="n">
+        <v>0.001758352172820915</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -24295,6 +27403,12 @@
       <c r="N518" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O518" s="1" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="P518" s="3" t="n">
+        <v>0.001947419668938712</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -24341,6 +27455,12 @@
       <c r="N519" s="2" t="n">
         <v>-0.002275312855517541</v>
       </c>
+      <c r="O519" s="1" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="P519" s="2" t="n">
+        <v>-0.001140250855188095</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -24387,6 +27507,12 @@
       <c r="N520" s="2" t="n">
         <v>-0.004987531172069796</v>
       </c>
+      <c r="O520" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="P520" s="3" t="n">
+        <v>0.003132832080200504</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -24433,6 +27559,12 @@
       <c r="N521" s="3" t="n">
         <v>0.0005577244841048295</v>
       </c>
+      <c r="O521" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="P521" s="2" t="n">
+        <v>-0.003901895206243066</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -24479,6 +27611,12 @@
       <c r="N522" s="2" t="n">
         <v>-0.004239854633555458</v>
       </c>
+      <c r="O522" s="1" t="n">
+        <v>0.01645</v>
+      </c>
+      <c r="P522" s="3" t="n">
+        <v>0.0006082725060827002</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -24525,6 +27663,12 @@
       <c r="N523" s="2" t="n">
         <v>-0.002145922746780987</v>
       </c>
+      <c r="O523" s="1" t="n">
+        <v>0.004183</v>
+      </c>
+      <c r="P523" s="2" t="n">
+        <v>-0.0004778972520908639</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -24571,6 +27715,12 @@
       <c r="N524" s="2" t="n">
         <v>-0.002109704641350247</v>
       </c>
+      <c r="O524" s="1" t="n">
+        <v>0.01426</v>
+      </c>
+      <c r="P524" s="3" t="n">
+        <v>0.004933051444679396</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -24617,6 +27767,12 @@
       <c r="N525" s="2" t="n">
         <v>-0.004008016032064104</v>
       </c>
+      <c r="O525" s="1" t="n">
+        <v>0.02488</v>
+      </c>
+      <c r="P525" s="3" t="n">
+        <v>0.001207243460764538</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -24663,6 +27819,12 @@
       <c r="N526" s="2" t="n">
         <v>-0.001659751037344331</v>
       </c>
+      <c r="O526" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="P526" s="3" t="n">
+        <v>0.001662510390689874</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -24709,6 +27871,12 @@
       <c r="N527" s="2" t="n">
         <v>-0.001813616071428449</v>
       </c>
+      <c r="O527" s="1" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="P527" s="3" t="n">
+        <v>0.0006988120195666595</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -24755,6 +27923,12 @@
       <c r="N528" s="3" t="n">
         <v>0.002084298286243627</v>
       </c>
+      <c r="O528" s="1" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="P528" s="3" t="n">
+        <v>0.002542177027963924</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -24801,6 +27975,12 @@
       <c r="N529" s="2" t="n">
         <v>-0.001427212178877366</v>
       </c>
+      <c r="O529" s="1" t="n">
+        <v>0.06304</v>
+      </c>
+      <c r="P529" s="3" t="n">
+        <v>0.001111640463712889</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -24847,6 +28027,12 @@
       <c r="N530" s="2" t="n">
         <v>-0.002187748607796458</v>
       </c>
+      <c r="O530" s="1" t="n">
+        <v>0.00503</v>
+      </c>
+      <c r="P530" s="3" t="n">
+        <v>0.002591189954155868</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -24893,6 +28079,12 @@
       <c r="N531" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O531" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="P531" s="2" t="n">
+        <v>-0.0007662835249043428</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -24939,6 +28131,12 @@
       <c r="N532" s="2" t="n">
         <v>-0.001498407941562029</v>
       </c>
+      <c r="O532" s="1" t="n">
+        <v>0.05347</v>
+      </c>
+      <c r="P532" s="3" t="n">
+        <v>0.003001313074469958</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -24985,6 +28183,12 @@
       <c r="N533" s="2" t="n">
         <v>-0.008483563096500621</v>
       </c>
+      <c r="O533" s="1" t="n">
+        <v>0.003759</v>
+      </c>
+      <c r="P533" s="3" t="n">
+        <v>0.00508021390374341</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -25031,6 +28235,12 @@
       <c r="N534" s="3" t="n">
         <v>0.0005827505827505186</v>
       </c>
+      <c r="O534" s="1" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="P534" s="3" t="n">
+        <v>0.0005824111822947975</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -25077,6 +28287,12 @@
       <c r="N535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O535" s="1" t="n">
+        <v>1.13e-05</v>
+      </c>
+      <c r="P535" s="3" t="n">
+        <v>0.008928571428571494</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -25123,6 +28339,12 @@
       <c r="N536" s="2" t="n">
         <v>-0.00291088222122712</v>
       </c>
+      <c r="O536" s="1" t="n">
+        <v>0.0004456</v>
+      </c>
+      <c r="P536" s="3" t="n">
+        <v>0.000673703121491146</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -25169,6 +28391,12 @@
       <c r="N537" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="O537" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="P537" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -25215,6 +28443,12 @@
       <c r="N538" s="3" t="n">
         <v>0.0001831501831501121</v>
       </c>
+      <c r="O538" s="1" t="n">
+        <v>0.05475</v>
+      </c>
+      <c r="P538" s="3" t="n">
+        <v>0.002563633034242835</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -25261,6 +28495,12 @@
       <c r="N539" s="2" t="n">
         <v>-0.003508771929824662</v>
       </c>
+      <c r="O539" s="1" t="n">
+        <v>0.6821</v>
+      </c>
+      <c r="P539" s="3" t="n">
+        <v>0.000733568075117453</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -25307,6 +28547,12 @@
       <c r="N540" s="2" t="n">
         <v>-0.003952569169960405</v>
       </c>
+      <c r="O540" s="1" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="P540" s="3" t="n">
+        <v>0.002645502645502721</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -25353,6 +28599,12 @@
       <c r="N541" s="3" t="n">
         <v>0.0007639419404126301</v>
       </c>
+      <c r="O541" s="1" t="n">
+        <v>0.01313</v>
+      </c>
+      <c r="P541" s="3" t="n">
+        <v>0.002290076335877769</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -25399,6 +28651,12 @@
       <c r="N542" s="3" t="n">
         <v>0.01149425287356325</v>
       </c>
+      <c r="O542" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="P542" s="2" t="n">
+        <v>-0.01065340909090915</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -25444,6 +28702,12 @@
       </c>
       <c r="N543" s="2" t="n">
         <v>-0.0008719916288803877</v>
+      </c>
+      <c r="O543" s="1" t="n">
+        <v>0.05732</v>
+      </c>
+      <c r="P543" s="3" t="n">
+        <v>0.0005236515971374105</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R543"/>
+  <dimension ref="A1:T543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,8 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,16 @@
           <t>change_02:00</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>price_02:15</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>change_02:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -595,6 +607,12 @@
       <c r="R2" s="2" t="n">
         <v>-0.002236773812824875</v>
       </c>
+      <c r="S2" s="1" t="n">
+        <v>70155.3</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.000169594910442403</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -653,6 +671,12 @@
       <c r="R3" s="2" t="n">
         <v>-0.003535965124727625</v>
       </c>
+      <c r="S3" s="1" t="n">
+        <v>2055.9</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.0006319268909195641</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -711,6 +735,12 @@
       <c r="R4" s="2" t="n">
         <v>-0.002995046653611394</v>
       </c>
+      <c r="S4" s="1" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.001039861351819797</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,6 +799,12 @@
       <c r="R5" s="3" t="n">
         <v>0.005950720595072042</v>
       </c>
+      <c r="S5" s="1" t="n">
+        <v>0.010492</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>-0.03022460486181726</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -827,6 +863,12 @@
       <c r="R6" s="2" t="n">
         <v>-0.0009414831981460595</v>
       </c>
+      <c r="S6" s="1" t="n">
+        <v>1.3781</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.001014860456687094</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -885,6 +927,12 @@
       <c r="R7" s="2" t="n">
         <v>-0.003065539112050725</v>
       </c>
+      <c r="S7" s="1" t="n">
+        <v>0.09419</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.0012723995334536</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -943,6 +991,12 @@
       <c r="R8" s="3" t="n">
         <v>0.0015673564806205</v>
       </c>
+      <c r="S8" s="1" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.005888281788764557</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1001,6 +1055,12 @@
       <c r="R9" s="2" t="n">
         <v>-0.004857316332726251</v>
       </c>
+      <c r="S9" s="1" t="n">
+        <v>0.04926</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>0.001830384380719947</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1059,6 +1119,12 @@
       <c r="R10" s="3" t="n">
         <v>0.01445523193096012</v>
       </c>
+      <c r="S10" s="1" t="n">
+        <v>18.696</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.005954912803062437</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1117,6 +1183,12 @@
       <c r="R11" s="2" t="n">
         <v>-0.002208351864063758</v>
       </c>
+      <c r="S11" s="1" t="n">
+        <v>651.15</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>0.0007992253661835172</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1175,6 +1247,12 @@
       <c r="R12" s="2" t="n">
         <v>-0.03335557038025353</v>
       </c>
+      <c r="S12" s="1" t="n">
+        <v>0.8754999999999999</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>0.007016333103289619</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1233,6 +1311,12 @@
       <c r="R13" s="2" t="n">
         <v>-0.0004746309744173635</v>
       </c>
+      <c r="S13" s="1" t="n">
+        <v>210.68</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>0.0004273707203571082</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1291,6 +1375,12 @@
       <c r="R14" s="2" t="n">
         <v>-0.003395432692307596</v>
       </c>
+      <c r="S14" s="1" t="n">
+        <v>0.0033199</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.0009648144239756619</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1349,6 +1439,12 @@
       <c r="R15" s="3" t="n">
         <v>0.06762354651162797</v>
       </c>
+      <c r="S15" s="1" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>0.02443756168952712</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1407,6 +1503,12 @@
       <c r="R16" s="2" t="n">
         <v>-0.001230516817063145</v>
       </c>
+      <c r="S16" s="1" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>-0.000616016427104655</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1465,6 +1567,12 @@
       <c r="R17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S17" s="1" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>-0.01067615658362995</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1523,6 +1631,12 @@
       <c r="R18" s="2" t="n">
         <v>-0.005631311956066496</v>
       </c>
+      <c r="S18" s="1" t="n">
+        <v>213.14</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>-0.002433773284657915</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1581,6 +1695,12 @@
       <c r="R19" s="2" t="n">
         <v>-0.001903311762466694</v>
       </c>
+      <c r="S19" s="1" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>-0.0007627765064835163</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1639,6 +1759,12 @@
       <c r="R20" s="3" t="n">
         <v>0.01167083482196033</v>
       </c>
+      <c r="S20" s="1" t="n">
+        <v>0.017035</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0.002648616833431424</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1697,6 +1823,12 @@
       <c r="R21" s="2" t="n">
         <v>-0.001777498954412323</v>
       </c>
+      <c r="S21" s="1" t="n">
+        <v>9.569000000000001</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>0.002304388813239786</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1755,6 +1887,12 @@
       <c r="R22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S22" s="1" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>-0.0005945303210463079</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1813,6 +1951,12 @@
       <c r="R23" s="3" t="n">
         <v>0.00702186810352242</v>
       </c>
+      <c r="S23" s="1" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>0.003301457194899802</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1871,6 +2015,12 @@
       <c r="R24" s="3" t="n">
         <v>0.003464203233256354</v>
       </c>
+      <c r="S24" s="1" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>-0.006904487917146152</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1929,6 +2079,12 @@
       <c r="R25" s="2" t="n">
         <v>-0.001663155560483487</v>
       </c>
+      <c r="S25" s="1" t="n">
+        <v>9.005000000000001</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>0.000111061750333321</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1987,6 +2143,12 @@
       <c r="R26" s="3" t="n">
         <v>0.001495886312640241</v>
       </c>
+      <c r="S26" s="1" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.003734129947722267</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2045,6 +2207,12 @@
       <c r="R27" s="2" t="n">
         <v>-0.001052133405822348</v>
       </c>
+      <c r="S27" s="1" t="n">
+        <v>5109.27</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>0.0002407968614185623</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2103,6 +2271,12 @@
       <c r="R28" s="3" t="n">
         <v>0.0002822466836014366</v>
       </c>
+      <c r="S28" s="1" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>0.004514672686230221</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2161,6 +2335,12 @@
       <c r="R29" s="3" t="n">
         <v>0.001142857142857186</v>
       </c>
+      <c r="S29" s="1" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>-0.003424657534246536</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2219,6 +2399,12 @@
       <c r="R30" s="2" t="n">
         <v>-0.005019975681778614</v>
       </c>
+      <c r="S30" s="1" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>-0.0060753129309894</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2277,6 +2463,12 @@
       <c r="R31" s="2" t="n">
         <v>-0.003807710613993429</v>
       </c>
+      <c r="S31" s="1" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>-0.001433349259436199</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2335,6 +2527,12 @@
       <c r="R32" s="3" t="n">
         <v>0.009657320872274116</v>
       </c>
+      <c r="S32" s="1" t="n">
+        <v>1.2943</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>-0.001619870410367163</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2393,6 +2591,12 @@
       <c r="R33" s="2" t="n">
         <v>-0.003661885871223616</v>
       </c>
+      <c r="S33" s="1" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>0.01470137825421124</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2451,6 +2655,12 @@
       <c r="R34" s="2" t="n">
         <v>-0.00200400801603214</v>
       </c>
+      <c r="S34" s="1" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>-0.001338688085676039</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2509,6 +2719,12 @@
       <c r="R35" s="2" t="n">
         <v>-0.001405913624181809</v>
       </c>
+      <c r="S35" s="1" t="n">
+        <v>454.29</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>-0.000637951515684728</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2567,6 +2783,12 @@
       <c r="R36" s="2" t="n">
         <v>-0.002284053156146158</v>
       </c>
+      <c r="S36" s="1" t="n">
+        <v>0.04784</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>-0.004370447450572358</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2625,6 +2847,12 @@
       <c r="R37" s="2" t="n">
         <v>-0.000565530892125077</v>
       </c>
+      <c r="S37" s="1" t="n">
+        <v>0.7060999999999999</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>-0.001131701796576634</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2683,6 +2911,12 @@
       <c r="R38" s="2" t="n">
         <v>-0.003784295175023629</v>
       </c>
+      <c r="S38" s="1" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>0.002849002849002799</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2741,6 +2975,12 @@
       <c r="R39" s="2" t="n">
         <v>-0.002633251611731518</v>
       </c>
+      <c r="S39" s="1" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>-0.003732702112163115</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2799,6 +3039,12 @@
       <c r="R40" s="3" t="n">
         <v>0.01079330814894759</v>
       </c>
+      <c r="S40" s="1" t="n">
+        <v>0.03789</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>0.01147891083822744</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2857,6 +3103,12 @@
       <c r="R41" s="3" t="n">
         <v>0.002357207615593928</v>
       </c>
+      <c r="S41" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>-0.007235890014471861</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2915,6 +3167,12 @@
       <c r="R42" s="2" t="n">
         <v>-0.002577319587628876</v>
       </c>
+      <c r="S42" s="1" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>-0.001107419712070917</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2973,6 +3231,12 @@
       <c r="R43" s="3" t="n">
         <v>0.002288329519450761</v>
       </c>
+      <c r="S43" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>0.002283105022831221</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3031,6 +3295,12 @@
       <c r="R44" s="2" t="n">
         <v>-0.001356852103120793</v>
       </c>
+      <c r="S44" s="1" t="n">
+        <v>0.005898</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>0.001698369565217322</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3089,6 +3359,12 @@
       <c r="R45" s="2" t="n">
         <v>-0.01127707982985461</v>
       </c>
+      <c r="S45" s="1" t="n">
+        <v>0.10079</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0.0084042021010506</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3147,6 +3423,12 @@
       <c r="R46" s="2" t="n">
         <v>-0.002148227712137568</v>
       </c>
+      <c r="S46" s="1" t="n">
+        <v>2.787</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3205,6 +3487,12 @@
       <c r="R47" s="2" t="n">
         <v>-0.0008988764044943213</v>
       </c>
+      <c r="S47" s="1" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>-0.0004498425551057787</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3263,6 +3551,12 @@
       <c r="R48" s="2" t="n">
         <v>-0.000932835820895549</v>
       </c>
+      <c r="S48" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>-0.003734827264239006</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3321,6 +3615,12 @@
       <c r="R49" s="2" t="n">
         <v>-0.003229452607782961</v>
       </c>
+      <c r="S49" s="1" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>-0.004535882067066296</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3379,6 +3679,12 @@
       <c r="R50" s="2" t="n">
         <v>-0.005482918599746866</v>
       </c>
+      <c r="S50" s="1" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>0.004028837998303704</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3437,6 +3743,12 @@
       <c r="R51" s="2" t="n">
         <v>-0.003836317135549904</v>
       </c>
+      <c r="S51" s="1" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3495,6 +3807,12 @@
       <c r="R52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S52" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3553,6 +3871,12 @@
       <c r="R53" s="2" t="n">
         <v>-0.007177033492822841</v>
       </c>
+      <c r="S53" s="1" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>0.007228915662650475</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3611,6 +3935,12 @@
       <c r="R54" s="3" t="n">
         <v>0.009112709832134254</v>
       </c>
+      <c r="S54" s="1" t="n">
+        <v>0.04199</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>-0.002138783269961972</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3669,6 +3999,12 @@
       <c r="R55" s="2" t="n">
         <v>-0.001691911053818788</v>
       </c>
+      <c r="S55" s="1" t="n">
+        <v>0.12473</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>0.006617706399806209</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3727,6 +4063,12 @@
       <c r="R56" s="2" t="n">
         <v>-0.0009457755359393663</v>
       </c>
+      <c r="S56" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>-0.002840012622278358</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3785,6 +4127,12 @@
       <c r="R57" s="3" t="n">
         <v>0.004325259515570908</v>
       </c>
+      <c r="S57" s="1" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="T57" s="3" t="n">
+        <v>0.004306632213608931</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3843,6 +4191,12 @@
       <c r="R58" s="2" t="n">
         <v>-0.003015075376884508</v>
       </c>
+      <c r="S58" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>-0.002016129032257982</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3901,6 +4255,12 @@
       <c r="R59" s="2" t="n">
         <v>-0.005952380952380968</v>
       </c>
+      <c r="S59" s="1" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>-0.002994011976047912</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3959,6 +4319,12 @@
       <c r="R60" s="2" t="n">
         <v>-0.006455777921239515</v>
       </c>
+      <c r="S60" s="1" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="T60" s="3" t="n">
+        <v>0.001299545159194139</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4017,6 +4383,12 @@
       <c r="R61" s="2" t="n">
         <v>-0.0005641218503195373</v>
       </c>
+      <c r="S61" s="1" t="n">
+        <v>0.15947</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>0.0001254311696456083</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4075,6 +4447,12 @@
       <c r="R62" s="2" t="n">
         <v>-0.007029382820188394</v>
       </c>
+      <c r="S62" s="1" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>0.003822738213223736</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4133,6 +4511,12 @@
       <c r="R63" s="3" t="n">
         <v>0.0003410641200545327</v>
       </c>
+      <c r="S63" s="1" t="n">
+        <v>5.824</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>-0.007159904534606174</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4191,6 +4575,12 @@
       <c r="R64" s="2" t="n">
         <v>-0.00614096301465466</v>
       </c>
+      <c r="S64" s="1" t="n">
+        <v>0.007152</v>
+      </c>
+      <c r="T64" s="3" t="n">
+        <v>0.00435332116275813</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4249,6 +4639,12 @@
       <c r="R65" s="3" t="n">
         <v>0.01345291479820629</v>
       </c>
+      <c r="S65" s="1" t="n">
+        <v>0.03147</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>-0.005372945638432474</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4307,6 +4703,12 @@
       <c r="R66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S66" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>0.004273504273504159</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4365,6 +4767,12 @@
       <c r="R67" s="2" t="n">
         <v>-0.009846153846153855</v>
       </c>
+      <c r="S67" s="1" t="n">
+        <v>1.619</v>
+      </c>
+      <c r="T67" s="3" t="n">
+        <v>0.006215040397762591</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4423,6 +4831,12 @@
       <c r="R68" s="2" t="n">
         <v>-0.001594340092671064</v>
       </c>
+      <c r="S68" s="1" t="n">
+        <v>2.0038</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>-4.990268975486149e-05</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4481,6 +4895,12 @@
       <c r="R69" s="3" t="n">
         <v>0.0005218298834581284</v>
       </c>
+      <c r="S69" s="1" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="T69" s="3" t="n">
+        <v>0.001043115438108369</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4539,6 +4959,12 @@
       <c r="R70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>-0.009523809523809533</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4597,6 +5023,12 @@
       <c r="R71" s="2" t="n">
         <v>-0.001976284584980263</v>
       </c>
+      <c r="S71" s="1" t="n">
+        <v>0.9069</v>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>-0.0023102310231023</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4655,6 +5087,12 @@
       <c r="R72" s="2" t="n">
         <v>-0.002812939521800232</v>
       </c>
+      <c r="S72" s="1" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="T72" s="3" t="n">
+        <v>0.0002350728725904772</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4713,6 +5151,12 @@
       <c r="R73" s="2" t="n">
         <v>-0.003073661897191294</v>
       </c>
+      <c r="S73" s="1" t="n">
+        <v>0.09394</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>-0.001275781416117467</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4771,6 +5215,12 @@
       <c r="R74" s="3" t="n">
         <v>0.002806771335847813</v>
       </c>
+      <c r="S74" s="1" t="n">
+        <v>1.1391</v>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>-0.003673576489110454</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4829,6 +5279,12 @@
       <c r="R75" s="2" t="n">
         <v>-0.003757044458359488</v>
       </c>
+      <c r="S75" s="1" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>0.002514142049025667</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4887,6 +5343,12 @@
       <c r="R76" s="3" t="n">
         <v>0.006648828346712084</v>
       </c>
+      <c r="S76" s="1" t="n">
+        <v>0.12481</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>0.005316149818767683</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4945,6 +5407,12 @@
       <c r="R77" s="2" t="n">
         <v>-0.00341005967604431</v>
       </c>
+      <c r="S77" s="1" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>-0.0008554319931565685</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5003,6 +5471,12 @@
       <c r="R78" s="2" t="n">
         <v>-0.002958579881656889</v>
       </c>
+      <c r="S78" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5061,6 +5535,12 @@
       <c r="R79" s="2" t="n">
         <v>-0.005655355954757181</v>
       </c>
+      <c r="S79" s="1" t="n">
+        <v>0.006014</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>0.006022080963533029</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5119,6 +5599,12 @@
       <c r="R80" s="2" t="n">
         <v>-0.003864854756264777</v>
       </c>
+      <c r="S80" s="1" t="n">
+        <v>0.007946999999999999</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>-0.005381727158948857</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5177,6 +5663,12 @@
       <c r="R81" s="2" t="n">
         <v>-0.001676914477361718</v>
       </c>
+      <c r="S81" s="1" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>0.001679731243001183</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5235,6 +5727,12 @@
       <c r="R82" s="3" t="n">
         <v>0.003722084367245592</v>
       </c>
+      <c r="S82" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>0.004326328800988913</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5293,6 +5791,12 @@
       <c r="R83" s="2" t="n">
         <v>-0.002922908293752394</v>
       </c>
+      <c r="S83" s="1" t="n">
+        <v>8.186</v>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>-0.0001221448638084092</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5351,6 +5855,12 @@
       <c r="R84" s="3" t="n">
         <v>0.0008814079781638347</v>
       </c>
+      <c r="S84" s="1" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>0.002215783194136781</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5409,6 +5919,12 @@
       <c r="R85" s="2" t="n">
         <v>-0.004863813229571997</v>
       </c>
+      <c r="S85" s="1" t="n">
+        <v>0.004079</v>
+      </c>
+      <c r="T85" s="2" t="n">
+        <v>-0.003176930596285433</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5467,6 +5983,12 @@
       <c r="R86" s="2" t="n">
         <v>-0.00203819732769678</v>
       </c>
+      <c r="S86" s="1" t="n">
+        <v>0.13113</v>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>-0.008093797276853368</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5525,6 +6047,12 @@
       <c r="R87" s="3" t="n">
         <v>0.003159557661927384</v>
       </c>
+      <c r="S87" s="1" t="n">
+        <v>0.01876</v>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>-0.015223097112861</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5583,6 +6111,12 @@
       <c r="R88" s="2" t="n">
         <v>-0.003530450132391883</v>
       </c>
+      <c r="S88" s="1" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5641,6 +6175,12 @@
       <c r="R89" s="3" t="n">
         <v>0.00272294077603801</v>
       </c>
+      <c r="S89" s="1" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>-0.001357773251866789</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5699,6 +6239,12 @@
       <c r="R90" s="2" t="n">
         <v>-0.001943256898561992</v>
       </c>
+      <c r="S90" s="1" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>0.0003894080996886468</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5757,6 +6303,12 @@
       <c r="R91" s="3" t="n">
         <v>0.005893909626719127</v>
       </c>
+      <c r="S91" s="1" t="n">
+        <v>0.05634</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>0.0003551136363636219</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5815,6 +6367,12 @@
       <c r="R92" s="2" t="n">
         <v>-0.002147898128260307</v>
       </c>
+      <c r="S92" s="1" t="n">
+        <v>1.3061</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>0.004074415744157505</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5873,6 +6431,12 @@
       <c r="R93" s="2" t="n">
         <v>-0.001744093863960663</v>
       </c>
+      <c r="S93" s="1" t="n">
+        <v>0.06312</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>0.002541296060991002</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5931,6 +6495,12 @@
       <c r="R94" s="2" t="n">
         <v>-0.002265005662514064</v>
       </c>
+      <c r="S94" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="T94" s="3" t="n">
+        <v>0.002270147559591281</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5989,6 +6559,12 @@
       <c r="R95" s="2" t="n">
         <v>-0.002999400119976008</v>
       </c>
+      <c r="S95" s="1" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="T95" s="3" t="n">
+        <v>0.0006016847172082837</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6047,6 +6623,12 @@
       <c r="R96" s="2" t="n">
         <v>-0.00220750551876386</v>
       </c>
+      <c r="S96" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="T96" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6105,6 +6687,12 @@
       <c r="R97" s="2" t="n">
         <v>-0.00152765047357156</v>
       </c>
+      <c r="S97" s="1" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>-0.003977968176254668</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6163,6 +6751,12 @@
       <c r="R98" s="3" t="n">
         <v>0.002724795640327079</v>
       </c>
+      <c r="S98" s="1" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="T98" s="3" t="n">
+        <v>0.00452898550724628</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6221,6 +6815,12 @@
       <c r="R99" s="2" t="n">
         <v>-0.002329450915141322</v>
       </c>
+      <c r="S99" s="1" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="T99" s="3" t="n">
+        <v>0.001667778519012639</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6279,6 +6879,12 @@
       <c r="R100" s="2" t="n">
         <v>-0.005782017924255731</v>
       </c>
+      <c r="S100" s="1" t="n">
+        <v>0.03419</v>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>-0.005815644082582111</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6337,6 +6943,12 @@
       <c r="R101" s="2" t="n">
         <v>-0.001101321585903085</v>
       </c>
+      <c r="S101" s="1" t="n">
+        <v>1.813</v>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>-0.0005512679162073384</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6395,6 +7007,12 @@
       <c r="R102" s="2" t="n">
         <v>-0.01684121143504107</v>
       </c>
+      <c r="S102" s="1" t="n">
+        <v>0.006846</v>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>-0.01453864977688216</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6453,6 +7071,12 @@
       <c r="R103" s="2" t="n">
         <v>-0.004158004158004195</v>
       </c>
+      <c r="S103" s="1" t="n">
+        <v>0.06718</v>
+      </c>
+      <c r="T103" s="3" t="n">
+        <v>0.001789442290486266</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6511,6 +7135,12 @@
       <c r="R104" s="2" t="n">
         <v>-0.0002434274586173052</v>
       </c>
+      <c r="S104" s="1" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6569,6 +7199,12 @@
       <c r="R105" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S105" s="1" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="T105" s="3" t="n">
+        <v>0.0005608524957936691</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6627,6 +7263,12 @@
       <c r="R106" s="2" t="n">
         <v>-0.01250303471716444</v>
       </c>
+      <c r="S106" s="1" t="n">
+        <v>0.008181000000000001</v>
+      </c>
+      <c r="T106" s="3" t="n">
+        <v>0.005654578979717382</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6685,6 +7327,12 @@
       <c r="R107" s="2" t="n">
         <v>-0.002202643171806078</v>
       </c>
+      <c r="S107" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="T107" s="3" t="n">
+        <v>0.001103752759381853</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6743,6 +7391,12 @@
       <c r="R108" s="2" t="n">
         <v>-0.003747072599531625</v>
       </c>
+      <c r="S108" s="1" t="n">
+        <v>0.02155</v>
+      </c>
+      <c r="T108" s="3" t="n">
+        <v>0.01316408086506812</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6801,6 +7455,12 @@
       <c r="R109" s="2" t="n">
         <v>-0.01027822080453667</v>
       </c>
+      <c r="S109" s="1" t="n">
+        <v>0.05554</v>
+      </c>
+      <c r="T109" s="2" t="n">
+        <v>-0.005550581915845977</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6859,6 +7519,12 @@
       <c r="R110" s="2" t="n">
         <v>-0.002834077636550987</v>
       </c>
+      <c r="S110" s="1" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="T110" s="3" t="n">
+        <v>0.004220136077857122</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6917,6 +7583,12 @@
       <c r="R111" s="2" t="n">
         <v>-0.001219760113844228</v>
       </c>
+      <c r="S111" s="1" t="n">
+        <v>0.09797</v>
+      </c>
+      <c r="T111" s="2" t="n">
+        <v>-0.002951353551801329</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6975,6 +7647,12 @@
       <c r="R112" s="2" t="n">
         <v>-0.005390835579514792</v>
       </c>
+      <c r="S112" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="T112" s="3" t="n">
+        <v>0.002710027100270892</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7033,6 +7711,12 @@
       <c r="R113" s="2" t="n">
         <v>-0.002240097749720108</v>
       </c>
+      <c r="S113" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="T113" s="3" t="n">
+        <v>0.0001020512297174202</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7091,6 +7775,12 @@
       <c r="R114" s="2" t="n">
         <v>-0.02546689303904918</v>
       </c>
+      <c r="S114" s="1" t="n">
+        <v>0.001716</v>
+      </c>
+      <c r="T114" s="2" t="n">
+        <v>-0.003484320557491248</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7149,6 +7839,12 @@
       <c r="R115" s="2" t="n">
         <v>-0.001991714467814028</v>
       </c>
+      <c r="S115" s="1" t="n">
+        <v>1.2562</v>
+      </c>
+      <c r="T115" s="3" t="n">
+        <v>0.002793965035523317</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7207,6 +7903,12 @@
       <c r="R116" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S116" s="1" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="T116" s="3" t="n">
+        <v>0.002963590177815437</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7265,6 +7967,12 @@
       <c r="R117" s="3" t="n">
         <v>0.004111842105263161</v>
       </c>
+      <c r="S117" s="1" t="n">
+        <v>0.06132</v>
+      </c>
+      <c r="T117" s="3" t="n">
+        <v>0.004422604422604413</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7323,6 +8031,12 @@
       <c r="R118" s="2" t="n">
         <v>-0.001595987232102157</v>
       </c>
+      <c r="S118" s="1" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="T118" s="3" t="n">
+        <v>0.006165791276547143</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7381,6 +8095,12 @@
       <c r="R119" s="2" t="n">
         <v>-0.0002684563758389618</v>
       </c>
+      <c r="S119" s="1" t="n">
+        <v>0.003721</v>
+      </c>
+      <c r="T119" s="2" t="n">
+        <v>-0.000805585392051548</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7439,6 +8159,12 @@
       <c r="R120" s="3" t="n">
         <v>0.003826530612244901</v>
       </c>
+      <c r="S120" s="1" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="T120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7497,6 +8223,12 @@
       <c r="R121" s="2" t="n">
         <v>-0.004026845637583822</v>
       </c>
+      <c r="S121" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>-0.0006738544474394659</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7555,6 +8287,12 @@
       <c r="R122" s="2" t="n">
         <v>-0.002104155707522319</v>
       </c>
+      <c r="S122" s="1" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>-0.001932876471622036</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7613,6 +8351,12 @@
       <c r="R123" s="3" t="n">
         <v>0.00438278634779315</v>
       </c>
+      <c r="S123" s="1" t="n">
+        <v>0.029009</v>
+      </c>
+      <c r="T123" s="2" t="n">
+        <v>-0.003264156129741662</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7671,6 +8415,12 @@
       <c r="R124" s="2" t="n">
         <v>-0.001407729715894535</v>
       </c>
+      <c r="S124" s="1" t="n">
+        <v>0.07797999999999999</v>
+      </c>
+      <c r="T124" s="2" t="n">
+        <v>-0.0006407791874920975</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7729,6 +8479,12 @@
       <c r="R125" s="2" t="n">
         <v>-0.003020853634769097</v>
       </c>
+      <c r="S125" s="1" t="n">
+        <v>0.10354</v>
+      </c>
+      <c r="T125" s="3" t="n">
+        <v>0.01202228521161172</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7787,6 +8543,12 @@
       <c r="R126" s="2" t="n">
         <v>-0.003735524841240172</v>
       </c>
+      <c r="S126" s="1" t="n">
+        <v>0.02661</v>
+      </c>
+      <c r="T126" s="2" t="n">
+        <v>-0.002249718785151764</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7845,6 +8607,12 @@
       <c r="R127" s="3" t="n">
         <v>0.001825650387950792</v>
       </c>
+      <c r="S127" s="1" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="T127" s="3" t="n">
+        <v>0.001822323462414504</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7903,6 +8671,12 @@
       <c r="R128" s="2" t="n">
         <v>-0.003082614056720101</v>
       </c>
+      <c r="S128" s="1" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="T128" s="3" t="n">
+        <v>0.001855287569573251</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7961,6 +8735,12 @@
       <c r="R129" s="2" t="n">
         <v>-0.03020110714035462</v>
       </c>
+      <c r="S129" s="1" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="T129" s="3" t="n">
+        <v>0.01878612716763</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8019,6 +8799,12 @@
       <c r="R130" s="3" t="n">
         <v>0.01287828792306973</v>
       </c>
+      <c r="S130" s="1" t="n">
+        <v>0.053322</v>
+      </c>
+      <c r="T130" s="2" t="n">
+        <v>-0.007371830671283378</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8077,6 +8863,12 @@
       <c r="R131" s="2" t="n">
         <v>-0.002197533878647291</v>
       </c>
+      <c r="S131" s="1" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="T131" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8135,6 +8927,12 @@
       <c r="R132" s="2" t="n">
         <v>-0.00570776255707763</v>
       </c>
+      <c r="S132" s="1" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="T132" s="3" t="n">
+        <v>0.002296211251435198</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8193,6 +8991,12 @@
       <c r="R133" s="2" t="n">
         <v>-0.005172413793103453</v>
       </c>
+      <c r="S133" s="1" t="n">
+        <v>0.5783</v>
+      </c>
+      <c r="T133" s="3" t="n">
+        <v>0.002253032928942945</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8251,6 +9055,12 @@
       <c r="R134" s="2" t="n">
         <v>-0.005982053838484534</v>
       </c>
+      <c r="S134" s="1" t="n">
+        <v>0.02981</v>
+      </c>
+      <c r="T134" s="2" t="n">
+        <v>-0.003343363423604126</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8309,6 +9119,12 @@
       <c r="R135" s="3" t="n">
         <v>0.001140901312036462</v>
       </c>
+      <c r="S135" s="1" t="n">
+        <v>0.01762</v>
+      </c>
+      <c r="T135" s="3" t="n">
+        <v>0.003988603988604024</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8367,6 +9183,12 @@
       <c r="R136" s="3" t="n">
         <v>0.0002688172043011576</v>
       </c>
+      <c r="S136" s="1" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="T136" s="3" t="n">
+        <v>0.00241870464928782</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8425,6 +9247,12 @@
       <c r="R137" s="2" t="n">
         <v>-0.006607929515418488</v>
       </c>
+      <c r="S137" s="1" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="T137" s="3" t="n">
+        <v>0.001478196600147759</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8483,6 +9311,12 @@
       <c r="R138" s="2" t="n">
         <v>-0.007898894154818332</v>
       </c>
+      <c r="S138" s="1" t="n">
+        <v>2.518</v>
+      </c>
+      <c r="T138" s="3" t="n">
+        <v>0.002388535031847047</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8541,6 +9375,12 @@
       <c r="R139" s="2" t="n">
         <v>-0.003372681281618896</v>
       </c>
+      <c r="S139" s="1" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="T139" s="2" t="n">
+        <v>-0.0008460236886633949</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8599,6 +9439,12 @@
       <c r="R140" s="2" t="n">
         <v>-0.002661343978709255</v>
       </c>
+      <c r="S140" s="1" t="n">
+        <v>0.01495</v>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>-0.002668445630420287</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8657,6 +9503,12 @@
       <c r="R141" s="2" t="n">
         <v>-0.003273221343873569</v>
       </c>
+      <c r="S141" s="1" t="n">
+        <v>16.108</v>
+      </c>
+      <c r="T141" s="2" t="n">
+        <v>-0.001920812937604486</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8715,6 +9567,12 @@
       <c r="R142" s="2" t="n">
         <v>-0.005608974358974408</v>
       </c>
+      <c r="S142" s="1" t="n">
+        <v>0.01244</v>
+      </c>
+      <c r="T142" s="3" t="n">
+        <v>0.002417405318291742</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8773,6 +9631,12 @@
       <c r="R143" s="3" t="n">
         <v>0.00453001132502839</v>
       </c>
+      <c r="S143" s="1" t="n">
+        <v>0.02668</v>
+      </c>
+      <c r="T143" s="3" t="n">
+        <v>0.002630590003757878</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8831,6 +9695,12 @@
       <c r="R144" s="3" t="n">
         <v>0.008835873647006871</v>
       </c>
+      <c r="S144" s="1" t="n">
+        <v>0.004765</v>
+      </c>
+      <c r="T144" s="3" t="n">
+        <v>0.04335449967155688</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8889,6 +9759,12 @@
       <c r="R145" s="2" t="n">
         <v>-0.007586485939712788</v>
       </c>
+      <c r="S145" s="1" t="n">
+        <v>1.9685</v>
+      </c>
+      <c r="T145" s="3" t="n">
+        <v>0.003210681887677083</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8947,6 +9823,12 @@
       <c r="R146" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S146" s="1" t="n">
+        <v>0.02305</v>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>-0.001299826689774644</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9005,6 +9887,12 @@
       <c r="R147" s="3" t="n">
         <v>0.0003352329869259386</v>
       </c>
+      <c r="S147" s="1" t="n">
+        <v>0.08985</v>
+      </c>
+      <c r="T147" s="3" t="n">
+        <v>0.003686327077747955</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9063,6 +9951,12 @@
       <c r="R148" s="3" t="n">
         <v>0.01552142279708977</v>
       </c>
+      <c r="S148" s="1" t="n">
+        <v>0.06297</v>
+      </c>
+      <c r="T148" s="3" t="n">
+        <v>0.002547365069256384</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9121,6 +10015,12 @@
       <c r="R149" s="2" t="n">
         <v>-0.001513368084748609</v>
       </c>
+      <c r="S149" s="1" t="n">
+        <v>0.05947</v>
+      </c>
+      <c r="T149" s="3" t="n">
+        <v>0.001515661839003028</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9179,6 +10079,12 @@
       <c r="R150" s="3" t="n">
         <v>0.001220008133387534</v>
       </c>
+      <c r="S150" s="1" t="n">
+        <v>0.24586</v>
+      </c>
+      <c r="T150" s="2" t="n">
+        <v>-0.001380991064175495</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9237,6 +10143,12 @@
       <c r="R151" s="2" t="n">
         <v>-0.01083032490974736</v>
       </c>
+      <c r="S151" s="1" t="n">
+        <v>6.907e-05</v>
+      </c>
+      <c r="T151" s="3" t="n">
+        <v>0.008321167883211723</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9295,6 +10207,12 @@
       <c r="R152" s="3" t="n">
         <v>0.003834874802616691</v>
       </c>
+      <c r="S152" s="1" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="T152" s="3" t="n">
+        <v>0.0002247191011235707</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9353,6 +10271,12 @@
       <c r="R153" s="2" t="n">
         <v>-0.001635055591890126</v>
       </c>
+      <c r="S153" s="1" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="T153" s="3" t="n">
+        <v>0.001637733377006225</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9411,6 +10335,12 @@
       <c r="R154" s="2" t="n">
         <v>-0.003573391973611939</v>
       </c>
+      <c r="S154" s="1" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>-0.008827586206896498</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9469,6 +10399,12 @@
       <c r="R155" s="2" t="n">
         <v>-0.003027681660899561</v>
       </c>
+      <c r="S155" s="1" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="T155" s="3" t="n">
+        <v>0.003470715835140977</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9527,6 +10463,12 @@
       <c r="R156" s="3" t="n">
         <v>0.01149425287356327</v>
       </c>
+      <c r="S156" s="1" t="n">
+        <v>0.08086</v>
+      </c>
+      <c r="T156" s="2" t="n">
+        <v>-0.001235177865612684</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9585,6 +10527,12 @@
       <c r="R157" s="3" t="n">
         <v>0.003061046003148531</v>
       </c>
+      <c r="S157" s="1" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="T157" s="2" t="n">
+        <v>-0.00714970790827449</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9643,6 +10591,12 @@
       <c r="R158" s="2" t="n">
         <v>-0.002803364036844238</v>
       </c>
+      <c r="S158" s="1" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="T158" s="3" t="n">
+        <v>0.005622489959839407</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9701,6 +10655,12 @@
       <c r="R159" s="3" t="n">
         <v>0.00204918032786893</v>
       </c>
+      <c r="S159" s="1" t="n">
+        <v>2.927</v>
+      </c>
+      <c r="T159" s="2" t="n">
+        <v>-0.002385821404226352</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9759,6 +10719,12 @@
       <c r="R160" s="2" t="n">
         <v>-0.001996007984031855</v>
       </c>
+      <c r="S160" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="T160" s="2" t="n">
+        <v>-0.001000000000000029</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9817,6 +10783,12 @@
       <c r="R161" s="2" t="n">
         <v>-0.002669769989047108</v>
       </c>
+      <c r="S161" s="1" t="n">
+        <v>0.14566</v>
+      </c>
+      <c r="T161" s="2" t="n">
+        <v>-0.0002059166723863992</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9875,6 +10847,12 @@
       <c r="R162" s="2" t="n">
         <v>-0.003353658536585282</v>
       </c>
+      <c r="S162" s="1" t="n">
+        <v>0.003281</v>
+      </c>
+      <c r="T162" s="3" t="n">
+        <v>0.003670847353930822</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9933,6 +10911,12 @@
       <c r="R163" s="3" t="n">
         <v>0.0008014425966741196</v>
       </c>
+      <c r="S163" s="1" t="n">
+        <v>0.004978</v>
+      </c>
+      <c r="T163" s="2" t="n">
+        <v>-0.003403403403403508</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9991,6 +10975,12 @@
       <c r="R164" s="2" t="n">
         <v>-0.005230125523012556</v>
       </c>
+      <c r="S164" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="T164" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10049,6 +11039,12 @@
       <c r="R165" s="2" t="n">
         <v>-0.005198180636777096</v>
       </c>
+      <c r="S165" s="1" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="T165" s="3" t="n">
+        <v>0.0006531678641410123</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10107,6 +11103,12 @@
       <c r="R166" s="2" t="n">
         <v>-0.002295058452270022</v>
       </c>
+      <c r="S166" s="1" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T166" s="2" t="n">
+        <v>-0.0007907411401050254</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10165,6 +11167,12 @@
       <c r="R167" s="2" t="n">
         <v>-0.0007222824124231779</v>
       </c>
+      <c r="S167" s="1" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="T167" s="3" t="n">
+        <v>0.001084206722081758</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10223,6 +11231,12 @@
       <c r="R168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S168" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="T168" s="2" t="n">
+        <v>-0.003205128205128208</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10281,6 +11295,12 @@
       <c r="R169" s="2" t="n">
         <v>-0.006354515050167197</v>
       </c>
+      <c r="S169" s="1" t="n">
+        <v>0.02987</v>
+      </c>
+      <c r="T169" s="3" t="n">
+        <v>0.005385392123864033</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10339,6 +11359,12 @@
       <c r="R170" s="2" t="n">
         <v>-0.005267979844250896</v>
       </c>
+      <c r="S170" s="1" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="T170" s="3" t="n">
+        <v>0.0002302555836978154</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10397,6 +11423,12 @@
       <c r="R171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="T171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10455,6 +11487,12 @@
       <c r="R172" s="2" t="n">
         <v>-0.007462686567164234</v>
       </c>
+      <c r="S172" s="1" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>-0.02255639097744365</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10513,6 +11551,12 @@
       <c r="R173" s="2" t="n">
         <v>-0.0009478672985781604</v>
       </c>
+      <c r="S173" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="T173" s="3" t="n">
+        <v>0.001423149905123282</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10571,6 +11615,12 @@
       <c r="R174" s="2" t="n">
         <v>-0.004210992907801477</v>
       </c>
+      <c r="S174" s="1" t="n">
+        <v>0.09014</v>
+      </c>
+      <c r="T174" s="3" t="n">
+        <v>0.003115958157133346</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10629,6 +11679,12 @@
       <c r="R175" s="2" t="n">
         <v>-0.0002763957987838281</v>
       </c>
+      <c r="S175" s="1" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="T175" s="3" t="n">
+        <v>0.004976499861763805</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10687,6 +11743,12 @@
       <c r="R176" s="2" t="n">
         <v>-0.001863932898415581</v>
       </c>
+      <c r="S176" s="1" t="n">
+        <v>0.02147</v>
+      </c>
+      <c r="T176" s="3" t="n">
+        <v>0.002334267040149298</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10745,6 +11807,12 @@
       <c r="R177" s="2" t="n">
         <v>-0.002531645569620369</v>
       </c>
+      <c r="S177" s="1" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="T177" s="2" t="n">
+        <v>-0.003807106598984837</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10803,6 +11871,12 @@
       <c r="R178" s="2" t="n">
         <v>-0.01026694045174541</v>
       </c>
+      <c r="S178" s="1" t="n">
+        <v>0.000964</v>
+      </c>
+      <c r="T178" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10861,6 +11935,12 @@
       <c r="R179" s="2" t="n">
         <v>-0.004322766570605117</v>
       </c>
+      <c r="S179" s="1" t="n">
+        <v>0.022808</v>
+      </c>
+      <c r="T179" s="3" t="n">
+        <v>0.0002192693943778477</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10919,6 +11999,12 @@
       <c r="R180" s="2" t="n">
         <v>-0.01498929336188451</v>
       </c>
+      <c r="S180" s="1" t="n">
+        <v>4.115</v>
+      </c>
+      <c r="T180" s="2" t="n">
+        <v>-0.006038647342995041</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10977,6 +12063,12 @@
       <c r="R181" s="2" t="n">
         <v>-0.01607387140902867</v>
       </c>
+      <c r="S181" s="1" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="T181" s="3" t="n">
+        <v>0.001737921445950645</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11035,6 +12127,12 @@
       <c r="R182" s="2" t="n">
         <v>-0.005769996020692372</v>
       </c>
+      <c r="S182" s="1" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="T182" s="3" t="n">
+        <v>0.003602161296778059</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11093,6 +12191,12 @@
       <c r="R183" s="2" t="n">
         <v>-0.001642036124794646</v>
       </c>
+      <c r="S183" s="1" t="n">
+        <v>5.477</v>
+      </c>
+      <c r="T183" s="3" t="n">
+        <v>0.00091374269005846</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11151,6 +12255,12 @@
       <c r="R184" s="3" t="n">
         <v>0.001743983257760626</v>
       </c>
+      <c r="S184" s="1" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T184" s="2" t="n">
+        <v>-0.0006963788300835506</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11209,6 +12319,12 @@
       <c r="R185" s="3" t="n">
         <v>0.0005356186395286338</v>
       </c>
+      <c r="S185" s="1" t="n">
+        <v>0.01872</v>
+      </c>
+      <c r="T185" s="3" t="n">
+        <v>0.002141327623126437</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11267,6 +12383,12 @@
       <c r="R186" s="2" t="n">
         <v>-0.003174603174603252</v>
       </c>
+      <c r="S186" s="1" t="n">
+        <v>3.13e-05</v>
+      </c>
+      <c r="T186" s="2" t="n">
+        <v>-0.00318471337579604</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11325,6 +12447,12 @@
       <c r="R187" s="2" t="n">
         <v>-0.001248439450686591</v>
       </c>
+      <c r="S187" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="T187" s="2" t="n">
+        <v>-0.005000000000000013</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11383,6 +12511,12 @@
       <c r="R188" s="2" t="n">
         <v>-0.002469135802469206</v>
       </c>
+      <c r="S188" s="1" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="T188" s="2" t="n">
+        <v>-0.0004950495049504749</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11441,6 +12575,12 @@
       <c r="R189" s="2" t="n">
         <v>-0.007906031172351549</v>
       </c>
+      <c r="S189" s="1" t="n">
+        <v>0.0004408</v>
+      </c>
+      <c r="T189" s="3" t="n">
+        <v>0.003642987249544592</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11499,6 +12639,12 @@
       <c r="R190" s="3" t="n">
         <v>0.002145002145002058</v>
       </c>
+      <c r="S190" s="1" t="n">
+        <v>0.02348</v>
+      </c>
+      <c r="T190" s="3" t="n">
+        <v>0.005136986301369951</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11557,6 +12703,12 @@
       <c r="R191" s="3" t="n">
         <v>0.001903553299492308</v>
       </c>
+      <c r="S191" s="1" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="T191" s="3" t="n">
+        <v>0.0006333122229260964</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11615,6 +12767,12 @@
       <c r="R192" s="3" t="n">
         <v>0.002315639472746672</v>
       </c>
+      <c r="S192" s="1" t="n">
+        <v>0.05633</v>
+      </c>
+      <c r="T192" s="3" t="n">
+        <v>0.001066287542207172</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11673,6 +12831,12 @@
       <c r="R193" s="2" t="n">
         <v>-0.002133333333333395</v>
       </c>
+      <c r="S193" s="1" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="T193" s="3" t="n">
+        <v>0.0005344735435596833</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11731,6 +12895,12 @@
       <c r="R194" s="2" t="n">
         <v>-0.003124999999999873</v>
       </c>
+      <c r="S194" s="1" t="n">
+        <v>0.01917</v>
+      </c>
+      <c r="T194" s="3" t="n">
+        <v>0.001567398119122193</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11789,6 +12959,12 @@
       <c r="R195" s="2" t="n">
         <v>-0.005580097651708807</v>
       </c>
+      <c r="S195" s="1" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="T195" s="3" t="n">
+        <v>0.003039513677811475</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11847,6 +13023,12 @@
       <c r="R196" s="2" t="n">
         <v>-0.001602564102564037</v>
       </c>
+      <c r="S196" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="T196" s="2" t="n">
+        <v>-0.004012841091492892</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11905,6 +13087,12 @@
       <c r="R197" s="2" t="n">
         <v>-0.006465517241379197</v>
       </c>
+      <c r="S197" s="1" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="T197" s="3" t="n">
+        <v>0.005422993492407813</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11963,6 +13151,12 @@
       <c r="R198" s="2" t="n">
         <v>-0.003718199608610593</v>
       </c>
+      <c r="S198" s="1" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="T198" s="2" t="n">
+        <v>-0.0001964250638381241</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12021,6 +13215,12 @@
       <c r="R199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="T199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12079,6 +13279,12 @@
       <c r="R200" s="3" t="n">
         <v>0.006048387096774184</v>
       </c>
+      <c r="S200" s="1" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="T200" s="2" t="n">
+        <v>-0.00200400801603214</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12137,6 +13343,12 @@
       <c r="R201" s="3" t="n">
         <v>0.00298297947008241</v>
       </c>
+      <c r="S201" s="1" t="n">
+        <v>0.005717</v>
+      </c>
+      <c r="T201" s="3" t="n">
+        <v>0.0001749475157452996</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12195,6 +13407,12 @@
       <c r="R202" s="2" t="n">
         <v>-0.003922921067379288</v>
       </c>
+      <c r="S202" s="1" t="n">
+        <v>0.023218</v>
+      </c>
+      <c r="T202" s="3" t="n">
+        <v>0.004847225828788952</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12253,6 +13471,12 @@
       <c r="R203" s="3" t="n">
         <v>0.003636363636363614</v>
       </c>
+      <c r="S203" s="1" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="T203" s="2" t="n">
+        <v>-0.01086956521739124</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12311,6 +13535,12 @@
       <c r="R204" s="2" t="n">
         <v>-0.007924860581156629</v>
       </c>
+      <c r="S204" s="1" t="n">
+        <v>0.03372</v>
+      </c>
+      <c r="T204" s="2" t="n">
+        <v>-0.002366863905325348</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12369,6 +13599,12 @@
       <c r="R205" s="2" t="n">
         <v>-0.00142213794738095</v>
       </c>
+      <c r="S205" s="1" t="n">
+        <v>4.233</v>
+      </c>
+      <c r="T205" s="3" t="n">
+        <v>0.00474721101352945</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12427,6 +13663,12 @@
       <c r="R206" s="2" t="n">
         <v>-0.002762430939226522</v>
       </c>
+      <c r="S206" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="T206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12485,6 +13727,12 @@
       <c r="R207" s="2" t="n">
         <v>-0.02639656230816445</v>
       </c>
+      <c r="S207" s="1" t="n">
+        <v>0.0011386</v>
+      </c>
+      <c r="T207" s="3" t="n">
+        <v>0.02558097640064857</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12543,6 +13791,12 @@
       <c r="R208" s="3" t="n">
         <v>0.0006859651529702011</v>
       </c>
+      <c r="S208" s="1" t="n">
+        <v>0.007271</v>
+      </c>
+      <c r="T208" s="2" t="n">
+        <v>-0.003153276665752735</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12601,6 +13855,12 @@
       <c r="R209" s="2" t="n">
         <v>-0.001666666666666599</v>
       </c>
+      <c r="S209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="T209" s="2" t="n">
+        <v>-0.001669449081803053</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12659,6 +13919,12 @@
       <c r="R210" s="2" t="n">
         <v>-0.0007710100231304297</v>
       </c>
+      <c r="S210" s="1" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="T210" s="3" t="n">
+        <v>0.001543209876543254</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12717,6 +13983,12 @@
       <c r="R211" s="2" t="n">
         <v>-0.002386299831555379</v>
       </c>
+      <c r="S211" s="1" t="n">
+        <v>0.007113</v>
+      </c>
+      <c r="T211" s="3" t="n">
+        <v>0.0008442380751373008</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12775,6 +14047,12 @@
       <c r="R212" s="3" t="n">
         <v>0.02262598560164551</v>
       </c>
+      <c r="S212" s="1" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="T212" s="3" t="n">
+        <v>0.009386523633925475</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12833,6 +14111,12 @@
       <c r="R213" s="2" t="n">
         <v>-0.006175017642907605</v>
       </c>
+      <c r="S213" s="1" t="n">
+        <v>0.05662</v>
+      </c>
+      <c r="T213" s="3" t="n">
+        <v>0.005148233623291294</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12891,6 +14175,12 @@
       <c r="R214" s="2" t="n">
         <v>-0.001590668080593821</v>
       </c>
+      <c r="S214" s="1" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="T214" s="3" t="n">
+        <v>0.003186404673393612</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12949,6 +14239,12 @@
       <c r="R215" s="2" t="n">
         <v>-0.002471952842745735</v>
       </c>
+      <c r="S215" s="1" t="n">
+        <v>0.05267</v>
+      </c>
+      <c r="T215" s="3" t="n">
+        <v>0.004003049942813607</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13007,6 +14303,12 @@
       <c r="R216" s="2" t="n">
         <v>-0.001915708812260583</v>
       </c>
+      <c r="S216" s="1" t="n">
+        <v>0.002082</v>
+      </c>
+      <c r="T216" s="2" t="n">
+        <v>-0.0009596928982724721</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13065,6 +14367,12 @@
       <c r="R217" s="2" t="n">
         <v>-0.00298755186722003</v>
       </c>
+      <c r="S217" s="1" t="n">
+        <v>6.003</v>
+      </c>
+      <c r="T217" s="2" t="n">
+        <v>-0.0006658897952388147</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13123,6 +14431,12 @@
       <c r="R218" s="2" t="n">
         <v>-0.002259887005649669</v>
       </c>
+      <c r="S218" s="1" t="n">
+        <v>4.379</v>
+      </c>
+      <c r="T218" s="2" t="n">
+        <v>-0.008154020385051071</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13181,6 +14495,12 @@
       <c r="R219" s="3" t="n">
         <v>0.001489203276247244</v>
       </c>
+      <c r="S219" s="1" t="n">
+        <v>0.005354</v>
+      </c>
+      <c r="T219" s="2" t="n">
+        <v>-0.004832713754646836</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13239,6 +14559,12 @@
       <c r="R220" s="2" t="n">
         <v>-0.0004852013585637842</v>
       </c>
+      <c r="S220" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="T220" s="3" t="n">
+        <v>0.002669902912621334</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13297,6 +14623,12 @@
       <c r="R221" s="2" t="n">
         <v>-0.003618194348725049</v>
       </c>
+      <c r="S221" s="1" t="n">
+        <v>0.005762</v>
+      </c>
+      <c r="T221" s="2" t="n">
+        <v>-0.003631333218052946</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13355,6 +14687,12 @@
       <c r="R222" s="2" t="n">
         <v>-0.003300330033003242</v>
       </c>
+      <c r="S222" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="T222" s="3" t="n">
+        <v>0.00110375275938193</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13413,6 +14751,12 @@
       <c r="R223" s="2" t="n">
         <v>-0.002375296912113918</v>
       </c>
+      <c r="S223" s="1" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="T223" s="2" t="n">
+        <v>-0.004761904761904898</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13471,6 +14815,12 @@
       <c r="R224" s="2" t="n">
         <v>-0.002308935580697301</v>
       </c>
+      <c r="S224" s="1" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="T224" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13529,6 +14879,12 @@
       <c r="R225" s="3" t="n">
         <v>0.001196172248803862</v>
       </c>
+      <c r="S225" s="1" t="n">
+        <v>0.08347</v>
+      </c>
+      <c r="T225" s="2" t="n">
+        <v>-0.002747909199522032</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13587,6 +14943,12 @@
       <c r="R226" s="3" t="n">
         <v>0.001063829787233999</v>
       </c>
+      <c r="S226" s="1" t="n">
+        <v>0.01887</v>
+      </c>
+      <c r="T226" s="3" t="n">
+        <v>0.002656748140276378</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13645,6 +15007,12 @@
       <c r="R227" s="2" t="n">
         <v>-0.003842049092849511</v>
       </c>
+      <c r="S227" s="1" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="T227" s="3" t="n">
+        <v>0.001499892864795236</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13703,6 +15071,12 @@
       <c r="R228" s="2" t="n">
         <v>-0.00386431945040804</v>
       </c>
+      <c r="S228" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="T228" s="2" t="n">
+        <v>-0.005603448275861991</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13761,6 +15135,12 @@
       <c r="R229" s="2" t="n">
         <v>-0.001855287569573337</v>
       </c>
+      <c r="S229" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="T229" s="3" t="n">
+        <v>0.001858736059479607</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13819,6 +15199,12 @@
       <c r="R230" s="2" t="n">
         <v>-0.005385996409335798</v>
       </c>
+      <c r="S230" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="T230" s="2" t="n">
+        <v>-0.001203369434416233</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13877,6 +15263,12 @@
       <c r="R231" s="2" t="n">
         <v>-0.001963350785340347</v>
       </c>
+      <c r="S231" s="1" t="n">
+        <v>0.03055</v>
+      </c>
+      <c r="T231" s="3" t="n">
+        <v>0.001639344262295129</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13935,6 +15327,12 @@
       <c r="R232" s="2" t="n">
         <v>-0.005242463958060378</v>
       </c>
+      <c r="S232" s="1" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="T232" s="2" t="n">
+        <v>-0.003074220465524688</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13993,6 +15391,12 @@
       <c r="R233" s="2" t="n">
         <v>-0.002083680613435575</v>
       </c>
+      <c r="S233" s="1" t="n">
+        <v>0.11557</v>
+      </c>
+      <c r="T233" s="2" t="n">
+        <v>-0.03474484256243211</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14051,6 +15455,12 @@
       <c r="R234" s="2" t="n">
         <v>-0.003544702638834233</v>
       </c>
+      <c r="S234" s="1" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="T234" s="3" t="n">
+        <v>0.002371541501976243</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14109,6 +15519,12 @@
       <c r="R235" s="3" t="n">
         <v>0.001301142113633175</v>
       </c>
+      <c r="S235" s="1" t="n">
+        <v>0.06927</v>
+      </c>
+      <c r="T235" s="3" t="n">
+        <v>0.0001443834825295426</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14167,6 +15583,12 @@
       <c r="R236" s="2" t="n">
         <v>-7.965588657009718e-05</v>
       </c>
+      <c r="S236" s="1" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="T236" s="2" t="n">
+        <v>-0.001832231339122186</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14225,6 +15647,12 @@
       <c r="R237" s="2" t="n">
         <v>-0.002313030069390897</v>
       </c>
+      <c r="S237" s="1" t="n">
+        <v>0.03901</v>
+      </c>
+      <c r="T237" s="3" t="n">
+        <v>0.004894384337970187</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14283,6 +15711,12 @@
       <c r="R238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="T238" s="2" t="n">
+        <v>-0.008333333333333342</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14341,6 +15775,12 @@
       <c r="R239" s="2" t="n">
         <v>-0.006466053220591888</v>
       </c>
+      <c r="S239" s="1" t="n">
+        <v>0.00398</v>
+      </c>
+      <c r="T239" s="2" t="n">
+        <v>-0.00375469336670845</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14399,6 +15839,12 @@
       <c r="R240" s="2" t="n">
         <v>-0.002911208151382831</v>
       </c>
+      <c r="S240" s="1" t="n">
+        <v>0.01367</v>
+      </c>
+      <c r="T240" s="2" t="n">
+        <v>-0.002189781021897848</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14457,6 +15903,12 @@
       <c r="R241" s="3" t="n">
         <v>0.0120231213872832</v>
       </c>
+      <c r="S241" s="1" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="T241" s="3" t="n">
+        <v>0.006397075622572595</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14515,6 +15967,12 @@
       <c r="R242" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S242" s="1" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="T242" s="3" t="n">
+        <v>0.005369127516778538</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14573,6 +16031,12 @@
       <c r="R243" s="3" t="n">
         <v>0.003482803656943849</v>
       </c>
+      <c r="S243" s="1" t="n">
+        <v>0.02269</v>
+      </c>
+      <c r="T243" s="2" t="n">
+        <v>-0.01561822125813461</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14631,6 +16095,12 @@
       <c r="R244" s="2" t="n">
         <v>-0.002977963073257899</v>
       </c>
+      <c r="S244" s="1" t="n">
+        <v>0.001676</v>
+      </c>
+      <c r="T244" s="3" t="n">
+        <v>0.00119474313022703</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14689,6 +16159,12 @@
       <c r="R245" s="2" t="n">
         <v>-0.002279635258358623</v>
       </c>
+      <c r="S245" s="1" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="T245" s="2" t="n">
+        <v>-0.004569687738004489</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14747,6 +16223,12 @@
       <c r="R246" s="2" t="n">
         <v>-0.01449732114717939</v>
       </c>
+      <c r="S246" s="1" t="n">
+        <v>0.03171</v>
+      </c>
+      <c r="T246" s="3" t="n">
+        <v>0.01407099456347947</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14805,6 +16287,12 @@
       <c r="R247" s="2" t="n">
         <v>-0.001125492402926313</v>
       </c>
+      <c r="S247" s="1" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="T247" s="3" t="n">
+        <v>0.001126760563380314</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14863,6 +16351,12 @@
       <c r="R248" s="3" t="n">
         <v>0.002620373403209851</v>
       </c>
+      <c r="S248" s="1" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="T248" s="2" t="n">
+        <v>-0.003593596863769977</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14921,6 +16415,12 @@
       <c r="R249" s="2" t="n">
         <v>-0.006352193859545963</v>
       </c>
+      <c r="S249" s="1" t="n">
+        <v>0.008455000000000001</v>
+      </c>
+      <c r="T249" s="3" t="n">
+        <v>0.0009470818041909627</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14979,6 +16479,12 @@
       <c r="R250" s="2" t="n">
         <v>-0.005873715124816377</v>
       </c>
+      <c r="S250" s="1" t="n">
+        <v>0.02005</v>
+      </c>
+      <c r="T250" s="2" t="n">
+        <v>-0.0128015755785329</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15037,6 +16543,12 @@
       <c r="R251" s="2" t="n">
         <v>-0.002358490566037714</v>
       </c>
+      <c r="S251" s="1" t="n">
+        <v>0.04643</v>
+      </c>
+      <c r="T251" s="2" t="n">
+        <v>-0.00214915108532136</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15095,6 +16607,12 @@
       <c r="R252" s="2" t="n">
         <v>-0.00353565114908648</v>
       </c>
+      <c r="S252" s="1" t="n">
+        <v>0.008515</v>
+      </c>
+      <c r="T252" s="3" t="n">
+        <v>0.007096392667060826</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -15153,6 +16671,12 @@
       <c r="R253" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S253" s="1" t="n">
+        <v>0.03885</v>
+      </c>
+      <c r="T253" s="3" t="n">
+        <v>0.00647668393782384</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -15211,6 +16735,12 @@
       <c r="R254" s="3" t="n">
         <v>0.001799443808277539</v>
       </c>
+      <c r="S254" s="1" t="n">
+        <v>0.06128</v>
+      </c>
+      <c r="T254" s="3" t="n">
+        <v>0.0006531678641410576</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15269,6 +16799,12 @@
       <c r="R255" s="2" t="n">
         <v>-0.002238388360380459</v>
       </c>
+      <c r="S255" s="1" t="n">
+        <v>0.003557</v>
+      </c>
+      <c r="T255" s="2" t="n">
+        <v>-0.00252383623107132</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15327,6 +16863,12 @@
       <c r="R256" s="3" t="n">
         <v>0.001377199693955674</v>
       </c>
+      <c r="S256" s="1" t="n">
+        <v>0.013261</v>
+      </c>
+      <c r="T256" s="3" t="n">
+        <v>0.01321821515892417</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15385,6 +16927,12 @@
       <c r="R257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S257" s="1" t="n">
+        <v>0.999426</v>
+      </c>
+      <c r="T257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15443,6 +16991,12 @@
       <c r="R258" s="2" t="n">
         <v>-0.001604584527220486</v>
       </c>
+      <c r="S258" s="1" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="T258" s="2" t="n">
+        <v>-0.001836758121914905</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15501,6 +17055,12 @@
       <c r="R259" s="2" t="n">
         <v>-0.003744493392070561</v>
       </c>
+      <c r="S259" s="1" t="n">
+        <v>0.09088</v>
+      </c>
+      <c r="T259" s="3" t="n">
+        <v>0.004642936104355557</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15559,6 +17119,12 @@
       <c r="R260" s="2" t="n">
         <v>-0.001225039813793813</v>
       </c>
+      <c r="S260" s="1" t="n">
+        <v>0.08153000000000001</v>
+      </c>
+      <c r="T260" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15617,6 +17183,12 @@
       <c r="R261" s="2" t="n">
         <v>-0.00782608695652165</v>
       </c>
+      <c r="S261" s="1" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="T261" s="3" t="n">
+        <v>0.008764241893076256</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15675,6 +17247,12 @@
       <c r="R262" s="3" t="n">
         <v>0.008792965627498013</v>
       </c>
+      <c r="S262" s="1" t="n">
+        <v>0.003765</v>
+      </c>
+      <c r="T262" s="2" t="n">
+        <v>-0.005546751188589475</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15733,6 +17311,12 @@
       <c r="R263" s="2" t="n">
         <v>-0.00255102040816322</v>
       </c>
+      <c r="S263" s="1" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="T263" s="2" t="n">
+        <v>-0.005115089514066524</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15791,6 +17375,12 @@
       <c r="R264" s="3" t="n">
         <v>0.004966603870525617</v>
       </c>
+      <c r="S264" s="1" t="n">
+        <v>0.0005965</v>
+      </c>
+      <c r="T264" s="3" t="n">
+        <v>0.01653033401499672</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15849,6 +17439,12 @@
       <c r="R265" s="2" t="n">
         <v>-0.001349527665317084</v>
       </c>
+      <c r="S265" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="T265" s="2" t="n">
+        <v>-0.004054054054054123</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15907,6 +17503,12 @@
       <c r="R266" s="2" t="n">
         <v>-0.004709576138147701</v>
       </c>
+      <c r="S266" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="T266" s="3" t="n">
+        <v>0.003154574132492204</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15965,6 +17567,12 @@
       <c r="R267" s="3" t="n">
         <v>0.001846153846153771</v>
       </c>
+      <c r="S267" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="T267" s="2" t="n">
+        <v>-0.004299754299754338</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16023,6 +17631,12 @@
       <c r="R268" s="2" t="n">
         <v>-0.01801396081963529</v>
       </c>
+      <c r="S268" s="1" t="n">
+        <v>0.0004371</v>
+      </c>
+      <c r="T268" s="3" t="n">
+        <v>0.002293052052281643</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16081,6 +17695,12 @@
       <c r="R269" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S269" s="1" t="n">
+        <v>0.02066</v>
+      </c>
+      <c r="T269" s="2" t="n">
+        <v>-0.002895752895752778</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -16139,6 +17759,12 @@
       <c r="R270" s="2" t="n">
         <v>-0.001106806862202577</v>
       </c>
+      <c r="S270" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="T270" s="3" t="n">
+        <v>0.001108033240997262</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16197,6 +17823,12 @@
       <c r="R271" s="2" t="n">
         <v>-0.0006802721088434626</v>
       </c>
+      <c r="S271" s="1" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="T271" s="3" t="n">
+        <v>0.0013614703880191</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16255,6 +17887,12 @@
       <c r="R272" s="2" t="n">
         <v>-0.007980049875311569</v>
       </c>
+      <c r="S272" s="1" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="T272" s="2" t="n">
+        <v>-0.01080945198592257</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16313,6 +17951,12 @@
       <c r="R273" s="2" t="n">
         <v>-0.004296455424274977</v>
       </c>
+      <c r="S273" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="T273" s="3" t="n">
+        <v>0.002157497303128373</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16371,6 +18015,12 @@
       <c r="R274" s="2" t="n">
         <v>-0.0003167062549484722</v>
       </c>
+      <c r="S274" s="1" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="T274" s="2" t="n">
+        <v>-0.001425629653096838</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16429,6 +18079,12 @@
       <c r="R275" s="2" t="n">
         <v>-0.006118881118881173</v>
       </c>
+      <c r="S275" s="1" t="n">
+        <v>0.01131</v>
+      </c>
+      <c r="T275" s="2" t="n">
+        <v>-0.005277044854881204</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16487,6 +18143,12 @@
       <c r="R276" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S276" s="1" t="n">
+        <v>2.598</v>
+      </c>
+      <c r="T276" s="3" t="n">
+        <v>0.001542020046260603</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16545,6 +18207,12 @@
       <c r="R277" s="2" t="n">
         <v>-0.001663893510815322</v>
       </c>
+      <c r="S277" s="1" t="n">
+        <v>0.04191</v>
+      </c>
+      <c r="T277" s="2" t="n">
+        <v>-0.002142857142857138</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16603,6 +18271,12 @@
       <c r="R278" s="3" t="n">
         <v>0.006122448979591941</v>
       </c>
+      <c r="S278" s="1" t="n">
+        <v>0.01963</v>
+      </c>
+      <c r="T278" s="2" t="n">
+        <v>-0.004563894523326562</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16661,6 +18335,12 @@
       <c r="R279" s="3" t="n">
         <v>0.006095374686267511</v>
       </c>
+      <c r="S279" s="1" t="n">
+        <v>0.005576</v>
+      </c>
+      <c r="T279" s="2" t="n">
+        <v>-0.006414825374198071</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16719,6 +18399,12 @@
       <c r="R280" s="2" t="n">
         <v>-0.0007774034724022349</v>
       </c>
+      <c r="S280" s="1" t="n">
+        <v>0.03894</v>
+      </c>
+      <c r="T280" s="3" t="n">
+        <v>0.009854771784232504</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16777,6 +18463,12 @@
       <c r="R281" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S281" s="1" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="T281" s="2" t="n">
+        <v>-0.003325942350332597</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16835,6 +18527,12 @@
       <c r="R282" s="2" t="n">
         <v>-0.004442250740375098</v>
       </c>
+      <c r="S282" s="1" t="n">
+        <v>0.0004045</v>
+      </c>
+      <c r="T282" s="3" t="n">
+        <v>0.002726822012890498</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16893,6 +18591,12 @@
       <c r="R283" s="2" t="n">
         <v>-0.0002502502502503268</v>
       </c>
+      <c r="S283" s="1" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="T283" s="2" t="n">
+        <v>-0.0007509386733417333</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16951,6 +18655,12 @@
       <c r="R284" s="2" t="n">
         <v>-0.001908396946564808</v>
       </c>
+      <c r="S284" s="1" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="T284" s="2" t="n">
+        <v>-0.001434034416826111</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -17009,6 +18719,12 @@
       <c r="R285" s="2" t="n">
         <v>-0.001391982182628038</v>
       </c>
+      <c r="S285" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="T285" s="2" t="n">
+        <v>-0.00195149149707278</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -17067,6 +18783,12 @@
       <c r="R286" s="2" t="n">
         <v>-0.004761904761904774</v>
       </c>
+      <c r="S286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="T286" s="3" t="n">
+        <v>0.002392344497607766</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -17125,6 +18847,12 @@
       <c r="R287" s="3" t="n">
         <v>0.001315183796935477</v>
       </c>
+      <c r="S287" s="1" t="n">
+        <v>0.15296</v>
+      </c>
+      <c r="T287" s="3" t="n">
+        <v>0.004531424443423025</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -17183,6 +18911,12 @@
       <c r="R288" s="3" t="n">
         <v>0.003324099722991785</v>
       </c>
+      <c r="S288" s="1" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="T288" s="2" t="n">
+        <v>-0.003313086692435214</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -17241,6 +18975,12 @@
       <c r="R289" s="2" t="n">
         <v>-0.002892263195950941</v>
       </c>
+      <c r="S289" s="1" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="T289" s="3" t="n">
+        <v>0.002175489485134238</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -17299,6 +19039,12 @@
       <c r="R290" s="2" t="n">
         <v>-0.001759530791788988</v>
       </c>
+      <c r="S290" s="1" t="n">
+        <v>0.08520999999999999</v>
+      </c>
+      <c r="T290" s="3" t="n">
+        <v>0.001292596944770846</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -17357,6 +19103,12 @@
       <c r="R291" s="2" t="n">
         <v>-0.0014096419509445</v>
       </c>
+      <c r="S291" s="1" t="n">
+        <v>0.03551</v>
+      </c>
+      <c r="T291" s="3" t="n">
+        <v>0.002540937323546014</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -17415,6 +19167,12 @@
       <c r="R292" s="2" t="n">
         <v>-0.000615426695842383</v>
       </c>
+      <c r="S292" s="1" t="n">
+        <v>1.4672</v>
+      </c>
+      <c r="T292" s="3" t="n">
+        <v>0.003900102634279875</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17473,6 +19231,12 @@
       <c r="R293" s="2" t="n">
         <v>-0.00375683060109295</v>
       </c>
+      <c r="S293" s="1" t="n">
+        <v>0.005852</v>
+      </c>
+      <c r="T293" s="3" t="n">
+        <v>0.003085361672951775</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17531,6 +19295,12 @@
       <c r="R294" s="3" t="n">
         <v>0.003524229074889826</v>
       </c>
+      <c r="S294" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="T294" s="3" t="n">
+        <v>0.0008779631255487165</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17589,6 +19359,12 @@
       <c r="R295" s="2" t="n">
         <v>-0.001855287569573285</v>
       </c>
+      <c r="S295" s="1" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="T295" s="3" t="n">
+        <v>0.0009293680297396746</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -17647,6 +19423,12 @@
       <c r="R296" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S296" s="1" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="T296" s="2" t="n">
+        <v>-0.001776988005330966</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -17705,6 +19487,12 @@
       <c r="R297" s="2" t="n">
         <v>-0.007054673721340508</v>
       </c>
+      <c r="S297" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="T297" s="2" t="n">
+        <v>-0.001184132622853711</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -17763,6 +19551,12 @@
       <c r="R298" s="3" t="n">
         <v>0.007808142777468</v>
       </c>
+      <c r="S298" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="T298" s="2" t="n">
+        <v>-0.006640841173215311</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -17821,6 +19615,12 @@
       <c r="R299" s="2" t="n">
         <v>-0.001805054151624475</v>
       </c>
+      <c r="S299" s="1" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="T299" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -17879,6 +19679,12 @@
       <c r="R300" s="2" t="n">
         <v>-0.001449975833736045</v>
       </c>
+      <c r="S300" s="1" t="n">
+        <v>0.02066</v>
+      </c>
+      <c r="T300" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -17937,6 +19743,12 @@
       <c r="R301" s="3" t="n">
         <v>0.005254515599343154</v>
       </c>
+      <c r="S301" s="1" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="T301" s="3" t="n">
+        <v>0.0003266906239792372</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -17995,6 +19807,12 @@
       <c r="R302" s="2" t="n">
         <v>-0.003641660597232316</v>
       </c>
+      <c r="S302" s="1" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="T302" s="3" t="n">
+        <v>0.008040935672514673</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -18053,6 +19871,12 @@
       <c r="R303" s="2" t="n">
         <v>-0.001351899418683101</v>
       </c>
+      <c r="S303" s="1" t="n">
+        <v>0.07385</v>
+      </c>
+      <c r="T303" s="2" t="n">
+        <v>-0.0002707459049682702</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -18111,6 +19935,12 @@
       <c r="R304" s="3" t="n">
         <v>0.001257861635220075</v>
       </c>
+      <c r="S304" s="1" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="T304" s="2" t="n">
+        <v>-0.005653266331658279</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -18169,6 +19999,12 @@
       <c r="R305" s="2" t="n">
         <v>-0.001079913606911456</v>
       </c>
+      <c r="S305" s="1" t="n">
+        <v>0.06463000000000001</v>
+      </c>
+      <c r="T305" s="2" t="n">
+        <v>-0.001853281853281778</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -18227,6 +20063,12 @@
       <c r="R306" s="2" t="n">
         <v>-0.004800000000000082</v>
       </c>
+      <c r="S306" s="1" t="n">
+        <v>0.04948</v>
+      </c>
+      <c r="T306" s="2" t="n">
+        <v>-0.005627009646302161</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -18285,6 +20127,12 @@
       <c r="R307" s="2" t="n">
         <v>-0.006444683136412465</v>
       </c>
+      <c r="S307" s="1" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="T307" s="2" t="n">
+        <v>-0.006486486486486492</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -18343,6 +20191,12 @@
       <c r="R308" s="3" t="n">
         <v>0.001511715797430021</v>
       </c>
+      <c r="S308" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="T308" s="3" t="n">
+        <v>0.003270440251572281</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -18401,6 +20255,12 @@
       <c r="R309" s="2" t="n">
         <v>-0.006997455470737959</v>
       </c>
+      <c r="S309" s="1" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="T309" s="3" t="n">
+        <v>0.002562459961563107</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -18459,6 +20319,12 @@
       <c r="R310" s="2" t="n">
         <v>-0.002209944751381253</v>
       </c>
+      <c r="S310" s="1" t="n">
+        <v>0.05423</v>
+      </c>
+      <c r="T310" s="3" t="n">
+        <v>0.0009228497600590888</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -18517,6 +20383,12 @@
       <c r="R311" s="3" t="n">
         <v>0.00269118636465572</v>
       </c>
+      <c r="S311" s="1" t="n">
+        <v>0.004459</v>
+      </c>
+      <c r="T311" s="2" t="n">
+        <v>-0.00268396331916794</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -18575,6 +20447,12 @@
       <c r="R312" s="2" t="n">
         <v>-0.001182033096926584</v>
       </c>
+      <c r="S312" s="1" t="n">
+        <v>0.08457000000000001</v>
+      </c>
+      <c r="T312" s="3" t="n">
+        <v>0.0008284023668639126</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -18633,6 +20511,12 @@
       <c r="R313" s="2" t="n">
         <v>-0.001866169021594258</v>
       </c>
+      <c r="S313" s="1" t="n">
+        <v>0.07482</v>
+      </c>
+      <c r="T313" s="2" t="n">
+        <v>-0.0008012820512821113</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -18691,6 +20575,12 @@
       <c r="R314" s="2" t="n">
         <v>-0.001954397394136773</v>
       </c>
+      <c r="S314" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="T314" s="2" t="n">
+        <v>-0.0006527415143602414</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -18749,6 +20639,12 @@
       <c r="R315" s="2" t="n">
         <v>-0.001876172607879892</v>
       </c>
+      <c r="S315" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="T315" s="3" t="n">
+        <v>0.001879699248120268</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -18807,6 +20703,12 @@
       <c r="R316" s="3" t="n">
         <v>0.01047409040793817</v>
       </c>
+      <c r="S316" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="T316" s="2" t="n">
+        <v>-0.008728859792689527</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -18865,6 +20767,12 @@
       <c r="R317" s="2" t="n">
         <v>-0.0006664889362836305</v>
       </c>
+      <c r="S317" s="1" t="n">
+        <v>0.007493</v>
+      </c>
+      <c r="T317" s="2" t="n">
+        <v>-0.0005335467520342178</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -18923,6 +20831,12 @@
       <c r="R318" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S318" s="1" t="n">
+        <v>0.05003</v>
+      </c>
+      <c r="T318" s="3" t="n">
+        <v>0.002002803925495612</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -18981,6 +20895,12 @@
       <c r="R319" s="2" t="n">
         <v>-0.001330313162909364</v>
       </c>
+      <c r="S319" s="1" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="T319" s="3" t="n">
+        <v>0.00392425115207366</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -19039,6 +20959,12 @@
       <c r="R320" s="2" t="n">
         <v>-0.002039891205802258</v>
       </c>
+      <c r="S320" s="1" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="T320" s="2" t="n">
+        <v>-0.0004542357483534714</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -19097,6 +21023,12 @@
       <c r="R321" s="3" t="n">
         <v>0.0005165289256198137</v>
       </c>
+      <c r="S321" s="1" t="n">
+        <v>0.07738</v>
+      </c>
+      <c r="T321" s="2" t="n">
+        <v>-0.001290655653071618</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -19155,6 +21087,12 @@
       <c r="R322" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S322" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="T322" s="3" t="n">
+        <v>0.003071253071253074</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -19213,6 +21151,12 @@
       <c r="R323" s="3" t="n">
         <v>0.002022244691607686</v>
       </c>
+      <c r="S323" s="1" t="n">
+        <v>1.982</v>
+      </c>
+      <c r="T323" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -19271,6 +21215,12 @@
       <c r="R324" s="2" t="n">
         <v>-0.001368912558366244</v>
       </c>
+      <c r="S324" s="1" t="n">
+        <v>0.05324</v>
+      </c>
+      <c r="T324" s="2" t="n">
+        <v>-0.0002628910504375281</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -19329,6 +21279,12 @@
       <c r="R325" s="2" t="n">
         <v>-0.002864956374527907</v>
       </c>
+      <c r="S325" s="1" t="n">
+        <v>0.15412</v>
+      </c>
+      <c r="T325" s="3" t="n">
+        <v>0.006399373122632942</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -19387,6 +21343,12 @@
       <c r="R326" s="3" t="n">
         <v>0.0001540120129370295</v>
       </c>
+      <c r="S326" s="1" t="n">
+        <v>0.006459</v>
+      </c>
+      <c r="T326" s="2" t="n">
+        <v>-0.005389590391130189</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -19445,6 +21407,12 @@
       <c r="R327" s="3" t="n">
         <v>0.001715605410755525</v>
       </c>
+      <c r="S327" s="1" t="n">
+        <v>0.015213</v>
+      </c>
+      <c r="T327" s="3" t="n">
+        <v>0.002107898030432829</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -19503,6 +21471,12 @@
       <c r="R328" s="2" t="n">
         <v>-0.003154574132492204</v>
       </c>
+      <c r="S328" s="1" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="T328" s="3" t="n">
+        <v>0.005274261603375532</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -19561,6 +21535,12 @@
       <c r="R329" s="2" t="n">
         <v>-0.000903750564844223</v>
       </c>
+      <c r="S329" s="1" t="n">
+        <v>0.004419</v>
+      </c>
+      <c r="T329" s="2" t="n">
+        <v>-0.0006784260515602738</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -19619,6 +21599,12 @@
       <c r="R330" s="2" t="n">
         <v>-0.002706883217324076</v>
       </c>
+      <c r="S330" s="1" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="T330" s="3" t="n">
+        <v>0.0001938735944163653</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -19677,6 +21663,12 @@
       <c r="R331" s="3" t="n">
         <v>0.001657000828500347</v>
       </c>
+      <c r="S331" s="1" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="T331" s="2" t="n">
+        <v>-0.001929969671904982</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -19735,6 +21727,12 @@
       <c r="R332" s="2" t="n">
         <v>-0.001367053998632985</v>
       </c>
+      <c r="S332" s="1" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="T332" s="3" t="n">
+        <v>0.00205338809034904</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -19793,6 +21791,12 @@
       <c r="R333" s="2" t="n">
         <v>-0.003102378490175747</v>
       </c>
+      <c r="S333" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="T333" s="3" t="n">
+        <v>0.001037344398340279</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -19851,6 +21855,12 @@
       <c r="R334" s="3" t="n">
         <v>0.003205128205128234</v>
       </c>
+      <c r="S334" s="1" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="T334" s="3" t="n">
+        <v>0.003651300775901425</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -19909,6 +21919,12 @@
       <c r="R335" s="2" t="n">
         <v>-0.002339037301489545</v>
       </c>
+      <c r="S335" s="1" t="n">
+        <v>0.08101999999999999</v>
+      </c>
+      <c r="T335" s="2" t="n">
+        <v>-0.0002467917077986935</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19967,6 +21983,12 @@
       <c r="R336" s="2" t="n">
         <v>-0.001953125000000056</v>
       </c>
+      <c r="S336" s="1" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="T336" s="2" t="n">
+        <v>-0.0004892367906065997</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -20025,6 +22047,12 @@
       <c r="R337" s="2" t="n">
         <v>-0.0009794319294808612</v>
       </c>
+      <c r="S337" s="1" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="T337" s="2" t="n">
+        <v>-0.002941176470588285</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -20083,6 +22111,12 @@
       <c r="R338" s="2" t="n">
         <v>-0.002647837599293863</v>
       </c>
+      <c r="S338" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="T338" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -20141,6 +22175,12 @@
       <c r="R339" s="2" t="n">
         <v>-0.001090512540894176</v>
       </c>
+      <c r="S339" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="T339" s="2" t="n">
+        <v>-0.002729257641921286</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -20199,6 +22239,12 @@
       <c r="R340" s="2" t="n">
         <v>-0.0005364423145697142</v>
       </c>
+      <c r="S340" s="1" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="T340" s="2" t="n">
+        <v>-0.003792893691630606</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -20257,6 +22303,12 @@
       <c r="R341" s="3" t="n">
         <v>0.0002323420074348542</v>
       </c>
+      <c r="S341" s="1" t="n">
+        <v>0.04288</v>
+      </c>
+      <c r="T341" s="2" t="n">
+        <v>-0.003948896631823381</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -20315,6 +22367,12 @@
       <c r="R342" s="2" t="n">
         <v>-0.01763803680981603</v>
       </c>
+      <c r="S342" s="1" t="n">
+        <v>0.07695</v>
+      </c>
+      <c r="T342" s="3" t="n">
+        <v>0.001170960187353718</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -20373,6 +22431,12 @@
       <c r="R343" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S343" s="1" t="n">
+        <v>7.657</v>
+      </c>
+      <c r="T343" s="3" t="n">
+        <v>0.001307702366941256</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -20431,6 +22495,12 @@
       <c r="R344" s="2" t="n">
         <v>-0.003148823334438204</v>
       </c>
+      <c r="S344" s="1" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="T344" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -20489,6 +22559,12 @@
       <c r="R345" s="2" t="n">
         <v>-0.001877178868329141</v>
       </c>
+      <c r="S345" s="1" t="n">
+        <v>0.03726</v>
+      </c>
+      <c r="T345" s="3" t="n">
+        <v>0.001074691026329886</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -20547,6 +22623,12 @@
       <c r="R346" s="2" t="n">
         <v>-0.002409638554216936</v>
       </c>
+      <c r="S346" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="T346" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -20605,6 +22687,12 @@
       <c r="R347" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S347" s="1" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="T347" s="3" t="n">
+        <v>0.001724137931034612</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -20663,6 +22751,12 @@
       <c r="R348" s="2" t="n">
         <v>-7.706683621381148e-05</v>
       </c>
+      <c r="S348" s="1" t="n">
+        <v>5192.8</v>
+      </c>
+      <c r="T348" s="3" t="n">
+        <v>0.0005587776257732415</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -20721,6 +22815,12 @@
       <c r="R349" s="3" t="n">
         <v>0.03450807635829662</v>
       </c>
+      <c r="S349" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="T349" s="2" t="n">
+        <v>-0.01064584811923356</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -20779,6 +22879,12 @@
       <c r="R350" s="3" t="n">
         <v>0.001327140013271346</v>
       </c>
+      <c r="S350" s="1" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="T350" s="3" t="n">
+        <v>0.004638833664678636</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -20837,6 +22943,12 @@
       <c r="R351" s="2" t="n">
         <v>-0.003430251551780459</v>
       </c>
+      <c r="S351" s="1" t="n">
+        <v>0.0006098</v>
+      </c>
+      <c r="T351" s="2" t="n">
+        <v>-0.0004917226684151147</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -20895,6 +23007,12 @@
       <c r="R352" s="2" t="n">
         <v>-0.003542510121457521</v>
       </c>
+      <c r="S352" s="1" t="n">
+        <v>0.01982</v>
+      </c>
+      <c r="T352" s="3" t="n">
+        <v>0.006602336211274843</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -20953,6 +23071,12 @@
       <c r="R353" s="3" t="n">
         <v>0.0003213023455071463</v>
       </c>
+      <c r="S353" s="1" t="n">
+        <v>0.09315</v>
+      </c>
+      <c r="T353" s="2" t="n">
+        <v>-0.002676659528907925</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -21011,6 +23135,12 @@
       <c r="R354" s="2" t="n">
         <v>-0.001100110011000979</v>
       </c>
+      <c r="S354" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="T354" s="2" t="n">
+        <v>-0.003303964757709346</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -21069,6 +23199,12 @@
       <c r="R355" s="3" t="n">
         <v>0.00533894191878341</v>
       </c>
+      <c r="S355" s="1" t="n">
+        <v>0.0006293</v>
+      </c>
+      <c r="T355" s="3" t="n">
+        <v>0.01271322819439961</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -21127,6 +23263,12 @@
       <c r="R356" s="2" t="n">
         <v>-0.004852013585637936</v>
       </c>
+      <c r="S356" s="1" t="n">
+        <v>2.035</v>
+      </c>
+      <c r="T356" s="2" t="n">
+        <v>-0.007801072647489036</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -21185,6 +23327,12 @@
       <c r="R357" s="2" t="n">
         <v>-0.006974716652135875</v>
       </c>
+      <c r="S357" s="1" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="T357" s="3" t="n">
+        <v>0.001316944688323037</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -21243,6 +23391,12 @@
       <c r="R358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="T358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -21301,6 +23455,12 @@
       <c r="R359" s="3" t="n">
         <v>0.0006807351940095026</v>
       </c>
+      <c r="S359" s="1" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="T359" s="2" t="n">
+        <v>-0.002721088435374157</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -21359,6 +23519,12 @@
       <c r="R360" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S360" s="1" t="n">
+        <v>0.003328</v>
+      </c>
+      <c r="T360" s="2" t="n">
+        <v>-0.004486987735566932</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -21417,6 +23583,12 @@
       <c r="R361" s="2" t="n">
         <v>-0.0009377930603314237</v>
       </c>
+      <c r="S361" s="1" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="T361" s="3" t="n">
+        <v>0.004067584480600824</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -21475,6 +23647,12 @@
       <c r="R362" s="2" t="n">
         <v>-0.002568493150684827</v>
       </c>
+      <c r="S362" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="T362" s="3" t="n">
+        <v>0.0008583690987124113</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -21533,6 +23711,12 @@
       <c r="R363" s="2" t="n">
         <v>-0.002288329519450761</v>
       </c>
+      <c r="S363" s="1" t="n">
+        <v>0.06535000000000001</v>
+      </c>
+      <c r="T363" s="2" t="n">
+        <v>-0.0007645259938837078</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -21591,6 +23775,12 @@
       <c r="R364" s="3" t="n">
         <v>0.0006376195536663366</v>
       </c>
+      <c r="S364" s="1" t="n">
+        <v>4.715</v>
+      </c>
+      <c r="T364" s="3" t="n">
+        <v>0.001486830926083193</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -21649,6 +23839,12 @@
       <c r="R365" s="2" t="n">
         <v>-0.0007005744710663917</v>
       </c>
+      <c r="S365" s="1" t="n">
+        <v>0.07148</v>
+      </c>
+      <c r="T365" s="3" t="n">
+        <v>0.002243409983174528</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -21707,6 +23903,12 @@
       <c r="R366" s="2" t="n">
         <v>-0.001962183374955387</v>
       </c>
+      <c r="S366" s="1" t="n">
+        <v>0.05629</v>
+      </c>
+      <c r="T366" s="3" t="n">
+        <v>0.006076854334226989</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -21765,6 +23967,12 @@
       <c r="R367" s="2" t="n">
         <v>-0.0008552856654122722</v>
       </c>
+      <c r="S367" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="T367" s="3" t="n">
+        <v>0.001540832049306741</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -21823,6 +24031,12 @@
       <c r="R368" s="2" t="n">
         <v>-0.001914708442123568</v>
       </c>
+      <c r="S368" s="1" t="n">
+        <v>0.05729</v>
+      </c>
+      <c r="T368" s="2" t="n">
+        <v>-0.0008719916288803877</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -21881,6 +24095,12 @@
       <c r="R369" s="3" t="n">
         <v>0.00161603102779578</v>
       </c>
+      <c r="S369" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="T369" s="3" t="n">
+        <v>0.0003226847370119262</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -21939,6 +24159,12 @@
       <c r="R370" s="2" t="n">
         <v>-0.001843884449907851</v>
       </c>
+      <c r="S370" s="1" t="n">
+        <v>0.0001622</v>
+      </c>
+      <c r="T370" s="2" t="n">
+        <v>-0.001231527093595922</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -21997,6 +24223,12 @@
       <c r="R371" s="3" t="n">
         <v>0.004551460872118599</v>
       </c>
+      <c r="S371" s="1" t="n">
+        <v>0.006826</v>
+      </c>
+      <c r="T371" s="2" t="n">
+        <v>-0.002338497515346447</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -22055,6 +24287,12 @@
       <c r="R372" s="2" t="n">
         <v>-0.001575479805213491</v>
       </c>
+      <c r="S372" s="1" t="n">
+        <v>0.006996</v>
+      </c>
+      <c r="T372" s="3" t="n">
+        <v>0.003586286042174702</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -22113,6 +24351,12 @@
       <c r="R373" s="2" t="n">
         <v>-0.0005256241787122796</v>
       </c>
+      <c r="S373" s="1" t="n">
+        <v>3.781</v>
+      </c>
+      <c r="T373" s="2" t="n">
+        <v>-0.005784906652642597</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -22171,6 +24415,12 @@
       <c r="R374" s="3" t="n">
         <v>0.0005661712668081864</v>
       </c>
+      <c r="S374" s="1" t="n">
+        <v>0.07045</v>
+      </c>
+      <c r="T374" s="2" t="n">
+        <v>-0.003395105389729864</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -22229,6 +24479,12 @@
       <c r="R375" s="2" t="n">
         <v>-0.002165053489556845</v>
       </c>
+      <c r="S375" s="1" t="n">
+        <v>0.07907</v>
+      </c>
+      <c r="T375" s="3" t="n">
+        <v>0.009189534141671963</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -22287,6 +24543,12 @@
       <c r="R376" s="2" t="n">
         <v>-0.000797066794197266</v>
       </c>
+      <c r="S376" s="1" t="n">
+        <v>0.06275</v>
+      </c>
+      <c r="T376" s="3" t="n">
+        <v>0.001116783663050425</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -22345,6 +24607,12 @@
       <c r="R377" s="2" t="n">
         <v>-0.001701125359853508</v>
       </c>
+      <c r="S377" s="1" t="n">
+        <v>0.07641000000000001</v>
+      </c>
+      <c r="T377" s="3" t="n">
+        <v>0.001572945340149548</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -22403,6 +24671,12 @@
       <c r="R378" s="3" t="n">
         <v>0.002741091452778537</v>
       </c>
+      <c r="S378" s="1" t="n">
+        <v>0.0004017</v>
+      </c>
+      <c r="T378" s="2" t="n">
+        <v>-0.001739562624254515</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -22461,6 +24735,12 @@
       <c r="R379" s="2" t="n">
         <v>-0.001476311904442529</v>
       </c>
+      <c r="S379" s="1" t="n">
+        <v>0.07448</v>
+      </c>
+      <c r="T379" s="3" t="n">
+        <v>0.001075268817204444</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -22519,6 +24799,12 @@
       <c r="R380" s="3" t="n">
         <v>0.002956393200295551</v>
       </c>
+      <c r="S380" s="1" t="n">
+        <v>0.001362</v>
+      </c>
+      <c r="T380" s="3" t="n">
+        <v>0.003684598378776723</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -22577,6 +24863,12 @@
       <c r="R381" s="2" t="n">
         <v>-0.008694302126998921</v>
       </c>
+      <c r="S381" s="1" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="T381" s="3" t="n">
+        <v>0.003132341425215421</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -22635,6 +24927,12 @@
       <c r="R382" s="2" t="n">
         <v>-0.005098324836125192</v>
       </c>
+      <c r="S382" s="1" t="n">
+        <v>0.01367</v>
+      </c>
+      <c r="T382" s="3" t="n">
+        <v>0.0007320644216690771</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -22693,6 +24991,12 @@
       <c r="R383" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S383" s="1" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="T383" s="3" t="n">
+        <v>0.0005691519635742512</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -22751,6 +25055,12 @@
       <c r="R384" s="3" t="n">
         <v>0.001966568338249811</v>
       </c>
+      <c r="S384" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="T384" s="2" t="n">
+        <v>-0.002944062806673293</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -22809,6 +25119,12 @@
       <c r="R385" s="2" t="n">
         <v>-0.003338526596928682</v>
       </c>
+      <c r="S385" s="1" t="n">
+        <v>4.485</v>
+      </c>
+      <c r="T385" s="3" t="n">
+        <v>0.001563197856185923</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -22867,6 +25183,12 @@
       <c r="R386" s="2" t="n">
         <v>-0.006191950464396268</v>
       </c>
+      <c r="S386" s="1" t="n">
+        <v>0.001284</v>
+      </c>
+      <c r="T386" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -22925,6 +25247,12 @@
       <c r="R387" s="2" t="n">
         <v>-0.002360478839993313</v>
       </c>
+      <c r="S387" s="1" t="n">
+        <v>0.0005922</v>
+      </c>
+      <c r="T387" s="3" t="n">
+        <v>0.0008450228156159505</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -22983,6 +25311,12 @@
       <c r="R388" s="3" t="n">
         <v>0.004389815627743608</v>
       </c>
+      <c r="S388" s="1" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="T388" s="2" t="n">
+        <v>-0.001748251748251828</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -23041,6 +25375,12 @@
       <c r="R389" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S389" s="1" t="n">
+        <v>0.009050000000000001</v>
+      </c>
+      <c r="T389" s="2" t="n">
+        <v>-0.003303964757709117</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -23099,6 +25439,12 @@
       <c r="R390" s="2" t="n">
         <v>-0.00101278642866199</v>
       </c>
+      <c r="S390" s="1" t="n">
+        <v>0.07901</v>
+      </c>
+      <c r="T390" s="3" t="n">
+        <v>0.001267266506146279</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -23157,6 +25503,12 @@
       <c r="R391" s="2" t="n">
         <v>-0.003675048355899471</v>
       </c>
+      <c r="S391" s="1" t="n">
+        <v>0.05165</v>
+      </c>
+      <c r="T391" s="3" t="n">
+        <v>0.002717918850708624</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -23215,6 +25567,12 @@
       <c r="R392" s="2" t="n">
         <v>-0.008368200836820106</v>
       </c>
+      <c r="S392" s="1" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="T392" s="3" t="n">
+        <v>0.004219409282700433</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -23273,6 +25631,12 @@
       <c r="R393" s="3" t="n">
         <v>0.005164319248826244</v>
       </c>
+      <c r="S393" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="T393" s="3" t="n">
+        <v>0.001868285847734789</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -23331,6 +25695,12 @@
       <c r="R394" s="2" t="n">
         <v>-0.002430724355858048</v>
       </c>
+      <c r="S394" s="1" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="T394" s="2" t="n">
+        <v>-0.004385964912280624</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -23389,6 +25759,12 @@
       <c r="R395" s="2" t="n">
         <v>-0.001026694045174567</v>
       </c>
+      <c r="S395" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="T395" s="2" t="n">
+        <v>-0.001027749229188108</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -23447,6 +25823,12 @@
       <c r="R396" s="2" t="n">
         <v>-0.001102535832414595</v>
       </c>
+      <c r="S396" s="1" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T396" s="3" t="n">
+        <v>0.000735835172921348</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -23505,6 +25887,12 @@
       <c r="R397" s="2" t="n">
         <v>-0.004750593824228033</v>
       </c>
+      <c r="S397" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T397" s="3" t="n">
+        <v>0.002386634844868826</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -23563,6 +25951,12 @@
       <c r="R398" s="2" t="n">
         <v>-0.003111050994183748</v>
       </c>
+      <c r="S398" s="1" t="n">
+        <v>0.007392</v>
+      </c>
+      <c r="T398" s="3" t="n">
+        <v>0.002985074626865715</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -23621,6 +26015,12 @@
       <c r="R399" s="2" t="n">
         <v>-0.004209720627631037</v>
       </c>
+      <c r="S399" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="T399" s="2" t="n">
+        <v>-0.004996156802459523</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -23679,6 +26079,12 @@
       <c r="R400" s="2" t="n">
         <v>-0.003146633102580242</v>
       </c>
+      <c r="S400" s="1" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="T400" s="3" t="n">
+        <v>0.005997474747474612</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -23737,6 +26143,12 @@
       <c r="R401" s="2" t="n">
         <v>-0.005895256375102893</v>
       </c>
+      <c r="S401" s="1" t="n">
+        <v>0.007218</v>
+      </c>
+      <c r="T401" s="2" t="n">
+        <v>-0.004551096400496489</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -23795,6 +26207,12 @@
       <c r="R402" s="2" t="n">
         <v>-0.001960784313725561</v>
       </c>
+      <c r="S402" s="1" t="n">
+        <v>0.004583</v>
+      </c>
+      <c r="T402" s="3" t="n">
+        <v>0.0004365858982755437</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -23853,6 +26271,12 @@
       <c r="R403" s="2" t="n">
         <v>-0.001509433962264194</v>
       </c>
+      <c r="S403" s="1" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="T403" s="3" t="n">
+        <v>0.001511715797430126</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -23911,6 +26335,12 @@
       <c r="R404" s="2" t="n">
         <v>-0.002493765586034984</v>
       </c>
+      <c r="S404" s="1" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="T404" s="2" t="n">
+        <v>-0.003333333333333313</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -23969,6 +26399,12 @@
       <c r="R405" s="3" t="n">
         <v>0.00766941391941392</v>
       </c>
+      <c r="S405" s="1" t="n">
+        <v>0.000875</v>
+      </c>
+      <c r="T405" s="2" t="n">
+        <v>-0.006020674769964747</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -24027,6 +26463,12 @@
       <c r="R406" s="2" t="n">
         <v>-0.0005912495072921557</v>
       </c>
+      <c r="S406" s="1" t="n">
+        <v>0.00507</v>
+      </c>
+      <c r="T406" s="2" t="n">
+        <v>-0.0001971997633603101</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -24085,6 +26527,12 @@
       <c r="R407" s="2" t="n">
         <v>-0.003300330033003309</v>
       </c>
+      <c r="S407" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="T407" s="2" t="n">
+        <v>-0.004139072847682094</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -24143,6 +26591,12 @@
       <c r="R408" s="3" t="n">
         <v>0.0006915629322267745</v>
       </c>
+      <c r="S408" s="1" t="n">
+        <v>0.001452</v>
+      </c>
+      <c r="T408" s="3" t="n">
+        <v>0.003455425017277134</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -24201,6 +26655,12 @@
       <c r="R409" s="2" t="n">
         <v>-0.005088377075522114</v>
       </c>
+      <c r="S409" s="1" t="n">
+        <v>0.03751</v>
+      </c>
+      <c r="T409" s="3" t="n">
+        <v>0.009690444145356641</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -24259,6 +26719,12 @@
       <c r="R410" s="2" t="n">
         <v>-0.003061849357011722</v>
       </c>
+      <c r="S410" s="1" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="T410" s="2" t="n">
+        <v>-0.001842751842751768</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -24317,6 +26783,12 @@
       <c r="R411" s="3" t="n">
         <v>0.0005252100840335555</v>
       </c>
+      <c r="S411" s="1" t="n">
+        <v>0.1903</v>
+      </c>
+      <c r="T411" s="2" t="n">
+        <v>-0.00104986876640423</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -24375,6 +26847,12 @@
       <c r="R412" s="3" t="n">
         <v>0.0008927242969794764</v>
       </c>
+      <c r="S412" s="1" t="n">
+        <v>0.06729</v>
+      </c>
+      <c r="T412" s="3" t="n">
+        <v>0.0002973093503791605</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -24433,6 +26911,12 @@
       <c r="R413" s="2" t="n">
         <v>-0.00157294534014943</v>
       </c>
+      <c r="S413" s="1" t="n">
+        <v>2538</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>-0.0003938558487593541</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -24491,6 +26975,12 @@
       <c r="R414" s="3" t="n">
         <v>0.002294893861158828</v>
       </c>
+      <c r="S414" s="1" t="n">
+        <v>0.05272</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>0.005914901736309955</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -24549,6 +27039,12 @@
       <c r="R415" s="2" t="n">
         <v>-0.001141552511415526</v>
       </c>
+      <c r="S415" s="1" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>-0.006857142857142863</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -24607,6 +27103,12 @@
       <c r="R416" s="3" t="n">
         <v>0.001013904982618781</v>
       </c>
+      <c r="S416" s="1" t="n">
+        <v>0.06887</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>-0.00347272464187533</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -24665,6 +27167,12 @@
       <c r="R417" s="2" t="n">
         <v>-0.02666666666666669</v>
       </c>
+      <c r="S417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="T417" s="3" t="n">
+        <v>0.02739726027397263</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -24723,6 +27231,12 @@
       <c r="R418" s="3" t="n">
         <v>0.0006518904823988852</v>
       </c>
+      <c r="S418" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="T418" s="2" t="n">
+        <v>-0.003257328990228016</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -24781,6 +27295,12 @@
       <c r="R419" s="3" t="n">
         <v>0.008130081300812959</v>
       </c>
+      <c r="S419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="T419" s="2" t="n">
+        <v>-0.008064516129032209</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -24839,6 +27359,12 @@
       <c r="R420" s="2" t="n">
         <v>-0.006725297465080271</v>
       </c>
+      <c r="S420" s="1" t="n">
+        <v>0.01929</v>
+      </c>
+      <c r="T420" s="3" t="n">
+        <v>0.004687500000000171</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -24897,6 +27423,12 @@
       <c r="R421" s="2" t="n">
         <v>-0.00263212221304698</v>
       </c>
+      <c r="S421" s="1" t="n">
+        <v>0.19342</v>
+      </c>
+      <c r="T421" s="3" t="n">
+        <v>0.0008796895213454255</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -24955,6 +27487,12 @@
       <c r="R422" s="2" t="n">
         <v>-0.002045587375803641</v>
       </c>
+      <c r="S422" s="1" t="n">
+        <v>0.03408</v>
+      </c>
+      <c r="T422" s="2" t="n">
+        <v>-0.002049780380673517</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -25013,6 +27551,12 @@
       <c r="R423" s="2" t="n">
         <v>-0.001410437235543059</v>
       </c>
+      <c r="S423" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="T423" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -25071,6 +27615,12 @@
       <c r="R424" s="2" t="n">
         <v>-0.001893939393939317</v>
       </c>
+      <c r="S424" s="1" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="T424" s="3" t="n">
+        <v>0.001897533206831042</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -25129,6 +27679,12 @@
       <c r="R425" s="2" t="n">
         <v>-0.0009523809523809797</v>
       </c>
+      <c r="S425" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="T425" s="2" t="n">
+        <v>-0.0009532888465203907</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -25187,6 +27743,12 @@
       <c r="R426" s="3" t="n">
         <v>0.00227563646707444</v>
       </c>
+      <c r="S426" s="1" t="n">
+        <v>0.007036</v>
+      </c>
+      <c r="T426" s="2" t="n">
+        <v>-0.001560947921101262</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -25245,6 +27807,12 @@
       <c r="R427" s="3" t="n">
         <v>0.0003920031360250722</v>
       </c>
+      <c r="S427" s="1" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="T427" s="2" t="n">
+        <v>-0.002742946708463974</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -25303,6 +27871,12 @@
       <c r="R428" s="3" t="n">
         <v>0.0002480774001488794</v>
       </c>
+      <c r="S428" s="1" t="n">
+        <v>0.008038</v>
+      </c>
+      <c r="T428" s="2" t="n">
+        <v>-0.003224206349206347</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -25361,6 +27935,12 @@
       <c r="R429" s="3" t="n">
         <v>0.0008084074373483906</v>
       </c>
+      <c r="S429" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="T429" s="3" t="n">
+        <v>0.0008077544426494017</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -25419,6 +27999,12 @@
       <c r="R430" s="2" t="n">
         <v>-0.0004479617739286583</v>
       </c>
+      <c r="S430" s="1" t="n">
+        <v>0.06686</v>
+      </c>
+      <c r="T430" s="2" t="n">
+        <v>-0.001195100089632458</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -25477,6 +28063,12 @@
       <c r="R431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S431" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="T431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -25535,6 +28127,12 @@
       <c r="R432" s="2" t="n">
         <v>-0.0009265932255738281</v>
       </c>
+      <c r="S432" s="1" t="n">
+        <v>0.009682</v>
+      </c>
+      <c r="T432" s="2" t="n">
+        <v>-0.002267106347897896</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -25593,6 +28191,12 @@
       <c r="R433" s="3" t="n">
         <v>0.001689596910451379</v>
       </c>
+      <c r="S433" s="1" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="T433" s="2" t="n">
+        <v>-0.003132530120482051</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -25651,6 +28255,12 @@
       <c r="R434" s="3" t="n">
         <v>0.003832335329341327</v>
       </c>
+      <c r="S434" s="1" t="n">
+        <v>0.04171</v>
+      </c>
+      <c r="T434" s="2" t="n">
+        <v>-0.004772130756382861</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -25709,6 +28319,12 @@
       <c r="R435" s="2" t="n">
         <v>-0.0006489292667100148</v>
       </c>
+      <c r="S435" s="1" t="n">
+        <v>0.001542</v>
+      </c>
+      <c r="T435" s="3" t="n">
+        <v>0.00129870129870133</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -25767,6 +28383,12 @@
       <c r="R436" s="3" t="n">
         <v>0.0007270083605961172</v>
       </c>
+      <c r="S436" s="1" t="n">
+        <v>0.02742</v>
+      </c>
+      <c r="T436" s="2" t="n">
+        <v>-0.003995641118779477</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -25825,6 +28447,12 @@
       <c r="R437" s="3" t="n">
         <v>0.002565355484974369</v>
       </c>
+      <c r="S437" s="1" t="n">
+        <v>0.08186</v>
+      </c>
+      <c r="T437" s="2" t="n">
+        <v>-0.002558791275740244</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -25883,6 +28511,12 @@
       <c r="R438" s="2" t="n">
         <v>-0.003463203463203562</v>
       </c>
+      <c r="S438" s="1" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="T438" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -25941,6 +28575,12 @@
       <c r="R439" s="2" t="n">
         <v>-0.0006472491909384401</v>
       </c>
+      <c r="S439" s="1" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="T439" s="3" t="n">
+        <v>0.0006476683937823121</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -25999,6 +28639,12 @@
       <c r="R440" s="2" t="n">
         <v>-0.001109262340543445</v>
       </c>
+      <c r="S440" s="1" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="T440" s="2" t="n">
+        <v>-0.0005552470849528777</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -26057,6 +28703,12 @@
       <c r="R441" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S441" s="1" t="n">
+        <v>0.03703</v>
+      </c>
+      <c r="T441" s="3" t="n">
+        <v>0.007070981778623968</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -26115,6 +28767,12 @@
       <c r="R442" s="2" t="n">
         <v>-0.003769520732364061</v>
       </c>
+      <c r="S442" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="T442" s="2" t="n">
+        <v>-0.002702702702702593</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -26173,6 +28831,12 @@
       <c r="R443" s="2" t="n">
         <v>-0.002108716026241741</v>
       </c>
+      <c r="S443" s="1" t="n">
+        <v>0.12779</v>
+      </c>
+      <c r="T443" s="3" t="n">
+        <v>0.0001565312671205467</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -26231,6 +28895,12 @@
       <c r="R444" s="3" t="n">
         <v>0.00812794965915044</v>
       </c>
+      <c r="S444" s="1" t="n">
+        <v>0.011541</v>
+      </c>
+      <c r="T444" s="3" t="n">
+        <v>0.0005201560468139629</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -26289,6 +28959,12 @@
       <c r="R445" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S445" s="1" t="n">
+        <v>0.08087999999999999</v>
+      </c>
+      <c r="T445" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -26347,6 +29023,12 @@
       <c r="R446" s="3" t="n">
         <v>0.0009456264775413942</v>
       </c>
+      <c r="S446" s="1" t="n">
+        <v>0.0002116</v>
+      </c>
+      <c r="T446" s="2" t="n">
+        <v>-0.000472366556447815</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -26405,6 +29087,12 @@
       <c r="R447" s="3" t="n">
         <v>0.01531393568147004</v>
       </c>
+      <c r="S447" s="1" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="T447" s="2" t="n">
+        <v>-0.001508295625942623</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -26463,6 +29151,12 @@
       <c r="R448" s="2" t="n">
         <v>-0.006900259879917492</v>
       </c>
+      <c r="S448" s="1" t="n">
+        <v>0.10054</v>
+      </c>
+      <c r="T448" s="2" t="n">
+        <v>-0.092763039162606</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -26521,6 +29215,12 @@
       <c r="R449" s="2" t="n">
         <v>-0.0005934718100890995</v>
       </c>
+      <c r="S449" s="1" t="n">
+        <v>0.001682</v>
+      </c>
+      <c r="T449" s="2" t="n">
+        <v>-0.001187648456057036</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -26579,6 +29279,12 @@
       <c r="R450" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S450" s="1" t="n">
+        <v>0.0002066</v>
+      </c>
+      <c r="T450" s="2" t="n">
+        <v>-0.000483792936623137</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -26637,6 +29343,12 @@
       <c r="R451" s="2" t="n">
         <v>-0.008292499057670653</v>
       </c>
+      <c r="S451" s="1" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="T451" s="3" t="n">
+        <v>0.001900418091980263</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -26695,6 +29407,12 @@
       <c r="R452" s="2" t="n">
         <v>-0.002227171492204861</v>
       </c>
+      <c r="S452" s="1" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="T452" s="2" t="n">
+        <v>-0.0007440476190475371</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -26753,6 +29471,12 @@
       <c r="R453" s="2" t="n">
         <v>-0.0005711022272987004</v>
       </c>
+      <c r="S453" s="1" t="n">
+        <v>0.0001749</v>
+      </c>
+      <c r="T453" s="2" t="n">
+        <v>-0.0005714285714285853</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -26811,6 +29535,12 @@
       <c r="R454" s="2" t="n">
         <v>-0.001187974047336243</v>
       </c>
+      <c r="S454" s="1" t="n">
+        <v>0.10886</v>
+      </c>
+      <c r="T454" s="2" t="n">
+        <v>-0.004025617566331162</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -26869,6 +29599,12 @@
       <c r="R455" s="3" t="n">
         <v>0.002393776181926948</v>
       </c>
+      <c r="S455" s="1" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="T455" s="2" t="n">
+        <v>-0.002587064676616852</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -26927,6 +29663,12 @@
       <c r="R456" s="2" t="n">
         <v>-0.0002504225881174814</v>
       </c>
+      <c r="S456" s="1" t="n">
+        <v>0.015972</v>
+      </c>
+      <c r="T456" s="3" t="n">
+        <v>0.0001878639864737636</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -26985,6 +29727,12 @@
       <c r="R457" s="2" t="n">
         <v>-0.002385567317727805</v>
       </c>
+      <c r="S457" s="1" t="n">
+        <v>0.006706</v>
+      </c>
+      <c r="T457" s="3" t="n">
+        <v>0.002241817366611905</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -27043,6 +29791,12 @@
       <c r="R458" s="2" t="n">
         <v>-0.001038205980066331</v>
       </c>
+      <c r="S458" s="1" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="T458" s="2" t="n">
+        <v>-0.0004157139887757919</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -27101,6 +29855,12 @@
       <c r="R459" s="2" t="n">
         <v>-0.001411764705882268</v>
       </c>
+      <c r="S459" s="1" t="n">
+        <v>0.006368</v>
+      </c>
+      <c r="T459" s="3" t="n">
+        <v>0.0003141690229343804</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -27159,6 +29919,12 @@
       <c r="R460" s="3" t="n">
         <v>0.0007235890014472992</v>
       </c>
+      <c r="S460" s="1" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="T460" s="2" t="n">
+        <v>-0.001446131597975457</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -27217,6 +29983,12 @@
       <c r="R461" s="3" t="n">
         <v>0.003013392857142928</v>
       </c>
+      <c r="S461" s="1" t="n">
+        <v>0.09132999999999999</v>
+      </c>
+      <c r="T461" s="3" t="n">
+        <v>0.01624568821631233</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -27275,6 +30047,12 @@
       <c r="R462" s="3" t="n">
         <v>0.004354452427607202</v>
       </c>
+      <c r="S462" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="T462" s="2" t="n">
+        <v>-0.002818122696726603</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -27333,6 +30111,12 @@
       <c r="R463" s="2" t="n">
         <v>-0.001430615164520686</v>
       </c>
+      <c r="S463" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="T463" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -27391,6 +30175,12 @@
       <c r="R464" s="3" t="n">
         <v>0.0007621951219511355</v>
       </c>
+      <c r="S464" s="1" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="T464" s="2" t="n">
+        <v>-0.001523229246001525</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -27449,6 +30239,12 @@
       <c r="R465" s="2" t="n">
         <v>-0.001766784452296821</v>
       </c>
+      <c r="S465" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="T465" s="3" t="n">
+        <v>0.0003539823008851133</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -27507,6 +30303,12 @@
       <c r="R466" s="2" t="n">
         <v>-0.001406469760900142</v>
       </c>
+      <c r="S466" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T466" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -27565,6 +30367,12 @@
       <c r="R467" s="2" t="n">
         <v>-0.00261233019853717</v>
       </c>
+      <c r="S467" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="T467" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -27623,6 +30431,12 @@
       <c r="R468" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S468" s="1" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="T468" s="3" t="n">
+        <v>0.007014028056112287</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -27681,6 +30495,12 @@
       <c r="R469" s="2" t="n">
         <v>-0.001739130434782693</v>
       </c>
+      <c r="S469" s="1" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="T469" s="2" t="n">
+        <v>-0.002986560477849624</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -27739,6 +30559,12 @@
       <c r="R470" s="2" t="n">
         <v>-0.001132502831257079</v>
       </c>
+      <c r="S470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="T470" s="2" t="n">
+        <v>-0.001133786848072563</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -27797,6 +30623,12 @@
       <c r="R471" s="2" t="n">
         <v>-0.0009276437847866771</v>
       </c>
+      <c r="S471" s="1" t="n">
+        <v>3.229</v>
+      </c>
+      <c r="T471" s="2" t="n">
+        <v>-0.0006190034045186567</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -27855,6 +30687,12 @@
       <c r="R472" s="3" t="n">
         <v>0.005316578057032333</v>
       </c>
+      <c r="S472" s="1" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="T472" s="3" t="n">
+        <v>0.004326923076923068</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -27913,6 +30751,12 @@
       <c r="R473" s="3" t="n">
         <v>0.0007987220447283465</v>
       </c>
+      <c r="S473" s="1" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="T473" s="2" t="n">
+        <v>-0.0007980845969671908</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -27971,6 +30815,12 @@
       <c r="R474" s="2" t="n">
         <v>-0.0002341920374707571</v>
       </c>
+      <c r="S474" s="1" t="n">
+        <v>0.008541</v>
+      </c>
+      <c r="T474" s="3" t="n">
+        <v>0.0003513703443428825</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -28029,6 +30879,12 @@
       <c r="R475" s="2" t="n">
         <v>-0.003352490421455968</v>
       </c>
+      <c r="S475" s="1" t="n">
+        <v>0.04173</v>
+      </c>
+      <c r="T475" s="3" t="n">
+        <v>0.002642960115329311</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -28087,6 +30943,12 @@
       <c r="R476" s="3" t="n">
         <v>0.0007606490872209763</v>
       </c>
+      <c r="S476" s="1" t="n">
+        <v>0.07883</v>
+      </c>
+      <c r="T476" s="2" t="n">
+        <v>-0.00139346338991638</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -28145,6 +31007,12 @@
       <c r="R477" s="3" t="n">
         <v>0.001755669348939415</v>
       </c>
+      <c r="S477" s="1" t="n">
+        <v>0.13661</v>
+      </c>
+      <c r="T477" s="2" t="n">
+        <v>-0.002409814517306827</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -28203,6 +31071,12 @@
       <c r="R478" s="2" t="n">
         <v>-0.00126182965299694</v>
       </c>
+      <c r="S478" s="1" t="n">
+        <v>0.04747</v>
+      </c>
+      <c r="T478" s="2" t="n">
+        <v>-0.0004211412929037521</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -28261,6 +31135,12 @@
       <c r="R479" s="2" t="n">
         <v>-0.002449594874693799</v>
       </c>
+      <c r="S479" s="1" t="n">
+        <v>0.00531</v>
+      </c>
+      <c r="T479" s="3" t="n">
+        <v>0.003022289384208448</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -28319,6 +31199,12 @@
       <c r="R480" s="3" t="n">
         <v>0.001076812634601461</v>
       </c>
+      <c r="S480" s="1" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="T480" s="3" t="n">
+        <v>0.00250986016493379</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -28377,6 +31263,12 @@
       <c r="R481" s="3" t="n">
         <v>0.0002636435539151875</v>
       </c>
+      <c r="S481" s="1" t="n">
+        <v>0.07587000000000001</v>
+      </c>
+      <c r="T481" s="2" t="n">
+        <v>-0.0001317870321559848</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -28435,6 +31327,12 @@
       <c r="R482" s="3" t="n">
         <v>0.001350438892640053</v>
       </c>
+      <c r="S482" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="T482" s="3" t="n">
+        <v>0.002022926500337189</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -28493,6 +31391,12 @@
       <c r="R483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="T483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -28551,6 +31455,12 @@
       <c r="R484" s="2" t="n">
         <v>-0.002776492364646044</v>
       </c>
+      <c r="S484" s="1" t="n">
+        <v>0.02155</v>
+      </c>
+      <c r="T484" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -28609,6 +31519,12 @@
       <c r="R485" s="2" t="n">
         <v>-0.01190046880634693</v>
       </c>
+      <c r="S485" s="1" t="n">
+        <v>0.008298</v>
+      </c>
+      <c r="T485" s="3" t="n">
+        <v>0.009489051094890504</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -28667,6 +31583,12 @@
       <c r="R486" s="3" t="n">
         <v>0.0005361211633829957</v>
       </c>
+      <c r="S486" s="1" t="n">
+        <v>0.007467</v>
+      </c>
+      <c r="T486" s="3" t="n">
+        <v>0.0002679169457467379</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -28725,6 +31647,12 @@
       <c r="R487" s="3" t="n">
         <v>0.002692998204667816</v>
       </c>
+      <c r="S487" s="1" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="T487" s="2" t="n">
+        <v>-0.0008952551477170008</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -28783,6 +31711,12 @@
       <c r="R488" s="2" t="n">
         <v>-0.001388147357181085</v>
       </c>
+      <c r="S488" s="1" t="n">
+        <v>0.00936</v>
+      </c>
+      <c r="T488" s="3" t="n">
+        <v>0.0008554319931566576</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -28841,6 +31775,12 @@
       <c r="R489" s="3" t="n">
         <v>0.001556824078879203</v>
       </c>
+      <c r="S489" s="1" t="n">
+        <v>0.03846</v>
+      </c>
+      <c r="T489" s="2" t="n">
+        <v>-0.003626943005181379</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -28899,6 +31839,12 @@
       <c r="R490" s="3" t="n">
         <v>0.001023716089404497</v>
       </c>
+      <c r="S490" s="1" t="n">
+        <v>0.05853</v>
+      </c>
+      <c r="T490" s="2" t="n">
+        <v>-0.002386228055224156</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -28957,6 +31903,12 @@
       <c r="R491" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S491" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="T491" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -29015,6 +31967,12 @@
       <c r="R492" s="2" t="n">
         <v>-0.0007518796992482044</v>
       </c>
+      <c r="S492" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T492" s="3" t="n">
+        <v>0.0007524454477051256</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -29073,6 +32031,12 @@
       <c r="R493" s="2" t="n">
         <v>-0.002265647125460314</v>
       </c>
+      <c r="S493" s="1" t="n">
+        <v>0.03528</v>
+      </c>
+      <c r="T493" s="3" t="n">
+        <v>0.001419244961680427</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -29131,6 +32095,12 @@
       <c r="R494" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S494" s="1" t="n">
+        <v>0.01711</v>
+      </c>
+      <c r="T494" s="2" t="n">
+        <v>-0.002913752913752997</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -29189,6 +32159,12 @@
       <c r="R495" s="2" t="n">
         <v>-0.003585741404767</v>
       </c>
+      <c r="S495" s="1" t="n">
+        <v>0.04725</v>
+      </c>
+      <c r="T495" s="3" t="n">
+        <v>0.0002116850127011656</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -29247,6 +32223,12 @@
       <c r="R496" s="3" t="n">
         <v>0.001449275362318853</v>
       </c>
+      <c r="S496" s="1" t="n">
+        <v>0.04814</v>
+      </c>
+      <c r="T496" s="2" t="n">
+        <v>-0.004755013438081476</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -29305,6 +32287,12 @@
       <c r="R497" s="2" t="n">
         <v>-0.0008048289738430256</v>
       </c>
+      <c r="S497" s="1" t="n">
+        <v>0.04966</v>
+      </c>
+      <c r="T497" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -29363,6 +32351,12 @@
       <c r="R498" s="2" t="n">
         <v>-0.001384083044982547</v>
       </c>
+      <c r="S498" s="1" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="T498" s="3" t="n">
+        <v>0.0006930006930006167</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -29421,6 +32415,12 @@
       <c r="R499" s="2" t="n">
         <v>-0.001831501831501833</v>
       </c>
+      <c r="S499" s="1" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="T499" s="3" t="n">
+        <v>0.0007339449541283595</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -29479,6 +32479,12 @@
       <c r="R500" s="2" t="n">
         <v>-0.003745318352059935</v>
       </c>
+      <c r="S500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="T500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -29537,6 +32543,12 @@
       <c r="R501" s="2" t="n">
         <v>-0.004732739420935509</v>
       </c>
+      <c r="S501" s="1" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="T501" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -29595,6 +32607,12 @@
       <c r="R502" s="3" t="n">
         <v>0.001255098839033523</v>
       </c>
+      <c r="S502" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="T502" s="2" t="n">
+        <v>-0.001253525540582838</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -29653,6 +32671,12 @@
       <c r="R503" s="2" t="n">
         <v>-0.003101977510663011</v>
       </c>
+      <c r="S503" s="1" t="n">
+        <v>0.007741</v>
+      </c>
+      <c r="T503" s="3" t="n">
+        <v>0.003630234668741006</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -29711,6 +32735,12 @@
       <c r="R504" s="2" t="n">
         <v>-0.0003244646333549286</v>
       </c>
+      <c r="S504" s="1" t="n">
+        <v>3.074</v>
+      </c>
+      <c r="T504" s="2" t="n">
+        <v>-0.002271989613761804</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -29769,6 +32799,12 @@
       <c r="R505" s="3" t="n">
         <v>0.001618996222342187</v>
       </c>
+      <c r="S505" s="1" t="n">
+        <v>0.0007379</v>
+      </c>
+      <c r="T505" s="2" t="n">
+        <v>-0.006061422413793177</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -29827,6 +32863,12 @@
       <c r="R506" s="2" t="n">
         <v>-0.003371544167228594</v>
       </c>
+      <c r="S506" s="1" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="T506" s="2" t="n">
+        <v>-0.001014884979702189</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -29885,6 +32927,12 @@
       <c r="R507" s="2" t="n">
         <v>-0.001753155680224333</v>
       </c>
+      <c r="S507" s="1" t="n">
+        <v>0.002838</v>
+      </c>
+      <c r="T507" s="2" t="n">
+        <v>-0.003161222339304646</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -29943,6 +32991,12 @@
       <c r="R508" s="3" t="n">
         <v>0.0003155071777881723</v>
       </c>
+      <c r="S508" s="1" t="n">
+        <v>0.06339</v>
+      </c>
+      <c r="T508" s="2" t="n">
+        <v>-0.0003154076644061228</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -30001,6 +33055,12 @@
       <c r="R509" s="3" t="n">
         <v>0.0008892841262782479</v>
       </c>
+      <c r="S509" s="1" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="T509" s="2" t="n">
+        <v>-0.0008884940026653842</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -30059,6 +33119,12 @@
       <c r="R510" s="2" t="n">
         <v>-0.0005459260270233516</v>
       </c>
+      <c r="S510" s="1" t="n">
+        <v>0.0007327</v>
+      </c>
+      <c r="T510" s="3" t="n">
+        <v>0.000546224225044394</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -30117,6 +33183,12 @@
       <c r="R511" s="2" t="n">
         <v>-0.0003616636528030542</v>
       </c>
+      <c r="S511" s="1" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="T511" s="3" t="n">
+        <v>0.001085383502170848</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -30175,6 +33247,12 @@
       <c r="R512" s="3" t="n">
         <v>0.003723624327678919</v>
       </c>
+      <c r="S512" s="1" t="n">
+        <v>0.0004838</v>
+      </c>
+      <c r="T512" s="2" t="n">
+        <v>-0.00288540807914258</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -30233,6 +33311,12 @@
       <c r="R513" s="3" t="n">
         <v>0.0007217610970769633</v>
       </c>
+      <c r="S513" s="1" t="n">
+        <v>0.05558</v>
+      </c>
+      <c r="T513" s="3" t="n">
+        <v>0.002163721601153897</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -30291,6 +33375,12 @@
       <c r="R514" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S514" s="1" t="n">
+        <v>0.03033</v>
+      </c>
+      <c r="T514" s="2" t="n">
+        <v>-0.0009881422924901925</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -30349,6 +33439,12 @@
       <c r="R515" s="2" t="n">
         <v>-0.001748251748251791</v>
       </c>
+      <c r="S515" s="1" t="n">
+        <v>0.001142</v>
+      </c>
+      <c r="T515" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -30407,6 +33503,12 @@
       <c r="R516" s="2" t="n">
         <v>-0.001357670840247447</v>
       </c>
+      <c r="S516" s="1" t="n">
+        <v>0.006621</v>
+      </c>
+      <c r="T516" s="3" t="n">
+        <v>0.0001510574018127089</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -30465,6 +33567,12 @@
       <c r="R517" s="2" t="n">
         <v>-0.0002507522567702137</v>
       </c>
+      <c r="S517" s="1" t="n">
+        <v>0.03983</v>
+      </c>
+      <c r="T517" s="2" t="n">
+        <v>-0.001003260596940188</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -30523,6 +33631,12 @@
       <c r="R518" s="2" t="n">
         <v>-0.0009718172983479384</v>
       </c>
+      <c r="S518" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="T518" s="3" t="n">
+        <v>0.001945525291828714</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -30581,6 +33695,12 @@
       <c r="R519" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S519" s="1" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="T519" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -30639,6 +33759,12 @@
       <c r="R520" s="3" t="n">
         <v>0.001249219237976301</v>
       </c>
+      <c r="S520" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="T520" s="2" t="n">
+        <v>-0.004990642545227668</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -30697,6 +33823,12 @@
       <c r="R521" s="3" t="n">
         <v>0.0005595970900951087</v>
       </c>
+      <c r="S521" s="1" t="n">
+        <v>0.01792</v>
+      </c>
+      <c r="T521" s="3" t="n">
+        <v>0.002237136465324294</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -30755,6 +33887,12 @@
       <c r="R522" s="2" t="n">
         <v>-0.004255319148936208</v>
       </c>
+      <c r="S522" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="T522" s="3" t="n">
+        <v>0.001221001221001383</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -30813,6 +33951,12 @@
       <c r="R523" s="2" t="n">
         <v>-0.0009562514941428792</v>
       </c>
+      <c r="S523" s="1" t="n">
+        <v>0.004181</v>
+      </c>
+      <c r="T523" s="3" t="n">
+        <v>0.0004785833931561134</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -30871,6 +34015,12 @@
       <c r="R524" s="2" t="n">
         <v>-0.002103786816269321</v>
       </c>
+      <c r="S524" s="1" t="n">
+        <v>0.01419</v>
+      </c>
+      <c r="T524" s="2" t="n">
+        <v>-0.002810962754743507</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -30929,6 +34079,12 @@
       <c r="R525" s="2" t="n">
         <v>-0.0004019292604501444</v>
       </c>
+      <c r="S525" s="1" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="T525" s="3" t="n">
+        <v>0.0008041817450743541</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -30987,6 +34143,12 @@
       <c r="R526" s="2" t="n">
         <v>-0.000829875518672223</v>
       </c>
+      <c r="S526" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="T526" s="2" t="n">
+        <v>-0.0008305647840530648</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -31045,6 +34207,12 @@
       <c r="R527" s="3" t="n">
         <v>0.005307262569832477</v>
       </c>
+      <c r="S527" s="1" t="n">
+        <v>0.07207</v>
+      </c>
+      <c r="T527" s="3" t="n">
+        <v>0.00125034731869954</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -31103,6 +34271,12 @@
       <c r="R528" s="2" t="n">
         <v>-0.001613646841862624</v>
       </c>
+      <c r="S528" s="1" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="T528" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -31161,6 +34335,12 @@
       <c r="R529" s="2" t="n">
         <v>-0.0006345177664974361</v>
       </c>
+      <c r="S529" s="1" t="n">
+        <v>0.06307</v>
+      </c>
+      <c r="T529" s="3" t="n">
+        <v>0.001111111111111121</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -31219,6 +34399,12 @@
       <c r="R530" s="2" t="n">
         <v>-0.002584493041749501</v>
       </c>
+      <c r="S530" s="1" t="n">
+        <v>0.005019</v>
+      </c>
+      <c r="T530" s="3" t="n">
+        <v>0.0003986446083317252</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -31277,6 +34463,12 @@
       <c r="R531" s="2" t="n">
         <v>-0.00460122699386495</v>
       </c>
+      <c r="S531" s="1" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="T531" s="2" t="n">
+        <v>-0.003852080123266567</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -31335,6 +34527,12 @@
       <c r="R532" s="2" t="n">
         <v>-0.000935103796521311</v>
       </c>
+      <c r="S532" s="1" t="n">
+        <v>0.05331</v>
+      </c>
+      <c r="T532" s="2" t="n">
+        <v>-0.002059153874953182</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -31393,6 +34591,12 @@
       <c r="R533" s="2" t="n">
         <v>-0.008778930566640074</v>
       </c>
+      <c r="S533" s="1" t="n">
+        <v>0.003742</v>
+      </c>
+      <c r="T533" s="3" t="n">
+        <v>0.004294149221685441</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -31451,6 +34655,12 @@
       <c r="R534" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S534" s="1" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="T534" s="2" t="n">
+        <v>-0.001164144353899917</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -31509,6 +34719,12 @@
       <c r="R535" s="2" t="n">
         <v>-0.00884955752212396</v>
       </c>
+      <c r="S535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="T535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -31567,6 +34783,12 @@
       <c r="R536" s="2" t="n">
         <v>-0.004263913824057433</v>
       </c>
+      <c r="S536" s="1" t="n">
+        <v>0.0004436</v>
+      </c>
+      <c r="T536" s="2" t="n">
+        <v>-0.0002253775073247745</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -31625,6 +34847,12 @@
       <c r="R537" s="2" t="n">
         <v>-0.002061855670103187</v>
       </c>
+      <c r="S537" s="1" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="T537" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -31683,6 +34911,12 @@
       <c r="R538" s="2" t="n">
         <v>-0.001095890410958859</v>
       </c>
+      <c r="S538" s="1" t="n">
+        <v>0.05463</v>
+      </c>
+      <c r="T538" s="2" t="n">
+        <v>-0.001097092704333598</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -31741,6 +34975,12 @@
       <c r="R539" s="3" t="n">
         <v>0.0004398182084737824</v>
       </c>
+      <c r="S539" s="1" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="T539" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -31799,6 +35039,12 @@
       <c r="R540" s="2" t="n">
         <v>-0.002638522427440709</v>
       </c>
+      <c r="S540" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="T540" s="3" t="n">
+        <v>0.0006613756613755885</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -31857,6 +35103,12 @@
       <c r="R541" s="2" t="n">
         <v>-0.003046458492003055</v>
       </c>
+      <c r="S541" s="1" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="T541" s="2" t="n">
+        <v>-0.002291825821237493</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -31915,6 +35167,12 @@
       <c r="R542" s="3" t="n">
         <v>0.005743000717875105</v>
       </c>
+      <c r="S542" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="T542" s="2" t="n">
+        <v>-0.004996431120628167</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -31972,6 +35230,12 @@
       </c>
       <c r="R543" s="2" t="n">
         <v>-0.002267969295185016</v>
+      </c>
+      <c r="S543" s="1" t="n">
+        <v>0.05718</v>
+      </c>
+      <c r="T543" s="2" t="n">
+        <v>-0.000174855744011123</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V543"/>
+  <dimension ref="A1:X543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,8 @@
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,6 +563,16 @@
           <t>change_02:30</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>price_02:45</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>change_02:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -631,6 +643,12 @@
       <c r="V2" s="2" t="n">
         <v>-0.002631305118786547</v>
       </c>
+      <c r="W2" s="1" t="n">
+        <v>69890.10000000001</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.001151910728347598</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,6 +719,12 @@
       <c r="V3" s="2" t="n">
         <v>-0.002047764969113301</v>
       </c>
+      <c r="W3" s="1" t="n">
+        <v>2052.74</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>0.0005117732211005206</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +795,12 @@
       <c r="V4" s="2" t="n">
         <v>-0.004279435577145389</v>
       </c>
+      <c r="W4" s="1" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.0009292600766639365</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -841,6 +871,12 @@
       <c r="V5" s="3" t="n">
         <v>0.004765535646206605</v>
       </c>
+      <c r="W5" s="1" t="n">
+        <v>0.010548</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>0.0005691519635743499</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -911,6 +947,12 @@
       <c r="V6" s="2" t="n">
         <v>-0.002031782889485622</v>
       </c>
+      <c r="W6" s="1" t="n">
+        <v>1.3738</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.001090671126299758</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -981,6 +1023,12 @@
       <c r="V7" s="2" t="n">
         <v>-0.001380188979721746</v>
       </c>
+      <c r="W7" s="1" t="n">
+        <v>0.09392</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.001488411652136947</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1051,6 +1099,12 @@
       <c r="V8" s="2" t="n">
         <v>-0.0003735325506935911</v>
       </c>
+      <c r="W8" s="1" t="n">
+        <v>37.162</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.008114023381199008</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1121,6 +1175,12 @@
       <c r="V9" s="3" t="n">
         <v>0.00649614291514415</v>
       </c>
+      <c r="W9" s="1" t="n">
+        <v>0.04948</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.002016942315449696</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1191,6 +1251,12 @@
       <c r="V10" s="2" t="n">
         <v>-0.001497646555413042</v>
       </c>
+      <c r="W10" s="1" t="n">
+        <v>18.378</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.01553460467109488</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1261,6 +1327,12 @@
       <c r="V11" s="2" t="n">
         <v>-0.002518620901481972</v>
       </c>
+      <c r="W11" s="1" t="n">
+        <v>648.8099999999999</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>-0.001077735523702553</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1331,6 +1403,12 @@
       <c r="V12" s="2" t="n">
         <v>-0.008223872073101067</v>
       </c>
+      <c r="W12" s="1" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>-0.001842681101001883</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1401,6 +1479,12 @@
       <c r="V13" s="3" t="n">
         <v>0.0004746535029428247</v>
       </c>
+      <c r="W13" s="1" t="n">
+        <v>209.81</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>-0.004601954644653188</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1471,6 +1555,12 @@
       <c r="V14" s="3" t="n">
         <v>0.0006626705623663197</v>
       </c>
+      <c r="W14" s="1" t="n">
+        <v>0.0033218</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>-9.030432557718103e-05</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1541,6 +1631,12 @@
       <c r="V15" s="3" t="n">
         <v>0.04535034386524468</v>
       </c>
+      <c r="W15" s="1" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>-0.003845664886854783</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1611,6 +1707,12 @@
       <c r="V16" s="3" t="n">
         <v>0.000924594205876322</v>
       </c>
+      <c r="W16" s="1" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>-0.001436929077286326</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1681,6 +1783,12 @@
       <c r="V17" s="3" t="n">
         <v>0.003597122302158377</v>
       </c>
+      <c r="W17" s="1" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>0.02150537634408602</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1751,6 +1859,12 @@
       <c r="V18" s="2" t="n">
         <v>-0.001266773013042985</v>
       </c>
+      <c r="W18" s="1" t="n">
+        <v>211.1</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>-0.00831493399727538</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1821,6 +1935,12 @@
       <c r="V19" s="2" t="n">
         <v>-0.001908396946564887</v>
       </c>
+      <c r="W19" s="1" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>-0.0007648183556406634</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1891,6 +2011,12 @@
       <c r="V20" s="3" t="n">
         <v>0.001291458761373508</v>
       </c>
+      <c r="W20" s="1" t="n">
+        <v>0.017105</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>0.00281409392038456</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1961,6 +2087,12 @@
       <c r="V21" s="3" t="n">
         <v>0.0001045041279129946</v>
       </c>
+      <c r="W21" s="1" t="n">
+        <v>9.554</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>-0.001671891327063742</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2031,6 +2163,12 @@
       <c r="V22" s="3" t="n">
         <v>0.005353955978584247</v>
       </c>
+      <c r="W22" s="1" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>-0.001183431952662756</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2101,6 +2239,12 @@
       <c r="V23" s="2" t="n">
         <v>-0.007205264949506373</v>
       </c>
+      <c r="W23" s="1" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>-0.006000342876735787</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2171,6 +2315,12 @@
       <c r="V24" s="3" t="n">
         <v>0.002317497103128623</v>
       </c>
+      <c r="W24" s="1" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.002312138728323701</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2241,6 +2391,12 @@
       <c r="V25" s="3" t="n">
         <v>0.0003331482509714977</v>
       </c>
+      <c r="W25" s="1" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>-0.001998223801065598</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2311,6 +2467,12 @@
       <c r="V26" s="2" t="n">
         <v>-0.00669642857142866</v>
       </c>
+      <c r="W26" s="1" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2381,6 +2543,12 @@
       <c r="V27" s="2" t="n">
         <v>-0.0002877123346388534</v>
       </c>
+      <c r="W27" s="1" t="n">
+        <v>5102.51</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>-0.001035670934648961</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2451,6 +2619,12 @@
       <c r="V28" s="3" t="n">
         <v>0.001685393258426937</v>
       </c>
+      <c r="W28" s="1" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>-0.002243409983174334</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2521,6 +2695,12 @@
       <c r="V29" s="2" t="n">
         <v>-0.001145475372279539</v>
       </c>
+      <c r="W29" s="1" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>0.001529051987767585</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2591,6 +2771,12 @@
       <c r="V30" s="2" t="n">
         <v>-0.0008079672597615021</v>
       </c>
+      <c r="W30" s="1" t="n">
+        <v>0.56326</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>-0.009861655562782365</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2661,6 +2847,12 @@
       <c r="V31" s="2" t="n">
         <v>-0.0009569377990429818</v>
       </c>
+      <c r="W31" s="1" t="n">
+        <v>0.002079</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>-0.004310344827586156</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2731,6 +2923,12 @@
       <c r="V32" s="2" t="n">
         <v>-0.003167735455458543</v>
       </c>
+      <c r="W32" s="1" t="n">
+        <v>1.2963</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0.004727949155169737</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2801,6 +2999,12 @@
       <c r="V33" s="3" t="n">
         <v>0.02626018714156366</v>
       </c>
+      <c r="W33" s="1" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>-0.002352941176470655</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2871,6 +3075,12 @@
       <c r="V34" s="3" t="n">
         <v>0.002680965147453085</v>
       </c>
+      <c r="W34" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>0.002673796791443853</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2941,6 +3151,12 @@
       <c r="V35" s="3" t="n">
         <v>0.001276717515243532</v>
       </c>
+      <c r="W35" s="1" t="n">
+        <v>455.38</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>0.001121199463582982</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3011,6 +3227,12 @@
       <c r="V36" s="3" t="n">
         <v>0.002090301003344541</v>
       </c>
+      <c r="W36" s="1" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>0.003337505214851762</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3081,6 +3303,12 @@
       <c r="V37" s="2" t="n">
         <v>-0.0005664919983004616</v>
       </c>
+      <c r="W37" s="1" t="n">
+        <v>0.7050999999999999</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>-0.0008502196400737494</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3151,6 +3379,12 @@
       <c r="V38" s="2" t="n">
         <v>-0.001893939393939448</v>
       </c>
+      <c r="W38" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>-0.002846299810246629</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3221,6 +3455,12 @@
       <c r="V39" s="3" t="n">
         <v>0.00475189618934475</v>
       </c>
+      <c r="W39" s="1" t="n">
+        <v>109.78</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>-0.001546157344247401</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3291,6 +3531,12 @@
       <c r="V40" s="2" t="n">
         <v>-0.00633412509897063</v>
       </c>
+      <c r="W40" s="1" t="n">
+        <v>0.03772</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>0.001859229747675795</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3361,6 +3607,12 @@
       <c r="V41" s="3" t="n">
         <v>0.001275510204081644</v>
       </c>
+      <c r="W41" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="X41" s="2" t="n">
+        <v>-0.001273885350318483</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3431,6 +3683,12 @@
       <c r="V42" s="3" t="n">
         <v>0.001108647450110907</v>
       </c>
+      <c r="W42" s="1" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>0.001661129568106375</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3501,6 +3759,12 @@
       <c r="V43" s="3" t="n">
         <v>0.001518602885345315</v>
       </c>
+      <c r="W43" s="1" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.001516300227445078</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3571,6 +3835,12 @@
       <c r="V44" s="2" t="n">
         <v>-0.0001695489996607775</v>
       </c>
+      <c r="W44" s="1" t="n">
+        <v>0.005866</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>-0.005256910293369619</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3641,6 +3911,12 @@
       <c r="V45" s="3" t="n">
         <v>0.0007937295366603506</v>
       </c>
+      <c r="W45" s="1" t="n">
+        <v>0.10026</v>
+      </c>
+      <c r="X45" s="2" t="n">
+        <v>-0.006047387726777034</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3711,6 +3987,12 @@
       <c r="V46" s="3" t="n">
         <v>0.001076426264800902</v>
       </c>
+      <c r="W46" s="1" t="n">
+        <v>2.786</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>-0.001433691756272403</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3781,6 +4063,12 @@
       <c r="V47" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W47" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>0.0004846638510003929</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3851,6 +4139,12 @@
       <c r="V48" s="3" t="n">
         <v>0.004686035613870669</v>
       </c>
+      <c r="W48" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>0.000932835820895549</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3921,6 +4215,12 @@
       <c r="V49" s="2" t="n">
         <v>-0.005817737998372608</v>
       </c>
+      <c r="W49" s="1" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>0.006015468347178455</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3991,6 +4291,12 @@
       <c r="V50" s="3" t="n">
         <v>0.005279831045406551</v>
       </c>
+      <c r="W50" s="1" t="n">
+        <v>0.04792</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>0.006722689075630123</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4061,6 +4367,12 @@
       <c r="V51" s="3" t="n">
         <v>0.001797175866495537</v>
       </c>
+      <c r="W51" s="1" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>-0.00307534597642235</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4131,6 +4443,12 @@
       <c r="V52" s="2" t="n">
         <v>-0.004329004329004317</v>
       </c>
+      <c r="W52" s="1" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4201,6 +4519,12 @@
       <c r="V53" s="3" t="n">
         <v>0.001196172248803862</v>
       </c>
+      <c r="W53" s="1" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="X53" s="2" t="n">
+        <v>-0.00179211469534047</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4271,6 +4595,12 @@
       <c r="V54" s="3" t="n">
         <v>0.001190759704691627</v>
       </c>
+      <c r="W54" s="1" t="n">
+        <v>0.04234</v>
+      </c>
+      <c r="X54" s="3" t="n">
+        <v>0.007136060894386338</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4341,6 +4671,12 @@
       <c r="V55" s="2" t="n">
         <v>-0.01715705924797554</v>
       </c>
+      <c r="W55" s="1" t="n">
+        <v>0.12137</v>
+      </c>
+      <c r="X55" s="2" t="n">
+        <v>-0.009951872093971767</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4411,6 +4747,12 @@
       <c r="V56" s="2" t="n">
         <v>-0.006645569620253135</v>
       </c>
+      <c r="W56" s="1" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>0.007645747053201699</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4481,6 +4823,12 @@
       <c r="V57" s="2" t="n">
         <v>-0.003430531732418534</v>
       </c>
+      <c r="W57" s="1" t="n">
+        <v>0.01158</v>
+      </c>
+      <c r="X57" s="2" t="n">
+        <v>-0.003442340791738391</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4551,6 +4899,12 @@
       <c r="V58" s="3" t="n">
         <v>0.001010101010100899</v>
       </c>
+      <c r="W58" s="1" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="X58" s="3" t="n">
+        <v>0.001009081735620614</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4621,6 +4975,12 @@
       <c r="V59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W59" s="1" t="n">
+        <v>0.00332</v>
+      </c>
+      <c r="X59" s="2" t="n">
+        <v>-0.003003003003003011</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4691,6 +5051,12 @@
       <c r="V60" s="2" t="n">
         <v>-0.001297858533419714</v>
       </c>
+      <c r="W60" s="1" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="X60" s="2" t="n">
+        <v>-0.001949317738791569</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4761,6 +5127,12 @@
       <c r="V61" s="2" t="n">
         <v>-0.00294726280805166</v>
       </c>
+      <c r="W61" s="1" t="n">
+        <v>0.15908</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>0.0005031446540880298</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4831,6 +5203,12 @@
       <c r="V62" s="2" t="n">
         <v>-0.0007052186177714315</v>
       </c>
+      <c r="W62" s="1" t="n">
+        <v>0.7057</v>
+      </c>
+      <c r="X62" s="2" t="n">
+        <v>-0.003952011291460868</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4901,6 +5279,12 @@
       <c r="V63" s="3" t="n">
         <v>0.0006868131868132637</v>
       </c>
+      <c r="W63" s="1" t="n">
+        <v>5.904</v>
+      </c>
+      <c r="X63" s="3" t="n">
+        <v>0.01304049416609465</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4971,6 +5355,12 @@
       <c r="V64" s="2" t="n">
         <v>-0.002237136465324439</v>
       </c>
+      <c r="W64" s="1" t="n">
+        <v>0.007121</v>
+      </c>
+      <c r="X64" s="2" t="n">
+        <v>-0.002102017937219767</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5041,6 +5431,12 @@
       <c r="V65" s="3" t="n">
         <v>0.01620591039084854</v>
       </c>
+      <c r="W65" s="1" t="n">
+        <v>0.03199</v>
+      </c>
+      <c r="X65" s="3" t="n">
+        <v>0.0003126954346465329</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5111,6 +5507,12 @@
       <c r="V66" s="2" t="n">
         <v>-0.004255319148936056</v>
       </c>
+      <c r="W66" s="1" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="X66" s="2" t="n">
+        <v>-0.004273504273504277</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5181,6 +5583,12 @@
       <c r="V67" s="2" t="n">
         <v>-0.009882643607164926</v>
       </c>
+      <c r="W67" s="1" t="n">
+        <v>1.598</v>
+      </c>
+      <c r="X67" s="2" t="n">
+        <v>-0.003119151590767245</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5251,6 +5659,12 @@
       <c r="V68" s="3" t="n">
         <v>0.003243836710250499</v>
       </c>
+      <c r="W68" s="1" t="n">
+        <v>2.0081</v>
+      </c>
+      <c r="X68" s="2" t="n">
+        <v>-0.00109436402526974</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5321,6 +5735,12 @@
       <c r="V69" s="3" t="n">
         <v>0.001736714136853076</v>
       </c>
+      <c r="W69" s="1" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>0.007281553398058221</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5391,6 +5811,12 @@
       <c r="V70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="X70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5461,6 +5887,12 @@
       <c r="V71" s="3" t="n">
         <v>0.001433454625647776</v>
       </c>
+      <c r="W71" s="1" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="X71" s="2" t="n">
+        <v>-0.0004404316229904822</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5531,6 +5963,12 @@
       <c r="V72" s="2" t="n">
         <v>-0.0002350176263219483</v>
       </c>
+      <c r="W72" s="1" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="X72" s="2" t="n">
+        <v>-0.003055947343676595</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5601,6 +6039,12 @@
       <c r="V73" s="2" t="n">
         <v>-0.0009580583351074395</v>
       </c>
+      <c r="W73" s="1" t="n">
+        <v>0.09387</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>0.0002131060202449893</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5671,6 +6115,12 @@
       <c r="V74" s="3" t="n">
         <v>0.005881836537617354</v>
       </c>
+      <c r="W74" s="1" t="n">
+        <v>1.1494</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>0.003141909582824269</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5741,6 +6191,12 @@
       <c r="V75" s="2" t="n">
         <v>-0.001880877742946632</v>
       </c>
+      <c r="W75" s="1" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="X75" s="2" t="n">
+        <v>-0.001884422110552687</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5811,6 +6267,12 @@
       <c r="V76" s="3" t="n">
         <v>0.006329621023956295</v>
       </c>
+      <c r="W76" s="1" t="n">
+        <v>0.12676</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>0.009235668789809094</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5881,6 +6343,12 @@
       <c r="V77" s="3" t="n">
         <v>0.002568493150684886</v>
       </c>
+      <c r="W77" s="1" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>0.0008539709649872149</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5951,6 +6419,12 @@
       <c r="V78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W78" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="X78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6021,6 +6495,12 @@
       <c r="V79" s="2" t="n">
         <v>-0.001829065513801229</v>
       </c>
+      <c r="W79" s="1" t="n">
+        <v>0.005991</v>
+      </c>
+      <c r="X79" s="2" t="n">
+        <v>-0.001999000499750101</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6091,6 +6571,12 @@
       <c r="V80" s="2" t="n">
         <v>-0.003649175789606079</v>
       </c>
+      <c r="W80" s="1" t="n">
+        <v>0.007965</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>0.005935842384440537</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6161,6 +6647,12 @@
       <c r="V81" s="2" t="n">
         <v>-0.002794857462269464</v>
       </c>
+      <c r="W81" s="1" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>0.001681614349775849</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6231,6 +6723,12 @@
       <c r="V82" s="2" t="n">
         <v>-0.007384615384615425</v>
       </c>
+      <c r="W82" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="X82" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6301,6 +6799,12 @@
       <c r="V83" s="3" t="n">
         <v>0.001710236989982818</v>
       </c>
+      <c r="W83" s="1" t="n">
+        <v>8.205</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>0.000609756097561071</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6371,6 +6875,12 @@
       <c r="V84" s="3" t="n">
         <v>0.0004251700680271464</v>
       </c>
+      <c r="W84" s="1" t="n">
+        <v>354.09</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>0.003229919252018661</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6441,6 +6951,12 @@
       <c r="V85" s="2" t="n">
         <v>-0.003187055650894825</v>
       </c>
+      <c r="W85" s="1" t="n">
+        <v>0.004072</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>0.001475651746187882</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6511,6 +7027,12 @@
       <c r="V86" s="3" t="n">
         <v>0.006100815984137841</v>
       </c>
+      <c r="W86" s="1" t="n">
+        <v>0.13111</v>
+      </c>
+      <c r="X86" s="2" t="n">
+        <v>-0.006215417266732263</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6581,6 +7103,12 @@
       <c r="V87" s="2" t="n">
         <v>-0.001066098081023411</v>
       </c>
+      <c r="W87" s="1" t="n">
+        <v>0.01898</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>0.01280683030949843</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6651,6 +7179,12 @@
       <c r="V88" s="3" t="n">
         <v>0.002657218777679266</v>
       </c>
+      <c r="W88" s="1" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>0.0008833922261485089</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6721,6 +7255,12 @@
       <c r="V89" s="3" t="n">
         <v>0.001019714479945503</v>
       </c>
+      <c r="W89" s="1" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>0.001018675721562046</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6791,6 +7331,12 @@
       <c r="V90" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W90" s="1" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>0.0003892565200466679</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6861,6 +7407,12 @@
       <c r="V91" s="3" t="n">
         <v>0.009229676961306348</v>
       </c>
+      <c r="W91" s="1" t="n">
+        <v>0.05615</v>
+      </c>
+      <c r="X91" s="2" t="n">
+        <v>-0.01248680970805491</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6931,6 +7483,12 @@
       <c r="V92" s="3" t="n">
         <v>0.001607840134752309</v>
       </c>
+      <c r="W92" s="1" t="n">
+        <v>1.3164</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>0.006268154716404208</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7001,6 +7559,12 @@
       <c r="V93" s="2" t="n">
         <v>-0.001267427122940379</v>
       </c>
+      <c r="W93" s="1" t="n">
+        <v>0.06311</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>0.001110406091370568</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7071,6 +7635,12 @@
       <c r="V94" s="2" t="n">
         <v>-0.002265005662514064</v>
       </c>
+      <c r="W94" s="1" t="n">
+        <v>0.00893</v>
+      </c>
+      <c r="X94" s="3" t="n">
+        <v>0.01362088535754828</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7141,6 +7711,12 @@
       <c r="V95" s="3" t="n">
         <v>0.001202645820805807</v>
       </c>
+      <c r="W95" s="1" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="X95" s="3" t="n">
+        <v>0.001201201201201069</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7211,6 +7787,12 @@
       <c r="V96" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W96" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="X96" s="2" t="n">
+        <v>-0.001769911504424707</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7281,6 +7863,12 @@
       <c r="V97" s="3" t="n">
         <v>0.002150537634408611</v>
       </c>
+      <c r="W97" s="1" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="X97" s="2" t="n">
+        <v>-0.0003065603923972413</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7351,6 +7939,12 @@
       <c r="V98" s="2" t="n">
         <v>-0.000901713255184752</v>
       </c>
+      <c r="W98" s="1" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="X98" s="3" t="n">
+        <v>0.002707581227436725</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7421,6 +8015,12 @@
       <c r="V99" s="3" t="n">
         <v>0.0003330003330002963</v>
       </c>
+      <c r="W99" s="1" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="X99" s="3" t="n">
+        <v>0.001331557922769642</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7491,6 +8091,12 @@
       <c r="V100" s="3" t="n">
         <v>0.002047382275519176</v>
       </c>
+      <c r="W100" s="1" t="n">
+        <v>0.03429</v>
+      </c>
+      <c r="X100" s="3" t="n">
+        <v>0.0008756567425569833</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7561,6 +8167,12 @@
       <c r="V101" s="3" t="n">
         <v>0.003309431880860455</v>
       </c>
+      <c r="W101" s="1" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="X101" s="3" t="n">
+        <v>0.002748763056624583</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7631,6 +8243,12 @@
       <c r="V102" s="3" t="n">
         <v>0.002921413964358758</v>
       </c>
+      <c r="W102" s="1" t="n">
+        <v>0.006968</v>
+      </c>
+      <c r="X102" s="3" t="n">
+        <v>0.01485581124381016</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7701,6 +8319,12 @@
       <c r="V103" s="2" t="n">
         <v>-0.01295028282226868</v>
       </c>
+      <c r="W103" s="1" t="n">
+        <v>0.06639</v>
+      </c>
+      <c r="X103" s="3" t="n">
+        <v>0.001206454531744995</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7771,6 +8395,12 @@
       <c r="V104" s="3" t="n">
         <v>0.0007304601899195689</v>
       </c>
+      <c r="W104" s="1" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="X104" s="2" t="n">
+        <v>-0.0009732360097322529</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7841,6 +8471,12 @@
       <c r="V105" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W105" s="1" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="X105" s="3" t="n">
+        <v>0.00448430493273543</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7911,6 +8547,12 @@
       <c r="V106" s="3" t="n">
         <v>0.01026769343601015</v>
       </c>
+      <c r="W106" s="1" t="n">
+        <v>0.008245000000000001</v>
+      </c>
+      <c r="X106" s="2" t="n">
+        <v>-0.002419842710223737</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7981,6 +8623,12 @@
       <c r="V107" s="3" t="n">
         <v>0.001653803748621763</v>
       </c>
+      <c r="W107" s="1" t="n">
+        <v>0.01813</v>
+      </c>
+      <c r="X107" s="2" t="n">
+        <v>-0.002201430930104479</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8051,6 +8699,12 @@
       <c r="V108" s="2" t="n">
         <v>-0.003248259860788892</v>
       </c>
+      <c r="W108" s="1" t="n">
+        <v>0.02153</v>
+      </c>
+      <c r="X108" s="3" t="n">
+        <v>0.002327746741154629</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8121,6 +8775,12 @@
       <c r="V109" s="2" t="n">
         <v>-0.0001800504141158827</v>
       </c>
+      <c r="W109" s="1" t="n">
+        <v>0.05548</v>
+      </c>
+      <c r="X109" s="2" t="n">
+        <v>-0.0009004141905276685</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8191,6 +8851,12 @@
       <c r="V110" s="2" t="n">
         <v>-0.004202401372212611</v>
       </c>
+      <c r="W110" s="1" t="n">
+        <v>0.11573</v>
+      </c>
+      <c r="X110" s="2" t="n">
+        <v>-0.003272758590991347</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8261,6 +8927,12 @@
       <c r="V111" s="2" t="n">
         <v>-0.001429008880269483</v>
       </c>
+      <c r="W111" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="X111" s="2" t="n">
+        <v>-0.001328835735459523</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8331,6 +9003,12 @@
       <c r="V112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W112" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="X112" s="3" t="n">
+        <v>0.005405405405405373</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8401,6 +9079,12 @@
       <c r="V113" s="2" t="n">
         <v>-0.0001020408163266327</v>
       </c>
+      <c r="W113" s="1" t="n">
+        <v>0.09798</v>
+      </c>
+      <c r="X113" s="2" t="n">
+        <v>-0.0001020512297172785</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8471,6 +9155,12 @@
       <c r="V114" s="2" t="n">
         <v>-0.002913752913752921</v>
       </c>
+      <c r="W114" s="1" t="n">
+        <v>0.001739</v>
+      </c>
+      <c r="X114" s="3" t="n">
+        <v>0.01636469900642901</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8541,6 +9231,12 @@
       <c r="V115" s="2" t="n">
         <v>-0.0006368412673140518</v>
       </c>
+      <c r="W115" s="1" t="n">
+        <v>1.2526</v>
+      </c>
+      <c r="X115" s="2" t="n">
+        <v>-0.002230364823960599</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8611,6 +9307,12 @@
       <c r="V116" s="2" t="n">
         <v>-0.001688476150274426</v>
       </c>
+      <c r="W116" s="1" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="X116" s="2" t="n">
+        <v>-0.0008456659619449386</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8681,6 +9383,12 @@
       <c r="V117" s="3" t="n">
         <v>0.001630789302022225</v>
       </c>
+      <c r="W117" s="1" t="n">
+        <v>0.06156</v>
+      </c>
+      <c r="X117" s="3" t="n">
+        <v>0.002279387821556403</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8751,6 +9459,12 @@
       <c r="V118" s="2" t="n">
         <v>-0.001134816159782148</v>
       </c>
+      <c r="W118" s="1" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="X118" s="2" t="n">
+        <v>-0.01226993865030672</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8821,6 +9535,12 @@
       <c r="V119" s="3" t="n">
         <v>0.001612469766191865</v>
       </c>
+      <c r="W119" s="1" t="n">
+        <v>0.003701</v>
+      </c>
+      <c r="X119" s="2" t="n">
+        <v>-0.006976120203917355</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8891,6 +9611,12 @@
       <c r="V120" s="3" t="n">
         <v>0.001270648030495554</v>
       </c>
+      <c r="W120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="X120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8961,6 +9687,12 @@
       <c r="V121" s="3" t="n">
         <v>0.0006743088334458311</v>
       </c>
+      <c r="W121" s="1" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="X121" s="2" t="n">
+        <v>-0.001010781671159105</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9031,6 +9763,12 @@
       <c r="V122" s="3" t="n">
         <v>0.001584507042253542</v>
       </c>
+      <c r="W122" s="1" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="X122" s="2" t="n">
+        <v>-0.002988222886271619</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9101,6 +9839,12 @@
       <c r="V123" s="3" t="n">
         <v>0.003826398703850529</v>
       </c>
+      <c r="W123" s="1" t="n">
+        <v>0.029144</v>
+      </c>
+      <c r="X123" s="3" t="n">
+        <v>0.0008241758241758144</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9171,6 +9915,12 @@
       <c r="V124" s="3" t="n">
         <v>0.006924852526288956</v>
       </c>
+      <c r="W124" s="1" t="n">
+        <v>0.07821</v>
+      </c>
+      <c r="X124" s="2" t="n">
+        <v>-0.003948038716250697</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9241,6 +9991,12 @@
       <c r="V125" s="2" t="n">
         <v>-0.001931620629708247</v>
       </c>
+      <c r="W125" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="X125" s="3" t="n">
+        <v>0.0005806077027288997</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9311,6 +10067,12 @@
       <c r="V126" s="3" t="n">
         <v>0.004885381435550476</v>
       </c>
+      <c r="W126" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="X126" s="3" t="n">
+        <v>0.001121914734480134</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9381,6 +10143,12 @@
       <c r="V127" s="2" t="n">
         <v>-0.002728512960436451</v>
       </c>
+      <c r="W127" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="X127" s="3" t="n">
+        <v>0.0009119927040583303</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9451,6 +10219,12 @@
       <c r="V128" s="2" t="n">
         <v>-0.001851851851851819</v>
       </c>
+      <c r="W128" s="1" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="X128" s="2" t="n">
+        <v>-0.001236858379715558</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9521,6 +10295,12 @@
       <c r="V129" s="2" t="n">
         <v>-0.002978723404255149</v>
       </c>
+      <c r="W129" s="1" t="n">
+        <v>0.14307</v>
+      </c>
+      <c r="X129" s="3" t="n">
+        <v>0.01771233461374301</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9591,6 +10371,12 @@
       <c r="V130" s="2" t="n">
         <v>-0.004107122763587335</v>
       </c>
+      <c r="W130" s="1" t="n">
+        <v>0.053127</v>
+      </c>
+      <c r="X130" s="3" t="n">
+        <v>0.0004519518671262111</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9661,6 +10447,12 @@
       <c r="V131" s="3" t="n">
         <v>0.001101186834699703</v>
       </c>
+      <c r="W131" s="1" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="X131" s="2" t="n">
+        <v>-0.001099975556098836</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9731,6 +10523,12 @@
       <c r="V132" s="3" t="n">
         <v>0.003436426116838427</v>
       </c>
+      <c r="W132" s="1" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="X132" s="2" t="n">
+        <v>-0.001141552511415558</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9801,6 +10599,12 @@
       <c r="V133" s="3" t="n">
         <v>0.0006916825177242883</v>
       </c>
+      <c r="W133" s="1" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="X133" s="2" t="n">
+        <v>-0.0008640055296352945</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9871,6 +10675,12 @@
       <c r="V134" s="3" t="n">
         <v>0.005031868500503214</v>
       </c>
+      <c r="W134" s="1" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="X134" s="2" t="n">
+        <v>-0.004672897196261724</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9941,6 +10751,12 @@
       <c r="V135" s="2" t="n">
         <v>-0.001702610669693461</v>
       </c>
+      <c r="W135" s="1" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="X135" s="3" t="n">
+        <v>0.0005685048322910512</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10011,6 +10827,12 @@
       <c r="V136" s="2" t="n">
         <v>-0.001876675603217175</v>
       </c>
+      <c r="W136" s="1" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="X136" s="2" t="n">
+        <v>-0.00402900886381943</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10081,6 +10903,12 @@
       <c r="V137" s="3" t="n">
         <v>0.001845018450184555</v>
       </c>
+      <c r="W137" s="1" t="n">
+        <v>0.02705</v>
+      </c>
+      <c r="X137" s="2" t="n">
+        <v>-0.003683241252302003</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10151,6 +10979,12 @@
       <c r="V138" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W138" s="1" t="n">
+        <v>2.524</v>
+      </c>
+      <c r="X138" s="3" t="n">
+        <v>0.00238284352660851</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10221,6 +11055,12 @@
       <c r="V139" s="3" t="n">
         <v>0.001693480101608884</v>
       </c>
+      <c r="W139" s="1" t="n">
+        <v>0.01187</v>
+      </c>
+      <c r="X139" s="3" t="n">
+        <v>0.003381234150464929</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10291,6 +11131,12 @@
       <c r="V140" s="2" t="n">
         <v>-0.002006688963210737</v>
       </c>
+      <c r="W140" s="1" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="X140" s="2" t="n">
+        <v>-0.004691689008042821</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10361,6 +11207,12 @@
       <c r="V141" s="3" t="n">
         <v>0.0009932952570150383</v>
       </c>
+      <c r="W141" s="1" t="n">
+        <v>16.136</v>
+      </c>
+      <c r="X141" s="3" t="n">
+        <v>0.0007442322004465676</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10431,6 +11283,12 @@
       <c r="V142" s="3" t="n">
         <v>0.004019292604501583</v>
       </c>
+      <c r="W142" s="1" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="X142" s="3" t="n">
+        <v>0.0008006405124100342</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10501,6 +11359,12 @@
       <c r="V143" s="2" t="n">
         <v>-0.002623688155921932</v>
       </c>
+      <c r="W143" s="1" t="n">
+        <v>0.02659</v>
+      </c>
+      <c r="X143" s="2" t="n">
+        <v>-0.0007515971439309528</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10571,6 +11435,12 @@
       <c r="V144" s="2" t="n">
         <v>-0.005036726128016729</v>
       </c>
+      <c r="W144" s="1" t="n">
+        <v>0.004715</v>
+      </c>
+      <c r="X144" s="2" t="n">
+        <v>-0.005484075089643714</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10641,6 +11511,12 @@
       <c r="V145" s="3" t="n">
         <v>0.004673609347218744</v>
       </c>
+      <c r="W145" s="1" t="n">
+        <v>1.9704</v>
+      </c>
+      <c r="X145" s="2" t="n">
+        <v>-0.00369115639379081</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10711,6 +11587,12 @@
       <c r="V146" s="3" t="n">
         <v>0.005206073752711435</v>
       </c>
+      <c r="W146" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="X146" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10781,6 +11663,12 @@
       <c r="V147" s="2" t="n">
         <v>-0.0002225932109071355</v>
       </c>
+      <c r="W147" s="1" t="n">
+        <v>0.08962000000000001</v>
+      </c>
+      <c r="X147" s="2" t="n">
+        <v>-0.002337749081598441</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10851,6 +11739,12 @@
       <c r="V148" s="2" t="n">
         <v>-0.02985548673971732</v>
       </c>
+      <c r="W148" s="1" t="n">
+        <v>0.06194</v>
+      </c>
+      <c r="X148" s="3" t="n">
+        <v>0.01391389752823709</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10921,6 +11815,12 @@
       <c r="V149" s="2" t="n">
         <v>-0.001345216075332162</v>
       </c>
+      <c r="W149" s="1" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="X149" s="3" t="n">
+        <v>0.0001683785149015501</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10991,6 +11891,12 @@
       <c r="V150" s="3" t="n">
         <v>0.0001626942162206632</v>
       </c>
+      <c r="W150" s="1" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="X150" s="2" t="n">
+        <v>-0.0002846685644571553</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11061,6 +11967,12 @@
       <c r="V151" s="2" t="n">
         <v>-0.002606051831475339</v>
       </c>
+      <c r="W151" s="1" t="n">
+        <v>6.906000000000001e-05</v>
+      </c>
+      <c r="X151" s="3" t="n">
+        <v>0.002467702133836651</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11131,6 +12043,12 @@
       <c r="V152" s="3" t="n">
         <v>0.0008986744551786373</v>
       </c>
+      <c r="W152" s="1" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="X152" s="2" t="n">
+        <v>-0.001571268237934981</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11201,6 +12119,12 @@
       <c r="V153" s="3" t="n">
         <v>0.002289077828646103</v>
       </c>
+      <c r="W153" s="1" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="X153" s="3" t="n">
+        <v>0.003262642740619905</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11271,6 +12195,12 @@
       <c r="V154" s="3" t="n">
         <v>0.007792930698580488</v>
       </c>
+      <c r="W154" s="1" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="X154" s="3" t="n">
+        <v>0.001657000828500538</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11341,6 +12271,12 @@
       <c r="V155" s="3" t="n">
         <v>0.001297016861219173</v>
       </c>
+      <c r="W155" s="1" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="X155" s="2" t="n">
+        <v>-0.001727115716753072</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11411,6 +12347,12 @@
       <c r="V156" s="2" t="n">
         <v>-0.004204798417017153</v>
       </c>
+      <c r="W156" s="1" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="X156" s="3" t="n">
+        <v>0.003477396920019902</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11481,6 +12423,12 @@
       <c r="V157" s="2" t="n">
         <v>-0.002107666637393555</v>
       </c>
+      <c r="W157" s="1" t="n">
+        <v>0.22857</v>
+      </c>
+      <c r="X157" s="3" t="n">
+        <v>0.005764322802076941</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11551,6 +12499,12 @@
       <c r="V158" s="3" t="n">
         <v>0.002396166134185261</v>
       </c>
+      <c r="W158" s="1" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="X158" s="3" t="n">
+        <v>0.003585657370517976</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11621,6 +12575,12 @@
       <c r="V159" s="3" t="n">
         <v>0.002391527160915653</v>
       </c>
+      <c r="W159" s="1" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="X159" s="3" t="n">
+        <v>0.0006816632583502998</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11691,6 +12651,12 @@
       <c r="V160" s="2" t="n">
         <v>-0.003003003003003089</v>
       </c>
+      <c r="W160" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="X160" s="3" t="n">
+        <v>0.001004016064257057</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11761,6 +12727,12 @@
       <c r="V161" s="3" t="n">
         <v>0.00631607853906341</v>
       </c>
+      <c r="W161" s="1" t="n">
+        <v>0.14776</v>
+      </c>
+      <c r="X161" s="3" t="n">
+        <v>0.008050211488607004</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11831,6 +12803,12 @@
       <c r="V162" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W162" s="1" t="n">
+        <v>0.003273</v>
+      </c>
+      <c r="X162" s="2" t="n">
+        <v>-0.002438281011886679</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11901,6 +12879,12 @@
       <c r="V163" s="3" t="n">
         <v>0.002008838891121024</v>
       </c>
+      <c r="W163" s="1" t="n">
+        <v>0.004994</v>
+      </c>
+      <c r="X163" s="3" t="n">
+        <v>0.001202886928628695</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11971,6 +12955,12 @@
       <c r="V164" s="3" t="n">
         <v>0.003154574132492058</v>
       </c>
+      <c r="W164" s="1" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="X164" s="2" t="n">
+        <v>-0.001048218029350135</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12041,6 +13031,12 @@
       <c r="V165" s="3" t="n">
         <v>0.002610966057441147</v>
       </c>
+      <c r="W165" s="1" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="X165" s="2" t="n">
+        <v>-0.0055338541666666</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12111,6 +13107,12 @@
       <c r="V166" s="3" t="n">
         <v>0.0005035971223022626</v>
       </c>
+      <c r="W166" s="1" t="n">
+        <v>1.3875</v>
+      </c>
+      <c r="X166" s="2" t="n">
+        <v>-0.002300999496656426</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12181,6 +13183,12 @@
       <c r="V167" s="2" t="n">
         <v>-0.0003610108303250704</v>
       </c>
+      <c r="W167" s="1" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="X167" s="3" t="n">
+        <v>0.002889129649693113</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12251,6 +13259,12 @@
       <c r="V168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W168" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="X168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12321,6 +13335,12 @@
       <c r="V169" s="2" t="n">
         <v>-0.001004352192835696</v>
       </c>
+      <c r="W169" s="1" t="n">
+        <v>0.02979</v>
+      </c>
+      <c r="X169" s="2" t="n">
+        <v>-0.001675603217158109</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12391,6 +13411,12 @@
       <c r="V170" s="3" t="n">
         <v>0.003222836095764301</v>
       </c>
+      <c r="W170" s="1" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="X170" s="2" t="n">
+        <v>-0.008031206975676986</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12461,6 +13487,12 @@
       <c r="V171" s="2" t="n">
         <v>-0.006024096385542133</v>
       </c>
+      <c r="W171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="X171" s="3" t="n">
+        <v>0.006060606060606023</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12531,6 +13563,12 @@
       <c r="V172" s="3" t="n">
         <v>0.0153846153846155</v>
       </c>
+      <c r="W172" s="1" t="n">
+        <v>1.31e-05</v>
+      </c>
+      <c r="X172" s="2" t="n">
+        <v>-0.007575757575757631</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12601,6 +13639,12 @@
       <c r="V173" s="2" t="n">
         <v>-0.0004737091425864326</v>
       </c>
+      <c r="W173" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="X173" s="2" t="n">
+        <v>-0.002369668246445565</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12671,6 +13715,12 @@
       <c r="V174" s="3" t="n">
         <v>0.005546927002440653</v>
       </c>
+      <c r="W174" s="1" t="n">
+        <v>0.09092</v>
+      </c>
+      <c r="X174" s="3" t="n">
+        <v>0.003089143865842922</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12741,6 +13791,12 @@
       <c r="V175" s="3" t="n">
         <v>0.000825309491059209</v>
       </c>
+      <c r="W175" s="1" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="X175" s="2" t="n">
+        <v>-0.0024738867509621</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12811,6 +13867,12 @@
       <c r="V176" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W176" s="1" t="n">
+        <v>0.02143</v>
+      </c>
+      <c r="X176" s="2" t="n">
+        <v>-0.001863064741499691</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12881,6 +13943,12 @@
       <c r="V177" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W177" s="1" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="X177" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12951,6 +14019,12 @@
       <c r="V178" s="2" t="n">
         <v>-0.001037344398340274</v>
       </c>
+      <c r="W178" s="1" t="n">
+        <v>0.00096</v>
+      </c>
+      <c r="X178" s="2" t="n">
+        <v>-0.003115264797507751</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13021,6 +14095,12 @@
       <c r="V179" s="3" t="n">
         <v>0.001753770606804711</v>
       </c>
+      <c r="W179" s="1" t="n">
+        <v>0.022726</v>
+      </c>
+      <c r="X179" s="2" t="n">
+        <v>-0.005339635854341762</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -13091,6 +14171,12 @@
       <c r="V180" s="3" t="n">
         <v>0.001944106925880925</v>
       </c>
+      <c r="W180" s="1" t="n">
+        <v>4.121</v>
+      </c>
+      <c r="X180" s="2" t="n">
+        <v>-0.0004850836769342177</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13161,6 +14247,12 @@
       <c r="V181" s="3" t="n">
         <v>0.01509368494101306</v>
       </c>
+      <c r="W181" s="1" t="n">
+        <v>0.5822000000000001</v>
+      </c>
+      <c r="X181" s="2" t="n">
+        <v>-0.004956417706374812</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13231,6 +14323,12 @@
       <c r="V182" s="3" t="n">
         <v>0.0009970089730807863</v>
       </c>
+      <c r="W182" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="X182" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -13301,6 +14399,12 @@
       <c r="V183" s="3" t="n">
         <v>0.0009129085265656186</v>
       </c>
+      <c r="W183" s="1" t="n">
+        <v>5.471</v>
+      </c>
+      <c r="X183" s="2" t="n">
+        <v>-0.00200656694636996</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13371,6 +14475,12 @@
       <c r="V184" s="3" t="n">
         <v>0.001742160278745669</v>
       </c>
+      <c r="W184" s="1" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="X184" s="2" t="n">
+        <v>-0.0003478260869565761</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13441,6 +14551,12 @@
       <c r="V185" s="3" t="n">
         <v>0.01228632478632484</v>
       </c>
+      <c r="W185" s="1" t="n">
+        <v>0.01887</v>
+      </c>
+      <c r="X185" s="2" t="n">
+        <v>-0.004221635883905024</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13511,6 +14627,12 @@
       <c r="V186" s="3" t="n">
         <v>0.003194888178913599</v>
       </c>
+      <c r="W186" s="1" t="n">
+        <v>3.11e-05</v>
+      </c>
+      <c r="X186" s="2" t="n">
+        <v>-0.009554140127388552</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13581,6 +14703,12 @@
       <c r="V187" s="3" t="n">
         <v>0.0006281407035175624</v>
       </c>
+      <c r="W187" s="1" t="n">
+        <v>0.01591</v>
+      </c>
+      <c r="X187" s="2" t="n">
+        <v>-0.001255492780916459</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13651,6 +14779,12 @@
       <c r="V188" s="3" t="n">
         <v>0.000247647350173429</v>
       </c>
+      <c r="W188" s="1" t="n">
+        <v>0.04056</v>
+      </c>
+      <c r="X188" s="3" t="n">
+        <v>0.004208962614508456</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13721,6 +14855,12 @@
       <c r="V189" s="3" t="n">
         <v>0.0002268602540834901</v>
       </c>
+      <c r="W189" s="1" t="n">
+        <v>0.0004405</v>
+      </c>
+      <c r="X189" s="2" t="n">
+        <v>-0.0009072352007258103</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13791,6 +14931,12 @@
       <c r="V190" s="2" t="n">
         <v>-0.0004258943781941904</v>
       </c>
+      <c r="W190" s="1" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="X190" s="2" t="n">
+        <v>-0.000852151682999687</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13861,6 +15007,12 @@
       <c r="V191" s="2" t="n">
         <v>-0.004430379746835481</v>
       </c>
+      <c r="W191" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="X191" s="2" t="n">
+        <v>-0.001271455816910531</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13931,6 +15083,12 @@
       <c r="V192" s="3" t="n">
         <v>0.00142020237883905</v>
       </c>
+      <c r="W192" s="1" t="n">
+        <v>0.05593</v>
+      </c>
+      <c r="X192" s="2" t="n">
+        <v>-0.00850912958695269</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -14001,6 +15159,12 @@
       <c r="V193" s="3" t="n">
         <v>0.0005341880341879754</v>
       </c>
+      <c r="W193" s="1" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="X193" s="2" t="n">
+        <v>-0.002135611318739902</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -14071,6 +15235,12 @@
       <c r="V194" s="3" t="n">
         <v>0.001564945226916994</v>
       </c>
+      <c r="W194" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="X194" s="3" t="n">
+        <v>0.001041666666666805</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -14141,6 +15311,12 @@
       <c r="V195" s="2" t="n">
         <v>-0.003729603729603707</v>
       </c>
+      <c r="W195" s="1" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="X195" s="3" t="n">
+        <v>0.001637810014038321</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14211,6 +15387,12 @@
       <c r="V196" s="2" t="n">
         <v>-0.003223207091055469</v>
       </c>
+      <c r="W196" s="1" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="X196" s="2" t="n">
+        <v>-0.004042037186742234</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14281,6 +15463,12 @@
       <c r="V197" s="3" t="n">
         <v>0.0004314994606256566</v>
       </c>
+      <c r="W197" s="1" t="n">
+        <v>0.04637</v>
+      </c>
+      <c r="X197" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14351,6 +15539,12 @@
       <c r="V198" s="2" t="n">
         <v>-0.004715127701375162</v>
       </c>
+      <c r="W198" s="1" t="n">
+        <v>0.5114</v>
+      </c>
+      <c r="X198" s="3" t="n">
+        <v>0.009474930911961933</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14421,6 +15615,12 @@
       <c r="V199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="X199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14491,6 +15691,12 @@
       <c r="V200" s="3" t="n">
         <v>0.002008032128514132</v>
       </c>
+      <c r="W200" s="1" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="X200" s="2" t="n">
+        <v>-0.004676018704074835</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14561,6 +15767,12 @@
       <c r="V201" s="3" t="n">
         <v>0.006646842749693868</v>
       </c>
+      <c r="W201" s="1" t="n">
+        <v>0.005724</v>
+      </c>
+      <c r="X201" s="2" t="n">
+        <v>-0.005386620330147659</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14631,6 +15843,12 @@
       <c r="V202" s="2" t="n">
         <v>-0.000344560254974485</v>
       </c>
+      <c r="W202" s="1" t="n">
+        <v>0.023108</v>
+      </c>
+      <c r="X202" s="2" t="n">
+        <v>-0.004394657475226256</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14701,6 +15919,12 @@
       <c r="V203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W203" s="1" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="X203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14771,6 +15995,12 @@
       <c r="V204" s="3" t="n">
         <v>0.0005931198102016366</v>
       </c>
+      <c r="W204" s="1" t="n">
+        <v>0.03356</v>
+      </c>
+      <c r="X204" s="2" t="n">
+        <v>-0.005334914048606983</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14841,6 +16071,12 @@
       <c r="V205" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W205" s="1" t="n">
+        <v>4.194</v>
+      </c>
+      <c r="X205" s="2" t="n">
+        <v>-0.009213323883770306</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14911,6 +16147,12 @@
       <c r="V206" s="2" t="n">
         <v>-0.005540166204986155</v>
       </c>
+      <c r="W206" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="X206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14981,6 +16223,12 @@
       <c r="V207" s="2" t="n">
         <v>-0.01624802388898654</v>
       </c>
+      <c r="W207" s="1" t="n">
+        <v>0.001145</v>
+      </c>
+      <c r="X207" s="3" t="n">
+        <v>0.02223015802160522</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15051,6 +16299,12 @@
       <c r="V208" s="3" t="n">
         <v>0.002888185944161764</v>
       </c>
+      <c r="W208" s="1" t="n">
+        <v>0.007269</v>
+      </c>
+      <c r="X208" s="2" t="n">
+        <v>-0.003154141524958802</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15121,6 +16375,12 @@
       <c r="V209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W209" s="1" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="X209" s="2" t="n">
+        <v>-0.003344481605351151</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15191,6 +16451,12 @@
       <c r="V210" s="2" t="n">
         <v>-0.0007704160246532279</v>
       </c>
+      <c r="W210" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="X210" s="3" t="n">
+        <v>0.001542020046260432</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15261,6 +16527,12 @@
       <c r="V211" s="3" t="n">
         <v>0.00140587656403762</v>
       </c>
+      <c r="W211" s="1" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="X211" s="2" t="n">
+        <v>-0.0004211708549768915</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15331,6 +16603,12 @@
       <c r="V212" s="2" t="n">
         <v>-0.02125539687811346</v>
       </c>
+      <c r="W212" s="1" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="X212" s="2" t="n">
+        <v>-0.008822531387852023</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15401,6 +16679,12 @@
       <c r="V213" s="2" t="n">
         <v>-0.001589544330625217</v>
       </c>
+      <c r="W213" s="1" t="n">
+        <v>0.05596</v>
+      </c>
+      <c r="X213" s="2" t="n">
+        <v>-0.01008314169467529</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15471,6 +16755,12 @@
       <c r="V214" s="3" t="n">
         <v>0.001058761249338158</v>
       </c>
+      <c r="W214" s="1" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="X214" s="2" t="n">
+        <v>-0.002115282919090342</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15541,6 +16831,12 @@
       <c r="V215" s="3" t="n">
         <v>0.004176950825897057</v>
       </c>
+      <c r="W215" s="1" t="n">
+        <v>0.05273</v>
+      </c>
+      <c r="X215" s="2" t="n">
+        <v>-0.003025146530535081</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15611,6 +16907,12 @@
       <c r="V216" s="3" t="n">
         <v>0.002881844380403424</v>
       </c>
+      <c r="W216" s="1" t="n">
+        <v>0.002086</v>
+      </c>
+      <c r="X216" s="2" t="n">
+        <v>-0.0009578544061301876</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15681,6 +16983,12 @@
       <c r="V217" s="3" t="n">
         <v>0.000666333499916635</v>
       </c>
+      <c r="W217" s="1" t="n">
+        <v>6.001</v>
+      </c>
+      <c r="X217" s="2" t="n">
+        <v>-0.0009988346928582221</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15751,6 +17059,12 @@
       <c r="V218" s="3" t="n">
         <v>0.007764329755652135</v>
       </c>
+      <c r="W218" s="1" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X218" s="2" t="n">
+        <v>-0.002945841830953977</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15821,6 +17135,12 @@
       <c r="V219" s="2" t="n">
         <v>-0.001494209936496114</v>
       </c>
+      <c r="W219" s="1" t="n">
+        <v>0.005328</v>
+      </c>
+      <c r="X219" s="2" t="n">
+        <v>-0.003367003367003327</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15891,6 +17211,12 @@
       <c r="V220" s="3" t="n">
         <v>0.001452432824981785</v>
       </c>
+      <c r="W220" s="1" t="n">
+        <v>0.04126</v>
+      </c>
+      <c r="X220" s="2" t="n">
+        <v>-0.002658931592941721</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15961,6 +17287,12 @@
       <c r="V221" s="2" t="n">
         <v>-0.003644567858382538</v>
       </c>
+      <c r="W221" s="1" t="n">
+        <v>0.005732</v>
+      </c>
+      <c r="X221" s="2" t="n">
+        <v>-0.001567671137432409</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16031,6 +17363,12 @@
       <c r="V222" s="3" t="n">
         <v>0.001102535832414585</v>
       </c>
+      <c r="W222" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="X222" s="3" t="n">
+        <v>0.001101321585902962</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16101,6 +17439,12 @@
       <c r="V223" s="3" t="n">
         <v>0.0020933014354068</v>
       </c>
+      <c r="W223" s="1" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="X223" s="2" t="n">
+        <v>-0.002387347060579</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16171,6 +17515,12 @@
       <c r="V224" s="2" t="n">
         <v>-0.001851423281647691</v>
       </c>
+      <c r="W224" s="1" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="X224" s="2" t="n">
+        <v>-0.001159285879897984</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -16241,6 +17591,12 @@
       <c r="V225" s="3" t="n">
         <v>0.00287528453336533</v>
       </c>
+      <c r="W225" s="1" t="n">
+        <v>0.08359</v>
+      </c>
+      <c r="X225" s="2" t="n">
+        <v>-0.001433520487397073</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16311,6 +17667,12 @@
       <c r="V226" s="3" t="n">
         <v>0.001059883412824546</v>
       </c>
+      <c r="W226" s="1" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="X226" s="2" t="n">
+        <v>-0.002117522498676646</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16381,6 +17743,12 @@
       <c r="V227" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W227" s="1" t="n">
+        <v>0.04666</v>
+      </c>
+      <c r="X227" s="2" t="n">
+        <v>-0.001711596063328985</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16451,6 +17819,12 @@
       <c r="V228" s="3" t="n">
         <v>0.001300390117035057</v>
       </c>
+      <c r="W228" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="X228" s="3" t="n">
+        <v>0.001731601731601811</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16521,6 +17895,12 @@
       <c r="V229" s="2" t="n">
         <v>-0.001855287569573337</v>
       </c>
+      <c r="W229" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="X229" s="2" t="n">
+        <v>-0.002788104089219282</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16591,6 +17971,12 @@
       <c r="V230" s="2" t="n">
         <v>-0.002409638554216936</v>
       </c>
+      <c r="W230" s="1" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="X230" s="2" t="n">
+        <v>-0.001207729468599068</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16661,6 +18047,12 @@
       <c r="V231" s="2" t="n">
         <v>-0.004255319148936224</v>
       </c>
+      <c r="W231" s="1" t="n">
+        <v>0.03037</v>
+      </c>
+      <c r="X231" s="2" t="n">
+        <v>-0.001643655489809269</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -16731,6 +18123,12 @@
       <c r="V232" s="3" t="n">
         <v>0.001762114537444862</v>
       </c>
+      <c r="W232" s="1" t="n">
+        <v>0.02255</v>
+      </c>
+      <c r="X232" s="2" t="n">
+        <v>-0.008355321020228637</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16801,6 +18199,12 @@
       <c r="V233" s="2" t="n">
         <v>-0.01081595569784547</v>
       </c>
+      <c r="W233" s="1" t="n">
+        <v>0.11242</v>
+      </c>
+      <c r="X233" s="2" t="n">
+        <v>-0.01662001399580125</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16871,6 +18275,12 @@
       <c r="V234" s="2" t="n">
         <v>-0.002760252365930515</v>
       </c>
+      <c r="W234" s="1" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="X234" s="2" t="n">
+        <v>-0.001581652827204474</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16941,6 +18351,12 @@
       <c r="V235" s="3" t="n">
         <v>0.0002887252778981684</v>
       </c>
+      <c r="W235" s="1" t="n">
+        <v>0.06904</v>
+      </c>
+      <c r="X235" s="2" t="n">
+        <v>-0.003608024245922936</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17011,6 +18427,12 @@
       <c r="V236" s="2" t="n">
         <v>-0.002553870710295298</v>
       </c>
+      <c r="W236" s="1" t="n">
+        <v>0.12667</v>
+      </c>
+      <c r="X236" s="3" t="n">
+        <v>0.01352216354616747</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -17081,6 +18503,12 @@
       <c r="V237" s="2" t="n">
         <v>-0.003845167905665324</v>
       </c>
+      <c r="W237" s="1" t="n">
+        <v>0.03852</v>
+      </c>
+      <c r="X237" s="2" t="n">
+        <v>-0.008749356664951108</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17151,6 +18579,12 @@
       <c r="V238" s="3" t="n">
         <v>0.008403361344537823</v>
       </c>
+      <c r="W238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="X238" s="2" t="n">
+        <v>-0.008333333333333342</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17221,6 +18655,12 @@
       <c r="V239" s="2" t="n">
         <v>-0.00402010050251266</v>
       </c>
+      <c r="W239" s="1" t="n">
+        <v>0.003997</v>
+      </c>
+      <c r="X239" s="3" t="n">
+        <v>0.008324924318869839</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -17291,6 +18731,12 @@
       <c r="V240" s="3" t="n">
         <v>0.002194586686174141</v>
       </c>
+      <c r="W240" s="1" t="n">
+        <v>0.01367</v>
+      </c>
+      <c r="X240" s="2" t="n">
+        <v>-0.002189781021897848</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17361,6 +18807,12 @@
       <c r="V241" s="2" t="n">
         <v>-0.003178206583427951</v>
       </c>
+      <c r="W241" s="1" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="X241" s="3" t="n">
+        <v>0.006376679571851571</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -17431,6 +18883,12 @@
       <c r="V242" s="3" t="n">
         <v>0.004005340453938537</v>
       </c>
+      <c r="W242" s="1" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="X242" s="2" t="n">
+        <v>-0.002659574468085113</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17501,6 +18959,12 @@
       <c r="V243" s="3" t="n">
         <v>0.00661084178052009</v>
       </c>
+      <c r="W243" s="1" t="n">
+        <v>0.02283</v>
+      </c>
+      <c r="X243" s="2" t="n">
+        <v>-0.000437828371278441</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -17571,6 +19035,12 @@
       <c r="V244" s="3" t="n">
         <v>0.007756563245823384</v>
       </c>
+      <c r="W244" s="1" t="n">
+        <v>0.001682</v>
+      </c>
+      <c r="X244" s="2" t="n">
+        <v>-0.004144464179988195</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17641,6 +19111,12 @@
       <c r="V245" s="3" t="n">
         <v>0.003825554705432291</v>
       </c>
+      <c r="W245" s="1" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="X245" s="2" t="n">
+        <v>-0.003048780487804965</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -17711,6 +19187,12 @@
       <c r="V246" s="3" t="n">
         <v>0.007883948281299281</v>
       </c>
+      <c r="W246" s="1" t="n">
+        <v>0.03134</v>
+      </c>
+      <c r="X246" s="2" t="n">
+        <v>-0.01939924906132674</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17781,6 +19263,12 @@
       <c r="V247" s="2" t="n">
         <v>-0.001688238604389391</v>
       </c>
+      <c r="W247" s="1" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="X247" s="2" t="n">
+        <v>-0.002818489289740701</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17851,6 +19339,12 @@
       <c r="V248" s="3" t="n">
         <v>0.005901639344262282</v>
       </c>
+      <c r="W248" s="1" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="X248" s="2" t="n">
+        <v>-0.006192959582790065</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17921,6 +19415,12 @@
       <c r="V249" s="3" t="n">
         <v>0.0007096392667059801</v>
       </c>
+      <c r="W249" s="1" t="n">
+        <v>0.008517</v>
+      </c>
+      <c r="X249" s="3" t="n">
+        <v>0.006618603002009277</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17991,6 +19491,12 @@
       <c r="V250" s="3" t="n">
         <v>0.009975062344139765</v>
       </c>
+      <c r="W250" s="1" t="n">
+        <v>0.02005</v>
+      </c>
+      <c r="X250" s="2" t="n">
+        <v>-0.009876543209876654</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -18061,6 +19567,12 @@
       <c r="V251" s="2" t="n">
         <v>-0.0006461339651088143</v>
       </c>
+      <c r="W251" s="1" t="n">
+        <v>0.04646</v>
+      </c>
+      <c r="X251" s="3" t="n">
+        <v>0.001293103448275959</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -18131,6 +19643,12 @@
       <c r="V252" s="2" t="n">
         <v>-0.003288314738696447</v>
       </c>
+      <c r="W252" s="1" t="n">
+        <v>0.008519000000000001</v>
+      </c>
+      <c r="X252" s="3" t="n">
+        <v>0.003770472487333661</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -18201,6 +19719,12 @@
       <c r="V253" s="3" t="n">
         <v>0.005920205920205768</v>
       </c>
+      <c r="W253" s="1" t="n">
+        <v>0.03891</v>
+      </c>
+      <c r="X253" s="2" t="n">
+        <v>-0.004350051177072584</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -18271,6 +19795,12 @@
       <c r="V254" s="3" t="n">
         <v>0.006037859007832935</v>
       </c>
+      <c r="W254" s="1" t="n">
+        <v>0.06143</v>
+      </c>
+      <c r="X254" s="2" t="n">
+        <v>-0.0035685320356854</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -18341,6 +19871,12 @@
       <c r="V255" s="2" t="n">
         <v>-0.00309249367444468</v>
       </c>
+      <c r="W255" s="1" t="n">
+        <v>0.003535</v>
+      </c>
+      <c r="X255" s="2" t="n">
+        <v>-0.003102086858432081</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -18411,6 +19947,12 @@
       <c r="V256" s="3" t="n">
         <v>0.0002262272830102957</v>
       </c>
+      <c r="W256" s="1" t="n">
+        <v>0.013219</v>
+      </c>
+      <c r="X256" s="2" t="n">
+        <v>-0.003392641737032562</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -18481,6 +20023,12 @@
       <c r="V257" s="2" t="n">
         <v>-1.000574329694e-06</v>
       </c>
+      <c r="W257" s="1" t="n">
+        <v>0.999425</v>
+      </c>
+      <c r="X257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18551,6 +20099,12 @@
       <c r="V258" s="3" t="n">
         <v>0.02656699252443941</v>
       </c>
+      <c r="W258" s="1" t="n">
+        <v>0.08946999999999999</v>
+      </c>
+      <c r="X258" s="3" t="n">
+        <v>0.002352677571140353</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -18621,6 +20175,12 @@
       <c r="V259" s="3" t="n">
         <v>0.01023327464788733</v>
       </c>
+      <c r="W259" s="1" t="n">
+        <v>0.09107999999999999</v>
+      </c>
+      <c r="X259" s="2" t="n">
+        <v>-0.007951203572595669</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18691,6 +20251,12 @@
       <c r="V260" s="3" t="n">
         <v>0.006132711885195639</v>
       </c>
+      <c r="W260" s="1" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="X260" s="2" t="n">
+        <v>-0.0003657198585883487</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18761,6 +20327,12 @@
       <c r="V261" s="2" t="n">
         <v>-0.001737619461337968</v>
       </c>
+      <c r="W261" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="X261" s="2" t="n">
+        <v>-0.00174064403829417</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18831,6 +20403,12 @@
       <c r="V262" s="2" t="n">
         <v>-0.002124833997344009</v>
       </c>
+      <c r="W262" s="1" t="n">
+        <v>0.003793</v>
+      </c>
+      <c r="X262" s="3" t="n">
+        <v>0.009582113388341765</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -18901,6 +20479,12 @@
       <c r="V263" s="2" t="n">
         <v>-0.002570694087403554</v>
       </c>
+      <c r="W263" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="X263" s="2" t="n">
+        <v>-0.01202749140893469</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18971,6 +20555,12 @@
       <c r="V264" s="3" t="n">
         <v>0.07996647108130767</v>
       </c>
+      <c r="W264" s="1" t="n">
+        <v>0.0006254</v>
+      </c>
+      <c r="X264" s="2" t="n">
+        <v>-0.02918348339025151</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -19041,6 +20631,12 @@
       <c r="V265" s="3" t="n">
         <v>0.0006784260515603523</v>
       </c>
+      <c r="W265" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="X265" s="2" t="n">
+        <v>-0.002711864406779551</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -19111,6 +20707,12 @@
       <c r="V266" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W266" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="X266" s="2" t="n">
+        <v>-0.001572327044025202</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -19181,6 +20783,12 @@
       <c r="V267" s="3" t="n">
         <v>0.001850709438618276</v>
       </c>
+      <c r="W267" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="X267" s="2" t="n">
+        <v>-0.001231527093596222</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -19251,6 +20859,12 @@
       <c r="V268" s="2" t="n">
         <v>-0.0118965911690689</v>
       </c>
+      <c r="W268" s="1" t="n">
+        <v>0.0004299</v>
+      </c>
+      <c r="X268" s="2" t="n">
+        <v>-0.004630701551285007</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -19321,6 +20935,12 @@
       <c r="V269" s="3" t="n">
         <v>0.004356243949661171</v>
       </c>
+      <c r="W269" s="1" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="X269" s="2" t="n">
+        <v>-0.0009638554216868749</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -19391,6 +21011,12 @@
       <c r="V270" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W270" s="1" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="X270" s="2" t="n">
+        <v>-0.001660210293303789</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -19461,6 +21087,12 @@
       <c r="V271" s="2" t="n">
         <v>-0.0006798096532971906</v>
       </c>
+      <c r="W271" s="1" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="X271" s="3" t="n">
+        <v>0.002721088435374228</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19531,6 +21163,12 @@
       <c r="V272" s="3" t="n">
         <v>0.002541296060991002</v>
       </c>
+      <c r="W272" s="1" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="X272" s="3" t="n">
+        <v>0.003548795944233238</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -19601,6 +21239,12 @@
       <c r="V273" s="2" t="n">
         <v>-0.001076426264800862</v>
       </c>
+      <c r="W273" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="X273" s="2" t="n">
+        <v>-0.001077586206896553</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -19671,6 +21315,12 @@
       <c r="V274" s="3" t="n">
         <v>0.002220812182741126</v>
       </c>
+      <c r="W274" s="1" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="X274" s="2" t="n">
+        <v>-0.001266223488445684</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -19741,6 +21391,12 @@
       <c r="V275" s="3" t="n">
         <v>0.0008841732979663654</v>
       </c>
+      <c r="W275" s="1" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="X275" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -19811,6 +21467,12 @@
       <c r="V276" s="3" t="n">
         <v>0.001924557351809214</v>
       </c>
+      <c r="W276" s="1" t="n">
+        <v>2.608</v>
+      </c>
+      <c r="X276" s="3" t="n">
+        <v>0.001920860545524354</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -19881,6 +21543,12 @@
       <c r="V277" s="3" t="n">
         <v>0.000477213075638253</v>
       </c>
+      <c r="W277" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="X277" s="3" t="n">
+        <v>0.00166944908180302</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -19951,6 +21619,12 @@
       <c r="V278" s="2" t="n">
         <v>-0.005603667855323609</v>
       </c>
+      <c r="W278" s="1" t="n">
+        <v>0.01984</v>
+      </c>
+      <c r="X278" s="3" t="n">
+        <v>0.01639344262295086</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -20021,6 +21695,12 @@
       <c r="V279" s="3" t="n">
         <v>0.00789096126255376</v>
       </c>
+      <c r="W279" s="1" t="n">
+        <v>0.005591</v>
+      </c>
+      <c r="X279" s="2" t="n">
+        <v>-0.005160142348754516</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -20091,6 +21771,12 @@
       <c r="V280" s="3" t="n">
         <v>0.006420133538777612</v>
       </c>
+      <c r="W280" s="1" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="X280" s="2" t="n">
+        <v>-0.001786169941311575</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -20161,6 +21847,12 @@
       <c r="V281" s="3" t="n">
         <v>0.002224694104560625</v>
       </c>
+      <c r="W281" s="1" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="X281" s="3" t="n">
+        <v>0.001109877913429524</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -20231,6 +21923,12 @@
       <c r="V282" s="3" t="n">
         <v>0.0009888751545116328</v>
       </c>
+      <c r="W282" s="1" t="n">
+        <v>0.0004084</v>
+      </c>
+      <c r="X282" s="3" t="n">
+        <v>0.008644109656705435</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -20301,6 +21999,12 @@
       <c r="V283" s="3" t="n">
         <v>0.02204408817635285</v>
       </c>
+      <c r="W283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="X283" s="3" t="n">
+        <v>0.004901960784313695</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -20371,6 +22075,12 @@
       <c r="V284" s="3" t="n">
         <v>0.0004786979415988317</v>
       </c>
+      <c r="W284" s="1" t="n">
+        <v>0.04176</v>
+      </c>
+      <c r="X284" s="2" t="n">
+        <v>-0.0009569377990430233</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -20441,6 +22151,12 @@
       <c r="V285" s="2" t="n">
         <v>-0.0007448789571694297</v>
       </c>
+      <c r="W285" s="1" t="n">
+        <v>0.10726</v>
+      </c>
+      <c r="X285" s="2" t="n">
+        <v>-0.000559075661572908</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -20511,6 +22227,12 @@
       <c r="V286" s="2" t="n">
         <v>-0.002386634844868845</v>
       </c>
+      <c r="W286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="X286" s="3" t="n">
+        <v>0.002392344497607766</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -20581,6 +22303,12 @@
       <c r="V287" s="3" t="n">
         <v>0.001046025104602468</v>
       </c>
+      <c r="W287" s="1" t="n">
+        <v>0.15352</v>
+      </c>
+      <c r="X287" s="3" t="n">
+        <v>0.002612330198536988</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -20651,6 +22379,12 @@
       <c r="V288" s="2" t="n">
         <v>-0.000554016620498554</v>
       </c>
+      <c r="W288" s="1" t="n">
+        <v>0.1799</v>
+      </c>
+      <c r="X288" s="2" t="n">
+        <v>-0.002771618625277164</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -20721,6 +22455,12 @@
       <c r="V289" s="3" t="n">
         <v>0.001205981669078604</v>
       </c>
+      <c r="W289" s="1" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="X289" s="2" t="n">
+        <v>-0.001204529029149577</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -20791,6 +22531,12 @@
       <c r="V290" s="3" t="n">
         <v>0.006571998591714646</v>
       </c>
+      <c r="W290" s="1" t="n">
+        <v>0.08558</v>
+      </c>
+      <c r="X290" s="2" t="n">
+        <v>-0.002215226769266593</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -20861,6 +22607,12 @@
       <c r="V291" s="3" t="n">
         <v>0.001126443255420962</v>
       </c>
+      <c r="W291" s="1" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="X291" s="2" t="n">
+        <v>-0.002812939521800167</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -20931,6 +22683,12 @@
       <c r="V292" s="3" t="n">
         <v>0.002044711014176589</v>
       </c>
+      <c r="W292" s="1" t="n">
+        <v>1.4722</v>
+      </c>
+      <c r="X292" s="3" t="n">
+        <v>0.001360359134811592</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -21001,6 +22759,12 @@
       <c r="V293" s="2" t="n">
         <v>-0.003588516746411515</v>
       </c>
+      <c r="W293" s="1" t="n">
+        <v>0.005822</v>
+      </c>
+      <c r="X293" s="2" t="n">
+        <v>-0.001543474532670267</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -21071,6 +22835,12 @@
       <c r="V294" s="3" t="n">
         <v>0.003508771929824647</v>
       </c>
+      <c r="W294" s="1" t="n">
+        <v>0.003435</v>
+      </c>
+      <c r="X294" s="3" t="n">
+        <v>0.0008741258741258637</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -21141,6 +22911,12 @@
       <c r="V295" s="3" t="n">
         <v>0.0009285051067781913</v>
       </c>
+      <c r="W295" s="1" t="n">
+        <v>0.5376</v>
+      </c>
+      <c r="X295" s="2" t="n">
+        <v>-0.002597402597402723</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -21211,6 +22987,12 @@
       <c r="V296" s="3" t="n">
         <v>0.0008900756564308962</v>
       </c>
+      <c r="W296" s="1" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="X296" s="2" t="n">
+        <v>-0.003112494441974263</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -21281,6 +23063,12 @@
       <c r="V297" s="3" t="n">
         <v>0.0005927682276229753</v>
       </c>
+      <c r="W297" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="X297" s="3" t="n">
+        <v>0.0005924170616113503</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -21351,6 +23139,12 @@
       <c r="V298" s="3" t="n">
         <v>0.001949860724234078</v>
       </c>
+      <c r="W298" s="1" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="X298" s="3" t="n">
+        <v>0.01918265221017504</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -21421,6 +23215,12 @@
       <c r="V299" s="3" t="n">
         <v>0.001808318264014393</v>
       </c>
+      <c r="W299" s="1" t="n">
+        <v>0.01109</v>
+      </c>
+      <c r="X299" s="3" t="n">
+        <v>0.0009025270758122376</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -21491,6 +23291,12 @@
       <c r="V300" s="2" t="n">
         <v>-0.0009680542110359464</v>
       </c>
+      <c r="W300" s="1" t="n">
+        <v>0.02064</v>
+      </c>
+      <c r="X300" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -21561,6 +23367,12 @@
       <c r="V301" s="3" t="n">
         <v>0.004572175048987448</v>
       </c>
+      <c r="W301" s="1" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="X301" s="2" t="n">
+        <v>-0.001950585175552632</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -21631,6 +23443,12 @@
       <c r="V302" s="2" t="n">
         <v>-0.003625815808556903</v>
       </c>
+      <c r="W302" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="X302" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -21701,6 +23519,12 @@
       <c r="V303" s="3" t="n">
         <v>0.0009478672985782074</v>
       </c>
+      <c r="W303" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="X303" s="3" t="n">
+        <v>0.001082251082251038</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -21771,6 +23595,12 @@
       <c r="V304" s="3" t="n">
         <v>0.00315855969677814</v>
       </c>
+      <c r="W304" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="X304" s="2" t="n">
+        <v>-0.0006297229219143321</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -21841,6 +23671,12 @@
       <c r="V305" s="2" t="n">
         <v>-0.002011449791118754</v>
       </c>
+      <c r="W305" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="X305" s="2" t="n">
+        <v>-0.003100775193798538</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -21911,6 +23747,12 @@
       <c r="V306" s="3" t="n">
         <v>0.00606305578011307</v>
       </c>
+      <c r="W306" s="1" t="n">
+        <v>0.04974</v>
+      </c>
+      <c r="X306" s="2" t="n">
+        <v>-0.0008035355564483402</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -21981,6 +23823,12 @@
       <c r="V307" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W307" s="1" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="X307" s="2" t="n">
+        <v>-0.001088139281828075</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -22051,6 +23899,12 @@
       <c r="V308" s="2" t="n">
         <v>-0.002758274824473395</v>
       </c>
+      <c r="W308" s="1" t="n">
+        <v>0.03976</v>
+      </c>
+      <c r="X308" s="2" t="n">
+        <v>-0.0002514458134272834</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -22121,6 +23975,12 @@
       <c r="V309" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W309" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="X309" s="2" t="n">
+        <v>-0.005750798722044826</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -22191,6 +24051,12 @@
       <c r="V310" s="3" t="n">
         <v>0.001475198229762064</v>
       </c>
+      <c r="W310" s="1" t="n">
+        <v>0.05426</v>
+      </c>
+      <c r="X310" s="2" t="n">
+        <v>-0.0009206407659730159</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -22261,6 +24127,12 @@
       <c r="V311" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W311" s="1" t="n">
+        <v>0.004479</v>
+      </c>
+      <c r="X311" s="3" t="n">
+        <v>0.004485310607759599</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -22331,6 +24203,12 @@
       <c r="V312" s="3" t="n">
         <v>0.0009459619250324788</v>
       </c>
+      <c r="W312" s="1" t="n">
+        <v>0.08467</v>
+      </c>
+      <c r="X312" s="3" t="n">
+        <v>0.0002362669816892173</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -22401,6 +24279,12 @@
       <c r="V313" s="3" t="n">
         <v>0.001069232825447698</v>
       </c>
+      <c r="W313" s="1" t="n">
+        <v>0.07475999999999999</v>
+      </c>
+      <c r="X313" s="2" t="n">
+        <v>-0.001869158878504689</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -22471,6 +24355,12 @@
       <c r="V314" s="3" t="n">
         <v>0.001306335728282025</v>
       </c>
+      <c r="W314" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="X314" s="2" t="n">
+        <v>-0.001304631441617599</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -22541,6 +24431,12 @@
       <c r="V315" s="3" t="n">
         <v>0.0006253908692934131</v>
       </c>
+      <c r="W315" s="1" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="X315" s="2" t="n">
+        <v>-0.001874999999999967</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -22611,6 +24507,12 @@
       <c r="V316" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W316" s="1" t="n">
+        <v>0.1812</v>
+      </c>
+      <c r="X316" s="2" t="n">
+        <v>-0.002751788662630712</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -22681,6 +24583,12 @@
       <c r="V317" s="2" t="n">
         <v>-0.0005338315761376837</v>
       </c>
+      <c r="W317" s="1" t="n">
+        <v>0.007487</v>
+      </c>
+      <c r="X317" s="2" t="n">
+        <v>-0.000267058352250002</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -22751,6 +24659,12 @@
       <c r="V318" s="3" t="n">
         <v>0.003198081151309223</v>
       </c>
+      <c r="W318" s="1" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="X318" s="3" t="n">
+        <v>0.002590157401872847</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -22821,6 +24735,12 @@
       <c r="V319" s="2" t="n">
         <v>-0.003586157432311282</v>
       </c>
+      <c r="W319" s="1" t="n">
+        <v>0.27805</v>
+      </c>
+      <c r="X319" s="3" t="n">
+        <v>0.0007198128486594691</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -22891,6 +24811,12 @@
       <c r="V320" s="3" t="n">
         <v>0.0004544421722336594</v>
       </c>
+      <c r="W320" s="1" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="X320" s="2" t="n">
+        <v>-0.0004542357483534714</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -22961,6 +24887,12 @@
       <c r="V321" s="3" t="n">
         <v>0.004652364952184017</v>
       </c>
+      <c r="W321" s="1" t="n">
+        <v>0.07764</v>
+      </c>
+      <c r="X321" s="2" t="n">
+        <v>-0.001286339078981256</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -23031,6 +24963,12 @@
       <c r="V322" s="3" t="n">
         <v>0.001224739742804689</v>
       </c>
+      <c r="W322" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="X322" s="3" t="n">
+        <v>0.001223241590214102</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -23101,6 +25039,12 @@
       <c r="V323" s="3" t="n">
         <v>0.0005045408678103491</v>
       </c>
+      <c r="W323" s="1" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="X323" s="2" t="n">
+        <v>-0.002521432173474592</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -23171,6 +25115,12 @@
       <c r="V324" s="3" t="n">
         <v>0.001483846731780536</v>
       </c>
+      <c r="W324" s="1" t="n">
+        <v>0.05322</v>
+      </c>
+      <c r="X324" s="2" t="n">
+        <v>-0.001856749001294003</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -23241,6 +25191,12 @@
       <c r="V325" s="2" t="n">
         <v>-0.002465611212042689</v>
       </c>
+      <c r="W325" s="1" t="n">
+        <v>0.15373</v>
+      </c>
+      <c r="X325" s="2" t="n">
+        <v>-6.504488096775234e-05</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -23311,6 +25267,12 @@
       <c r="V326" s="2" t="n">
         <v>-0.000309645455952975</v>
       </c>
+      <c r="W326" s="1" t="n">
+        <v>0.006458</v>
+      </c>
+      <c r="X326" s="3" t="n">
+        <v>0.0001548706829797325</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -23381,6 +25343,12 @@
       <c r="V327" s="2" t="n">
         <v>-0.0007887990534412405</v>
       </c>
+      <c r="W327" s="1" t="n">
+        <v>0.015189</v>
+      </c>
+      <c r="X327" s="2" t="n">
+        <v>-0.0007894217485691638</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -23451,6 +25419,12 @@
       <c r="V328" s="3" t="n">
         <v>0.004197271773347299</v>
       </c>
+      <c r="W328" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="X328" s="2" t="n">
+        <v>-0.001044932079414723</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -23521,6 +25495,12 @@
       <c r="V329" s="2" t="n">
         <v>-0.001810364335822628</v>
       </c>
+      <c r="W329" s="1" t="n">
+        <v>0.004402</v>
+      </c>
+      <c r="X329" s="2" t="n">
+        <v>-0.002040353661301366</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -23591,6 +25571,12 @@
       <c r="V330" s="2" t="n">
         <v>-0.000193836014731462</v>
       </c>
+      <c r="W330" s="1" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="X330" s="3" t="n">
+        <v>0.0003877471888328652</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -23661,6 +25647,12 @@
       <c r="V331" s="3" t="n">
         <v>0.003038674033149143</v>
       </c>
+      <c r="W331" s="1" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="X331" s="2" t="n">
+        <v>-0.005783530707794047</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -23731,6 +25723,12 @@
       <c r="V332" s="3" t="n">
         <v>0.005464480874316907</v>
       </c>
+      <c r="W332" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="X332" s="2" t="n">
+        <v>-0.001358695652173952</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -23801,6 +25799,12 @@
       <c r="V333" s="3" t="n">
         <v>0.001036269430051843</v>
       </c>
+      <c r="W333" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="X333" s="2" t="n">
+        <v>-0.00310559006211189</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -23871,6 +25875,12 @@
       <c r="V334" s="3" t="n">
         <v>0.002046384720327417</v>
       </c>
+      <c r="W334" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="X334" s="2" t="n">
+        <v>-0.001588382119355585</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -23941,6 +25951,12 @@
       <c r="V335" s="3" t="n">
         <v>0.003455936805727012</v>
       </c>
+      <c r="W335" s="1" t="n">
+        <v>0.08201</v>
+      </c>
+      <c r="X335" s="3" t="n">
+        <v>0.008733087330873338</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -24011,6 +26027,12 @@
       <c r="V336" s="3" t="n">
         <v>0.002447381302006855</v>
       </c>
+      <c r="W336" s="1" t="n">
+        <v>0.2047</v>
+      </c>
+      <c r="X336" s="2" t="n">
+        <v>-0.0004882812500000817</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -24081,6 +26103,12 @@
       <c r="V337" s="3" t="n">
         <v>0.000983284169124837</v>
       </c>
+      <c r="W337" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="X337" s="2" t="n">
+        <v>-0.002946954813359579</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -24151,6 +26179,12 @@
       <c r="V338" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W338" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="X338" s="2" t="n">
+        <v>-0.0008849557522124147</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -24221,6 +26255,12 @@
       <c r="V339" s="3" t="n">
         <v>0.004378762999452666</v>
       </c>
+      <c r="W339" s="1" t="n">
+        <v>0.01834</v>
+      </c>
+      <c r="X339" s="2" t="n">
+        <v>-0.0005449591280655619</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -24291,6 +26331,12 @@
       <c r="V340" s="2" t="n">
         <v>-0.01307424302287984</v>
       </c>
+      <c r="W340" s="1" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="X340" s="2" t="n">
+        <v>-0.001892491902318377</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -24361,6 +26407,12 @@
       <c r="V341" s="3" t="n">
         <v>0.001166044776119436</v>
       </c>
+      <c r="W341" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="X341" s="2" t="n">
+        <v>-0.003494060097833783</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -24431,6 +26483,12 @@
       <c r="V342" s="3" t="n">
         <v>0.00311890838206615</v>
       </c>
+      <c r="W342" s="1" t="n">
+        <v>0.07677</v>
+      </c>
+      <c r="X342" s="2" t="n">
+        <v>-0.00544111931597344</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -24501,6 +26559,12 @@
       <c r="V343" s="3" t="n">
         <v>0.001697792869269936</v>
       </c>
+      <c r="W343" s="1" t="n">
+        <v>7.648</v>
+      </c>
+      <c r="X343" s="2" t="n">
+        <v>-0.002868318122555442</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -24571,6 +26635,12 @@
       <c r="V344" s="2" t="n">
         <v>-0.002493765586035007</v>
       </c>
+      <c r="W344" s="1" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="X344" s="2" t="n">
+        <v>-0.0008333333333332416</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -24641,6 +26711,12 @@
       <c r="V345" s="3" t="n">
         <v>0.00107353730542132</v>
       </c>
+      <c r="W345" s="1" t="n">
+        <v>0.03734</v>
+      </c>
+      <c r="X345" s="3" t="n">
+        <v>0.00107238605898119</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -24711,6 +26787,12 @@
       <c r="V346" s="3" t="n">
         <v>0.004830917874396106</v>
       </c>
+      <c r="W346" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="X346" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -24781,6 +26863,12 @@
       <c r="V347" s="3" t="n">
         <v>0.002294893861158828</v>
       </c>
+      <c r="W347" s="1" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="X347" s="3" t="n">
+        <v>0.001144819690898716</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -24851,6 +26939,12 @@
       <c r="V348" s="2" t="n">
         <v>-0.0005969804344477668</v>
       </c>
+      <c r="W348" s="1" t="n">
+        <v>5188.4</v>
+      </c>
+      <c r="X348" s="2" t="n">
+        <v>-0.0002504961751161304</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -24921,6 +27015,12 @@
       <c r="V349" s="2" t="n">
         <v>-0.00358680057388807</v>
       </c>
+      <c r="W349" s="1" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="X349" s="2" t="n">
+        <v>-0.0007199424046076021</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -24991,6 +27091,12 @@
       <c r="V350" s="3" t="n">
         <v>0.006596306068601543</v>
       </c>
+      <c r="W350" s="1" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="X350" s="3" t="n">
+        <v>0.01572739187418091</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -25061,6 +27167,12 @@
       <c r="V351" s="2" t="n">
         <v>-0.002623811085601723</v>
       </c>
+      <c r="W351" s="1" t="n">
+        <v>0.0006089</v>
+      </c>
+      <c r="X351" s="3" t="n">
+        <v>0.001150937191713191</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -25131,6 +27243,12 @@
       <c r="V352" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W352" s="1" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="X352" s="2" t="n">
+        <v>-0.006054490413723614</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -25201,6 +27319,12 @@
       <c r="V353" s="2" t="n">
         <v>-0.0001073537305420947</v>
       </c>
+      <c r="W353" s="1" t="n">
+        <v>0.09344</v>
+      </c>
+      <c r="X353" s="3" t="n">
+        <v>0.003220957698088841</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -25271,6 +27395,12 @@
       <c r="V354" s="3" t="n">
         <v>0.001104972375690639</v>
       </c>
+      <c r="W354" s="1" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="X354" s="2" t="n">
+        <v>-0.004415011037527567</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -25341,6 +27471,12 @@
       <c r="V355" s="3" t="n">
         <v>0.002860320991578014</v>
       </c>
+      <c r="W355" s="1" t="n">
+        <v>0.0006238</v>
+      </c>
+      <c r="X355" s="2" t="n">
+        <v>-0.01156710505466648</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -25411,6 +27547,12 @@
       <c r="V356" s="2" t="n">
         <v>-0.0009828009828010927</v>
       </c>
+      <c r="W356" s="1" t="n">
+        <v>2.039</v>
+      </c>
+      <c r="X356" s="3" t="n">
+        <v>0.002951303492375911</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -25481,6 +27623,12 @@
       <c r="V357" s="3" t="n">
         <v>0.0004384042086803855</v>
       </c>
+      <c r="W357" s="1" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="X357" s="3" t="n">
+        <v>0.006134969325153428</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -25551,6 +27699,12 @@
       <c r="V358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="X358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -25621,6 +27775,12 @@
       <c r="V359" s="3" t="n">
         <v>0.002046384720327457</v>
       </c>
+      <c r="W359" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="X359" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -25691,6 +27851,12 @@
       <c r="V360" s="3" t="n">
         <v>0.0006009615384616183</v>
       </c>
+      <c r="W360" s="1" t="n">
+        <v>0.003326</v>
+      </c>
+      <c r="X360" s="2" t="n">
+        <v>-0.00120120120120123</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -25761,6 +27927,12 @@
       <c r="V361" s="3" t="n">
         <v>0.001713929573075709</v>
       </c>
+      <c r="W361" s="1" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="X361" s="2" t="n">
+        <v>-0.004044174832788998</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -25831,6 +28003,12 @@
       <c r="V362" s="3" t="n">
         <v>0.00428816466552313</v>
       </c>
+      <c r="W362" s="1" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="X362" s="3" t="n">
+        <v>0.002134927412468037</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25901,6 +28079,12 @@
       <c r="V363" s="3" t="n">
         <v>0.0001530221882172322</v>
       </c>
+      <c r="W363" s="1" t="n">
+        <v>0.06523</v>
+      </c>
+      <c r="X363" s="2" t="n">
+        <v>-0.001988984088127373</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25971,6 +28155,12 @@
       <c r="V364" s="2" t="n">
         <v>-0.002120890774125087</v>
       </c>
+      <c r="W364" s="1" t="n">
+        <v>4.709</v>
+      </c>
+      <c r="X364" s="3" t="n">
+        <v>0.0008501594048883229</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -26041,6 +28231,12 @@
       <c r="V365" s="3" t="n">
         <v>0.003777280358142032</v>
       </c>
+      <c r="W365" s="1" t="n">
+        <v>0.07192999999999999</v>
+      </c>
+      <c r="X365" s="3" t="n">
+        <v>0.002508710801393723</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -26111,6 +28307,12 @@
       <c r="V366" s="2" t="n">
         <v>-0.002131817374311637</v>
       </c>
+      <c r="W366" s="1" t="n">
+        <v>0.05609</v>
+      </c>
+      <c r="X366" s="2" t="n">
+        <v>-0.001424247819120469</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -26181,6 +28383,12 @@
       <c r="V367" s="3" t="n">
         <v>0.001196581196581088</v>
       </c>
+      <c r="W367" s="1" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="X367" s="2" t="n">
+        <v>-0.001878094587672853</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -26251,6 +28459,12 @@
       <c r="V368" s="3" t="n">
         <v>0.0005236515971374105</v>
       </c>
+      <c r="W368" s="1" t="n">
+        <v>0.05729</v>
+      </c>
+      <c r="X368" s="2" t="n">
+        <v>-0.0005233775296580992</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -26321,6 +28535,12 @@
       <c r="V369" s="3" t="n">
         <v>0.0009677419354838315</v>
       </c>
+      <c r="W369" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="X369" s="2" t="n">
+        <v>-0.0009668063164678949</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -26391,6 +28611,12 @@
       <c r="V370" s="3" t="n">
         <v>0.001849568434031937</v>
       </c>
+      <c r="W370" s="1" t="n">
+        <v>0.0001623</v>
+      </c>
+      <c r="X370" s="2" t="n">
+        <v>-0.001230769230769261</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -26461,6 +28687,12 @@
       <c r="V371" s="3" t="n">
         <v>0.001025490770583074</v>
       </c>
+      <c r="W371" s="1" t="n">
+        <v>0.006826</v>
+      </c>
+      <c r="X371" s="2" t="n">
+        <v>-0.001024440216595941</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -26531,6 +28763,12 @@
       <c r="V372" s="3" t="n">
         <v>0.00314465408805036</v>
       </c>
+      <c r="W372" s="1" t="n">
+        <v>0.006978</v>
+      </c>
+      <c r="X372" s="2" t="n">
+        <v>-0.00569962952408095</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -26601,6 +28839,12 @@
       <c r="V373" s="3" t="n">
         <v>0.001586881777307533</v>
       </c>
+      <c r="W373" s="1" t="n">
+        <v>3.792</v>
+      </c>
+      <c r="X373" s="3" t="n">
+        <v>0.001320306311064139</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -26671,6 +28915,12 @@
       <c r="V374" s="3" t="n">
         <v>0.001135557132718194</v>
       </c>
+      <c r="W374" s="1" t="n">
+        <v>0.07028</v>
+      </c>
+      <c r="X374" s="2" t="n">
+        <v>-0.003544590954203888</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -26741,6 +28991,12 @@
       <c r="V375" s="3" t="n">
         <v>0.005817629948147237</v>
       </c>
+      <c r="W375" s="1" t="n">
+        <v>0.07901</v>
+      </c>
+      <c r="X375" s="2" t="n">
+        <v>-0.006538413177417409</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -26811,6 +29067,12 @@
       <c r="V376" s="3" t="n">
         <v>0.001434262948207058</v>
       </c>
+      <c r="W376" s="1" t="n">
+        <v>0.06275</v>
+      </c>
+      <c r="X376" s="2" t="n">
+        <v>-0.001432208784213763</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -26881,6 +29143,12 @@
       <c r="V377" s="3" t="n">
         <v>0.002355712603062421</v>
       </c>
+      <c r="W377" s="1" t="n">
+        <v>0.07658</v>
+      </c>
+      <c r="X377" s="2" t="n">
+        <v>-0.0001305653479567829</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -26951,6 +29219,12 @@
       <c r="V378" s="3" t="n">
         <v>0.002738361961662864</v>
       </c>
+      <c r="W378" s="1" t="n">
+        <v>0.0004015</v>
+      </c>
+      <c r="X378" s="2" t="n">
+        <v>-0.003227408142998951</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -27021,6 +29295,12 @@
       <c r="V379" s="2" t="n">
         <v>-0.0006713211600430769</v>
       </c>
+      <c r="W379" s="1" t="n">
+        <v>0.07417</v>
+      </c>
+      <c r="X379" s="2" t="n">
+        <v>-0.003493215101437543</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -27091,6 +29371,12 @@
       <c r="V380" s="3" t="n">
         <v>0.004405286343612442</v>
       </c>
+      <c r="W380" s="1" t="n">
+        <v>0.001367</v>
+      </c>
+      <c r="X380" s="2" t="n">
+        <v>-0.0007309941520468806</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -27161,6 +29447,12 @@
       <c r="V381" s="2" t="n">
         <v>-0.0001561280249805361</v>
       </c>
+      <c r="W381" s="1" t="n">
+        <v>6.395</v>
+      </c>
+      <c r="X381" s="2" t="n">
+        <v>-0.001405371642723351</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -27231,6 +29523,12 @@
       <c r="V382" s="3" t="n">
         <v>0.005120702267739621</v>
       </c>
+      <c r="W382" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="X382" s="3" t="n">
+        <v>0.01455604075691403</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -27301,6 +29599,12 @@
       <c r="V383" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W383" s="1" t="n">
+        <v>0.01761</v>
+      </c>
+      <c r="X383" s="3" t="n">
+        <v>0.001706484641638353</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -27371,6 +29675,12 @@
       <c r="V384" s="3" t="n">
         <v>0.0009842519685039652</v>
       </c>
+      <c r="W384" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="X384" s="2" t="n">
+        <v>-0.0009832841691249053</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -27441,6 +29751,12 @@
       <c r="V385" s="3" t="n">
         <v>0.0006688963210702595</v>
       </c>
+      <c r="W385" s="1" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="X385" s="3" t="n">
+        <v>0.000222816399286864</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -27511,6 +29827,12 @@
       <c r="V386" s="2" t="n">
         <v>-0.003115264797507695</v>
       </c>
+      <c r="W386" s="1" t="n">
+        <v>0.001306</v>
+      </c>
+      <c r="X386" s="3" t="n">
+        <v>0.02031249999999998</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -27581,6 +29903,12 @@
       <c r="V387" s="3" t="n">
         <v>0.002870651806821998</v>
       </c>
+      <c r="W387" s="1" t="n">
+        <v>0.0005944</v>
+      </c>
+      <c r="X387" s="3" t="n">
+        <v>0.0008418925745076047</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -27651,6 +29979,12 @@
       <c r="V388" s="3" t="n">
         <v>0.000875656742556882</v>
       </c>
+      <c r="W388" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="X388" s="3" t="n">
+        <v>0.0008748906386702824</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -27721,6 +30055,12 @@
       <c r="V389" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W389" s="1" t="n">
+        <v>0.009050000000000001</v>
+      </c>
+      <c r="X389" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -27791,6 +30131,12 @@
       <c r="V390" s="3" t="n">
         <v>0.0006328312871789441</v>
       </c>
+      <c r="W390" s="1" t="n">
+        <v>0.07889</v>
+      </c>
+      <c r="X390" s="2" t="n">
+        <v>-0.00215026562104735</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -27861,6 +30207,12 @@
       <c r="V391" s="2" t="n">
         <v>-0.002323330106486003</v>
       </c>
+      <c r="W391" s="1" t="n">
+        <v>0.05154</v>
+      </c>
+      <c r="X391" s="3" t="n">
+        <v>0.0001940617116243559</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -27931,6 +30283,12 @@
       <c r="V392" s="2" t="n">
         <v>-0.008403361344537837</v>
       </c>
+      <c r="W392" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="X392" s="3" t="n">
+        <v>0.004237288135593232</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -28001,6 +30359,12 @@
       <c r="V393" s="2" t="n">
         <v>-0.002797202797202845</v>
       </c>
+      <c r="W393" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="X393" s="2" t="n">
+        <v>-0.0004675081813931553</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -28071,6 +30435,12 @@
       <c r="V394" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W394" s="1" t="n">
+        <v>0.2037</v>
+      </c>
+      <c r="X394" s="2" t="n">
+        <v>-0.002936857562408307</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -28141,6 +30511,12 @@
       <c r="V395" s="3" t="n">
         <v>0.001028806584362169</v>
       </c>
+      <c r="W395" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="X395" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -28211,6 +30587,12 @@
       <c r="V396" s="3" t="n">
         <v>0.002941176470588238</v>
       </c>
+      <c r="W396" s="1" t="n">
+        <v>2.731</v>
+      </c>
+      <c r="X396" s="3" t="n">
+        <v>0.001099706744867914</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -28281,6 +30663,12 @@
       <c r="V397" s="3" t="n">
         <v>0.003968253968253884</v>
       </c>
+      <c r="W397" s="1" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="X397" s="2" t="n">
+        <v>-0.007905138339920957</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -28351,6 +30739,12 @@
       <c r="V398" s="2" t="n">
         <v>-0.00257034632034631</v>
       </c>
+      <c r="W398" s="1" t="n">
+        <v>0.007349</v>
+      </c>
+      <c r="X398" s="2" t="n">
+        <v>-0.003255120032551279</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -28421,6 +30815,12 @@
       <c r="V399" s="3" t="n">
         <v>0.001158748551564183</v>
       </c>
+      <c r="W399" s="1" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="X399" s="3" t="n">
+        <v>0.0007716049382717341</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -28491,6 +30891,12 @@
       <c r="V400" s="3" t="n">
         <v>0.0003137747097583589</v>
       </c>
+      <c r="W400" s="1" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="X400" s="2" t="n">
+        <v>-0.001254705144290954</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -28561,6 +30967,12 @@
       <c r="V401" s="3" t="n">
         <v>0.001246882793017502</v>
       </c>
+      <c r="W401" s="1" t="n">
+        <v>0.007227</v>
+      </c>
+      <c r="X401" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -28631,6 +31043,12 @@
       <c r="V402" s="3" t="n">
         <v>0.008073314422867054</v>
       </c>
+      <c r="W402" s="1" t="n">
+        <v>0.004589</v>
+      </c>
+      <c r="X402" s="2" t="n">
+        <v>-0.006709956709956662</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -28701,6 +31119,12 @@
       <c r="V403" s="3" t="n">
         <v>0.002264150943396187</v>
       </c>
+      <c r="W403" s="1" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="X403" s="2" t="n">
+        <v>-0.002635542168674618</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -28771,6 +31195,12 @@
       <c r="V404" s="3" t="n">
         <v>0.003344481605351151</v>
       </c>
+      <c r="W404" s="1" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="X404" s="3" t="n">
+        <v>0.001250000000000094</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -28841,6 +31271,12 @@
       <c r="V405" s="3" t="n">
         <v>0.001942857142857128</v>
       </c>
+      <c r="W405" s="1" t="n">
+        <v>0.0008765999999999999</v>
+      </c>
+      <c r="X405" s="2" t="n">
+        <v>-0.0001140641040265275</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -28911,6 +31347,12 @@
       <c r="V406" s="3" t="n">
         <v>0.000788954635108586</v>
       </c>
+      <c r="W406" s="1" t="n">
+        <v>0.005068</v>
+      </c>
+      <c r="X406" s="2" t="n">
+        <v>-0.001182499014584311</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -28981,6 +31423,12 @@
       <c r="V407" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W407" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="X407" s="2" t="n">
+        <v>-0.0008312551953450812</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -29051,6 +31499,12 @@
       <c r="V408" s="3" t="n">
         <v>0.001377410468319593</v>
       </c>
+      <c r="W408" s="1" t="n">
+        <v>0.001458</v>
+      </c>
+      <c r="X408" s="3" t="n">
+        <v>0.002751031636863891</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -29121,6 +31575,12 @@
       <c r="V409" s="3" t="n">
         <v>0.002132764596107618</v>
       </c>
+      <c r="W409" s="1" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="X409" s="3" t="n">
+        <v>0.007448789571694665</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -29191,6 +31651,12 @@
       <c r="V410" s="3" t="n">
         <v>0.003076923076922952</v>
       </c>
+      <c r="W410" s="1" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="X410" s="3" t="n">
+        <v>0.0006134969325155254</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -29261,6 +31727,12 @@
       <c r="V411" s="2" t="n">
         <v>-0.001050972149238075</v>
       </c>
+      <c r="W411" s="1" t="n">
+        <v>0.1895</v>
+      </c>
+      <c r="X411" s="2" t="n">
+        <v>-0.003156233561283479</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -29331,6 +31803,12 @@
       <c r="V412" s="3" t="n">
         <v>0.004904146232723985</v>
       </c>
+      <c r="W412" s="1" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="X412" s="3" t="n">
+        <v>0.0034013605442176</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -29401,6 +31879,12 @@
       <c r="V413" s="3" t="n">
         <v>0.0003940110323089047</v>
       </c>
+      <c r="W413" s="1" t="n">
+        <v>2535</v>
+      </c>
+      <c r="X413" s="2" t="n">
+        <v>-0.001575423395037416</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -29471,6 +31955,12 @@
       <c r="V414" s="2" t="n">
         <v>-0.002465857359635909</v>
       </c>
+      <c r="W414" s="1" t="n">
+        <v>0.05247</v>
+      </c>
+      <c r="X414" s="2" t="n">
+        <v>-0.002281802624072925</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -29541,6 +32031,12 @@
       <c r="V415" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W415" s="1" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="X415" s="2" t="n">
+        <v>-0.0005753739930954488</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -29611,6 +32107,12 @@
       <c r="V416" s="3" t="n">
         <v>0.002032815449397433</v>
       </c>
+      <c r="W416" s="1" t="n">
+        <v>0.06908</v>
+      </c>
+      <c r="X416" s="3" t="n">
+        <v>0.001014345746993198</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -29681,6 +32183,12 @@
       <c r="V417" s="2" t="n">
         <v>-0.01333333333333335</v>
       </c>
+      <c r="W417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="X417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -29751,6 +32259,12 @@
       <c r="V418" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W418" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="X418" s="2" t="n">
+        <v>-0.003267973856209153</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -29821,6 +32335,12 @@
       <c r="V419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="X419" s="3" t="n">
+        <v>0.008130081300812959</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -29891,6 +32411,12 @@
       <c r="V420" s="2" t="n">
         <v>-0.002073613271125031</v>
       </c>
+      <c r="W420" s="1" t="n">
+        <v>0.01911</v>
+      </c>
+      <c r="X420" s="2" t="n">
+        <v>-0.007272727272727337</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -29961,6 +32487,12 @@
       <c r="V421" s="3" t="n">
         <v>0.005118395202150712</v>
       </c>
+      <c r="W421" s="1" t="n">
+        <v>0.19546</v>
+      </c>
+      <c r="X421" s="3" t="n">
+        <v>0.005400956740908366</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -30031,6 +32563,12 @@
       <c r="V422" s="2" t="n">
         <v>-0.0002934272300468346</v>
       </c>
+      <c r="W422" s="1" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="X422" s="3" t="n">
+        <v>0.0008805400645728003</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -30101,6 +32639,12 @@
       <c r="V423" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W423" s="1" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="X423" s="3" t="n">
+        <v>0.0007062146892654589</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -30171,6 +32715,12 @@
       <c r="V424" s="2" t="n">
         <v>-0.001893939393939317</v>
       </c>
+      <c r="W424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="X424" s="3" t="n">
+        <v>0.003795066413662249</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -30241,6 +32791,12 @@
       <c r="V425" s="2" t="n">
         <v>-0.00095419847328247</v>
       </c>
+      <c r="W425" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="X425" s="2" t="n">
+        <v>-0.002865329512893932</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -30311,6 +32867,12 @@
       <c r="V426" s="3" t="n">
         <v>0.0007106310403639374</v>
       </c>
+      <c r="W426" s="1" t="n">
+        <v>0.00705</v>
+      </c>
+      <c r="X426" s="3" t="n">
+        <v>0.001278227524499284</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -30381,6 +32943,12 @@
       <c r="V427" s="3" t="n">
         <v>0.0007858546168958422</v>
       </c>
+      <c r="W427" s="1" t="n">
+        <v>0.02544</v>
+      </c>
+      <c r="X427" s="2" t="n">
+        <v>-0.001177856301531165</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -30451,6 +33019,12 @@
       <c r="V428" s="3" t="n">
         <v>0.00149290868375216</v>
       </c>
+      <c r="W428" s="1" t="n">
+        <v>0.008052</v>
+      </c>
+      <c r="X428" s="3" t="n">
+        <v>0.0002484472049689771</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -30521,6 +33095,12 @@
       <c r="V429" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W429" s="1" t="n">
+        <v>0.01238</v>
+      </c>
+      <c r="X429" s="2" t="n">
+        <v>-0.0008071025020177234</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -30591,6 +33171,12 @@
       <c r="V430" s="2" t="n">
         <v>-0.001346096320670158</v>
       </c>
+      <c r="W430" s="1" t="n">
+        <v>0.06676</v>
+      </c>
+      <c r="X430" s="2" t="n">
+        <v>-0.0001497678598172252</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -30661,6 +33247,12 @@
       <c r="V431" s="3" t="n">
         <v>0.001851851851851776</v>
       </c>
+      <c r="W431" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="X431" s="2" t="n">
+        <v>-0.001848428835489758</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -30731,6 +33323,12 @@
       <c r="V432" s="3" t="n">
         <v>0.003924808923776063</v>
       </c>
+      <c r="W432" s="1" t="n">
+        <v>0.009651</v>
+      </c>
+      <c r="X432" s="2" t="n">
+        <v>-0.007098765432098727</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -30801,6 +33399,12 @@
       <c r="V433" s="3" t="n">
         <v>0.001933768431230449</v>
       </c>
+      <c r="W433" s="1" t="n">
+        <v>0.04141</v>
+      </c>
+      <c r="X433" s="2" t="n">
+        <v>-0.0009650180940892248</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -30871,6 +33475,12 @@
       <c r="V434" s="3" t="n">
         <v>0.001918005274514593</v>
       </c>
+      <c r="W434" s="1" t="n">
+        <v>0.04192</v>
+      </c>
+      <c r="X434" s="3" t="n">
+        <v>0.00311079205551563</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -30941,6 +33551,12 @@
       <c r="V435" s="3" t="n">
         <v>0.000648508430609684</v>
       </c>
+      <c r="W435" s="1" t="n">
+        <v>0.001541</v>
+      </c>
+      <c r="X435" s="2" t="n">
+        <v>-0.001296176279974108</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -31011,6 +33627,12 @@
       <c r="V436" s="3" t="n">
         <v>0.002917578409919774</v>
       </c>
+      <c r="W436" s="1" t="n">
+        <v>0.02741</v>
+      </c>
+      <c r="X436" s="2" t="n">
+        <v>-0.003272727272727266</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -31081,6 +33703,12 @@
       <c r="V437" s="2" t="n">
         <v>-0.00134375763498655</v>
       </c>
+      <c r="W437" s="1" t="n">
+        <v>0.08189</v>
+      </c>
+      <c r="X437" s="3" t="n">
+        <v>0.001712538226299709</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -31151,6 +33779,12 @@
       <c r="V438" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W438" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="X438" s="2" t="n">
+        <v>-0.0008688097306688878</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -31221,6 +33855,12 @@
       <c r="V439" s="2" t="n">
         <v>-0.0006472491909384401</v>
       </c>
+      <c r="W439" s="1" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="X439" s="3" t="n">
+        <v>0.0006476683937823121</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -31291,6 +33931,12 @@
       <c r="V440" s="3" t="n">
         <v>0.001111111111111138</v>
       </c>
+      <c r="W440" s="1" t="n">
+        <v>0.001801</v>
+      </c>
+      <c r="X440" s="2" t="n">
+        <v>-0.0005549389567147147</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -31361,6 +34007,12 @@
       <c r="V441" s="2" t="n">
         <v>-0.0013502565487443</v>
       </c>
+      <c r="W441" s="1" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="X441" s="2" t="n">
+        <v>-0.001622498647917727</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -31431,6 +34083,12 @@
       <c r="V442" s="3" t="n">
         <v>0.001084010840108357</v>
       </c>
+      <c r="W442" s="1" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="X442" s="2" t="n">
+        <v>-0.001624255549539728</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -31501,6 +34159,12 @@
       <c r="V443" s="2" t="n">
         <v>-0.002582361687142945</v>
       </c>
+      <c r="W443" s="1" t="n">
+        <v>0.12712</v>
+      </c>
+      <c r="X443" s="2" t="n">
+        <v>-0.002667503530519216</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -31571,6 +34235,12 @@
       <c r="V444" s="2" t="n">
         <v>-0.002339485313231024</v>
       </c>
+      <c r="W444" s="1" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="X444" s="2" t="n">
+        <v>-0.003821434775056508</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -31641,6 +34311,12 @@
       <c r="V445" s="3" t="n">
         <v>0.000247279920870501</v>
       </c>
+      <c r="W445" s="1" t="n">
+        <v>0.08084</v>
+      </c>
+      <c r="X445" s="2" t="n">
+        <v>-0.0007416563658838627</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -31711,6 +34387,12 @@
       <c r="V446" s="3" t="n">
         <v>0.001890359168242012</v>
       </c>
+      <c r="W446" s="1" t="n">
+        <v>0.0002131</v>
+      </c>
+      <c r="X446" s="3" t="n">
+        <v>0.005188679245283017</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -31781,6 +34463,12 @@
       <c r="V447" s="3" t="n">
         <v>0.01510574018126892</v>
       </c>
+      <c r="W447" s="1" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="X447" s="2" t="n">
+        <v>-0.002976190476190484</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -31851,6 +34539,12 @@
       <c r="V448" s="2" t="n">
         <v>-0.01173662223990452</v>
       </c>
+      <c r="W448" s="1" t="n">
+        <v>0.10031</v>
+      </c>
+      <c r="X448" s="3" t="n">
+        <v>0.009561191626408942</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -31921,6 +34615,12 @@
       <c r="V449" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W449" s="1" t="n">
+        <v>0.001677</v>
+      </c>
+      <c r="X449" s="2" t="n">
+        <v>-0.002972651605231746</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -31991,6 +34691,12 @@
       <c r="V450" s="2" t="n">
         <v>-0.001452081316553762</v>
       </c>
+      <c r="W450" s="1" t="n">
+        <v>0.0002059</v>
+      </c>
+      <c r="X450" s="2" t="n">
+        <v>-0.001938923897237081</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -32061,6 +34767,12 @@
       <c r="V451" s="2" t="n">
         <v>-0.0007587253414263875</v>
       </c>
+      <c r="W451" s="1" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="X451" s="3" t="n">
+        <v>0.00379650721336376</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -32131,6 +34843,12 @@
       <c r="V452" s="3" t="n">
         <v>0.00148920327624725</v>
       </c>
+      <c r="W452" s="1" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="X452" s="2" t="n">
+        <v>-0.000743494423791946</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -32201,6 +34919,12 @@
       <c r="V453" s="3" t="n">
         <v>0.001143510577472869</v>
       </c>
+      <c r="W453" s="1" t="n">
+        <v>0.0001747</v>
+      </c>
+      <c r="X453" s="2" t="n">
+        <v>-0.002284408909194801</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -32271,6 +34995,12 @@
       <c r="V454" s="3" t="n">
         <v>0.006705860738563369</v>
       </c>
+      <c r="W454" s="1" t="n">
+        <v>0.11064</v>
+      </c>
+      <c r="X454" s="3" t="n">
+        <v>0.009581166164796016</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -32341,6 +35071,12 @@
       <c r="V455" s="3" t="n">
         <v>0.003790901835594599</v>
       </c>
+      <c r="W455" s="1" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="X455" s="2" t="n">
+        <v>-0.001987676406281059</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -32411,6 +35147,12 @@
       <c r="V456" s="3" t="n">
         <v>0.0004382669671925909</v>
       </c>
+      <c r="W456" s="1" t="n">
+        <v>0.015943</v>
+      </c>
+      <c r="X456" s="2" t="n">
+        <v>-0.002252957006070549</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -32481,6 +35223,12 @@
       <c r="V457" s="3" t="n">
         <v>0.001640322099612246</v>
       </c>
+      <c r="W457" s="1" t="n">
+        <v>0.006698</v>
+      </c>
+      <c r="X457" s="2" t="n">
+        <v>-0.002828643739764764</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -32551,6 +35299,12 @@
       <c r="V458" s="3" t="n">
         <v>0.001247660636306903</v>
       </c>
+      <c r="W458" s="1" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="X458" s="2" t="n">
+        <v>-0.0002076843198338297</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -32621,6 +35375,12 @@
       <c r="V459" s="2" t="n">
         <v>-0.0006281407035176713</v>
       </c>
+      <c r="W459" s="1" t="n">
+        <v>0.006356</v>
+      </c>
+      <c r="X459" s="2" t="n">
+        <v>-0.001257071024512916</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -32691,6 +35451,12 @@
       <c r="V460" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W460" s="1" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="X460" s="2" t="n">
+        <v>-0.005068790731354136</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -32761,6 +35527,12 @@
       <c r="V461" s="3" t="n">
         <v>0.00514617321800079</v>
       </c>
+      <c r="W461" s="1" t="n">
+        <v>0.09132</v>
+      </c>
+      <c r="X461" s="2" t="n">
+        <v>-0.005228758169934729</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -32831,6 +35603,12 @@
       <c r="V462" s="2" t="n">
         <v>-0.005869565217391292</v>
       </c>
+      <c r="W462" s="1" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="X462" s="2" t="n">
+        <v>-0.005029521102121169</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -32901,6 +35679,12 @@
       <c r="V463" s="2" t="n">
         <v>-0.001432664756447057</v>
       </c>
+      <c r="W463" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="X463" s="3" t="n">
+        <v>0.001434720229555303</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -32971,6 +35755,12 @@
       <c r="V464" s="3" t="n">
         <v>0.0007627765064836857</v>
       </c>
+      <c r="W464" s="1" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="X464" s="3" t="n">
+        <v>0.0007621951219511355</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -33041,6 +35831,12 @@
       <c r="V465" s="3" t="n">
         <v>0.0003538570417550919</v>
       </c>
+      <c r="W465" s="1" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="X465" s="2" t="n">
+        <v>-0.009197028652281539</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -33111,6 +35907,12 @@
       <c r="V466" s="2" t="n">
         <v>-0.0007042253521125986</v>
       </c>
+      <c r="W466" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X466" s="3" t="n">
+        <v>0.0007047216349541155</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -33181,6 +35983,12 @@
       <c r="V467" s="2" t="n">
         <v>-0.0005238344683079933</v>
       </c>
+      <c r="W467" s="1" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="X467" s="3" t="n">
+        <v>0.001048218029350062</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -33251,6 +36059,12 @@
       <c r="V468" s="2" t="n">
         <v>-0.003980099502487572</v>
       </c>
+      <c r="W468" s="1" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="X468" s="3" t="n">
+        <v>0.003996003996004006</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -33321,6 +36135,12 @@
       <c r="V469" s="2" t="n">
         <v>-0.00124812780828757</v>
       </c>
+      <c r="W469" s="1" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="X469" s="2" t="n">
+        <v>-0.004998750312421899</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -33391,6 +36211,12 @@
       <c r="V470" s="3" t="n">
         <v>0.001135073779795688</v>
       </c>
+      <c r="W470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="X470" s="2" t="n">
+        <v>-0.001133786848072563</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -33461,6 +36287,12 @@
       <c r="V471" s="3" t="n">
         <v>0.0006193868070609414</v>
       </c>
+      <c r="W471" s="1" t="n">
+        <v>3.226</v>
+      </c>
+      <c r="X471" s="2" t="n">
+        <v>-0.001547508511296779</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -33531,6 +36363,12 @@
       <c r="V472" s="3" t="n">
         <v>0.001196744853997162</v>
       </c>
+      <c r="W472" s="1" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="X472" s="3" t="n">
+        <v>0.008606263447286617</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -33601,6 +36439,12 @@
       <c r="V473" s="2" t="n">
         <v>-0.00159744408945687</v>
       </c>
+      <c r="W473" s="1" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="X473" s="2" t="n">
+        <v>-0.003200000000000003</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -33671,6 +36515,12 @@
       <c r="V474" s="2" t="n">
         <v>-0.0002341646177262926</v>
       </c>
+      <c r="W474" s="1" t="n">
+        <v>0.008547000000000001</v>
+      </c>
+      <c r="X474" s="3" t="n">
+        <v>0.0009368778545498375</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -33741,6 +36591,12 @@
       <c r="V475" s="3" t="n">
         <v>0.0004792715073088709</v>
       </c>
+      <c r="W475" s="1" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="X475" s="3" t="n">
+        <v>0.002634730538922131</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -33811,6 +36667,12 @@
       <c r="V476" s="3" t="n">
         <v>0.001902828872256722</v>
       </c>
+      <c r="W476" s="1" t="n">
+        <v>0.07896</v>
+      </c>
+      <c r="X476" s="2" t="n">
+        <v>-0.0002532286654848348</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -33881,6 +36743,12 @@
       <c r="V477" s="2" t="n">
         <v>-0.0001464021667522143</v>
       </c>
+      <c r="W477" s="1" t="n">
+        <v>0.13651</v>
+      </c>
+      <c r="X477" s="2" t="n">
+        <v>-0.0005856944139395032</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -33951,6 +36819,12 @@
       <c r="V478" s="2" t="n">
         <v>-0.0008426374552348509</v>
       </c>
+      <c r="W478" s="1" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="X478" s="3" t="n">
+        <v>0.0002108370229813001</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -34021,6 +36895,12 @@
       <c r="V479" s="3" t="n">
         <v>0.003201506591337198</v>
       </c>
+      <c r="W479" s="1" t="n">
+        <v>0.005338</v>
+      </c>
+      <c r="X479" s="3" t="n">
+        <v>0.002064952130655101</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -34091,6 +36971,12 @@
       <c r="V480" s="2" t="n">
         <v>-0.0007153075822604917</v>
       </c>
+      <c r="W480" s="1" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="X480" s="3" t="n">
+        <v>0.002505368647101052</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -34161,6 +37047,12 @@
       <c r="V481" s="2" t="n">
         <v>-0.0006590220113352888</v>
       </c>
+      <c r="W481" s="1" t="n">
+        <v>0.07586</v>
+      </c>
+      <c r="X481" s="3" t="n">
+        <v>0.0005275652862041462</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -34231,6 +37123,12 @@
       <c r="V482" s="3" t="n">
         <v>0.00471063257065953</v>
       </c>
+      <c r="W482" s="1" t="n">
+        <v>0.01494</v>
+      </c>
+      <c r="X482" s="3" t="n">
+        <v>0.0006697923643670189</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -34301,6 +37199,12 @@
       <c r="V483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W483" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="X483" s="2" t="n">
+        <v>-0.007968127490039931</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -34371,6 +37275,12 @@
       <c r="V484" s="3" t="n">
         <v>0.0009280742459396373</v>
       </c>
+      <c r="W484" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="X484" s="2" t="n">
+        <v>-0.001390820584144589</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -34441,6 +37351,12 @@
       <c r="V485" s="3" t="n">
         <v>0.001687153530971333</v>
       </c>
+      <c r="W485" s="1" t="n">
+        <v>0.008314999999999999</v>
+      </c>
+      <c r="X485" s="3" t="n">
+        <v>0.0003609239653512429</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -34511,6 +37427,12 @@
       <c r="V486" s="2" t="n">
         <v>-0.0006696129637069502</v>
       </c>
+      <c r="W486" s="1" t="n">
+        <v>0.007455</v>
+      </c>
+      <c r="X486" s="2" t="n">
+        <v>-0.0009380863039399707</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -34581,6 +37503,12 @@
       <c r="V487" s="2" t="n">
         <v>-0.005376344086021534</v>
       </c>
+      <c r="W487" s="1" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="X487" s="2" t="n">
+        <v>-0.001801801801801853</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -34651,6 +37579,12 @@
       <c r="V488" s="2" t="n">
         <v>-0.00138888888888898</v>
       </c>
+      <c r="W488" s="1" t="n">
+        <v>0.009164</v>
+      </c>
+      <c r="X488" s="2" t="n">
+        <v>-0.0195784743768053</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -34721,6 +37655,12 @@
       <c r="V489" s="2" t="n">
         <v>-0.0002600104004160962</v>
       </c>
+      <c r="W489" s="1" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="X489" s="3" t="n">
+        <v>0.005201560468140411</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -34791,6 +37731,12 @@
       <c r="V490" s="3" t="n">
         <v>0.00153767298821117</v>
       </c>
+      <c r="W490" s="1" t="n">
+        <v>0.05853</v>
+      </c>
+      <c r="X490" s="2" t="n">
+        <v>-0.001535312180143292</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -34861,6 +37807,12 @@
       <c r="V491" s="3" t="n">
         <v>0.001038421599169292</v>
       </c>
+      <c r="W491" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="X491" s="2" t="n">
+        <v>-0.001037344398340279</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -34931,6 +37883,12 @@
       <c r="V492" s="2" t="n">
         <v>-0.002255639097744446</v>
       </c>
+      <c r="W492" s="1" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="X492" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -35001,6 +37959,12 @@
       <c r="V493" s="3" t="n">
         <v>0.0002834467120182274</v>
       </c>
+      <c r="W493" s="1" t="n">
+        <v>0.03525</v>
+      </c>
+      <c r="X493" s="2" t="n">
+        <v>-0.001133465570983432</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -35071,6 +38035,12 @@
       <c r="V494" s="2" t="n">
         <v>-0.00526008182349502</v>
       </c>
+      <c r="W494" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="X494" s="2" t="n">
+        <v>-0.001175088131609823</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -35141,6 +38111,12 @@
       <c r="V495" s="3" t="n">
         <v>0.000846560846560812</v>
       </c>
+      <c r="W495" s="1" t="n">
+        <v>0.04715</v>
+      </c>
+      <c r="X495" s="2" t="n">
+        <v>-0.002960456756185266</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -35211,6 +38187,12 @@
       <c r="V496" s="2" t="n">
         <v>-0.0006231823847113055</v>
       </c>
+      <c r="W496" s="1" t="n">
+        <v>0.04827</v>
+      </c>
+      <c r="X496" s="3" t="n">
+        <v>0.003325711910205787</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -35281,6 +38263,12 @@
       <c r="V497" s="2" t="n">
         <v>-0.0006041079339509111</v>
       </c>
+      <c r="W497" s="1" t="n">
+        <v>0.04959</v>
+      </c>
+      <c r="X497" s="2" t="n">
+        <v>-0.0008059641345959776</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -35351,6 +38339,12 @@
       <c r="V498" s="2" t="n">
         <v>-0.002077562326869769</v>
       </c>
+      <c r="W498" s="1" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="X498" s="3" t="n">
+        <v>0.002428868841082506</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -35421,6 +38415,12 @@
       <c r="V499" s="3" t="n">
         <v>0.001100110011001182</v>
       </c>
+      <c r="W499" s="1" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="X499" s="3" t="n">
+        <v>0.0007326007326006518</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -35491,6 +38491,12 @@
       <c r="V500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="X500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -35561,6 +38567,12 @@
       <c r="V501" s="2" t="n">
         <v>-0.003636363636363586</v>
       </c>
+      <c r="W501" s="1" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="X501" s="3" t="n">
+        <v>0.003649635036496299</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -35631,6 +38643,12 @@
       <c r="V502" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W502" s="1" t="n">
+        <v>0.03193</v>
+      </c>
+      <c r="X502" s="3" t="n">
+        <v>0.001882648258550284</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -35701,6 +38719,12 @@
       <c r="V503" s="2" t="n">
         <v>-0.0001291822761916116</v>
       </c>
+      <c r="W503" s="1" t="n">
+        <v>0.007748</v>
+      </c>
+      <c r="X503" s="3" t="n">
+        <v>0.001033591731266063</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -35771,6 +38795,12 @@
       <c r="V504" s="2" t="n">
         <v>-0.000325309043591376</v>
       </c>
+      <c r="W504" s="1" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="X504" s="2" t="n">
+        <v>-0.001301659616010414</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -35841,6 +38871,12 @@
       <c r="V505" s="3" t="n">
         <v>0.001490716899308812</v>
       </c>
+      <c r="W505" s="1" t="n">
+        <v>0.0007419</v>
+      </c>
+      <c r="X505" s="3" t="n">
+        <v>0.003924221921515584</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -35911,6 +38947,12 @@
       <c r="V506" s="2" t="n">
         <v>-0.0006772773450729207</v>
       </c>
+      <c r="W506" s="1" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="X506" s="2" t="n">
+        <v>-0.005421890884445918</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -35981,6 +39023,12 @@
       <c r="V507" s="3" t="n">
         <v>0.003875968992248118</v>
       </c>
+      <c r="W507" s="1" t="n">
+        <v>0.002844</v>
+      </c>
+      <c r="X507" s="2" t="n">
+        <v>-0.001755001755001684</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -36051,6 +39099,12 @@
       <c r="V508" s="2" t="n">
         <v>-0.0007887679444708687</v>
       </c>
+      <c r="W508" s="1" t="n">
+        <v>0.06326</v>
+      </c>
+      <c r="X508" s="2" t="n">
+        <v>-0.001263024944742607</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -36121,6 +39175,12 @@
       <c r="V509" s="2" t="n">
         <v>-0.002223210315695817</v>
       </c>
+      <c r="W509" s="1" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="X509" s="2" t="n">
+        <v>-0.003565062388591803</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -36191,6 +39251,12 @@
       <c r="V510" s="2" t="n">
         <v>-0.002047222601337495</v>
       </c>
+      <c r="W510" s="1" t="n">
+        <v>0.0007292000000000001</v>
+      </c>
+      <c r="X510" s="2" t="n">
+        <v>-0.0027352297592997</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -36261,6 +39327,12 @@
       <c r="V511" s="3" t="n">
         <v>0.0003614022406938525</v>
       </c>
+      <c r="W511" s="1" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="X511" s="2" t="n">
+        <v>-0.001083815028901615</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -36331,6 +39403,12 @@
       <c r="V512" s="3" t="n">
         <v>0.003307151715584921</v>
       </c>
+      <c r="W512" s="1" t="n">
+        <v>0.0004842</v>
+      </c>
+      <c r="X512" s="2" t="n">
+        <v>-0.002472187886279306</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -36401,6 +39479,12 @@
       <c r="V513" s="3" t="n">
         <v>0.001439366678661455</v>
       </c>
+      <c r="W513" s="1" t="n">
+        <v>0.05559</v>
+      </c>
+      <c r="X513" s="2" t="n">
+        <v>-0.001257635644987435</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -36471,6 +39555,12 @@
       <c r="V514" s="2" t="n">
         <v>-0.0006594131223211073</v>
       </c>
+      <c r="W514" s="1" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="X514" s="3" t="n">
+        <v>0.002969317057076866</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -36541,6 +39631,12 @@
       <c r="V515" s="2" t="n">
         <v>-0.001751313485113878</v>
       </c>
+      <c r="W515" s="1" t="n">
+        <v>0.001138</v>
+      </c>
+      <c r="X515" s="2" t="n">
+        <v>-0.001754385964912323</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -36611,6 +39707,12 @@
       <c r="V516" s="3" t="n">
         <v>0.00196344962996526</v>
       </c>
+      <c r="W516" s="1" t="n">
+        <v>0.006604</v>
+      </c>
+      <c r="X516" s="2" t="n">
+        <v>-0.004522158577027512</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -36681,6 +39783,12 @@
       <c r="V517" s="3" t="n">
         <v>0.0002510670348983947</v>
       </c>
+      <c r="W517" s="1" t="n">
+        <v>0.03981</v>
+      </c>
+      <c r="X517" s="2" t="n">
+        <v>-0.0007530120481928275</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -36751,6 +39859,12 @@
       <c r="V518" s="2" t="n">
         <v>-0.0009708737864076602</v>
       </c>
+      <c r="W518" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="X518" s="3" t="n">
+        <v>0.001943634596695742</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -36821,6 +39935,12 @@
       <c r="V519" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W519" s="1" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="X519" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -36891,6 +40011,12 @@
       <c r="V520" s="3" t="n">
         <v>0.004388714733542358</v>
       </c>
+      <c r="W520" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="X520" s="2" t="n">
+        <v>-0.005617977528089961</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -36961,6 +40087,12 @@
       <c r="V521" s="3" t="n">
         <v>0.0005580357142858852</v>
       </c>
+      <c r="W521" s="1" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="X521" s="2" t="n">
+        <v>-0.001115448968209852</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -37031,6 +40163,12 @@
       <c r="V522" s="2" t="n">
         <v>-0.003048780487804965</v>
       </c>
+      <c r="W522" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="X522" s="2" t="n">
+        <v>-0.001834862385321026</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -37101,6 +40239,12 @@
       <c r="V523" s="2" t="n">
         <v>-0.001195886151638315</v>
       </c>
+      <c r="W523" s="1" t="n">
+        <v>0.004175</v>
+      </c>
+      <c r="X523" s="2" t="n">
+        <v>-0.0002394636015325988</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -37171,6 +40315,12 @@
       <c r="V524" s="3" t="n">
         <v>0.001409443269908451</v>
       </c>
+      <c r="W524" s="1" t="n">
+        <v>0.01426</v>
+      </c>
+      <c r="X524" s="3" t="n">
+        <v>0.003518648838845862</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -37241,6 +40391,12 @@
       <c r="V525" s="2" t="n">
         <v>-0.0008035355564483402</v>
       </c>
+      <c r="W525" s="1" t="n">
+        <v>0.02479</v>
+      </c>
+      <c r="X525" s="2" t="n">
+        <v>-0.003216726980297556</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -37311,6 +40467,12 @@
       <c r="V526" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W526" s="1" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="X526" s="2" t="n">
+        <v>-0.0008312551953449947</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -37381,6 +40543,12 @@
       <c r="V527" s="3" t="n">
         <v>0.0004162619675315977</v>
       </c>
+      <c r="W527" s="1" t="n">
+        <v>0.07217</v>
+      </c>
+      <c r="X527" s="3" t="n">
+        <v>0.0009708737864077756</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -37451,6 +40619,12 @@
       <c r="V528" s="2" t="n">
         <v>-0.0004617871161394409</v>
       </c>
+      <c r="W528" s="1" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="X528" s="2" t="n">
+        <v>-0.0009240009240010466</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -37521,6 +40695,12 @@
       <c r="V529" s="2" t="n">
         <v>-0.0001585539876327275</v>
       </c>
+      <c r="W529" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="X529" s="3" t="n">
+        <v>0.0006343165239454229</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -37591,6 +40771,12 @@
       <c r="V530" s="3" t="n">
         <v>0.001593943016537198</v>
       </c>
+      <c r="W530" s="1" t="n">
+        <v>0.005029</v>
+      </c>
+      <c r="X530" s="3" t="n">
+        <v>0.0003978516013525757</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -37661,6 +40847,12 @@
       <c r="V531" s="3" t="n">
         <v>0.0007733952049496441</v>
       </c>
+      <c r="W531" s="1" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="X531" s="2" t="n">
+        <v>-0.001545595054095657</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -37731,6 +40923,12 @@
       <c r="V532" s="2" t="n">
         <v>-0.0007503282686176197</v>
       </c>
+      <c r="W532" s="1" t="n">
+        <v>0.05317</v>
+      </c>
+      <c r="X532" s="2" t="n">
+        <v>-0.001877229209686426</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -37801,6 +40999,12 @@
       <c r="V533" s="2" t="n">
         <v>-0.004275788348476738</v>
       </c>
+      <c r="W533" s="1" t="n">
+        <v>0.003733</v>
+      </c>
+      <c r="X533" s="3" t="n">
+        <v>0.001878690284487403</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -37871,6 +41075,12 @@
       <c r="V534" s="2" t="n">
         <v>-0.0005827505827505186</v>
       </c>
+      <c r="W534" s="1" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="X534" s="3" t="n">
+        <v>0.0005830903790086821</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -37941,6 +41151,12 @@
       <c r="V535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="X535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -38011,6 +41227,12 @@
       <c r="V536" s="2" t="n">
         <v>-0.001577998196573528</v>
       </c>
+      <c r="W536" s="1" t="n">
+        <v>0.0004429</v>
+      </c>
+      <c r="X536" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -38081,6 +41303,12 @@
       <c r="V537" s="2" t="n">
         <v>-0.001033057851239627</v>
       </c>
+      <c r="W537" s="1" t="n">
+        <v>0.00963</v>
+      </c>
+      <c r="X537" s="2" t="n">
+        <v>-0.004136504653567746</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -38151,6 +41379,12 @@
       <c r="V538" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="W538" s="1" t="n">
+        <v>0.05456</v>
+      </c>
+      <c r="X538" s="2" t="n">
+        <v>-0.001281347245103434</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -38221,6 +41455,12 @@
       <c r="V539" s="2" t="n">
         <v>-0.0007327080890973856</v>
       </c>
+      <c r="W539" s="1" t="n">
+        <v>0.6804</v>
+      </c>
+      <c r="X539" s="2" t="n">
+        <v>-0.00219973603167612</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -38291,6 +41531,12 @@
       <c r="V540" s="2" t="n">
         <v>-0.001982815598149337</v>
       </c>
+      <c r="W540" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="X540" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -38361,6 +41607,12 @@
       <c r="V541" s="2" t="n">
         <v>-0.00229709035222056</v>
       </c>
+      <c r="W541" s="1" t="n">
+        <v>0.01303</v>
+      </c>
+      <c r="X541" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -38431,6 +41683,12 @@
       <c r="V542" s="3" t="n">
         <v>0.001434720229555303</v>
       </c>
+      <c r="W542" s="1" t="n">
+        <v>0.01398</v>
+      </c>
+      <c r="X542" s="3" t="n">
+        <v>0.001432664756446933</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -38500,6 +41758,12 @@
       </c>
       <c r="V543" s="2" t="n">
         <v>-0.002273522210563223</v>
+      </c>
+      <c r="W543" s="1" t="n">
+        <v>0.05704</v>
+      </c>
+      <c r="X543" s="2" t="n">
+        <v>-0.000175284837861457</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD543"/>
+  <dimension ref="A1:AF543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -456,6 +456,8 @@
     <col width="18" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -609,6 +611,16 @@
           <t>change_03:30</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>price_03:45</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>change_03:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -703,6 +715,12 @@
       <c r="AD2" s="3" t="n">
         <v>0.003779869120958632</v>
       </c>
+      <c r="AE2" s="1" t="n">
+        <v>70265.8</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>0.001496562182871347</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -797,6 +815,12 @@
       <c r="AD3" s="3" t="n">
         <v>0.005828683566920051</v>
       </c>
+      <c r="AE3" s="1" t="n">
+        <v>2067.2</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0.003285721912416332</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -891,6 +915,12 @@
       <c r="AD4" s="3" t="n">
         <v>0.006993822123790585</v>
       </c>
+      <c r="AE4" s="1" t="n">
+        <v>86.66</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>0.003125361731681861</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -985,6 +1015,12 @@
       <c r="AD5" s="3" t="n">
         <v>0.008472944348161109</v>
       </c>
+      <c r="AE5" s="1" t="n">
+        <v>0.010475</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>9.547450830621208e-05</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1079,6 +1115,12 @@
       <c r="AD6" s="3" t="n">
         <v>0.003790640034990592</v>
       </c>
+      <c r="AE6" s="1" t="n">
+        <v>1.3783</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>0.0009440813362382562</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1173,6 +1215,12 @@
       <c r="AD7" s="3" t="n">
         <v>0.003937426838352616</v>
       </c>
+      <c r="AE7" s="1" t="n">
+        <v>0.09433999999999999</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1267,6 +1315,12 @@
       <c r="AD8" s="3" t="n">
         <v>0.005264720969788608</v>
       </c>
+      <c r="AE8" s="1" t="n">
+        <v>37.185</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.001316001504001705</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1361,6 +1415,12 @@
       <c r="AD9" s="2" t="n">
         <v>-0.01479289940828404</v>
       </c>
+      <c r="AE9" s="1" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0.00300300300300295</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1455,6 +1515,12 @@
       <c r="AD10" s="3" t="n">
         <v>0.005939083528578336</v>
       </c>
+      <c r="AE10" s="1" t="n">
+        <v>18.567</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>0.005687357816054622</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1549,6 +1615,12 @@
       <c r="AD11" s="3" t="n">
         <v>0.004461115742027085</v>
       </c>
+      <c r="AE11" s="1" t="n">
+        <v>650.85</v>
+      </c>
+      <c r="AF11" s="3" t="n">
+        <v>0.0002151496058151655</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1643,6 +1715,12 @@
       <c r="AD12" s="2" t="n">
         <v>-0.002721705602177443</v>
       </c>
+      <c r="AE12" s="1" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="AF12" s="3" t="n">
+        <v>0.01159881737548327</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1737,6 +1815,12 @@
       <c r="AD13" s="3" t="n">
         <v>0.002399232245681382</v>
       </c>
+      <c r="AE13" s="1" t="n">
+        <v>209.1</v>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>0.0009573958831976478</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1831,6 +1915,12 @@
       <c r="AD14" s="3" t="n">
         <v>0.006893645203046503</v>
       </c>
+      <c r="AE14" s="1" t="n">
+        <v>0.0033433</v>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>-0.000448457306864446</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1925,6 +2015,12 @@
       <c r="AD15" s="3" t="n">
         <v>0.01393912935013089</v>
       </c>
+      <c r="AE15" s="1" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>-0.0001230201445486221</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2019,6 +2115,12 @@
       <c r="AD16" s="3" t="n">
         <v>0.008538216232897938</v>
       </c>
+      <c r="AE16" s="1" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>-0.00142798857609146</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2113,6 +2215,12 @@
       <c r="AD17" s="3" t="n">
         <v>0.007462686567164134</v>
       </c>
+      <c r="AE17" s="1" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>-0.01111111111111104</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2207,6 +2315,12 @@
       <c r="AD18" s="3" t="n">
         <v>0.01198824867323731</v>
       </c>
+      <c r="AE18" s="1" t="n">
+        <v>213.38</v>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>-0.0008896380577796401</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2301,6 +2415,12 @@
       <c r="AD19" s="3" t="n">
         <v>0.005751533742331294</v>
       </c>
+      <c r="AE19" s="1" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2395,6 +2515,12 @@
       <c r="AD20" s="2" t="n">
         <v>-0.006976198850979074</v>
       </c>
+      <c r="AE20" s="1" t="n">
+        <v>0.016935</v>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>-0.0002361414487278193</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2489,6 +2615,12 @@
       <c r="AD21" s="3" t="n">
         <v>0.00576036866359444</v>
       </c>
+      <c r="AE21" s="1" t="n">
+        <v>9.593</v>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>-0.001041341247526792</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2583,6 +2715,12 @@
       <c r="AD22" s="2" t="n">
         <v>-0.005350772889417267</v>
       </c>
+      <c r="AE22" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="AF22" s="3" t="n">
+        <v>0.005379557680812816</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2677,6 +2815,12 @@
       <c r="AD23" s="3" t="n">
         <v>0.005990450007234729</v>
       </c>
+      <c r="AE23" s="1" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>-0.002445198780277205</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2771,6 +2915,12 @@
       <c r="AD24" s="3" t="n">
         <v>0.008111239860950182</v>
       </c>
+      <c r="AE24" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2865,6 +3015,12 @@
       <c r="AD25" s="3" t="n">
         <v>0.005233853006681383</v>
       </c>
+      <c r="AE25" s="1" t="n">
+        <v>9.019</v>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>-0.0008862301982939093</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2959,6 +3115,12 @@
       <c r="AD26" s="3" t="n">
         <v>0.006736526946107707</v>
       </c>
+      <c r="AE26" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="AF26" s="3" t="n">
+        <v>0.0007434944237919048</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3053,6 +3215,12 @@
       <c r="AD27" s="3" t="n">
         <v>0.001614823371326916</v>
       </c>
+      <c r="AE27" s="1" t="n">
+        <v>5096.74</v>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>-0.0003569635348021046</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3147,6 +3315,12 @@
       <c r="AD28" s="3" t="n">
         <v>0.01119194180190264</v>
       </c>
+      <c r="AE28" s="1" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="AF28" s="3" t="n">
+        <v>0.001936912008854395</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3241,6 +3415,12 @@
       <c r="AD29" s="3" t="n">
         <v>0.002669717772692646</v>
       </c>
+      <c r="AE29" s="1" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="AF29" s="3" t="n">
+        <v>0.001901863826549979</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3335,6 +3515,12 @@
       <c r="AD30" s="3" t="n">
         <v>0.001764315410683832</v>
       </c>
+      <c r="AE30" s="1" t="n">
+        <v>0.5752699999999999</v>
+      </c>
+      <c r="AF30" s="3" t="n">
+        <v>0.003138786684569224</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3429,6 +3615,12 @@
       <c r="AD31" s="3" t="n">
         <v>0.0126152353226589</v>
       </c>
+      <c r="AE31" s="1" t="n">
+        <v>0.002095</v>
+      </c>
+      <c r="AF31" s="3" t="n">
+        <v>0.003833253473886054</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3523,6 +3715,12 @@
       <c r="AD32" s="3" t="n">
         <v>0.01586445899114359</v>
       </c>
+      <c r="AE32" s="1" t="n">
+        <v>1.3151</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>-0.003032370555681907</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3617,6 +3815,12 @@
       <c r="AD33" s="2" t="n">
         <v>-0.0008992805755396357</v>
       </c>
+      <c r="AE33" s="1" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AF33" s="2" t="n">
+        <v>-0.008700870087008575</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3711,6 +3915,12 @@
       <c r="AD34" s="3" t="n">
         <v>0.006666666666666672</v>
       </c>
+      <c r="AE34" s="1" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="AF34" s="2" t="n">
+        <v>-0.001324503311258279</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3805,6 +4015,12 @@
       <c r="AD35" s="3" t="n">
         <v>0.002505109104093846</v>
       </c>
+      <c r="AE35" s="1" t="n">
+        <v>456.11</v>
+      </c>
+      <c r="AF35" s="2" t="n">
+        <v>-0.0002191972994891955</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3899,6 +4115,12 @@
       <c r="AD36" s="3" t="n">
         <v>0.001672940192388054</v>
       </c>
+      <c r="AE36" s="1" t="n">
+        <v>0.04784</v>
+      </c>
+      <c r="AF36" s="2" t="n">
+        <v>-0.001252609603340241</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3993,6 +4215,12 @@
       <c r="AD37" s="3" t="n">
         <v>0.001284063347125142</v>
       </c>
+      <c r="AE37" s="1" t="n">
+        <v>0.7028</v>
+      </c>
+      <c r="AF37" s="3" t="n">
+        <v>0.001424907381020235</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4087,6 +4315,12 @@
       <c r="AD38" s="3" t="n">
         <v>0.01142857142857149</v>
       </c>
+      <c r="AE38" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>-0.001883239171374819</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4181,6 +4415,12 @@
       <c r="AD39" s="3" t="n">
         <v>0.01202404809619232</v>
       </c>
+      <c r="AE39" s="1" t="n">
+        <v>111.38</v>
+      </c>
+      <c r="AF39" s="3" t="n">
+        <v>0.002520252025202531</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4275,6 +4515,12 @@
       <c r="AD40" s="3" t="n">
         <v>0.006555585905490415</v>
       </c>
+      <c r="AE40" s="1" t="n">
+        <v>0.03663</v>
+      </c>
+      <c r="AF40" s="2" t="n">
+        <v>-0.005970149253731288</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4369,6 +4615,12 @@
       <c r="AD41" s="2" t="n">
         <v>-0.0007278020378458025</v>
       </c>
+      <c r="AE41" s="1" t="n">
+        <v>0.05484</v>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>-0.001456664238892876</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4463,6 +4715,12 @@
       <c r="AD42" s="3" t="n">
         <v>0.002585888437384569</v>
       </c>
+      <c r="AE42" s="1" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="AF42" s="3" t="n">
+        <v>0.000184229918938799</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4557,6 +4815,12 @@
       <c r="AD43" s="3" t="n">
         <v>0.01207547169811313</v>
       </c>
+      <c r="AE43" s="1" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="AF43" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4651,6 +4915,12 @@
       <c r="AD44" s="3" t="n">
         <v>0.0075085324232083</v>
       </c>
+      <c r="AE44" s="1" t="n">
+        <v>0.005926</v>
+      </c>
+      <c r="AF44" s="3" t="n">
+        <v>0.003726287262872535</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4745,6 +5015,12 @@
       <c r="AD45" s="2" t="n">
         <v>-0.0005030181086519956</v>
       </c>
+      <c r="AE45" s="1" t="n">
+        <v>0.09962</v>
+      </c>
+      <c r="AF45" s="3" t="n">
+        <v>0.002717664821338766</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4839,6 +5115,12 @@
       <c r="AD46" s="3" t="n">
         <v>0.09916454776607325</v>
       </c>
+      <c r="AE46" s="1" t="n">
+        <v>3.077</v>
+      </c>
+      <c r="AF46" s="3" t="n">
+        <v>0.01685393258426971</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4933,6 +5215,12 @@
       <c r="AD47" s="3" t="n">
         <v>0.0004158004158002545</v>
       </c>
+      <c r="AE47" s="1" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="AF47" s="2" t="n">
+        <v>-3.463563313921616e-05</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5027,6 +5315,12 @@
       <c r="AD48" s="3" t="n">
         <v>0.006572769953051701</v>
       </c>
+      <c r="AE48" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="AF48" s="2" t="n">
+        <v>-0.001865671641791098</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5121,6 +5415,12 @@
       <c r="AD49" s="2" t="n">
         <v>-0.001144632491210868</v>
       </c>
+      <c r="AE49" s="1" t="n">
+        <v>0.24531</v>
+      </c>
+      <c r="AF49" s="3" t="n">
+        <v>0.00396987803879839</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5215,6 +5515,12 @@
       <c r="AD50" s="3" t="n">
         <v>0.0002098195551824617</v>
       </c>
+      <c r="AE50" s="1" t="n">
+        <v>0.04814</v>
+      </c>
+      <c r="AF50" s="3" t="n">
+        <v>0.009859450388084858</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5309,6 +5615,12 @@
       <c r="AD51" s="3" t="n">
         <v>0.005659891947517313</v>
       </c>
+      <c r="AE51" s="1" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="AF51" s="2" t="n">
+        <v>-0.001023279611153749</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5403,6 +5715,12 @@
       <c r="AD52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE52" s="1" t="n">
+        <v>0.000227</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>-0.008733624454148565</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5497,6 +5815,12 @@
       <c r="AD53" s="3" t="n">
         <v>0.01134328358208946</v>
       </c>
+      <c r="AE53" s="1" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5591,6 +5915,12 @@
       <c r="AD54" s="3" t="n">
         <v>0.0002379252914585549</v>
       </c>
+      <c r="AE54" s="1" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="AF54" s="3" t="n">
+        <v>0.003805899143672702</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5685,6 +6015,12 @@
       <c r="AD55" s="2" t="n">
         <v>-0.007235184131371336</v>
       </c>
+      <c r="AE55" s="1" t="n">
+        <v>0.12273</v>
+      </c>
+      <c r="AF55" s="3" t="n">
+        <v>0.004995086799868977</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5779,6 +6115,12 @@
       <c r="AD56" s="3" t="n">
         <v>0.005089058524172997</v>
       </c>
+      <c r="AE56" s="1" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AF56" s="2" t="n">
+        <v>-0.001898734177215156</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5873,6 +6215,12 @@
       <c r="AD57" s="3" t="n">
         <v>0.001737619461338047</v>
       </c>
+      <c r="AE57" s="1" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="AF57" s="3" t="n">
+        <v>0.0008673026886382994</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5967,6 +6315,12 @@
       <c r="AD58" s="3" t="n">
         <v>0.009063444108761309</v>
       </c>
+      <c r="AE58" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="AF58" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6061,6 +6415,12 @@
       <c r="AD59" s="3" t="n">
         <v>0.009063444108761353</v>
       </c>
+      <c r="AE59" s="1" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="AF59" s="2" t="n">
+        <v>-0.002994011976047912</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6155,6 +6515,12 @@
       <c r="AD60" s="3" t="n">
         <v>0.01297016861219197</v>
       </c>
+      <c r="AE60" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="AF60" s="2" t="n">
+        <v>-0.001280409731113993</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6249,6 +6615,12 @@
       <c r="AD61" s="3" t="n">
         <v>0.005536332179930744</v>
       </c>
+      <c r="AE61" s="1" t="n">
+        <v>0.15975</v>
+      </c>
+      <c r="AF61" s="2" t="n">
+        <v>-0.000500531815053474</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6343,6 +6715,12 @@
       <c r="AD62" s="3" t="n">
         <v>0.007789264976632291</v>
       </c>
+      <c r="AE62" s="1" t="n">
+        <v>0.7131</v>
+      </c>
+      <c r="AF62" s="3" t="n">
+        <v>0.002107925801011728</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6437,6 +6815,12 @@
       <c r="AD63" s="3" t="n">
         <v>0.02987846049966232</v>
       </c>
+      <c r="AE63" s="1" t="n">
+        <v>6.053</v>
+      </c>
+      <c r="AF63" s="2" t="n">
+        <v>-0.007867562694640231</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6531,6 +6915,12 @@
       <c r="AD64" s="3" t="n">
         <v>0.01063532045899812</v>
       </c>
+      <c r="AE64" s="1" t="n">
+        <v>0.007209</v>
+      </c>
+      <c r="AF64" s="2" t="n">
+        <v>-0.001800055386319578</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6625,6 +7015,12 @@
       <c r="AD65" s="2" t="n">
         <v>-0.006205398696866236</v>
       </c>
+      <c r="AE65" s="1" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="AF65" s="3" t="n">
+        <v>0.005307524196066079</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6719,6 +7115,12 @@
       <c r="AD66" s="3" t="n">
         <v>0.008583690987124351</v>
       </c>
+      <c r="AE66" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AF66" s="2" t="n">
+        <v>-0.004255319148936056</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6813,6 +7215,12 @@
       <c r="AD67" s="3" t="n">
         <v>0.00557275541795673</v>
       </c>
+      <c r="AE67" s="1" t="n">
+        <v>1.618</v>
+      </c>
+      <c r="AF67" s="2" t="n">
+        <v>-0.00369458128078818</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6907,6 +7315,12 @@
       <c r="AD68" s="3" t="n">
         <v>0.00693824957874925</v>
       </c>
+      <c r="AE68" s="1" t="n">
+        <v>2.0353</v>
+      </c>
+      <c r="AF68" s="3" t="n">
+        <v>0.001722610493158695</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7001,6 +7415,12 @@
       <c r="AD69" s="3" t="n">
         <v>0.004292582417582326</v>
       </c>
+      <c r="AE69" s="1" t="n">
+        <v>0.5866</v>
+      </c>
+      <c r="AF69" s="3" t="n">
+        <v>0.002906479740126577</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7095,6 +7515,12 @@
       <c r="AD70" s="3" t="n">
         <v>0.00980392156862746</v>
       </c>
+      <c r="AE70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AF70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7189,6 +7615,12 @@
       <c r="AD71" s="3" t="n">
         <v>0.005724980733237898</v>
       </c>
+      <c r="AE71" s="1" t="n">
+        <v>0.9118000000000001</v>
+      </c>
+      <c r="AF71" s="2" t="n">
+        <v>-0.001860974274767295</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7283,6 +7715,12 @@
       <c r="AD72" s="2" t="n">
         <v>-0.004488542404913803</v>
       </c>
+      <c r="AE72" s="1" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="AF72" s="3" t="n">
+        <v>0.002135738016136716</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7377,6 +7815,12 @@
       <c r="AD73" s="3" t="n">
         <v>0.005970785798059547</v>
       </c>
+      <c r="AE73" s="1" t="n">
+        <v>0.09424</v>
+      </c>
+      <c r="AF73" s="2" t="n">
+        <v>-0.001165871754107037</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7471,6 +7915,12 @@
       <c r="AD74" s="3" t="n">
         <v>0.00113626431256016</v>
       </c>
+      <c r="AE74" s="1" t="n">
+        <v>1.1473</v>
+      </c>
+      <c r="AF74" s="3" t="n">
+        <v>0.001658809149642058</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7565,6 +8015,12 @@
       <c r="AD75" s="3" t="n">
         <v>0.005653266331658279</v>
       </c>
+      <c r="AE75" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="AF75" s="3" t="n">
+        <v>0.000624609618988107</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7659,6 +8115,12 @@
       <c r="AD76" s="2" t="n">
         <v>-0.008322454308094052</v>
       </c>
+      <c r="AE76" s="1" t="n">
+        <v>0.12239</v>
+      </c>
+      <c r="AF76" s="3" t="n">
+        <v>0.006993582359716995</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7753,6 +8215,12 @@
       <c r="AD77" s="3" t="n">
         <v>0.009353741496598672</v>
       </c>
+      <c r="AE77" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="AF77" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7847,6 +8315,12 @@
       <c r="AD78" s="3" t="n">
         <v>0.01190476190476183</v>
       </c>
+      <c r="AE78" s="1" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="AF78" s="3" t="n">
+        <v>0.001960784313725547</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7941,6 +8415,12 @@
       <c r="AD79" s="3" t="n">
         <v>0.007141670818800802</v>
       </c>
+      <c r="AE79" s="1" t="n">
+        <v>0.006058</v>
+      </c>
+      <c r="AF79" s="2" t="n">
+        <v>-0.0009894459102902258</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8035,6 +8515,12 @@
       <c r="AD80" s="2" t="n">
         <v>-0.005797832114948437</v>
       </c>
+      <c r="AE80" s="1" t="n">
+        <v>0.007859</v>
+      </c>
+      <c r="AF80" s="2" t="n">
+        <v>-0.003676470588235232</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8129,6 +8615,12 @@
       <c r="AD81" s="3" t="n">
         <v>0.002232142857142809</v>
       </c>
+      <c r="AE81" s="1" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="AF81" s="3" t="n">
+        <v>0.0005567928730511141</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8223,6 +8715,12 @@
       <c r="AD82" s="3" t="n">
         <v>0.006769230769230707</v>
       </c>
+      <c r="AE82" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="AF82" s="3" t="n">
+        <v>0.0006112469437653835</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8317,6 +8815,12 @@
       <c r="AD83" s="3" t="n">
         <v>0.005858659831563535</v>
       </c>
+      <c r="AE83" s="1" t="n">
+        <v>8.247</v>
+      </c>
+      <c r="AF83" s="3" t="n">
+        <v>0.0007280669821623866</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8411,6 +8915,12 @@
       <c r="AD84" s="3" t="n">
         <v>0.003946352483628343</v>
       </c>
+      <c r="AE84" s="1" t="n">
+        <v>350.19</v>
+      </c>
+      <c r="AF84" s="2" t="n">
+        <v>-0.002506622610875311</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8505,6 +9015,12 @@
       <c r="AD85" s="3" t="n">
         <v>0.005160973212091469</v>
       </c>
+      <c r="AE85" s="1" t="n">
+        <v>0.004101</v>
+      </c>
+      <c r="AF85" s="3" t="n">
+        <v>0.00268948655256717</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8599,6 +9115,12 @@
       <c r="AD86" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE86" s="1" t="n">
+        <v>0.13002</v>
+      </c>
+      <c r="AF86" s="2" t="n">
+        <v>-0.008540491078237074</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8693,6 +9215,12 @@
       <c r="AD87" s="2" t="n">
         <v>-0.02064095600217265</v>
       </c>
+      <c r="AE87" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AF87" s="2" t="n">
+        <v>-0.001663893510815432</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8787,6 +9315,12 @@
       <c r="AD88" s="3" t="n">
         <v>0.005314437555358729</v>
       </c>
+      <c r="AE88" s="1" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AF88" s="2" t="n">
+        <v>-0.0008810572687225656</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8881,6 +9415,12 @@
       <c r="AD89" s="3" t="n">
         <v>0.003747870528108995</v>
       </c>
+      <c r="AE89" s="1" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="AF89" s="3" t="n">
+        <v>0.00101832993890028</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8975,6 +9515,12 @@
       <c r="AD90" s="3" t="n">
         <v>0.008952899961074226</v>
       </c>
+      <c r="AE90" s="1" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="AF90" s="2" t="n">
+        <v>-0.003086419753086294</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9069,6 +9615,12 @@
       <c r="AD91" s="2" t="n">
         <v>-0.01717659688674186</v>
       </c>
+      <c r="AE91" s="1" t="n">
+        <v>0.05513</v>
+      </c>
+      <c r="AF91" s="3" t="n">
+        <v>0.003640997633351516</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9163,6 +9715,12 @@
       <c r="AD92" s="2" t="n">
         <v>-7.613826709303258e-05</v>
       </c>
+      <c r="AE92" s="1" t="n">
+        <v>1.3154</v>
+      </c>
+      <c r="AF92" s="3" t="n">
+        <v>0.001599025355973495</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9257,6 +9815,12 @@
       <c r="AD93" s="3" t="n">
         <v>0.008229150181990925</v>
       </c>
+      <c r="AE93" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="AF93" s="3" t="n">
+        <v>0.001412651075184317</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9351,6 +9915,12 @@
       <c r="AD94" s="3" t="n">
         <v>0.001131221719456967</v>
       </c>
+      <c r="AE94" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="AF94" s="2" t="n">
+        <v>-0.002259887005649821</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9445,6 +10015,12 @@
       <c r="AD95" s="3" t="n">
         <v>0.01078813305364097</v>
       </c>
+      <c r="AE95" s="1" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AF95" s="2" t="n">
+        <v>-0.0008894159501926089</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9539,6 +10115,12 @@
       <c r="AD96" s="3" t="n">
         <v>0.002669039145907519</v>
       </c>
+      <c r="AE96" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="AF96" s="3" t="n">
+        <v>0.002661934338952864</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9633,6 +10215,12 @@
       <c r="AD97" s="3" t="n">
         <v>0.004912496162112269</v>
       </c>
+      <c r="AE97" s="1" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="AF97" s="2" t="n">
+        <v>-0.0003055300947142686</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9727,6 +10315,12 @@
       <c r="AD98" s="3" t="n">
         <v>0.00718778077268644</v>
       </c>
+      <c r="AE98" s="1" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="AF98" s="3" t="n">
+        <v>0.002676181980374767</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9821,6 +10415,12 @@
       <c r="AD99" s="3" t="n">
         <v>0.004965243296921591</v>
       </c>
+      <c r="AE99" s="1" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AF99" s="2" t="n">
+        <v>-0.001976284584980312</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9915,6 +10515,12 @@
       <c r="AD100" s="3" t="n">
         <v>0.006721215663354794</v>
       </c>
+      <c r="AE100" s="1" t="n">
+        <v>0.03432</v>
+      </c>
+      <c r="AF100" s="2" t="n">
+        <v>-0.003773584905660324</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10009,6 +10615,12 @@
       <c r="AD101" s="3" t="n">
         <v>0.002738225629791836</v>
       </c>
+      <c r="AE101" s="1" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="AF101" s="3" t="n">
+        <v>0.0005461496450027919</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10103,6 +10715,12 @@
       <c r="AD102" s="2" t="n">
         <v>-0.0008640552995391604</v>
       </c>
+      <c r="AE102" s="1" t="n">
+        <v>0.006936</v>
+      </c>
+      <c r="AF102" s="2" t="n">
+        <v>-0.0002882675122512826</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10197,6 +10815,12 @@
       <c r="AD103" s="3" t="n">
         <v>0.003189066059225329</v>
       </c>
+      <c r="AE103" s="1" t="n">
+        <v>0.06596</v>
+      </c>
+      <c r="AF103" s="2" t="n">
+        <v>-0.001513775355737042</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10291,6 +10915,12 @@
       <c r="AD104" s="3" t="n">
         <v>0.00121832358674464</v>
       </c>
+      <c r="AE104" s="1" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="AF104" s="3" t="n">
+        <v>0.005354100754441556</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10385,6 +11015,12 @@
       <c r="AD105" s="3" t="n">
         <v>0.01277777777777773</v>
       </c>
+      <c r="AE105" s="1" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="AF105" s="2" t="n">
+        <v>-0.001097092704333517</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10479,6 +11115,12 @@
       <c r="AD106" s="3" t="n">
         <v>0.006894853484363304</v>
       </c>
+      <c r="AE106" s="1" t="n">
+        <v>0.008248999999999999</v>
+      </c>
+      <c r="AF106" s="3" t="n">
+        <v>0.008681829298116886</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10573,6 +11215,12 @@
       <c r="AD107" s="3" t="n">
         <v>0.01488423373759644</v>
       </c>
+      <c r="AE107" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="AF107" s="2" t="n">
+        <v>-0.00271591526344367</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10667,6 +11315,12 @@
       <c r="AD108" s="3" t="n">
         <v>0.004182156133828987</v>
       </c>
+      <c r="AE108" s="1" t="n">
+        <v>0.02169</v>
+      </c>
+      <c r="AF108" s="3" t="n">
+        <v>0.003701989819528006</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10761,6 +11415,12 @@
       <c r="AD109" s="2" t="n">
         <v>-0.0003602954422626407</v>
       </c>
+      <c r="AE109" s="1" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="AF109" s="3" t="n">
+        <v>0.00288340241484953</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10855,6 +11515,12 @@
       <c r="AD110" s="2" t="n">
         <v>-0.001387203051846658</v>
       </c>
+      <c r="AE110" s="1" t="n">
+        <v>0.11531</v>
+      </c>
+      <c r="AF110" s="3" t="n">
+        <v>0.001128668171557486</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10949,6 +11615,12 @@
       <c r="AD111" s="3" t="n">
         <v>0.001437962202136414</v>
       </c>
+      <c r="AE111" s="1" t="n">
+        <v>0.09782</v>
+      </c>
+      <c r="AF111" s="3" t="n">
+        <v>0.003282051282051291</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11043,6 +11715,12 @@
       <c r="AD112" s="3" t="n">
         <v>0.00268096514745316</v>
       </c>
+      <c r="AE112" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="AF112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11137,6 +11815,12 @@
       <c r="AD113" s="3" t="n">
         <v>0.007984440577336502</v>
       </c>
+      <c r="AE113" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="AF113" s="3" t="n">
+        <v>0.002335736772621043</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11231,6 +11915,12 @@
       <c r="AD114" s="3" t="n">
         <v>0.006310958118187</v>
       </c>
+      <c r="AE114" s="1" t="n">
+        <v>0.001764</v>
+      </c>
+      <c r="AF114" s="3" t="n">
+        <v>0.005701254275940722</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11325,6 +12015,12 @@
       <c r="AD115" s="3" t="n">
         <v>0.01047916166706672</v>
       </c>
+      <c r="AE115" s="1" t="n">
+        <v>1.2628</v>
+      </c>
+      <c r="AF115" s="2" t="n">
+        <v>-0.0003166561114630921</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11419,6 +12115,12 @@
       <c r="AD116" s="3" t="n">
         <v>0.001695633743111536</v>
       </c>
+      <c r="AE116" s="1" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="AF116" s="3" t="n">
+        <v>0.01015658061785859</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11513,6 +12215,12 @@
       <c r="AD117" s="2" t="n">
         <v>-0.003593596863769977</v>
       </c>
+      <c r="AE117" s="1" t="n">
+        <v>0.06084</v>
+      </c>
+      <c r="AF117" s="2" t="n">
+        <v>-0.002622950819672138</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11607,6 +12315,12 @@
       <c r="AD118" s="2" t="n">
         <v>-0.004101161995898829</v>
       </c>
+      <c r="AE118" s="1" t="n">
+        <v>0.04364</v>
+      </c>
+      <c r="AF118" s="2" t="n">
+        <v>-0.001601464195836207</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11701,6 +12415,12 @@
       <c r="AD119" s="3" t="n">
         <v>0.003256445047489903</v>
       </c>
+      <c r="AE119" s="1" t="n">
+        <v>0.003707</v>
+      </c>
+      <c r="AF119" s="3" t="n">
+        <v>0.002704895861509222</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11795,6 +12515,12 @@
       <c r="AD120" s="3" t="n">
         <v>0.00253807106598985</v>
       </c>
+      <c r="AE120" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AF120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11889,6 +12615,12 @@
       <c r="AD121" s="3" t="n">
         <v>0.008417508417508426</v>
       </c>
+      <c r="AE121" s="1" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AF121" s="2" t="n">
+        <v>-0.0003338898163605642</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11983,6 +12715,12 @@
       <c r="AD122" s="3" t="n">
         <v>0.008986784140969151</v>
       </c>
+      <c r="AE122" s="1" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="AF122" s="2" t="n">
+        <v>-0.00139713587146354</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12077,6 +12815,12 @@
       <c r="AD123" s="2" t="n">
         <v>-0.001846303908590451</v>
       </c>
+      <c r="AE123" s="1" t="n">
+        <v>0.028442</v>
+      </c>
+      <c r="AF123" s="2" t="n">
+        <v>-0.007363975848951343</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12171,6 +12915,12 @@
       <c r="AD124" s="3" t="n">
         <v>0.0006341958396753979</v>
       </c>
+      <c r="AE124" s="1" t="n">
+        <v>0.07881000000000001</v>
+      </c>
+      <c r="AF124" s="2" t="n">
+        <v>-0.001014070224362996</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12265,6 +13015,12 @@
       <c r="AD125" s="3" t="n">
         <v>0.02366921070427972</v>
       </c>
+      <c r="AE125" s="1" t="n">
+        <v>0.10564</v>
+      </c>
+      <c r="AF125" s="2" t="n">
+        <v>-0.003020007550018883</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12359,6 +13115,12 @@
       <c r="AD126" s="3" t="n">
         <v>0.005287009063444155</v>
       </c>
+      <c r="AE126" s="1" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="AF126" s="3" t="n">
+        <v>0.003005259203606319</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12453,6 +13215,12 @@
       <c r="AD127" s="3" t="n">
         <v>0.0009128251939754749</v>
       </c>
+      <c r="AE127" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="AF127" s="2" t="n">
+        <v>-0.001367989056087654</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12547,6 +13315,12 @@
       <c r="AD128" s="3" t="n">
         <v>0.008674101610904662</v>
       </c>
+      <c r="AE128" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="AF128" s="3" t="n">
+        <v>0.001228501228501264</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12641,6 +13415,12 @@
       <c r="AD129" s="2" t="n">
         <v>-0.01082206035379817</v>
       </c>
+      <c r="AE129" s="1" t="n">
+        <v>0.14312</v>
+      </c>
+      <c r="AF129" s="3" t="n">
+        <v>0.003716950697804914</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12735,6 +13515,12 @@
       <c r="AD130" s="2" t="n">
         <v>-0.003899152029073248</v>
       </c>
+      <c r="AE130" s="1" t="n">
+        <v>0.05237</v>
+      </c>
+      <c r="AF130" s="2" t="n">
+        <v>-0.004864515638657684</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12829,6 +13615,12 @@
       <c r="AD131" s="3" t="n">
         <v>0.008950465914664155</v>
       </c>
+      <c r="AE131" s="1" t="n">
+        <v>0.08221000000000001</v>
+      </c>
+      <c r="AF131" s="2" t="n">
+        <v>-0.0009721715882852927</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12923,6 +13715,12 @@
       <c r="AD132" s="3" t="n">
         <v>0.004561003420752538</v>
       </c>
+      <c r="AE132" s="1" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="AF132" s="2" t="n">
+        <v>-0.002270147559591281</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13017,6 +13815,12 @@
       <c r="AD133" s="3" t="n">
         <v>0.003618817852834725</v>
       </c>
+      <c r="AE133" s="1" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="AF133" s="3" t="n">
+        <v>0.002747252747252635</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13111,6 +13915,12 @@
       <c r="AD134" s="3" t="n">
         <v>0.00537092984222895</v>
       </c>
+      <c r="AE134" s="1" t="n">
+        <v>0.02978</v>
+      </c>
+      <c r="AF134" s="2" t="n">
+        <v>-0.005676126878130217</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13205,6 +14015,12 @@
       <c r="AD135" s="3" t="n">
         <v>0.001138952164009065</v>
       </c>
+      <c r="AE135" s="1" t="n">
+        <v>0.01754</v>
+      </c>
+      <c r="AF135" s="2" t="n">
+        <v>-0.002275312855517541</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13299,6 +14115,12 @@
       <c r="AD136" s="3" t="n">
         <v>0.005402485143166011</v>
       </c>
+      <c r="AE136" s="1" t="n">
+        <v>0.03725</v>
+      </c>
+      <c r="AF136" s="3" t="n">
+        <v>0.0008060182697473215</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13393,6 +14215,12 @@
       <c r="AD137" s="3" t="n">
         <v>0.007393715341959289</v>
       </c>
+      <c r="AE137" s="1" t="n">
+        <v>0.02715</v>
+      </c>
+      <c r="AF137" s="2" t="n">
+        <v>-0.003669724770642179</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13487,6 +14315,12 @@
       <c r="AD138" s="3" t="n">
         <v>0.009823182711198393</v>
       </c>
+      <c r="AE138" s="1" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="AF138" s="2" t="n">
+        <v>-0.001945525291828752</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13581,6 +14415,12 @@
       <c r="AD139" s="2" t="n">
         <v>-0.005008347245408956</v>
       </c>
+      <c r="AE139" s="1" t="n">
+        <v>0.01189</v>
+      </c>
+      <c r="AF139" s="2" t="n">
+        <v>-0.002516778523489976</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13675,6 +14515,12 @@
       <c r="AD140" s="2" t="n">
         <v>-0.002691790040376858</v>
       </c>
+      <c r="AE140" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="AF140" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13769,6 +14615,12 @@
       <c r="AD141" s="3" t="n">
         <v>0.009308098045299544</v>
       </c>
+      <c r="AE141" s="1" t="n">
+        <v>16.263</v>
+      </c>
+      <c r="AF141" s="2" t="n">
+        <v>-0.0001229634183829629</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13863,6 +14715,12 @@
       <c r="AD142" s="3" t="n">
         <v>0.0007942811755361074</v>
       </c>
+      <c r="AE142" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="AF142" s="2" t="n">
+        <v>-0.0007936507936507613</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13957,6 +14815,12 @@
       <c r="AD143" s="3" t="n">
         <v>0.0133283968900407</v>
       </c>
+      <c r="AE143" s="1" t="n">
+        <v>0.02729</v>
+      </c>
+      <c r="AF143" s="2" t="n">
+        <v>-0.002922908293752291</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14051,6 +14915,12 @@
       <c r="AD144" s="3" t="n">
         <v>0.005491024287222805</v>
       </c>
+      <c r="AE144" s="1" t="n">
+        <v>0.004758</v>
+      </c>
+      <c r="AF144" s="2" t="n">
+        <v>-0.0006301197227472235</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14145,6 +15015,12 @@
       <c r="AD145" s="3" t="n">
         <v>0.004645464291183769</v>
       </c>
+      <c r="AE145" s="1" t="n">
+        <v>1.9679</v>
+      </c>
+      <c r="AF145" s="2" t="n">
+        <v>-5.08130081300757e-05</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14239,6 +15115,12 @@
       <c r="AD146" s="3" t="n">
         <v>0.006468305304010385</v>
       </c>
+      <c r="AE146" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="AF146" s="3" t="n">
+        <v>0.002999143101970892</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14333,6 +15215,12 @@
       <c r="AD147" s="2" t="n">
         <v>-0.005662262684578623</v>
       </c>
+      <c r="AE147" s="1" t="n">
+        <v>0.08993</v>
+      </c>
+      <c r="AF147" s="3" t="n">
+        <v>0.004131308619919555</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14427,6 +15315,12 @@
       <c r="AD148" s="3" t="n">
         <v>0.003059088713572737</v>
       </c>
+      <c r="AE148" s="1" t="n">
+        <v>0.06245</v>
+      </c>
+      <c r="AF148" s="3" t="n">
+        <v>0.002407704654895624</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14521,6 +15415,12 @@
       <c r="AD149" s="3" t="n">
         <v>0.002529084471421301</v>
       </c>
+      <c r="AE149" s="1" t="n">
+        <v>0.05932</v>
+      </c>
+      <c r="AF149" s="2" t="n">
+        <v>-0.002354524049781386</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14615,6 +15515,12 @@
       <c r="AD150" s="3" t="n">
         <v>0.002246640251623687</v>
       </c>
+      <c r="AE150" s="1" t="n">
+        <v>0.24437</v>
+      </c>
+      <c r="AF150" s="2" t="n">
+        <v>-0.004034887512226895</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14709,6 +15615,12 @@
       <c r="AD151" s="3" t="n">
         <v>0.004557755305512185</v>
       </c>
+      <c r="AE151" s="1" t="n">
+        <v>7.016000000000001e-05</v>
+      </c>
+      <c r="AF151" s="2" t="n">
+        <v>-0.005245994612221723</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14803,6 +15715,12 @@
       <c r="AD152" s="2" t="n">
         <v>-0.002022017524151903</v>
       </c>
+      <c r="AE152" s="1" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="AF152" s="3" t="n">
+        <v>0.00585321927059881</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14897,6 +15815,12 @@
       <c r="AD153" s="3" t="n">
         <v>0.002923976608186993</v>
       </c>
+      <c r="AE153" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AF153" s="3" t="n">
+        <v>0.004211208292841022</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14991,6 +15915,12 @@
       <c r="AD154" s="3" t="n">
         <v>0.0005486968449932331</v>
       </c>
+      <c r="AE154" s="1" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AF154" s="3" t="n">
+        <v>0.0008225939128049546</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15085,6 +16015,12 @@
       <c r="AD155" s="3" t="n">
         <v>0.001737619461338017</v>
       </c>
+      <c r="AE155" s="1" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="AF155" s="2" t="n">
+        <v>-0.0004336513443191196</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15179,6 +16115,12 @@
       <c r="AD156" s="2" t="n">
         <v>-0.0001237930180739044</v>
       </c>
+      <c r="AE156" s="1" t="n">
+        <v>0.08068</v>
+      </c>
+      <c r="AF156" s="2" t="n">
+        <v>-0.001114275102141796</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15273,6 +16215,12 @@
       <c r="AD157" s="2" t="n">
         <v>-0.002218259318863948</v>
       </c>
+      <c r="AE157" s="1" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="AF157" s="3" t="n">
+        <v>0.01211857018308633</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15367,6 +16315,12 @@
       <c r="AD158" s="3" t="n">
         <v>0.001971608832807573</v>
       </c>
+      <c r="AE158" s="1" t="n">
+        <v>0.2551</v>
+      </c>
+      <c r="AF158" s="3" t="n">
+        <v>0.00393545848091303</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15461,6 +16415,12 @@
       <c r="AD159" s="2" t="n">
         <v>-0.00816048962937777</v>
       </c>
+      <c r="AE159" s="1" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="AF159" s="3" t="n">
+        <v>0.00274254370929037</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15555,6 +16515,12 @@
       <c r="AD160" s="3" t="n">
         <v>0.002020202020201938</v>
       </c>
+      <c r="AE160" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="AF160" s="2" t="n">
+        <v>-0.003024193548387044</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15649,6 +16615,12 @@
       <c r="AD161" s="3" t="n">
         <v>0.001627228964675505</v>
       </c>
+      <c r="AE161" s="1" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="AF161" s="3" t="n">
+        <v>0.003181479726528113</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15743,6 +16715,12 @@
       <c r="AD162" s="3" t="n">
         <v>0.009477224090492136</v>
       </c>
+      <c r="AE162" s="1" t="n">
+        <v>0.003322</v>
+      </c>
+      <c r="AF162" s="3" t="n">
+        <v>0.006056935190793475</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15837,6 +16815,12 @@
       <c r="AD163" s="3" t="n">
         <v>0.004183266932270953</v>
       </c>
+      <c r="AE163" s="1" t="n">
+        <v>0.005039</v>
+      </c>
+      <c r="AF163" s="2" t="n">
+        <v>-0.0003967466772466307</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15931,6 +16915,12 @@
       <c r="AD164" s="3" t="n">
         <v>0.01151832460732988</v>
       </c>
+      <c r="AE164" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="AF164" s="2" t="n">
+        <v>-0.00414078674948252</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16025,6 +17015,12 @@
       <c r="AD165" s="3" t="n">
         <v>0.01075970003260523</v>
       </c>
+      <c r="AE165" s="1" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AF165" s="3" t="n">
+        <v>0.001935483870967708</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16119,6 +17115,12 @@
       <c r="AD166" s="3" t="n">
         <v>0.00432494774021481</v>
       </c>
+      <c r="AE166" s="1" t="n">
+        <v>1.3947</v>
+      </c>
+      <c r="AF166" s="3" t="n">
+        <v>0.001004808727481567</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16213,6 +17215,12 @@
       <c r="AD167" s="3" t="n">
         <v>0.006495849873691693</v>
       </c>
+      <c r="AE167" s="1" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AF167" s="3" t="n">
+        <v>0.002868411617067131</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -16307,6 +17315,12 @@
       <c r="AD168" s="3" t="n">
         <v>0.003205128205128208</v>
       </c>
+      <c r="AE168" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AF168" s="3" t="n">
+        <v>0.003194888178913741</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -16401,6 +17415,12 @@
       <c r="AD169" s="3" t="n">
         <v>0.006677796327211979</v>
       </c>
+      <c r="AE169" s="1" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="AF169" s="2" t="n">
+        <v>-0.003316749585406282</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16495,6 +17515,12 @@
       <c r="AD170" s="3" t="n">
         <v>0.003239241092087025</v>
       </c>
+      <c r="AE170" s="1" t="n">
+        <v>0.04329</v>
+      </c>
+      <c r="AF170" s="2" t="n">
+        <v>-0.001614391143911453</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16589,6 +17615,12 @@
       <c r="AD171" s="3" t="n">
         <v>0.006060606060606023</v>
       </c>
+      <c r="AE171" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="AF171" s="3" t="n">
+        <v>0.01204819277108427</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16683,6 +17715,12 @@
       <c r="AD172" s="2" t="n">
         <v>-0.01492537313432834</v>
       </c>
+      <c r="AE172" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="AF172" s="2" t="n">
+        <v>-0.0303030303030304</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16777,6 +17815,12 @@
       <c r="AD173" s="3" t="n">
         <v>0.01187648456057008</v>
       </c>
+      <c r="AE173" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AF173" s="2" t="n">
+        <v>-0.001877934272300393</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16871,6 +17915,12 @@
       <c r="AD174" s="3" t="n">
         <v>0.001110001110001142</v>
       </c>
+      <c r="AE174" s="1" t="n">
+        <v>0.08985</v>
+      </c>
+      <c r="AF174" s="2" t="n">
+        <v>-0.003769819270429171</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16965,6 +18015,12 @@
       <c r="AD175" s="3" t="n">
         <v>0.003593145384190072</v>
       </c>
+      <c r="AE175" s="1" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AF175" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -17059,6 +18115,12 @@
       <c r="AD176" s="3" t="n">
         <v>0.003278688524590193</v>
       </c>
+      <c r="AE176" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="AF176" s="2" t="n">
+        <v>-0.0009337068160598811</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -17153,6 +18215,12 @@
       <c r="AD177" s="3" t="n">
         <v>0.006402048655569855</v>
       </c>
+      <c r="AE177" s="1" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="AF177" s="3" t="n">
+        <v>0.001272264631043205</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -17247,6 +18315,12 @@
       <c r="AD178" s="3" t="n">
         <v>0.003131524008350807</v>
       </c>
+      <c r="AE178" s="1" t="n">
+        <v>0.000955</v>
+      </c>
+      <c r="AF178" s="2" t="n">
+        <v>-0.006243496357960497</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -17341,6 +18415,12 @@
       <c r="AD179" s="3" t="n">
         <v>0.005062733876293221</v>
       </c>
+      <c r="AE179" s="1" t="n">
+        <v>0.022864</v>
+      </c>
+      <c r="AF179" s="3" t="n">
+        <v>0.001489268506351262</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -17435,6 +18515,12 @@
       <c r="AD180" s="3" t="n">
         <v>0.004135246898564911</v>
       </c>
+      <c r="AE180" s="1" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AF180" s="3" t="n">
+        <v>0.0004844961240309544</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17529,6 +18615,12 @@
       <c r="AD181" s="2" t="n">
         <v>-0.008245614035087591</v>
       </c>
+      <c r="AE181" s="1" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="AF181" s="3" t="n">
+        <v>0.007606580576684893</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17623,6 +18715,12 @@
       <c r="AD182" s="3" t="n">
         <v>0.01007905138339928</v>
       </c>
+      <c r="AE182" s="1" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="AF182" s="2" t="n">
+        <v>-0.006456662101350106</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17717,6 +18815,12 @@
       <c r="AD183" s="3" t="n">
         <v>0.003665017408832777</v>
       </c>
+      <c r="AE183" s="1" t="n">
+        <v>5.486</v>
+      </c>
+      <c r="AF183" s="3" t="n">
+        <v>0.001643235347818049</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17811,6 +18915,12 @@
       <c r="AD184" s="3" t="n">
         <v>0.004160887656033322</v>
       </c>
+      <c r="AE184" s="1" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AF184" s="3" t="n">
+        <v>0.002071823204419845</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -17905,6 +19015,12 @@
       <c r="AD185" s="3" t="n">
         <v>0.006881948120698685</v>
       </c>
+      <c r="AE185" s="1" t="n">
+        <v>0.01881</v>
+      </c>
+      <c r="AF185" s="2" t="n">
+        <v>-0.01104100946372231</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17999,6 +19115,12 @@
       <c r="AD186" s="2" t="n">
         <v>-0.003236245954692416</v>
       </c>
+      <c r="AE186" s="1" t="n">
+        <v>3.09e-05</v>
+      </c>
+      <c r="AF186" s="3" t="n">
+        <v>0.003246753246753105</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -18093,6 +19215,12 @@
       <c r="AD187" s="3" t="n">
         <v>0.001895135818066884</v>
       </c>
+      <c r="AE187" s="1" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="AF187" s="2" t="n">
+        <v>-0.004413619167717568</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -18187,6 +19315,12 @@
       <c r="AD188" s="3" t="n">
         <v>0.008126077320856857</v>
       </c>
+      <c r="AE188" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="AF188" s="2" t="n">
+        <v>-0.002198339032730821</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -18281,6 +19415,12 @@
       <c r="AD189" s="3" t="n">
         <v>0.01825969341749319</v>
       </c>
+      <c r="AE189" s="1" t="n">
+        <v>0.0004481</v>
+      </c>
+      <c r="AF189" s="2" t="n">
+        <v>-0.007969891520920919</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -18375,6 +19515,12 @@
       <c r="AD190" s="2" t="n">
         <v>-0.002150537634408664</v>
       </c>
+      <c r="AE190" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="AF190" s="2" t="n">
+        <v>-0.002586206896551619</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18469,6 +19615,12 @@
       <c r="AD191" s="3" t="n">
         <v>0.002539682539682436</v>
       </c>
+      <c r="AE191" s="1" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="AF191" s="3" t="n">
+        <v>0.0006333122229260964</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18563,6 +19715,12 @@
       <c r="AD192" s="3" t="n">
         <v>0.002508061626657134</v>
       </c>
+      <c r="AE192" s="1" t="n">
+        <v>0.05585</v>
+      </c>
+      <c r="AF192" s="2" t="n">
+        <v>-0.001965689778413258</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18657,6 +19815,12 @@
       <c r="AD193" s="3" t="n">
         <v>0.009605122732123777</v>
       </c>
+      <c r="AE193" s="1" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="AF193" s="2" t="n">
+        <v>-0.003171247357293959</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -18751,6 +19915,12 @@
       <c r="AD194" s="3" t="n">
         <v>0.002596053997923231</v>
       </c>
+      <c r="AE194" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="AF194" s="2" t="n">
+        <v>-0.003107198342827603</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -18845,6 +20015,12 @@
       <c r="AD195" s="3" t="n">
         <v>0.009442870632672341</v>
       </c>
+      <c r="AE195" s="1" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="AF195" s="2" t="n">
+        <v>-0.001403180542563119</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -18939,6 +20115,12 @@
       <c r="AD196" s="3" t="n">
         <v>0.004035512510088757</v>
       </c>
+      <c r="AE196" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="AF196" s="2" t="n">
+        <v>-0.005627009646302161</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -19033,6 +20215,12 @@
       <c r="AD197" s="3" t="n">
         <v>0.01772206613356389</v>
       </c>
+      <c r="AE197" s="1" t="n">
+        <v>0.04689</v>
+      </c>
+      <c r="AF197" s="2" t="n">
+        <v>-0.00424718623911656</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -19127,6 +20315,12 @@
       <c r="AD198" s="3" t="n">
         <v>0.003718199608610593</v>
       </c>
+      <c r="AE198" s="1" t="n">
+        <v>0.5115</v>
+      </c>
+      <c r="AF198" s="2" t="n">
+        <v>-0.002729576915578217</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -19221,6 +20415,12 @@
       <c r="AD199" s="3" t="n">
         <v>0.02298850574712646</v>
       </c>
+      <c r="AE199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AF199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -19315,6 +20515,12 @@
       <c r="AD200" s="3" t="n">
         <v>0.001344989912575747</v>
       </c>
+      <c r="AE200" s="1" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="AF200" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -19409,6 +20615,12 @@
       <c r="AD201" s="3" t="n">
         <v>0.001573426573426479</v>
       </c>
+      <c r="AE201" s="1" t="n">
+        <v>0.00569</v>
+      </c>
+      <c r="AF201" s="2" t="n">
+        <v>-0.006807470762785822</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -19503,6 +20715,12 @@
       <c r="AD202" s="2" t="n">
         <v>-0.002337459960176693</v>
       </c>
+      <c r="AE202" s="1" t="n">
+        <v>0.023079</v>
+      </c>
+      <c r="AF202" s="3" t="n">
+        <v>0.001345019090593534</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -19597,6 +20815,12 @@
       <c r="AD203" s="3" t="n">
         <v>0.007352941176470671</v>
       </c>
+      <c r="AE203" s="1" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="AF203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -19691,6 +20915,12 @@
       <c r="AD204" s="3" t="n">
         <v>0.003887559808612593</v>
       </c>
+      <c r="AE204" s="1" t="n">
+        <v>0.03363</v>
+      </c>
+      <c r="AF204" s="3" t="n">
+        <v>0.001787310098301983</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -19785,6 +21015,12 @@
       <c r="AD205" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE205" s="1" t="n">
+        <v>4.189</v>
+      </c>
+      <c r="AF205" s="2" t="n">
+        <v>-0.002143878037160634</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -19879,6 +21115,12 @@
       <c r="AD206" s="3" t="n">
         <v>0.008333333333333342</v>
       </c>
+      <c r="AE206" s="1" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AF206" s="3" t="n">
+        <v>0.002754820936639121</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -19973,6 +21215,12 @@
       <c r="AD207" s="3" t="n">
         <v>0.003149345267694335</v>
       </c>
+      <c r="AE207" s="1" t="n">
+        <v>0.0012039</v>
+      </c>
+      <c r="AF207" s="2" t="n">
+        <v>-0.005370125578321213</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -20067,6 +21315,12 @@
       <c r="AD208" s="3" t="n">
         <v>0.007670850767085006</v>
       </c>
+      <c r="AE208" s="1" t="n">
+        <v>0.007152</v>
+      </c>
+      <c r="AF208" s="2" t="n">
+        <v>-0.0101038062283736</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -20161,6 +21415,12 @@
       <c r="AD209" s="3" t="n">
         <v>0.001672240802675633</v>
       </c>
+      <c r="AE209" s="1" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AF209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -20255,6 +21515,12 @@
       <c r="AD210" s="3" t="n">
         <v>0.003855050115651507</v>
       </c>
+      <c r="AE210" s="1" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="AF210" s="2" t="n">
+        <v>-0.0007680491551460578</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -20349,6 +21615,12 @@
       <c r="AD211" s="3" t="n">
         <v>0.007177033492822942</v>
       </c>
+      <c r="AE211" s="1" t="n">
+        <v>0.007157</v>
+      </c>
+      <c r="AF211" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -20443,6 +21715,12 @@
       <c r="AD212" s="2" t="n">
         <v>-0.00512470105910489</v>
       </c>
+      <c r="AE212" s="1" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AF212" s="2" t="n">
+        <v>-0.008585164835164843</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -20537,6 +21815,12 @@
       <c r="AD213" s="2" t="n">
         <v>-0.008955758552749426</v>
       </c>
+      <c r="AE213" s="1" t="n">
+        <v>0.05517</v>
+      </c>
+      <c r="AF213" s="2" t="n">
+        <v>-0.002891740466293158</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -20631,6 +21915,12 @@
       <c r="AD214" s="3" t="n">
         <v>0.005823186871360454</v>
       </c>
+      <c r="AE214" s="1" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="AF214" s="2" t="n">
+        <v>-0.001052631578947399</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -20725,6 +22015,12 @@
       <c r="AD215" s="3" t="n">
         <v>0.00813931478326708</v>
       </c>
+      <c r="AE215" s="1" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="AF215" s="3" t="n">
+        <v>0.005257228689447907</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -20819,6 +22115,12 @@
       <c r="AD216" s="3" t="n">
         <v>0.007232401157184309</v>
       </c>
+      <c r="AE216" s="1" t="n">
+        <v>0.002086</v>
+      </c>
+      <c r="AF216" s="2" t="n">
+        <v>-0.001436093824796536</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -20913,6 +22215,12 @@
       <c r="AD217" s="3" t="n">
         <v>0.007332111314780802</v>
       </c>
+      <c r="AE217" s="1" t="n">
+        <v>6.046</v>
+      </c>
+      <c r="AF217" s="3" t="n">
+        <v>0.00016542597187764</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -21007,6 +22315,12 @@
       <c r="AD218" s="3" t="n">
         <v>0.01083883129123475</v>
       </c>
+      <c r="AE218" s="1" t="n">
+        <v>4.299</v>
+      </c>
+      <c r="AF218" s="3" t="n">
+        <v>0.002097902097902177</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -21101,6 +22415,12 @@
       <c r="AD219" s="3" t="n">
         <v>0.00300075018754696</v>
       </c>
+      <c r="AE219" s="1" t="n">
+        <v>0.005351</v>
+      </c>
+      <c r="AF219" s="3" t="n">
+        <v>0.000560957367240002</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -21195,6 +22515,12 @@
       <c r="AD220" s="3" t="n">
         <v>0.0009692270414344165</v>
       </c>
+      <c r="AE220" s="1" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="AF220" s="3" t="n">
+        <v>0.0004841442749939285</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -21289,6 +22615,12 @@
       <c r="AD221" s="3" t="n">
         <v>0.009623797025371892</v>
       </c>
+      <c r="AE221" s="1" t="n">
+        <v>0.005763</v>
+      </c>
+      <c r="AF221" s="2" t="n">
+        <v>-0.001213171577123061</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -21383,6 +22715,12 @@
       <c r="AD222" s="3" t="n">
         <v>0.006622516556291427</v>
       </c>
+      <c r="AE222" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="AF222" s="3" t="n">
+        <v>0.001096491228070207</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -21477,6 +22815,12 @@
       <c r="AD223" s="3" t="n">
         <v>0.01077521700089791</v>
       </c>
+      <c r="AE223" s="1" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AF223" s="2" t="n">
+        <v>-0.0005922416345868463</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -21571,6 +22915,12 @@
       <c r="AD224" s="3" t="n">
         <v>0.00604089219330853</v>
       </c>
+      <c r="AE224" s="1" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="AF224" s="3" t="n">
+        <v>0.0004618937644341293</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -21665,6 +23015,12 @@
       <c r="AD225" s="3" t="n">
         <v>0.003003724618526976</v>
       </c>
+      <c r="AE225" s="1" t="n">
+        <v>0.08325</v>
+      </c>
+      <c r="AF225" s="2" t="n">
+        <v>-0.002755150934355464</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -21759,6 +23115,12 @@
       <c r="AD226" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE226" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="AF226" s="3" t="n">
+        <v>0.0005341880341880124</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -21853,6 +23215,12 @@
       <c r="AD227" s="3" t="n">
         <v>0.01005777872886793</v>
       </c>
+      <c r="AE227" s="1" t="n">
+        <v>0.04716</v>
+      </c>
+      <c r="AF227" s="2" t="n">
+        <v>-0.0008474576271186096</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -21947,6 +23315,12 @@
       <c r="AD228" s="3" t="n">
         <v>0.002170138888888801</v>
       </c>
+      <c r="AE228" s="1" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="AF228" s="3" t="n">
+        <v>0.002598527501082764</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -22041,6 +23415,12 @@
       <c r="AD229" s="3" t="n">
         <v>0.01576994434137285</v>
       </c>
+      <c r="AE229" s="1" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="AF229" s="2" t="n">
+        <v>-0.002739726027397212</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -22135,6 +23515,12 @@
       <c r="AD230" s="3" t="n">
         <v>0.009667673716012026</v>
       </c>
+      <c r="AE230" s="1" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AF230" s="2" t="n">
+        <v>-0.002393776181927058</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -22229,6 +23615,12 @@
       <c r="AD231" s="3" t="n">
         <v>0.005938634114153732</v>
       </c>
+      <c r="AE231" s="1" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="AF231" s="2" t="n">
+        <v>-0.001967858314201411</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -22323,6 +23715,12 @@
       <c r="AD232" s="3" t="n">
         <v>0.0008904719501335345</v>
       </c>
+      <c r="AE232" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="AF232" s="2" t="n">
+        <v>-0.00177935943060491</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -22417,6 +23815,12 @@
       <c r="AD233" s="3" t="n">
         <v>0.05017660502804904</v>
       </c>
+      <c r="AE233" s="1" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="AF233" s="3" t="n">
+        <v>0.05747353843110096</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -22511,6 +23915,12 @@
       <c r="AD234" s="3" t="n">
         <v>0.00672734467748332</v>
       </c>
+      <c r="AE234" s="1" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="AF234" s="2" t="n">
+        <v>-0.000393081761006246</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -22605,6 +24015,12 @@
       <c r="AD235" s="3" t="n">
         <v>0.003359135387760977</v>
       </c>
+      <c r="AE235" s="1" t="n">
+        <v>0.06889000000000001</v>
+      </c>
+      <c r="AF235" s="3" t="n">
+        <v>0.002765647743813823</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -22699,6 +24115,12 @@
       <c r="AD236" s="3" t="n">
         <v>0.00360432519022821</v>
       </c>
+      <c r="AE236" s="1" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="AF236" s="3" t="n">
+        <v>0.003990422984836396</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -22793,6 +24215,12 @@
       <c r="AD237" s="3" t="n">
         <v>0.01006711409395977</v>
       </c>
+      <c r="AE237" s="1" t="n">
+        <v>0.03901</v>
+      </c>
+      <c r="AF237" s="2" t="n">
+        <v>-0.003066700741119221</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -22887,6 +24315,12 @@
       <c r="AD238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AF238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -22981,6 +24415,12 @@
       <c r="AD239" s="3" t="n">
         <v>0.003268795574553682</v>
       </c>
+      <c r="AE239" s="1" t="n">
+        <v>0.003976</v>
+      </c>
+      <c r="AF239" s="2" t="n">
+        <v>-0.003508771929824375</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -23075,6 +24515,12 @@
       <c r="AD240" s="3" t="n">
         <v>0.005109489051094809</v>
       </c>
+      <c r="AE240" s="1" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="AF240" s="3" t="n">
+        <v>0.002904865649963697</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -23169,6 +24615,12 @@
       <c r="AD241" s="3" t="n">
         <v>0.006201194304088149</v>
       </c>
+      <c r="AE241" s="1" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="AF241" s="3" t="n">
+        <v>0.007532526820360706</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -23263,6 +24715,12 @@
       <c r="AD242" s="3" t="n">
         <v>0.006640106241699827</v>
       </c>
+      <c r="AE242" s="1" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="AF242" s="2" t="n">
+        <v>-0.00263852242744064</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -23357,6 +24815,12 @@
       <c r="AD243" s="2" t="n">
         <v>-0.001306620209059331</v>
       </c>
+      <c r="AE243" s="1" t="n">
+        <v>0.02295</v>
+      </c>
+      <c r="AF243" s="3" t="n">
+        <v>0.000872219799389562</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -23451,6 +24915,12 @@
       <c r="AD244" s="3" t="n">
         <v>0.01083684527393137</v>
       </c>
+      <c r="AE244" s="1" t="n">
+        <v>0.001708</v>
+      </c>
+      <c r="AF244" s="3" t="n">
+        <v>0.01727218582489587</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -23545,6 +25015,12 @@
       <c r="AD245" s="3" t="n">
         <v>0.007639419404125294</v>
       </c>
+      <c r="AE245" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="AF245" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -23639,6 +25115,12 @@
       <c r="AD246" s="3" t="n">
         <v>0.01127113337507825</v>
       </c>
+      <c r="AE246" s="1" t="n">
+        <v>0.03178</v>
+      </c>
+      <c r="AF246" s="2" t="n">
+        <v>-0.01609907120743033</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -23733,6 +25215,12 @@
       <c r="AD247" s="3" t="n">
         <v>0.008503401360544225</v>
       </c>
+      <c r="AE247" s="1" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="AF247" s="3" t="n">
+        <v>0.002248454187745833</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -23827,6 +25315,12 @@
       <c r="AD248" s="2" t="n">
         <v>-0.00783545543584723</v>
       </c>
+      <c r="AE248" s="1" t="n">
+        <v>0.03039</v>
+      </c>
+      <c r="AF248" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -23921,6 +25415,12 @@
       <c r="AD249" s="2" t="n">
         <v>-0.005626538506623042</v>
       </c>
+      <c r="AE249" s="1" t="n">
+        <v>0.008418999999999999</v>
+      </c>
+      <c r="AF249" s="2" t="n">
+        <v>-0.007544500766238338</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -24015,6 +25515,12 @@
       <c r="AD250" s="3" t="n">
         <v>0.01002506265664172</v>
       </c>
+      <c r="AE250" s="1" t="n">
+        <v>0.01994</v>
+      </c>
+      <c r="AF250" s="2" t="n">
+        <v>-0.01042183622828793</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -24109,6 +25615,12 @@
       <c r="AD251" s="3" t="n">
         <v>0.006472491909384999</v>
       </c>
+      <c r="AE251" s="1" t="n">
+        <v>0.04661</v>
+      </c>
+      <c r="AF251" s="2" t="n">
+        <v>-0.0008574490889603081</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -24203,6 +25715,12 @@
       <c r="AD252" s="3" t="n">
         <v>0.004568884723523793</v>
       </c>
+      <c r="AE252" s="1" t="n">
+        <v>0.008631</v>
+      </c>
+      <c r="AF252" s="3" t="n">
+        <v>0.006530612244898018</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -24297,6 +25815,12 @@
       <c r="AD253" s="3" t="n">
         <v>0.0005175983436852791</v>
       </c>
+      <c r="AE253" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="AF253" s="3" t="n">
+        <v>0.001034661148473833</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -24391,6 +25915,12 @@
       <c r="AD254" s="3" t="n">
         <v>0.005224489795918381</v>
       </c>
+      <c r="AE254" s="1" t="n">
+        <v>0.06134</v>
+      </c>
+      <c r="AF254" s="2" t="n">
+        <v>-0.003735585512424899</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -24485,6 +26015,12 @@
       <c r="AD255" s="3" t="n">
         <v>0.008983717012914068</v>
       </c>
+      <c r="AE255" s="1" t="n">
+        <v>0.003573</v>
+      </c>
+      <c r="AF255" s="2" t="n">
+        <v>-0.005843071786310569</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -24579,6 +26115,12 @@
       <c r="AD256" s="3" t="n">
         <v>0.007807221680054045</v>
       </c>
+      <c r="AE256" s="1" t="n">
+        <v>0.013405</v>
+      </c>
+      <c r="AF256" s="2" t="n">
+        <v>-0.001489757914338859</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -24673,6 +26215,12 @@
       <c r="AD257" s="3" t="n">
         <v>4.702699349417388e-05</v>
       </c>
+      <c r="AE257" s="1" t="n">
+        <v>0.999472</v>
+      </c>
+      <c r="AF257" s="2" t="n">
+        <v>-1.00052727779313e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -24767,6 +26315,12 @@
       <c r="AD258" s="3" t="n">
         <v>0.0005642067253441039</v>
       </c>
+      <c r="AE258" s="1" t="n">
+        <v>0.08851000000000001</v>
+      </c>
+      <c r="AF258" s="2" t="n">
+        <v>-0.001804443441975792</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -24861,6 +26415,12 @@
       <c r="AD259" s="3" t="n">
         <v>0.000881057268722431</v>
       </c>
+      <c r="AE259" s="1" t="n">
+        <v>0.09005000000000001</v>
+      </c>
+      <c r="AF259" s="2" t="n">
+        <v>-0.009132922535211238</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -24955,6 +26515,12 @@
       <c r="AD260" s="3" t="n">
         <v>0.00109876693932373</v>
       </c>
+      <c r="AE260" s="1" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="AF260" s="2" t="n">
+        <v>-0.004878048780487775</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -25049,6 +26615,12 @@
       <c r="AD261" s="2" t="n">
         <v>-0.005277044854881272</v>
       </c>
+      <c r="AE261" s="1" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="AF261" s="2" t="n">
+        <v>-0.002652519893899305</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -25143,6 +26715,12 @@
       <c r="AD262" s="2" t="n">
         <v>-0.01369155257039516</v>
       </c>
+      <c r="AE262" s="1" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="AF262" s="3" t="n">
+        <v>0.0005238344683079706</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -25237,6 +26815,12 @@
       <c r="AD263" s="3" t="n">
         <v>0.007832898172323742</v>
       </c>
+      <c r="AE263" s="1" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="AF263" s="2" t="n">
+        <v>-0.000863557858376536</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -25331,6 +26915,12 @@
       <c r="AD264" s="2" t="n">
         <v>-0.0109820149610059</v>
       </c>
+      <c r="AE264" s="1" t="n">
+        <v>0.000624</v>
+      </c>
+      <c r="AF264" s="3" t="n">
+        <v>0.004184100418409969</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -25425,6 +27015,12 @@
       <c r="AD265" s="3" t="n">
         <v>0.006854009595613392</v>
       </c>
+      <c r="AE265" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="AF265" s="3" t="n">
+        <v>0.0006807351940095026</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -25519,6 +27115,12 @@
       <c r="AD266" s="3" t="n">
         <v>0.003149606299212689</v>
       </c>
+      <c r="AE266" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="AF266" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -25613,6 +27215,12 @@
       <c r="AD267" s="3" t="n">
         <v>0.004307692307692346</v>
       </c>
+      <c r="AE267" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="AF267" s="2" t="n">
+        <v>-0.001225490196078594</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -25707,6 +27315,12 @@
       <c r="AD268" s="3" t="n">
         <v>0.005096131572851516</v>
       </c>
+      <c r="AE268" s="1" t="n">
+        <v>0.0004329</v>
+      </c>
+      <c r="AF268" s="2" t="n">
+        <v>-0.002304678497349551</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -25801,6 +27415,12 @@
       <c r="AD269" s="3" t="n">
         <v>0.006743737957610682</v>
       </c>
+      <c r="AE269" s="1" t="n">
+        <v>0.02087</v>
+      </c>
+      <c r="AF269" s="2" t="n">
+        <v>-0.001435406698564535</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -25895,6 +27515,12 @@
       <c r="AD270" s="3" t="n">
         <v>0.006640841173215311</v>
       </c>
+      <c r="AE270" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="AF270" s="3" t="n">
+        <v>0.002748763056624521</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -25989,6 +27615,12 @@
       <c r="AD271" s="3" t="n">
         <v>0.004065040650406433</v>
       </c>
+      <c r="AE271" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="AF271" s="2" t="n">
+        <v>-0.0006747638326584952</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -26083,6 +27715,12 @@
       <c r="AD272" s="3" t="n">
         <v>0.0005062009617818067</v>
       </c>
+      <c r="AE272" s="1" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="AF272" s="3" t="n">
+        <v>0.002782696686061193</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -26177,6 +27815,12 @@
       <c r="AD273" s="3" t="n">
         <v>0.006507592190889377</v>
       </c>
+      <c r="AE273" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="AF273" s="2" t="n">
+        <v>-0.001077586206896553</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -26271,6 +27915,12 @@
       <c r="AD274" s="3" t="n">
         <v>0.005703422053231931</v>
       </c>
+      <c r="AE274" s="1" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="AF274" s="3" t="n">
+        <v>0.0007876496534342197</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -26365,6 +28015,12 @@
       <c r="AD275" s="3" t="n">
         <v>0.002671415850400604</v>
       </c>
+      <c r="AE275" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="AF275" s="3" t="n">
+        <v>0.003552397868561289</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -26459,6 +28115,12 @@
       <c r="AD276" s="3" t="n">
         <v>0.001921598770176917</v>
       </c>
+      <c r="AE276" s="1" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="AF276" s="2" t="n">
+        <v>-0.0003835826620638028</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -26553,6 +28215,12 @@
       <c r="AD277" s="3" t="n">
         <v>0.002382654276864495</v>
       </c>
+      <c r="AE277" s="1" t="n">
+        <v>0.04199</v>
+      </c>
+      <c r="AF277" s="2" t="n">
+        <v>-0.001901592583789011</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -26647,6 +28315,12 @@
       <c r="AD278" s="3" t="n">
         <v>0.01467611336032382</v>
       </c>
+      <c r="AE278" s="1" t="n">
+        <v>0.01974</v>
+      </c>
+      <c r="AF278" s="2" t="n">
+        <v>-0.01546134663341635</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -26741,6 +28415,12 @@
       <c r="AD279" s="2" t="n">
         <v>-0.004646175839885629</v>
       </c>
+      <c r="AE279" s="1" t="n">
+        <v>0.005626</v>
+      </c>
+      <c r="AF279" s="3" t="n">
+        <v>0.01005385996409329</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -26835,6 +28515,12 @@
       <c r="AD280" s="2" t="n">
         <v>-0.01455823293172684</v>
       </c>
+      <c r="AE280" s="1" t="n">
+        <v>0.03918</v>
+      </c>
+      <c r="AF280" s="2" t="n">
+        <v>-0.002037697401935906</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -26929,6 +28615,12 @@
       <c r="AD281" s="3" t="n">
         <v>0.004429678848283504</v>
       </c>
+      <c r="AE281" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AF281" s="3" t="n">
+        <v>0.002205071664829109</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -27023,6 +28715,12 @@
       <c r="AD282" s="3" t="n">
         <v>0.010986328125</v>
       </c>
+      <c r="AE282" s="1" t="n">
+        <v>0.000415</v>
+      </c>
+      <c r="AF282" s="3" t="n">
+        <v>0.002173388070514422</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -27117,6 +28815,12 @@
       <c r="AD283" s="2" t="n">
         <v>-0.002439024390243972</v>
       </c>
+      <c r="AE283" s="1" t="n">
+        <v>0.04098</v>
+      </c>
+      <c r="AF283" s="3" t="n">
+        <v>0.00195599022004899</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -27211,6 +28915,12 @@
       <c r="AD284" s="3" t="n">
         <v>0.006186057577920612</v>
       </c>
+      <c r="AE284" s="1" t="n">
+        <v>0.04228</v>
+      </c>
+      <c r="AF284" s="2" t="n">
+        <v>-0.000236462520690543</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -27305,6 +29015,12 @@
       <c r="AD285" s="3" t="n">
         <v>0.0007448789571695588</v>
       </c>
+      <c r="AE285" s="1" t="n">
+        <v>0.10754</v>
+      </c>
+      <c r="AF285" s="3" t="n">
+        <v>0.0005582433941197489</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -27399,6 +29115,12 @@
       <c r="AD286" s="3" t="n">
         <v>0.007159904534606121</v>
       </c>
+      <c r="AE286" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="AF286" s="2" t="n">
+        <v>-0.002369668246445401</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -27493,6 +29215,12 @@
       <c r="AD287" s="3" t="n">
         <v>0.006941741274166262</v>
       </c>
+      <c r="AE287" s="1" t="n">
+        <v>0.15572</v>
+      </c>
+      <c r="AF287" s="3" t="n">
+        <v>0.003285870755750341</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -27587,6 +29315,12 @@
       <c r="AD288" s="3" t="n">
         <v>0.003331482509716765</v>
       </c>
+      <c r="AE288" s="1" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="AF288" s="2" t="n">
+        <v>-0.001660210293303789</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -27681,6 +29415,12 @@
       <c r="AD289" s="3" t="n">
         <v>0.006984585741811155</v>
       </c>
+      <c r="AE289" s="1" t="n">
+        <v>4.172</v>
+      </c>
+      <c r="AF289" s="2" t="n">
+        <v>-0.002152595072949137</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -27775,6 +29515,12 @@
       <c r="AD290" s="3" t="n">
         <v>0.005258852401542667</v>
       </c>
+      <c r="AE290" s="1" t="n">
+        <v>0.08599</v>
+      </c>
+      <c r="AF290" s="2" t="n">
+        <v>-0.0003487561032318327</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -27869,6 +29615,12 @@
       <c r="AD291" s="3" t="n">
         <v>0.00451467268623026</v>
       </c>
+      <c r="AE291" s="1" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="AF291" s="2" t="n">
+        <v>-0.001685393258426898</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -27963,6 +29715,12 @@
       <c r="AD292" s="3" t="n">
         <v>0.0002735042735043952</v>
       </c>
+      <c r="AE292" s="1" t="n">
+        <v>1.4602</v>
+      </c>
+      <c r="AF292" s="2" t="n">
+        <v>-0.001845649053250493</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -28057,6 +29815,12 @@
       <c r="AD293" s="3" t="n">
         <v>0.005142269454919526</v>
       </c>
+      <c r="AE293" s="1" t="n">
+        <v>0.005887</v>
+      </c>
+      <c r="AF293" s="3" t="n">
+        <v>0.003922237380627486</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -28151,6 +29915,12 @@
       <c r="AD294" s="3" t="n">
         <v>0.003794512551080101</v>
       </c>
+      <c r="AE294" s="1" t="n">
+        <v>0.003447</v>
+      </c>
+      <c r="AF294" s="3" t="n">
+        <v>0.002326257633032788</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -28245,6 +30015,12 @@
       <c r="AD295" s="3" t="n">
         <v>0.00389827362168181</v>
       </c>
+      <c r="AE295" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AF295" s="2" t="n">
+        <v>-0.001479289940828239</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -28339,6 +30115,12 @@
       <c r="AD296" s="3" t="n">
         <v>0.007139669790272206</v>
       </c>
+      <c r="AE296" s="1" t="n">
+        <v>2.261</v>
+      </c>
+      <c r="AF296" s="3" t="n">
+        <v>0.001772264067346036</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -28433,6 +30215,12 @@
       <c r="AD297" s="3" t="n">
         <v>0.005353955978584165</v>
       </c>
+      <c r="AE297" s="1" t="n">
+        <v>0.01683</v>
+      </c>
+      <c r="AF297" s="2" t="n">
+        <v>-0.004142011834319359</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -28527,6 +30315,12 @@
       <c r="AD298" s="2" t="n">
         <v>-0.007395234182415723</v>
       </c>
+      <c r="AE298" s="1" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AF298" s="3" t="n">
+        <v>0.008554083885209691</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -28621,6 +30415,12 @@
       <c r="AD299" s="3" t="n">
         <v>0.003606853020739415</v>
       </c>
+      <c r="AE299" s="1" t="n">
+        <v>0.01112</v>
+      </c>
+      <c r="AF299" s="2" t="n">
+        <v>-0.0008984725965857675</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -28715,6 +30515,12 @@
       <c r="AD300" s="3" t="n">
         <v>0.005319148936170164</v>
       </c>
+      <c r="AE300" s="1" t="n">
+        <v>0.02078</v>
+      </c>
+      <c r="AF300" s="2" t="n">
+        <v>-0.0004810004810004614</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -28809,6 +30615,12 @@
       <c r="AD301" s="3" t="n">
         <v>0.00391006842619739</v>
       </c>
+      <c r="AE301" s="1" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AF301" s="2" t="n">
+        <v>-0.001298279779292475</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -28903,6 +30715,12 @@
       <c r="AD302" s="3" t="n">
         <v>0.004363636363636312</v>
       </c>
+      <c r="AE302" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="AF302" s="3" t="n">
+        <v>0.0007241129616221092</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -28997,6 +30815,12 @@
       <c r="AD303" s="3" t="n">
         <v>0.0001350438892639585</v>
       </c>
+      <c r="AE303" s="1" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="AF303" s="3" t="n">
+        <v>0.0005401026194976825</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -29091,6 +30915,12 @@
       <c r="AD304" s="3" t="n">
         <v>0.005671077504725886</v>
       </c>
+      <c r="AE304" s="1" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="AF304" s="2" t="n">
+        <v>-0.001879699248120224</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -29185,6 +31015,12 @@
       <c r="AD305" s="3" t="n">
         <v>0.006709315025745044</v>
       </c>
+      <c r="AE305" s="1" t="n">
+        <v>0.06453</v>
+      </c>
+      <c r="AF305" s="3" t="n">
+        <v>0.0001549907005581215</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -29279,6 +31115,12 @@
       <c r="AD306" s="3" t="n">
         <v>0.004439959636730675</v>
       </c>
+      <c r="AE306" s="1" t="n">
+        <v>0.04966</v>
+      </c>
+      <c r="AF306" s="2" t="n">
+        <v>-0.002210166767128772</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -29373,6 +31215,12 @@
       <c r="AD307" s="3" t="n">
         <v>0.006500541711809323</v>
       </c>
+      <c r="AE307" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AF307" s="3" t="n">
+        <v>0.001076426264800862</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -29467,6 +31315,12 @@
       <c r="AD308" s="3" t="n">
         <v>0.003762227238525141</v>
       </c>
+      <c r="AE308" s="1" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="AF308" s="2" t="n">
+        <v>-0.004247876061969103</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -29561,6 +31415,12 @@
       <c r="AD309" s="3" t="n">
         <v>0.001283697047496738</v>
       </c>
+      <c r="AE309" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AF309" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -29655,6 +31515,12 @@
       <c r="AD310" s="3" t="n">
         <v>0.005153690410454547</v>
       </c>
+      <c r="AE310" s="1" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="AF310" s="3" t="n">
+        <v>0.002929866324848937</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -29749,6 +31615,12 @@
       <c r="AD311" s="3" t="n">
         <v>0.001792114695340545</v>
       </c>
+      <c r="AE311" s="1" t="n">
+        <v>0.004477</v>
+      </c>
+      <c r="AF311" s="3" t="n">
+        <v>0.001118067978533049</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -29843,6 +31715,12 @@
       <c r="AD312" s="3" t="n">
         <v>0.00224003772695114</v>
       </c>
+      <c r="AE312" s="1" t="n">
+        <v>0.08487</v>
+      </c>
+      <c r="AF312" s="2" t="n">
+        <v>-0.001646865074697109</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -29937,6 +31815,12 @@
       <c r="AD313" s="3" t="n">
         <v>0.003076511503477903</v>
       </c>
+      <c r="AE313" s="1" t="n">
+        <v>0.07489</v>
+      </c>
+      <c r="AF313" s="2" t="n">
+        <v>-0.001333511134818014</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -30031,6 +31915,12 @@
       <c r="AD314" s="2" t="n">
         <v>-0.0006540222367561591</v>
       </c>
+      <c r="AE314" s="1" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="AF314" s="3" t="n">
+        <v>0.003272251308900527</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -30125,6 +32015,12 @@
       <c r="AD315" s="3" t="n">
         <v>0.004388714733542358</v>
       </c>
+      <c r="AE315" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="AF315" s="2" t="n">
+        <v>-0.001872659176030103</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -30219,6 +32115,12 @@
       <c r="AD316" s="3" t="n">
         <v>0.003858875413450971</v>
       </c>
+      <c r="AE316" s="1" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="AF316" s="2" t="n">
+        <v>-0.00604063701263052</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -30313,6 +32215,12 @@
       <c r="AD317" s="3" t="n">
         <v>0.005345449685954845</v>
       </c>
+      <c r="AE317" s="1" t="n">
+        <v>0.007503</v>
+      </c>
+      <c r="AF317" s="2" t="n">
+        <v>-0.002658513890735086</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -30407,6 +32315,12 @@
       <c r="AD318" s="3" t="n">
         <v>0.004793289394847157</v>
       </c>
+      <c r="AE318" s="1" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="AF318" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -30501,6 +32415,12 @@
       <c r="AD319" s="2" t="n">
         <v>-0.000824165979861712</v>
       </c>
+      <c r="AE319" s="1" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="AF319" s="3" t="n">
+        <v>0.001291062975182997</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -30595,6 +32515,12 @@
       <c r="AD320" s="3" t="n">
         <v>0.00546448087431697</v>
       </c>
+      <c r="AE320" s="1" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="AF320" s="2" t="n">
+        <v>-0.001585144927536183</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -30689,6 +32615,12 @@
       <c r="AD321" s="3" t="n">
         <v>0.003737595050908604</v>
       </c>
+      <c r="AE321" s="1" t="n">
+        <v>0.07794</v>
+      </c>
+      <c r="AF321" s="3" t="n">
+        <v>0.0007704160246531923</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -30783,6 +32715,12 @@
       <c r="AD322" s="2" t="n">
         <v>-0.001831501831501799</v>
       </c>
+      <c r="AE322" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="AF322" s="2" t="n">
+        <v>-0.001223241590214102</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -30877,6 +32815,12 @@
       <c r="AD323" s="3" t="n">
         <v>0.0050761421319797</v>
       </c>
+      <c r="AE323" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF323" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -30971,6 +32915,12 @@
       <c r="AD324" s="3" t="n">
         <v>0.004089324413455233</v>
       </c>
+      <c r="AE324" s="1" t="n">
+        <v>0.053318</v>
+      </c>
+      <c r="AF324" s="3" t="n">
+        <v>0.0006756503134265674</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -31065,6 +33015,12 @@
       <c r="AD325" s="3" t="n">
         <v>0.004379084967320287</v>
       </c>
+      <c r="AE325" s="1" t="n">
+        <v>0.15297</v>
+      </c>
+      <c r="AF325" s="2" t="n">
+        <v>-0.004555215722001732</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -31159,6 +33115,12 @@
       <c r="AD326" s="3" t="n">
         <v>0.002629137024435455</v>
       </c>
+      <c r="AE326" s="1" t="n">
+        <v>0.006456</v>
+      </c>
+      <c r="AF326" s="2" t="n">
+        <v>-0.004164738546969014</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -31253,6 +33215,12 @@
       <c r="AD327" s="3" t="n">
         <v>0.00981757877280269</v>
       </c>
+      <c r="AE327" s="1" t="n">
+        <v>0.015195</v>
+      </c>
+      <c r="AF327" s="2" t="n">
+        <v>-0.001839322078433965</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -31347,6 +33315,12 @@
       <c r="AD328" s="3" t="n">
         <v>0.009404388714733668</v>
       </c>
+      <c r="AE328" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="AF328" s="2" t="n">
+        <v>-0.00310559006211189</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -31441,6 +33415,12 @@
       <c r="AD329" s="3" t="n">
         <v>0.002498864152658018</v>
       </c>
+      <c r="AE329" s="1" t="n">
+        <v>0.004399</v>
+      </c>
+      <c r="AF329" s="2" t="n">
+        <v>-0.00317244504871972</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -31535,6 +33515,12 @@
       <c r="AD330" s="3" t="n">
         <v>0.002704791344667721</v>
       </c>
+      <c r="AE330" s="1" t="n">
+        <v>0.05201</v>
+      </c>
+      <c r="AF330" s="3" t="n">
+        <v>0.002119460500963372</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -31629,6 +33615,12 @@
       <c r="AD331" s="3" t="n">
         <v>0.003625209146681488</v>
       </c>
+      <c r="AE331" s="1" t="n">
+        <v>0.03587</v>
+      </c>
+      <c r="AF331" s="2" t="n">
+        <v>-0.003334259516532427</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -31723,6 +33715,12 @@
       <c r="AD332" s="3" t="n">
         <v>0.01161202185792354</v>
       </c>
+      <c r="AE332" s="1" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="AF332" s="3" t="n">
+        <v>0.004726536124240232</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -31817,6 +33815,12 @@
       <c r="AD333" s="3" t="n">
         <v>0.00728407908428712</v>
       </c>
+      <c r="AE333" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="AF333" s="2" t="n">
+        <v>-0.003099173553718954</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -31911,6 +33915,12 @@
       <c r="AD334" s="2" t="n">
         <v>-0.001360852801088627</v>
       </c>
+      <c r="AE334" s="1" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="AF334" s="2" t="n">
+        <v>-0.0004542357483533769</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -32005,6 +34015,12 @@
       <c r="AD335" s="3" t="n">
         <v>0.003423820004891032</v>
       </c>
+      <c r="AE335" s="1" t="n">
+        <v>0.08187999999999999</v>
+      </c>
+      <c r="AF335" s="2" t="n">
+        <v>-0.002193516938825245</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -32099,6 +34115,12 @@
       <c r="AD336" s="3" t="n">
         <v>0.00926377376889315</v>
       </c>
+      <c r="AE336" s="1" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="AF336" s="2" t="n">
+        <v>-0.00241545893719807</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -32193,6 +34215,12 @@
       <c r="AD337" s="2" t="n">
         <v>-0.00493583415597233</v>
       </c>
+      <c r="AE337" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="AF337" s="3" t="n">
+        <v>0.00496031746031743</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -32287,6 +34315,12 @@
       <c r="AD338" s="3" t="n">
         <v>0.009700176366843066</v>
       </c>
+      <c r="AE338" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AF338" s="2" t="n">
+        <v>-0.00436681222707424</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -32381,6 +34415,12 @@
       <c r="AD339" s="3" t="n">
         <v>0.005476451259583947</v>
       </c>
+      <c r="AE339" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="AF339" s="2" t="n">
+        <v>-0.002178649237472867</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -32475,6 +34515,12 @@
       <c r="AD340" s="2" t="n">
         <v>-0.005011522844496405</v>
       </c>
+      <c r="AE340" s="1" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AF340" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -32569,6 +34615,12 @@
       <c r="AD341" s="3" t="n">
         <v>0.003962703962703882</v>
       </c>
+      <c r="AE341" s="1" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="AF341" s="2" t="n">
+        <v>-0.002553981889946575</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -32663,6 +34715,12 @@
       <c r="AD342" s="3" t="n">
         <v>0.006063668519454374</v>
       </c>
+      <c r="AE342" s="1" t="n">
+        <v>0.07953</v>
+      </c>
+      <c r="AF342" s="2" t="n">
+        <v>-0.001381215469613247</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -32757,6 +34815,12 @@
       <c r="AD343" s="3" t="n">
         <v>0.003412521328258276</v>
       </c>
+      <c r="AE343" s="1" t="n">
+        <v>7.659</v>
+      </c>
+      <c r="AF343" s="3" t="n">
+        <v>0.00183126226291697</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -32851,6 +34915,12 @@
       <c r="AD344" s="3" t="n">
         <v>0.006182121971595531</v>
       </c>
+      <c r="AE344" s="1" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="AF344" s="3" t="n">
+        <v>0.001826635669212869</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -32945,6 +35015,12 @@
       <c r="AD345" s="3" t="n">
         <v>0.004545454545454452</v>
       </c>
+      <c r="AE345" s="1" t="n">
+        <v>0.03757</v>
+      </c>
+      <c r="AF345" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -33039,6 +35115,12 @@
       <c r="AD346" s="3" t="n">
         <v>0.002403846153846223</v>
       </c>
+      <c r="AE346" s="1" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AF346" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -33133,6 +35215,12 @@
       <c r="AD347" s="3" t="n">
         <v>0.003438395415472878</v>
       </c>
+      <c r="AE347" s="1" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="AF347" s="3" t="n">
+        <v>0.001713306681896029</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -33227,6 +35315,12 @@
       <c r="AD348" s="2" t="n">
         <v>-0.0005005679520995675</v>
       </c>
+      <c r="AE348" s="1" t="n">
+        <v>5188.5</v>
+      </c>
+      <c r="AF348" s="2" t="n">
+        <v>-0.0005778676683039584</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -33321,6 +35415,12 @@
       <c r="AD349" s="3" t="n">
         <v>0.004444444444444392</v>
       </c>
+      <c r="AE349" s="1" t="n">
+        <v>0.01369</v>
+      </c>
+      <c r="AF349" s="3" t="n">
+        <v>0.009587020648967673</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -33415,6 +35515,12 @@
       <c r="AD350" s="3" t="n">
         <v>0.009038089089735392</v>
       </c>
+      <c r="AE350" s="1" t="n">
+        <v>0.01559</v>
+      </c>
+      <c r="AF350" s="2" t="n">
+        <v>-0.002559181062060258</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -33509,6 +35615,12 @@
       <c r="AD351" s="3" t="n">
         <v>0.008330610911466777</v>
       </c>
+      <c r="AE351" s="1" t="n">
+        <v>0.0006185</v>
+      </c>
+      <c r="AF351" s="3" t="n">
+        <v>0.001943949457314157</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -33603,6 +35715,12 @@
       <c r="AD352" s="3" t="n">
         <v>0.004050632911392416</v>
       </c>
+      <c r="AE352" s="1" t="n">
+        <v>0.01985</v>
+      </c>
+      <c r="AF352" s="3" t="n">
+        <v>0.001008572869389772</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -33697,6 +35815,12 @@
       <c r="AD353" s="2" t="n">
         <v>-0.0009648370497427823</v>
       </c>
+      <c r="AE353" s="1" t="n">
+        <v>0.09317</v>
+      </c>
+      <c r="AF353" s="2" t="n">
+        <v>-0.0002146153020709545</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -33791,6 +35915,12 @@
       <c r="AD354" s="3" t="n">
         <v>0.005549389567147619</v>
       </c>
+      <c r="AE354" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="AF354" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -33885,6 +36015,12 @@
       <c r="AD355" s="2" t="n">
         <v>-0.0008163265306121763</v>
       </c>
+      <c r="AE355" s="1" t="n">
+        <v>0.0006084</v>
+      </c>
+      <c r="AF355" s="2" t="n">
+        <v>-0.005882352941176436</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -33979,6 +36115,12 @@
       <c r="AD356" s="3" t="n">
         <v>0.004940711462450487</v>
       </c>
+      <c r="AE356" s="1" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="AF356" s="2" t="n">
+        <v>-0.004916420845624281</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -34073,6 +36215,12 @@
       <c r="AD357" s="3" t="n">
         <v>0.003067484662576714</v>
       </c>
+      <c r="AE357" s="1" t="n">
+        <v>0.02299</v>
+      </c>
+      <c r="AF357" s="3" t="n">
+        <v>0.004368719965050213</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -34167,6 +36315,12 @@
       <c r="AD358" s="3" t="n">
         <v>0.004926108374384223</v>
       </c>
+      <c r="AE358" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AF358" s="3" t="n">
+        <v>0.004901960784313712</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -34261,6 +36415,12 @@
       <c r="AD359" s="3" t="n">
         <v>0.003405994550408699</v>
       </c>
+      <c r="AE359" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="AF359" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -34355,6 +36515,12 @@
       <c r="AD360" s="3" t="n">
         <v>0.007845503922751955</v>
       </c>
+      <c r="AE360" s="1" t="n">
+        <v>0.003356</v>
+      </c>
+      <c r="AF360" s="3" t="n">
+        <v>0.004790419161676633</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -34449,6 +36615,12 @@
       <c r="AD361" s="3" t="n">
         <v>0.002986012887003006</v>
       </c>
+      <c r="AE361" s="1" t="n">
+        <v>0.6388</v>
+      </c>
+      <c r="AF361" s="3" t="n">
+        <v>0.0009401441554372375</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -34543,6 +36715,12 @@
       <c r="AD362" s="3" t="n">
         <v>0.004248088360238015</v>
       </c>
+      <c r="AE362" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="AF362" s="2" t="n">
+        <v>-0.001692047377326643</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -34637,6 +36815,12 @@
       <c r="AD363" s="3" t="n">
         <v>0.00522433927473889</v>
       </c>
+      <c r="AE363" s="1" t="n">
+        <v>0.06544999999999999</v>
+      </c>
+      <c r="AF363" s="3" t="n">
+        <v>0.0004585753592171869</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -34731,6 +36915,12 @@
       <c r="AD364" s="3" t="n">
         <v>0.00467886005954918</v>
       </c>
+      <c r="AE364" s="1" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AF364" s="2" t="n">
+        <v>-0.0008467400508044978</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -34825,6 +37015,12 @@
       <c r="AD365" s="3" t="n">
         <v>0.00460700823677226</v>
       </c>
+      <c r="AE365" s="1" t="n">
+        <v>0.07181999999999999</v>
+      </c>
+      <c r="AF365" s="2" t="n">
+        <v>-0.001945525291828811</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -34919,6 +37115,12 @@
       <c r="AD366" s="3" t="n">
         <v>0.005167498218104037</v>
       </c>
+      <c r="AE366" s="1" t="n">
+        <v>0.05608</v>
+      </c>
+      <c r="AF366" s="2" t="n">
+        <v>-0.005850026591030028</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -35013,6 +37215,12 @@
       <c r="AD367" s="3" t="n">
         <v>0.002570694087403673</v>
       </c>
+      <c r="AE367" s="1" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="AF367" s="2" t="n">
+        <v>-0.0006837606837607745</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -35107,6 +37315,12 @@
       <c r="AD368" s="2" t="n">
         <v>-0.00104931794333691</v>
       </c>
+      <c r="AE368" s="1" t="n">
+        <v>0.05723</v>
+      </c>
+      <c r="AF368" s="3" t="n">
+        <v>0.001925770308123353</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -35201,6 +37415,12 @@
       <c r="AD369" s="3" t="n">
         <v>0.004203039120594945</v>
       </c>
+      <c r="AE369" s="1" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="AF369" s="3" t="n">
+        <v>0.001287830006439098</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -35295,6 +37515,12 @@
       <c r="AD370" s="3" t="n">
         <v>0.003701418877236197</v>
       </c>
+      <c r="AE370" s="1" t="n">
+        <v>0.0001626</v>
+      </c>
+      <c r="AF370" s="2" t="n">
+        <v>-0.0006146281499692835</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -35389,6 +37615,12 @@
       <c r="AD371" s="3" t="n">
         <v>0.002510707428740165</v>
       </c>
+      <c r="AE371" s="1" t="n">
+        <v>0.006834</v>
+      </c>
+      <c r="AF371" s="3" t="n">
+        <v>0.006776664702416033</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -35483,6 +37715,12 @@
       <c r="AD372" s="3" t="n">
         <v>0.000573805766748032</v>
       </c>
+      <c r="AE372" s="1" t="n">
+        <v>0.006985</v>
+      </c>
+      <c r="AF372" s="3" t="n">
+        <v>0.001433691756272343</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -35577,6 +37815,12 @@
       <c r="AD373" s="3" t="n">
         <v>0.003446447507953432</v>
       </c>
+      <c r="AE373" s="1" t="n">
+        <v>3.803</v>
+      </c>
+      <c r="AF373" s="3" t="n">
+        <v>0.004755614266842746</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -35671,6 +37915,12 @@
       <c r="AD374" s="3" t="n">
         <v>0.0004268639726807377</v>
       </c>
+      <c r="AE374" s="1" t="n">
+        <v>0.07037</v>
+      </c>
+      <c r="AF374" s="3" t="n">
+        <v>0.0008533636751529583</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -35765,6 +38015,12 @@
       <c r="AD375" s="3" t="n">
         <v>0.003145841197936331</v>
       </c>
+      <c r="AE375" s="1" t="n">
+        <v>0.07979</v>
+      </c>
+      <c r="AF375" s="3" t="n">
+        <v>0.0008780732563973986</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -35859,6 +38115,12 @@
       <c r="AD376" s="3" t="n">
         <v>0.001113762927605419</v>
       </c>
+      <c r="AE376" s="1" t="n">
+        <v>0.06293</v>
+      </c>
+      <c r="AF376" s="3" t="n">
+        <v>0.0001589319771137337</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -35953,6 +38215,12 @@
       <c r="AD377" s="3" t="n">
         <v>0.002607222004953797</v>
       </c>
+      <c r="AE377" s="1" t="n">
+        <v>0.07686</v>
+      </c>
+      <c r="AF377" s="2" t="n">
+        <v>-0.0006501105187883028</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -36047,6 +38315,12 @@
       <c r="AD378" s="3" t="n">
         <v>0.0002473410833539511</v>
       </c>
+      <c r="AE378" s="1" t="n">
+        <v>0.0004047</v>
+      </c>
+      <c r="AF378" s="3" t="n">
+        <v>0.000741839762611294</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -36141,6 +38415,12 @@
       <c r="AD379" s="3" t="n">
         <v>0.001221001221001313</v>
       </c>
+      <c r="AE379" s="1" t="n">
+        <v>0.07385</v>
+      </c>
+      <c r="AF379" s="3" t="n">
+        <v>0.000677506775067676</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -36235,6 +38515,12 @@
       <c r="AD380" s="3" t="n">
         <v>0.004395604395604503</v>
       </c>
+      <c r="AE380" s="1" t="n">
+        <v>0.001383</v>
+      </c>
+      <c r="AF380" s="3" t="n">
+        <v>0.008752735229759195</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -36329,6 +38615,12 @@
       <c r="AD381" s="3" t="n">
         <v>0.005375494071146215</v>
       </c>
+      <c r="AE381" s="1" t="n">
+        <v>6.372</v>
+      </c>
+      <c r="AF381" s="3" t="n">
+        <v>0.002044346595376616</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -36423,6 +38715,12 @@
       <c r="AD382" s="3" t="n">
         <v>0.01002147458840369</v>
       </c>
+      <c r="AE382" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="AF382" s="2" t="n">
+        <v>-0.009922041105598831</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -36517,6 +38815,12 @@
       <c r="AD383" s="3" t="n">
         <v>0.003414911781445705</v>
       </c>
+      <c r="AE383" s="1" t="n">
+        <v>0.01756</v>
+      </c>
+      <c r="AF383" s="2" t="n">
+        <v>-0.003970504821327318</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -36611,6 +38915,12 @@
       <c r="AD384" s="3" t="n">
         <v>0.002961500493583364</v>
       </c>
+      <c r="AE384" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="AF384" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -36705,6 +39015,12 @@
       <c r="AD385" s="3" t="n">
         <v>0.00557911180540066</v>
       </c>
+      <c r="AE385" s="1" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="AF385" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -36799,6 +39115,12 @@
       <c r="AD386" s="3" t="n">
         <v>0.0007686395080706501</v>
       </c>
+      <c r="AE386" s="1" t="n">
+        <v>0.001306</v>
+      </c>
+      <c r="AF386" s="3" t="n">
+        <v>0.003072196620583792</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -36893,6 +39215,12 @@
       <c r="AD387" s="3" t="n">
         <v>0.002533783783783754</v>
       </c>
+      <c r="AE387" s="1" t="n">
+        <v>0.0005925</v>
+      </c>
+      <c r="AF387" s="2" t="n">
+        <v>-0.001684919966301459</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -36987,6 +39315,12 @@
       <c r="AD388" s="3" t="n">
         <v>0.003496503496503506</v>
       </c>
+      <c r="AE388" s="1" t="n">
+        <v>0.01143</v>
+      </c>
+      <c r="AF388" s="2" t="n">
+        <v>-0.004355400696864236</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -37081,6 +39415,12 @@
       <c r="AD389" s="3" t="n">
         <v>0.004424778761061959</v>
       </c>
+      <c r="AE389" s="1" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="AF389" s="2" t="n">
+        <v>-0.001101321585903039</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -37175,6 +39515,12 @@
       <c r="AD390" s="3" t="n">
         <v>0.006354855109303514</v>
       </c>
+      <c r="AE390" s="1" t="n">
+        <v>0.07913000000000001</v>
+      </c>
+      <c r="AF390" s="2" t="n">
+        <v>-0.0006314725940893469</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -37269,6 +39615,12 @@
       <c r="AD391" s="3" t="n">
         <v>0.01024748646558383</v>
       </c>
+      <c r="AE391" s="1" t="n">
+        <v>0.05206</v>
+      </c>
+      <c r="AF391" s="2" t="n">
+        <v>-0.003636363636363555</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -37363,6 +39715,12 @@
       <c r="AD392" s="3" t="n">
         <v>0.008474576271186463</v>
       </c>
+      <c r="AE392" s="1" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="AF392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -37457,6 +39815,12 @@
       <c r="AD393" s="3" t="n">
         <v>0.007045561296383318</v>
       </c>
+      <c r="AE393" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AF393" s="2" t="n">
+        <v>-0.008395522388059682</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -37551,6 +39915,12 @@
       <c r="AD394" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE394" s="1" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="AF394" s="2" t="n">
+        <v>-0.0009837678307919612</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -37645,6 +40015,12 @@
       <c r="AD395" s="3" t="n">
         <v>0.005144032921810705</v>
       </c>
+      <c r="AE395" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="AF395" s="3" t="n">
+        <v>0.001023541453428893</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -37739,6 +40115,12 @@
       <c r="AD396" s="3" t="n">
         <v>0.009057971014492882</v>
       </c>
+      <c r="AE396" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF396" s="2" t="n">
+        <v>-0.001795332136445363</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -37833,6 +40215,12 @@
       <c r="AD397" s="3" t="n">
         <v>0.00396196513470673</v>
       </c>
+      <c r="AE397" s="1" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF397" s="3" t="n">
+        <v>0.002367797947908535</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -37927,6 +40315,12 @@
       <c r="AD398" s="3" t="n">
         <v>0.01156619948292285</v>
       </c>
+      <c r="AE398" s="1" t="n">
+        <v>0.007502</v>
+      </c>
+      <c r="AF398" s="3" t="n">
+        <v>0.00914716168953462</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -38021,6 +40415,12 @@
       <c r="AD399" s="3" t="n">
         <v>0.002701659590891465</v>
       </c>
+      <c r="AE399" s="1" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="AF399" s="2" t="n">
+        <v>-0.001154734411085323</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -38115,6 +40515,12 @@
       <c r="AD400" s="3" t="n">
         <v>0.002833753148614647</v>
       </c>
+      <c r="AE400" s="1" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AF400" s="3" t="n">
+        <v>0.002825745682888577</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -38209,6 +40615,12 @@
       <c r="AD401" s="3" t="n">
         <v>0.004185267857142929</v>
       </c>
+      <c r="AE401" s="1" t="n">
+        <v>0.007246</v>
+      </c>
+      <c r="AF401" s="3" t="n">
+        <v>0.006668519033064661</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -38303,6 +40715,12 @@
       <c r="AD402" s="3" t="n">
         <v>0.002622377622377591</v>
       </c>
+      <c r="AE402" s="1" t="n">
+        <v>0.004607</v>
+      </c>
+      <c r="AF402" s="3" t="n">
+        <v>0.004141238012205737</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -38397,6 +40815,12 @@
       <c r="AD403" s="3" t="n">
         <v>0.004516371847948944</v>
       </c>
+      <c r="AE403" s="1" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="AF403" s="2" t="n">
+        <v>-0.001124016485575206</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -38491,6 +40915,12 @@
       <c r="AD404" s="3" t="n">
         <v>0.0004177109440266875</v>
       </c>
+      <c r="AE404" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AF404" s="3" t="n">
+        <v>0.002087682672233822</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -38585,6 +41015,12 @@
       <c r="AD405" s="3" t="n">
         <v>0.003535583941605864</v>
       </c>
+      <c r="AE405" s="1" t="n">
+        <v>0.0008814</v>
+      </c>
+      <c r="AF405" s="3" t="n">
+        <v>0.001704739174906219</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -38679,6 +41115,12 @@
       <c r="AD406" s="3" t="n">
         <v>0.003951007506914274</v>
       </c>
+      <c r="AE406" s="1" t="n">
+        <v>0.005075</v>
+      </c>
+      <c r="AF406" s="2" t="n">
+        <v>-0.001377410468319571</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -38773,6 +41215,12 @@
       <c r="AD407" s="3" t="n">
         <v>0.004991680532446009</v>
       </c>
+      <c r="AE407" s="1" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="AF407" s="2" t="n">
+        <v>-0.0008278145695363901</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -38867,6 +41315,12 @@
       <c r="AD408" s="2" t="n">
         <v>-0.002051983584131303</v>
       </c>
+      <c r="AE408" s="1" t="n">
+        <v>0.001467</v>
+      </c>
+      <c r="AF408" s="3" t="n">
+        <v>0.005483207676490732</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -38961,6 +41415,12 @@
       <c r="AD409" s="2" t="n">
         <v>-0.003613835828600782</v>
       </c>
+      <c r="AE409" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="AF409" s="3" t="n">
+        <v>0.006217616580310807</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -39055,6 +41515,12 @@
       <c r="AD410" s="3" t="n">
         <v>0.002449479485609208</v>
       </c>
+      <c r="AE410" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="AF410" s="2" t="n">
+        <v>-0.002443494196701184</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -39149,6 +41615,12 @@
       <c r="AD411" s="3" t="n">
         <v>0.006889242183359807</v>
       </c>
+      <c r="AE411" s="1" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="AF411" s="3" t="n">
+        <v>0.002631578947368423</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -39243,6 +41715,12 @@
       <c r="AD412" s="3" t="n">
         <v>0.002818991097922785</v>
       </c>
+      <c r="AE412" s="1" t="n">
+        <v>0.06753000000000001</v>
+      </c>
+      <c r="AF412" s="2" t="n">
+        <v>-0.0008877052818462882</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -39337,6 +41815,12 @@
       <c r="AD413" s="3" t="n">
         <v>0.00435471100554236</v>
       </c>
+      <c r="AE413" s="1" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AF413" s="2" t="n">
+        <v>-0.0003941663381947182</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -39431,6 +41915,12 @@
       <c r="AD414" s="3" t="n">
         <v>0.00171657448025939</v>
       </c>
+      <c r="AE414" s="1" t="n">
+        <v>0.05256</v>
+      </c>
+      <c r="AF414" s="3" t="n">
+        <v>0.0007616146230008628</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -39525,6 +42015,12 @@
       <c r="AD415" s="3" t="n">
         <v>0.001720183486238597</v>
       </c>
+      <c r="AE415" s="1" t="n">
+        <v>1.748</v>
+      </c>
+      <c r="AF415" s="3" t="n">
+        <v>0.0005724098454492787</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -39619,6 +42115,12 @@
       <c r="AD416" s="3" t="n">
         <v>0.005071728734965992</v>
       </c>
+      <c r="AE416" s="1" t="n">
+        <v>0.06927</v>
+      </c>
+      <c r="AF416" s="2" t="n">
+        <v>-0.001297577854671377</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -39713,6 +42215,12 @@
       <c r="AD417" s="3" t="n">
         <v>0.01351351351351353</v>
       </c>
+      <c r="AE417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AF417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -39807,6 +42315,12 @@
       <c r="AD418" s="3" t="n">
         <v>0.003289473684210529</v>
       </c>
+      <c r="AE418" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="AF418" s="2" t="n">
+        <v>-0.003934426229508127</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -39901,6 +42415,12 @@
       <c r="AD419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AF419" s="3" t="n">
+        <v>0.008130081300812959</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -39995,6 +42515,12 @@
       <c r="AD420" s="3" t="n">
         <v>0.008909853249475892</v>
       </c>
+      <c r="AE420" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="AF420" s="2" t="n">
+        <v>-0.001558441558441495</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -40089,6 +42615,12 @@
       <c r="AD421" s="2" t="n">
         <v>-0.002314695746103626</v>
       </c>
+      <c r="AE421" s="1" t="n">
+        <v>0.19433</v>
+      </c>
+      <c r="AF421" s="3" t="n">
+        <v>0.001907609816457049</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -40183,6 +42715,12 @@
       <c r="AD422" s="3" t="n">
         <v>0.004681100058513763</v>
       </c>
+      <c r="AE422" s="1" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="AF422" s="3" t="n">
+        <v>0.0002912055911472371</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -40277,6 +42815,12 @@
       <c r="AD423" s="3" t="n">
         <v>0.006364922206506449</v>
       </c>
+      <c r="AE423" s="1" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="AF423" s="2" t="n">
+        <v>-0.0007027406886859925</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -40371,6 +42915,12 @@
       <c r="AD424" s="3" t="n">
         <v>0.005671077504725831</v>
       </c>
+      <c r="AE424" s="1" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="AF424" s="2" t="n">
+        <v>-0.003759398496240611</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -40465,6 +43015,12 @@
       <c r="AD425" s="3" t="n">
         <v>0.001919385796545161</v>
       </c>
+      <c r="AE425" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="AF425" s="3" t="n">
+        <v>0.0009578544061301627</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -40559,6 +43115,12 @@
       <c r="AD426" s="3" t="n">
         <v>0.002811357885858877</v>
       </c>
+      <c r="AE426" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="AF426" s="2" t="n">
+        <v>-0.003364171572750171</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -40653,6 +43215,12 @@
       <c r="AD427" s="3" t="n">
         <v>0.003543307086614166</v>
       </c>
+      <c r="AE427" s="1" t="n">
+        <v>0.02551</v>
+      </c>
+      <c r="AF427" s="3" t="n">
+        <v>0.0007846214201648747</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -40747,6 +43315,12 @@
       <c r="AD428" s="3" t="n">
         <v>0.009166356992443876</v>
       </c>
+      <c r="AE428" s="1" t="n">
+        <v>0.008123</v>
+      </c>
+      <c r="AF428" s="2" t="n">
+        <v>-0.002945869645268162</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -40841,6 +43415,12 @@
       <c r="AD429" s="3" t="n">
         <v>0.004058441558441675</v>
       </c>
+      <c r="AE429" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="AF429" s="2" t="n">
+        <v>-0.001616814874696922</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -40935,6 +43515,12 @@
       <c r="AD430" s="3" t="n">
         <v>0.004194756554307153</v>
       </c>
+      <c r="AE430" s="1" t="n">
+        <v>0.06691</v>
+      </c>
+      <c r="AF430" s="2" t="n">
+        <v>-0.00179024317469803</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -41029,6 +43615,12 @@
       <c r="AD431" s="3" t="n">
         <v>0.003690036900369013</v>
       </c>
+      <c r="AE431" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AF431" s="3" t="n">
+        <v>0.001838235294117572</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -41123,6 +43715,12 @@
       <c r="AD432" s="3" t="n">
         <v>0.005536982866694445</v>
       </c>
+      <c r="AE432" s="1" t="n">
+        <v>0.009597</v>
+      </c>
+      <c r="AF432" s="2" t="n">
+        <v>-0.002909090909090935</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -41217,6 +43815,12 @@
       <c r="AD433" s="3" t="n">
         <v>0.003880669415474179</v>
       </c>
+      <c r="AE433" s="1" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="AF433" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -41311,6 +43915,12 @@
       <c r="AD434" s="3" t="n">
         <v>0.0004718093890069858</v>
       </c>
+      <c r="AE434" s="1" t="n">
+        <v>0.04276</v>
+      </c>
+      <c r="AF434" s="3" t="n">
+        <v>0.008252770572977981</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -41405,6 +44015,12 @@
       <c r="AD435" s="3" t="n">
         <v>0.007777057679844366</v>
       </c>
+      <c r="AE435" s="1" t="n">
+        <v>0.001556</v>
+      </c>
+      <c r="AF435" s="3" t="n">
+        <v>0.0006430868167203426</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -41499,6 +44115,12 @@
       <c r="AD436" s="3" t="n">
         <v>0.005847953216374284</v>
       </c>
+      <c r="AE436" s="1" t="n">
+        <v>0.02753</v>
+      </c>
+      <c r="AF436" s="3" t="n">
+        <v>0.000363372093023241</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -41593,6 +44215,12 @@
       <c r="AD437" s="3" t="n">
         <v>0.002207234825260571</v>
       </c>
+      <c r="AE437" s="1" t="n">
+        <v>0.08233</v>
+      </c>
+      <c r="AF437" s="3" t="n">
+        <v>0.007341245564664179</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -41687,6 +44315,12 @@
       <c r="AD438" s="3" t="n">
         <v>0.004355400696864116</v>
       </c>
+      <c r="AE438" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="AF438" s="2" t="n">
+        <v>-0.0008673026886383596</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -41781,6 +44415,12 @@
       <c r="AD439" s="3" t="n">
         <v>0.006480881399870389</v>
       </c>
+      <c r="AE439" s="1" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="AF439" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -41875,6 +44515,12 @@
       <c r="AD440" s="3" t="n">
         <v>0.005509641873278252</v>
       </c>
+      <c r="AE440" s="1" t="n">
+        <v>0.001821</v>
+      </c>
+      <c r="AF440" s="2" t="n">
+        <v>-0.002191780821917861</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -41969,6 +44615,12 @@
       <c r="AD441" s="3" t="n">
         <v>0.0008158825129182009</v>
       </c>
+      <c r="AE441" s="1" t="n">
+        <v>0.03669</v>
+      </c>
+      <c r="AF441" s="2" t="n">
+        <v>-0.002989130434782581</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -42063,6 +44715,12 @@
       <c r="AD442" s="3" t="n">
         <v>0.005470459518599529</v>
       </c>
+      <c r="AE442" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="AF442" s="2" t="n">
+        <v>-0.002720348204570263</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -42157,6 +44815,12 @@
       <c r="AD443" s="3" t="n">
         <v>0.004732607666824337</v>
       </c>
+      <c r="AE443" s="1" t="n">
+        <v>0.12723</v>
+      </c>
+      <c r="AF443" s="2" t="n">
+        <v>-0.001177578897786022</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -42251,6 +44915,12 @@
       <c r="AD444" s="3" t="n">
         <v>0.002185696800139796</v>
       </c>
+      <c r="AE444" s="1" t="n">
+        <v>0.011495</v>
+      </c>
+      <c r="AF444" s="3" t="n">
+        <v>0.002791590334118536</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -42345,6 +45015,12 @@
       <c r="AD445" s="3" t="n">
         <v>0.006457220911461476</v>
       </c>
+      <c r="AE445" s="1" t="n">
+        <v>0.08079</v>
+      </c>
+      <c r="AF445" s="2" t="n">
+        <v>-0.003207896360271393</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -42439,6 +45115,12 @@
       <c r="AD446" s="3" t="n">
         <v>0.0009324009324008286</v>
       </c>
+      <c r="AE446" s="1" t="n">
+        <v>0.0002147</v>
+      </c>
+      <c r="AF446" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -42533,6 +45215,12 @@
       <c r="AD447" s="3" t="n">
         <v>0.007530120481927665</v>
       </c>
+      <c r="AE447" s="1" t="n">
+        <v>0.00669</v>
+      </c>
+      <c r="AF447" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -42627,6 +45315,12 @@
       <c r="AD448" s="2" t="n">
         <v>-0.001109206413229797</v>
       </c>
+      <c r="AE448" s="1" t="n">
+        <v>0.09915</v>
+      </c>
+      <c r="AF448" s="3" t="n">
+        <v>0.0009085402786190869</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -42721,6 +45415,12 @@
       <c r="AD449" s="3" t="n">
         <v>0.004181600955794541</v>
       </c>
+      <c r="AE449" s="1" t="n">
+        <v>0.001677</v>
+      </c>
+      <c r="AF449" s="2" t="n">
+        <v>-0.002379535990481785</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -42815,6 +45515,12 @@
       <c r="AD450" s="3" t="n">
         <v>0.00533204071740184</v>
       </c>
+      <c r="AE450" s="1" t="n">
+        <v>0.0002079</v>
+      </c>
+      <c r="AF450" s="3" t="n">
+        <v>0.00241080038572812</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -42909,6 +45615,12 @@
       <c r="AD451" s="3" t="n">
         <v>0.005714285714285661</v>
       </c>
+      <c r="AE451" s="1" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="AF451" s="3" t="n">
+        <v>0.001893939393939421</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -43003,6 +45715,12 @@
       <c r="AD452" s="3" t="n">
         <v>0.005212211466865273</v>
       </c>
+      <c r="AE452" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AF452" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -43097,6 +45815,12 @@
       <c r="AD453" s="3" t="n">
         <v>0.002293577981651277</v>
       </c>
+      <c r="AE453" s="1" t="n">
+        <v>0.0001747</v>
+      </c>
+      <c r="AF453" s="2" t="n">
+        <v>-0.0005720823798627141</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -43191,6 +45915,12 @@
       <c r="AD454" s="2" t="n">
         <v>-0.000543773790103232</v>
       </c>
+      <c r="AE454" s="1" t="n">
+        <v>0.11036</v>
+      </c>
+      <c r="AF454" s="3" t="n">
+        <v>0.000725426187885353</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -43285,6 +46015,12 @@
       <c r="AD455" s="3" t="n">
         <v>0.002989238740533969</v>
       </c>
+      <c r="AE455" s="1" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="AF455" s="3" t="n">
+        <v>0.0001986886548777846</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -43379,6 +46115,12 @@
       <c r="AD456" s="3" t="n">
         <v>0.002950037660055136</v>
       </c>
+      <c r="AE456" s="1" t="n">
+        <v>0.015975</v>
+      </c>
+      <c r="AF456" s="2" t="n">
+        <v>-0.0002503285562300852</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -43473,6 +46215,12 @@
       <c r="AD457" s="3" t="n">
         <v>0.001496557916791449</v>
       </c>
+      <c r="AE457" s="1" t="n">
+        <v>0.006684</v>
+      </c>
+      <c r="AF457" s="2" t="n">
+        <v>-0.001195457262402898</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -43567,6 +46315,12 @@
       <c r="AD458" s="3" t="n">
         <v>0.004162330905306976</v>
       </c>
+      <c r="AE458" s="1" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="AF458" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -43661,6 +46415,12 @@
       <c r="AD459" s="3" t="n">
         <v>0.004097714736012606</v>
       </c>
+      <c r="AE459" s="1" t="n">
+        <v>0.006364</v>
+      </c>
+      <c r="AF459" s="2" t="n">
+        <v>-0.001098728614032344</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -43755,6 +46515,12 @@
       <c r="AD460" s="3" t="n">
         <v>0.005079825834542861</v>
       </c>
+      <c r="AE460" s="1" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="AF460" s="2" t="n">
+        <v>-0.002166064981949621</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -43849,6 +46615,12 @@
       <c r="AD461" s="2" t="n">
         <v>-0.002443629901144041</v>
       </c>
+      <c r="AE461" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="AF461" s="3" t="n">
+        <v>0.005455962587685161</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -43943,6 +46715,12 @@
       <c r="AD462" s="2" t="n">
         <v>-0.001762891141471942</v>
       </c>
+      <c r="AE462" s="1" t="n">
+        <v>0.04512</v>
+      </c>
+      <c r="AF462" s="2" t="n">
+        <v>-0.003973509933774826</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -44037,6 +46815,12 @@
       <c r="AD463" s="3" t="n">
         <v>0.001432664756446933</v>
       </c>
+      <c r="AE463" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AF463" s="3" t="n">
+        <v>0.00143061516452081</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -44131,6 +46915,12 @@
       <c r="AD464" s="3" t="n">
         <v>0.002291825821237673</v>
       </c>
+      <c r="AE464" s="1" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="AF464" s="2" t="n">
+        <v>-0.0007621951219513048</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -44225,6 +47015,12 @@
       <c r="AD465" s="3" t="n">
         <v>0.002513464991023262</v>
       </c>
+      <c r="AE465" s="1" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="AF465" s="2" t="n">
+        <v>-0.0007163323782234168</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -44319,6 +47115,12 @@
       <c r="AD466" s="3" t="n">
         <v>0.005645730416372623</v>
       </c>
+      <c r="AE466" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="AF466" s="2" t="n">
+        <v>-0.002807017543859652</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -44413,6 +47215,12 @@
       <c r="AD467" s="3" t="n">
         <v>0.005213764337851898</v>
       </c>
+      <c r="AE467" s="1" t="n">
+        <v>0.01924</v>
+      </c>
+      <c r="AF467" s="2" t="n">
+        <v>-0.002074688796680413</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -44507,6 +47315,12 @@
       <c r="AD468" s="3" t="n">
         <v>0.00390624999999984</v>
       </c>
+      <c r="AE468" s="1" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="AF468" s="2" t="n">
+        <v>-0.01070038910505827</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -44601,6 +47415,12 @@
       <c r="AD469" s="3" t="n">
         <v>0.003774534474081534</v>
       </c>
+      <c r="AE469" s="1" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="AF469" s="2" t="n">
+        <v>-0.001253446979192781</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -44695,6 +47515,12 @@
       <c r="AD470" s="3" t="n">
         <v>0.003412969283276454</v>
       </c>
+      <c r="AE470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="AF470" s="2" t="n">
+        <v>-0.001133786848072563</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -44789,6 +47615,12 @@
       <c r="AD471" s="3" t="n">
         <v>0.009959539371304086</v>
       </c>
+      <c r="AE471" s="1" t="n">
+        <v>3.243</v>
+      </c>
+      <c r="AF471" s="2" t="n">
+        <v>-0.0006163328197227192</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -44883,6 +47715,12 @@
       <c r="AD472" s="3" t="n">
         <v>0.00331989566042213</v>
       </c>
+      <c r="AE472" s="1" t="n">
+        <v>0.04201</v>
+      </c>
+      <c r="AF472" s="2" t="n">
+        <v>-0.007090522335145395</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -44977,6 +47815,12 @@
       <c r="AD473" s="3" t="n">
         <v>0.008012820512820521</v>
       </c>
+      <c r="AE473" s="1" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="AF473" s="2" t="n">
+        <v>-0.0007949125596185309</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -45071,6 +47915,12 @@
       <c r="AD474" s="3" t="n">
         <v>0.00210501695708112</v>
       </c>
+      <c r="AE474" s="1" t="n">
+        <v>0.008571</v>
+      </c>
+      <c r="AF474" s="3" t="n">
+        <v>0.0002333994631812657</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -45165,6 +48015,12 @@
       <c r="AD475" s="3" t="n">
         <v>0.006254510464277035</v>
       </c>
+      <c r="AE475" s="1" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="AF475" s="3" t="n">
+        <v>0.002629691608893115</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -45259,6 +48115,12 @@
       <c r="AD476" s="3" t="n">
         <v>0.006851922344880076</v>
       </c>
+      <c r="AE476" s="1" t="n">
+        <v>0.07926</v>
+      </c>
+      <c r="AF476" s="2" t="n">
+        <v>-0.001134215500945264</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -45353,6 +48215,12 @@
       <c r="AD477" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE477" s="1" t="n">
+        <v>0.13622</v>
+      </c>
+      <c r="AF477" s="2" t="n">
+        <v>-0.0002935564362247504</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -45447,6 +48315,12 @@
       <c r="AD478" s="3" t="n">
         <v>0.002535925612848733</v>
       </c>
+      <c r="AE478" s="1" t="n">
+        <v>0.04747</v>
+      </c>
+      <c r="AF478" s="3" t="n">
+        <v>0.0006323777403034424</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -45541,6 +48415,12 @@
       <c r="AD479" s="3" t="n">
         <v>0.00187371182312169</v>
       </c>
+      <c r="AE479" s="1" t="n">
+        <v>0.005345</v>
+      </c>
+      <c r="AF479" s="2" t="n">
+        <v>-0.0003740415186086152</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -45635,6 +48515,12 @@
       <c r="AD480" s="3" t="n">
         <v>0.003205128205128248</v>
       </c>
+      <c r="AE480" s="1" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="AF480" s="2" t="n">
+        <v>-0.00141995030173948</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -45729,6 +48615,12 @@
       <c r="AD481" s="3" t="n">
         <v>0.0044955705407906</v>
       </c>
+      <c r="AE481" s="1" t="n">
+        <v>0.07596</v>
+      </c>
+      <c r="AF481" s="2" t="n">
+        <v>-0.0001316309069368978</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -45823,6 +48715,12 @@
       <c r="AD482" s="3" t="n">
         <v>0.002689979825151319</v>
       </c>
+      <c r="AE482" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="AF482" s="2" t="n">
+        <v>-0.001341381623071709</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -45917,6 +48815,12 @@
       <c r="AD483" s="3" t="n">
         <v>0.003999999999999976</v>
       </c>
+      <c r="AE483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="AF483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -46011,6 +48915,12 @@
       <c r="AD484" s="3" t="n">
         <v>0.004178272980501383</v>
       </c>
+      <c r="AE484" s="1" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="AF484" s="2" t="n">
+        <v>-0.001849283402681386</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -46105,6 +49015,12 @@
       <c r="AD485" s="3" t="n">
         <v>0.01307664366146007</v>
       </c>
+      <c r="AE485" s="1" t="n">
+        <v>0.008376</v>
+      </c>
+      <c r="AF485" s="3" t="n">
+        <v>0.001075654356400183</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -46199,6 +49115,12 @@
       <c r="AD486" s="3" t="n">
         <v>0.0068483953269774</v>
       </c>
+      <c r="AE486" s="1" t="n">
+        <v>0.007488</v>
+      </c>
+      <c r="AF486" s="2" t="n">
+        <v>-0.001333688983729056</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -46293,6 +49215,12 @@
       <c r="AD487" s="3" t="n">
         <v>0.04602888086642606</v>
       </c>
+      <c r="AE487" s="1" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="AF487" s="3" t="n">
+        <v>0.007765314926660897</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -46387,6 +49315,12 @@
       <c r="AD488" s="2" t="n">
         <v>-0.000433181719731297</v>
       </c>
+      <c r="AE488" s="1" t="n">
+        <v>0.009204</v>
+      </c>
+      <c r="AF488" s="2" t="n">
+        <v>-0.002816901408450702</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -46481,6 +49415,12 @@
       <c r="AD489" s="3" t="n">
         <v>0.00881057268722467</v>
       </c>
+      <c r="AE489" s="1" t="n">
+        <v>0.03916</v>
+      </c>
+      <c r="AF489" s="3" t="n">
+        <v>0.005908040071923993</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -46575,6 +49515,12 @@
       <c r="AD490" s="2" t="n">
         <v>-0.00395528804815135</v>
       </c>
+      <c r="AE490" s="1" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="AF490" s="3" t="n">
+        <v>0.006560773480662955</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -46669,6 +49615,12 @@
       <c r="AD491" s="3" t="n">
         <v>0.003089598352214157</v>
       </c>
+      <c r="AE491" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="AF491" s="3" t="n">
+        <v>0.004106776180698127</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -46763,6 +49715,12 @@
       <c r="AD492" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE492" s="1" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="AF492" s="3" t="n">
+        <v>0.003012048192771087</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -46857,6 +49815,12 @@
       <c r="AD493" s="3" t="n">
         <v>0.001135073779795641</v>
       </c>
+      <c r="AE493" s="1" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="AF493" s="3" t="n">
+        <v>0.0005668934240362581</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -46951,6 +49915,12 @@
       <c r="AD494" s="3" t="n">
         <v>0.003531489111241763</v>
       </c>
+      <c r="AE494" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="AF494" s="2" t="n">
+        <v>-0.004105571847507368</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -47045,6 +50015,12 @@
       <c r="AD495" s="3" t="n">
         <v>0.004675876726886248</v>
       </c>
+      <c r="AE495" s="1" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="AF495" s="3" t="n">
+        <v>0.0002115506663846639</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -47139,6 +50115,12 @@
       <c r="AD496" s="3" t="n">
         <v>0.002481902792140684</v>
       </c>
+      <c r="AE496" s="1" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="AF496" s="2" t="n">
+        <v>-0.0006189395502373066</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -47233,6 +50215,12 @@
       <c r="AD497" s="3" t="n">
         <v>0.005449041372351289</v>
       </c>
+      <c r="AE497" s="1" t="n">
+        <v>0.04979</v>
+      </c>
+      <c r="AF497" s="2" t="n">
+        <v>-0.0006021678040947861</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -47327,6 +50315,12 @@
       <c r="AD498" s="3" t="n">
         <v>0.004509191814082634</v>
       </c>
+      <c r="AE498" s="1" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="AF498" s="2" t="n">
+        <v>-0.0003453038674034685</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -47421,6 +50415,12 @@
       <c r="AD499" s="3" t="n">
         <v>0.002555677254472559</v>
       </c>
+      <c r="AE499" s="1" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="AF499" s="3" t="n">
+        <v>0.0003641660597231937</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -47515,6 +50515,12 @@
       <c r="AD500" s="3" t="n">
         <v>0.003759398496240611</v>
       </c>
+      <c r="AE500" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="AF500" s="3" t="n">
+        <v>0.003745318352059935</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -47609,6 +50615,12 @@
       <c r="AD501" s="3" t="n">
         <v>0.001957494407158854</v>
       </c>
+      <c r="AE501" s="1" t="n">
+        <v>0.03586</v>
+      </c>
+      <c r="AF501" s="3" t="n">
+        <v>0.0008372871895060632</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -47703,6 +50715,12 @@
       <c r="AD502" s="3" t="n">
         <v>0.0003138731952292236</v>
       </c>
+      <c r="AE502" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="AF502" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -47797,6 +50815,12 @@
       <c r="AD503" s="3" t="n">
         <v>0.007246376811594267</v>
       </c>
+      <c r="AE503" s="1" t="n">
+        <v>0.007818</v>
+      </c>
+      <c r="AF503" s="3" t="n">
+        <v>0.004367934224049354</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -47891,6 +50915,12 @@
       <c r="AD504" s="3" t="n">
         <v>0.000328731097961977</v>
       </c>
+      <c r="AE504" s="1" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="AF504" s="2" t="n">
+        <v>-0.003943476832073614</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -47985,6 +51015,12 @@
       <c r="AD505" s="3" t="n">
         <v>0.004321404456448451</v>
       </c>
+      <c r="AE505" s="1" t="n">
+        <v>0.0007446</v>
+      </c>
+      <c r="AF505" s="3" t="n">
+        <v>0.001210165389269823</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -48079,6 +51115,12 @@
       <c r="AD506" s="2" t="n">
         <v>-0.0003423485107841304</v>
       </c>
+      <c r="AE506" s="1" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="AF506" s="2" t="n">
+        <v>-0.001369863013698479</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -48173,6 +51215,12 @@
       <c r="AD507" s="3" t="n">
         <v>0.009500351864883926</v>
       </c>
+      <c r="AE507" s="1" t="n">
+        <v>0.002863</v>
+      </c>
+      <c r="AF507" s="2" t="n">
+        <v>-0.002091321017776204</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -48267,6 +51315,12 @@
       <c r="AD508" s="3" t="n">
         <v>0.005076142131979709</v>
       </c>
+      <c r="AE508" s="1" t="n">
+        <v>0.06333</v>
+      </c>
+      <c r="AF508" s="2" t="n">
+        <v>-0.000473484848484884</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -48361,6 +51415,12 @@
       <c r="AD509" s="3" t="n">
         <v>0.004480286738351159</v>
       </c>
+      <c r="AE509" s="1" t="n">
+        <v>2.234</v>
+      </c>
+      <c r="AF509" s="2" t="n">
+        <v>-0.003568242640499557</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -48455,6 +51515,12 @@
       <c r="AD510" s="3" t="n">
         <v>0.007396247089439834</v>
       </c>
+      <c r="AE510" s="1" t="n">
+        <v>0.0007351</v>
+      </c>
+      <c r="AF510" s="2" t="n">
+        <v>-0.0005438477226376746</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -48549,6 +51615,12 @@
       <c r="AD511" s="3" t="n">
         <v>0.003267973856209194</v>
       </c>
+      <c r="AE511" s="1" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="AF511" s="2" t="n">
+        <v>-0.002895403546869227</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -48643,6 +51715,12 @@
       <c r="AD512" s="3" t="n">
         <v>0.006462372316030897</v>
       </c>
+      <c r="AE512" s="1" t="n">
+        <v>0.0004829</v>
+      </c>
+      <c r="AF512" s="3" t="n">
+        <v>0.0002071251035624445</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -48737,6 +51815,12 @@
       <c r="AD513" s="2" t="n">
         <v>-0.0009010632546403765</v>
       </c>
+      <c r="AE513" s="1" t="n">
+        <v>0.05542</v>
+      </c>
+      <c r="AF513" s="2" t="n">
+        <v>-0.0003607503607504712</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -48831,6 +51915,12 @@
       <c r="AD514" s="3" t="n">
         <v>0.001978239366963436</v>
       </c>
+      <c r="AE514" s="1" t="n">
+        <v>0.03036</v>
+      </c>
+      <c r="AF514" s="2" t="n">
+        <v>-0.0009871668311944317</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -48925,6 +52015,12 @@
       <c r="AD515" s="3" t="n">
         <v>0.002638522427440602</v>
       </c>
+      <c r="AE515" s="1" t="n">
+        <v>0.001139</v>
+      </c>
+      <c r="AF515" s="2" t="n">
+        <v>-0.0008771929824560666</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -49019,6 +52115,12 @@
       <c r="AD516" s="3" t="n">
         <v>0.006969696969696975</v>
       </c>
+      <c r="AE516" s="1" t="n">
+        <v>0.006652</v>
+      </c>
+      <c r="AF516" s="3" t="n">
+        <v>0.0009027986758952647</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -49113,6 +52215,12 @@
       <c r="AD517" s="3" t="n">
         <v>0.003522898842476126</v>
       </c>
+      <c r="AE517" s="1" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="AF517" s="2" t="n">
+        <v>-0.0002507522567702137</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -49207,6 +52315,12 @@
       <c r="AD518" s="3" t="n">
         <v>0.005825242718446634</v>
       </c>
+      <c r="AE518" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="AF518" s="2" t="n">
+        <v>-0.0009652509652509929</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -49301,6 +52415,12 @@
       <c r="AD519" s="3" t="n">
         <v>0.005733944954128405</v>
       </c>
+      <c r="AE519" s="1" t="n">
+        <v>0.00873</v>
+      </c>
+      <c r="AF519" s="2" t="n">
+        <v>-0.004561003420752578</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -49395,6 +52515,12 @@
       <c r="AD520" s="3" t="n">
         <v>0.005642633228840026</v>
       </c>
+      <c r="AE520" s="1" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="AF520" s="3" t="n">
+        <v>0.0006234413965088326</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -49489,6 +52615,12 @@
       <c r="AD521" s="3" t="n">
         <v>0.001679731243001051</v>
       </c>
+      <c r="AE521" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="AF521" s="2" t="n">
+        <v>-0.002235885969815448</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -49583,6 +52715,12 @@
       <c r="AD522" s="3" t="n">
         <v>0.006727828746177308</v>
       </c>
+      <c r="AE522" s="1" t="n">
+        <v>0.01646</v>
+      </c>
+      <c r="AF522" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -49677,6 +52815,12 @@
       <c r="AD523" s="2" t="n">
         <v>-0.001677852348993303</v>
       </c>
+      <c r="AE523" s="1" t="n">
+        <v>0.004162</v>
+      </c>
+      <c r="AF523" s="2" t="n">
+        <v>-0.000720288115246194</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -49771,6 +52915,12 @@
       <c r="AD524" s="3" t="n">
         <v>0.003513703443429354</v>
       </c>
+      <c r="AE524" s="1" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="AF524" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -49865,6 +53015,12 @@
       <c r="AD525" s="3" t="n">
         <v>0.003657049979683048</v>
       </c>
+      <c r="AE525" s="1" t="n">
+        <v>0.02478</v>
+      </c>
+      <c r="AF525" s="3" t="n">
+        <v>0.003238866396761142</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -49959,6 +53115,12 @@
       <c r="AD526" s="3" t="n">
         <v>0.004166666666666671</v>
       </c>
+      <c r="AE526" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="AF526" s="2" t="n">
+        <v>-0.000829875518672223</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -50053,6 +53215,12 @@
       <c r="AD527" s="3" t="n">
         <v>0.001669449081802937</v>
       </c>
+      <c r="AE527" s="1" t="n">
+        <v>0.07208000000000001</v>
+      </c>
+      <c r="AF527" s="3" t="n">
+        <v>0.001111111111111259</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -50147,6 +53315,12 @@
       <c r="AD528" s="3" t="n">
         <v>0.003704561241028026</v>
       </c>
+      <c r="AE528" s="1" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AF528" s="3" t="n">
+        <v>0.0002306805074971871</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -50241,6 +53415,12 @@
       <c r="AD529" s="3" t="n">
         <v>0.001109526073862746</v>
       </c>
+      <c r="AE529" s="1" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="AF529" s="2" t="n">
+        <v>-0.001108296390120339</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -50335,6 +53515,12 @@
       <c r="AD530" s="3" t="n">
         <v>0.001790332206087022</v>
       </c>
+      <c r="AE530" s="1" t="n">
+        <v>0.005029</v>
+      </c>
+      <c r="AF530" s="2" t="n">
+        <v>-0.001389992057188257</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -50429,6 +53615,12 @@
       <c r="AD531" s="3" t="n">
         <v>0.004629629629629762</v>
       </c>
+      <c r="AE531" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AF531" s="2" t="n">
+        <v>-0.001536098310291902</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -50523,6 +53715,12 @@
       <c r="AD532" s="3" t="n">
         <v>0.0001881467544684125</v>
       </c>
+      <c r="AE532" s="1" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="AF532" s="3" t="n">
+        <v>0.007900677200903004</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -50617,6 +53815,12 @@
       <c r="AD533" s="3" t="n">
         <v>0.001878186208746998</v>
       </c>
+      <c r="AE533" s="1" t="n">
+        <v>0.003746</v>
+      </c>
+      <c r="AF533" s="3" t="n">
+        <v>0.003213711837172012</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -50711,6 +53915,12 @@
       <c r="AD534" s="3" t="n">
         <v>0.004084014002333759</v>
       </c>
+      <c r="AE534" s="1" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="AF534" s="2" t="n">
+        <v>-0.001743172574084804</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -50805,6 +54015,12 @@
       <c r="AD535" s="2" t="n">
         <v>-0.00884955752212396</v>
       </c>
+      <c r="AE535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AF535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -50899,6 +54115,12 @@
       <c r="AD536" s="2" t="n">
         <v>-0.001131990038487689</v>
       </c>
+      <c r="AE536" s="1" t="n">
+        <v>0.0004413</v>
+      </c>
+      <c r="AF536" s="3" t="n">
+        <v>0.0002266545784224896</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -50993,6 +54215,12 @@
       <c r="AD537" s="3" t="n">
         <v>0.008333333333333356</v>
       </c>
+      <c r="AE537" s="1" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="AF537" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -51087,6 +54315,12 @@
       <c r="AD538" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AE538" s="1" t="n">
+        <v>0.05457</v>
+      </c>
+      <c r="AF538" s="3" t="n">
+        <v>0.0003666361136571803</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -51181,6 +54415,12 @@
       <c r="AD539" s="3" t="n">
         <v>0.003828032979976348</v>
       </c>
+      <c r="AE539" s="1" t="n">
+        <v>0.6817</v>
+      </c>
+      <c r="AF539" s="2" t="n">
+        <v>-0.0001466705778820607</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -51275,6 +54515,12 @@
       <c r="AD540" s="3" t="n">
         <v>0.001986754966887382</v>
       </c>
+      <c r="AE540" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AF540" s="2" t="n">
+        <v>-0.001982815598149337</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -51369,6 +54615,12 @@
       <c r="AD541" s="3" t="n">
         <v>0.003072196620583725</v>
       </c>
+      <c r="AE541" s="1" t="n">
+        <v>0.01303</v>
+      </c>
+      <c r="AF541" s="2" t="n">
+        <v>-0.00229709035222056</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -51463,6 +54715,12 @@
       <c r="AD542" s="2" t="n">
         <v>-0.008571428571428594</v>
       </c>
+      <c r="AE542" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="AF542" s="3" t="n">
+        <v>0.002881844380403466</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -51556,6 +54814,12 @@
       </c>
       <c r="AD543" s="3" t="n">
         <v>0.0008770391159445963</v>
+      </c>
+      <c r="AE543" s="1" t="n">
+        <v>0.05715</v>
+      </c>
+      <c r="AF543" s="3" t="n">
+        <v>0.001577287066246053</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL543"/>
+  <dimension ref="A1:AN543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -464,6 +464,8 @@
     <col width="18" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,6 +659,16 @@
           <t>change_04:30</t>
         </is>
       </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>price_04:45</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>change_04:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -775,6 +787,12 @@
       <c r="AL2" s="2" t="n">
         <v>-0.001084620283394405</v>
       </c>
+      <c r="AM2" s="1" t="n">
+        <v>70102.89999999999</v>
+      </c>
+      <c r="AN2" s="2" t="n">
+        <v>-0.002390747805990816</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -893,6 +911,12 @@
       <c r="AL3" s="2" t="n">
         <v>-5.808325266209625e-05</v>
       </c>
+      <c r="AM3" s="1" t="n">
+        <v>2060.31</v>
+      </c>
+      <c r="AN3" s="2" t="n">
+        <v>-0.002696187581079329</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1011,6 +1035,12 @@
       <c r="AL4" s="2" t="n">
         <v>-0.0001154068090017901</v>
       </c>
+      <c r="AM4" s="1" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="AN4" s="2" t="n">
+        <v>-0.002539242843951972</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1129,6 +1159,12 @@
       <c r="AL5" s="3" t="n">
         <v>0.01174480879451284</v>
       </c>
+      <c r="AM5" s="1" t="n">
+        <v>0.010671</v>
+      </c>
+      <c r="AN5" s="2" t="n">
+        <v>-0.009008172362555708</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1247,6 +1283,12 @@
       <c r="AL6" s="2" t="n">
         <v>-0.0008004074801717971</v>
       </c>
+      <c r="AM6" s="1" t="n">
+        <v>1.3716</v>
+      </c>
+      <c r="AN6" s="2" t="n">
+        <v>-0.001165161666181216</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1365,6 +1407,12 @@
       <c r="AL7" s="2" t="n">
         <v>-0.002649708532061475</v>
       </c>
+      <c r="AM7" s="1" t="n">
+        <v>0.09425</v>
+      </c>
+      <c r="AN7" s="3" t="n">
+        <v>0.001594048884165753</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1483,6 +1531,12 @@
       <c r="AL8" s="2" t="n">
         <v>-0.0001353876147408804</v>
       </c>
+      <c r="AM8" s="1" t="n">
+        <v>36.975</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>0.001326978280886083</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1601,6 +1655,12 @@
       <c r="AL9" s="3" t="n">
         <v>0.005472233481961884</v>
       </c>
+      <c r="AM9" s="1" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="AN9" s="2" t="n">
+        <v>-0.005039306591413026</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1719,6 +1779,12 @@
       <c r="AL10" s="3" t="n">
         <v>0.006653940550859007</v>
       </c>
+      <c r="AM10" s="1" t="n">
+        <v>18.207</v>
+      </c>
+      <c r="AN10" s="2" t="n">
+        <v>-0.01354499647830091</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1837,6 +1903,12 @@
       <c r="AL11" s="2" t="n">
         <v>-0.000845347514678237</v>
       </c>
+      <c r="AM11" s="1" t="n">
+        <v>649.37</v>
+      </c>
+      <c r="AN11" s="2" t="n">
+        <v>-0.0010768071130802</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1955,6 +2027,12 @@
       <c r="AL12" s="2" t="n">
         <v>-0.00684700864294533</v>
       </c>
+      <c r="AM12" s="1" t="n">
+        <v>0.8786</v>
+      </c>
+      <c r="AN12" s="2" t="n">
+        <v>-0.007007233273056039</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2073,6 +2151,12 @@
       <c r="AL13" s="2" t="n">
         <v>-0.002499759638496348</v>
       </c>
+      <c r="AM13" s="1" t="n">
+        <v>207.58</v>
+      </c>
+      <c r="AN13" s="3" t="n">
+        <v>0.0003855421686747591</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2191,6 +2275,12 @@
       <c r="AL14" s="2" t="n">
         <v>-0.003437658804890381</v>
       </c>
+      <c r="AM14" s="1" t="n">
+        <v>0.0033262</v>
+      </c>
+      <c r="AN14" s="2" t="n">
+        <v>-0.002279680844681735</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2309,6 +2399,12 @@
       <c r="AL15" s="3" t="n">
         <v>0.01438311385075189</v>
       </c>
+      <c r="AM15" s="1" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AN15" s="3" t="n">
+        <v>0.007181659147408185</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2427,6 +2523,12 @@
       <c r="AL16" s="2" t="n">
         <v>-0.001537200245951984</v>
       </c>
+      <c r="AM16" s="1" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="AN16" s="2" t="n">
+        <v>-0.0008211023298778845</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2545,6 +2647,12 @@
       <c r="AL17" s="3" t="n">
         <v>0.01140684410646381</v>
       </c>
+      <c r="AM17" s="1" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="AN17" s="2" t="n">
+        <v>-0.007518796992481157</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2663,6 +2771,12 @@
       <c r="AL18" s="2" t="n">
         <v>-0.0004678362573099149</v>
       </c>
+      <c r="AM18" s="1" t="n">
+        <v>213.07</v>
+      </c>
+      <c r="AN18" s="2" t="n">
+        <v>-0.002714720336999825</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2781,6 +2895,12 @@
       <c r="AL19" s="2" t="n">
         <v>-0.001904761904761906</v>
       </c>
+      <c r="AM19" s="1" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="AN19" s="2" t="n">
+        <v>-0.000381679389312935</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2899,6 +3019,12 @@
       <c r="AL20" s="2" t="n">
         <v>-0.003293923886830012</v>
       </c>
+      <c r="AM20" s="1" t="n">
+        <v>0.016909</v>
+      </c>
+      <c r="AN20" s="2" t="n">
+        <v>-0.00212452050752442</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3017,6 +3143,12 @@
       <c r="AL21" s="3" t="n">
         <v>0.0006251302354655606</v>
       </c>
+      <c r="AM21" s="1" t="n">
+        <v>9.601000000000001</v>
+      </c>
+      <c r="AN21" s="2" t="n">
+        <v>-0.0003123698458973696</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3135,6 +3267,12 @@
       <c r="AL22" s="2" t="n">
         <v>-0.001797483523067674</v>
       </c>
+      <c r="AM22" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="AN22" s="2" t="n">
+        <v>-0.007803121248499374</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3253,6 +3391,12 @@
       <c r="AL23" s="3" t="n">
         <v>0.003831196888952896</v>
       </c>
+      <c r="AM23" s="1" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AN23" s="2" t="n">
+        <v>-0.001520890725436267</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3371,6 +3515,12 @@
       <c r="AL24" s="2" t="n">
         <v>-0.002312138728323701</v>
       </c>
+      <c r="AM24" s="1" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="AN24" s="3" t="n">
+        <v>0.001158748551564312</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3489,6 +3639,12 @@
       <c r="AL25" s="2" t="n">
         <v>-0.001333333333333384</v>
       </c>
+      <c r="AM25" s="1" t="n">
+        <v>8.974</v>
+      </c>
+      <c r="AN25" s="2" t="n">
+        <v>-0.001557632398753821</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3607,6 +3763,12 @@
       <c r="AL26" s="2" t="n">
         <v>-0.003009781790820168</v>
       </c>
+      <c r="AM26" s="1" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="AN26" s="3" t="n">
+        <v>0.003018867924528305</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3725,6 +3887,12 @@
       <c r="AL27" s="2" t="n">
         <v>-0.002057617208591037</v>
       </c>
+      <c r="AM27" s="1" t="n">
+        <v>5082.99</v>
+      </c>
+      <c r="AN27" s="3" t="n">
+        <v>3.934846806573124e-05</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3843,6 +4011,12 @@
       <c r="AL28" s="2" t="n">
         <v>-0.006688963210702377</v>
       </c>
+      <c r="AM28" s="1" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="AN28" s="3" t="n">
+        <v>0.002244668911335642</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3961,6 +4135,12 @@
       <c r="AL29" s="2" t="n">
         <v>-0.0003793626707133285</v>
       </c>
+      <c r="AM29" s="1" t="n">
+        <v>2.643</v>
+      </c>
+      <c r="AN29" s="3" t="n">
+        <v>0.003036053130929794</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4079,6 +4259,12 @@
       <c r="AL30" s="3" t="n">
         <v>0.007591057873110994</v>
       </c>
+      <c r="AM30" s="1" t="n">
+        <v>0.5704900000000001</v>
+      </c>
+      <c r="AN30" s="2" t="n">
+        <v>-0.01422103953552661</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4197,6 +4383,12 @@
       <c r="AL31" s="2" t="n">
         <v>-0.003362151777137397</v>
       </c>
+      <c r="AM31" s="1" t="n">
+        <v>0.002077</v>
+      </c>
+      <c r="AN31" s="3" t="n">
+        <v>0.000963855421686666</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4315,6 +4507,12 @@
       <c r="AL32" s="3" t="n">
         <v>0.001008533747090829</v>
       </c>
+      <c r="AM32" s="1" t="n">
+        <v>1.2961</v>
+      </c>
+      <c r="AN32" s="3" t="n">
+        <v>0.004495078663876639</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4433,6 +4631,12 @@
       <c r="AL33" s="2" t="n">
         <v>-0.00208457415128046</v>
       </c>
+      <c r="AM33" s="1" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AN33" s="2" t="n">
+        <v>-0.0002984183825723336</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4551,6 +4755,12 @@
       <c r="AL34" s="2" t="n">
         <v>-0.001327140013271401</v>
       </c>
+      <c r="AM34" s="1" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="AN34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4669,6 +4879,12 @@
       <c r="AL35" s="2" t="n">
         <v>-0.001099964801126364</v>
       </c>
+      <c r="AM35" s="1" t="n">
+        <v>454.04</v>
+      </c>
+      <c r="AN35" s="2" t="n">
+        <v>-4.404704224107345e-05</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4787,6 +5003,12 @@
       <c r="AL36" s="2" t="n">
         <v>-0.003363464368299357</v>
       </c>
+      <c r="AM36" s="1" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="AN36" s="2" t="n">
+        <v>-0.001898333684876604</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4905,6 +5127,12 @@
       <c r="AL37" s="3" t="n">
         <v>0.0005711022272986236</v>
       </c>
+      <c r="AM37" s="1" t="n">
+        <v>0.7000999999999999</v>
+      </c>
+      <c r="AN37" s="2" t="n">
+        <v>-0.000998858447488633</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5023,6 +5251,12 @@
       <c r="AL38" s="2" t="n">
         <v>-0.00378071833648404</v>
       </c>
+      <c r="AM38" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5141,6 +5375,12 @@
       <c r="AL39" s="2" t="n">
         <v>-0.0008983918785374946</v>
       </c>
+      <c r="AM39" s="1" t="n">
+        <v>110.59</v>
+      </c>
+      <c r="AN39" s="2" t="n">
+        <v>-0.005575038215987684</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5259,6 +5499,12 @@
       <c r="AL40" s="3" t="n">
         <v>0.00246778173841513</v>
       </c>
+      <c r="AM40" s="1" t="n">
+        <v>0.03612</v>
+      </c>
+      <c r="AN40" s="2" t="n">
+        <v>-0.01203501094091912</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5377,6 +5623,12 @@
       <c r="AL41" s="3" t="n">
         <v>0.004750593824227962</v>
       </c>
+      <c r="AM41" s="1" t="n">
+        <v>0.05492</v>
+      </c>
+      <c r="AN41" s="2" t="n">
+        <v>-0.001272958719767242</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5495,6 +5747,12 @@
       <c r="AL42" s="2" t="n">
         <v>-0.002399852316780553</v>
       </c>
+      <c r="AM42" s="1" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="AN42" s="3" t="n">
+        <v>0.001295336787564772</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5613,6 +5871,12 @@
       <c r="AL43" s="3" t="n">
         <v>0.004559270516717456</v>
       </c>
+      <c r="AM43" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="AN43" s="2" t="n">
+        <v>-0.005295007564296567</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5731,6 +5995,12 @@
       <c r="AL44" s="2" t="n">
         <v>-0.004902789518174197</v>
       </c>
+      <c r="AM44" s="1" t="n">
+        <v>0.005871</v>
+      </c>
+      <c r="AN44" s="2" t="n">
+        <v>-0.002548419979612537</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5849,6 +6119,12 @@
       <c r="AL45" s="3" t="n">
         <v>0.0007019655034095529</v>
       </c>
+      <c r="AM45" s="1" t="n">
+        <v>0.09961</v>
+      </c>
+      <c r="AN45" s="2" t="n">
+        <v>-0.001803787954704876</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5967,6 +6243,12 @@
       <c r="AL46" s="2" t="n">
         <v>-0.01661016949152555</v>
       </c>
+      <c r="AM46" s="1" t="n">
+        <v>2.894</v>
+      </c>
+      <c r="AN46" s="2" t="n">
+        <v>-0.0024129610479144</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6085,6 +6367,12 @@
       <c r="AL47" s="3" t="n">
         <v>0.0003117746908235511</v>
       </c>
+      <c r="AM47" s="1" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="AN47" s="2" t="n">
+        <v>-0.0001038925058873459</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6203,6 +6491,12 @@
       <c r="AL48" s="3" t="n">
         <v>0.00380228136882127</v>
       </c>
+      <c r="AM48" s="1" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="AN48" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6321,6 +6615,12 @@
       <c r="AL49" s="2" t="n">
         <v>-0.002007045138035514</v>
       </c>
+      <c r="AM49" s="1" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AN49" s="2" t="n">
+        <v>-0.001559614200697801</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6439,6 +6739,12 @@
       <c r="AL50" s="3" t="n">
         <v>0.002493247454809932</v>
       </c>
+      <c r="AM50" s="1" t="n">
+        <v>0.04817</v>
+      </c>
+      <c r="AN50" s="2" t="n">
+        <v>-0.001658031088082978</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6557,6 +6863,12 @@
       <c r="AL51" s="2" t="n">
         <v>-0.00153806716226603</v>
       </c>
+      <c r="AM51" s="1" t="n">
+        <v>3.889</v>
+      </c>
+      <c r="AN51" s="2" t="n">
+        <v>-0.001540436456996207</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6675,6 +6987,12 @@
       <c r="AL52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM52" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AN52" s="3" t="n">
+        <v>0.004405286343612442</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6793,6 +7111,12 @@
       <c r="AL53" s="2" t="n">
         <v>-0.004146919431279658</v>
       </c>
+      <c r="AM53" s="1" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="AN53" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6911,6 +7235,12 @@
       <c r="AL54" s="2" t="n">
         <v>-0.003597985128328073</v>
       </c>
+      <c r="AM54" s="1" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="AN54" s="2" t="n">
+        <v>-0.00216658642272508</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7029,6 +7359,12 @@
       <c r="AL55" s="2" t="n">
         <v>-0.001456546366726004</v>
       </c>
+      <c r="AM55" s="1" t="n">
+        <v>0.12284</v>
+      </c>
+      <c r="AN55" s="2" t="n">
+        <v>-0.004538087520259247</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7147,6 +7483,12 @@
       <c r="AL56" s="2" t="n">
         <v>-0.006995230524642225</v>
       </c>
+      <c r="AM56" s="1" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AN56" s="3" t="n">
+        <v>0.0016010246557797</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7265,6 +7607,12 @@
       <c r="AL57" s="2" t="n">
         <v>-0.001739130434782538</v>
       </c>
+      <c r="AM57" s="1" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="AN57" s="2" t="n">
+        <v>-0.0008710801393729379</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7383,6 +7731,12 @@
       <c r="AL58" s="2" t="n">
         <v>-0.003006012024048043</v>
       </c>
+      <c r="AM58" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="AN58" s="3" t="n">
+        <v>0.00100502512562803</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7501,6 +7855,12 @@
       <c r="AL59" s="2" t="n">
         <v>-0.003012048192771092</v>
       </c>
+      <c r="AM59" s="1" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="AN59" s="3" t="n">
+        <v>0.006042296072507568</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7619,6 +7979,12 @@
       <c r="AL60" s="2" t="n">
         <v>-0.005157962604771084</v>
       </c>
+      <c r="AM60" s="1" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="AN60" s="3" t="n">
+        <v>0.00194426441996108</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7737,6 +8103,12 @@
       <c r="AL61" s="2" t="n">
         <v>-0.002630260521041934</v>
       </c>
+      <c r="AM61" s="1" t="n">
+        <v>0.15925</v>
+      </c>
+      <c r="AN61" s="2" t="n">
+        <v>-6.279040562608314e-05</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7855,6 +8227,12 @@
       <c r="AL62" s="2" t="n">
         <v>-0.004798193621224892</v>
       </c>
+      <c r="AM62" s="1" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="AN62" s="3" t="n">
+        <v>0.002410663641520028</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7973,6 +8351,12 @@
       <c r="AL63" s="2" t="n">
         <v>-0.0001647989452866588</v>
       </c>
+      <c r="AM63" s="1" t="n">
+        <v>6.032</v>
+      </c>
+      <c r="AN63" s="2" t="n">
+        <v>-0.005768913795945301</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8091,6 +8475,12 @@
       <c r="AL64" s="2" t="n">
         <v>-0.004587793688308084</v>
       </c>
+      <c r="AM64" s="1" t="n">
+        <v>0.007155</v>
+      </c>
+      <c r="AN64" s="2" t="n">
+        <v>-0.0006983240223463403</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8209,6 +8599,12 @@
       <c r="AL65" s="3" t="n">
         <v>0.006853582554517288</v>
       </c>
+      <c r="AM65" s="1" t="n">
+        <v>0.03229</v>
+      </c>
+      <c r="AN65" s="2" t="n">
+        <v>-0.0009282178217822477</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8327,6 +8723,12 @@
       <c r="AL66" s="2" t="n">
         <v>-0.004273504273504277</v>
       </c>
+      <c r="AM66" s="1" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="AN66" s="2" t="n">
+        <v>-0.004291845493562235</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8445,6 +8847,12 @@
       <c r="AL67" s="2" t="n">
         <v>-0.003683241252302029</v>
       </c>
+      <c r="AM67" s="1" t="n">
+        <v>1.626</v>
+      </c>
+      <c r="AN67" s="3" t="n">
+        <v>0.001848428835489767</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8563,6 +8971,12 @@
       <c r="AL68" s="3" t="n">
         <v>0.002174772637406069</v>
       </c>
+      <c r="AM68" s="1" t="n">
+        <v>2.0339</v>
+      </c>
+      <c r="AN68" s="3" t="n">
+        <v>0.003107121720260393</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8681,6 +9095,12 @@
       <c r="AL69" s="3" t="n">
         <v>0.001529311809685662</v>
       </c>
+      <c r="AM69" s="1" t="n">
+        <v>0.5893</v>
+      </c>
+      <c r="AN69" s="2" t="n">
+        <v>-0.0001696640651509823</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8799,6 +9219,12 @@
       <c r="AL70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AN70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8917,6 +9343,12 @@
       <c r="AL71" s="2" t="n">
         <v>-0.002863751514484025</v>
       </c>
+      <c r="AM71" s="1" t="n">
+        <v>0.9054</v>
+      </c>
+      <c r="AN71" s="3" t="n">
+        <v>0.0001104606207886767</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9035,6 +9467,12 @@
       <c r="AL72" s="3" t="n">
         <v>0.01149694978883144</v>
       </c>
+      <c r="AM72" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN72" s="2" t="n">
+        <v>-0.002551612154952424</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9153,6 +9591,12 @@
       <c r="AL73" s="2" t="n">
         <v>-0.00233545647558399</v>
       </c>
+      <c r="AM73" s="1" t="n">
+        <v>0.09397999999999999</v>
+      </c>
+      <c r="AN73" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9271,6 +9715,12 @@
       <c r="AL74" s="3" t="n">
         <v>0.003930817610062848</v>
       </c>
+      <c r="AM74" s="1" t="n">
+        <v>1.1526</v>
+      </c>
+      <c r="AN74" s="3" t="n">
+        <v>0.00287131297311414</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9389,6 +9839,12 @@
       <c r="AL75" s="3" t="n">
         <v>0.002503128911138821</v>
       </c>
+      <c r="AM75" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="AN75" s="3" t="n">
+        <v>0.001248439450686591</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9507,6 +9963,12 @@
       <c r="AL76" s="2" t="n">
         <v>-0.003223939819789928</v>
       </c>
+      <c r="AM76" s="1" t="n">
+        <v>0.12155</v>
+      </c>
+      <c r="AN76" s="3" t="n">
+        <v>0.008044451816221584</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9625,6 +10087,12 @@
       <c r="AL77" s="2" t="n">
         <v>-0.005897219882055655</v>
       </c>
+      <c r="AM77" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="AN77" s="2" t="n">
+        <v>-0.0008474576271185508</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9743,6 +10211,12 @@
       <c r="AL78" s="2" t="n">
         <v>-0.003940886699507502</v>
       </c>
+      <c r="AM78" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AN78" s="2" t="n">
+        <v>-0.0009891196834815924</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9861,6 +10335,12 @@
       <c r="AL79" s="2" t="n">
         <v>-0.005128205128205092</v>
       </c>
+      <c r="AM79" s="1" t="n">
+        <v>0.006023</v>
+      </c>
+      <c r="AN79" s="3" t="n">
+        <v>0.001496508147655381</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9979,6 +10459,12 @@
       <c r="AL80" s="2" t="n">
         <v>-0.002806838479203808</v>
       </c>
+      <c r="AM80" s="1" t="n">
+        <v>0.007782</v>
+      </c>
+      <c r="AN80" s="2" t="n">
+        <v>-0.004350051177072694</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10097,6 +10583,12 @@
       <c r="AL81" s="2" t="n">
         <v>-0.003910614525139681</v>
       </c>
+      <c r="AM81" s="1" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="AN81" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10215,6 +10707,12 @@
       <c r="AL82" s="3" t="n">
         <v>0.006097560975609762</v>
       </c>
+      <c r="AM82" s="1" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="AN82" s="3" t="n">
+        <v>0.01393939393939392</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10333,6 +10831,12 @@
       <c r="AL83" s="2" t="n">
         <v>-0.0006076072426782119</v>
       </c>
+      <c r="AM83" s="1" t="n">
+        <v>8.228999999999999</v>
+      </c>
+      <c r="AN83" s="3" t="n">
+        <v>0.0006079766536963771</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10451,6 +10955,12 @@
       <c r="AL84" s="3" t="n">
         <v>0.0006812182452953623</v>
       </c>
+      <c r="AM84" s="1" t="n">
+        <v>351.18</v>
+      </c>
+      <c r="AN84" s="2" t="n">
+        <v>-0.003885973620763025</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10569,6 +11079,12 @@
       <c r="AL85" s="2" t="n">
         <v>-0.00196608503317752</v>
       </c>
+      <c r="AM85" s="1" t="n">
+        <v>0.004045</v>
+      </c>
+      <c r="AN85" s="2" t="n">
+        <v>-0.003939916276779214</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10687,6 +11203,12 @@
       <c r="AL86" s="3" t="n">
         <v>0.00190956309196456</v>
       </c>
+      <c r="AM86" s="1" t="n">
+        <v>0.13101</v>
+      </c>
+      <c r="AN86" s="2" t="n">
+        <v>-0.001219791110772442</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10805,6 +11327,12 @@
       <c r="AL87" s="2" t="n">
         <v>-0.001100715465052239</v>
       </c>
+      <c r="AM87" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="AN87" s="3" t="n">
+        <v>0.004958677685950402</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10923,6 +11451,12 @@
       <c r="AL88" s="2" t="n">
         <v>-0.002654867256637073</v>
       </c>
+      <c r="AM88" s="1" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="AN88" s="3" t="n">
+        <v>0.001774622892635317</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11041,6 +11575,12 @@
       <c r="AL89" s="2" t="n">
         <v>-0.001024940211821054</v>
       </c>
+      <c r="AM89" s="1" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="AN89" s="2" t="n">
+        <v>-0.004445964432284432</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11159,6 +11699,12 @@
       <c r="AL90" s="2" t="n">
         <v>-0.002323780015491826</v>
       </c>
+      <c r="AM90" s="1" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="AN90" s="2" t="n">
+        <v>-0.0003881987577639324</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11277,6 +11823,12 @@
       <c r="AL91" s="3" t="n">
         <v>0.01776103336921429</v>
       </c>
+      <c r="AM91" s="1" t="n">
+        <v>0.05636</v>
+      </c>
+      <c r="AN91" s="2" t="n">
+        <v>-0.006522122333862194</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11395,6 +11947,12 @@
       <c r="AL92" s="2" t="n">
         <v>-0.007785070981529528</v>
       </c>
+      <c r="AM92" s="1" t="n">
+        <v>1.3004</v>
+      </c>
+      <c r="AN92" s="3" t="n">
+        <v>0.0003076923076922738</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11513,6 +12071,12 @@
       <c r="AL93" s="3" t="n">
         <v>0.0006242197253432955</v>
       </c>
+      <c r="AM93" s="1" t="n">
+        <v>0.06383</v>
+      </c>
+      <c r="AN93" s="2" t="n">
+        <v>-0.00452276980661258</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11631,6 +12195,12 @@
       <c r="AL94" s="3" t="n">
         <v>0.002277904328018328</v>
       </c>
+      <c r="AM94" s="1" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="AN94" s="2" t="n">
+        <v>-0.01250000000000008</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11749,6 +12319,12 @@
       <c r="AL95" s="2" t="n">
         <v>-0.0044457617071725</v>
       </c>
+      <c r="AM95" s="1" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AN95" s="3" t="n">
+        <v>0.001786245906519931</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11867,6 +12443,12 @@
       <c r="AL96" s="2" t="n">
         <v>-0.001329198050509472</v>
       </c>
+      <c r="AM96" s="1" t="n">
+        <v>0.02259</v>
+      </c>
+      <c r="AN96" s="3" t="n">
+        <v>0.002218278615794053</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11985,6 +12567,12 @@
       <c r="AL97" s="2" t="n">
         <v>-0.002143294549907936</v>
       </c>
+      <c r="AM97" s="1" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="AN97" s="2" t="n">
+        <v>-0.003988953666769025</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12103,6 +12691,12 @@
       <c r="AL98" s="2" t="n">
         <v>-0.001773049645390073</v>
       </c>
+      <c r="AM98" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN98" s="3" t="n">
+        <v>0.003552397868561282</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12221,6 +12815,12 @@
       <c r="AL99" s="2" t="n">
         <v>-0.00197954470471799</v>
       </c>
+      <c r="AM99" s="1" t="n">
+        <v>3.028</v>
+      </c>
+      <c r="AN99" s="3" t="n">
+        <v>0.0009917355371901202</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12339,6 +12939,12 @@
       <c r="AL100" s="2" t="n">
         <v>-0.001172332942555638</v>
       </c>
+      <c r="AM100" s="1" t="n">
+        <v>0.03402</v>
+      </c>
+      <c r="AN100" s="2" t="n">
+        <v>-0.001760563380281618</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12457,6 +13063,12 @@
       <c r="AL101" s="2" t="n">
         <v>-0.0005479452054793917</v>
       </c>
+      <c r="AM101" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="AN101" s="3" t="n">
+        <v>0.001096491228070176</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12575,6 +13187,12 @@
       <c r="AL102" s="3" t="n">
         <v>0.003975014196479308</v>
       </c>
+      <c r="AM102" s="1" t="n">
+        <v>0.007084</v>
+      </c>
+      <c r="AN102" s="3" t="n">
+        <v>0.0016968325791855</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12693,6 +13311,12 @@
       <c r="AL103" s="2" t="n">
         <v>-0.001375095492742443</v>
       </c>
+      <c r="AM103" s="1" t="n">
+        <v>0.06499000000000001</v>
+      </c>
+      <c r="AN103" s="2" t="n">
+        <v>-0.005660954712362229</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12811,6 +13435,12 @@
       <c r="AL104" s="3" t="n">
         <v>0.003654970760233921</v>
       </c>
+      <c r="AM104" s="1" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="AN104" s="3" t="n">
+        <v>0.00315610585093475</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12929,6 +13559,12 @@
       <c r="AL105" s="3" t="n">
         <v>0.000551267916207216</v>
       </c>
+      <c r="AM105" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="AN105" s="3" t="n">
+        <v>0.006060606060606127</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13047,6 +13683,12 @@
       <c r="AL106" s="2" t="n">
         <v>-0.006789524733268731</v>
       </c>
+      <c r="AM106" s="1" t="n">
+        <v>0.008121</v>
+      </c>
+      <c r="AN106" s="2" t="n">
+        <v>-0.008666992187499986</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13165,6 +13807,12 @@
       <c r="AL107" s="2" t="n">
         <v>-0.00927441352973268</v>
       </c>
+      <c r="AM107" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="AN107" s="3" t="n">
+        <v>0.0005506607929515195</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13283,6 +13931,12 @@
       <c r="AL108" s="2" t="n">
         <v>-0.009195402298850519</v>
       </c>
+      <c r="AM108" s="1" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="AN108" s="3" t="n">
+        <v>0.002784222737819073</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13401,6 +14055,12 @@
       <c r="AL109" s="3" t="n">
         <v>0.003779017455461613</v>
       </c>
+      <c r="AM109" s="1" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="AN109" s="2" t="n">
+        <v>-0.00143420580853359</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13519,6 +14179,12 @@
       <c r="AL110" s="2" t="n">
         <v>-0.004076322636600157</v>
       </c>
+      <c r="AM110" s="1" t="n">
+        <v>0.11501</v>
+      </c>
+      <c r="AN110" s="3" t="n">
+        <v>0.001567534616389442</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13637,6 +14303,12 @@
       <c r="AL111" s="2" t="n">
         <v>-0.0004145507306457897</v>
       </c>
+      <c r="AM111" s="1" t="n">
+        <v>0.09607</v>
+      </c>
+      <c r="AN111" s="2" t="n">
+        <v>-0.003939865215137289</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13755,6 +14427,12 @@
       <c r="AL112" s="2" t="n">
         <v>-0.005361930294906134</v>
       </c>
+      <c r="AM112" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="AN112" s="3" t="n">
+        <v>0.002695417789757302</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13873,6 +14551,12 @@
       <c r="AL113" s="2" t="n">
         <v>-0.0008146639511201298</v>
       </c>
+      <c r="AM113" s="1" t="n">
+        <v>0.09818</v>
+      </c>
+      <c r="AN113" s="3" t="n">
+        <v>0.0006114961271912403</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13991,6 +14675,12 @@
       <c r="AL114" s="3" t="n">
         <v>0.002828054298642541</v>
       </c>
+      <c r="AM114" s="1" t="n">
+        <v>0.001771</v>
+      </c>
+      <c r="AN114" s="2" t="n">
+        <v>-0.001128031584884404</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14109,6 +14799,12 @@
       <c r="AL115" s="2" t="n">
         <v>-0.001349527665317167</v>
       </c>
+      <c r="AM115" s="1" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="AN115" s="2" t="n">
+        <v>-0.0007949125596185309</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14227,6 +14923,12 @@
       <c r="AL116" s="2" t="n">
         <v>-0.003803888419273085</v>
       </c>
+      <c r="AM116" s="1" t="n">
+        <v>0.2356</v>
+      </c>
+      <c r="AN116" s="2" t="n">
+        <v>-0.0004242681374628298</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14345,6 +15047,12 @@
       <c r="AL117" s="2" t="n">
         <v>-0.002957121734844745</v>
       </c>
+      <c r="AM117" s="1" t="n">
+        <v>0.06048</v>
+      </c>
+      <c r="AN117" s="2" t="n">
+        <v>-0.003460207612456778</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14463,6 +15171,12 @@
       <c r="AL118" s="3" t="n">
         <v>0.009163802978235913</v>
       </c>
+      <c r="AM118" s="1" t="n">
+        <v>0.04434</v>
+      </c>
+      <c r="AN118" s="3" t="n">
+        <v>0.006583427922814951</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14581,6 +15295,12 @@
       <c r="AL119" s="2" t="n">
         <v>-0.002977801840822882</v>
       </c>
+      <c r="AM119" s="1" t="n">
+        <v>0.003669</v>
+      </c>
+      <c r="AN119" s="2" t="n">
+        <v>-0.003801248981808342</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14699,6 +15419,12 @@
       <c r="AL120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AN120" s="2" t="n">
+        <v>-0.001267427122940432</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14817,6 +15543,12 @@
       <c r="AL121" s="2" t="n">
         <v>-0.002012072434607797</v>
       </c>
+      <c r="AM121" s="1" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AN121" s="2" t="n">
+        <v>-0.001680107526881722</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14935,6 +15667,12 @@
       <c r="AL122" s="2" t="n">
         <v>-0.002812939521800167</v>
       </c>
+      <c r="AM122" s="1" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="AN122" s="2" t="n">
+        <v>-0.001410437235543059</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15053,6 +15791,12 @@
       <c r="AL123" s="3" t="n">
         <v>0.00162068844026357</v>
       </c>
+      <c r="AM123" s="1" t="n">
+        <v>0.02851</v>
+      </c>
+      <c r="AN123" s="3" t="n">
+        <v>0.00284920327834258</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15171,6 +15915,12 @@
       <c r="AL124" s="3" t="n">
         <v>0.001519756838905713</v>
       </c>
+      <c r="AM124" s="1" t="n">
+        <v>0.07853</v>
+      </c>
+      <c r="AN124" s="2" t="n">
+        <v>-0.006954982296408637</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15289,6 +16039,12 @@
       <c r="AL125" s="2" t="n">
         <v>-0.0001889109284972714</v>
       </c>
+      <c r="AM125" s="1" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="AN125" s="2" t="n">
+        <v>-0.005007085498346743</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15407,6 +16163,12 @@
       <c r="AL126" s="2" t="n">
         <v>-0.003393665158371033</v>
       </c>
+      <c r="AM126" s="1" t="n">
+        <v>0.02641</v>
+      </c>
+      <c r="AN126" s="2" t="n">
+        <v>-0.0007567158531970937</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15525,6 +16287,12 @@
       <c r="AL127" s="2" t="n">
         <v>-0.002747252747252636</v>
       </c>
+      <c r="AM127" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="AN127" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15643,6 +16411,12 @@
       <c r="AL128" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM128" s="1" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="AN128" s="2" t="n">
+        <v>-0.0006199628022317979</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15761,6 +16535,12 @@
       <c r="AL129" s="2" t="n">
         <v>-0.004524256977796228</v>
       </c>
+      <c r="AM129" s="1" t="n">
+        <v>0.14379</v>
+      </c>
+      <c r="AN129" s="3" t="n">
+        <v>0.005383862396867521</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15879,6 +16659,12 @@
       <c r="AL130" s="2" t="n">
         <v>-0.007512262948514936</v>
       </c>
+      <c r="AM130" s="1" t="n">
+        <v>0.051567</v>
+      </c>
+      <c r="AN130" s="3" t="n">
+        <v>0.003385675091938601</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15997,6 +16783,12 @@
       <c r="AL131" s="2" t="n">
         <v>-0.001097694840834161</v>
       </c>
+      <c r="AM131" s="1" t="n">
+        <v>0.08196000000000001</v>
+      </c>
+      <c r="AN131" s="3" t="n">
+        <v>0.0007326007326007875</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16115,6 +16907,12 @@
       <c r="AL132" s="2" t="n">
         <v>-0.001136363636363511</v>
       </c>
+      <c r="AM132" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AN132" s="3" t="n">
+        <v>0.001137656427758691</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -16233,6 +17031,12 @@
       <c r="AL133" s="2" t="n">
         <v>-0.002925989672977494</v>
       </c>
+      <c r="AM133" s="1" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="AN133" s="3" t="n">
+        <v>0.0001726221301570671</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16351,6 +17155,12 @@
       <c r="AL134" s="2" t="n">
         <v>-0.0006731740154829749</v>
       </c>
+      <c r="AM134" s="1" t="n">
+        <v>0.02956</v>
+      </c>
+      <c r="AN134" s="2" t="n">
+        <v>-0.004378578646008813</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16469,6 +17279,12 @@
       <c r="AL135" s="2" t="n">
         <v>-0.003438395415472838</v>
       </c>
+      <c r="AM135" s="1" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="AN135" s="3" t="n">
+        <v>0.0005750431282345942</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -16587,6 +17403,12 @@
       <c r="AL136" s="2" t="n">
         <v>-0.004298764105319731</v>
       </c>
+      <c r="AM136" s="1" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="AN136" s="3" t="n">
+        <v>0.002698327037236803</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16705,6 +17527,12 @@
       <c r="AL137" s="2" t="n">
         <v>-0.0003706449221645513</v>
       </c>
+      <c r="AM137" s="1" t="n">
+        <v>0.02701</v>
+      </c>
+      <c r="AN137" s="3" t="n">
+        <v>0.001483129403040355</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16823,6 +17651,12 @@
       <c r="AL138" s="2" t="n">
         <v>-0.005490196078431291</v>
       </c>
+      <c r="AM138" s="1" t="n">
+        <v>2.556</v>
+      </c>
+      <c r="AN138" s="3" t="n">
+        <v>0.00788643533123029</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16941,6 +17775,12 @@
       <c r="AL139" s="3" t="n">
         <v>0.001689189189189267</v>
       </c>
+      <c r="AM139" s="1" t="n">
+        <v>0.01179</v>
+      </c>
+      <c r="AN139" s="2" t="n">
+        <v>-0.005902192242833104</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -17059,6 +17899,12 @@
       <c r="AL140" s="2" t="n">
         <v>-0.00271002710027101</v>
       </c>
+      <c r="AM140" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="AN140" s="2" t="n">
+        <v>-0.0006793478260869289</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -17177,6 +18023,12 @@
       <c r="AL141" s="2" t="n">
         <v>-0.005242059821153305</v>
       </c>
+      <c r="AM141" s="1" t="n">
+        <v>16.167</v>
+      </c>
+      <c r="AN141" s="3" t="n">
+        <v>0.002293862368258065</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -17295,6 +18147,12 @@
       <c r="AL142" s="2" t="n">
         <v>-0.01190476190476197</v>
       </c>
+      <c r="AM142" s="1" t="n">
+        <v>0.01244</v>
+      </c>
+      <c r="AN142" s="2" t="n">
+        <v>-0.0008032128514055898</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -17413,6 +18271,12 @@
       <c r="AL143" s="2" t="n">
         <v>-0.01338028169014091</v>
       </c>
+      <c r="AM143" s="1" t="n">
+        <v>0.02813</v>
+      </c>
+      <c r="AN143" s="3" t="n">
+        <v>0.003925767309064918</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -17531,6 +18395,12 @@
       <c r="AL144" s="2" t="n">
         <v>-0.002309953800923924</v>
       </c>
+      <c r="AM144" s="1" t="n">
+        <v>0.004751</v>
+      </c>
+      <c r="AN144" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -17649,6 +18519,12 @@
       <c r="AL145" s="3" t="n">
         <v>0.002026650453463041</v>
       </c>
+      <c r="AM145" s="1" t="n">
+        <v>1.9731</v>
+      </c>
+      <c r="AN145" s="2" t="n">
+        <v>-0.002325934165950315</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17767,6 +18643,12 @@
       <c r="AL146" s="3" t="n">
         <v>0.0008539709649871556</v>
       </c>
+      <c r="AM146" s="1" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="AN146" s="2" t="n">
+        <v>-0.0008532423208190779</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17885,6 +18767,12 @@
       <c r="AL147" s="2" t="n">
         <v>-0.002107130974825283</v>
       </c>
+      <c r="AM147" s="1" t="n">
+        <v>0.09014999999999999</v>
+      </c>
+      <c r="AN147" s="3" t="n">
+        <v>0.00188930873527439</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18003,6 +18891,12 @@
       <c r="AL148" s="2" t="n">
         <v>-0.02183406113537116</v>
       </c>
+      <c r="AM148" s="1" t="n">
+        <v>0.06329</v>
+      </c>
+      <c r="AN148" s="3" t="n">
+        <v>0.00908801020408165</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -18121,6 +19015,12 @@
       <c r="AL149" s="2" t="n">
         <v>-0.002534640081108555</v>
       </c>
+      <c r="AM149" s="1" t="n">
+        <v>0.05895</v>
+      </c>
+      <c r="AN149" s="2" t="n">
+        <v>-0.001355243096730421</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -18239,6 +19139,12 @@
       <c r="AL150" s="2" t="n">
         <v>-0.006296508299942701</v>
       </c>
+      <c r="AM150" s="1" t="n">
+        <v>0.24284</v>
+      </c>
+      <c r="AN150" s="2" t="n">
+        <v>-0.0008229098090849478</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -18357,6 +19263,12 @@
       <c r="AL151" s="2" t="n">
         <v>-0.004689498365780947</v>
       </c>
+      <c r="AM151" s="1" t="n">
+        <v>7.020999999999999e-05</v>
+      </c>
+      <c r="AN151" s="3" t="n">
+        <v>0.002427184466019322</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -18475,6 +19387,12 @@
       <c r="AL152" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM152" s="1" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="AN152" s="2" t="n">
+        <v>-0.003150315031503178</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -18593,6 +19511,12 @@
       <c r="AL153" s="3" t="n">
         <v>0.003243593902043467</v>
       </c>
+      <c r="AM153" s="1" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="AN153" s="3" t="n">
+        <v>0.005819592628515901</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -18711,6 +19635,12 @@
       <c r="AL154" s="3" t="n">
         <v>0.001106194690265519</v>
       </c>
+      <c r="AM154" s="1" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="AN154" s="2" t="n">
+        <v>-0.0002762430939226215</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -18829,6 +19759,12 @@
       <c r="AL155" s="3" t="n">
         <v>0.003916449086161811</v>
       </c>
+      <c r="AM155" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AN155" s="2" t="n">
+        <v>-0.003034243606415164</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -18947,6 +19883,12 @@
       <c r="AL156" s="3" t="n">
         <v>0.006185056902523509</v>
       </c>
+      <c r="AM156" s="1" t="n">
+        <v>0.08124000000000001</v>
+      </c>
+      <c r="AN156" s="2" t="n">
+        <v>-0.001229407425620715</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -19065,6 +20007,12 @@
       <c r="AL157" s="2" t="n">
         <v>-0.0006462731581215478</v>
       </c>
+      <c r="AM157" s="1" t="n">
+        <v>0.23143</v>
+      </c>
+      <c r="AN157" s="2" t="n">
+        <v>-0.00224186247035996</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -19183,6 +20131,12 @@
       <c r="AL158" s="3" t="n">
         <v>0.001966181675186789</v>
       </c>
+      <c r="AM158" s="1" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="AN158" s="3" t="n">
+        <v>0.0003924646781789206</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -19301,6 +20255,12 @@
       <c r="AL159" s="2" t="n">
         <v>-0.0003429355281206756</v>
       </c>
+      <c r="AM159" s="1" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="AN159" s="3" t="n">
+        <v>0.0006861063464836294</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -19419,6 +20379,12 @@
       <c r="AL160" s="2" t="n">
         <v>-0.002018163471241089</v>
       </c>
+      <c r="AM160" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="AN160" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -19537,6 +20503,12 @@
       <c r="AL161" s="2" t="n">
         <v>-0.003655317132606869</v>
       </c>
+      <c r="AM161" s="1" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="AN161" s="2" t="n">
+        <v>-0.004008424485358921</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -19655,6 +20627,12 @@
       <c r="AL162" s="3" t="n">
         <v>0.0003036744609778721</v>
       </c>
+      <c r="AM162" s="1" t="n">
+        <v>0.003302</v>
+      </c>
+      <c r="AN162" s="3" t="n">
+        <v>0.002428658166363012</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -19773,6 +20751,12 @@
       <c r="AL163" s="3" t="n">
         <v>0.004398240703718402</v>
       </c>
+      <c r="AM163" s="1" t="n">
+        <v>0.005011</v>
+      </c>
+      <c r="AN163" s="2" t="n">
+        <v>-0.002587579617834393</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -19891,6 +20875,12 @@
       <c r="AL164" s="2" t="n">
         <v>-0.003112033195020692</v>
       </c>
+      <c r="AM164" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="AN164" s="3" t="n">
+        <v>0.003121748178980174</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -20009,6 +20999,12 @@
       <c r="AL165" s="2" t="n">
         <v>-0.004873294346978562</v>
       </c>
+      <c r="AM165" s="1" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AN165" s="2" t="n">
+        <v>-0.002611818478615811</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -20127,6 +21123,12 @@
       <c r="AL166" s="2" t="n">
         <v>-0.001861664041243132</v>
       </c>
+      <c r="AM166" s="1" t="n">
+        <v>1.3919</v>
+      </c>
+      <c r="AN166" s="2" t="n">
+        <v>-0.001506456241032992</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -20245,6 +21247,12 @@
       <c r="AL167" s="2" t="n">
         <v>-0.006428571428571513</v>
       </c>
+      <c r="AM167" s="1" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="AN167" s="2" t="n">
+        <v>-0.001078360891445084</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -20363,6 +21371,12 @@
       <c r="AL168" s="2" t="n">
         <v>-0.003215434083601289</v>
       </c>
+      <c r="AM168" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AN168" s="3" t="n">
+        <v>0.003225806451612906</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -20481,6 +21495,12 @@
       <c r="AL169" s="2" t="n">
         <v>-0.003324468085106363</v>
       </c>
+      <c r="AM169" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="AN169" s="2" t="n">
+        <v>-0.002334889926617766</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -20599,6 +21619,12 @@
       <c r="AL170" s="3" t="n">
         <v>0.003933364183248416</v>
       </c>
+      <c r="AM170" s="1" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="AN170" s="2" t="n">
+        <v>-0.001843742797879621</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -20717,6 +21743,12 @@
       <c r="AL171" s="2" t="n">
         <v>-0.005988023952095772</v>
       </c>
+      <c r="AM171" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="AN171" s="2" t="n">
+        <v>-0.006024096385542133</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -20835,6 +21867,12 @@
       <c r="AL172" s="2" t="n">
         <v>-0.007692307692307619</v>
       </c>
+      <c r="AM172" s="1" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="AN172" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -20953,6 +21991,12 @@
       <c r="AL173" s="2" t="n">
         <v>-0.003305004721435345</v>
       </c>
+      <c r="AM173" s="1" t="n">
+        <v>0.02109</v>
+      </c>
+      <c r="AN173" s="2" t="n">
+        <v>-0.0009474182851728652</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -21071,6 +22115,12 @@
       <c r="AL174" s="2" t="n">
         <v>-0.003669112741828006</v>
       </c>
+      <c r="AM174" s="1" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="AN174" s="2" t="n">
+        <v>-0.003459435330878148</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -21189,6 +22239,12 @@
       <c r="AL175" s="2" t="n">
         <v>-0.002763957987838587</v>
       </c>
+      <c r="AM175" s="1" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="AN175" s="2" t="n">
+        <v>-0.0005543237250555252</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -21307,6 +22363,12 @@
       <c r="AL176" s="2" t="n">
         <v>-0.002346316283434912</v>
       </c>
+      <c r="AM176" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AN176" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -21425,6 +22487,12 @@
       <c r="AL177" s="3" t="n">
         <v>0.008962868117797663</v>
       </c>
+      <c r="AM177" s="1" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="AN177" s="2" t="n">
+        <v>-0.003807106598984837</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -21543,6 +22611,12 @@
       <c r="AL178" s="2" t="n">
         <v>-0.004197271773347313</v>
       </c>
+      <c r="AM178" s="1" t="n">
+        <v>0.000949</v>
+      </c>
+      <c r="AN178" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -21661,6 +22735,12 @@
       <c r="AL179" s="2" t="n">
         <v>-0.002716319824753692</v>
       </c>
+      <c r="AM179" s="1" t="n">
+        <v>0.022889</v>
+      </c>
+      <c r="AN179" s="3" t="n">
+        <v>0.005535298510741164</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -21779,6 +22859,12 @@
       <c r="AL180" s="2" t="n">
         <v>-0.00146341463414618</v>
       </c>
+      <c r="AM180" s="1" t="n">
+        <v>4.082</v>
+      </c>
+      <c r="AN180" s="2" t="n">
+        <v>-0.002931118710307878</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -21897,6 +22983,12 @@
       <c r="AL181" s="2" t="n">
         <v>-0.004209787756534062</v>
       </c>
+      <c r="AM181" s="1" t="n">
+        <v>0.5677</v>
+      </c>
+      <c r="AN181" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -22015,6 +23107,12 @@
       <c r="AL182" s="2" t="n">
         <v>-0.005911330049261116</v>
       </c>
+      <c r="AM182" s="1" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="AN182" s="2" t="n">
+        <v>-0.002378592666005987</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -22133,6 +23231,12 @@
       <c r="AL183" s="2" t="n">
         <v>-0.004761904761904726</v>
       </c>
+      <c r="AM183" s="1" t="n">
+        <v>5.422</v>
+      </c>
+      <c r="AN183" s="2" t="n">
+        <v>-0.002208317997791765</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -22251,6 +23355,12 @@
       <c r="AL184" s="2" t="n">
         <v>-0.001734304543877806</v>
       </c>
+      <c r="AM184" s="1" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AN184" s="2" t="n">
+        <v>-0.003474635163307902</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -22369,6 +23479,12 @@
       <c r="AL185" s="2" t="n">
         <v>-0.009646302250803838</v>
       </c>
+      <c r="AM185" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="AN185" s="2" t="n">
+        <v>-0.001623376623376557</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -22487,6 +23603,12 @@
       <c r="AL186" s="2" t="n">
         <v>-0.003246753246753325</v>
       </c>
+      <c r="AM186" s="1" t="n">
+        <v>3.07e-05</v>
+      </c>
+      <c r="AN186" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -22605,6 +23727,12 @@
       <c r="AL187" s="2" t="n">
         <v>-0.0006381620931716396</v>
       </c>
+      <c r="AM187" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="AN187" s="2" t="n">
+        <v>-0.001915708812260458</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -22723,6 +23851,12 @@
       <c r="AL188" s="2" t="n">
         <v>-0.001227596366314791</v>
       </c>
+      <c r="AM188" s="1" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="AN188" s="3" t="n">
+        <v>0.001229105211406132</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -22841,6 +23975,12 @@
       <c r="AL189" s="2" t="n">
         <v>-0.00759437123073481</v>
       </c>
+      <c r="AM189" s="1" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="AN189" s="2" t="n">
+        <v>-0.002700877785280282</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -22959,6 +24099,12 @@
       <c r="AL190" s="2" t="n">
         <v>-0.001733853489380227</v>
       </c>
+      <c r="AM190" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="AN190" s="3" t="n">
+        <v>0.0004342162396874973</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -23077,6 +24223,12 @@
       <c r="AL191" s="2" t="n">
         <v>-0.004447268106734474</v>
       </c>
+      <c r="AM191" s="1" t="n">
+        <v>0.01569</v>
+      </c>
+      <c r="AN191" s="3" t="n">
+        <v>0.001276324186343279</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -23195,6 +24347,12 @@
       <c r="AL192" s="2" t="n">
         <v>-0.002510310202617917</v>
       </c>
+      <c r="AM192" s="1" t="n">
+        <v>0.05577</v>
+      </c>
+      <c r="AN192" s="3" t="n">
+        <v>0.002516627718856754</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -23313,6 +24471,12 @@
       <c r="AL193" s="2" t="n">
         <v>-0.004259850905218292</v>
       </c>
+      <c r="AM193" s="1" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="AN193" s="2" t="n">
+        <v>-0.002139037433155141</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -23431,6 +24595,12 @@
       <c r="AL194" s="2" t="n">
         <v>-0.003107198342827603</v>
       </c>
+      <c r="AM194" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="AN194" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -23549,6 +24719,12 @@
       <c r="AL195" s="2" t="n">
         <v>-0.0007070469007778046</v>
       </c>
+      <c r="AM195" s="1" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="AN195" s="3" t="n">
+        <v>0.004481132075471728</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -23667,6 +24843,12 @@
       <c r="AL196" s="2" t="n">
         <v>-0.00325467860048821</v>
       </c>
+      <c r="AM196" s="1" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="AN196" s="3" t="n">
+        <v>0.002448979591836635</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -23785,6 +24967,12 @@
       <c r="AL197" s="2" t="n">
         <v>-0.005586592178770872</v>
       </c>
+      <c r="AM197" s="1" t="n">
+        <v>0.04608</v>
+      </c>
+      <c r="AN197" s="2" t="n">
+        <v>-0.004321521175453733</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -23903,6 +25091,12 @@
       <c r="AL198" s="2" t="n">
         <v>-0.003876720294630746</v>
       </c>
+      <c r="AM198" s="1" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="AN198" s="2" t="n">
+        <v>-0.00272426542128832</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -24021,6 +25215,12 @@
       <c r="AL199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AN199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -24139,6 +25339,12 @@
       <c r="AL200" s="2" t="n">
         <v>-0.002020202020201977</v>
       </c>
+      <c r="AM200" s="1" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="AN200" s="2" t="n">
+        <v>-0.0006747638326585551</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -24257,6 +25463,12 @@
       <c r="AL201" s="2" t="n">
         <v>-0.002825357584319181</v>
       </c>
+      <c r="AM201" s="1" t="n">
+        <v>0.005627</v>
+      </c>
+      <c r="AN201" s="2" t="n">
+        <v>-0.003541703559412086</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -24375,6 +25587,12 @@
       <c r="AL202" s="2" t="n">
         <v>-0.001431794515793054</v>
       </c>
+      <c r="AM202" s="1" t="n">
+        <v>0.022972</v>
+      </c>
+      <c r="AN202" s="2" t="n">
+        <v>-0.001868346730393281</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -24493,6 +25711,12 @@
       <c r="AL203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AN203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -24611,6 +25835,12 @@
       <c r="AL204" s="2" t="n">
         <v>-0.003596044351213519</v>
       </c>
+      <c r="AM204" s="1" t="n">
+        <v>0.03325</v>
+      </c>
+      <c r="AN204" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -24729,6 +25959,12 @@
       <c r="AL205" s="2" t="n">
         <v>-0.001670245764733876</v>
       </c>
+      <c r="AM205" s="1" t="n">
+        <v>4.169</v>
+      </c>
+      <c r="AN205" s="2" t="n">
+        <v>-0.003585086042065145</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -24847,6 +26083,12 @@
       <c r="AL206" s="2" t="n">
         <v>-0.002762430939226522</v>
       </c>
+      <c r="AM206" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN206" s="2" t="n">
+        <v>-0.002770083102493077</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -24965,6 +26207,12 @@
       <c r="AL207" s="2" t="n">
         <v>-0.01615784976306988</v>
       </c>
+      <c r="AM207" s="1" t="n">
+        <v>0.001262</v>
+      </c>
+      <c r="AN207" s="2" t="n">
+        <v>-0.003553099091985746</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -25083,6 +26331,12 @@
       <c r="AL208" s="2" t="n">
         <v>-0.002946954813359555</v>
       </c>
+      <c r="AM208" s="1" t="n">
+        <v>0.007134</v>
+      </c>
+      <c r="AN208" s="3" t="n">
+        <v>0.004081632653061155</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -25201,6 +26455,12 @@
       <c r="AL209" s="2" t="n">
         <v>-0.001669449081803053</v>
       </c>
+      <c r="AM209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="AN209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -25319,6 +26579,12 @@
       <c r="AL210" s="2" t="n">
         <v>-0.003091190108191528</v>
       </c>
+      <c r="AM210" s="1" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AN210" s="2" t="n">
+        <v>-0.002325581395348796</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -25437,6 +26703,12 @@
       <c r="AL211" s="2" t="n">
         <v>-0.002664796633941083</v>
       </c>
+      <c r="AM211" s="1" t="n">
+        <v>0.007122</v>
+      </c>
+      <c r="AN211" s="3" t="n">
+        <v>0.001546899170299497</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -25555,6 +26827,12 @@
       <c r="AL212" s="3" t="n">
         <v>0.009986225895316852</v>
       </c>
+      <c r="AM212" s="1" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="AN212" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -25673,6 +26951,12 @@
       <c r="AL213" s="3" t="n">
         <v>0.00590188122464037</v>
       </c>
+      <c r="AM213" s="1" t="n">
+        <v>0.05445</v>
+      </c>
+      <c r="AN213" s="2" t="n">
+        <v>-0.001650165016501646</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -25791,6 +27075,12 @@
       <c r="AL214" s="2" t="n">
         <v>-0.002120890774125046</v>
       </c>
+      <c r="AM214" s="1" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AN214" s="2" t="n">
+        <v>-0.001062699256110551</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -25909,6 +27199,12 @@
       <c r="AL215" s="3" t="n">
         <v>0.00112507031689476</v>
       </c>
+      <c r="AM215" s="1" t="n">
+        <v>0.05326</v>
+      </c>
+      <c r="AN215" s="2" t="n">
+        <v>-0.002434912905038362</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -26027,6 +27323,12 @@
       <c r="AL216" s="2" t="n">
         <v>-0.0004866180048662446</v>
       </c>
+      <c r="AM216" s="1" t="n">
+        <v>0.002015</v>
+      </c>
+      <c r="AN216" s="2" t="n">
+        <v>-0.01898734177215189</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -26145,6 +27447,12 @@
       <c r="AL217" s="2" t="n">
         <v>-0.002157318287421159</v>
       </c>
+      <c r="AM217" s="1" t="n">
+        <v>6.006</v>
+      </c>
+      <c r="AN217" s="2" t="n">
+        <v>-0.001164144353899829</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -26263,6 +27571,12 @@
       <c r="AL218" s="2" t="n">
         <v>-0.005406676069581498</v>
       </c>
+      <c r="AM218" s="1" t="n">
+        <v>4.237</v>
+      </c>
+      <c r="AN218" s="3" t="n">
+        <v>0.001418104467029125</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -26381,6 +27695,12 @@
       <c r="AL219" s="3" t="n">
         <v>0.0003756574004508388</v>
       </c>
+      <c r="AM219" s="1" t="n">
+        <v>0.005341</v>
+      </c>
+      <c r="AN219" s="3" t="n">
+        <v>0.002816372512204329</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -26499,6 +27819,12 @@
       <c r="AL220" s="2" t="n">
         <v>-0.002921129503407865</v>
       </c>
+      <c r="AM220" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="AN220" s="2" t="n">
+        <v>-0.002685546875000144</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -26617,6 +27943,12 @@
       <c r="AL221" s="2" t="n">
         <v>-0.002257336343115123</v>
       </c>
+      <c r="AM221" s="1" t="n">
+        <v>0.005741</v>
+      </c>
+      <c r="AN221" s="2" t="n">
+        <v>-0.0008701705534285874</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -26735,6 +28067,12 @@
       <c r="AL222" s="3" t="n">
         <v>0.002190580503833426</v>
       </c>
+      <c r="AM222" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="AN222" s="3" t="n">
+        <v>0.006557377049180364</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -26853,6 +28191,12 @@
       <c r="AL223" s="2" t="n">
         <v>-0.000594353640416147</v>
       </c>
+      <c r="AM223" s="1" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AN223" s="2" t="n">
+        <v>-0.003865596193874422</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -26971,6 +28315,12 @@
       <c r="AL224" s="2" t="n">
         <v>-0.001848428835489887</v>
       </c>
+      <c r="AM224" s="1" t="n">
+        <v>0.4317</v>
+      </c>
+      <c r="AN224" s="2" t="n">
+        <v>-0.0006944444444444965</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -27089,6 +28439,12 @@
       <c r="AL225" s="2" t="n">
         <v>-0.001564568540137095</v>
       </c>
+      <c r="AM225" s="1" t="n">
+        <v>0.08305</v>
+      </c>
+      <c r="AN225" s="3" t="n">
+        <v>0.001084860173577542</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -27207,6 +28563,12 @@
       <c r="AL226" s="2" t="n">
         <v>-0.01123595505617969</v>
       </c>
+      <c r="AM226" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="AN226" s="3" t="n">
+        <v>0.002164502164502076</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -27325,6 +28687,12 @@
       <c r="AL227" s="2" t="n">
         <v>-0.003394865266284753</v>
       </c>
+      <c r="AM227" s="1" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AN227" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -27443,6 +28811,12 @@
       <c r="AL228" s="3" t="n">
         <v>0.0008680555555555202</v>
       </c>
+      <c r="AM228" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="AN228" s="3" t="n">
+        <v>0.006071118820468247</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -27561,6 +28935,12 @@
       <c r="AL229" s="2" t="n">
         <v>-0.002762430939226599</v>
       </c>
+      <c r="AM229" s="1" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="AN229" s="3" t="n">
+        <v>0.002770083102493154</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -27679,6 +29059,12 @@
       <c r="AL230" s="2" t="n">
         <v>-0.003003003003003006</v>
       </c>
+      <c r="AM230" s="1" t="n">
+        <v>0.1662</v>
+      </c>
+      <c r="AN230" s="3" t="n">
+        <v>0.001204819277108301</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -27797,6 +29183,12 @@
       <c r="AL231" s="2" t="n">
         <v>-0.001317957166392039</v>
       </c>
+      <c r="AM231" s="1" t="n">
+        <v>0.03028</v>
+      </c>
+      <c r="AN231" s="2" t="n">
+        <v>-0.0009897723523589171</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -27915,6 +29307,12 @@
       <c r="AL232" s="2" t="n">
         <v>-0.004930524428507351</v>
       </c>
+      <c r="AM232" s="1" t="n">
+        <v>0.02226</v>
+      </c>
+      <c r="AN232" s="3" t="n">
+        <v>0.002702702702702592</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -28033,6 +29431,12 @@
       <c r="AL233" s="3" t="n">
         <v>0.0310559006211179</v>
       </c>
+      <c r="AM233" s="1" t="n">
+        <v>0.12213</v>
+      </c>
+      <c r="AN233" s="3" t="n">
+        <v>0.1318813716404079</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -28151,6 +29555,12 @@
       <c r="AL234" s="2" t="n">
         <v>-0.0003943217665614708</v>
       </c>
+      <c r="AM234" s="1" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="AN234" s="2" t="n">
+        <v>-0.001577909270217008</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -28269,6 +29679,12 @@
       <c r="AL235" s="2" t="n">
         <v>-0.000436554132712489</v>
       </c>
+      <c r="AM235" s="1" t="n">
+        <v>0.06866999999999999</v>
+      </c>
+      <c r="AN235" s="2" t="n">
+        <v>-0.0002911631969719919</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -28387,6 +29803,12 @@
       <c r="AL236" s="2" t="n">
         <v>-0.001675442795596104</v>
       </c>
+      <c r="AM236" s="1" t="n">
+        <v>0.12573</v>
+      </c>
+      <c r="AN236" s="3" t="n">
+        <v>0.0047950131862864</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -28505,6 +29927,12 @@
       <c r="AL237" s="2" t="n">
         <v>-0.002585315408479729</v>
       </c>
+      <c r="AM237" s="1" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="AN237" s="2" t="n">
+        <v>-0.008553654743390458</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -28623,6 +30051,12 @@
       <c r="AL238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AN238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -28741,6 +30175,12 @@
       <c r="AL239" s="2" t="n">
         <v>-0.0002521432173474868</v>
       </c>
+      <c r="AM239" s="1" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="AN239" s="3" t="n">
+        <v>0.001261034047919242</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -28859,6 +30299,12 @@
       <c r="AL240" s="2" t="n">
         <v>-0.002183406113537155</v>
       </c>
+      <c r="AM240" s="1" t="n">
+        <v>0.01372</v>
+      </c>
+      <c r="AN240" s="3" t="n">
+        <v>0.000729394602479912</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -28977,6 +30423,12 @@
       <c r="AL241" s="3" t="n">
         <v>0.002258866049243282</v>
       </c>
+      <c r="AM241" s="1" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AN241" s="3" t="n">
+        <v>0.002929907595222049</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -29095,6 +30547,12 @@
       <c r="AL242" s="2" t="n">
         <v>-0.005340453938584793</v>
       </c>
+      <c r="AM242" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="AN242" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -29213,6 +30671,12 @@
       <c r="AL243" s="2" t="n">
         <v>-0.0008830022075054828</v>
       </c>
+      <c r="AM243" s="1" t="n">
+        <v>0.02259</v>
+      </c>
+      <c r="AN243" s="2" t="n">
+        <v>-0.001767565178966056</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -29331,6 +30795,12 @@
       <c r="AL244" s="2" t="n">
         <v>-0.008244994110718565</v>
       </c>
+      <c r="AM244" s="1" t="n">
+        <v>0.001682</v>
+      </c>
+      <c r="AN244" s="2" t="n">
+        <v>-0.001187648456057036</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -29449,6 +30919,12 @@
       <c r="AL245" s="2" t="n">
         <v>-0.001524390243902483</v>
       </c>
+      <c r="AM245" s="1" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="AN245" s="2" t="n">
+        <v>-0.003053435114503904</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -29567,6 +31043,12 @@
       <c r="AL246" s="2" t="n">
         <v>-0.006285355122564387</v>
       </c>
+      <c r="AM246" s="1" t="n">
+        <v>0.03133</v>
+      </c>
+      <c r="AN246" s="2" t="n">
+        <v>-0.009171410499683919</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -29685,6 +31167,12 @@
       <c r="AL247" s="2" t="n">
         <v>-0.003939223410242016</v>
       </c>
+      <c r="AM247" s="1" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="AN247" s="3" t="n">
+        <v>0.002824858757062149</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -29803,6 +31291,12 @@
       <c r="AL248" s="2" t="n">
         <v>-0.003293807641633823</v>
       </c>
+      <c r="AM248" s="1" t="n">
+        <v>0.03032</v>
+      </c>
+      <c r="AN248" s="3" t="n">
+        <v>0.001982815598149406</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -29921,6 +31415,12 @@
       <c r="AL249" s="3" t="n">
         <v>0.0002445585717779733</v>
       </c>
+      <c r="AM249" s="1" t="n">
+        <v>0.008182999999999999</v>
+      </c>
+      <c r="AN249" s="3" t="n">
+        <v>0.0003667481662591114</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -30039,6 +31539,12 @@
       <c r="AL250" s="2" t="n">
         <v>-0.009049773755656262</v>
       </c>
+      <c r="AM250" s="1" t="n">
+        <v>0.01978</v>
+      </c>
+      <c r="AN250" s="3" t="n">
+        <v>0.003551496702181665</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -30157,6 +31663,12 @@
       <c r="AL251" s="2" t="n">
         <v>-0.00107735401853052</v>
       </c>
+      <c r="AM251" s="1" t="n">
+        <v>0.04632</v>
+      </c>
+      <c r="AN251" s="2" t="n">
+        <v>-0.0008628127696289554</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -30275,6 +31787,12 @@
       <c r="AL252" s="2" t="n">
         <v>-0.0005807200929151912</v>
       </c>
+      <c r="AM252" s="1" t="n">
+        <v>0.008543</v>
+      </c>
+      <c r="AN252" s="2" t="n">
+        <v>-0.007205113306217264</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -30393,6 +31911,12 @@
       <c r="AL253" s="2" t="n">
         <v>-0.001298701298701336</v>
       </c>
+      <c r="AM253" s="1" t="n">
+        <v>0.03852</v>
+      </c>
+      <c r="AN253" s="3" t="n">
+        <v>0.001820546163849171</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -30511,6 +32035,12 @@
       <c r="AL254" s="2" t="n">
         <v>-0.001636393388970642</v>
       </c>
+      <c r="AM254" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AN254" s="2" t="n">
+        <v>-0.0001639075561383882</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -30629,6 +32159,12 @@
       <c r="AL255" s="2" t="n">
         <v>-0.001698273422020925</v>
       </c>
+      <c r="AM255" s="1" t="n">
+        <v>0.003528</v>
+      </c>
+      <c r="AN255" s="3" t="n">
+        <v>0.0002835270768357525</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -30747,6 +32283,12 @@
       <c r="AL256" s="3" t="n">
         <v>0.003433860853986332</v>
       </c>
+      <c r="AM256" s="1" t="n">
+        <v>0.013344</v>
+      </c>
+      <c r="AN256" s="2" t="n">
+        <v>-0.007290581758666929</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -30865,6 +32407,12 @@
       <c r="AL257" s="2" t="n">
         <v>-1.000556309336747e-06</v>
       </c>
+      <c r="AM257" s="1" t="n">
+        <v>0.999444</v>
+      </c>
+      <c r="AN257" s="3" t="n">
+        <v>1.000557310450677e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -30983,6 +32531,12 @@
       <c r="AL258" s="2" t="n">
         <v>-0.0001131477709888677</v>
       </c>
+      <c r="AM258" s="1" t="n">
+        <v>0.08832</v>
+      </c>
+      <c r="AN258" s="2" t="n">
+        <v>-0.000565802874278696</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -31101,6 +32655,12 @@
       <c r="AL259" s="2" t="n">
         <v>-0.005571651437486076</v>
       </c>
+      <c r="AM259" s="1" t="n">
+        <v>0.08925</v>
+      </c>
+      <c r="AN259" s="3" t="n">
+        <v>0.0001120573733751246</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -31219,6 +32779,12 @@
       <c r="AL260" s="2" t="n">
         <v>-0.001840716652350119</v>
       </c>
+      <c r="AM260" s="1" t="n">
+        <v>0.08101</v>
+      </c>
+      <c r="AN260" s="2" t="n">
+        <v>-0.00405704450454877</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -31337,6 +32903,12 @@
       <c r="AL261" s="3" t="n">
         <v>0.006216696269982343</v>
       </c>
+      <c r="AM261" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN261" s="3" t="n">
+        <v>0.006178287731685697</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -31455,6 +33027,12 @@
       <c r="AL262" s="3" t="n">
         <v>0.004389362251484548</v>
       </c>
+      <c r="AM262" s="1" t="n">
+        <v>0.003892</v>
+      </c>
+      <c r="AN262" s="3" t="n">
+        <v>0.0005141388174807881</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -31573,6 +33151,12 @@
       <c r="AL263" s="2" t="n">
         <v>-0.01908065915004331</v>
       </c>
+      <c r="AM263" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="AN263" s="3" t="n">
+        <v>0.002652519893899157</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -31691,6 +33275,12 @@
       <c r="AL264" s="2" t="n">
         <v>-0.00439238653001466</v>
       </c>
+      <c r="AM264" s="1" t="n">
+        <v>0.0006168</v>
+      </c>
+      <c r="AN264" s="3" t="n">
+        <v>0.007843137254901975</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -31809,6 +33399,12 @@
       <c r="AL265" s="2" t="n">
         <v>-0.002739726027397267</v>
       </c>
+      <c r="AM265" s="1" t="n">
+        <v>0.01455</v>
+      </c>
+      <c r="AN265" s="2" t="n">
+        <v>-0.0006868131868131588</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -31927,6 +33523,12 @@
       <c r="AL266" s="2" t="n">
         <v>-0.006299212598425159</v>
       </c>
+      <c r="AM266" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AN266" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -32045,6 +33647,12 @@
       <c r="AL267" s="2" t="n">
         <v>-0.0006157635467980044</v>
       </c>
+      <c r="AM267" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AN267" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -32163,6 +33771,12 @@
       <c r="AL268" s="2" t="n">
         <v>-0.007113354749885317</v>
       </c>
+      <c r="AM268" s="1" t="n">
+        <v>0.0004309</v>
+      </c>
+      <c r="AN268" s="2" t="n">
+        <v>-0.004159926045759163</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -32281,6 +33895,12 @@
       <c r="AL269" s="2" t="n">
         <v>-0.0004819277108433538</v>
       </c>
+      <c r="AM269" s="1" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="AN269" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -32399,6 +34019,12 @@
       <c r="AL270" s="3" t="n">
         <v>0.001102535832414585</v>
       </c>
+      <c r="AM270" s="1" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="AN270" s="3" t="n">
+        <v>0.003303964757709193</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -32517,6 +34143,12 @@
       <c r="AL271" s="2" t="n">
         <v>-0.001354096140826037</v>
       </c>
+      <c r="AM271" s="1" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="AN271" s="3" t="n">
+        <v>0.0006779661016950288</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -32635,6 +34267,12 @@
       <c r="AL272" s="2" t="n">
         <v>-0.0005056890012642019</v>
       </c>
+      <c r="AM272" s="1" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="AN272" s="2" t="n">
+        <v>-0.004300531242094699</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -32753,6 +34391,12 @@
       <c r="AL273" s="2" t="n">
         <v>-0.005387931034482763</v>
       </c>
+      <c r="AM273" s="1" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="AN273" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -32871,6 +34515,12 @@
       <c r="AL274" s="2" t="n">
         <v>-0.001104449353108241</v>
       </c>
+      <c r="AM274" s="1" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="AN274" s="3" t="n">
+        <v>0.001105670510187968</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -32989,6 +34639,12 @@
       <c r="AL275" s="2" t="n">
         <v>-0.006172839506172741</v>
       </c>
+      <c r="AM275" s="1" t="n">
+        <v>0.01127</v>
+      </c>
+      <c r="AN275" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -33107,6 +34763,12 @@
       <c r="AL276" s="2" t="n">
         <v>-0.00114766641162956</v>
       </c>
+      <c r="AM276" s="1" t="n">
+        <v>2.611</v>
+      </c>
+      <c r="AN276" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -33225,6 +34887,12 @@
       <c r="AL277" s="2" t="n">
         <v>-0.0009553379508000566</v>
       </c>
+      <c r="AM277" s="1" t="n">
+        <v>0.04177</v>
+      </c>
+      <c r="AN277" s="2" t="n">
+        <v>-0.001434377241214381</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -33343,6 +35011,12 @@
       <c r="AL278" s="2" t="n">
         <v>-0.002557544757033321</v>
       </c>
+      <c r="AM278" s="1" t="n">
+        <v>0.01951</v>
+      </c>
+      <c r="AN278" s="3" t="n">
+        <v>0.0005128205128204919</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -33461,6 +35135,12 @@
       <c r="AL279" s="3" t="n">
         <v>0.0007058408328921234</v>
       </c>
+      <c r="AM279" s="1" t="n">
+        <v>0.005691</v>
+      </c>
+      <c r="AN279" s="3" t="n">
+        <v>0.003526714865103166</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -33579,6 +35259,12 @@
       <c r="AL280" s="2" t="n">
         <v>-0.002572016460905245</v>
       </c>
+      <c r="AM280" s="1" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="AN280" s="3" t="n">
+        <v>0.003094378545641957</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -33697,6 +35383,12 @@
       <c r="AL281" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM281" s="1" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="AN281" s="2" t="n">
+        <v>-0.002209944751381217</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -33815,6 +35507,12 @@
       <c r="AL282" s="2" t="n">
         <v>-0.003622313450857238</v>
       </c>
+      <c r="AM282" s="1" t="n">
+        <v>0.0004155</v>
+      </c>
+      <c r="AN282" s="3" t="n">
+        <v>0.007028599127484286</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -33933,6 +35631,12 @@
       <c r="AL283" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AN283" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -34051,6 +35755,12 @@
       <c r="AL284" s="2" t="n">
         <v>-0.0002378686964796161</v>
       </c>
+      <c r="AM284" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AN284" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -34169,6 +35879,12 @@
       <c r="AL285" s="2" t="n">
         <v>-0.0119877334820184</v>
       </c>
+      <c r="AM285" s="1" t="n">
+        <v>0.10621</v>
+      </c>
+      <c r="AN285" s="2" t="n">
+        <v>-0.001034612490594422</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -34287,6 +36003,12 @@
       <c r="AL286" s="2" t="n">
         <v>-0.004750593824228041</v>
       </c>
+      <c r="AM286" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="AN286" s="2" t="n">
+        <v>-0.002386634844868845</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -34405,6 +36127,12 @@
       <c r="AL287" s="3" t="n">
         <v>0.003201844262295085</v>
       </c>
+      <c r="AM287" s="1" t="n">
+        <v>0.15679</v>
+      </c>
+      <c r="AN287" s="3" t="n">
+        <v>0.0008298225456403613</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -34523,6 +36251,12 @@
       <c r="AL288" s="3" t="n">
         <v>0.001668520578420592</v>
       </c>
+      <c r="AM288" s="1" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="AN288" s="3" t="n">
+        <v>0.002776235424764022</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -34641,6 +36375,12 @@
       <c r="AL289" s="2" t="n">
         <v>-0.004340487099107953</v>
       </c>
+      <c r="AM289" s="1" t="n">
+        <v>4.132</v>
+      </c>
+      <c r="AN289" s="3" t="n">
+        <v>0.000726568176313905</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -34759,6 +36499,12 @@
       <c r="AL290" s="2" t="n">
         <v>-0.001869814187215069</v>
       </c>
+      <c r="AM290" s="1" t="n">
+        <v>0.08519</v>
+      </c>
+      <c r="AN290" s="2" t="n">
+        <v>-0.002575810794988853</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -34877,6 +36623,12 @@
       <c r="AL291" s="3" t="n">
         <v>0.0002822466836013582</v>
       </c>
+      <c r="AM291" s="1" t="n">
+        <v>0.03539</v>
+      </c>
+      <c r="AN291" s="2" t="n">
+        <v>-0.001410835214446993</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -34995,6 +36747,12 @@
       <c r="AL292" s="3" t="n">
         <v>0.003483368622361932</v>
       </c>
+      <c r="AM292" s="1" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="AN292" s="3" t="n">
+        <v>0.001905799074326105</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -35113,6 +36871,12 @@
       <c r="AL293" s="2" t="n">
         <v>-0.004768392370572101</v>
       </c>
+      <c r="AM293" s="1" t="n">
+        <v>0.005841</v>
+      </c>
+      <c r="AN293" s="2" t="n">
+        <v>-0.0005133470225873371</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -35231,6 +36995,12 @@
       <c r="AL294" s="2" t="n">
         <v>-0.002334403268164506</v>
       </c>
+      <c r="AM294" s="1" t="n">
+        <v>0.003413</v>
+      </c>
+      <c r="AN294" s="2" t="n">
+        <v>-0.001754899093302241</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -35349,6 +37119,12 @@
       <c r="AL295" s="2" t="n">
         <v>-0.003340757238307188</v>
       </c>
+      <c r="AM295" s="1" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="AN295" s="2" t="n">
+        <v>-0.0005586592178772402</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -35467,6 +37243,12 @@
       <c r="AL296" s="2" t="n">
         <v>-0.000444642063139124</v>
       </c>
+      <c r="AM296" s="1" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="AN296" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -35585,6 +37367,12 @@
       <c r="AL297" s="3" t="n">
         <v>0.001201923076923237</v>
       </c>
+      <c r="AM297" s="1" t="n">
+        <v>0.01673</v>
+      </c>
+      <c r="AN297" s="3" t="n">
+        <v>0.004201680672268736</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -35703,6 +37491,12 @@
       <c r="AL298" s="2" t="n">
         <v>-0.0008167710318541314</v>
       </c>
+      <c r="AM298" s="1" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AN298" s="2" t="n">
+        <v>-0.003542234332424981</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -35821,6 +37615,12 @@
       <c r="AL299" s="2" t="n">
         <v>-0.002707581227436713</v>
       </c>
+      <c r="AM299" s="1" t="n">
+        <v>0.01109</v>
+      </c>
+      <c r="AN299" s="3" t="n">
+        <v>0.003619909502262296</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -35939,6 +37739,12 @@
       <c r="AL300" s="2" t="n">
         <v>-0.01396917148362245</v>
       </c>
+      <c r="AM300" s="1" t="n">
+        <v>0.02047</v>
+      </c>
+      <c r="AN300" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -36057,6 +37863,12 @@
       <c r="AL301" s="3" t="n">
         <v>0.002647253474520077</v>
       </c>
+      <c r="AM301" s="1" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AN301" s="3" t="n">
+        <v>0.0102310231023102</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -36175,6 +37987,12 @@
       <c r="AL302" s="2" t="n">
         <v>-0.004329004329004403</v>
       </c>
+      <c r="AM302" s="1" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="AN302" s="2" t="n">
+        <v>-0.0007246376811593908</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -36293,6 +38111,12 @@
       <c r="AL303" s="2" t="n">
         <v>-0.003789416700500778</v>
       </c>
+      <c r="AM303" s="1" t="n">
+        <v>0.07353999999999999</v>
+      </c>
+      <c r="AN303" s="2" t="n">
+        <v>-0.0009509577503056735</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -36411,6 +38235,12 @@
       <c r="AL304" s="2" t="n">
         <v>-0.003148614609571661</v>
       </c>
+      <c r="AM304" s="1" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="AN304" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -36529,6 +38359,12 @@
       <c r="AL305" s="2" t="n">
         <v>-0.002183065647902717</v>
       </c>
+      <c r="AM305" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="AN305" s="2" t="n">
+        <v>-0.002969213939678225</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -36647,6 +38483,12 @@
       <c r="AL306" s="3" t="n">
         <v>0.0006077795786062043</v>
       </c>
+      <c r="AM306" s="1" t="n">
+        <v>0.04915</v>
+      </c>
+      <c r="AN306" s="2" t="n">
+        <v>-0.004859283255719864</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -36765,6 +38607,12 @@
       <c r="AL307" s="3" t="n">
         <v>0.001083423618634887</v>
       </c>
+      <c r="AM307" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="AN307" s="2" t="n">
+        <v>-0.002164502164502166</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -36883,6 +38731,12 @@
       <c r="AL308" s="2" t="n">
         <v>-0.001510193808205499</v>
       </c>
+      <c r="AM308" s="1" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="AN308" s="3" t="n">
+        <v>0.001008318628686799</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -37001,6 +38855,12 @@
       <c r="AL309" s="2" t="n">
         <v>-0.0006459948320414293</v>
       </c>
+      <c r="AM309" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="AN309" s="2" t="n">
+        <v>-0.002585649644473181</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -37119,6 +38979,12 @@
       <c r="AL310" s="2" t="n">
         <v>-0.003293687099725519</v>
       </c>
+      <c r="AM310" s="1" t="n">
+        <v>0.05438</v>
+      </c>
+      <c r="AN310" s="2" t="n">
+        <v>-0.001652285661832198</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -37237,6 +39103,12 @@
       <c r="AL311" s="2" t="n">
         <v>-0.006457359162770068</v>
       </c>
+      <c r="AM311" s="1" t="n">
+        <v>0.004457</v>
+      </c>
+      <c r="AN311" s="2" t="n">
+        <v>-0.001120573733751635</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -37355,6 +39227,12 @@
       <c r="AL312" s="2" t="n">
         <v>-0.000708382526564234</v>
       </c>
+      <c r="AM312" s="1" t="n">
+        <v>0.08456</v>
+      </c>
+      <c r="AN312" s="2" t="n">
+        <v>-0.0009451795841211083</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -37473,6 +39351,12 @@
       <c r="AL313" s="2" t="n">
         <v>-0.002949457031773669</v>
       </c>
+      <c r="AM313" s="1" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="AN313" s="2" t="n">
+        <v>-0.002285867957509795</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -37591,6 +39475,12 @@
       <c r="AL314" s="2" t="n">
         <v>-0.001308044473512137</v>
       </c>
+      <c r="AM314" s="1" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="AN314" s="2" t="n">
+        <v>-0.001964636542239651</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -37709,6 +39599,12 @@
       <c r="AL315" s="2" t="n">
         <v>-0.002510985561832917</v>
       </c>
+      <c r="AM315" s="1" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="AN315" s="2" t="n">
+        <v>-0.0006293266205161531</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -37827,6 +39723,12 @@
       <c r="AL316" s="2" t="n">
         <v>-0.002214839424141813</v>
       </c>
+      <c r="AM316" s="1" t="n">
+        <v>0.1793</v>
+      </c>
+      <c r="AN316" s="2" t="n">
+        <v>-0.004994450610432919</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -37945,6 +39847,12 @@
       <c r="AL317" s="2" t="n">
         <v>-0.004272363150867812</v>
       </c>
+      <c r="AM317" s="1" t="n">
+        <v>0.007468</v>
+      </c>
+      <c r="AN317" s="3" t="n">
+        <v>0.001340842048806596</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -38063,6 +39971,12 @@
       <c r="AL318" s="3" t="n">
         <v>0.002759164367363052</v>
       </c>
+      <c r="AM318" s="1" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="AN318" s="3" t="n">
+        <v>0.002948113207547118</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -38181,6 +40095,12 @@
       <c r="AL319" s="2" t="n">
         <v>-0.0002501340003573861</v>
       </c>
+      <c r="AM319" s="1" t="n">
+        <v>0.27959</v>
+      </c>
+      <c r="AN319" s="2" t="n">
+        <v>-0.00067910501108002</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -38299,6 +40219,12 @@
       <c r="AL320" s="2" t="n">
         <v>-0.004089050431621918</v>
       </c>
+      <c r="AM320" s="1" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="AN320" s="3" t="n">
+        <v>0.0002281021897809968</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -38417,6 +40343,12 @@
       <c r="AL321" s="2" t="n">
         <v>-0.0005163955589981715</v>
       </c>
+      <c r="AM321" s="1" t="n">
+        <v>0.07754999999999999</v>
+      </c>
+      <c r="AN321" s="3" t="n">
+        <v>0.001679152673727606</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -38535,6 +40467,12 @@
       <c r="AL322" s="2" t="n">
         <v>-0.001856435643564324</v>
       </c>
+      <c r="AM322" s="1" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="AN322" s="2" t="n">
+        <v>-0.001239925604463768</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -38653,6 +40591,12 @@
       <c r="AL323" s="2" t="n">
         <v>-0.002023267577137078</v>
       </c>
+      <c r="AM323" s="1" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AN323" s="3" t="n">
+        <v>0.001013684744044603</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -38771,6 +40715,12 @@
       <c r="AL324" s="2" t="n">
         <v>-0.0002443012045929766</v>
       </c>
+      <c r="AM324" s="1" t="n">
+        <v>0.053047</v>
+      </c>
+      <c r="AN324" s="2" t="n">
+        <v>-0.002875939849624067</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -38889,6 +40839,12 @@
       <c r="AL325" s="3" t="n">
         <v>0.002228047182175486</v>
       </c>
+      <c r="AM325" s="1" t="n">
+        <v>0.15217</v>
+      </c>
+      <c r="AN325" s="2" t="n">
+        <v>-0.005034654112723898</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -39007,6 +40963,12 @@
       <c r="AL326" s="3" t="n">
         <v>0.0009300883583940364</v>
       </c>
+      <c r="AM326" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="AN326" s="2" t="n">
+        <v>-0.001084094780857993</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -39125,6 +41087,12 @@
       <c r="AL327" s="2" t="n">
         <v>-0.0001319087191663544</v>
       </c>
+      <c r="AM327" s="1" t="n">
+        <v>0.015169</v>
+      </c>
+      <c r="AN327" s="3" t="n">
+        <v>0.000593667546174164</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -39243,6 +41211,12 @@
       <c r="AL328" s="2" t="n">
         <v>-0.002083333333333393</v>
       </c>
+      <c r="AM328" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AN328" s="2" t="n">
+        <v>-0.002087682672233736</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -39361,6 +41335,12 @@
       <c r="AL329" s="2" t="n">
         <v>-0.002742230347349145</v>
       </c>
+      <c r="AM329" s="1" t="n">
+        <v>0.00436</v>
+      </c>
+      <c r="AN329" s="2" t="n">
+        <v>-0.000916590284142911</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -39479,6 +41459,12 @@
       <c r="AL330" s="2" t="n">
         <v>-0.00615148019992299</v>
       </c>
+      <c r="AM330" s="1" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="AN330" s="3" t="n">
+        <v>0.0009671179883944776</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -39597,6 +41583,12 @@
       <c r="AL331" s="2" t="n">
         <v>-0.003076062639821001</v>
       </c>
+      <c r="AM331" s="1" t="n">
+        <v>0.03559</v>
+      </c>
+      <c r="AN331" s="2" t="n">
+        <v>-0.001683029453015554</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -39715,6 +41707,12 @@
       <c r="AL332" s="2" t="n">
         <v>-0.002700877785280293</v>
       </c>
+      <c r="AM332" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AN332" s="2" t="n">
+        <v>-0.004739336492891037</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -39833,6 +41831,12 @@
       <c r="AL333" s="2" t="n">
         <v>-0.002079002079001995</v>
       </c>
+      <c r="AM333" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="AN333" s="2" t="n">
+        <v>-0.002083333333333393</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -39951,6 +41955,12 @@
       <c r="AL334" s="2" t="n">
         <v>-0.001360544217687019</v>
       </c>
+      <c r="AM334" s="1" t="n">
+        <v>0.04407</v>
+      </c>
+      <c r="AN334" s="3" t="n">
+        <v>0.0006811989100816373</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -40069,6 +42079,12 @@
       <c r="AL335" s="2" t="n">
         <v>-0.0008607968519429491</v>
       </c>
+      <c r="AM335" s="1" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="AN335" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -40187,6 +42203,12 @@
       <c r="AL336" s="2" t="n">
         <v>-0.0009689922480620432</v>
       </c>
+      <c r="AM336" s="1" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="AN336" s="3" t="n">
+        <v>0.00193986420950539</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -40305,6 +42327,12 @@
       <c r="AL337" s="2" t="n">
         <v>-0.0019801980198019</v>
       </c>
+      <c r="AM337" s="1" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="AN337" s="2" t="n">
+        <v>-0.002976190476190527</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -40423,6 +42451,12 @@
       <c r="AL338" s="2" t="n">
         <v>-0.002638522427440587</v>
       </c>
+      <c r="AM338" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="AN338" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -40541,6 +42575,12 @@
       <c r="AL339" s="2" t="n">
         <v>-0.002742731760833679</v>
       </c>
+      <c r="AM339" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="AN339" s="2" t="n">
+        <v>-0.001100110011001246</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -40659,6 +42699,12 @@
       <c r="AL340" s="3" t="n">
         <v>0.01061269146608324</v>
       </c>
+      <c r="AM340" s="1" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="AN340" s="2" t="n">
+        <v>-0.01050124499296317</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -40777,6 +42823,12 @@
       <c r="AL341" s="3" t="n">
         <v>0.0002340276152586722</v>
       </c>
+      <c r="AM341" s="1" t="n">
+        <v>0.04271</v>
+      </c>
+      <c r="AN341" s="2" t="n">
+        <v>-0.0007019185774450689</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -40895,6 +42947,12 @@
       <c r="AL342" s="3" t="n">
         <v>0.002291242362525453</v>
       </c>
+      <c r="AM342" s="1" t="n">
+        <v>0.07887</v>
+      </c>
+      <c r="AN342" s="3" t="n">
+        <v>0.001651003302006493</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -41013,6 +43071,12 @@
       <c r="AL343" s="2" t="n">
         <v>-0.001703131141097852</v>
       </c>
+      <c r="AM343" s="1" t="n">
+        <v>7.605</v>
+      </c>
+      <c r="AN343" s="2" t="n">
+        <v>-0.001968503937007832</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -41131,6 +43195,12 @@
       <c r="AL344" s="2" t="n">
         <v>-0.000663570006635627</v>
       </c>
+      <c r="AM344" s="1" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="AN344" s="2" t="n">
+        <v>-0.001826029216467631</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -41249,6 +43319,12 @@
       <c r="AL345" s="2" t="n">
         <v>-0.002143048486472105</v>
       </c>
+      <c r="AM345" s="1" t="n">
+        <v>0.03724</v>
+      </c>
+      <c r="AN345" s="2" t="n">
+        <v>-0.0002684563758388221</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -41367,6 +43443,12 @@
       <c r="AL346" s="2" t="n">
         <v>-0.002403846153846056</v>
       </c>
+      <c r="AM346" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AN346" s="3" t="n">
+        <v>0.002409638554216769</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -41485,6 +43567,12 @@
       <c r="AL347" s="2" t="n">
         <v>-0.001713306681896029</v>
       </c>
+      <c r="AM347" s="1" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="AN347" s="3" t="n">
+        <v>0.00171624713958807</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -41603,6 +43691,12 @@
       <c r="AL348" s="2" t="n">
         <v>-0.0001731435167371366</v>
       </c>
+      <c r="AM348" s="1" t="n">
+        <v>5194.2</v>
+      </c>
+      <c r="AN348" s="2" t="n">
+        <v>-0.0005580035019531173</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -41721,6 +43815,12 @@
       <c r="AL349" s="3" t="n">
         <v>0.00294334069168507</v>
       </c>
+      <c r="AM349" s="1" t="n">
+        <v>0.01364</v>
+      </c>
+      <c r="AN349" s="3" t="n">
+        <v>0.0007336757153337926</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -41839,6 +43939,12 @@
       <c r="AL350" s="2" t="n">
         <v>-0.0006402048655569522</v>
       </c>
+      <c r="AM350" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="AN350" s="2" t="n">
+        <v>-0.002562459961563107</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -41957,6 +44063,12 @@
       <c r="AL351" s="2" t="n">
         <v>-0.005021056041464239</v>
       </c>
+      <c r="AM351" s="1" t="n">
+        <v>0.0006145</v>
+      </c>
+      <c r="AN351" s="3" t="n">
+        <v>0.0003255738238645692</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -42075,6 +44187,12 @@
       <c r="AL352" s="2" t="n">
         <v>-0.0060575466935892</v>
       </c>
+      <c r="AM352" s="1" t="n">
+        <v>0.01974</v>
+      </c>
+      <c r="AN352" s="3" t="n">
+        <v>0.002539360081259595</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -42193,6 +44311,12 @@
       <c r="AL353" s="3" t="n">
         <v>0.001825993555316901</v>
       </c>
+      <c r="AM353" s="1" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="AN353" s="3" t="n">
+        <v>0.00246595904363669</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -42311,6 +44435,12 @@
       <c r="AL354" s="2" t="n">
         <v>-0.004429678848283626</v>
       </c>
+      <c r="AM354" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AN354" s="3" t="n">
+        <v>0.001112347052280343</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -42429,6 +44559,12 @@
       <c r="AL355" s="2" t="n">
         <v>-0.007638550300666439</v>
       </c>
+      <c r="AM355" s="1" t="n">
+        <v>0.0006094</v>
+      </c>
+      <c r="AN355" s="2" t="n">
+        <v>-0.001965280052407516</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -42547,6 +44683,12 @@
       <c r="AL356" s="2" t="n">
         <v>-0.01039089559623944</v>
       </c>
+      <c r="AM356" s="1" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AN356" s="3" t="n">
+        <v>0.004999999999999893</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -42665,6 +44807,12 @@
       <c r="AL357" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM357" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="AN357" s="3" t="n">
+        <v>0.006544502617801084</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -42783,6 +44931,12 @@
       <c r="AL358" s="2" t="n">
         <v>-0.004889975550122235</v>
       </c>
+      <c r="AM358" s="1" t="n">
+        <v>0.000407</v>
+      </c>
+      <c r="AN358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -42901,6 +45055,12 @@
       <c r="AL359" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM359" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="AN359" s="2" t="n">
+        <v>-0.001358695652173975</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -43019,6 +45179,12 @@
       <c r="AL360" s="2" t="n">
         <v>-0.003002101471029728</v>
       </c>
+      <c r="AM360" s="1" t="n">
+        <v>0.003321</v>
+      </c>
+      <c r="AN360" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -43137,6 +45303,12 @@
       <c r="AL361" s="2" t="n">
         <v>-0.004242614707730868</v>
       </c>
+      <c r="AM361" s="1" t="n">
+        <v>0.6312</v>
+      </c>
+      <c r="AN361" s="2" t="n">
+        <v>-0.003945084424806782</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -43255,6 +45427,12 @@
       <c r="AL362" s="3" t="n">
         <v>0.0004242681374628592</v>
       </c>
+      <c r="AM362" s="1" t="n">
+        <v>0.02363</v>
+      </c>
+      <c r="AN362" s="3" t="n">
+        <v>0.002120441051738822</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -43373,6 +45551,12 @@
       <c r="AL363" s="2" t="n">
         <v>-0.005669629175605199</v>
       </c>
+      <c r="AM363" s="1" t="n">
+        <v>0.06503</v>
+      </c>
+      <c r="AN363" s="3" t="n">
+        <v>0.00215749730312839</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -43491,6 +45675,12 @@
       <c r="AL364" s="2" t="n">
         <v>-0.001913265306122333</v>
       </c>
+      <c r="AM364" s="1" t="n">
+        <v>4.695</v>
+      </c>
+      <c r="AN364" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -43609,6 +45799,12 @@
       <c r="AL365" s="3" t="n">
         <v>0.0005564056196967363</v>
       </c>
+      <c r="AM365" s="1" t="n">
+        <v>0.07184</v>
+      </c>
+      <c r="AN365" s="2" t="n">
+        <v>-0.001251216460447558</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -43727,6 +45923,12 @@
       <c r="AL366" s="2" t="n">
         <v>-0.004828326180257501</v>
       </c>
+      <c r="AM366" s="1" t="n">
+        <v>0.05564</v>
+      </c>
+      <c r="AN366" s="2" t="n">
+        <v>-0.0001796945193170912</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -43845,6 +46047,12 @@
       <c r="AL367" s="2" t="n">
         <v>-0.00360020572604152</v>
       </c>
+      <c r="AM367" s="1" t="n">
+        <v>0.05794</v>
+      </c>
+      <c r="AN367" s="2" t="n">
+        <v>-0.003097040605643489</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -43963,6 +46171,12 @@
       <c r="AL368" s="2" t="n">
         <v>-0.002984026680709084</v>
       </c>
+      <c r="AM368" s="1" t="n">
+        <v>0.05691</v>
+      </c>
+      <c r="AN368" s="3" t="n">
+        <v>0.001936619718309841</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -44081,6 +46295,12 @@
       <c r="AL369" s="2" t="n">
         <v>-0.00193485972267014</v>
       </c>
+      <c r="AM369" s="1" t="n">
+        <v>0.03102</v>
+      </c>
+      <c r="AN369" s="3" t="n">
+        <v>0.002261712439418437</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -44199,6 +46419,12 @@
       <c r="AL370" s="2" t="n">
         <v>-0.002476780185758407</v>
       </c>
+      <c r="AM370" s="1" t="n">
+        <v>0.0001609</v>
+      </c>
+      <c r="AN370" s="2" t="n">
+        <v>-0.001241464928615797</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -44317,6 +46543,12 @@
       <c r="AL371" s="2" t="n">
         <v>-0.002934272300469491</v>
       </c>
+      <c r="AM371" s="1" t="n">
+        <v>0.006778</v>
+      </c>
+      <c r="AN371" s="2" t="n">
+        <v>-0.002648616833431399</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -44435,6 +46667,12 @@
       <c r="AL372" s="2" t="n">
         <v>-0.008914450035945423</v>
       </c>
+      <c r="AM372" s="1" t="n">
+        <v>0.006911</v>
+      </c>
+      <c r="AN372" s="3" t="n">
+        <v>0.002611344842593905</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -44553,6 +46791,12 @@
       <c r="AL373" s="2" t="n">
         <v>-0.008785529715762339</v>
       </c>
+      <c r="AM373" s="1" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="AN373" s="2" t="n">
+        <v>-0.0007820646506777033</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -44671,6 +46915,12 @@
       <c r="AL374" s="2" t="n">
         <v>-0.001141552511415479</v>
       </c>
+      <c r="AM374" s="1" t="n">
+        <v>0.06968000000000001</v>
+      </c>
+      <c r="AN374" s="2" t="n">
+        <v>-0.004571428571428583</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -44789,6 +47039,12 @@
       <c r="AL375" s="2" t="n">
         <v>-0.006791598541064002</v>
       </c>
+      <c r="AM375" s="1" t="n">
+        <v>0.07907</v>
+      </c>
+      <c r="AN375" s="3" t="n">
+        <v>0.001266303659617613</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -44907,6 +47163,12 @@
       <c r="AL376" s="2" t="n">
         <v>-0.002062837194541496</v>
       </c>
+      <c r="AM376" s="1" t="n">
+        <v>0.06293</v>
+      </c>
+      <c r="AN376" s="3" t="n">
+        <v>0.0006360311655270849</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -45025,6 +47287,12 @@
       <c r="AL377" s="2" t="n">
         <v>-0.002470419971395262</v>
       </c>
+      <c r="AM377" s="1" t="n">
+        <v>0.07684000000000001</v>
+      </c>
+      <c r="AN377" s="3" t="n">
+        <v>0.001564129301355696</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -45143,6 +47411,12 @@
       <c r="AL378" s="2" t="n">
         <v>-0.004189255791030033</v>
       </c>
+      <c r="AM378" s="1" t="n">
+        <v>0.0004036</v>
+      </c>
+      <c r="AN378" s="2" t="n">
+        <v>-0.001237317495669419</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -45261,6 +47535,12 @@
       <c r="AL379" s="2" t="n">
         <v>-0.0002712600027126831</v>
       </c>
+      <c r="AM379" s="1" t="n">
+        <v>0.07344000000000001</v>
+      </c>
+      <c r="AN379" s="2" t="n">
+        <v>-0.003663003663003561</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -45379,6 +47659,12 @@
       <c r="AL380" s="3" t="n">
         <v>0.006583760058522393</v>
       </c>
+      <c r="AM380" s="1" t="n">
+        <v>0.001369</v>
+      </c>
+      <c r="AN380" s="2" t="n">
+        <v>-0.005087209302325626</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -45497,6 +47783,12 @@
       <c r="AL381" s="2" t="n">
         <v>-0.003935148748622614</v>
       </c>
+      <c r="AM381" s="1" t="n">
+        <v>6.346</v>
+      </c>
+      <c r="AN381" s="3" t="n">
+        <v>0.002844500632111219</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -45615,6 +47907,12 @@
       <c r="AL382" s="2" t="n">
         <v>-0.01198026779422128</v>
       </c>
+      <c r="AM382" s="1" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="AN382" s="2" t="n">
+        <v>-0.0007132667617688725</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -45733,6 +48031,12 @@
       <c r="AL383" s="2" t="n">
         <v>-0.001144164759725354</v>
       </c>
+      <c r="AM383" s="1" t="n">
+        <v>0.01743</v>
+      </c>
+      <c r="AN383" s="2" t="n">
+        <v>-0.001718213058419174</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -45851,6 +48155,12 @@
       <c r="AL384" s="2" t="n">
         <v>-0.002949852507374579</v>
       </c>
+      <c r="AM384" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="AN384" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -45969,6 +48279,12 @@
       <c r="AL385" s="2" t="n">
         <v>-0.00245098039215689</v>
       </c>
+      <c r="AM385" s="1" t="n">
+        <v>4.475</v>
+      </c>
+      <c r="AN385" s="2" t="n">
+        <v>-0.0004467277194551414</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -46087,6 +48403,12 @@
       <c r="AL386" s="3" t="n">
         <v>0.0007686395080706501</v>
       </c>
+      <c r="AM386" s="1" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="AN386" s="2" t="n">
+        <v>-0.001536098310291896</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -46205,6 +48527,12 @@
       <c r="AL387" s="2" t="n">
         <v>-0.002202270032186985</v>
       </c>
+      <c r="AM387" s="1" t="n">
+        <v>0.0005879</v>
+      </c>
+      <c r="AN387" s="2" t="n">
+        <v>-0.001867572156196897</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -46323,6 +48651,12 @@
       <c r="AL388" s="2" t="n">
         <v>-0.004374453193350805</v>
       </c>
+      <c r="AM388" s="1" t="n">
+        <v>0.01135</v>
+      </c>
+      <c r="AN388" s="2" t="n">
+        <v>-0.00263620386643223</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -46441,6 +48775,12 @@
       <c r="AL389" s="2" t="n">
         <v>-0.002209944751381317</v>
       </c>
+      <c r="AM389" s="1" t="n">
+        <v>0.00902</v>
+      </c>
+      <c r="AN389" s="2" t="n">
+        <v>-0.00110741971207083</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -46559,6 +48899,12 @@
       <c r="AL390" s="2" t="n">
         <v>-0.002914712964136283</v>
       </c>
+      <c r="AM390" s="1" t="n">
+        <v>0.07847</v>
+      </c>
+      <c r="AN390" s="2" t="n">
+        <v>-0.002669039145907497</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -46677,6 +49023,12 @@
       <c r="AL391" s="2" t="n">
         <v>-0.00499519692603259</v>
       </c>
+      <c r="AM391" s="1" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="AN391" s="2" t="n">
+        <v>-0.0007723498744932479</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -46795,6 +49147,12 @@
       <c r="AL392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM392" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="AN392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -46913,6 +49271,12 @@
       <c r="AL393" s="2" t="n">
         <v>-0.001893043066729691</v>
       </c>
+      <c r="AM393" s="1" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="AN393" s="3" t="n">
+        <v>0.004267425320056889</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -47031,6 +49395,12 @@
       <c r="AL394" s="2" t="n">
         <v>-0.001489572989076439</v>
       </c>
+      <c r="AM394" s="1" t="n">
+        <v>0.2003</v>
+      </c>
+      <c r="AN394" s="2" t="n">
+        <v>-0.003978120338140205</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -47149,6 +49519,12 @@
       <c r="AL395" s="2" t="n">
         <v>-0.002047082906857645</v>
       </c>
+      <c r="AM395" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="AN395" s="2" t="n">
+        <v>-0.00205128205128211</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -47267,6 +49643,12 @@
       <c r="AL396" s="2" t="n">
         <v>-0.003269160915365019</v>
       </c>
+      <c r="AM396" s="1" t="n">
+        <v>2.741</v>
+      </c>
+      <c r="AN396" s="2" t="n">
+        <v>-0.001093294460641441</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -47385,6 +49767,12 @@
       <c r="AL397" s="2" t="n">
         <v>-0.001581027667984191</v>
       </c>
+      <c r="AM397" s="1" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="AN397" s="3" t="n">
+        <v>0.003167062549485355</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -47503,6 +49891,12 @@
       <c r="AL398" s="2" t="n">
         <v>-0.001731255826341722</v>
       </c>
+      <c r="AM398" s="1" t="n">
+        <v>0.007586</v>
+      </c>
+      <c r="AN398" s="3" t="n">
+        <v>0.01200640341515472</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -47621,6 +50015,12 @@
       <c r="AL399" s="2" t="n">
         <v>-0.002715283165244292</v>
       </c>
+      <c r="AM399" s="1" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="AN399" s="2" t="n">
+        <v>-0.003889537145079739</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -47739,6 +50139,12 @@
       <c r="AL400" s="2" t="n">
         <v>-0.002510197678067046</v>
       </c>
+      <c r="AM400" s="1" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AN400" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -47857,6 +50263,12 @@
       <c r="AL401" s="3" t="n">
         <v>0.0004140215291195692</v>
       </c>
+      <c r="AM401" s="1" t="n">
+        <v>0.007239</v>
+      </c>
+      <c r="AN401" s="2" t="n">
+        <v>-0.001379500620775343</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -47975,6 +50387,12 @@
       <c r="AL402" s="2" t="n">
         <v>-0.002184837229626493</v>
       </c>
+      <c r="AM402" s="1" t="n">
+        <v>0.004564</v>
+      </c>
+      <c r="AN402" s="2" t="n">
+        <v>-0.0006568863586598491</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -48093,6 +50511,12 @@
       <c r="AL403" s="2" t="n">
         <v>-0.001883948756593822</v>
       </c>
+      <c r="AM403" s="1" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="AN403" s="2" t="n">
+        <v>-0.003775009437523597</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -48211,6 +50635,12 @@
       <c r="AL404" s="2" t="n">
         <v>-0.0070951585976628</v>
       </c>
+      <c r="AM404" s="1" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="AN404" s="2" t="n">
+        <v>-0.005044136191677203</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -48329,6 +50759,12 @@
       <c r="AL405" s="2" t="n">
         <v>-0.0007008527041233671</v>
       </c>
+      <c r="AM405" s="1" t="n">
+        <v>0.0008553</v>
+      </c>
+      <c r="AN405" s="2" t="n">
+        <v>-0.0002337814143775627</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -48447,6 +50883,12 @@
       <c r="AL406" s="2" t="n">
         <v>-0.001586986708986351</v>
       </c>
+      <c r="AM406" s="1" t="n">
+        <v>0.005036</v>
+      </c>
+      <c r="AN406" s="3" t="n">
+        <v>0.0005960659646333262</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -48565,6 +51007,12 @@
       <c r="AL407" s="2" t="n">
         <v>-0.00166805671392835</v>
       </c>
+      <c r="AM407" s="1" t="n">
+        <v>0.01191</v>
+      </c>
+      <c r="AN407" s="2" t="n">
+        <v>-0.005012531328320743</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -48683,6 +51131,12 @@
       <c r="AL408" s="3" t="n">
         <v>0.002022926500337131</v>
       </c>
+      <c r="AM408" s="1" t="n">
+        <v>0.001495</v>
+      </c>
+      <c r="AN408" s="3" t="n">
+        <v>0.006056527590847989</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -48801,6 +51255,12 @@
       <c r="AL409" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM409" s="1" t="n">
+        <v>0.03901</v>
+      </c>
+      <c r="AN409" s="2" t="n">
+        <v>-0.007631645891630495</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -48919,6 +51379,12 @@
       <c r="AL410" s="2" t="n">
         <v>-0.0006161429451634665</v>
       </c>
+      <c r="AM410" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="AN410" s="3" t="n">
+        <v>0.001233045622688203</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -49037,6 +51503,12 @@
       <c r="AL411" s="2" t="n">
         <v>-0.002628811777076764</v>
       </c>
+      <c r="AM411" s="1" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="AN411" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -49155,6 +51627,12 @@
       <c r="AL412" s="3" t="n">
         <v>0.0007419498441904509</v>
       </c>
+      <c r="AM412" s="1" t="n">
+        <v>0.06754</v>
+      </c>
+      <c r="AN412" s="3" t="n">
+        <v>0.001482799525504194</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -49273,6 +51751,12 @@
       <c r="AL413" s="2" t="n">
         <v>-0.001185302252074279</v>
       </c>
+      <c r="AM413" s="1" t="n">
+        <v>2528</v>
+      </c>
+      <c r="AN413" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -49391,6 +51875,12 @@
       <c r="AL414" s="2" t="n">
         <v>-0.00152207001522077</v>
       </c>
+      <c r="AM414" s="1" t="n">
+        <v>0.05253</v>
+      </c>
+      <c r="AN414" s="3" t="n">
+        <v>0.0009527439024390517</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -49509,6 +51999,12 @@
       <c r="AL415" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM415" s="1" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="AN415" s="3" t="n">
+        <v>0.0005714285714285085</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -49627,6 +52123,12 @@
       <c r="AL416" s="2" t="n">
         <v>-0.003335750543872286</v>
       </c>
+      <c r="AM416" s="1" t="n">
+        <v>0.06852</v>
+      </c>
+      <c r="AN416" s="2" t="n">
+        <v>-0.002910360884749792</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -49745,6 +52247,12 @@
       <c r="AL417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AN417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -49863,6 +52371,12 @@
       <c r="AL418" s="2" t="n">
         <v>-0.001984126984126949</v>
       </c>
+      <c r="AM418" s="1" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="AN418" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -49981,6 +52495,12 @@
       <c r="AL419" s="2" t="n">
         <v>-0.008064516129032209</v>
       </c>
+      <c r="AM419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AN419" s="3" t="n">
+        <v>0.008130081300812959</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -50099,6 +52619,12 @@
       <c r="AL420" s="2" t="n">
         <v>-0.004697286012526085</v>
       </c>
+      <c r="AM420" s="1" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="AN420" s="3" t="n">
+        <v>0.0005243838489774301</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -50217,6 +52743,12 @@
       <c r="AL421" s="2" t="n">
         <v>-0.001957451192499827</v>
       </c>
+      <c r="AM421" s="1" t="n">
+        <v>0.19357</v>
+      </c>
+      <c r="AN421" s="2" t="n">
+        <v>-0.0009290322580645856</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -50335,6 +52867,12 @@
       <c r="AL422" s="2" t="n">
         <v>-0.002348796241925917</v>
       </c>
+      <c r="AM422" s="1" t="n">
+        <v>0.03398</v>
+      </c>
+      <c r="AN422" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -50453,6 +52991,12 @@
       <c r="AL423" s="2" t="n">
         <v>-0.002120141342756147</v>
       </c>
+      <c r="AM423" s="1" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="AN423" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -50571,6 +53115,12 @@
       <c r="AL424" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM424" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="AN424" s="2" t="n">
+        <v>-0.003780718336483942</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -50689,6 +53239,12 @@
       <c r="AL425" s="2" t="n">
         <v>-0.002868068833651957</v>
       </c>
+      <c r="AM425" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="AN425" s="2" t="n">
+        <v>-0.004793863854266543</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -50807,6 +53363,12 @@
       <c r="AL426" s="2" t="n">
         <v>-0.002401129943502898</v>
       </c>
+      <c r="AM426" s="1" t="n">
+        <v>0.007069</v>
+      </c>
+      <c r="AN426" s="3" t="n">
+        <v>0.0008494973807163994</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -50925,6 +53487,12 @@
       <c r="AL427" s="2" t="n">
         <v>-0.001176932130247108</v>
       </c>
+      <c r="AM427" s="1" t="n">
+        <v>0.02557</v>
+      </c>
+      <c r="AN427" s="3" t="n">
+        <v>0.004320502749410801</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -51043,6 +53611,12 @@
       <c r="AL428" s="2" t="n">
         <v>-0.001369180980831324</v>
       </c>
+      <c r="AM428" s="1" t="n">
+        <v>0.008033</v>
+      </c>
+      <c r="AN428" s="3" t="n">
+        <v>0.001246416552411765</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -51161,6 +53735,12 @@
       <c r="AL429" s="2" t="n">
         <v>-0.004055150040551616</v>
       </c>
+      <c r="AM429" s="1" t="n">
+        <v>0.01226</v>
+      </c>
+      <c r="AN429" s="2" t="n">
+        <v>-0.00162866449511394</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -51279,6 +53859,12 @@
       <c r="AL430" s="2" t="n">
         <v>-0.0004507888805409804</v>
       </c>
+      <c r="AM430" s="1" t="n">
+        <v>0.06645</v>
+      </c>
+      <c r="AN430" s="2" t="n">
+        <v>-0.00105231509320506</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -51397,6 +53983,12 @@
       <c r="AL431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM431" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AN431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -51515,6 +54107,12 @@
       <c r="AL432" s="2" t="n">
         <v>-0.003127280308558377</v>
       </c>
+      <c r="AM432" s="1" t="n">
+        <v>0.00953</v>
+      </c>
+      <c r="AN432" s="2" t="n">
+        <v>-0.003450799958172126</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -51633,6 +54231,12 @@
       <c r="AL433" s="2" t="n">
         <v>-0.003155339805825198</v>
       </c>
+      <c r="AM433" s="1" t="n">
+        <v>0.04097</v>
+      </c>
+      <c r="AN433" s="2" t="n">
+        <v>-0.002434867299732234</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -51751,6 +54355,12 @@
       <c r="AL434" s="3" t="n">
         <v>0.008466603951081824</v>
       </c>
+      <c r="AM434" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AN434" s="3" t="n">
+        <v>0.002798507462686453</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -51869,6 +54479,12 @@
       <c r="AL435" s="2" t="n">
         <v>-0.001290322580645193</v>
       </c>
+      <c r="AM435" s="1" t="n">
+        <v>0.001546</v>
+      </c>
+      <c r="AN435" s="2" t="n">
+        <v>-0.001291989664082579</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -51987,6 +54603,12 @@
       <c r="AL436" s="2" t="n">
         <v>-0.0007288629737609032</v>
       </c>
+      <c r="AM436" s="1" t="n">
+        <v>0.02734</v>
+      </c>
+      <c r="AN436" s="2" t="n">
+        <v>-0.002917578409919774</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -52105,6 +54727,12 @@
       <c r="AL437" s="3" t="n">
         <v>0.004886988393402535</v>
       </c>
+      <c r="AM437" s="1" t="n">
+        <v>0.08227</v>
+      </c>
+      <c r="AN437" s="3" t="n">
+        <v>0.0002431610942248297</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -52223,6 +54851,12 @@
       <c r="AL438" s="2" t="n">
         <v>-0.00173611111111104</v>
       </c>
+      <c r="AM438" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="AN438" s="2" t="n">
+        <v>-0.002608695652173988</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -52341,6 +54975,12 @@
       <c r="AL439" s="2" t="n">
         <v>-0.002574002574002576</v>
       </c>
+      <c r="AM439" s="1" t="n">
+        <v>1.549</v>
+      </c>
+      <c r="AN439" s="2" t="n">
+        <v>-0.0006451612903226529</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -52459,6 +55099,12 @@
       <c r="AL440" s="2" t="n">
         <v>-0.003294892915980192</v>
       </c>
+      <c r="AM440" s="1" t="n">
+        <v>0.001814</v>
+      </c>
+      <c r="AN440" s="2" t="n">
+        <v>-0.0005509641873277773</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -52577,6 +55223,12 @@
       <c r="AL441" s="2" t="n">
         <v>-0.001913091008472277</v>
       </c>
+      <c r="AM441" s="1" t="n">
+        <v>0.03673</v>
+      </c>
+      <c r="AN441" s="3" t="n">
+        <v>0.00575027382256303</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -52695,6 +55347,12 @@
       <c r="AL442" s="2" t="n">
         <v>-0.002188183807439925</v>
       </c>
+      <c r="AM442" s="1" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AN442" s="2" t="n">
+        <v>-0.002192982456140261</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -52813,6 +55471,12 @@
       <c r="AL443" s="2" t="n">
         <v>-0.0007887057338908174</v>
       </c>
+      <c r="AM443" s="1" t="n">
+        <v>0.12682</v>
+      </c>
+      <c r="AN443" s="3" t="n">
+        <v>0.001026126766121961</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -52931,6 +55595,12 @@
       <c r="AL444" s="3" t="n">
         <v>0.004419793742958571</v>
       </c>
+      <c r="AM444" s="1" t="n">
+        <v>0.011528</v>
+      </c>
+      <c r="AN444" s="2" t="n">
+        <v>-0.005349439171699703</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -53049,6 +55719,12 @@
       <c r="AL445" s="2" t="n">
         <v>-0.002608371630853333</v>
       </c>
+      <c r="AM445" s="1" t="n">
+        <v>0.08036</v>
+      </c>
+      <c r="AN445" s="3" t="n">
+        <v>0.000747198007472036</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -53167,6 +55843,12 @@
       <c r="AL446" s="2" t="n">
         <v>-0.001866542230518011</v>
       </c>
+      <c r="AM446" s="1" t="n">
+        <v>0.0002134</v>
+      </c>
+      <c r="AN446" s="2" t="n">
+        <v>-0.002337540906965802</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -53285,6 +55967,12 @@
       <c r="AL447" s="2" t="n">
         <v>-0.004511278195488668</v>
       </c>
+      <c r="AM447" s="1" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="AN447" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -53403,6 +56091,12 @@
       <c r="AL448" s="3" t="n">
         <v>0.01293410734290668</v>
       </c>
+      <c r="AM448" s="1" t="n">
+        <v>0.09968</v>
+      </c>
+      <c r="AN448" s="3" t="n">
+        <v>0.002211944500301608</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -53521,6 +56215,12 @@
       <c r="AL449" s="3" t="n">
         <v>0.0005970149253730841</v>
       </c>
+      <c r="AM449" s="1" t="n">
+        <v>0.001678</v>
+      </c>
+      <c r="AN449" s="3" t="n">
+        <v>0.001193317422434397</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -53639,6 +56339,12 @@
       <c r="AL450" s="2" t="n">
         <v>-0.002886002886002956</v>
       </c>
+      <c r="AM450" s="1" t="n">
+        <v>0.0002073</v>
+      </c>
+      <c r="AN450" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -53757,6 +56463,12 @@
       <c r="AL451" s="2" t="n">
         <v>-0.007210626185958302</v>
       </c>
+      <c r="AM451" s="1" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="AN451" s="3" t="n">
+        <v>0.001146788990825732</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -53875,6 +56587,12 @@
       <c r="AL452" s="2" t="n">
         <v>-0.002225519287833789</v>
       </c>
+      <c r="AM452" s="1" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="AN452" s="2" t="n">
+        <v>-0.001486988847583686</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -53993,6 +56711,12 @@
       <c r="AL453" s="2" t="n">
         <v>-0.005169442848937362</v>
       </c>
+      <c r="AM453" s="1" t="n">
+        <v>0.0001733</v>
+      </c>
+      <c r="AN453" s="3" t="n">
+        <v>0.0005773672055427392</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -54111,6 +56835,12 @@
       <c r="AL454" s="3" t="n">
         <v>0.007255577725376466</v>
       </c>
+      <c r="AM454" s="1" t="n">
+        <v>0.11219</v>
+      </c>
+      <c r="AN454" s="3" t="n">
+        <v>0.01017468035296229</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -54229,6 +56959,12 @@
       <c r="AL455" s="2" t="n">
         <v>-0.002399999999999958</v>
       </c>
+      <c r="AM455" s="1" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="AN455" s="3" t="n">
+        <v>0.001603849238171546</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -54347,6 +57083,12 @@
       <c r="AL456" s="3" t="n">
         <v>0.0008133641994618735</v>
       </c>
+      <c r="AM456" s="1" t="n">
+        <v>0.015978</v>
+      </c>
+      <c r="AN456" s="2" t="n">
+        <v>-0.001125281320330123</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -54465,6 +57207,12 @@
       <c r="AL457" s="2" t="n">
         <v>-0.0002995357196344763</v>
       </c>
+      <c r="AM457" s="1" t="n">
+        <v>0.006676</v>
+      </c>
+      <c r="AN457" s="3" t="n">
+        <v>0.0001498127340822869</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -54583,6 +57331,12 @@
       <c r="AL458" s="2" t="n">
         <v>-0.0006216328222129444</v>
       </c>
+      <c r="AM458" s="1" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="AN458" s="2" t="n">
+        <v>-0.002902757619738777</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -54701,6 +57455,12 @@
       <c r="AL459" s="2" t="n">
         <v>-0.0009460737937560385</v>
       </c>
+      <c r="AM459" s="1" t="n">
+        <v>0.006347</v>
+      </c>
+      <c r="AN459" s="3" t="n">
+        <v>0.001736111111111205</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -54819,6 +57579,12 @@
       <c r="AL460" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM460" s="1" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="AN460" s="2" t="n">
+        <v>-0.00291757840991985</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -54937,6 +57703,12 @@
       <c r="AL461" s="3" t="n">
         <v>0.002112049799911024</v>
       </c>
+      <c r="AM461" s="1" t="n">
+        <v>0.09011</v>
+      </c>
+      <c r="AN461" s="2" t="n">
+        <v>-0.0004437049362173974</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -55055,6 +57827,12 @@
       <c r="AL462" s="3" t="n">
         <v>0.0006660746003552897</v>
       </c>
+      <c r="AM462" s="1" t="n">
+        <v>0.04505</v>
+      </c>
+      <c r="AN462" s="2" t="n">
+        <v>-0.0004437541601952337</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -55173,6 +57951,12 @@
       <c r="AL463" s="2" t="n">
         <v>-0.001428571428571494</v>
       </c>
+      <c r="AM463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="AN463" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -55291,6 +58075,12 @@
       <c r="AL464" s="2" t="n">
         <v>-0.003843197540353492</v>
       </c>
+      <c r="AM464" s="1" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="AN464" s="3" t="n">
+        <v>0.0007716049382715199</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -55409,6 +58199,12 @@
       <c r="AL465" s="2" t="n">
         <v>-0.001080302484695796</v>
       </c>
+      <c r="AM465" s="1" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="AN465" s="2" t="n">
+        <v>-0.002523431867339504</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -55527,6 +58323,12 @@
       <c r="AL466" s="2" t="n">
         <v>-0.001409443269908387</v>
       </c>
+      <c r="AM466" s="1" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="AN466" s="2" t="n">
+        <v>-0.002117148906139812</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -55645,6 +58447,12 @@
       <c r="AL467" s="2" t="n">
         <v>-0.002088772845953099</v>
       </c>
+      <c r="AM467" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="AN467" s="2" t="n">
+        <v>-0.001046572475143861</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -55763,6 +58571,12 @@
       <c r="AL468" s="2" t="n">
         <v>-0.009832841691248711</v>
       </c>
+      <c r="AM468" s="1" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AN468" s="2" t="n">
+        <v>-0.00297914597815298</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -55881,6 +58695,12 @@
       <c r="AL469" s="2" t="n">
         <v>-0.002520161290322583</v>
       </c>
+      <c r="AM469" s="1" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="AN469" s="2" t="n">
+        <v>-0.002779181404749848</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -55999,6 +58819,12 @@
       <c r="AL470" s="2" t="n">
         <v>-0.002277904328018225</v>
       </c>
+      <c r="AM470" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AN470" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -56117,6 +58943,12 @@
       <c r="AL471" s="2" t="n">
         <v>-0.002485243864554212</v>
       </c>
+      <c r="AM471" s="1" t="n">
+        <v>3.213</v>
+      </c>
+      <c r="AN471" s="3" t="n">
+        <v>0.0006228589224541339</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -56235,6 +59067,12 @@
       <c r="AL472" s="3" t="n">
         <v>0.0009544261512765061</v>
       </c>
+      <c r="AM472" s="1" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="AN472" s="2" t="n">
+        <v>-0.0002383790226460801</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -56353,6 +59191,12 @@
       <c r="AL473" s="2" t="n">
         <v>-0.003194888178913741</v>
       </c>
+      <c r="AM473" s="1" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="AN473" s="3" t="n">
+        <v>0.0008012820512821409</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -56471,6 +59315,12 @@
       <c r="AL474" s="2" t="n">
         <v>-0.001754385964912412</v>
       </c>
+      <c r="AM474" s="1" t="n">
+        <v>0.008527</v>
+      </c>
+      <c r="AN474" s="2" t="n">
+        <v>-0.0009373169302869745</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -56589,6 +59439,12 @@
       <c r="AL475" s="2" t="n">
         <v>-0.003124999999999956</v>
       </c>
+      <c r="AM475" s="1" t="n">
+        <v>0.04191</v>
+      </c>
+      <c r="AN475" s="3" t="n">
+        <v>0.01061007957559689</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -56707,6 +59563,12 @@
       <c r="AL476" s="2" t="n">
         <v>-0.003170174993659653</v>
       </c>
+      <c r="AM476" s="1" t="n">
+        <v>0.07847</v>
+      </c>
+      <c r="AN476" s="2" t="n">
+        <v>-0.001780943900267157</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -56825,6 +59687,12 @@
       <c r="AL477" s="3" t="n">
         <v>0.001321391866098853</v>
       </c>
+      <c r="AM477" s="1" t="n">
+        <v>0.13632</v>
+      </c>
+      <c r="AN477" s="2" t="n">
+        <v>-0.0005865102639295949</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -56943,6 +59811,12 @@
       <c r="AL478" s="2" t="n">
         <v>-0.002106593638087127</v>
       </c>
+      <c r="AM478" s="1" t="n">
+        <v>0.04722</v>
+      </c>
+      <c r="AN478" s="2" t="n">
+        <v>-0.003166561114629603</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -57061,6 +59935,12 @@
       <c r="AL479" s="2" t="n">
         <v>-0.002814258911819773</v>
       </c>
+      <c r="AM479" s="1" t="n">
+        <v>0.005311</v>
+      </c>
+      <c r="AN479" s="2" t="n">
+        <v>-0.0007525870178740415</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -57179,6 +60059,12 @@
       <c r="AL480" s="3" t="n">
         <v>0.0003575259206292063</v>
       </c>
+      <c r="AM480" s="1" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AN480" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -57297,6 +60183,12 @@
       <c r="AL481" s="2" t="n">
         <v>-0.001449466332850164</v>
       </c>
+      <c r="AM481" s="1" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="AN481" s="2" t="n">
+        <v>-0.001055687516495074</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -57415,6 +60307,12 @@
       <c r="AL482" s="2" t="n">
         <v>-0.00201072386058973</v>
       </c>
+      <c r="AM482" s="1" t="n">
+        <v>0.01488</v>
+      </c>
+      <c r="AN482" s="2" t="n">
+        <v>-0.0006715916722632365</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -57533,6 +60431,12 @@
       <c r="AL483" s="2" t="n">
         <v>-0.003984063745019896</v>
       </c>
+      <c r="AM483" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AN483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -57651,6 +60555,12 @@
       <c r="AL484" s="2" t="n">
         <v>-0.002788104089219378</v>
       </c>
+      <c r="AM484" s="1" t="n">
+        <v>0.02149</v>
+      </c>
+      <c r="AN484" s="3" t="n">
+        <v>0.001397949673811686</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -57769,6 +60679,12 @@
       <c r="AL485" s="2" t="n">
         <v>-0.0007168458781362958</v>
       </c>
+      <c r="AM485" s="1" t="n">
+        <v>0.008385999999999999</v>
+      </c>
+      <c r="AN485" s="3" t="n">
+        <v>0.002630320420851202</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -57887,6 +60803,12 @@
       <c r="AL486" s="2" t="n">
         <v>-0.001071524243236029</v>
       </c>
+      <c r="AM486" s="1" t="n">
+        <v>0.007487</v>
+      </c>
+      <c r="AN486" s="3" t="n">
+        <v>0.003888441941539221</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -58005,6 +60927,12 @@
       <c r="AL487" s="2" t="n">
         <v>-0.008857395925597882</v>
       </c>
+      <c r="AM487" s="1" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="AN487" s="2" t="n">
+        <v>-0.001787310098302107</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -58123,6 +61051,12 @@
       <c r="AL488" s="3" t="n">
         <v>0.001834664364342721</v>
       </c>
+      <c r="AM488" s="1" t="n">
+        <v>0.009292999999999999</v>
+      </c>
+      <c r="AN488" s="3" t="n">
+        <v>0.001077237961865732</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -58241,6 +61175,12 @@
       <c r="AL489" s="2" t="n">
         <v>-0.004107830551989741</v>
       </c>
+      <c r="AM489" s="1" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="AN489" s="3" t="n">
+        <v>0.0007733952049497872</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -58359,6 +61299,12 @@
       <c r="AL490" s="2" t="n">
         <v>-0.01050275482093663</v>
       </c>
+      <c r="AM490" s="1" t="n">
+        <v>0.05754</v>
+      </c>
+      <c r="AN490" s="3" t="n">
+        <v>0.001218026796589536</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -58477,6 +61423,12 @@
       <c r="AL491" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM491" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="AN491" s="2" t="n">
+        <v>-0.00205128205128211</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -58595,6 +61547,12 @@
       <c r="AL492" s="2" t="n">
         <v>-0.003028009084027255</v>
       </c>
+      <c r="AM492" s="1" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="AN492" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -58713,6 +61671,12 @@
       <c r="AL493" s="2" t="n">
         <v>-0.003698435277382594</v>
       </c>
+      <c r="AM493" s="1" t="n">
+        <v>0.03508</v>
+      </c>
+      <c r="AN493" s="3" t="n">
+        <v>0.001713306681895989</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -58831,6 +61795,12 @@
       <c r="AL494" s="2" t="n">
         <v>-0.001775147928994011</v>
       </c>
+      <c r="AM494" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="AN494" s="2" t="n">
+        <v>-0.0005927682276229753</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -58949,6 +61919,12 @@
       <c r="AL495" s="2" t="n">
         <v>-0.0008510638297871993</v>
       </c>
+      <c r="AM495" s="1" t="n">
+        <v>0.04687</v>
+      </c>
+      <c r="AN495" s="2" t="n">
+        <v>-0.001916524701873931</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -59067,6 +62043,12 @@
       <c r="AL496" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM496" s="1" t="n">
+        <v>0.04815</v>
+      </c>
+      <c r="AN496" s="3" t="n">
+        <v>0.0004155412424682981</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -59185,6 +62167,12 @@
       <c r="AL497" s="2" t="n">
         <v>-0.001410153102336698</v>
       </c>
+      <c r="AM497" s="1" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="AN497" s="2" t="n">
+        <v>-0.001412144442202958</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -59303,6 +62291,12 @@
       <c r="AL498" s="2" t="n">
         <v>-0.0003454231433505665</v>
       </c>
+      <c r="AM498" s="1" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="AN498" s="3" t="n">
+        <v>0.003455425017277128</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -59421,6 +62415,12 @@
       <c r="AL499" s="2" t="n">
         <v>-0.001834862385321102</v>
       </c>
+      <c r="AM499" s="1" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="AN499" s="2" t="n">
+        <v>-0.00147058823529416</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -59539,6 +62539,12 @@
       <c r="AL500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AM500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AN500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -59657,6 +62663,12 @@
       <c r="AL501" s="2" t="n">
         <v>-0.005334081976417623</v>
       </c>
+      <c r="AM501" s="1" t="n">
+        <v>0.03551</v>
+      </c>
+      <c r="AN501" s="3" t="n">
+        <v>0.002257973468811649</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -59775,6 +62787,12 @@
       <c r="AL502" s="2" t="n">
         <v>-0.0003134796238243299</v>
       </c>
+      <c r="AM502" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="AN502" s="3" t="n">
+        <v>0.002195045468799016</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -59893,6 +62911,12 @@
       <c r="AL503" s="2" t="n">
         <v>-0.001796253528355161</v>
       </c>
+      <c r="AM503" s="1" t="n">
+        <v>0.007703</v>
+      </c>
+      <c r="AN503" s="2" t="n">
+        <v>-0.009897172236503833</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -60011,6 +63035,12 @@
       <c r="AL504" s="2" t="n">
         <v>-0.00264200792602378</v>
       </c>
+      <c r="AM504" s="1" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="AN504" s="2" t="n">
+        <v>-0.002317880794702026</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -60129,6 +63159,12 @@
       <c r="AL505" s="2" t="n">
         <v>-0.001079476453919729</v>
       </c>
+      <c r="AM505" s="1" t="n">
+        <v>0.000742</v>
+      </c>
+      <c r="AN505" s="3" t="n">
+        <v>0.002296366337971075</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -60247,6 +63283,12 @@
       <c r="AL506" s="2" t="n">
         <v>-0.001374570446735244</v>
       </c>
+      <c r="AM506" s="1" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="AN506" s="2" t="n">
+        <v>-0.0003441156228494304</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -60365,6 +63407,12 @@
       <c r="AL507" s="2" t="n">
         <v>-0.003507541213609117</v>
       </c>
+      <c r="AM507" s="1" t="n">
+        <v>0.002845</v>
+      </c>
+      <c r="AN507" s="3" t="n">
+        <v>0.001407954945441627</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -60483,6 +63531,12 @@
       <c r="AL508" s="2" t="n">
         <v>-0.0006326111023248201</v>
       </c>
+      <c r="AM508" s="1" t="n">
+        <v>0.06322</v>
+      </c>
+      <c r="AN508" s="3" t="n">
+        <v>0.0004747586643456599</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -60601,6 +63655,12 @@
       <c r="AL509" s="3" t="n">
         <v>0.002241147467503513</v>
       </c>
+      <c r="AM509" s="1" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="AN509" s="2" t="n">
+        <v>-0.01073345259391772</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -60719,6 +63779,12 @@
       <c r="AL510" s="2" t="n">
         <v>-0.003000954849270147</v>
       </c>
+      <c r="AM510" s="1" t="n">
+        <v>0.0007306</v>
+      </c>
+      <c r="AN510" s="2" t="n">
+        <v>-0.0004104528663292673</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -60837,6 +63903,12 @@
       <c r="AL511" s="2" t="n">
         <v>-0.0003639010189228129</v>
       </c>
+      <c r="AM511" s="1" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="AN511" s="2" t="n">
+        <v>-0.00145613396432476</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -60955,6 +64027,12 @@
       <c r="AL512" s="3" t="n">
         <v>0.001242236024844751</v>
       </c>
+      <c r="AM512" s="1" t="n">
+        <v>0.0004813</v>
+      </c>
+      <c r="AN512" s="2" t="n">
+        <v>-0.004755996691480566</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -61073,6 +64151,12 @@
       <c r="AL513" s="2" t="n">
         <v>-0.005251720391162597</v>
       </c>
+      <c r="AM513" s="1" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="AN513" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -61191,6 +64275,12 @@
       <c r="AL514" s="2" t="n">
         <v>-0.003635161929940482</v>
       </c>
+      <c r="AM514" s="1" t="n">
+        <v>0.03016</v>
+      </c>
+      <c r="AN514" s="3" t="n">
+        <v>0.0003316749585406167</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -61309,6 +64399,12 @@
       <c r="AL515" s="2" t="n">
         <v>-0.0008771929824560666</v>
       </c>
+      <c r="AM515" s="1" t="n">
+        <v>0.001138</v>
+      </c>
+      <c r="AN515" s="2" t="n">
+        <v>-0.0008779631255488435</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -61427,6 +64523,12 @@
       <c r="AL516" s="2" t="n">
         <v>-0.0006066120715801734</v>
       </c>
+      <c r="AM516" s="1" t="n">
+        <v>0.006576</v>
+      </c>
+      <c r="AN516" s="2" t="n">
+        <v>-0.002124430955993949</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -61545,6 +64647,12 @@
       <c r="AL517" s="3" t="n">
         <v>0.0002510040160641597</v>
       </c>
+      <c r="AM517" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="AN517" s="3" t="n">
+        <v>0.0007528230865747114</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -61663,6 +64771,12 @@
       <c r="AL518" s="2" t="n">
         <v>-0.00289855072463763</v>
       </c>
+      <c r="AM518" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="AN518" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -61781,6 +64895,12 @@
       <c r="AL519" s="2" t="n">
         <v>-0.002301495972381955</v>
       </c>
+      <c r="AM519" s="1" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="AN519" s="3" t="n">
+        <v>0.002306805074971071</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -61899,6 +65019,12 @@
       <c r="AL520" s="2" t="n">
         <v>-0.001249219237976301</v>
       </c>
+      <c r="AM520" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="AN520" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -62017,6 +65143,12 @@
       <c r="AL521" s="2" t="n">
         <v>-0.001118568232662147</v>
       </c>
+      <c r="AM521" s="1" t="n">
+        <v>0.01782</v>
+      </c>
+      <c r="AN521" s="2" t="n">
+        <v>-0.002239641657334929</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -62135,6 +65267,12 @@
       <c r="AL522" s="2" t="n">
         <v>-0.002434570906877775</v>
       </c>
+      <c r="AM522" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="AN522" s="2" t="n">
+        <v>-0.002440512507626502</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -62253,6 +65391,12 @@
       <c r="AL523" s="2" t="n">
         <v>-0.006025548324897529</v>
       </c>
+      <c r="AM523" s="1" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="AN523" s="2" t="n">
+        <v>-0.0009699321047525857</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -62371,6 +65515,12 @@
       <c r="AL524" s="3" t="n">
         <v>0.0007042253521126474</v>
       </c>
+      <c r="AM524" s="1" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="AN524" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -62489,6 +65639,12 @@
       <c r="AL525" s="2" t="n">
         <v>-0.002827140549273046</v>
       </c>
+      <c r="AM525" s="1" t="n">
+        <v>0.02467</v>
+      </c>
+      <c r="AN525" s="2" t="n">
+        <v>-0.0008100445524503517</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -62607,6 +65763,12 @@
       <c r="AL526" s="2" t="n">
         <v>-0.0008333333333332416</v>
       </c>
+      <c r="AM526" s="1" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="AN526" s="2" t="n">
+        <v>-0.003336113427856642</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -62725,6 +65887,12 @@
       <c r="AL527" s="2" t="n">
         <v>-0.004873294346978407</v>
       </c>
+      <c r="AM527" s="1" t="n">
+        <v>0.07129000000000001</v>
+      </c>
+      <c r="AN527" s="2" t="n">
+        <v>-0.002518539247236597</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -62843,6 +66011,12 @@
       <c r="AL528" s="2" t="n">
         <v>-0.001853997682502982</v>
       </c>
+      <c r="AM528" s="1" t="n">
+        <v>0.04305</v>
+      </c>
+      <c r="AN528" s="2" t="n">
+        <v>-0.0004643603436266354</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -62961,6 +66135,12 @@
       <c r="AL529" s="2" t="n">
         <v>-0.001588057805304159</v>
       </c>
+      <c r="AM529" s="1" t="n">
+        <v>0.06297999999999999</v>
+      </c>
+      <c r="AN529" s="3" t="n">
+        <v>0.001749642118657531</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -63079,6 +66259,12 @@
       <c r="AL530" s="2" t="n">
         <v>-0.001397205588822368</v>
       </c>
+      <c r="AM530" s="1" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="AN530" s="2" t="n">
+        <v>-0.0001998800719566791</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -63197,6 +66383,12 @@
       <c r="AL531" s="2" t="n">
         <v>-0.002307692307692267</v>
       </c>
+      <c r="AM531" s="1" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="AN531" s="2" t="n">
+        <v>-0.001542020046260645</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -63315,6 +66507,12 @@
       <c r="AL532" s="2" t="n">
         <v>-0.002428998505231655</v>
       </c>
+      <c r="AM532" s="1" t="n">
+        <v>0.05341</v>
+      </c>
+      <c r="AN532" s="3" t="n">
+        <v>0.0003746019853905073</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -63433,6 +66631,12 @@
       <c r="AL533" s="2" t="n">
         <v>-0.001337255950789042</v>
       </c>
+      <c r="AM533" s="1" t="n">
+        <v>0.003726</v>
+      </c>
+      <c r="AN533" s="2" t="n">
+        <v>-0.002142474558114559</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -63551,6 +66755,12 @@
       <c r="AL534" s="2" t="n">
         <v>-0.0005844535359438281</v>
       </c>
+      <c r="AM534" s="1" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="AN534" s="2" t="n">
+        <v>-0.001754385964912412</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -63669,6 +66879,12 @@
       <c r="AL535" s="2" t="n">
         <v>-0.00884955752212396</v>
       </c>
+      <c r="AM535" s="1" t="n">
+        <v>1.13e-05</v>
+      </c>
+      <c r="AN535" s="3" t="n">
+        <v>0.008928571428571494</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -63787,6 +67003,12 @@
       <c r="AL536" s="3" t="n">
         <v>0.0006832156684126789</v>
       </c>
+      <c r="AM536" s="1" t="n">
+        <v>0.0004394</v>
+      </c>
+      <c r="AN536" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -63905,6 +67127,12 @@
       <c r="AL537" s="2" t="n">
         <v>-0.004153686396677062</v>
       </c>
+      <c r="AM537" s="1" t="n">
+        <v>0.00959</v>
+      </c>
+      <c r="AN537" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -64023,6 +67251,12 @@
       <c r="AL538" s="2" t="n">
         <v>-0.001099908340971668</v>
       </c>
+      <c r="AM538" s="1" t="n">
+        <v>0.05449</v>
+      </c>
+      <c r="AN538" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -64141,6 +67375,12 @@
       <c r="AL539" s="2" t="n">
         <v>-0.001612903225806599</v>
       </c>
+      <c r="AM539" s="1" t="n">
+        <v>0.6805</v>
+      </c>
+      <c r="AN539" s="2" t="n">
+        <v>-0.0005874577764722514</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -64259,6 +67499,12 @@
       <c r="AL540" s="2" t="n">
         <v>-0.001326259946949456</v>
       </c>
+      <c r="AM540" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="AN540" s="3" t="n">
+        <v>0.0006640106241699135</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -64377,6 +67623,12 @@
       <c r="AL541" s="2" t="n">
         <v>-0.003074558032282867</v>
       </c>
+      <c r="AM541" s="1" t="n">
+        <v>0.01298</v>
+      </c>
+      <c r="AN541" s="3" t="n">
+        <v>0.0007710100231302692</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -64495,6 +67747,12 @@
       <c r="AL542" s="2" t="n">
         <v>-0.0007204610951008352</v>
       </c>
+      <c r="AM542" s="1" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="AN542" s="3" t="n">
+        <v>0.002162941600576696</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -64613,6 +67871,12 @@
       <c r="AL543" s="2" t="n">
         <v>-0.0001753770606805167</v>
       </c>
+      <c r="AM543" s="1" t="n">
+        <v>0.05692</v>
+      </c>
+      <c r="AN543" s="2" t="n">
+        <v>-0.001578670408700225</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN543"/>
+  <dimension ref="A1:AP543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -466,6 +466,8 @@
     <col width="18" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -669,6 +671,16 @@
           <t>change_04:45</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>price_05:00</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>change_05:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -793,6 +805,12 @@
       <c r="AN2" s="2" t="n">
         <v>-0.002390747805990816</v>
       </c>
+      <c r="AO2" s="1" t="n">
+        <v>70127</v>
+      </c>
+      <c r="AP2" s="3" t="n">
+        <v>0.0003437803571607711</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -917,6 +935,12 @@
       <c r="AN3" s="2" t="n">
         <v>-0.002696187581079329</v>
       </c>
+      <c r="AO3" s="1" t="n">
+        <v>2061.44</v>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>0.0005484611539040772</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1041,6 +1065,12 @@
       <c r="AN4" s="2" t="n">
         <v>-0.002539242843951972</v>
       </c>
+      <c r="AO4" s="1" t="n">
+        <v>86.41</v>
+      </c>
+      <c r="AP4" s="2" t="n">
+        <v>-0.0001157139551030446</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1165,6 +1195,12 @@
       <c r="AN5" s="2" t="n">
         <v>-0.009008172362555708</v>
       </c>
+      <c r="AO5" s="1" t="n">
+        <v>0.010667</v>
+      </c>
+      <c r="AP5" s="2" t="n">
+        <v>-0.0003748477181145657</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1289,6 +1325,12 @@
       <c r="AN6" s="2" t="n">
         <v>-0.001165161666181216</v>
       </c>
+      <c r="AO6" s="1" t="n">
+        <v>1.3711</v>
+      </c>
+      <c r="AP6" s="2" t="n">
+        <v>-0.0003645377661125291</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1413,6 +1455,12 @@
       <c r="AN7" s="3" t="n">
         <v>0.001594048884165753</v>
       </c>
+      <c r="AO7" s="1" t="n">
+        <v>0.09407</v>
+      </c>
+      <c r="AP7" s="2" t="n">
+        <v>-0.001909814323607423</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1537,6 +1585,12 @@
       <c r="AN8" s="3" t="n">
         <v>0.001326978280886083</v>
       </c>
+      <c r="AO8" s="1" t="n">
+        <v>37.059</v>
+      </c>
+      <c r="AP8" s="3" t="n">
+        <v>0.002271805273833565</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1661,6 +1715,12 @@
       <c r="AN9" s="2" t="n">
         <v>-0.005039306591413026</v>
       </c>
+      <c r="AO9" s="1" t="n">
+        <v>0.04881</v>
+      </c>
+      <c r="AP9" s="2" t="n">
+        <v>-0.01114262560777962</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1785,6 +1845,12 @@
       <c r="AN10" s="2" t="n">
         <v>-0.01354499647830091</v>
       </c>
+      <c r="AO10" s="1" t="n">
+        <v>18.299</v>
+      </c>
+      <c r="AP10" s="3" t="n">
+        <v>0.005053001592793912</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1909,6 +1975,12 @@
       <c r="AN11" s="2" t="n">
         <v>-0.0010768071130802</v>
       </c>
+      <c r="AO11" s="1" t="n">
+        <v>649.86</v>
+      </c>
+      <c r="AP11" s="3" t="n">
+        <v>0.000754577513590109</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2033,6 +2105,12 @@
       <c r="AN12" s="2" t="n">
         <v>-0.007007233273056039</v>
       </c>
+      <c r="AO12" s="1" t="n">
+        <v>0.8861</v>
+      </c>
+      <c r="AP12" s="3" t="n">
+        <v>0.008536307762349135</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2157,6 +2235,12 @@
       <c r="AN13" s="3" t="n">
         <v>0.0003855421686747591</v>
       </c>
+      <c r="AO13" s="1" t="n">
+        <v>207.4</v>
+      </c>
+      <c r="AP13" s="2" t="n">
+        <v>-0.0008671355621929223</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2281,6 +2365,12 @@
       <c r="AN14" s="2" t="n">
         <v>-0.002279680844681735</v>
       </c>
+      <c r="AO14" s="1" t="n">
+        <v>0.0033145</v>
+      </c>
+      <c r="AP14" s="2" t="n">
+        <v>-0.003517527508868951</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2405,6 +2495,12 @@
       <c r="AN15" s="3" t="n">
         <v>0.007181659147408185</v>
       </c>
+      <c r="AO15" s="1" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AP15" s="2" t="n">
+        <v>-0.005820154188378044</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2529,6 +2625,12 @@
       <c r="AN16" s="2" t="n">
         <v>-0.0008211023298778845</v>
       </c>
+      <c r="AO16" s="1" t="n">
+        <v>0.9719</v>
+      </c>
+      <c r="AP16" s="2" t="n">
+        <v>-0.001643554185927114</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2653,6 +2755,12 @@
       <c r="AN17" s="2" t="n">
         <v>-0.007518796992481157</v>
       </c>
+      <c r="AO17" s="1" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="AP17" s="2" t="n">
+        <v>-0.03030303030303025</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2777,6 +2885,12 @@
       <c r="AN18" s="2" t="n">
         <v>-0.002714720336999825</v>
       </c>
+      <c r="AO18" s="1" t="n">
+        <v>212.17</v>
+      </c>
+      <c r="AP18" s="2" t="n">
+        <v>-0.004223963955507607</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2901,6 +3015,12 @@
       <c r="AN19" s="2" t="n">
         <v>-0.000381679389312935</v>
       </c>
+      <c r="AO19" s="1" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="AP19" s="2" t="n">
+        <v>-0.0007636502481864584</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3025,6 +3145,12 @@
       <c r="AN20" s="2" t="n">
         <v>-0.00212452050752442</v>
       </c>
+      <c r="AO20" s="1" t="n">
+        <v>0.016863</v>
+      </c>
+      <c r="AP20" s="2" t="n">
+        <v>-0.00272044473357389</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3149,6 +3275,12 @@
       <c r="AN21" s="2" t="n">
         <v>-0.0003123698458973696</v>
       </c>
+      <c r="AO21" s="1" t="n">
+        <v>9.603999999999999</v>
+      </c>
+      <c r="AP21" s="3" t="n">
+        <v>0.0003124674513069823</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3273,6 +3405,12 @@
       <c r="AN22" s="2" t="n">
         <v>-0.007803121248499374</v>
       </c>
+      <c r="AO22" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="AP22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3397,6 +3535,12 @@
       <c r="AN23" s="2" t="n">
         <v>-0.001520890725436267</v>
       </c>
+      <c r="AO23" s="1" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AP23" s="3" t="n">
+        <v>0.004023566604397219</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3521,6 +3665,12 @@
       <c r="AN24" s="3" t="n">
         <v>0.001158748551564312</v>
       </c>
+      <c r="AO24" s="1" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="AP24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3645,6 +3795,12 @@
       <c r="AN25" s="2" t="n">
         <v>-0.001557632398753821</v>
       </c>
+      <c r="AO25" s="1" t="n">
+        <v>8.967000000000001</v>
+      </c>
+      <c r="AP25" s="2" t="n">
+        <v>-0.0007800312012480135</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3769,6 +3925,12 @@
       <c r="AN26" s="3" t="n">
         <v>0.003018867924528305</v>
       </c>
+      <c r="AO26" s="1" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AP26" s="3" t="n">
+        <v>0.003009781790820168</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3893,6 +4055,12 @@
       <c r="AN27" s="3" t="n">
         <v>3.934846806573124e-05</v>
       </c>
+      <c r="AO27" s="1" t="n">
+        <v>5089.21</v>
+      </c>
+      <c r="AP27" s="3" t="n">
+        <v>0.001223689206549738</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4017,6 +4185,12 @@
       <c r="AN28" s="3" t="n">
         <v>0.002244668911335642</v>
       </c>
+      <c r="AO28" s="1" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AP28" s="2" t="n">
+        <v>-0.001399776035834268</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4141,6 +4315,12 @@
       <c r="AN29" s="3" t="n">
         <v>0.003036053130929794</v>
       </c>
+      <c r="AO29" s="1" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="AP29" s="2" t="n">
+        <v>-0.0007567158531970412</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4265,6 +4445,12 @@
       <c r="AN30" s="2" t="n">
         <v>-0.01422103953552661</v>
       </c>
+      <c r="AO30" s="1" t="n">
+        <v>0.57605</v>
+      </c>
+      <c r="AP30" s="3" t="n">
+        <v>0.009746007817840624</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4389,6 +4575,12 @@
       <c r="AN31" s="3" t="n">
         <v>0.000963855421686666</v>
       </c>
+      <c r="AO31" s="1" t="n">
+        <v>0.002076</v>
+      </c>
+      <c r="AP31" s="2" t="n">
+        <v>-0.0004814636494943183</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4513,6 +4705,12 @@
       <c r="AN32" s="3" t="n">
         <v>0.004495078663876639</v>
       </c>
+      <c r="AO32" s="1" t="n">
+        <v>1.2876</v>
+      </c>
+      <c r="AP32" s="2" t="n">
+        <v>-0.006558135946300402</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4637,6 +4835,12 @@
       <c r="AN33" s="2" t="n">
         <v>-0.0002984183825723336</v>
       </c>
+      <c r="AO33" s="1" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AP33" s="2" t="n">
+        <v>-0.006268656716418048</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4761,6 +4965,12 @@
       <c r="AN34" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO34" s="1" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="AP34" s="3" t="n">
+        <v>0.001328903654485051</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4885,6 +5095,12 @@
       <c r="AN35" s="2" t="n">
         <v>-4.404704224107345e-05</v>
       </c>
+      <c r="AO35" s="1" t="n">
+        <v>453.81</v>
+      </c>
+      <c r="AP35" s="2" t="n">
+        <v>-0.0005065632983878473</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5009,6 +5225,12 @@
       <c r="AN36" s="2" t="n">
         <v>-0.001898333684876604</v>
       </c>
+      <c r="AO36" s="1" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="AP36" s="2" t="n">
+        <v>-0.0006339814032122199</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5133,6 +5355,12 @@
       <c r="AN37" s="2" t="n">
         <v>-0.000998858447488633</v>
       </c>
+      <c r="AO37" s="1" t="n">
+        <v>0.7007</v>
+      </c>
+      <c r="AP37" s="3" t="n">
+        <v>0.0008570204256535424</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5257,6 +5485,12 @@
       <c r="AN38" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO38" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>-0.001897533206831042</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5381,6 +5615,12 @@
       <c r="AN39" s="2" t="n">
         <v>-0.005575038215987684</v>
       </c>
+      <c r="AO39" s="1" t="n">
+        <v>110.52</v>
+      </c>
+      <c r="AP39" s="2" t="n">
+        <v>-0.0006329686228411916</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5505,6 +5745,12 @@
       <c r="AN40" s="2" t="n">
         <v>-0.01203501094091912</v>
       </c>
+      <c r="AO40" s="1" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="AP40" s="2" t="n">
+        <v>-0.01135105204872649</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5629,6 +5875,12 @@
       <c r="AN41" s="2" t="n">
         <v>-0.001272958719767242</v>
       </c>
+      <c r="AO41" s="1" t="n">
+        <v>0.05424</v>
+      </c>
+      <c r="AP41" s="2" t="n">
+        <v>-0.01238164603058995</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5753,6 +6005,12 @@
       <c r="AN42" s="3" t="n">
         <v>0.001295336787564772</v>
       </c>
+      <c r="AO42" s="1" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="AP42" s="3" t="n">
+        <v>0.0003696174459435063</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5877,6 +6135,12 @@
       <c r="AN43" s="2" t="n">
         <v>-0.005295007564296567</v>
       </c>
+      <c r="AO43" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="AP43" s="3" t="n">
+        <v>0.002281368821292735</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6001,6 +6265,12 @@
       <c r="AN44" s="2" t="n">
         <v>-0.002548419979612537</v>
       </c>
+      <c r="AO44" s="1" t="n">
+        <v>0.00586</v>
+      </c>
+      <c r="AP44" s="2" t="n">
+        <v>-0.001873616079032634</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6125,6 +6395,12 @@
       <c r="AN45" s="2" t="n">
         <v>-0.001803787954704876</v>
       </c>
+      <c r="AO45" s="1" t="n">
+        <v>0.09911</v>
+      </c>
+      <c r="AP45" s="2" t="n">
+        <v>-0.005019576347756254</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6249,6 +6525,12 @@
       <c r="AN46" s="2" t="n">
         <v>-0.0024129610479144</v>
       </c>
+      <c r="AO46" s="1" t="n">
+        <v>2.912</v>
+      </c>
+      <c r="AP46" s="3" t="n">
+        <v>0.006219765031098753</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6373,6 +6655,12 @@
       <c r="AN47" s="2" t="n">
         <v>-0.0001038925058873459</v>
       </c>
+      <c r="AO47" s="1" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="AP47" s="2" t="n">
+        <v>-0.0002078066013230509</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6497,6 +6785,12 @@
       <c r="AN48" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO48" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AP48" s="3" t="n">
+        <v>0.003787878787878765</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6621,6 +6915,12 @@
       <c r="AN49" s="2" t="n">
         <v>-0.001559614200697801</v>
       </c>
+      <c r="AO49" s="1" t="n">
+        <v>0.24248</v>
+      </c>
+      <c r="AP49" s="2" t="n">
+        <v>-0.00324742056151595</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6745,6 +7045,12 @@
       <c r="AN50" s="2" t="n">
         <v>-0.001658031088082978</v>
       </c>
+      <c r="AO50" s="1" t="n">
+        <v>0.04893</v>
+      </c>
+      <c r="AP50" s="3" t="n">
+        <v>0.01577745484741548</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6869,6 +7175,12 @@
       <c r="AN51" s="2" t="n">
         <v>-0.001540436456996207</v>
       </c>
+      <c r="AO51" s="1" t="n">
+        <v>3.888</v>
+      </c>
+      <c r="AP51" s="2" t="n">
+        <v>-0.0002571355104139599</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6993,6 +7305,12 @@
       <c r="AN52" s="3" t="n">
         <v>0.004405286343612442</v>
       </c>
+      <c r="AO52" s="1" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AP52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7117,6 +7435,12 @@
       <c r="AN53" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO53" s="1" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="AP53" s="2" t="n">
+        <v>-0.001189767995240962</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7241,6 +7565,12 @@
       <c r="AN54" s="2" t="n">
         <v>-0.00216658642272508</v>
       </c>
+      <c r="AO54" s="1" t="n">
+        <v>0.04143</v>
+      </c>
+      <c r="AP54" s="2" t="n">
+        <v>-0.0004825090470446124</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7365,6 +7695,12 @@
       <c r="AN55" s="2" t="n">
         <v>-0.004538087520259247</v>
       </c>
+      <c r="AO55" s="1" t="n">
+        <v>0.12437</v>
+      </c>
+      <c r="AP55" s="3" t="n">
+        <v>0.01245522631064791</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7489,6 +7825,12 @@
       <c r="AN56" s="3" t="n">
         <v>0.0016010246557797</v>
       </c>
+      <c r="AO56" s="1" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AP56" s="3" t="n">
+        <v>0.002237851662404023</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7613,6 +7955,12 @@
       <c r="AN57" s="2" t="n">
         <v>-0.0008710801393729379</v>
       </c>
+      <c r="AO57" s="1" t="n">
+        <v>0.01143</v>
+      </c>
+      <c r="AP57" s="2" t="n">
+        <v>-0.003487358326068013</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7737,6 +8085,12 @@
       <c r="AN58" s="3" t="n">
         <v>0.00100502512562803</v>
       </c>
+      <c r="AO58" s="1" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="AP58" s="2" t="n">
+        <v>-0.002008032128513975</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7861,6 +8215,12 @@
       <c r="AN59" s="3" t="n">
         <v>0.006042296072507568</v>
       </c>
+      <c r="AO59" s="1" t="n">
+        <v>0.00332</v>
+      </c>
+      <c r="AP59" s="2" t="n">
+        <v>-0.003003003003003011</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7985,6 +8345,12 @@
       <c r="AN60" s="3" t="n">
         <v>0.00194426441996108</v>
       </c>
+      <c r="AO60" s="1" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="AP60" s="2" t="n">
+        <v>-0.0006468305304009637</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8109,6 +8475,12 @@
       <c r="AN61" s="2" t="n">
         <v>-6.279040562608314e-05</v>
       </c>
+      <c r="AO61" s="1" t="n">
+        <v>0.15911</v>
+      </c>
+      <c r="AP61" s="2" t="n">
+        <v>-0.0008791208791208868</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8233,6 +8605,12 @@
       <c r="AN62" s="3" t="n">
         <v>0.002410663641520028</v>
       </c>
+      <c r="AO62" s="1" t="n">
+        <v>0.7064</v>
+      </c>
+      <c r="AP62" s="2" t="n">
+        <v>-0.0007073136228602984</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8357,6 +8735,12 @@
       <c r="AN63" s="2" t="n">
         <v>-0.005768913795945301</v>
       </c>
+      <c r="AO63" s="1" t="n">
+        <v>6.039</v>
+      </c>
+      <c r="AP63" s="3" t="n">
+        <v>0.001160477453580848</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8481,6 +8865,12 @@
       <c r="AN64" s="2" t="n">
         <v>-0.0006983240223463403</v>
       </c>
+      <c r="AO64" s="1" t="n">
+        <v>0.007136</v>
+      </c>
+      <c r="AP64" s="2" t="n">
+        <v>-0.002655485674353588</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8605,6 +8995,12 @@
       <c r="AN65" s="2" t="n">
         <v>-0.0009282178217822477</v>
       </c>
+      <c r="AO65" s="1" t="n">
+        <v>0.03272</v>
+      </c>
+      <c r="AP65" s="3" t="n">
+        <v>0.0133168163518117</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8729,6 +9125,12 @@
       <c r="AN66" s="2" t="n">
         <v>-0.004291845493562235</v>
       </c>
+      <c r="AO66" s="1" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="AP66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8853,6 +9255,12 @@
       <c r="AN67" s="3" t="n">
         <v>0.001848428835489767</v>
       </c>
+      <c r="AO67" s="1" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="AP67" s="2" t="n">
+        <v>-0.001845018450184435</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8977,6 +9385,12 @@
       <c r="AN68" s="3" t="n">
         <v>0.003107121720260393</v>
       </c>
+      <c r="AO68" s="1" t="n">
+        <v>2.0335</v>
+      </c>
+      <c r="AP68" s="2" t="n">
+        <v>-0.0001966665027778927</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9101,6 +9515,12 @@
       <c r="AN69" s="2" t="n">
         <v>-0.0001696640651509823</v>
       </c>
+      <c r="AO69" s="1" t="n">
+        <v>0.5914</v>
+      </c>
+      <c r="AP69" s="3" t="n">
+        <v>0.003563549974546055</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9225,6 +9645,12 @@
       <c r="AN70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AP70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9349,6 +9775,12 @@
       <c r="AN71" s="3" t="n">
         <v>0.0001104606207886767</v>
       </c>
+      <c r="AO71" s="1" t="n">
+        <v>0.9043</v>
+      </c>
+      <c r="AP71" s="2" t="n">
+        <v>-0.00121493262646343</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9473,6 +9905,12 @@
       <c r="AN72" s="2" t="n">
         <v>-0.002551612154952424</v>
       </c>
+      <c r="AO72" s="1" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="AP72" s="3" t="n">
+        <v>0.006046511627906957</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9597,6 +10035,12 @@
       <c r="AN73" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO73" s="1" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="AP73" s="2" t="n">
+        <v>-0.0008512449457331</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9721,6 +10165,12 @@
       <c r="AN74" s="3" t="n">
         <v>0.00287131297311414</v>
       </c>
+      <c r="AO74" s="1" t="n">
+        <v>1.1529</v>
+      </c>
+      <c r="AP74" s="3" t="n">
+        <v>0.0002602811035918505</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9845,6 +10295,12 @@
       <c r="AN75" s="3" t="n">
         <v>0.001248439450686591</v>
       </c>
+      <c r="AO75" s="1" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="AP75" s="2" t="n">
+        <v>-0.001870324189526108</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9969,6 +10425,12 @@
       <c r="AN76" s="3" t="n">
         <v>0.008044451816221584</v>
       </c>
+      <c r="AO76" s="1" t="n">
+        <v>0.12155</v>
+      </c>
+      <c r="AP76" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10093,6 +10555,12 @@
       <c r="AN77" s="2" t="n">
         <v>-0.0008474576271185508</v>
       </c>
+      <c r="AO77" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="AP77" s="2" t="n">
+        <v>-0.001696352841391058</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10217,6 +10685,12 @@
       <c r="AN78" s="2" t="n">
         <v>-0.0009891196834815924</v>
       </c>
+      <c r="AO78" s="1" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="AP78" s="2" t="n">
+        <v>-0.0009900990099010183</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10341,6 +10815,12 @@
       <c r="AN79" s="3" t="n">
         <v>0.001496508147655381</v>
       </c>
+      <c r="AO79" s="1" t="n">
+        <v>0.006004</v>
+      </c>
+      <c r="AP79" s="2" t="n">
+        <v>-0.0031545741324921</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10465,6 +10945,12 @@
       <c r="AN80" s="2" t="n">
         <v>-0.004350051177072694</v>
       </c>
+      <c r="AO80" s="1" t="n">
+        <v>0.00788</v>
+      </c>
+      <c r="AP80" s="3" t="n">
+        <v>0.01259316371112824</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10589,6 +11075,12 @@
       <c r="AN81" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO81" s="1" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AP81" s="2" t="n">
+        <v>-0.002804262478967872</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10713,6 +11205,12 @@
       <c r="AN82" s="3" t="n">
         <v>0.01393939393939392</v>
       </c>
+      <c r="AO82" s="1" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="AP82" s="2" t="n">
+        <v>-0.0005977286312015346</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10837,6 +11335,12 @@
       <c r="AN83" s="3" t="n">
         <v>0.0006079766536963771</v>
       </c>
+      <c r="AO83" s="1" t="n">
+        <v>8.215</v>
+      </c>
+      <c r="AP83" s="2" t="n">
+        <v>-0.001701300279499252</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10961,6 +11465,12 @@
       <c r="AN84" s="2" t="n">
         <v>-0.003885973620763025</v>
       </c>
+      <c r="AO84" s="1" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="AP84" s="3" t="n">
+        <v>0.003388575659206099</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11085,6 +11595,12 @@
       <c r="AN85" s="2" t="n">
         <v>-0.003939916276779214</v>
       </c>
+      <c r="AO85" s="1" t="n">
+        <v>0.004012</v>
+      </c>
+      <c r="AP85" s="2" t="n">
+        <v>-0.00815822002472189</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11209,6 +11725,12 @@
       <c r="AN86" s="2" t="n">
         <v>-0.001219791110772442</v>
       </c>
+      <c r="AO86" s="1" t="n">
+        <v>0.13113</v>
+      </c>
+      <c r="AP86" s="3" t="n">
+        <v>0.0009159606136936799</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11333,6 +11855,12 @@
       <c r="AN87" s="3" t="n">
         <v>0.004958677685950402</v>
       </c>
+      <c r="AO87" s="1" t="n">
+        <v>0.01819</v>
+      </c>
+      <c r="AP87" s="2" t="n">
+        <v>-0.002741228070175327</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11457,6 +11985,12 @@
       <c r="AN88" s="3" t="n">
         <v>0.001774622892635317</v>
       </c>
+      <c r="AO88" s="1" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="AP88" s="2" t="n">
+        <v>-0.001771479185119576</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11581,6 +12115,12 @@
       <c r="AN89" s="2" t="n">
         <v>-0.004445964432284432</v>
       </c>
+      <c r="AO89" s="1" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AP89" s="2" t="n">
+        <v>-0.0003435245620063363</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11705,6 +12245,12 @@
       <c r="AN90" s="2" t="n">
         <v>-0.0003881987577639324</v>
       </c>
+      <c r="AO90" s="1" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="AP90" s="2" t="n">
+        <v>-0.002718446601941879</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11829,6 +12375,12 @@
       <c r="AN91" s="2" t="n">
         <v>-0.006522122333862194</v>
       </c>
+      <c r="AO91" s="1" t="n">
+        <v>0.05606</v>
+      </c>
+      <c r="AP91" s="2" t="n">
+        <v>-0.005322924059616779</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11953,6 +12505,12 @@
       <c r="AN92" s="3" t="n">
         <v>0.0003076923076922738</v>
       </c>
+      <c r="AO92" s="1" t="n">
+        <v>1.3043</v>
+      </c>
+      <c r="AP92" s="3" t="n">
+        <v>0.002999077207013238</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12077,6 +12635,12 @@
       <c r="AN93" s="2" t="n">
         <v>-0.00452276980661258</v>
       </c>
+      <c r="AO93" s="1" t="n">
+        <v>0.06376</v>
+      </c>
+      <c r="AP93" s="2" t="n">
+        <v>-0.001096663011123306</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12201,6 +12765,12 @@
       <c r="AN94" s="2" t="n">
         <v>-0.01250000000000008</v>
       </c>
+      <c r="AO94" s="1" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="AP94" s="3" t="n">
+        <v>0.001150747986190977</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12325,6 +12895,12 @@
       <c r="AN95" s="3" t="n">
         <v>0.001786245906519931</v>
       </c>
+      <c r="AO95" s="1" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AP95" s="2" t="n">
+        <v>-0.002080237741456267</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12449,6 +13025,12 @@
       <c r="AN96" s="3" t="n">
         <v>0.002218278615794053</v>
       </c>
+      <c r="AO96" s="1" t="n">
+        <v>0.02251</v>
+      </c>
+      <c r="AP96" s="2" t="n">
+        <v>-0.003541389995573272</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12573,6 +13155,12 @@
       <c r="AN97" s="2" t="n">
         <v>-0.003988953666769025</v>
       </c>
+      <c r="AO97" s="1" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="AP97" s="3" t="n">
+        <v>0.0006161429451631553</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12697,6 +13285,12 @@
       <c r="AN98" s="3" t="n">
         <v>0.003552397868561282</v>
       </c>
+      <c r="AO98" s="1" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="AP98" s="3" t="n">
+        <v>0.0008849557522124885</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12821,6 +13415,12 @@
       <c r="AN99" s="3" t="n">
         <v>0.0009917355371901202</v>
       </c>
+      <c r="AO99" s="1" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="AP99" s="2" t="n">
+        <v>-0.001981505944517908</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12945,6 +13545,12 @@
       <c r="AN100" s="2" t="n">
         <v>-0.001760563380281618</v>
       </c>
+      <c r="AO100" s="1" t="n">
+        <v>0.03396</v>
+      </c>
+      <c r="AP100" s="2" t="n">
+        <v>-0.001763668430335229</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13069,6 +13675,12 @@
       <c r="AN101" s="3" t="n">
         <v>0.001096491228070176</v>
       </c>
+      <c r="AO101" s="1" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="AP101" s="2" t="n">
+        <v>-0.0005476451259584402</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13193,6 +13805,12 @@
       <c r="AN102" s="3" t="n">
         <v>0.0016968325791855</v>
       </c>
+      <c r="AO102" s="1" t="n">
+        <v>0.007076</v>
+      </c>
+      <c r="AP102" s="2" t="n">
+        <v>-0.001129305477131592</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13317,6 +13935,12 @@
       <c r="AN103" s="2" t="n">
         <v>-0.005660954712362229</v>
       </c>
+      <c r="AO103" s="1" t="n">
+        <v>0.06496</v>
+      </c>
+      <c r="AP103" s="2" t="n">
+        <v>-0.000461609478381324</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13441,6 +14065,12 @@
       <c r="AN104" s="3" t="n">
         <v>0.00315610585093475</v>
       </c>
+      <c r="AO104" s="1" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="AP104" s="2" t="n">
+        <v>-0.001210067763794774</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13565,6 +14195,12 @@
       <c r="AN105" s="3" t="n">
         <v>0.006060606060606127</v>
       </c>
+      <c r="AO105" s="1" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="AP105" s="2" t="n">
+        <v>-0.002738225629791958</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13689,6 +14325,12 @@
       <c r="AN106" s="2" t="n">
         <v>-0.008666992187499986</v>
       </c>
+      <c r="AO106" s="1" t="n">
+        <v>0.00805</v>
+      </c>
+      <c r="AP106" s="2" t="n">
+        <v>-0.00874276566925254</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13813,6 +14455,12 @@
       <c r="AN107" s="3" t="n">
         <v>0.0005506607929515195</v>
       </c>
+      <c r="AO107" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="AP107" s="2" t="n">
+        <v>-0.002751788662630598</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13937,6 +14585,12 @@
       <c r="AN108" s="3" t="n">
         <v>0.002784222737819073</v>
       </c>
+      <c r="AO108" s="1" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="AP108" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14061,6 +14715,12 @@
       <c r="AN109" s="2" t="n">
         <v>-0.00143420580853359</v>
       </c>
+      <c r="AO109" s="1" t="n">
+        <v>0.05581</v>
+      </c>
+      <c r="AP109" s="3" t="n">
+        <v>0.001974865350089749</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14185,6 +14845,12 @@
       <c r="AN110" s="3" t="n">
         <v>0.001567534616389442</v>
       </c>
+      <c r="AO110" s="1" t="n">
+        <v>0.11541</v>
+      </c>
+      <c r="AP110" s="3" t="n">
+        <v>0.00347795843839664</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14309,6 +14975,12 @@
       <c r="AN111" s="2" t="n">
         <v>-0.003939865215137289</v>
       </c>
+      <c r="AO111" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AP111" s="2" t="n">
+        <v>-0.0007286353700426836</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14433,6 +15105,12 @@
       <c r="AN112" s="3" t="n">
         <v>0.002695417789757302</v>
       </c>
+      <c r="AO112" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AP112" s="2" t="n">
+        <v>-0.002688172043010643</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14557,6 +15235,12 @@
       <c r="AN113" s="3" t="n">
         <v>0.0006114961271912403</v>
       </c>
+      <c r="AO113" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="AP113" s="2" t="n">
+        <v>-0.000814829904257453</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14681,6 +15365,12 @@
       <c r="AN114" s="2" t="n">
         <v>-0.001128031584884404</v>
       </c>
+      <c r="AO114" s="1" t="n">
+        <v>0.001773</v>
+      </c>
+      <c r="AP114" s="3" t="n">
+        <v>0.001129305477131592</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14805,6 +15495,12 @@
       <c r="AN115" s="2" t="n">
         <v>-0.0007949125596185309</v>
       </c>
+      <c r="AO115" s="1" t="n">
+        <v>1.2568</v>
+      </c>
+      <c r="AP115" s="2" t="n">
+        <v>-0.0001591089896578982</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14929,6 +15625,12 @@
       <c r="AN116" s="2" t="n">
         <v>-0.0004242681374628298</v>
       </c>
+      <c r="AO116" s="1" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="AP116" s="2" t="n">
+        <v>-0.001697792869269998</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -15053,6 +15755,12 @@
       <c r="AN117" s="2" t="n">
         <v>-0.003460207612456778</v>
       </c>
+      <c r="AO117" s="1" t="n">
+        <v>0.06045</v>
+      </c>
+      <c r="AP117" s="2" t="n">
+        <v>-0.0004960317460317832</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -15177,6 +15885,12 @@
       <c r="AN118" s="3" t="n">
         <v>0.006583427922814951</v>
       </c>
+      <c r="AO118" s="1" t="n">
+        <v>0.04484</v>
+      </c>
+      <c r="AP118" s="3" t="n">
+        <v>0.01127649977447001</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15301,6 +16015,12 @@
       <c r="AN119" s="2" t="n">
         <v>-0.003801248981808342</v>
       </c>
+      <c r="AO119" s="1" t="n">
+        <v>0.003652</v>
+      </c>
+      <c r="AP119" s="2" t="n">
+        <v>-0.004633415099482172</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15425,6 +16145,12 @@
       <c r="AN120" s="2" t="n">
         <v>-0.001267427122940432</v>
       </c>
+      <c r="AO120" s="1" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="AP120" s="2" t="n">
+        <v>-0.001269035532994925</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15549,6 +16275,12 @@
       <c r="AN121" s="2" t="n">
         <v>-0.001680107526881722</v>
       </c>
+      <c r="AO121" s="1" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AP121" s="2" t="n">
+        <v>-0.002356109054190436</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15673,6 +16405,12 @@
       <c r="AN122" s="2" t="n">
         <v>-0.001410437235543059</v>
       </c>
+      <c r="AO122" s="1" t="n">
+        <v>0.5658</v>
+      </c>
+      <c r="AP122" s="2" t="n">
+        <v>-0.001059322033898384</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15797,6 +16535,12 @@
       <c r="AN123" s="3" t="n">
         <v>0.00284920327834258</v>
       </c>
+      <c r="AO123" s="1" t="n">
+        <v>0.028531</v>
+      </c>
+      <c r="AP123" s="3" t="n">
+        <v>0.000736583654857951</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15921,6 +16665,12 @@
       <c r="AN124" s="2" t="n">
         <v>-0.006954982296408637</v>
       </c>
+      <c r="AO124" s="1" t="n">
+        <v>0.07815</v>
+      </c>
+      <c r="AP124" s="2" t="n">
+        <v>-0.004838915064306702</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -16045,6 +16795,12 @@
       <c r="AN125" s="2" t="n">
         <v>-0.005007085498346743</v>
       </c>
+      <c r="AO125" s="1" t="n">
+        <v>0.10562</v>
+      </c>
+      <c r="AP125" s="3" t="n">
+        <v>0.002848461830611551</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -16169,6 +16925,12 @@
       <c r="AN126" s="2" t="n">
         <v>-0.0007567158531970937</v>
       </c>
+      <c r="AO126" s="1" t="n">
+        <v>0.02629</v>
+      </c>
+      <c r="AP126" s="2" t="n">
+        <v>-0.004543733434305134</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -16293,6 +17055,12 @@
       <c r="AN127" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO127" s="1" t="n">
+        <v>0.02176</v>
+      </c>
+      <c r="AP127" s="2" t="n">
+        <v>-0.0009182736455463354</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -16417,6 +17185,12 @@
       <c r="AN128" s="2" t="n">
         <v>-0.0006199628022317979</v>
       </c>
+      <c r="AO128" s="1" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="AP128" s="2" t="n">
+        <v>-0.001861042183622968</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -16541,6 +17315,12 @@
       <c r="AN129" s="3" t="n">
         <v>0.005383862396867521</v>
       </c>
+      <c r="AO129" s="1" t="n">
+        <v>0.14255</v>
+      </c>
+      <c r="AP129" s="2" t="n">
+        <v>-0.008623687321788658</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -16665,6 +17445,12 @@
       <c r="AN130" s="3" t="n">
         <v>0.003385675091938601</v>
       </c>
+      <c r="AO130" s="1" t="n">
+        <v>0.051621</v>
+      </c>
+      <c r="AP130" s="3" t="n">
+        <v>0.001047181336901478</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -16789,6 +17575,12 @@
       <c r="AN131" s="3" t="n">
         <v>0.0007326007326007875</v>
       </c>
+      <c r="AO131" s="1" t="n">
+        <v>0.08187999999999999</v>
+      </c>
+      <c r="AP131" s="2" t="n">
+        <v>-0.0009760858955589387</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16913,6 +17705,12 @@
       <c r="AN132" s="3" t="n">
         <v>0.001137656427758691</v>
       </c>
+      <c r="AO132" s="1" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="AP132" s="2" t="n">
+        <v>-0.003409090909090849</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -17037,6 +17835,12 @@
       <c r="AN133" s="3" t="n">
         <v>0.0001726221301570671</v>
       </c>
+      <c r="AO133" s="1" t="n">
+        <v>0.5797</v>
+      </c>
+      <c r="AP133" s="3" t="n">
+        <v>0.0005177770107006679</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -17161,6 +17965,12 @@
       <c r="AN134" s="2" t="n">
         <v>-0.004378578646008813</v>
       </c>
+      <c r="AO134" s="1" t="n">
+        <v>0.02951</v>
+      </c>
+      <c r="AP134" s="2" t="n">
+        <v>-0.001691474966170432</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -17285,6 +18095,12 @@
       <c r="AN135" s="3" t="n">
         <v>0.0005750431282345942</v>
       </c>
+      <c r="AO135" s="1" t="n">
+        <v>0.01745</v>
+      </c>
+      <c r="AP135" s="3" t="n">
+        <v>0.002873563218390887</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -17409,6 +18225,12 @@
       <c r="AN136" s="3" t="n">
         <v>0.002698327037236803</v>
       </c>
+      <c r="AO136" s="1" t="n">
+        <v>0.03705</v>
+      </c>
+      <c r="AP136" s="2" t="n">
+        <v>-0.002960172228202341</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -17533,6 +18355,12 @@
       <c r="AN137" s="3" t="n">
         <v>0.001483129403040355</v>
       </c>
+      <c r="AO137" s="1" t="n">
+        <v>0.02692</v>
+      </c>
+      <c r="AP137" s="2" t="n">
+        <v>-0.003332099222510174</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17657,6 +18485,12 @@
       <c r="AN138" s="3" t="n">
         <v>0.00788643533123029</v>
       </c>
+      <c r="AO138" s="1" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="AP138" s="3" t="n">
+        <v>0.005868544600939015</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17781,6 +18615,12 @@
       <c r="AN139" s="2" t="n">
         <v>-0.005902192242833104</v>
       </c>
+      <c r="AO139" s="1" t="n">
+        <v>0.01178</v>
+      </c>
+      <c r="AP139" s="2" t="n">
+        <v>-0.0008481764206954701</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -17905,6 +18745,12 @@
       <c r="AN140" s="2" t="n">
         <v>-0.0006793478260869289</v>
       </c>
+      <c r="AO140" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="AP140" s="2" t="n">
+        <v>-0.001359619306594216</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -18029,6 +18875,12 @@
       <c r="AN141" s="3" t="n">
         <v>0.002293862368258065</v>
       </c>
+      <c r="AO141" s="1" t="n">
+        <v>16.158</v>
+      </c>
+      <c r="AP141" s="2" t="n">
+        <v>-0.000556689552792747</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -18153,6 +19005,12 @@
       <c r="AN142" s="2" t="n">
         <v>-0.0008032128514055898</v>
       </c>
+      <c r="AO142" s="1" t="n">
+        <v>0.01244</v>
+      </c>
+      <c r="AP142" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -18277,6 +19135,12 @@
       <c r="AN143" s="3" t="n">
         <v>0.003925767309064918</v>
       </c>
+      <c r="AO143" s="1" t="n">
+        <v>0.02813</v>
+      </c>
+      <c r="AP143" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -18401,6 +19265,12 @@
       <c r="AN144" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO144" s="1" t="n">
+        <v>0.004723</v>
+      </c>
+      <c r="AP144" s="2" t="n">
+        <v>-0.005893496106082982</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -18525,6 +19395,12 @@
       <c r="AN145" s="2" t="n">
         <v>-0.002325934165950315</v>
       </c>
+      <c r="AO145" s="1" t="n">
+        <v>1.9773</v>
+      </c>
+      <c r="AP145" s="3" t="n">
+        <v>0.002128630074502043</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -18649,6 +19525,12 @@
       <c r="AN146" s="2" t="n">
         <v>-0.0008532423208190779</v>
       </c>
+      <c r="AO146" s="1" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="AP146" s="3" t="n">
+        <v>0.001280956447480733</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -18773,6 +19655,12 @@
       <c r="AN147" s="3" t="n">
         <v>0.00188930873527439</v>
       </c>
+      <c r="AO147" s="1" t="n">
+        <v>0.08974</v>
+      </c>
+      <c r="AP147" s="2" t="n">
+        <v>-0.004547975596228438</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18897,6 +19785,12 @@
       <c r="AN148" s="3" t="n">
         <v>0.00908801020408165</v>
       </c>
+      <c r="AO148" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="AP148" s="3" t="n">
+        <v>0.006478116606099029</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -19021,6 +19915,12 @@
       <c r="AN149" s="2" t="n">
         <v>-0.001355243096730421</v>
       </c>
+      <c r="AO149" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AP149" s="3" t="n">
+        <v>0.0008481764206954112</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -19145,6 +20045,12 @@
       <c r="AN150" s="2" t="n">
         <v>-0.0008229098090849478</v>
       </c>
+      <c r="AO150" s="1" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="AP150" s="3" t="n">
+        <v>0.0006588700378850004</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -19269,6 +20175,12 @@
       <c r="AN151" s="3" t="n">
         <v>0.002427184466019322</v>
       </c>
+      <c r="AO151" s="1" t="n">
+        <v>6.991e-05</v>
+      </c>
+      <c r="AP151" s="2" t="n">
+        <v>-0.004272895598917444</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -19393,6 +20305,12 @@
       <c r="AN152" s="2" t="n">
         <v>-0.003150315031503178</v>
       </c>
+      <c r="AO152" s="1" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AP152" s="3" t="n">
+        <v>0.002031602708803639</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -19517,6 +20435,12 @@
       <c r="AN153" s="3" t="n">
         <v>0.005819592628515901</v>
       </c>
+      <c r="AO153" s="1" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="AP153" s="2" t="n">
+        <v>-0.0006428801028607457</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -19641,6 +20565,12 @@
       <c r="AN154" s="2" t="n">
         <v>-0.0002762430939226215</v>
       </c>
+      <c r="AO154" s="1" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="AP154" s="3" t="n">
+        <v>0.001105277701022414</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -19765,6 +20695,12 @@
       <c r="AN155" s="2" t="n">
         <v>-0.003034243606415164</v>
       </c>
+      <c r="AO155" s="1" t="n">
+        <v>0.2302</v>
+      </c>
+      <c r="AP155" s="3" t="n">
+        <v>0.0008695652173912085</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -19889,6 +20825,12 @@
       <c r="AN156" s="2" t="n">
         <v>-0.001229407425620715</v>
       </c>
+      <c r="AO156" s="1" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="AP156" s="2" t="n">
+        <v>-0.0009847365829641877</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -20013,6 +20955,12 @@
       <c r="AN157" s="2" t="n">
         <v>-0.00224186247035996</v>
       </c>
+      <c r="AO157" s="1" t="n">
+        <v>0.23279</v>
+      </c>
+      <c r="AP157" s="3" t="n">
+        <v>0.005876506935142376</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -20137,6 +21085,12 @@
       <c r="AN158" s="3" t="n">
         <v>0.0003924646781789206</v>
       </c>
+      <c r="AO158" s="1" t="n">
+        <v>0.2551</v>
+      </c>
+      <c r="AP158" s="3" t="n">
+        <v>0.0007846214201646841</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -20261,6 +21215,12 @@
       <c r="AN159" s="3" t="n">
         <v>0.0006861063464836294</v>
       </c>
+      <c r="AO159" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AP159" s="3" t="n">
+        <v>0.001028453890983927</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -20385,6 +21345,12 @@
       <c r="AN160" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO160" s="1" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="AP160" s="2" t="n">
+        <v>-0.001011122345803871</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -20509,6 +21475,12 @@
       <c r="AN161" s="2" t="n">
         <v>-0.004008424485358921</v>
       </c>
+      <c r="AO161" s="1" t="n">
+        <v>0.14735</v>
+      </c>
+      <c r="AP161" s="3" t="n">
+        <v>0.005115961800818558</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -20633,6 +21605,12 @@
       <c r="AN162" s="3" t="n">
         <v>0.002428658166363012</v>
       </c>
+      <c r="AO162" s="1" t="n">
+        <v>0.003283</v>
+      </c>
+      <c r="AP162" s="2" t="n">
+        <v>-0.005754088431253762</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -20757,6 +21735,12 @@
       <c r="AN163" s="2" t="n">
         <v>-0.002587579617834393</v>
       </c>
+      <c r="AO163" s="1" t="n">
+        <v>0.004999</v>
+      </c>
+      <c r="AP163" s="2" t="n">
+        <v>-0.00239473159050087</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -20881,6 +21865,12 @@
       <c r="AN164" s="3" t="n">
         <v>0.003121748178980174</v>
       </c>
+      <c r="AO164" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="AP164" s="2" t="n">
+        <v>-0.001037344398340279</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -21005,6 +21995,12 @@
       <c r="AN165" s="2" t="n">
         <v>-0.002611818478615811</v>
       </c>
+      <c r="AO165" s="1" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AP165" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -21129,6 +22125,12 @@
       <c r="AN166" s="2" t="n">
         <v>-0.001506456241032992</v>
       </c>
+      <c r="AO166" s="1" t="n">
+        <v>1.3907</v>
+      </c>
+      <c r="AP166" s="2" t="n">
+        <v>-0.0008621309002082534</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -21253,6 +22255,12 @@
       <c r="AN167" s="2" t="n">
         <v>-0.001078360891445084</v>
       </c>
+      <c r="AO167" s="1" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="AP167" s="3" t="n">
+        <v>0.000719683339330815</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -21377,6 +22385,12 @@
       <c r="AN168" s="3" t="n">
         <v>0.003225806451612906</v>
       </c>
+      <c r="AO168" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AP168" s="2" t="n">
+        <v>-0.003215434083601289</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -21501,6 +22515,12 @@
       <c r="AN169" s="2" t="n">
         <v>-0.002334889926617766</v>
       </c>
+      <c r="AO169" s="1" t="n">
+        <v>0.02979</v>
+      </c>
+      <c r="AP169" s="2" t="n">
+        <v>-0.004012036108324927</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -21625,6 +22645,12 @@
       <c r="AN170" s="2" t="n">
         <v>-0.001843742797879621</v>
       </c>
+      <c r="AO170" s="1" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="AP170" s="2" t="n">
+        <v>-0.0002308935580698005</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -21749,6 +22775,12 @@
       <c r="AN171" s="2" t="n">
         <v>-0.006024096385542133</v>
       </c>
+      <c r="AO171" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="AP171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -21873,6 +22905,12 @@
       <c r="AN172" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO172" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="AP172" s="2" t="n">
+        <v>-0.007751937984496181</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -21997,6 +23035,12 @@
       <c r="AN173" s="2" t="n">
         <v>-0.0009474182851728652</v>
       </c>
+      <c r="AO173" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="AP173" s="2" t="n">
+        <v>-0.0009483167377905478</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -22121,6 +23165,12 @@
       <c r="AN174" s="2" t="n">
         <v>-0.003459435330878148</v>
       </c>
+      <c r="AO174" s="1" t="n">
+        <v>0.08913</v>
+      </c>
+      <c r="AP174" s="2" t="n">
+        <v>-0.001903695408734641</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -22245,6 +23295,12 @@
       <c r="AN175" s="2" t="n">
         <v>-0.0005543237250555252</v>
       </c>
+      <c r="AO175" s="1" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AP175" s="2" t="n">
+        <v>-0.002218524681086987</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -22369,6 +23425,12 @@
       <c r="AN176" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO176" s="1" t="n">
+        <v>0.02117</v>
+      </c>
+      <c r="AP176" s="2" t="n">
+        <v>-0.004233301975540912</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -22493,6 +23555,12 @@
       <c r="AN177" s="2" t="n">
         <v>-0.003807106598984837</v>
       </c>
+      <c r="AO177" s="1" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="AP177" s="2" t="n">
+        <v>-0.002547770700636839</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -22617,6 +23685,12 @@
       <c r="AN178" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO178" s="1" t="n">
+        <v>0.000949</v>
+      </c>
+      <c r="AP178" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -22741,6 +23815,12 @@
       <c r="AN179" s="3" t="n">
         <v>0.005535298510741164</v>
       </c>
+      <c r="AO179" s="1" t="n">
+        <v>0.022807</v>
+      </c>
+      <c r="AP179" s="2" t="n">
+        <v>-0.003582506881034503</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -22865,6 +23945,12 @@
       <c r="AN180" s="2" t="n">
         <v>-0.002931118710307878</v>
       </c>
+      <c r="AO180" s="1" t="n">
+        <v>4.074</v>
+      </c>
+      <c r="AP180" s="2" t="n">
+        <v>-0.001959823615874573</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -22989,6 +24075,12 @@
       <c r="AN181" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO181" s="1" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="AP181" s="2" t="n">
+        <v>-0.0001761493746697005</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -23113,6 +24205,12 @@
       <c r="AN182" s="2" t="n">
         <v>-0.002378592666005987</v>
       </c>
+      <c r="AO182" s="1" t="n">
+        <v>0.05011</v>
+      </c>
+      <c r="AP182" s="2" t="n">
+        <v>-0.004371150407311702</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -23237,6 +24335,12 @@
       <c r="AN183" s="2" t="n">
         <v>-0.002208317997791765</v>
       </c>
+      <c r="AO183" s="1" t="n">
+        <v>5.426</v>
+      </c>
+      <c r="AP183" s="3" t="n">
+        <v>0.0007377351530801269</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -23361,6 +24465,12 @@
       <c r="AN184" s="2" t="n">
         <v>-0.003474635163307902</v>
       </c>
+      <c r="AO184" s="1" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="AP184" s="3" t="n">
+        <v>0.00104602510460255</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -23485,6 +24595,12 @@
       <c r="AN185" s="2" t="n">
         <v>-0.001623376623376557</v>
       </c>
+      <c r="AO185" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="AP185" s="3" t="n">
+        <v>0.002168021680216714</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -23609,6 +24725,12 @@
       <c r="AN186" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO186" s="1" t="n">
+        <v>3.05e-05</v>
+      </c>
+      <c r="AP186" s="2" t="n">
+        <v>-0.006514657980456074</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -23733,6 +24855,12 @@
       <c r="AN187" s="2" t="n">
         <v>-0.001915708812260458</v>
       </c>
+      <c r="AO187" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AP187" s="2" t="n">
+        <v>-0.001919385796545249</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -23857,6 +24985,12 @@
       <c r="AN188" s="3" t="n">
         <v>0.001229105211406132</v>
       </c>
+      <c r="AO188" s="1" t="n">
+        <v>0.04066</v>
+      </c>
+      <c r="AP188" s="2" t="n">
+        <v>-0.001718634912840673</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -23981,6 +25115,12 @@
       <c r="AN189" s="2" t="n">
         <v>-0.002700877785280282</v>
       </c>
+      <c r="AO189" s="1" t="n">
+        <v>0.0004416</v>
+      </c>
+      <c r="AP189" s="2" t="n">
+        <v>-0.003385240352064956</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -24105,6 +25245,12 @@
       <c r="AN190" s="3" t="n">
         <v>0.0004342162396874973</v>
       </c>
+      <c r="AO190" s="1" t="n">
+        <v>0.02302</v>
+      </c>
+      <c r="AP190" s="2" t="n">
+        <v>-0.0008680555555556708</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -24229,6 +25375,12 @@
       <c r="AN191" s="3" t="n">
         <v>0.001276324186343279</v>
       </c>
+      <c r="AO191" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="AP191" s="2" t="n">
+        <v>-0.003824091778202521</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -24353,6 +25505,12 @@
       <c r="AN192" s="3" t="n">
         <v>0.002516627718856754</v>
       </c>
+      <c r="AO192" s="1" t="n">
+        <v>0.05557</v>
+      </c>
+      <c r="AP192" s="2" t="n">
+        <v>-0.003586157432311257</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -24477,6 +25635,12 @@
       <c r="AN193" s="2" t="n">
         <v>-0.002139037433155141</v>
       </c>
+      <c r="AO193" s="1" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="AP193" s="2" t="n">
+        <v>-0.001071811361200311</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -24601,6 +25765,12 @@
       <c r="AN194" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO194" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="AP194" s="2" t="n">
+        <v>-0.001558441558441495</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -24725,6 +25895,12 @@
       <c r="AN195" s="3" t="n">
         <v>0.004481132075471728</v>
       </c>
+      <c r="AO195" s="1" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="AP195" s="3" t="n">
+        <v>0.0002347969006808852</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -24849,6 +26025,12 @@
       <c r="AN196" s="3" t="n">
         <v>0.002448979591836635</v>
       </c>
+      <c r="AO196" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="AP196" s="2" t="n">
+        <v>-0.004885993485341962</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -24973,6 +26155,12 @@
       <c r="AN197" s="2" t="n">
         <v>-0.004321521175453733</v>
       </c>
+      <c r="AO197" s="1" t="n">
+        <v>0.04555</v>
+      </c>
+      <c r="AP197" s="2" t="n">
+        <v>-0.01150173611111117</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -25097,6 +26285,12 @@
       <c r="AN198" s="2" t="n">
         <v>-0.00272426542128832</v>
       </c>
+      <c r="AO198" s="1" t="n">
+        <v>0.5119</v>
+      </c>
+      <c r="AP198" s="2" t="n">
+        <v>-0.001170731707316944</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -25221,6 +26415,12 @@
       <c r="AN199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AP199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -25345,6 +26545,12 @@
       <c r="AN200" s="2" t="n">
         <v>-0.0006747638326585551</v>
       </c>
+      <c r="AO200" s="1" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AP200" s="2" t="n">
+        <v>-0.0006752194463200396</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -25469,6 +26675,12 @@
       <c r="AN201" s="2" t="n">
         <v>-0.003541703559412086</v>
       </c>
+      <c r="AO201" s="1" t="n">
+        <v>0.00561</v>
+      </c>
+      <c r="AP201" s="2" t="n">
+        <v>-0.003021148036253715</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -25593,6 +26805,12 @@
       <c r="AN202" s="2" t="n">
         <v>-0.001868346730393281</v>
       </c>
+      <c r="AO202" s="1" t="n">
+        <v>0.023022</v>
+      </c>
+      <c r="AP202" s="3" t="n">
+        <v>0.002176562772070409</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -25717,6 +26935,12 @@
       <c r="AN203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AP203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -25841,6 +27065,12 @@
       <c r="AN204" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO204" s="1" t="n">
+        <v>0.03323</v>
+      </c>
+      <c r="AP204" s="2" t="n">
+        <v>-0.0006015037593984717</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -25965,6 +27195,12 @@
       <c r="AN205" s="2" t="n">
         <v>-0.003585086042065145</v>
       </c>
+      <c r="AO205" s="1" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="AP205" s="3" t="n">
+        <v>0.0004797313504439117</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -26089,6 +27325,12 @@
       <c r="AN206" s="2" t="n">
         <v>-0.002770083102493077</v>
       </c>
+      <c r="AO206" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -26213,6 +27455,12 @@
       <c r="AN207" s="2" t="n">
         <v>-0.003553099091985746</v>
       </c>
+      <c r="AO207" s="1" t="n">
+        <v>0.001216</v>
+      </c>
+      <c r="AP207" s="2" t="n">
+        <v>-0.03645007923930272</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -26337,6 +27585,12 @@
       <c r="AN208" s="3" t="n">
         <v>0.004081632653061155</v>
       </c>
+      <c r="AO208" s="1" t="n">
+        <v>0.007166</v>
+      </c>
+      <c r="AP208" s="3" t="n">
+        <v>0.004485562097000268</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -26461,6 +27715,12 @@
       <c r="AN209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO209" s="1" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="AP209" s="2" t="n">
+        <v>-0.003344481605351151</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -26585,6 +27845,12 @@
       <c r="AN210" s="2" t="n">
         <v>-0.002325581395348796</v>
       </c>
+      <c r="AO210" s="1" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="AP210" s="3" t="n">
+        <v>0.001554001554001383</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -26709,6 +27975,12 @@
       <c r="AN211" s="3" t="n">
         <v>0.001546899170299497</v>
       </c>
+      <c r="AO211" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="AP211" s="2" t="n">
+        <v>-0.001684919966301581</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -26833,6 +28105,12 @@
       <c r="AN212" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO212" s="1" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AP212" s="3" t="n">
+        <v>0.01363791339924993</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -26957,6 +28235,12 @@
       <c r="AN213" s="2" t="n">
         <v>-0.001650165016501646</v>
       </c>
+      <c r="AO213" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="AP213" s="3" t="n">
+        <v>0.005142332415059733</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -27081,6 +28365,12 @@
       <c r="AN214" s="2" t="n">
         <v>-0.001062699256110551</v>
       </c>
+      <c r="AO214" s="1" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="AP214" s="2" t="n">
+        <v>-0.001595744680851036</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -27205,6 +28495,12 @@
       <c r="AN215" s="2" t="n">
         <v>-0.002434912905038362</v>
       </c>
+      <c r="AO215" s="1" t="n">
+        <v>0.05327</v>
+      </c>
+      <c r="AP215" s="3" t="n">
+        <v>0.0001877581674802126</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -27329,6 +28625,12 @@
       <c r="AN216" s="2" t="n">
         <v>-0.01898734177215189</v>
       </c>
+      <c r="AO216" s="1" t="n">
+        <v>0.002013</v>
+      </c>
+      <c r="AP216" s="2" t="n">
+        <v>-0.0009925558312654252</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -27453,6 +28755,12 @@
       <c r="AN217" s="2" t="n">
         <v>-0.001164144353899829</v>
       </c>
+      <c r="AO217" s="1" t="n">
+        <v>5.993</v>
+      </c>
+      <c r="AP217" s="2" t="n">
+        <v>-0.002164502164502148</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -27577,6 +28885,12 @@
       <c r="AN218" s="3" t="n">
         <v>0.001418104467029125</v>
       </c>
+      <c r="AO218" s="1" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="AP218" s="2" t="n">
+        <v>-0.002596176540004749</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -27701,6 +29015,12 @@
       <c r="AN219" s="3" t="n">
         <v>0.002816372512204329</v>
       </c>
+      <c r="AO219" s="1" t="n">
+        <v>0.005324</v>
+      </c>
+      <c r="AP219" s="2" t="n">
+        <v>-0.003182924545965273</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -27825,6 +29145,12 @@
       <c r="AN220" s="2" t="n">
         <v>-0.002685546875000144</v>
       </c>
+      <c r="AO220" s="1" t="n">
+        <v>0.04093</v>
+      </c>
+      <c r="AP220" s="3" t="n">
+        <v>0.001958384332925427</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -27949,6 +29275,12 @@
       <c r="AN221" s="2" t="n">
         <v>-0.0008701705534285874</v>
       </c>
+      <c r="AO221" s="1" t="n">
+        <v>0.005752</v>
+      </c>
+      <c r="AP221" s="3" t="n">
+        <v>0.001916042501306496</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -28073,6 +29405,12 @@
       <c r="AN222" s="3" t="n">
         <v>0.006557377049180364</v>
       </c>
+      <c r="AO222" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="AP222" s="2" t="n">
+        <v>-0.005428881650380027</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -28197,6 +29535,12 @@
       <c r="AN223" s="2" t="n">
         <v>-0.003865596193874422</v>
       </c>
+      <c r="AO223" s="1" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AP223" s="2" t="n">
+        <v>-0.0002985074626867</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -28321,6 +29665,12 @@
       <c r="AN224" s="2" t="n">
         <v>-0.0006944444444444965</v>
       </c>
+      <c r="AO224" s="1" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="AP224" s="2" t="n">
+        <v>-0.00115821172110249</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -28445,6 +29795,12 @@
       <c r="AN225" s="3" t="n">
         <v>0.001084860173577542</v>
       </c>
+      <c r="AO225" s="1" t="n">
+        <v>0.08296000000000001</v>
+      </c>
+      <c r="AP225" s="2" t="n">
+        <v>-0.001083684527393051</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -28569,6 +29925,12 @@
       <c r="AN226" s="3" t="n">
         <v>0.002164502164502076</v>
       </c>
+      <c r="AO226" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="AP226" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -28693,6 +30055,12 @@
       <c r="AN227" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO227" s="1" t="n">
+        <v>0.04688</v>
+      </c>
+      <c r="AP227" s="2" t="n">
+        <v>-0.001916116670215027</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -28817,6 +30185,12 @@
       <c r="AN228" s="3" t="n">
         <v>0.006071118820468247</v>
       </c>
+      <c r="AO228" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="AP228" s="2" t="n">
+        <v>-0.0008620689655172063</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -28941,6 +30315,12 @@
       <c r="AN229" s="3" t="n">
         <v>0.002770083102493154</v>
       </c>
+      <c r="AO229" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="AP229" s="2" t="n">
+        <v>-0.003683241252302003</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -29065,6 +30445,12 @@
       <c r="AN230" s="3" t="n">
         <v>0.001204819277108301</v>
       </c>
+      <c r="AO230" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="AP230" s="2" t="n">
+        <v>-0.002406738868832634</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -29189,6 +30575,12 @@
       <c r="AN231" s="2" t="n">
         <v>-0.0009897723523589171</v>
       </c>
+      <c r="AO231" s="1" t="n">
+        <v>0.03032</v>
+      </c>
+      <c r="AP231" s="3" t="n">
+        <v>0.001321003963011835</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -29313,6 +30705,12 @@
       <c r="AN232" s="3" t="n">
         <v>0.002702702702702592</v>
       </c>
+      <c r="AO232" s="1" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="AP232" s="2" t="n">
+        <v>-0.007637017070979336</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -29437,6 +30835,12 @@
       <c r="AN233" s="3" t="n">
         <v>0.1318813716404079</v>
       </c>
+      <c r="AO233" s="1" t="n">
+        <v>0.11702</v>
+      </c>
+      <c r="AP233" s="2" t="n">
+        <v>-0.04184066159010893</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -29561,6 +30965,12 @@
       <c r="AN234" s="2" t="n">
         <v>-0.001577909270217008</v>
       </c>
+      <c r="AO234" s="1" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="AP234" s="2" t="n">
+        <v>-0.001185302252074149</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -29685,6 +31095,12 @@
       <c r="AN235" s="2" t="n">
         <v>-0.0002911631969719919</v>
       </c>
+      <c r="AO235" s="1" t="n">
+        <v>0.06868</v>
+      </c>
+      <c r="AP235" s="3" t="n">
+        <v>0.0001456239988351537</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -29809,6 +31225,12 @@
       <c r="AN236" s="3" t="n">
         <v>0.0047950131862864</v>
       </c>
+      <c r="AO236" s="1" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="AP236" s="2" t="n">
+        <v>-0.001033961663883075</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -29933,6 +31355,12 @@
       <c r="AN237" s="2" t="n">
         <v>-0.008553654743390458</v>
       </c>
+      <c r="AO237" s="1" t="n">
+        <v>0.03809</v>
+      </c>
+      <c r="AP237" s="2" t="n">
+        <v>-0.004183006535947723</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -30057,6 +31485,12 @@
       <c r="AN238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AP238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -30181,6 +31615,12 @@
       <c r="AN239" s="3" t="n">
         <v>0.001261034047919242</v>
       </c>
+      <c r="AO239" s="1" t="n">
+        <v>0.003901</v>
+      </c>
+      <c r="AP239" s="2" t="n">
+        <v>-0.01738035264483618</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -30305,6 +31745,12 @@
       <c r="AN240" s="3" t="n">
         <v>0.000729394602479912</v>
       </c>
+      <c r="AO240" s="1" t="n">
+        <v>0.01371</v>
+      </c>
+      <c r="AP240" s="2" t="n">
+        <v>-0.0007288629737609032</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -30429,6 +31875,12 @@
       <c r="AN241" s="3" t="n">
         <v>0.002929907595222049</v>
       </c>
+      <c r="AO241" s="1" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="AP241" s="2" t="n">
+        <v>-0.003820224719101077</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -30553,6 +32005,12 @@
       <c r="AN242" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO242" s="1" t="n">
+        <v>0.00742</v>
+      </c>
+      <c r="AP242" s="2" t="n">
+        <v>-0.004026845637583845</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -30677,6 +32135,12 @@
       <c r="AN243" s="2" t="n">
         <v>-0.001767565178966056</v>
       </c>
+      <c r="AO243" s="1" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="AP243" s="2" t="n">
+        <v>-0.005754758742806471</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -30801,6 +32265,12 @@
       <c r="AN244" s="2" t="n">
         <v>-0.001187648456057036</v>
       </c>
+      <c r="AO244" s="1" t="n">
+        <v>0.001686</v>
+      </c>
+      <c r="AP244" s="3" t="n">
+        <v>0.002378121284185551</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -30925,6 +32395,12 @@
       <c r="AN245" s="2" t="n">
         <v>-0.003053435114503904</v>
       </c>
+      <c r="AO245" s="1" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="AP245" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -31049,6 +32525,12 @@
       <c r="AN246" s="2" t="n">
         <v>-0.009171410499683919</v>
       </c>
+      <c r="AO246" s="1" t="n">
+        <v>0.03117</v>
+      </c>
+      <c r="AP246" s="2" t="n">
+        <v>-0.005106926268751898</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -31173,6 +32655,12 @@
       <c r="AN247" s="3" t="n">
         <v>0.002824858757062149</v>
       </c>
+      <c r="AO247" s="1" t="n">
+        <v>0.1773</v>
+      </c>
+      <c r="AP247" s="2" t="n">
+        <v>-0.001126760563380158</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -31297,6 +32785,12 @@
       <c r="AN248" s="3" t="n">
         <v>0.001982815598149406</v>
       </c>
+      <c r="AO248" s="1" t="n">
+        <v>0.03023</v>
+      </c>
+      <c r="AP248" s="2" t="n">
+        <v>-0.002968337730870706</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -31421,6 +32915,12 @@
       <c r="AN249" s="3" t="n">
         <v>0.0003667481662591114</v>
       </c>
+      <c r="AO249" s="1" t="n">
+        <v>0.008208</v>
+      </c>
+      <c r="AP249" s="3" t="n">
+        <v>0.003055114261273459</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -31545,6 +33045,12 @@
       <c r="AN250" s="3" t="n">
         <v>0.003551496702181665</v>
       </c>
+      <c r="AO250" s="1" t="n">
+        <v>0.01984</v>
+      </c>
+      <c r="AP250" s="3" t="n">
+        <v>0.003033367037411579</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -31669,6 +33175,12 @@
       <c r="AN251" s="2" t="n">
         <v>-0.0008628127696289554</v>
       </c>
+      <c r="AO251" s="1" t="n">
+        <v>0.04622</v>
+      </c>
+      <c r="AP251" s="2" t="n">
+        <v>-0.00215889464594134</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -31793,6 +33305,12 @@
       <c r="AN252" s="2" t="n">
         <v>-0.007205113306217264</v>
       </c>
+      <c r="AO252" s="1" t="n">
+        <v>0.008544</v>
+      </c>
+      <c r="AP252" s="3" t="n">
+        <v>0.0001170548987474266</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -31917,6 +33435,12 @@
       <c r="AN253" s="3" t="n">
         <v>0.001820546163849171</v>
       </c>
+      <c r="AO253" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="AP253" s="2" t="n">
+        <v>-0.007268951194184723</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -32041,6 +33565,12 @@
       <c r="AN254" s="2" t="n">
         <v>-0.0001639075561383882</v>
       </c>
+      <c r="AO254" s="1" t="n">
+        <v>0.06093</v>
+      </c>
+      <c r="AP254" s="2" t="n">
+        <v>-0.001147540983606568</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -32165,6 +33695,12 @@
       <c r="AN255" s="3" t="n">
         <v>0.0002835270768357525</v>
       </c>
+      <c r="AO255" s="1" t="n">
+        <v>0.003526</v>
+      </c>
+      <c r="AP255" s="2" t="n">
+        <v>-0.0005668934240362335</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -32289,6 +33825,12 @@
       <c r="AN256" s="2" t="n">
         <v>-0.007290581758666929</v>
       </c>
+      <c r="AO256" s="1" t="n">
+        <v>0.013375</v>
+      </c>
+      <c r="AP256" s="3" t="n">
+        <v>0.002323141486810535</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -32413,6 +33955,12 @@
       <c r="AN257" s="3" t="n">
         <v>1.000557310450677e-06</v>
       </c>
+      <c r="AO257" s="1" t="n">
+        <v>0.999443</v>
+      </c>
+      <c r="AP257" s="2" t="n">
+        <v>-1.000556309336747e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -32537,6 +34085,12 @@
       <c r="AN258" s="2" t="n">
         <v>-0.000565802874278696</v>
       </c>
+      <c r="AO258" s="1" t="n">
+        <v>0.08802</v>
+      </c>
+      <c r="AP258" s="2" t="n">
+        <v>-0.003396739130434723</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -32661,6 +34215,12 @@
       <c r="AN259" s="3" t="n">
         <v>0.0001120573733751246</v>
       </c>
+      <c r="AO259" s="1" t="n">
+        <v>0.08918</v>
+      </c>
+      <c r="AP259" s="2" t="n">
+        <v>-0.000784313725490203</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -32785,6 +34345,12 @@
       <c r="AN260" s="2" t="n">
         <v>-0.00405704450454877</v>
       </c>
+      <c r="AO260" s="1" t="n">
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="AP260" s="2" t="n">
+        <v>-0.003826688063202132</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -32909,6 +34475,12 @@
       <c r="AN261" s="3" t="n">
         <v>0.006178287731685697</v>
       </c>
+      <c r="AO261" s="1" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="AP261" s="2" t="n">
+        <v>-0.001754385964912282</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -33033,6 +34605,12 @@
       <c r="AN262" s="3" t="n">
         <v>0.0005141388174807881</v>
       </c>
+      <c r="AO262" s="1" t="n">
+        <v>0.003905</v>
+      </c>
+      <c r="AP262" s="3" t="n">
+        <v>0.003340184994861251</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -33157,6 +34735,12 @@
       <c r="AN263" s="3" t="n">
         <v>0.002652519893899157</v>
       </c>
+      <c r="AO263" s="1" t="n">
+        <v>0.1124</v>
+      </c>
+      <c r="AP263" s="2" t="n">
+        <v>-0.008818342151675493</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -33281,6 +34865,12 @@
       <c r="AN264" s="3" t="n">
         <v>0.007843137254901975</v>
       </c>
+      <c r="AO264" s="1" t="n">
+        <v>0.0006121</v>
+      </c>
+      <c r="AP264" s="2" t="n">
+        <v>-0.007619974059662873</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -33405,6 +34995,12 @@
       <c r="AN265" s="2" t="n">
         <v>-0.0006868131868131588</v>
       </c>
+      <c r="AO265" s="1" t="n">
+        <v>0.01453</v>
+      </c>
+      <c r="AP265" s="2" t="n">
+        <v>-0.001374570446735458</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -33529,6 +35125,12 @@
       <c r="AN266" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO266" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AP266" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -33653,6 +35255,12 @@
       <c r="AN267" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO267" s="1" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="AP267" s="2" t="n">
+        <v>-0.003080714725816477</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -33777,6 +35385,12 @@
       <c r="AN268" s="2" t="n">
         <v>-0.004159926045759163</v>
       </c>
+      <c r="AO268" s="1" t="n">
+        <v>0.0004292</v>
+      </c>
+      <c r="AP268" s="2" t="n">
+        <v>-0.003945230912044528</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -33901,6 +35515,12 @@
       <c r="AN269" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO269" s="1" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="AP269" s="3" t="n">
+        <v>0.0004821600771455927</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -34025,6 +35645,12 @@
       <c r="AN270" s="3" t="n">
         <v>0.003303964757709193</v>
       </c>
+      <c r="AO270" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="AP270" s="2" t="n">
+        <v>-0.0005488474204170636</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -34149,6 +35775,12 @@
       <c r="AN271" s="3" t="n">
         <v>0.0006779661016950288</v>
       </c>
+      <c r="AO271" s="1" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="AP271" s="2" t="n">
+        <v>-0.003387533875338756</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -34273,6 +35905,12 @@
       <c r="AN272" s="2" t="n">
         <v>-0.004300531242094699</v>
       </c>
+      <c r="AO272" s="1" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="AP272" s="2" t="n">
+        <v>-0.002540650406503962</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -34397,6 +36035,12 @@
       <c r="AN273" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO273" s="1" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="AP273" s="2" t="n">
+        <v>-0.002166847237269774</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -34521,6 +36165,12 @@
       <c r="AN274" s="3" t="n">
         <v>0.001105670510187968</v>
       </c>
+      <c r="AO274" s="1" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="AP274" s="2" t="n">
+        <v>-0.0007888923950773787</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -34645,6 +36295,12 @@
       <c r="AN275" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO275" s="1" t="n">
+        <v>0.01122</v>
+      </c>
+      <c r="AP275" s="2" t="n">
+        <v>-0.004436557231588261</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -34769,6 +36425,12 @@
       <c r="AN276" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO276" s="1" t="n">
+        <v>2.614</v>
+      </c>
+      <c r="AP276" s="3" t="n">
+        <v>0.001148985063194052</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -34893,6 +36555,12 @@
       <c r="AN277" s="2" t="n">
         <v>-0.001434377241214381</v>
       </c>
+      <c r="AO277" s="1" t="n">
+        <v>0.04176</v>
+      </c>
+      <c r="AP277" s="2" t="n">
+        <v>-0.0002394062724444113</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -35017,6 +36685,12 @@
       <c r="AN278" s="3" t="n">
         <v>0.0005128205128204919</v>
       </c>
+      <c r="AO278" s="1" t="n">
+        <v>0.01951</v>
+      </c>
+      <c r="AP278" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -35141,6 +36815,12 @@
       <c r="AN279" s="3" t="n">
         <v>0.003526714865103166</v>
       </c>
+      <c r="AO279" s="1" t="n">
+        <v>0.005679</v>
+      </c>
+      <c r="AP279" s="2" t="n">
+        <v>-0.002108592514496549</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -35265,6 +36945,12 @@
       <c r="AN280" s="3" t="n">
         <v>0.003094378545641957</v>
       </c>
+      <c r="AO280" s="1" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="AP280" s="3" t="n">
+        <v>0.004113110539845769</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -35389,6 +37075,12 @@
       <c r="AN281" s="2" t="n">
         <v>-0.002209944751381217</v>
       </c>
+      <c r="AO281" s="1" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="AP281" s="3" t="n">
+        <v>0.001107419712070876</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -35513,6 +37205,12 @@
       <c r="AN282" s="3" t="n">
         <v>0.007028599127484286</v>
       </c>
+      <c r="AO282" s="1" t="n">
+        <v>0.0004143</v>
+      </c>
+      <c r="AP282" s="2" t="n">
+        <v>-0.002888086642599348</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -35637,6 +37335,12 @@
       <c r="AN283" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO283" s="1" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="AP283" s="2" t="n">
+        <v>-0.0002439024390244649</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -35761,6 +37465,12 @@
       <c r="AN284" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO284" s="1" t="n">
+        <v>0.04198</v>
+      </c>
+      <c r="AP284" s="2" t="n">
+        <v>-0.001189626457292279</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -35885,6 +37595,12 @@
       <c r="AN285" s="2" t="n">
         <v>-0.001034612490594422</v>
       </c>
+      <c r="AO285" s="1" t="n">
+        <v>0.10614</v>
+      </c>
+      <c r="AP285" s="2" t="n">
+        <v>-0.0006590716505037249</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -36009,6 +37725,12 @@
       <c r="AN286" s="2" t="n">
         <v>-0.002386634844868845</v>
       </c>
+      <c r="AO286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="AP286" s="3" t="n">
+        <v>0.002392344497607766</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -36133,6 +37855,12 @@
       <c r="AN287" s="3" t="n">
         <v>0.0008298225456403613</v>
       </c>
+      <c r="AO287" s="1" t="n">
+        <v>0.15726</v>
+      </c>
+      <c r="AP287" s="3" t="n">
+        <v>0.002997640155622158</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -36257,6 +37985,12 @@
       <c r="AN288" s="3" t="n">
         <v>0.002776235424764022</v>
       </c>
+      <c r="AO288" s="1" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="AP288" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -36381,6 +38115,12 @@
       <c r="AN289" s="3" t="n">
         <v>0.000726568176313905</v>
       </c>
+      <c r="AO289" s="1" t="n">
+        <v>4.121</v>
+      </c>
+      <c r="AP289" s="2" t="n">
+        <v>-0.002662149080348314</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -36505,6 +38245,12 @@
       <c r="AN290" s="2" t="n">
         <v>-0.002575810794988853</v>
       </c>
+      <c r="AO290" s="1" t="n">
+        <v>0.08516</v>
+      </c>
+      <c r="AP290" s="2" t="n">
+        <v>-0.0003521540086864919</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -36629,6 +38375,12 @@
       <c r="AN291" s="2" t="n">
         <v>-0.001410835214446993</v>
       </c>
+      <c r="AO291" s="1" t="n">
+        <v>0.03547</v>
+      </c>
+      <c r="AP291" s="3" t="n">
+        <v>0.00226052557219564</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -36753,6 +38505,12 @@
       <c r="AN292" s="3" t="n">
         <v>0.001905799074326105</v>
       </c>
+      <c r="AO292" s="1" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AP292" s="2" t="n">
+        <v>-0.001358695652173914</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -36877,6 +38635,12 @@
       <c r="AN293" s="2" t="n">
         <v>-0.0005133470225873371</v>
       </c>
+      <c r="AO293" s="1" t="n">
+        <v>0.005829</v>
+      </c>
+      <c r="AP293" s="2" t="n">
+        <v>-0.00205444273240881</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -37001,6 +38765,12 @@
       <c r="AN294" s="2" t="n">
         <v>-0.001754899093302241</v>
       </c>
+      <c r="AO294" s="1" t="n">
+        <v>0.003408</v>
+      </c>
+      <c r="AP294" s="2" t="n">
+        <v>-0.001464986815118604</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -37125,6 +38895,12 @@
       <c r="AN295" s="2" t="n">
         <v>-0.0005586592178772402</v>
       </c>
+      <c r="AO295" s="1" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="AP295" s="2" t="n">
+        <v>-0.0003726476616358822</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -37249,6 +39025,12 @@
       <c r="AN296" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO296" s="1" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="AP296" s="3" t="n">
+        <v>0.0004448398576511965</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -37373,6 +39155,12 @@
       <c r="AN297" s="3" t="n">
         <v>0.004201680672268736</v>
       </c>
+      <c r="AO297" s="1" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="AP297" s="2" t="n">
+        <v>-0.004184100418409871</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -37497,6 +39285,12 @@
       <c r="AN298" s="2" t="n">
         <v>-0.003542234332424981</v>
       </c>
+      <c r="AO298" s="1" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AP298" s="3" t="n">
+        <v>0.00300792999726549</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -37621,6 +39415,12 @@
       <c r="AN299" s="3" t="n">
         <v>0.003619909502262296</v>
       </c>
+      <c r="AO299" s="1" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AP299" s="2" t="n">
+        <v>-0.002705139765554444</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -37745,6 +39545,12 @@
       <c r="AN300" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO300" s="1" t="n">
+        <v>0.02046</v>
+      </c>
+      <c r="AP300" s="2" t="n">
+        <v>-0.0004885197850512747</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -37869,6 +39675,12 @@
       <c r="AN301" s="3" t="n">
         <v>0.0102310231023102</v>
       </c>
+      <c r="AO301" s="1" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AP301" s="3" t="n">
+        <v>0.002613524991832809</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -37993,6 +39805,12 @@
       <c r="AN302" s="2" t="n">
         <v>-0.0007246376811593908</v>
       </c>
+      <c r="AO302" s="1" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="AP302" s="3" t="n">
+        <v>0.001450326323422711</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -38117,6 +39935,12 @@
       <c r="AN303" s="2" t="n">
         <v>-0.0009509577503056735</v>
       </c>
+      <c r="AO303" s="1" t="n">
+        <v>0.07359</v>
+      </c>
+      <c r="AP303" s="3" t="n">
+        <v>0.0006799020940985637</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -38241,6 +40065,12 @@
       <c r="AN304" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO304" s="1" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="AP304" s="2" t="n">
+        <v>-0.001263423878711256</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -38365,6 +40195,12 @@
       <c r="AN305" s="2" t="n">
         <v>-0.002969213939678225</v>
       </c>
+      <c r="AO305" s="1" t="n">
+        <v>0.06378</v>
+      </c>
+      <c r="AP305" s="2" t="n">
+        <v>-0.0003134796238243299</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -38489,6 +40325,12 @@
       <c r="AN306" s="2" t="n">
         <v>-0.004859283255719864</v>
       </c>
+      <c r="AO306" s="1" t="n">
+        <v>0.04905</v>
+      </c>
+      <c r="AP306" s="2" t="n">
+        <v>-0.002034587995930741</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -38613,6 +40455,12 @@
       <c r="AN307" s="2" t="n">
         <v>-0.002164502164502166</v>
       </c>
+      <c r="AO307" s="1" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="AP307" s="2" t="n">
+        <v>-0.003253796095444688</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -38737,6 +40585,12 @@
       <c r="AN308" s="3" t="n">
         <v>0.001008318628686799</v>
       </c>
+      <c r="AO308" s="1" t="n">
+        <v>0.03963</v>
+      </c>
+      <c r="AP308" s="2" t="n">
+        <v>-0.002014605892722329</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -38861,6 +40715,12 @@
       <c r="AN309" s="2" t="n">
         <v>-0.002585649644473181</v>
       </c>
+      <c r="AO309" s="1" t="n">
+        <v>0.01535</v>
+      </c>
+      <c r="AP309" s="2" t="n">
+        <v>-0.005184705119896207</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -38985,6 +40845,12 @@
       <c r="AN310" s="2" t="n">
         <v>-0.001652285661832198</v>
       </c>
+      <c r="AO310" s="1" t="n">
+        <v>0.05437</v>
+      </c>
+      <c r="AP310" s="2" t="n">
+        <v>-0.000183891136447152</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -39109,6 +40975,12 @@
       <c r="AN311" s="2" t="n">
         <v>-0.001120573733751635</v>
       </c>
+      <c r="AO311" s="1" t="n">
+        <v>0.004468</v>
+      </c>
+      <c r="AP311" s="3" t="n">
+        <v>0.002468027821404471</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -39233,6 +41105,12 @@
       <c r="AN312" s="2" t="n">
         <v>-0.0009451795841211083</v>
       </c>
+      <c r="AO312" s="1" t="n">
+        <v>0.08443000000000001</v>
+      </c>
+      <c r="AP312" s="2" t="n">
+        <v>-0.001537369914853255</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -39357,6 +41235,12 @@
       <c r="AN313" s="2" t="n">
         <v>-0.002285867957509795</v>
       </c>
+      <c r="AO313" s="1" t="n">
+        <v>0.07407</v>
+      </c>
+      <c r="AP313" s="2" t="n">
+        <v>-0.001752021563342387</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -39481,6 +41365,12 @@
       <c r="AN314" s="2" t="n">
         <v>-0.001964636542239651</v>
       </c>
+      <c r="AO314" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="AP314" s="2" t="n">
+        <v>-0.0006561679790027345</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -39605,6 +41495,12 @@
       <c r="AN315" s="2" t="n">
         <v>-0.0006293266205161531</v>
       </c>
+      <c r="AO315" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="AP315" s="3" t="n">
+        <v>0.0006297229219144632</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -39729,6 +41625,12 @@
       <c r="AN316" s="2" t="n">
         <v>-0.004994450610432919</v>
       </c>
+      <c r="AO316" s="1" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="AP316" s="2" t="n">
+        <v>-0.003904071388733845</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -39853,6 +41755,12 @@
       <c r="AN317" s="3" t="n">
         <v>0.001340842048806596</v>
       </c>
+      <c r="AO317" s="1" t="n">
+        <v>0.007457</v>
+      </c>
+      <c r="AP317" s="2" t="n">
+        <v>-0.001472951258703766</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -39977,6 +41885,12 @@
       <c r="AN318" s="3" t="n">
         <v>0.002948113207547118</v>
       </c>
+      <c r="AO318" s="1" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="AP318" s="2" t="n">
+        <v>-0.001763668430335093</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -40101,6 +42015,12 @@
       <c r="AN319" s="2" t="n">
         <v>-0.00067910501108002</v>
       </c>
+      <c r="AO319" s="1" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="AP319" s="3" t="n">
+        <v>0.0007153331664221824</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -40225,6 +42145,12 @@
       <c r="AN320" s="3" t="n">
         <v>0.0002281021897809968</v>
       </c>
+      <c r="AO320" s="1" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="AP320" s="2" t="n">
+        <v>-0.001596351197263349</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -40349,6 +42275,12 @@
       <c r="AN321" s="3" t="n">
         <v>0.001679152673727606</v>
       </c>
+      <c r="AO321" s="1" t="n">
+        <v>0.07739</v>
+      </c>
+      <c r="AP321" s="2" t="n">
+        <v>-0.002063185041908362</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -40473,6 +42405,12 @@
       <c r="AN322" s="2" t="n">
         <v>-0.001239925604463768</v>
       </c>
+      <c r="AO322" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="AP322" s="3" t="n">
+        <v>0.003103662321539419</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -40597,6 +42535,12 @@
       <c r="AN323" s="3" t="n">
         <v>0.001013684744044603</v>
       </c>
+      <c r="AO323" s="1" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="AP323" s="2" t="n">
+        <v>-0.00658227848101272</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -40721,6 +42665,12 @@
       <c r="AN324" s="2" t="n">
         <v>-0.002875939849624067</v>
       </c>
+      <c r="AO324" s="1" t="n">
+        <v>0.052933</v>
+      </c>
+      <c r="AP324" s="2" t="n">
+        <v>-0.002149037645861143</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -40845,6 +42795,12 @@
       <c r="AN325" s="2" t="n">
         <v>-0.005034654112723898</v>
       </c>
+      <c r="AO325" s="1" t="n">
+        <v>0.15174</v>
+      </c>
+      <c r="AP325" s="2" t="n">
+        <v>-0.002825786948807163</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -40969,6 +42925,12 @@
       <c r="AN326" s="2" t="n">
         <v>-0.001084094780857993</v>
       </c>
+      <c r="AO326" s="1" t="n">
+        <v>0.006455</v>
+      </c>
+      <c r="AP326" s="3" t="n">
+        <v>0.0007751937984495808</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -41093,6 +43055,12 @@
       <c r="AN327" s="3" t="n">
         <v>0.000593667546174164</v>
       </c>
+      <c r="AO327" s="1" t="n">
+        <v>0.015143</v>
+      </c>
+      <c r="AP327" s="2" t="n">
+        <v>-0.001714022018590545</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -41217,6 +43185,12 @@
       <c r="AN328" s="2" t="n">
         <v>-0.002087682672233736</v>
       </c>
+      <c r="AO328" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="AP328" s="2" t="n">
+        <v>-0.005230125523012556</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -41341,6 +43315,12 @@
       <c r="AN329" s="2" t="n">
         <v>-0.000916590284142911</v>
       </c>
+      <c r="AO329" s="1" t="n">
+        <v>0.004359</v>
+      </c>
+      <c r="AP329" s="2" t="n">
+        <v>-0.000229357798165168</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -41465,6 +43445,12 @@
       <c r="AN330" s="3" t="n">
         <v>0.0009671179883944776</v>
       </c>
+      <c r="AO330" s="1" t="n">
+        <v>0.05179</v>
+      </c>
+      <c r="AP330" s="3" t="n">
+        <v>0.0007729468599034843</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -41589,6 +43575,12 @@
       <c r="AN331" s="2" t="n">
         <v>-0.001683029453015554</v>
       </c>
+      <c r="AO331" s="1" t="n">
+        <v>0.03558</v>
+      </c>
+      <c r="AP331" s="2" t="n">
+        <v>-0.0002809778027534736</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -41713,6 +43705,12 @@
       <c r="AN332" s="2" t="n">
         <v>-0.004739336492891037</v>
       </c>
+      <c r="AO332" s="1" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="AP332" s="3" t="n">
+        <v>0.0006802721088436513</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -41837,6 +43835,12 @@
       <c r="AN333" s="2" t="n">
         <v>-0.002083333333333393</v>
       </c>
+      <c r="AO333" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="AP333" s="2" t="n">
+        <v>-0.00104384133611694</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -41961,6 +43965,12 @@
       <c r="AN334" s="3" t="n">
         <v>0.0006811989100816373</v>
       </c>
+      <c r="AO334" s="1" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="AP334" s="3" t="n">
+        <v>0.0006807351940095813</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -42085,6 +44095,12 @@
       <c r="AN335" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO335" s="1" t="n">
+        <v>0.08119</v>
+      </c>
+      <c r="AP335" s="2" t="n">
+        <v>-0.0007384615384615937</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -42209,6 +44225,12 @@
       <c r="AN336" s="3" t="n">
         <v>0.00193986420950539</v>
       </c>
+      <c r="AO336" s="1" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="AP336" s="2" t="n">
+        <v>-0.00048402710551799</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -42333,6 +44355,12 @@
       <c r="AN337" s="2" t="n">
         <v>-0.002976190476190527</v>
       </c>
+      <c r="AO337" s="1" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AP337" s="2" t="n">
+        <v>-0.0009950248756218499</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -42457,6 +44485,12 @@
       <c r="AN338" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO338" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AP338" s="2" t="n">
+        <v>-0.002645502645502599</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -42581,6 +44615,12 @@
       <c r="AN339" s="2" t="n">
         <v>-0.001100110011001246</v>
       </c>
+      <c r="AO339" s="1" t="n">
+        <v>0.01813</v>
+      </c>
+      <c r="AP339" s="2" t="n">
+        <v>-0.001651982378854558</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -42705,6 +44745,12 @@
       <c r="AN340" s="2" t="n">
         <v>-0.01050124499296317</v>
       </c>
+      <c r="AO340" s="1" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="AP340" s="3" t="n">
+        <v>0.01050328227571114</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -42829,6 +44875,12 @@
       <c r="AN341" s="2" t="n">
         <v>-0.0007019185774450689</v>
       </c>
+      <c r="AO341" s="1" t="n">
+        <v>0.04257</v>
+      </c>
+      <c r="AP341" s="2" t="n">
+        <v>-0.003277920861624941</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -42953,6 +45005,12 @@
       <c r="AN342" s="3" t="n">
         <v>0.001651003302006493</v>
       </c>
+      <c r="AO342" s="1" t="n">
+        <v>0.07854</v>
+      </c>
+      <c r="AP342" s="2" t="n">
+        <v>-0.004184100418410003</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -43077,6 +45135,12 @@
       <c r="AN343" s="2" t="n">
         <v>-0.001968503937007832</v>
       </c>
+      <c r="AO343" s="1" t="n">
+        <v>7.593</v>
+      </c>
+      <c r="AP343" s="2" t="n">
+        <v>-0.001577909270217022</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -43201,6 +45265,12 @@
       <c r="AN344" s="2" t="n">
         <v>-0.001826029216467631</v>
       </c>
+      <c r="AO344" s="1" t="n">
+        <v>0.6005</v>
+      </c>
+      <c r="AP344" s="2" t="n">
+        <v>-0.001330450690171149</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -43325,6 +45395,12 @@
       <c r="AN345" s="2" t="n">
         <v>-0.0002684563758388221</v>
       </c>
+      <c r="AO345" s="1" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="AP345" s="2" t="n">
+        <v>-0.002148227712137585</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -43449,6 +45525,12 @@
       <c r="AN346" s="3" t="n">
         <v>0.002409638554216769</v>
       </c>
+      <c r="AO346" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="AP346" s="2" t="n">
+        <v>-0.002403846153846056</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -43573,6 +45655,12 @@
       <c r="AN347" s="3" t="n">
         <v>0.00171624713958807</v>
       </c>
+      <c r="AO347" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="AP347" s="2" t="n">
+        <v>-0.002855511136493435</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -43697,6 +45785,12 @@
       <c r="AN348" s="2" t="n">
         <v>-0.0005580035019531173</v>
       </c>
+      <c r="AO348" s="1" t="n">
+        <v>5193.7</v>
+      </c>
+      <c r="AP348" s="2" t="n">
+        <v>-9.626121443148127e-05</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -43821,6 +45915,12 @@
       <c r="AN349" s="3" t="n">
         <v>0.0007336757153337926</v>
       </c>
+      <c r="AO349" s="1" t="n">
+        <v>0.01385</v>
+      </c>
+      <c r="AP349" s="3" t="n">
+        <v>0.0153958944281525</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -43945,6 +46045,12 @@
       <c r="AN350" s="2" t="n">
         <v>-0.002562459961563107</v>
       </c>
+      <c r="AO350" s="1" t="n">
+        <v>0.01541</v>
+      </c>
+      <c r="AP350" s="2" t="n">
+        <v>-0.01027617212588314</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -44069,6 +46175,12 @@
       <c r="AN351" s="3" t="n">
         <v>0.0003255738238645692</v>
       </c>
+      <c r="AO351" s="1" t="n">
+        <v>0.0006114</v>
+      </c>
+      <c r="AP351" s="2" t="n">
+        <v>-0.005044751830756747</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -44193,6 +46305,12 @@
       <c r="AN352" s="3" t="n">
         <v>0.002539360081259595</v>
       </c>
+      <c r="AO352" s="1" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="AP352" s="2" t="n">
+        <v>-0.001519756838905889</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -44317,6 +46435,12 @@
       <c r="AN353" s="3" t="n">
         <v>0.00246595904363669</v>
       </c>
+      <c r="AO353" s="1" t="n">
+        <v>0.09354999999999999</v>
+      </c>
+      <c r="AP353" s="3" t="n">
+        <v>0.0005347593582887112</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -44441,6 +46565,12 @@
       <c r="AN354" s="3" t="n">
         <v>0.001112347052280343</v>
       </c>
+      <c r="AO354" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="AP354" s="2" t="n">
+        <v>-0.001111111111111143</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -44565,6 +46695,12 @@
       <c r="AN355" s="2" t="n">
         <v>-0.001965280052407516</v>
       </c>
+      <c r="AO355" s="1" t="n">
+        <v>0.0006081</v>
+      </c>
+      <c r="AP355" s="2" t="n">
+        <v>-0.002133245815556248</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -44689,6 +46825,12 @@
       <c r="AN356" s="3" t="n">
         <v>0.004999999999999893</v>
       </c>
+      <c r="AO356" s="1" t="n">
+        <v>2.009</v>
+      </c>
+      <c r="AP356" s="2" t="n">
+        <v>-0.0004975124378108905</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -44813,6 +46955,12 @@
       <c r="AN357" s="3" t="n">
         <v>0.006544502617801084</v>
       </c>
+      <c r="AO357" s="1" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="AP357" s="2" t="n">
+        <v>-0.004768097095795361</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -44937,6 +47085,12 @@
       <c r="AN358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO358" s="1" t="n">
+        <v>0.000406</v>
+      </c>
+      <c r="AP358" s="2" t="n">
+        <v>-0.002457002457002516</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -45061,6 +47215,12 @@
       <c r="AN359" s="2" t="n">
         <v>-0.001358695652173975</v>
       </c>
+      <c r="AO359" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="AP359" s="3" t="n">
+        <v>0.001360544217687137</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -45185,6 +47345,12 @@
       <c r="AN360" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO360" s="1" t="n">
+        <v>0.003313</v>
+      </c>
+      <c r="AP360" s="2" t="n">
+        <v>-0.002408912978018728</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -45309,6 +47475,12 @@
       <c r="AN361" s="2" t="n">
         <v>-0.003945084424806782</v>
       </c>
+      <c r="AO361" s="1" t="n">
+        <v>0.6303</v>
+      </c>
+      <c r="AP361" s="2" t="n">
+        <v>-0.001425855513308004</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -45433,6 +47605,12 @@
       <c r="AN362" s="3" t="n">
         <v>0.002120441051738822</v>
       </c>
+      <c r="AO362" s="1" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="AP362" s="2" t="n">
+        <v>-0.00423190859077456</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -45557,6 +47735,12 @@
       <c r="AN363" s="3" t="n">
         <v>0.00215749730312839</v>
       </c>
+      <c r="AO363" s="1" t="n">
+        <v>0.06411</v>
+      </c>
+      <c r="AP363" s="2" t="n">
+        <v>-0.01414731662309709</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -45681,6 +47865,12 @@
       <c r="AN364" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO364" s="1" t="n">
+        <v>4.689</v>
+      </c>
+      <c r="AP364" s="2" t="n">
+        <v>-0.001277955271565544</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -45805,6 +47995,12 @@
       <c r="AN365" s="2" t="n">
         <v>-0.001251216460447558</v>
       </c>
+      <c r="AO365" s="1" t="n">
+        <v>0.07194</v>
+      </c>
+      <c r="AP365" s="3" t="n">
+        <v>0.001391982182628102</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -45929,6 +48125,12 @@
       <c r="AN366" s="2" t="n">
         <v>-0.0001796945193170912</v>
       </c>
+      <c r="AO366" s="1" t="n">
+        <v>0.05548</v>
+      </c>
+      <c r="AP366" s="2" t="n">
+        <v>-0.00287562904385335</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -46053,6 +48255,12 @@
       <c r="AN367" s="2" t="n">
         <v>-0.003097040605643489</v>
       </c>
+      <c r="AO367" s="1" t="n">
+        <v>0.05783</v>
+      </c>
+      <c r="AP367" s="2" t="n">
+        <v>-0.001898515705902641</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -46177,6 +48385,12 @@
       <c r="AN368" s="3" t="n">
         <v>0.001936619718309841</v>
       </c>
+      <c r="AO368" s="1" t="n">
+        <v>0.05674</v>
+      </c>
+      <c r="AP368" s="2" t="n">
+        <v>-0.002987172728870207</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -46301,6 +48515,12 @@
       <c r="AN369" s="3" t="n">
         <v>0.002261712439418437</v>
       </c>
+      <c r="AO369" s="1" t="n">
+        <v>0.03097</v>
+      </c>
+      <c r="AP369" s="2" t="n">
+        <v>-0.001611863313990908</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -46425,6 +48645,12 @@
       <c r="AN370" s="2" t="n">
         <v>-0.001241464928615797</v>
       </c>
+      <c r="AO370" s="1" t="n">
+        <v>0.0001604</v>
+      </c>
+      <c r="AP370" s="2" t="n">
+        <v>-0.003107520198881368</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -46549,6 +48775,12 @@
       <c r="AN371" s="2" t="n">
         <v>-0.002648616833431399</v>
       </c>
+      <c r="AO371" s="1" t="n">
+        <v>0.006776</v>
+      </c>
+      <c r="AP371" s="2" t="n">
+        <v>-0.0002950722927117535</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -46673,6 +48905,12 @@
       <c r="AN372" s="3" t="n">
         <v>0.002611344842593905</v>
       </c>
+      <c r="AO372" s="1" t="n">
+        <v>0.006902</v>
+      </c>
+      <c r="AP372" s="2" t="n">
+        <v>-0.001302271740703149</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -46797,6 +49035,12 @@
       <c r="AN373" s="2" t="n">
         <v>-0.0007820646506777033</v>
       </c>
+      <c r="AO373" s="1" t="n">
+        <v>3.836</v>
+      </c>
+      <c r="AP373" s="3" t="n">
+        <v>0.0007826767545003051</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -46921,6 +49165,12 @@
       <c r="AN374" s="2" t="n">
         <v>-0.004571428571428583</v>
       </c>
+      <c r="AO374" s="1" t="n">
+        <v>0.06969</v>
+      </c>
+      <c r="AP374" s="3" t="n">
+        <v>0.0001435132032146401</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -47045,6 +49295,12 @@
       <c r="AN375" s="3" t="n">
         <v>0.001266303659617613</v>
       </c>
+      <c r="AO375" s="1" t="n">
+        <v>0.07904</v>
+      </c>
+      <c r="AP375" s="2" t="n">
+        <v>-0.0003794106487922379</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -47169,6 +49425,12 @@
       <c r="AN376" s="3" t="n">
         <v>0.0006360311655270849</v>
       </c>
+      <c r="AO376" s="1" t="n">
+        <v>0.06289</v>
+      </c>
+      <c r="AP376" s="2" t="n">
+        <v>-0.0006356268870172949</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -47293,6 +49555,12 @@
       <c r="AN377" s="3" t="n">
         <v>0.001564129301355696</v>
       </c>
+      <c r="AO377" s="1" t="n">
+        <v>0.07668</v>
+      </c>
+      <c r="AP377" s="2" t="n">
+        <v>-0.00208224882873513</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -47417,6 +49685,12 @@
       <c r="AN378" s="2" t="n">
         <v>-0.001237317495669419</v>
       </c>
+      <c r="AO378" s="1" t="n">
+        <v>0.0004029</v>
+      </c>
+      <c r="AP378" s="2" t="n">
+        <v>-0.001734390485629378</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -47541,6 +49815,12 @@
       <c r="AN379" s="2" t="n">
         <v>-0.003663003663003561</v>
       </c>
+      <c r="AO379" s="1" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="AP379" s="2" t="n">
+        <v>-0.0005446623093681694</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -47665,6 +49945,12 @@
       <c r="AN380" s="2" t="n">
         <v>-0.005087209302325626</v>
       </c>
+      <c r="AO380" s="1" t="n">
+        <v>0.001378</v>
+      </c>
+      <c r="AP380" s="3" t="n">
+        <v>0.006574141709276925</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -47789,6 +50075,12 @@
       <c r="AN381" s="3" t="n">
         <v>0.002844500632111219</v>
       </c>
+      <c r="AO381" s="1" t="n">
+        <v>6.348</v>
+      </c>
+      <c r="AP381" s="3" t="n">
+        <v>0.0003151591553734289</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -47913,6 +50205,12 @@
       <c r="AN382" s="2" t="n">
         <v>-0.0007132667617688725</v>
       </c>
+      <c r="AO382" s="1" t="n">
+        <v>0.01395</v>
+      </c>
+      <c r="AP382" s="2" t="n">
+        <v>-0.004282655246252626</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -48037,6 +50335,12 @@
       <c r="AN383" s="2" t="n">
         <v>-0.001718213058419174</v>
       </c>
+      <c r="AO383" s="1" t="n">
+        <v>0.01741</v>
+      </c>
+      <c r="AP383" s="2" t="n">
+        <v>-0.001147446930579613</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -48161,6 +50465,12 @@
       <c r="AN384" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO384" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="AP384" s="2" t="n">
+        <v>-0.002958579881656889</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -48285,6 +50595,12 @@
       <c r="AN385" s="2" t="n">
         <v>-0.0004467277194551414</v>
       </c>
+      <c r="AO385" s="1" t="n">
+        <v>4.468</v>
+      </c>
+      <c r="AP385" s="2" t="n">
+        <v>-0.001564245810055793</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -48409,6 +50725,12 @@
       <c r="AN386" s="2" t="n">
         <v>-0.001536098310291896</v>
       </c>
+      <c r="AO386" s="1" t="n">
+        <v>0.001309</v>
+      </c>
+      <c r="AP386" s="3" t="n">
+        <v>0.006923076923077008</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -48533,6 +50855,12 @@
       <c r="AN387" s="2" t="n">
         <v>-0.001867572156196897</v>
       </c>
+      <c r="AO387" s="1" t="n">
+        <v>0.0005863</v>
+      </c>
+      <c r="AP387" s="2" t="n">
+        <v>-0.002721551284232078</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -48657,6 +50985,12 @@
       <c r="AN388" s="2" t="n">
         <v>-0.00263620386643223</v>
       </c>
+      <c r="AO388" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="AP388" s="2" t="n">
+        <v>-0.004405286343612461</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -48781,6 +51115,12 @@
       <c r="AN389" s="2" t="n">
         <v>-0.00110741971207083</v>
       </c>
+      <c r="AO389" s="1" t="n">
+        <v>0.00899</v>
+      </c>
+      <c r="AP389" s="2" t="n">
+        <v>-0.003325942350332651</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -48905,6 +51245,12 @@
       <c r="AN390" s="2" t="n">
         <v>-0.002669039145907497</v>
       </c>
+      <c r="AO390" s="1" t="n">
+        <v>0.07825</v>
+      </c>
+      <c r="AP390" s="2" t="n">
+        <v>-0.002803619217535338</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -49029,6 +51375,12 @@
       <c r="AN391" s="2" t="n">
         <v>-0.0007723498744932479</v>
       </c>
+      <c r="AO391" s="1" t="n">
+        <v>0.05163</v>
+      </c>
+      <c r="AP391" s="2" t="n">
+        <v>-0.002318840579710051</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -49153,6 +51505,12 @@
       <c r="AN392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO392" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="AP392" s="2" t="n">
+        <v>-0.008438818565400866</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -49277,6 +51635,12 @@
       <c r="AN393" s="3" t="n">
         <v>0.004267425320056889</v>
       </c>
+      <c r="AO393" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="AP393" s="2" t="n">
+        <v>-0.0009442870632671947</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -49401,6 +51765,12 @@
       <c r="AN394" s="2" t="n">
         <v>-0.003978120338140205</v>
       </c>
+      <c r="AO394" s="1" t="n">
+        <v>0.2006</v>
+      </c>
+      <c r="AP394" s="3" t="n">
+        <v>0.001497753369945056</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -49525,6 +51895,12 @@
       <c r="AN395" s="2" t="n">
         <v>-0.00205128205128211</v>
       </c>
+      <c r="AO395" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="AP395" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -49649,6 +52025,12 @@
       <c r="AN396" s="2" t="n">
         <v>-0.001093294460641441</v>
       </c>
+      <c r="AO396" s="1" t="n">
+        <v>2.743</v>
+      </c>
+      <c r="AP396" s="3" t="n">
+        <v>0.0007296607077708062</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -49773,6 +52155,12 @@
       <c r="AN397" s="3" t="n">
         <v>0.003167062549485355</v>
       </c>
+      <c r="AO397" s="1" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="AP397" s="2" t="n">
+        <v>-0.0007892659826360615</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -49897,6 +52285,12 @@
       <c r="AN398" s="3" t="n">
         <v>0.01200640341515472</v>
       </c>
+      <c r="AO398" s="1" t="n">
+        <v>0.007544</v>
+      </c>
+      <c r="AP398" s="2" t="n">
+        <v>-0.005536514632217177</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -50021,6 +52415,12 @@
       <c r="AN399" s="2" t="n">
         <v>-0.003889537145079739</v>
       </c>
+      <c r="AO399" s="1" t="n">
+        <v>0.2559</v>
+      </c>
+      <c r="AP399" s="2" t="n">
+        <v>-0.0007809449433814057</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -50145,6 +52545,12 @@
       <c r="AN400" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO400" s="1" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AP400" s="2" t="n">
+        <v>-0.0009436929852155472</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -50269,6 +52675,12 @@
       <c r="AN401" s="2" t="n">
         <v>-0.001379500620775343</v>
       </c>
+      <c r="AO401" s="1" t="n">
+        <v>0.007229</v>
+      </c>
+      <c r="AP401" s="2" t="n">
+        <v>-0.001381406271584417</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -50393,6 +52805,12 @@
       <c r="AN402" s="2" t="n">
         <v>-0.0006568863586598491</v>
       </c>
+      <c r="AO402" s="1" t="n">
+        <v>0.00456</v>
+      </c>
+      <c r="AP402" s="2" t="n">
+        <v>-0.0008764241893077411</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -50517,6 +52935,12 @@
       <c r="AN403" s="2" t="n">
         <v>-0.003775009437523597</v>
       </c>
+      <c r="AO403" s="1" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AP403" s="3" t="n">
+        <v>0.0003789314134141303</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -50641,6 +53065,12 @@
       <c r="AN404" s="2" t="n">
         <v>-0.005044136191677203</v>
       </c>
+      <c r="AO404" s="1" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="AP404" s="2" t="n">
+        <v>-0.008871989860582978</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -50765,6 +53195,12 @@
       <c r="AN405" s="2" t="n">
         <v>-0.0002337814143775627</v>
       </c>
+      <c r="AO405" s="1" t="n">
+        <v>0.0008563000000000001</v>
+      </c>
+      <c r="AP405" s="3" t="n">
+        <v>0.001169180404536448</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -50889,6 +53325,12 @@
       <c r="AN406" s="3" t="n">
         <v>0.0005960659646333262</v>
       </c>
+      <c r="AO406" s="1" t="n">
+        <v>0.005021</v>
+      </c>
+      <c r="AP406" s="2" t="n">
+        <v>-0.002978554408260403</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -51013,6 +53455,12 @@
       <c r="AN407" s="2" t="n">
         <v>-0.005012531328320743</v>
       </c>
+      <c r="AO407" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="AP407" s="3" t="n">
+        <v>0.003358522250209916</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -51137,6 +53585,12 @@
       <c r="AN408" s="3" t="n">
         <v>0.006056527590847989</v>
       </c>
+      <c r="AO408" s="1" t="n">
+        <v>0.001495</v>
+      </c>
+      <c r="AP408" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -51261,6 +53715,12 @@
       <c r="AN409" s="2" t="n">
         <v>-0.007631645891630495</v>
       </c>
+      <c r="AO409" s="1" t="n">
+        <v>0.03877</v>
+      </c>
+      <c r="AP409" s="2" t="n">
+        <v>-0.006152268649064447</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -51385,6 +53845,12 @@
       <c r="AN410" s="3" t="n">
         <v>0.001233045622688203</v>
       </c>
+      <c r="AO410" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="AP410" s="2" t="n">
+        <v>-0.001231527093596222</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -51509,6 +53975,12 @@
       <c r="AN411" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO411" s="1" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="AP411" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -51633,6 +54105,12 @@
       <c r="AN412" s="3" t="n">
         <v>0.001482799525504194</v>
       </c>
+      <c r="AO412" s="1" t="n">
+        <v>0.06756</v>
+      </c>
+      <c r="AP412" s="3" t="n">
+        <v>0.0002961208172933409</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -51757,6 +54235,12 @@
       <c r="AN413" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO413" s="1" t="n">
+        <v>2527</v>
+      </c>
+      <c r="AP413" s="2" t="n">
+        <v>-0.0003955696202531646</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -51881,6 +54365,12 @@
       <c r="AN414" s="3" t="n">
         <v>0.0009527439024390517</v>
       </c>
+      <c r="AO414" s="1" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="AP414" s="3" t="n">
+        <v>0.0003807348181991088</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -52005,6 +54495,12 @@
       <c r="AN415" s="3" t="n">
         <v>0.0005714285714285085</v>
       </c>
+      <c r="AO415" s="1" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="AP415" s="2" t="n">
+        <v>-0.003426613363791995</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -52129,6 +54625,12 @@
       <c r="AN416" s="2" t="n">
         <v>-0.002910360884749792</v>
       </c>
+      <c r="AO416" s="1" t="n">
+        <v>0.06844</v>
+      </c>
+      <c r="AP416" s="2" t="n">
+        <v>-0.001167542323409176</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -52253,6 +54755,12 @@
       <c r="AN417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO417" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AP417" s="2" t="n">
+        <v>-0.01351351351351353</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -52377,6 +54885,12 @@
       <c r="AN418" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO418" s="1" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="AP418" s="2" t="n">
+        <v>-0.001988071570576506</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -52501,6 +55015,12 @@
       <c r="AN419" s="3" t="n">
         <v>0.008130081300812959</v>
       </c>
+      <c r="AO419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AP419" s="2" t="n">
+        <v>-0.008064516129032209</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -52625,6 +55145,12 @@
       <c r="AN420" s="3" t="n">
         <v>0.0005243838489774301</v>
       </c>
+      <c r="AO420" s="1" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="AP420" s="3" t="n">
+        <v>0.001048218029350062</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -52749,6 +55275,12 @@
       <c r="AN421" s="2" t="n">
         <v>-0.0009290322580645856</v>
       </c>
+      <c r="AO421" s="1" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="AP421" s="3" t="n">
+        <v>0.0009298961615953582</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -52873,6 +55405,12 @@
       <c r="AN422" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO422" s="1" t="n">
+        <v>0.03396</v>
+      </c>
+      <c r="AP422" s="2" t="n">
+        <v>-0.000588581518540498</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -52997,6 +55535,12 @@
       <c r="AN423" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO423" s="1" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="AP423" s="2" t="n">
+        <v>-0.002832861189801584</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -53121,6 +55665,12 @@
       <c r="AN424" s="2" t="n">
         <v>-0.003780718336483942</v>
       </c>
+      <c r="AO424" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="AP424" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -53245,6 +55795,12 @@
       <c r="AN425" s="2" t="n">
         <v>-0.004793863854266543</v>
       </c>
+      <c r="AO425" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="AP425" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -53369,6 +55925,12 @@
       <c r="AN426" s="3" t="n">
         <v>0.0008494973807163994</v>
       </c>
+      <c r="AO426" s="1" t="n">
+        <v>0.007042</v>
+      </c>
+      <c r="AP426" s="2" t="n">
+        <v>-0.003819493563446048</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -53493,6 +56055,12 @@
       <c r="AN427" s="3" t="n">
         <v>0.004320502749410801</v>
       </c>
+      <c r="AO427" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="AP427" s="3" t="n">
+        <v>0.005084082909659822</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -53617,6 +56185,12 @@
       <c r="AN428" s="3" t="n">
         <v>0.001246416552411765</v>
       </c>
+      <c r="AO428" s="1" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="AP428" s="3" t="n">
+        <v>0.0008714054525084105</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -53741,6 +56315,12 @@
       <c r="AN429" s="2" t="n">
         <v>-0.00162866449511394</v>
       </c>
+      <c r="AO429" s="1" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="AP429" s="2" t="n">
+        <v>-0.001631321370310026</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -53865,6 +56445,12 @@
       <c r="AN430" s="2" t="n">
         <v>-0.00105231509320506</v>
       </c>
+      <c r="AO430" s="1" t="n">
+        <v>0.06645</v>
+      </c>
+      <c r="AP430" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -53989,6 +56575,12 @@
       <c r="AN431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO431" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AP431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -54113,6 +56705,12 @@
       <c r="AN432" s="2" t="n">
         <v>-0.003450799958172126</v>
       </c>
+      <c r="AO432" s="1" t="n">
+        <v>0.009514999999999999</v>
+      </c>
+      <c r="AP432" s="2" t="n">
+        <v>-0.001573976915005364</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -54237,6 +56835,12 @@
       <c r="AN433" s="2" t="n">
         <v>-0.002434867299732234</v>
       </c>
+      <c r="AO433" s="1" t="n">
+        <v>0.04089</v>
+      </c>
+      <c r="AP433" s="2" t="n">
+        <v>-0.001952648279228624</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -54361,6 +56965,12 @@
       <c r="AN434" s="3" t="n">
         <v>0.002798507462686453</v>
       </c>
+      <c r="AO434" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AP434" s="2" t="n">
+        <v>-0.006976744186046389</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -54485,6 +57095,12 @@
       <c r="AN435" s="2" t="n">
         <v>-0.001291989664082579</v>
       </c>
+      <c r="AO435" s="1" t="n">
+        <v>0.001544</v>
+      </c>
+      <c r="AP435" s="2" t="n">
+        <v>-0.001293661060802101</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -54609,6 +57225,12 @@
       <c r="AN436" s="2" t="n">
         <v>-0.002917578409919774</v>
       </c>
+      <c r="AO436" s="1" t="n">
+        <v>0.02738</v>
+      </c>
+      <c r="AP436" s="3" t="n">
+        <v>0.001463057790782803</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -54733,6 +57355,12 @@
       <c r="AN437" s="3" t="n">
         <v>0.0002431610942248297</v>
       </c>
+      <c r="AO437" s="1" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="AP437" s="3" t="n">
+        <v>0.004011182691139065</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -54857,6 +57485,12 @@
       <c r="AN438" s="2" t="n">
         <v>-0.002608695652173988</v>
       </c>
+      <c r="AO438" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="AP438" s="2" t="n">
+        <v>-0.001743679163033931</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -54981,6 +57615,12 @@
       <c r="AN439" s="2" t="n">
         <v>-0.0006451612903226529</v>
       </c>
+      <c r="AO439" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP439" s="3" t="n">
+        <v>0.0006455777921240232</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -55105,6 +57745,12 @@
       <c r="AN440" s="2" t="n">
         <v>-0.0005509641873277773</v>
       </c>
+      <c r="AO440" s="1" t="n">
+        <v>0.001814</v>
+      </c>
+      <c r="AP440" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -55229,6 +57875,12 @@
       <c r="AN441" s="3" t="n">
         <v>0.00575027382256303</v>
       </c>
+      <c r="AO441" s="1" t="n">
+        <v>0.03668</v>
+      </c>
+      <c r="AP441" s="2" t="n">
+        <v>-0.001361285053090156</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -55353,6 +58005,12 @@
       <c r="AN442" s="2" t="n">
         <v>-0.002192982456140261</v>
       </c>
+      <c r="AO442" s="1" t="n">
+        <v>0.01821</v>
+      </c>
+      <c r="AP442" s="3" t="n">
+        <v>0.000549450549450527</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -55477,6 +58135,12 @@
       <c r="AN443" s="3" t="n">
         <v>0.001026126766121961</v>
       </c>
+      <c r="AO443" s="1" t="n">
+        <v>0.12663</v>
+      </c>
+      <c r="AP443" s="2" t="n">
+        <v>-0.00149818640592963</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -55601,6 +58265,12 @@
       <c r="AN444" s="2" t="n">
         <v>-0.005349439171699703</v>
       </c>
+      <c r="AO444" s="1" t="n">
+        <v>0.011473</v>
+      </c>
+      <c r="AP444" s="2" t="n">
+        <v>-0.00477099236641217</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -55725,6 +58395,12 @@
       <c r="AN445" s="3" t="n">
         <v>0.000747198007472036</v>
       </c>
+      <c r="AO445" s="1" t="n">
+        <v>0.08029</v>
+      </c>
+      <c r="AP445" s="2" t="n">
+        <v>-0.00087108013937283</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -55849,6 +58525,12 @@
       <c r="AN446" s="2" t="n">
         <v>-0.002337540906965802</v>
       </c>
+      <c r="AO446" s="1" t="n">
+        <v>0.0002134</v>
+      </c>
+      <c r="AP446" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -55973,6 +58655,12 @@
       <c r="AN447" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO447" s="1" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="AP447" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -56097,6 +58785,12 @@
       <c r="AN448" s="3" t="n">
         <v>0.002211944500301608</v>
       </c>
+      <c r="AO448" s="1" t="n">
+        <v>0.09927</v>
+      </c>
+      <c r="AP448" s="2" t="n">
+        <v>-0.004113162118780172</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -56221,6 +58915,12 @@
       <c r="AN449" s="3" t="n">
         <v>0.001193317422434397</v>
       </c>
+      <c r="AO449" s="1" t="n">
+        <v>0.001673</v>
+      </c>
+      <c r="AP449" s="2" t="n">
+        <v>-0.002979737783075097</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -56345,6 +59045,12 @@
       <c r="AN450" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO450" s="1" t="n">
+        <v>0.000207</v>
+      </c>
+      <c r="AP450" s="2" t="n">
+        <v>-0.001447178002894391</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -56469,6 +59175,12 @@
       <c r="AN451" s="3" t="n">
         <v>0.001146788990825732</v>
       </c>
+      <c r="AO451" s="1" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="AP451" s="2" t="n">
+        <v>-0.005727376861397561</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -56593,6 +59305,12 @@
       <c r="AN452" s="2" t="n">
         <v>-0.001486988847583686</v>
       </c>
+      <c r="AO452" s="1" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="AP452" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -56717,6 +59435,12 @@
       <c r="AN453" s="3" t="n">
         <v>0.0005773672055427392</v>
       </c>
+      <c r="AO453" s="1" t="n">
+        <v>0.0001736</v>
+      </c>
+      <c r="AP453" s="3" t="n">
+        <v>0.001731102135025852</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -56841,6 +59565,12 @@
       <c r="AN454" s="3" t="n">
         <v>0.01017468035296229</v>
       </c>
+      <c r="AO454" s="1" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="AP454" s="3" t="n">
+        <v>8.913450396645088e-05</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -56965,6 +59695,12 @@
       <c r="AN455" s="3" t="n">
         <v>0.001603849238171546</v>
       </c>
+      <c r="AO455" s="1" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="AP455" s="2" t="n">
+        <v>-0.0004003202562049199</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -57089,6 +59825,12 @@
       <c r="AN456" s="2" t="n">
         <v>-0.001125281320330123</v>
       </c>
+      <c r="AO456" s="1" t="n">
+        <v>0.015977</v>
+      </c>
+      <c r="AP456" s="2" t="n">
+        <v>-6.258605582660725e-05</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -57213,6 +59955,12 @@
       <c r="AN457" s="3" t="n">
         <v>0.0001498127340822869</v>
       </c>
+      <c r="AO457" s="1" t="n">
+        <v>0.006672</v>
+      </c>
+      <c r="AP457" s="2" t="n">
+        <v>-0.0005991611743558513</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -57337,6 +60085,12 @@
       <c r="AN458" s="2" t="n">
         <v>-0.002902757619738777</v>
       </c>
+      <c r="AO458" s="1" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="AP458" s="3" t="n">
+        <v>0.0004158868787690445</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -57461,6 +60215,12 @@
       <c r="AN459" s="3" t="n">
         <v>0.001736111111111205</v>
       </c>
+      <c r="AO459" s="1" t="n">
+        <v>0.006339</v>
+      </c>
+      <c r="AP459" s="2" t="n">
+        <v>-0.001260438002205797</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -57585,6 +60345,12 @@
       <c r="AN460" s="2" t="n">
         <v>-0.00291757840991985</v>
       </c>
+      <c r="AO460" s="1" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="AP460" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -57709,6 +60475,12 @@
       <c r="AN461" s="2" t="n">
         <v>-0.0004437049362173974</v>
       </c>
+      <c r="AO461" s="1" t="n">
+        <v>0.08984</v>
+      </c>
+      <c r="AP461" s="2" t="n">
+        <v>-0.002996337809344051</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -57833,6 +60605,12 @@
       <c r="AN462" s="2" t="n">
         <v>-0.0004437541601952337</v>
       </c>
+      <c r="AO462" s="1" t="n">
+        <v>0.04501</v>
+      </c>
+      <c r="AP462" s="2" t="n">
+        <v>-0.000887902330743582</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -57957,6 +60735,12 @@
       <c r="AN463" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="AP463" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -58081,6 +60865,12 @@
       <c r="AN464" s="3" t="n">
         <v>0.0007716049382715199</v>
       </c>
+      <c r="AO464" s="1" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="AP464" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -58205,6 +60995,12 @@
       <c r="AN465" s="2" t="n">
         <v>-0.002523431867339504</v>
       </c>
+      <c r="AO465" s="1" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="AP465" s="3" t="n">
+        <v>0.0003614022406938525</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -58329,6 +61125,12 @@
       <c r="AN466" s="2" t="n">
         <v>-0.002117148906139812</v>
       </c>
+      <c r="AO466" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="AP466" s="2" t="n">
+        <v>-0.0007072135785006294</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -58453,6 +61255,12 @@
       <c r="AN467" s="2" t="n">
         <v>-0.001046572475143861</v>
       </c>
+      <c r="AO467" s="1" t="n">
+        <v>0.01906</v>
+      </c>
+      <c r="AP467" s="2" t="n">
+        <v>-0.00157150340492398</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -58577,6 +61385,12 @@
       <c r="AN468" s="2" t="n">
         <v>-0.00297914597815298</v>
       </c>
+      <c r="AO468" s="1" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="AP468" s="2" t="n">
+        <v>-0.00498007968127487</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -58701,6 +61515,12 @@
       <c r="AN469" s="2" t="n">
         <v>-0.002779181404749848</v>
       </c>
+      <c r="AO469" s="1" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="AP469" s="2" t="n">
+        <v>-0.002026855839878447</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -58825,6 +61645,12 @@
       <c r="AN470" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO470" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="AP470" s="2" t="n">
+        <v>-0.002283105022831052</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -58949,6 +61775,12 @@
       <c r="AN471" s="3" t="n">
         <v>0.0006228589224541339</v>
       </c>
+      <c r="AO471" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP471" s="2" t="n">
+        <v>-0.00404606286959225</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -59073,6 +61905,12 @@
       <c r="AN472" s="2" t="n">
         <v>-0.0002383790226460801</v>
       </c>
+      <c r="AO472" s="1" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="AP472" s="2" t="n">
+        <v>-0.001192179303767321</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -59197,6 +62035,12 @@
       <c r="AN473" s="3" t="n">
         <v>0.0008012820512821409</v>
       </c>
+      <c r="AO473" s="1" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="AP473" s="2" t="n">
+        <v>-0.001601281024819857</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -59321,6 +62165,12 @@
       <c r="AN474" s="2" t="n">
         <v>-0.0009373169302869745</v>
       </c>
+      <c r="AO474" s="1" t="n">
+        <v>0.008525</v>
+      </c>
+      <c r="AP474" s="2" t="n">
+        <v>-0.0002345490793948945</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -59445,6 +62295,12 @@
       <c r="AN475" s="3" t="n">
         <v>0.01061007957559689</v>
       </c>
+      <c r="AO475" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AP475" s="3" t="n">
+        <v>0.002147458840372222</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -59569,6 +62425,12 @@
       <c r="AN476" s="2" t="n">
         <v>-0.001780943900267157</v>
       </c>
+      <c r="AO476" s="1" t="n">
+        <v>0.07828</v>
+      </c>
+      <c r="AP476" s="2" t="n">
+        <v>-0.002421307506053214</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -59693,6 +62555,12 @@
       <c r="AN477" s="2" t="n">
         <v>-0.0005865102639295949</v>
       </c>
+      <c r="AO477" s="1" t="n">
+        <v>0.13655</v>
+      </c>
+      <c r="AP477" s="3" t="n">
+        <v>0.001687206572770012</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -59817,6 +62685,12 @@
       <c r="AN478" s="2" t="n">
         <v>-0.003166561114629603</v>
       </c>
+      <c r="AO478" s="1" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="AP478" s="2" t="n">
+        <v>-0.002541296060991002</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -59941,6 +62815,12 @@
       <c r="AN479" s="2" t="n">
         <v>-0.0007525870178740415</v>
       </c>
+      <c r="AO479" s="1" t="n">
+        <v>0.005313</v>
+      </c>
+      <c r="AP479" s="3" t="n">
+        <v>0.0003765769158351093</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -60065,6 +62945,12 @@
       <c r="AN480" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO480" s="1" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AP480" s="2" t="n">
+        <v>-0.0007147962830592494</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -60189,6 +63075,12 @@
       <c r="AN481" s="2" t="n">
         <v>-0.001055687516495074</v>
       </c>
+      <c r="AO481" s="1" t="n">
+        <v>0.07565</v>
+      </c>
+      <c r="AP481" s="2" t="n">
+        <v>-0.0006605019815060551</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -60313,6 +63205,12 @@
       <c r="AN482" s="2" t="n">
         <v>-0.0006715916722632365</v>
       </c>
+      <c r="AO482" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="AP482" s="2" t="n">
+        <v>-0.0006720430107527773</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -60437,6 +63335,12 @@
       <c r="AN483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO483" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AP483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -60561,6 +63465,12 @@
       <c r="AN484" s="3" t="n">
         <v>0.001397949673811686</v>
       </c>
+      <c r="AO484" s="1" t="n">
+        <v>0.02147</v>
+      </c>
+      <c r="AP484" s="2" t="n">
+        <v>-0.0009306654257793944</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -60685,6 +63595,12 @@
       <c r="AN485" s="3" t="n">
         <v>0.002630320420851202</v>
       </c>
+      <c r="AO485" s="1" t="n">
+        <v>0.008347</v>
+      </c>
+      <c r="AP485" s="2" t="n">
+        <v>-0.004650608156451122</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -60809,6 +63725,12 @@
       <c r="AN486" s="3" t="n">
         <v>0.003888441941539221</v>
       </c>
+      <c r="AO486" s="1" t="n">
+        <v>0.007476</v>
+      </c>
+      <c r="AP486" s="2" t="n">
+        <v>-0.001469213303058598</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -60933,6 +63855,12 @@
       <c r="AN487" s="2" t="n">
         <v>-0.001787310098302107</v>
       </c>
+      <c r="AO487" s="1" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="AP487" s="3" t="n">
+        <v>0.00179051029543425</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -61057,6 +63985,12 @@
       <c r="AN488" s="3" t="n">
         <v>0.001077237961865732</v>
       </c>
+      <c r="AO488" s="1" t="n">
+        <v>0.009334</v>
+      </c>
+      <c r="AP488" s="3" t="n">
+        <v>0.004411922952760262</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -61181,6 +64115,12 @@
       <c r="AN489" s="3" t="n">
         <v>0.0007733952049497872</v>
       </c>
+      <c r="AO489" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="AP489" s="3" t="n">
+        <v>0.0005151983513652546</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -61305,6 +64245,12 @@
       <c r="AN490" s="3" t="n">
         <v>0.001218026796589536</v>
       </c>
+      <c r="AO490" s="1" t="n">
+        <v>0.05761</v>
+      </c>
+      <c r="AP490" s="3" t="n">
+        <v>0.001216545012165461</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -61429,6 +64375,12 @@
       <c r="AN491" s="2" t="n">
         <v>-0.00205128205128211</v>
       </c>
+      <c r="AO491" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="AP491" s="2" t="n">
+        <v>-0.002055498458376073</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -61553,6 +64505,12 @@
       <c r="AN492" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO492" s="1" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="AP492" s="3" t="n">
+        <v>0.0007593014426728261</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -61677,6 +64635,12 @@
       <c r="AN493" s="3" t="n">
         <v>0.001713306681895989</v>
       </c>
+      <c r="AO493" s="1" t="n">
+        <v>0.03502</v>
+      </c>
+      <c r="AP493" s="2" t="n">
+        <v>-0.001710376282782142</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -61801,6 +64765,12 @@
       <c r="AN494" s="2" t="n">
         <v>-0.0005927682276229753</v>
       </c>
+      <c r="AO494" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="AP494" s="3" t="n">
+        <v>0.0005931198102016366</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -61925,6 +64895,12 @@
       <c r="AN495" s="2" t="n">
         <v>-0.001916524701873931</v>
       </c>
+      <c r="AO495" s="1" t="n">
+        <v>0.04685</v>
+      </c>
+      <c r="AP495" s="2" t="n">
+        <v>-0.0004267121826327968</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -62049,6 +65025,12 @@
       <c r="AN496" s="3" t="n">
         <v>0.0004155412424682981</v>
       </c>
+      <c r="AO496" s="1" t="n">
+        <v>0.04808</v>
+      </c>
+      <c r="AP496" s="2" t="n">
+        <v>-0.001453790238836981</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -62173,6 +65155,12 @@
       <c r="AN497" s="2" t="n">
         <v>-0.001412144442202958</v>
       </c>
+      <c r="AO497" s="1" t="n">
+        <v>0.04946</v>
+      </c>
+      <c r="AP497" s="2" t="n">
+        <v>-0.0008080808080809153</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -62297,6 +65285,12 @@
       <c r="AN498" s="3" t="n">
         <v>0.003455425017277128</v>
       </c>
+      <c r="AO498" s="1" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="AP498" s="2" t="n">
+        <v>-0.0006887052341597037</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -62421,6 +65415,12 @@
       <c r="AN499" s="2" t="n">
         <v>-0.00147058823529416</v>
       </c>
+      <c r="AO499" s="1" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="AP499" s="3" t="n">
+        <v>0.002209131075110417</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -62545,6 +65545,12 @@
       <c r="AN500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AP500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -62669,6 +65675,12 @@
       <c r="AN501" s="3" t="n">
         <v>0.002257973468811649</v>
       </c>
+      <c r="AO501" s="1" t="n">
+        <v>0.03556</v>
+      </c>
+      <c r="AP501" s="3" t="n">
+        <v>0.001408054069276301</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -62793,6 +65805,12 @@
       <c r="AN502" s="3" t="n">
         <v>0.002195045468799016</v>
       </c>
+      <c r="AO502" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="AP502" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -62917,6 +65935,12 @@
       <c r="AN503" s="2" t="n">
         <v>-0.009897172236503833</v>
       </c>
+      <c r="AO503" s="1" t="n">
+        <v>0.007701</v>
+      </c>
+      <c r="AP503" s="2" t="n">
+        <v>-0.0002596391016486301</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -63041,6 +66065,12 @@
       <c r="AN504" s="2" t="n">
         <v>-0.002317880794702026</v>
       </c>
+      <c r="AO504" s="1" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AP504" s="2" t="n">
+        <v>-0.0009956853634251954</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -63165,6 +66195,12 @@
       <c r="AN505" s="3" t="n">
         <v>0.002296366337971075</v>
       </c>
+      <c r="AO505" s="1" t="n">
+        <v>0.0007417</v>
+      </c>
+      <c r="AP505" s="2" t="n">
+        <v>-0.0004043126684636947</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -63289,6 +66325,12 @@
       <c r="AN506" s="2" t="n">
         <v>-0.0003441156228494304</v>
       </c>
+      <c r="AO506" s="1" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AP506" s="3" t="n">
+        <v>0.001721170395869193</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -63413,6 +66455,12 @@
       <c r="AN507" s="3" t="n">
         <v>0.001407954945441627</v>
       </c>
+      <c r="AO507" s="1" t="n">
+        <v>0.002845</v>
+      </c>
+      <c r="AP507" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -63537,6 +66585,12 @@
       <c r="AN508" s="3" t="n">
         <v>0.0004747586643456599</v>
       </c>
+      <c r="AO508" s="1" t="n">
+        <v>0.06328</v>
+      </c>
+      <c r="AP508" s="3" t="n">
+        <v>0.0009490667510282267</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -63661,6 +66715,12 @@
       <c r="AN509" s="2" t="n">
         <v>-0.01073345259391772</v>
       </c>
+      <c r="AO509" s="1" t="n">
+        <v>2.216</v>
+      </c>
+      <c r="AP509" s="3" t="n">
+        <v>0.001808318264014468</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -63785,6 +66845,12 @@
       <c r="AN510" s="2" t="n">
         <v>-0.0004104528663292673</v>
       </c>
+      <c r="AO510" s="1" t="n">
+        <v>0.0007296</v>
+      </c>
+      <c r="AP510" s="2" t="n">
+        <v>-0.001368738023542327</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -63909,6 +66975,12 @@
       <c r="AN511" s="2" t="n">
         <v>-0.00145613396432476</v>
       </c>
+      <c r="AO511" s="1" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AP511" s="2" t="n">
+        <v>-0.000729128691213919</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -64033,6 +67105,12 @@
       <c r="AN512" s="2" t="n">
         <v>-0.004755996691480566</v>
       </c>
+      <c r="AO512" s="1" t="n">
+        <v>0.0004816</v>
+      </c>
+      <c r="AP512" s="3" t="n">
+        <v>0.0006233118637024877</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -64157,6 +67235,12 @@
       <c r="AN513" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO513" s="1" t="n">
+        <v>0.05492</v>
+      </c>
+      <c r="AP513" s="2" t="n">
+        <v>-0.0001820498816676327</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -64281,6 +67365,12 @@
       <c r="AN514" s="3" t="n">
         <v>0.0003316749585406167</v>
       </c>
+      <c r="AO514" s="1" t="n">
+        <v>0.03012</v>
+      </c>
+      <c r="AP514" s="2" t="n">
+        <v>-0.001326259946949548</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -64405,6 +67495,12 @@
       <c r="AN515" s="2" t="n">
         <v>-0.0008779631255488435</v>
       </c>
+      <c r="AO515" s="1" t="n">
+        <v>0.001137</v>
+      </c>
+      <c r="AP515" s="2" t="n">
+        <v>-0.0008787346221440386</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -64529,6 +67625,12 @@
       <c r="AN516" s="2" t="n">
         <v>-0.002124430955993949</v>
       </c>
+      <c r="AO516" s="1" t="n">
+        <v>0.006579</v>
+      </c>
+      <c r="AP516" s="3" t="n">
+        <v>0.0004562043795619724</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -64653,6 +67755,12 @@
       <c r="AN517" s="3" t="n">
         <v>0.0007528230865747114</v>
       </c>
+      <c r="AO517" s="1" t="n">
+        <v>0.03991</v>
+      </c>
+      <c r="AP517" s="3" t="n">
+        <v>0.0007522567703109891</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -64777,6 +67885,12 @@
       <c r="AN518" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO518" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="AP518" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -64901,6 +68015,12 @@
       <c r="AN519" s="3" t="n">
         <v>0.002306805074971071</v>
       </c>
+      <c r="AO519" s="1" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="AP519" s="2" t="n">
+        <v>-0.001150747986190977</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -65025,6 +68145,12 @@
       <c r="AN520" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO520" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AP520" s="3" t="n">
+        <v>0.0006253908692934131</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -65149,6 +68275,12 @@
       <c r="AN521" s="2" t="n">
         <v>-0.002239641657334929</v>
       </c>
+      <c r="AO521" s="1" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="AP521" s="2" t="n">
+        <v>-0.001122334455667743</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -65273,6 +68405,12 @@
       <c r="AN522" s="2" t="n">
         <v>-0.002440512507626502</v>
       </c>
+      <c r="AO522" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="AP522" s="2" t="n">
+        <v>-0.0006116207951070088</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -65397,6 +68535,12 @@
       <c r="AN523" s="2" t="n">
         <v>-0.0009699321047525857</v>
       </c>
+      <c r="AO523" s="1" t="n">
+        <v>0.00413</v>
+      </c>
+      <c r="AP523" s="3" t="n">
+        <v>0.002427184466019318</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -65521,6 +68665,12 @@
       <c r="AN524" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO524" s="1" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="AP524" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -65645,6 +68795,12 @@
       <c r="AN525" s="2" t="n">
         <v>-0.0008100445524503517</v>
       </c>
+      <c r="AO525" s="1" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="AP525" s="3" t="n">
+        <v>0.001216051884880372</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -65769,6 +68925,12 @@
       <c r="AN526" s="2" t="n">
         <v>-0.003336113427856642</v>
       </c>
+      <c r="AO526" s="1" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="AP526" s="2" t="n">
+        <v>-0.0008368200836819163</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -65893,6 +69055,12 @@
       <c r="AN527" s="2" t="n">
         <v>-0.002518539247236597</v>
       </c>
+      <c r="AO527" s="1" t="n">
+        <v>0.07142</v>
+      </c>
+      <c r="AP527" s="3" t="n">
+        <v>0.001823537663066226</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -66017,6 +69185,12 @@
       <c r="AN528" s="2" t="n">
         <v>-0.0004643603436266354</v>
       </c>
+      <c r="AO528" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AP528" s="2" t="n">
+        <v>-0.001161440185830463</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -66141,6 +69315,12 @@
       <c r="AN529" s="3" t="n">
         <v>0.001749642118657531</v>
       </c>
+      <c r="AO529" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="AP529" s="2" t="n">
+        <v>-0.001270244522070447</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -66265,6 +69445,12 @@
       <c r="AN530" s="2" t="n">
         <v>-0.0001998800719566791</v>
       </c>
+      <c r="AO530" s="1" t="n">
+        <v>0.005022</v>
+      </c>
+      <c r="AP530" s="3" t="n">
+        <v>0.003998400639744113</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -66389,6 +69575,12 @@
       <c r="AN531" s="2" t="n">
         <v>-0.001542020046260645</v>
       </c>
+      <c r="AO531" s="1" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="AP531" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -66513,6 +69705,12 @@
       <c r="AN532" s="3" t="n">
         <v>0.0003746019853905073</v>
       </c>
+      <c r="AO532" s="1" t="n">
+        <v>0.05334</v>
+      </c>
+      <c r="AP532" s="2" t="n">
+        <v>-0.001310615989515084</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -66637,6 +69835,12 @@
       <c r="AN533" s="2" t="n">
         <v>-0.002142474558114559</v>
       </c>
+      <c r="AO533" s="1" t="n">
+        <v>0.003732</v>
+      </c>
+      <c r="AP533" s="3" t="n">
+        <v>0.001610305958132026</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -66761,6 +69965,12 @@
       <c r="AN534" s="2" t="n">
         <v>-0.001754385964912412</v>
       </c>
+      <c r="AO534" s="1" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="AP534" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -66885,6 +70095,12 @@
       <c r="AN535" s="3" t="n">
         <v>0.008928571428571494</v>
       </c>
+      <c r="AO535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AP535" s="2" t="n">
+        <v>-0.00884955752212396</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -67009,6 +70225,12 @@
       <c r="AN536" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO536" s="1" t="n">
+        <v>0.0004395</v>
+      </c>
+      <c r="AP536" s="3" t="n">
+        <v>0.0002275830678197597</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -67133,6 +70355,12 @@
       <c r="AN537" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO537" s="1" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="AP537" s="2" t="n">
+        <v>-0.002085505735140687</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -67257,6 +70485,12 @@
       <c r="AN538" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AO538" s="1" t="n">
+        <v>0.05445</v>
+      </c>
+      <c r="AP538" s="2" t="n">
+        <v>-0.0007340796476417393</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -67381,6 +70615,12 @@
       <c r="AN539" s="2" t="n">
         <v>-0.0005874577764722514</v>
       </c>
+      <c r="AO539" s="1" t="n">
+        <v>0.6816</v>
+      </c>
+      <c r="AP539" s="3" t="n">
+        <v>0.001616458486407039</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -67505,6 +70745,12 @@
       <c r="AN540" s="3" t="n">
         <v>0.0006640106241699135</v>
       </c>
+      <c r="AO540" s="1" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="AP540" s="2" t="n">
+        <v>-0.000663570006635627</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -67629,6 +70875,12 @@
       <c r="AN541" s="3" t="n">
         <v>0.0007710100231302692</v>
       </c>
+      <c r="AO541" s="1" t="n">
+        <v>0.01297</v>
+      </c>
+      <c r="AP541" s="2" t="n">
+        <v>-0.0007704160246532814</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -67753,6 +71005,12 @@
       <c r="AN542" s="3" t="n">
         <v>0.002162941600576696</v>
       </c>
+      <c r="AO542" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="AP542" s="3" t="n">
+        <v>0.002158273381295001</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -67877,6 +71135,12 @@
       <c r="AN543" s="2" t="n">
         <v>-0.001578670408700225</v>
       </c>
+      <c r="AO543" s="1" t="n">
+        <v>0.05688</v>
+      </c>
+      <c r="AP543" s="2" t="n">
+        <v>-0.0007027406886858463</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP543"/>
+  <dimension ref="A1:AR543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -468,6 +468,8 @@
     <col width="18" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="18" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -681,6 +683,16 @@
           <t>change_05:00</t>
         </is>
       </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>price_05:15</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>change_05:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -811,6 +823,12 @@
       <c r="AP2" s="3" t="n">
         <v>0.0003437803571607711</v>
       </c>
+      <c r="AQ2" s="1" t="n">
+        <v>70354.5</v>
+      </c>
+      <c r="AR2" s="3" t="n">
+        <v>0.003244114249860966</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -941,6 +959,12 @@
       <c r="AP3" s="3" t="n">
         <v>0.0005484611539040772</v>
       </c>
+      <c r="AQ3" s="1" t="n">
+        <v>2065.19</v>
+      </c>
+      <c r="AR3" s="3" t="n">
+        <v>0.001819116733933561</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1071,6 +1095,12 @@
       <c r="AP4" s="2" t="n">
         <v>-0.0001157139551030446</v>
       </c>
+      <c r="AQ4" s="1" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>0.001273000810091418</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1201,6 +1231,12 @@
       <c r="AP5" s="2" t="n">
         <v>-0.0003748477181145657</v>
       </c>
+      <c r="AQ5" s="1" t="n">
+        <v>0.010762</v>
+      </c>
+      <c r="AR5" s="3" t="n">
+        <v>0.008905971688384863</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1331,6 +1367,12 @@
       <c r="AP6" s="2" t="n">
         <v>-0.0003645377661125291</v>
       </c>
+      <c r="AQ6" s="1" t="n">
+        <v>1.3738</v>
+      </c>
+      <c r="AR6" s="3" t="n">
+        <v>0.001969221792721118</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1461,6 +1503,12 @@
       <c r="AP7" s="2" t="n">
         <v>-0.001909814323607423</v>
       </c>
+      <c r="AQ7" s="1" t="n">
+        <v>0.09431</v>
+      </c>
+      <c r="AR7" s="3" t="n">
+        <v>0.002551291591368174</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1591,6 +1639,12 @@
       <c r="AP8" s="3" t="n">
         <v>0.002271805273833565</v>
       </c>
+      <c r="AQ8" s="1" t="n">
+        <v>37.277</v>
+      </c>
+      <c r="AR8" s="3" t="n">
+        <v>0.005882511670579442</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1721,6 +1775,12 @@
       <c r="AP9" s="2" t="n">
         <v>-0.01114262560777962</v>
       </c>
+      <c r="AQ9" s="1" t="n">
+        <v>0.04897</v>
+      </c>
+      <c r="AR9" s="3" t="n">
+        <v>0.003278016799836108</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1851,6 +1911,12 @@
       <c r="AP10" s="3" t="n">
         <v>0.005053001592793912</v>
       </c>
+      <c r="AQ10" s="1" t="n">
+        <v>18.417</v>
+      </c>
+      <c r="AR10" s="3" t="n">
+        <v>0.006448439805453965</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1981,6 +2047,12 @@
       <c r="AP11" s="3" t="n">
         <v>0.000754577513590109</v>
       </c>
+      <c r="AQ11" s="1" t="n">
+        <v>651.35</v>
+      </c>
+      <c r="AR11" s="3" t="n">
+        <v>0.002292801526482641</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2111,6 +2183,12 @@
       <c r="AP12" s="3" t="n">
         <v>0.008536307762349135</v>
       </c>
+      <c r="AQ12" s="1" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="AR12" s="2" t="n">
+        <v>-0.02482789752849568</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2241,6 +2319,12 @@
       <c r="AP13" s="2" t="n">
         <v>-0.0008671355621929223</v>
       </c>
+      <c r="AQ13" s="1" t="n">
+        <v>208.24</v>
+      </c>
+      <c r="AR13" s="3" t="n">
+        <v>0.00405014464802316</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2371,6 +2455,12 @@
       <c r="AP14" s="2" t="n">
         <v>-0.003517527508868951</v>
       </c>
+      <c r="AQ14" s="1" t="n">
+        <v>0.0033264</v>
+      </c>
+      <c r="AR14" s="3" t="n">
+        <v>0.003590285110876457</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2501,6 +2591,12 @@
       <c r="AP15" s="2" t="n">
         <v>-0.005820154188378044</v>
       </c>
+      <c r="AQ15" s="1" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="AR15" s="2" t="n">
+        <v>-0.05989088457058788</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2631,6 +2727,12 @@
       <c r="AP16" s="2" t="n">
         <v>-0.001643554185927114</v>
       </c>
+      <c r="AQ16" s="1" t="n">
+        <v>0.9756</v>
+      </c>
+      <c r="AR16" s="3" t="n">
+        <v>0.003806976026340196</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2761,6 +2863,12 @@
       <c r="AP17" s="2" t="n">
         <v>-0.03030303030303025</v>
       </c>
+      <c r="AQ17" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AR17" s="3" t="n">
+        <v>0.0156249999999999</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2891,6 +2999,12 @@
       <c r="AP18" s="2" t="n">
         <v>-0.004223963955507607</v>
       </c>
+      <c r="AQ18" s="1" t="n">
+        <v>212.39</v>
+      </c>
+      <c r="AR18" s="3" t="n">
+        <v>0.00103690436913795</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3021,6 +3135,12 @@
       <c r="AP19" s="2" t="n">
         <v>-0.0007636502481864584</v>
       </c>
+      <c r="AQ19" s="1" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AR19" s="3" t="n">
+        <v>0.002674818494459434</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3151,6 +3271,12 @@
       <c r="AP20" s="2" t="n">
         <v>-0.00272044473357389</v>
       </c>
+      <c r="AQ20" s="1" t="n">
+        <v>0.016872</v>
+      </c>
+      <c r="AR20" s="3" t="n">
+        <v>0.000533712862480108</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3281,6 +3407,12 @@
       <c r="AP21" s="3" t="n">
         <v>0.0003124674513069823</v>
       </c>
+      <c r="AQ21" s="1" t="n">
+        <v>9.645</v>
+      </c>
+      <c r="AR21" s="3" t="n">
+        <v>0.004269054560599789</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3411,6 +3543,12 @@
       <c r="AP22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ22" s="1" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="AR22" s="3" t="n">
+        <v>0.0006049606775558922</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3541,6 +3679,12 @@
       <c r="AP23" s="3" t="n">
         <v>0.004023566604397219</v>
       </c>
+      <c r="AQ23" s="1" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AR23" s="2" t="n">
+        <v>-0.004952053814226447</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3671,6 +3815,12 @@
       <c r="AP24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ24" s="1" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="AR24" s="3" t="n">
+        <v>0.001157407407407408</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3801,6 +3951,12 @@
       <c r="AP25" s="2" t="n">
         <v>-0.0007800312012480135</v>
       </c>
+      <c r="AQ25" s="1" t="n">
+        <v>9.007</v>
+      </c>
+      <c r="AR25" s="3" t="n">
+        <v>0.004460800713728019</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3931,6 +4087,12 @@
       <c r="AP26" s="3" t="n">
         <v>0.003009781790820168</v>
       </c>
+      <c r="AQ26" s="1" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="AR26" s="3" t="n">
+        <v>0.006001500375093779</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4061,6 +4223,12 @@
       <c r="AP27" s="3" t="n">
         <v>0.001223689206549738</v>
       </c>
+      <c r="AQ27" s="1" t="n">
+        <v>5094.35</v>
+      </c>
+      <c r="AR27" s="3" t="n">
+        <v>0.001009979937947211</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4191,6 +4359,12 @@
       <c r="AP28" s="2" t="n">
         <v>-0.001399776035834268</v>
       </c>
+      <c r="AQ28" s="1" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AR28" s="3" t="n">
+        <v>0.001682085786375075</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4321,6 +4495,12 @@
       <c r="AP29" s="2" t="n">
         <v>-0.0007567158531970412</v>
       </c>
+      <c r="AQ29" s="1" t="n">
+        <v>2.642</v>
+      </c>
+      <c r="AR29" s="3" t="n">
+        <v>0.0003786444528587239</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4451,6 +4631,12 @@
       <c r="AP30" s="3" t="n">
         <v>0.009746007817840624</v>
       </c>
+      <c r="AQ30" s="1" t="n">
+        <v>0.58161</v>
+      </c>
+      <c r="AR30" s="3" t="n">
+        <v>0.009651939935769481</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4581,6 +4767,12 @@
       <c r="AP31" s="2" t="n">
         <v>-0.0004814636494943183</v>
       </c>
+      <c r="AQ31" s="1" t="n">
+        <v>0.002076</v>
+      </c>
+      <c r="AR31" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4711,6 +4903,12 @@
       <c r="AP32" s="2" t="n">
         <v>-0.006558135946300402</v>
       </c>
+      <c r="AQ32" s="1" t="n">
+        <v>1.2928</v>
+      </c>
+      <c r="AR32" s="3" t="n">
+        <v>0.00403852127990049</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4841,6 +5039,12 @@
       <c r="AP33" s="2" t="n">
         <v>-0.006268656716418048</v>
       </c>
+      <c r="AQ33" s="1" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AR33" s="3" t="n">
+        <v>0.006308200660859256</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4971,6 +5175,12 @@
       <c r="AP34" s="3" t="n">
         <v>0.001328903654485051</v>
       </c>
+      <c r="AQ34" s="1" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="AR34" s="3" t="n">
+        <v>0.0006635700066357743</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5101,6 +5311,12 @@
       <c r="AP35" s="2" t="n">
         <v>-0.0005065632983878473</v>
       </c>
+      <c r="AQ35" s="1" t="n">
+        <v>454.52</v>
+      </c>
+      <c r="AR35" s="3" t="n">
+        <v>0.001564531411824287</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5231,6 +5447,12 @@
       <c r="AP36" s="2" t="n">
         <v>-0.0006339814032122199</v>
       </c>
+      <c r="AQ36" s="1" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="AR36" s="3" t="n">
+        <v>0.005497991118629801</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5361,6 +5583,12 @@
       <c r="AP37" s="3" t="n">
         <v>0.0008570204256535424</v>
       </c>
+      <c r="AQ37" s="1" t="n">
+        <v>0.7026</v>
+      </c>
+      <c r="AR37" s="3" t="n">
+        <v>0.002711574140145587</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5491,6 +5719,12 @@
       <c r="AP38" s="2" t="n">
         <v>-0.001897533206831042</v>
       </c>
+      <c r="AQ38" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="AR38" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5621,6 +5855,12 @@
       <c r="AP39" s="2" t="n">
         <v>-0.0006329686228411916</v>
       </c>
+      <c r="AQ39" s="1" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="AR39" s="3" t="n">
+        <v>0.0007238508867173208</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5751,6 +5991,12 @@
       <c r="AP40" s="2" t="n">
         <v>-0.01135105204872649</v>
       </c>
+      <c r="AQ40" s="1" t="n">
+        <v>0.03593</v>
+      </c>
+      <c r="AR40" s="3" t="n">
+        <v>0.00616073928871459</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5881,6 +6127,12 @@
       <c r="AP41" s="2" t="n">
         <v>-0.01238164603058995</v>
       </c>
+      <c r="AQ41" s="1" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="AR41" s="3" t="n">
+        <v>0.00110619469026557</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6011,6 +6263,12 @@
       <c r="AP42" s="3" t="n">
         <v>0.0003696174459435063</v>
       </c>
+      <c r="AQ42" s="1" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="AR42" s="3" t="n">
+        <v>0.00351006835396264</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6141,6 +6399,12 @@
       <c r="AP43" s="3" t="n">
         <v>0.002281368821292735</v>
       </c>
+      <c r="AQ43" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="AR43" s="2" t="n">
+        <v>-0.003793626707132021</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6271,6 +6535,12 @@
       <c r="AP44" s="2" t="n">
         <v>-0.001873616079032634</v>
       </c>
+      <c r="AQ44" s="1" t="n">
+        <v>0.005874</v>
+      </c>
+      <c r="AR44" s="3" t="n">
+        <v>0.002389078498293536</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6401,6 +6671,12 @@
       <c r="AP45" s="2" t="n">
         <v>-0.005019576347756254</v>
       </c>
+      <c r="AQ45" s="1" t="n">
+        <v>0.09882000000000001</v>
+      </c>
+      <c r="AR45" s="2" t="n">
+        <v>-0.002926041771768727</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6531,6 +6807,12 @@
       <c r="AP46" s="3" t="n">
         <v>0.006219765031098753</v>
       </c>
+      <c r="AQ46" s="1" t="n">
+        <v>2.933</v>
+      </c>
+      <c r="AR46" s="3" t="n">
+        <v>0.00721153846153843</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6661,6 +6943,12 @@
       <c r="AP47" s="2" t="n">
         <v>-0.0002078066013230509</v>
       </c>
+      <c r="AQ47" s="1" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AR47" s="3" t="n">
+        <v>0.0004503412200783559</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6791,6 +7079,12 @@
       <c r="AP48" s="3" t="n">
         <v>0.003787878787878765</v>
       </c>
+      <c r="AQ48" s="1" t="n">
+        <v>0.1063</v>
+      </c>
+      <c r="AR48" s="3" t="n">
+        <v>0.002830188679245364</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6921,6 +7215,12 @@
       <c r="AP49" s="2" t="n">
         <v>-0.00324742056151595</v>
       </c>
+      <c r="AQ49" s="1" t="n">
+        <v>0.24215</v>
+      </c>
+      <c r="AR49" s="2" t="n">
+        <v>-0.001360936984493554</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7051,6 +7351,12 @@
       <c r="AP50" s="3" t="n">
         <v>0.01577745484741548</v>
       </c>
+      <c r="AQ50" s="1" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="AR50" s="3" t="n">
+        <v>0.006948702227672185</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7181,6 +7487,12 @@
       <c r="AP51" s="2" t="n">
         <v>-0.0002571355104139599</v>
       </c>
+      <c r="AQ51" s="1" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="AR51" s="3" t="n">
+        <v>0.001800411522633775</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7311,6 +7623,12 @@
       <c r="AP52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ52" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="AR52" s="3" t="n">
+        <v>0.03070175438596482</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7441,6 +7759,12 @@
       <c r="AP53" s="2" t="n">
         <v>-0.001189767995240962</v>
       </c>
+      <c r="AQ53" s="1" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="AR53" s="3" t="n">
+        <v>0.001191185229303191</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7571,6 +7895,12 @@
       <c r="AP54" s="2" t="n">
         <v>-0.0004825090470446124</v>
       </c>
+      <c r="AQ54" s="1" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="AR54" s="2" t="n">
+        <v>-0.006517016654598103</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7701,6 +8031,12 @@
       <c r="AP55" s="3" t="n">
         <v>0.01245522631064791</v>
       </c>
+      <c r="AQ55" s="1" t="n">
+        <v>0.12385</v>
+      </c>
+      <c r="AR55" s="2" t="n">
+        <v>-0.004181072605933848</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7831,6 +8167,12 @@
       <c r="AP56" s="3" t="n">
         <v>0.002237851662404023</v>
       </c>
+      <c r="AQ56" s="1" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AR56" s="3" t="n">
+        <v>0.003827751196172181</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7961,6 +8303,12 @@
       <c r="AP57" s="2" t="n">
         <v>-0.003487358326068013</v>
       </c>
+      <c r="AQ57" s="1" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="AR57" s="3" t="n">
+        <v>0.008748906386701762</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8091,6 +8439,12 @@
       <c r="AP58" s="2" t="n">
         <v>-0.002008032128513975</v>
       </c>
+      <c r="AQ58" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="AR58" s="3" t="n">
+        <v>0.004024144869215267</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8221,6 +8575,12 @@
       <c r="AP59" s="2" t="n">
         <v>-0.003003003003003011</v>
       </c>
+      <c r="AQ59" s="1" t="n">
+        <v>0.00332</v>
+      </c>
+      <c r="AR59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8351,6 +8711,12 @@
       <c r="AP60" s="2" t="n">
         <v>-0.0006468305304009637</v>
       </c>
+      <c r="AQ60" s="1" t="n">
+        <v>0.1552</v>
+      </c>
+      <c r="AR60" s="3" t="n">
+        <v>0.004530744336569619</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8481,6 +8847,12 @@
       <c r="AP61" s="2" t="n">
         <v>-0.0008791208791208868</v>
       </c>
+      <c r="AQ61" s="1" t="n">
+        <v>0.15979</v>
+      </c>
+      <c r="AR61" s="3" t="n">
+        <v>0.004273772861542242</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8611,6 +8983,12 @@
       <c r="AP62" s="2" t="n">
         <v>-0.0007073136228602984</v>
       </c>
+      <c r="AQ62" s="1" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="AR62" s="3" t="n">
+        <v>0.004813137032842523</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8741,6 +9119,12 @@
       <c r="AP63" s="3" t="n">
         <v>0.001160477453580848</v>
       </c>
+      <c r="AQ63" s="1" t="n">
+        <v>6.022</v>
+      </c>
+      <c r="AR63" s="2" t="n">
+        <v>-0.002815035601920758</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8871,6 +9255,12 @@
       <c r="AP64" s="2" t="n">
         <v>-0.002655485674353588</v>
       </c>
+      <c r="AQ64" s="1" t="n">
+        <v>0.007151</v>
+      </c>
+      <c r="AR64" s="3" t="n">
+        <v>0.002102017937219767</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9001,6 +9391,12 @@
       <c r="AP65" s="3" t="n">
         <v>0.0133168163518117</v>
       </c>
+      <c r="AQ65" s="1" t="n">
+        <v>0.03274</v>
+      </c>
+      <c r="AR65" s="3" t="n">
+        <v>0.0006112469437652562</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9131,6 +9527,12 @@
       <c r="AP66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ66" s="1" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="AR66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9261,6 +9663,12 @@
       <c r="AP67" s="2" t="n">
         <v>-0.001845018450184435</v>
       </c>
+      <c r="AQ67" s="1" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="AR67" s="3" t="n">
+        <v>0.003080714725816324</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9391,6 +9799,12 @@
       <c r="AP68" s="2" t="n">
         <v>-0.0001966665027778927</v>
       </c>
+      <c r="AQ68" s="1" t="n">
+        <v>2.0495</v>
+      </c>
+      <c r="AR68" s="3" t="n">
+        <v>0.007868207523973452</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9521,6 +9935,12 @@
       <c r="AP69" s="3" t="n">
         <v>0.003563549974546055</v>
       </c>
+      <c r="AQ69" s="1" t="n">
+        <v>0.5918</v>
+      </c>
+      <c r="AR69" s="3" t="n">
+        <v>0.0006763611768683732</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9651,6 +10071,12 @@
       <c r="AP70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AR70" s="3" t="n">
+        <v>0.009708737864077679</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9781,6 +10207,12 @@
       <c r="AP71" s="2" t="n">
         <v>-0.00121493262646343</v>
       </c>
+      <c r="AQ71" s="1" t="n">
+        <v>0.9072</v>
+      </c>
+      <c r="AR71" s="3" t="n">
+        <v>0.00320690036492316</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9911,6 +10343,12 @@
       <c r="AP72" s="3" t="n">
         <v>0.006046511627906957</v>
       </c>
+      <c r="AQ72" s="1" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="AR72" s="3" t="n">
+        <v>0.01086453999075367</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10041,6 +10479,12 @@
       <c r="AP73" s="2" t="n">
         <v>-0.0008512449457331</v>
       </c>
+      <c r="AQ73" s="1" t="n">
+        <v>0.09404999999999999</v>
+      </c>
+      <c r="AR73" s="3" t="n">
+        <v>0.001597444089456841</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10171,6 +10615,12 @@
       <c r="AP74" s="3" t="n">
         <v>0.0002602811035918505</v>
       </c>
+      <c r="AQ74" s="1" t="n">
+        <v>1.1552</v>
+      </c>
+      <c r="AR74" s="3" t="n">
+        <v>0.001994969208083935</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10301,6 +10751,12 @@
       <c r="AP75" s="2" t="n">
         <v>-0.001870324189526108</v>
       </c>
+      <c r="AQ75" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="AR75" s="3" t="n">
+        <v>0.001873828856964321</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10431,6 +10887,12 @@
       <c r="AP76" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ76" s="1" t="n">
+        <v>0.12188</v>
+      </c>
+      <c r="AR76" s="3" t="n">
+        <v>0.002714932126696807</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10561,6 +11023,12 @@
       <c r="AP77" s="2" t="n">
         <v>-0.001696352841391058</v>
       </c>
+      <c r="AQ77" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="AR77" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10691,6 +11159,12 @@
       <c r="AP78" s="2" t="n">
         <v>-0.0009900990099010183</v>
       </c>
+      <c r="AQ78" s="1" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="AR78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10821,6 +11295,12 @@
       <c r="AP79" s="2" t="n">
         <v>-0.0031545741324921</v>
       </c>
+      <c r="AQ79" s="1" t="n">
+        <v>0.006015</v>
+      </c>
+      <c r="AR79" s="3" t="n">
+        <v>0.001832111925383177</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10951,6 +11431,12 @@
       <c r="AP80" s="3" t="n">
         <v>0.01259316371112824</v>
       </c>
+      <c r="AQ80" s="1" t="n">
+        <v>0.007893000000000001</v>
+      </c>
+      <c r="AR80" s="3" t="n">
+        <v>0.00164974619289351</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -11081,6 +11567,12 @@
       <c r="AP81" s="2" t="n">
         <v>-0.002804262478967872</v>
       </c>
+      <c r="AQ81" s="1" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="AR81" s="3" t="n">
+        <v>0.00281214848143966</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -11211,6 +11703,12 @@
       <c r="AP82" s="2" t="n">
         <v>-0.0005977286312015346</v>
       </c>
+      <c r="AQ82" s="1" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="AR82" s="2" t="n">
+        <v>-0.004186602870813268</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11341,6 +11839,12 @@
       <c r="AP83" s="2" t="n">
         <v>-0.001701300279499252</v>
       </c>
+      <c r="AQ83" s="1" t="n">
+        <v>8.212</v>
+      </c>
+      <c r="AR83" s="2" t="n">
+        <v>-0.0003651856360316633</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11471,6 +11975,12 @@
       <c r="AP84" s="3" t="n">
         <v>0.003388575659206099</v>
       </c>
+      <c r="AQ84" s="1" t="n">
+        <v>353.25</v>
+      </c>
+      <c r="AR84" s="3" t="n">
+        <v>0.002497374918409613</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11601,6 +12111,12 @@
       <c r="AP85" s="2" t="n">
         <v>-0.00815822002472189</v>
       </c>
+      <c r="AQ85" s="1" t="n">
+        <v>0.003995</v>
+      </c>
+      <c r="AR85" s="2" t="n">
+        <v>-0.004237288135593134</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11731,6 +12247,12 @@
       <c r="AP86" s="3" t="n">
         <v>0.0009159606136936799</v>
       </c>
+      <c r="AQ86" s="1" t="n">
+        <v>0.13098</v>
+      </c>
+      <c r="AR86" s="2" t="n">
+        <v>-0.001143902997025726</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11861,6 +12383,12 @@
       <c r="AP87" s="2" t="n">
         <v>-0.002741228070175327</v>
       </c>
+      <c r="AQ87" s="1" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="AR87" s="3" t="n">
+        <v>0.01044529961517313</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11991,6 +12519,12 @@
       <c r="AP88" s="2" t="n">
         <v>-0.001771479185119576</v>
       </c>
+      <c r="AQ88" s="1" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="AR88" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -12121,6 +12655,12 @@
       <c r="AP89" s="2" t="n">
         <v>-0.0003435245620063363</v>
       </c>
+      <c r="AQ89" s="1" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AR89" s="3" t="n">
+        <v>0.001718213058419246</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12251,6 +12791,12 @@
       <c r="AP90" s="2" t="n">
         <v>-0.002718446601941879</v>
       </c>
+      <c r="AQ90" s="1" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="AR90" s="3" t="n">
+        <v>0.003504672897196308</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12381,6 +12927,12 @@
       <c r="AP91" s="2" t="n">
         <v>-0.005322924059616779</v>
       </c>
+      <c r="AQ91" s="1" t="n">
+        <v>0.05745</v>
+      </c>
+      <c r="AR91" s="3" t="n">
+        <v>0.0247948626471638</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -12511,6 +13063,12 @@
       <c r="AP92" s="3" t="n">
         <v>0.002999077207013238</v>
       </c>
+      <c r="AQ92" s="1" t="n">
+        <v>1.3045</v>
+      </c>
+      <c r="AR92" s="3" t="n">
+        <v>0.0001533389557616944</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12641,6 +13199,12 @@
       <c r="AP93" s="2" t="n">
         <v>-0.001096663011123306</v>
       </c>
+      <c r="AQ93" s="1" t="n">
+        <v>0.06405</v>
+      </c>
+      <c r="AR93" s="3" t="n">
+        <v>0.004548306148055186</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12771,6 +13335,12 @@
       <c r="AP94" s="3" t="n">
         <v>0.001150747986190977</v>
       </c>
+      <c r="AQ94" s="1" t="n">
+        <v>0.00856</v>
+      </c>
+      <c r="AR94" s="2" t="n">
+        <v>-0.01609195402298845</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12901,6 +13471,12 @@
       <c r="AP95" s="2" t="n">
         <v>-0.002080237741456267</v>
       </c>
+      <c r="AQ95" s="1" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AR95" s="3" t="n">
+        <v>0.002680166765932138</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13031,6 +13607,12 @@
       <c r="AP96" s="2" t="n">
         <v>-0.003541389995573272</v>
       </c>
+      <c r="AQ96" s="1" t="n">
+        <v>0.02258</v>
+      </c>
+      <c r="AR96" s="3" t="n">
+        <v>0.003109729009329215</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13161,6 +13743,12 @@
       <c r="AP97" s="3" t="n">
         <v>0.0006161429451631553</v>
       </c>
+      <c r="AQ97" s="1" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="AR97" s="3" t="n">
+        <v>0.002770935960591238</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13291,6 +13879,12 @@
       <c r="AP98" s="3" t="n">
         <v>0.0008849557522124885</v>
       </c>
+      <c r="AQ98" s="1" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="AR98" s="3" t="n">
+        <v>0.005305039787798413</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -13421,6 +14015,12 @@
       <c r="AP99" s="2" t="n">
         <v>-0.001981505944517908</v>
       </c>
+      <c r="AQ99" s="1" t="n">
+        <v>3.032</v>
+      </c>
+      <c r="AR99" s="3" t="n">
+        <v>0.003309066843150308</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -13551,6 +14151,12 @@
       <c r="AP100" s="2" t="n">
         <v>-0.001763668430335229</v>
       </c>
+      <c r="AQ100" s="1" t="n">
+        <v>0.03425</v>
+      </c>
+      <c r="AR100" s="3" t="n">
+        <v>0.008539458186101459</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13681,6 +14287,12 @@
       <c r="AP101" s="2" t="n">
         <v>-0.0005476451259584402</v>
       </c>
+      <c r="AQ101" s="1" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="AR101" s="2" t="n">
+        <v>-0.001643835616438297</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13811,6 +14423,12 @@
       <c r="AP102" s="2" t="n">
         <v>-0.001129305477131592</v>
       </c>
+      <c r="AQ102" s="1" t="n">
+        <v>0.007111</v>
+      </c>
+      <c r="AR102" s="3" t="n">
+        <v>0.004946297343131756</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13941,6 +14559,12 @@
       <c r="AP103" s="2" t="n">
         <v>-0.000461609478381324</v>
       </c>
+      <c r="AQ103" s="1" t="n">
+        <v>0.06489</v>
+      </c>
+      <c r="AR103" s="2" t="n">
+        <v>-0.001077586206896561</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -14071,6 +14695,12 @@
       <c r="AP104" s="2" t="n">
         <v>-0.001210067763794774</v>
       </c>
+      <c r="AQ104" s="1" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="AR104" s="2" t="n">
+        <v>-0.004846135207172284</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14201,6 +14831,12 @@
       <c r="AP105" s="2" t="n">
         <v>-0.002738225629791958</v>
       </c>
+      <c r="AQ105" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="AR105" s="3" t="n">
+        <v>0.002745744096650256</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14331,6 +14967,12 @@
       <c r="AP106" s="2" t="n">
         <v>-0.00874276566925254</v>
       </c>
+      <c r="AQ106" s="1" t="n">
+        <v>0.008083</v>
+      </c>
+      <c r="AR106" s="3" t="n">
+        <v>0.004099378881987583</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -14461,6 +15103,12 @@
       <c r="AP107" s="2" t="n">
         <v>-0.002751788662630598</v>
       </c>
+      <c r="AQ107" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="AR107" s="3" t="n">
+        <v>0.001103752759381853</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -14591,6 +15239,12 @@
       <c r="AP108" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ108" s="1" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="AR108" s="2" t="n">
+        <v>-0.0004627487274409807</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14721,6 +15375,12 @@
       <c r="AP109" s="3" t="n">
         <v>0.001974865350089749</v>
       </c>
+      <c r="AQ109" s="1" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="AR109" s="2" t="n">
+        <v>-0.001970972943916843</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14851,6 +15511,12 @@
       <c r="AP110" s="3" t="n">
         <v>0.00347795843839664</v>
       </c>
+      <c r="AQ110" s="1" t="n">
+        <v>0.11492</v>
+      </c>
+      <c r="AR110" s="2" t="n">
+        <v>-0.004245732605493496</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14981,6 +15647,12 @@
       <c r="AP111" s="2" t="n">
         <v>-0.0007286353700426836</v>
       </c>
+      <c r="AQ111" s="1" t="n">
+        <v>0.09603</v>
+      </c>
+      <c r="AR111" s="3" t="n">
+        <v>0.0003125000000000234</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -15111,6 +15783,12 @@
       <c r="AP112" s="2" t="n">
         <v>-0.002688172043010643</v>
       </c>
+      <c r="AQ112" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="AR112" s="3" t="n">
+        <v>0.002695417789757302</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -15241,6 +15919,12 @@
       <c r="AP113" s="2" t="n">
         <v>-0.000814829904257453</v>
       </c>
+      <c r="AQ113" s="1" t="n">
+        <v>0.09837</v>
+      </c>
+      <c r="AR113" s="3" t="n">
+        <v>0.002752293577981574</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -15371,6 +16055,12 @@
       <c r="AP114" s="3" t="n">
         <v>0.001129305477131592</v>
       </c>
+      <c r="AQ114" s="1" t="n">
+        <v>0.001788</v>
+      </c>
+      <c r="AR114" s="3" t="n">
+        <v>0.008460236886632848</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -15501,6 +16191,12 @@
       <c r="AP115" s="2" t="n">
         <v>-0.0001591089896578982</v>
       </c>
+      <c r="AQ115" s="1" t="n">
+        <v>1.2638</v>
+      </c>
+      <c r="AR115" s="3" t="n">
+        <v>0.005569700827498502</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -15631,6 +16327,12 @@
       <c r="AP116" s="2" t="n">
         <v>-0.001697792869269998</v>
       </c>
+      <c r="AQ116" s="1" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="AR116" s="2" t="n">
+        <v>-0.0004251700680271641</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -15761,6 +16463,12 @@
       <c r="AP117" s="2" t="n">
         <v>-0.0004960317460317832</v>
       </c>
+      <c r="AQ117" s="1" t="n">
+        <v>0.06052</v>
+      </c>
+      <c r="AR117" s="3" t="n">
+        <v>0.001157981803143104</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -15891,6 +16599,12 @@
       <c r="AP118" s="3" t="n">
         <v>0.01127649977447001</v>
       </c>
+      <c r="AQ118" s="1" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="AR118" s="2" t="n">
+        <v>-0.01204281891168597</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -16021,6 +16735,12 @@
       <c r="AP119" s="2" t="n">
         <v>-0.004633415099482172</v>
       </c>
+      <c r="AQ119" s="1" t="n">
+        <v>0.003637</v>
+      </c>
+      <c r="AR119" s="2" t="n">
+        <v>-0.004107338444687794</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -16151,6 +16871,12 @@
       <c r="AP120" s="2" t="n">
         <v>-0.001269035532994925</v>
       </c>
+      <c r="AQ120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AR120" s="3" t="n">
+        <v>0.001270648030495554</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -16281,6 +17007,12 @@
       <c r="AP121" s="2" t="n">
         <v>-0.002356109054190436</v>
       </c>
+      <c r="AQ121" s="1" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AR121" s="3" t="n">
+        <v>0.005398110661268524</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -16411,6 +17143,12 @@
       <c r="AP122" s="2" t="n">
         <v>-0.001059322033898384</v>
       </c>
+      <c r="AQ122" s="1" t="n">
+        <v>0.5684</v>
+      </c>
+      <c r="AR122" s="3" t="n">
+        <v>0.00459526334393787</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -16541,6 +17279,12 @@
       <c r="AP123" s="3" t="n">
         <v>0.000736583654857951</v>
       </c>
+      <c r="AQ123" s="1" t="n">
+        <v>0.028576</v>
+      </c>
+      <c r="AR123" s="3" t="n">
+        <v>0.001577231782972903</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -16671,6 +17415,12 @@
       <c r="AP124" s="2" t="n">
         <v>-0.004838915064306702</v>
       </c>
+      <c r="AQ124" s="1" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="AR124" s="3" t="n">
+        <v>0.002687140115163172</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -16801,6 +17551,12 @@
       <c r="AP125" s="3" t="n">
         <v>0.002848461830611551</v>
       </c>
+      <c r="AQ125" s="1" t="n">
+        <v>0.10555</v>
+      </c>
+      <c r="AR125" s="2" t="n">
+        <v>-0.0006627532664268189</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -16931,6 +17687,12 @@
       <c r="AP126" s="2" t="n">
         <v>-0.004543733434305134</v>
       </c>
+      <c r="AQ126" s="1" t="n">
+        <v>0.02625</v>
+      </c>
+      <c r="AR126" s="2" t="n">
+        <v>-0.001521491061240085</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -17061,6 +17823,12 @@
       <c r="AP127" s="2" t="n">
         <v>-0.0009182736455463354</v>
       </c>
+      <c r="AQ127" s="1" t="n">
+        <v>0.02174</v>
+      </c>
+      <c r="AR127" s="2" t="n">
+        <v>-0.0009191176470589455</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -17191,6 +17959,12 @@
       <c r="AP128" s="2" t="n">
         <v>-0.001861042183622968</v>
       </c>
+      <c r="AQ128" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="AR128" s="3" t="n">
+        <v>0.004972032318210211</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -17321,6 +18095,12 @@
       <c r="AP129" s="2" t="n">
         <v>-0.008623687321788658</v>
       </c>
+      <c r="AQ129" s="1" t="n">
+        <v>0.14278</v>
+      </c>
+      <c r="AR129" s="3" t="n">
+        <v>0.001613468958260121</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -17451,6 +18231,12 @@
       <c r="AP130" s="3" t="n">
         <v>0.001047181336901478</v>
       </c>
+      <c r="AQ130" s="1" t="n">
+        <v>0.052029</v>
+      </c>
+      <c r="AR130" s="3" t="n">
+        <v>0.007903760097634657</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -17581,6 +18367,12 @@
       <c r="AP131" s="2" t="n">
         <v>-0.0009760858955589387</v>
       </c>
+      <c r="AQ131" s="1" t="n">
+        <v>0.08211</v>
+      </c>
+      <c r="AR131" s="3" t="n">
+        <v>0.002808988764045041</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -17711,6 +18503,12 @@
       <c r="AP132" s="2" t="n">
         <v>-0.003409090909090849</v>
       </c>
+      <c r="AQ132" s="1" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="AR132" s="3" t="n">
+        <v>0.002280501710376348</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -17841,6 +18639,12 @@
       <c r="AP133" s="3" t="n">
         <v>0.0005177770107006679</v>
       </c>
+      <c r="AQ133" s="1" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="AR133" s="3" t="n">
+        <v>0.003967569432465014</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -17971,6 +18775,12 @@
       <c r="AP134" s="2" t="n">
         <v>-0.001691474966170432</v>
       </c>
+      <c r="AQ134" s="1" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="AR134" s="3" t="n">
+        <v>0.00304981362250084</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -18101,6 +18911,12 @@
       <c r="AP135" s="3" t="n">
         <v>0.002873563218390887</v>
       </c>
+      <c r="AQ135" s="1" t="n">
+        <v>0.01747</v>
+      </c>
+      <c r="AR135" s="3" t="n">
+        <v>0.001146131805157546</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -18231,6 +19047,12 @@
       <c r="AP136" s="2" t="n">
         <v>-0.002960172228202341</v>
       </c>
+      <c r="AQ136" s="1" t="n">
+        <v>0.03725</v>
+      </c>
+      <c r="AR136" s="3" t="n">
+        <v>0.005398110661268524</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -18361,6 +19183,12 @@
       <c r="AP137" s="2" t="n">
         <v>-0.003332099222510174</v>
       </c>
+      <c r="AQ137" s="1" t="n">
+        <v>0.02694</v>
+      </c>
+      <c r="AR137" s="3" t="n">
+        <v>0.0007429420505200291</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -18491,6 +19319,12 @@
       <c r="AP138" s="3" t="n">
         <v>0.005868544600939015</v>
       </c>
+      <c r="AQ138" s="1" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="AR138" s="2" t="n">
+        <v>-0.0116686114352393</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -18621,6 +19455,12 @@
       <c r="AP139" s="2" t="n">
         <v>-0.0008481764206954701</v>
       </c>
+      <c r="AQ139" s="1" t="n">
+        <v>0.01177</v>
+      </c>
+      <c r="AR139" s="2" t="n">
+        <v>-0.0008488964346350872</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -18751,6 +19591,12 @@
       <c r="AP140" s="2" t="n">
         <v>-0.001359619306594216</v>
       </c>
+      <c r="AQ140" s="1" t="n">
+        <v>0.01462</v>
+      </c>
+      <c r="AR140" s="2" t="n">
+        <v>-0.004765146358066754</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -18881,6 +19727,12 @@
       <c r="AP141" s="2" t="n">
         <v>-0.000556689552792747</v>
       </c>
+      <c r="AQ141" s="1" t="n">
+        <v>16.149</v>
+      </c>
+      <c r="AR141" s="2" t="n">
+        <v>-0.0005569996286669353</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -19011,6 +19863,12 @@
       <c r="AP142" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ142" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="AR142" s="3" t="n">
+        <v>0.002411575562701006</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -19141,6 +19999,12 @@
       <c r="AP143" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ143" s="1" t="n">
+        <v>0.02842</v>
+      </c>
+      <c r="AR143" s="3" t="n">
+        <v>0.01030927835051554</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -19271,6 +20135,12 @@
       <c r="AP144" s="2" t="n">
         <v>-0.005893496106082982</v>
       </c>
+      <c r="AQ144" s="1" t="n">
+        <v>0.004747</v>
+      </c>
+      <c r="AR144" s="3" t="n">
+        <v>0.005081515985602495</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -19401,6 +20271,12 @@
       <c r="AP145" s="3" t="n">
         <v>0.002128630074502043</v>
       </c>
+      <c r="AQ145" s="1" t="n">
+        <v>1.9813</v>
+      </c>
+      <c r="AR145" s="3" t="n">
+        <v>0.002022960602842261</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -19531,6 +20407,12 @@
       <c r="AP146" s="3" t="n">
         <v>0.001280956447480733</v>
       </c>
+      <c r="AQ146" s="1" t="n">
+        <v>0.02339</v>
+      </c>
+      <c r="AR146" s="2" t="n">
+        <v>-0.002558635394456186</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -19661,6 +20543,12 @@
       <c r="AP147" s="2" t="n">
         <v>-0.004547975596228438</v>
       </c>
+      <c r="AQ147" s="1" t="n">
+        <v>0.08987000000000001</v>
+      </c>
+      <c r="AR147" s="3" t="n">
+        <v>0.001448629373746435</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -19791,6 +20679,12 @@
       <c r="AP148" s="3" t="n">
         <v>0.006478116606099029</v>
       </c>
+      <c r="AQ148" s="1" t="n">
+        <v>0.06444999999999999</v>
+      </c>
+      <c r="AR148" s="3" t="n">
+        <v>0.01177394034536871</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -19921,6 +20815,12 @@
       <c r="AP149" s="3" t="n">
         <v>0.0008481764206954112</v>
       </c>
+      <c r="AQ149" s="1" t="n">
+        <v>0.05899</v>
+      </c>
+      <c r="AR149" s="2" t="n">
+        <v>-0.0001694915254236631</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -20051,6 +20951,12 @@
       <c r="AP150" s="3" t="n">
         <v>0.0006588700378850004</v>
       </c>
+      <c r="AQ150" s="1" t="n">
+        <v>0.24468</v>
+      </c>
+      <c r="AR150" s="3" t="n">
+        <v>0.006913580246913641</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -20181,6 +21087,12 @@
       <c r="AP151" s="2" t="n">
         <v>-0.004272895598917444</v>
       </c>
+      <c r="AQ151" s="1" t="n">
+        <v>7.022e-05</v>
+      </c>
+      <c r="AR151" s="3" t="n">
+        <v>0.004434272636246633</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -20311,6 +21223,12 @@
       <c r="AP152" s="3" t="n">
         <v>0.002031602708803639</v>
       </c>
+      <c r="AQ152" s="1" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="AR152" s="2" t="n">
+        <v>-0.002252759630547422</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -20441,6 +21359,12 @@
       <c r="AP153" s="2" t="n">
         <v>-0.0006428801028607457</v>
       </c>
+      <c r="AQ153" s="1" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AR153" s="3" t="n">
+        <v>0.003216468317787072</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -20571,6 +21495,12 @@
       <c r="AP154" s="3" t="n">
         <v>0.001105277701022414</v>
       </c>
+      <c r="AQ154" s="1" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AR154" s="3" t="n">
+        <v>0.01242064587358544</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -20701,6 +21631,12 @@
       <c r="AP155" s="3" t="n">
         <v>0.0008695652173912085</v>
       </c>
+      <c r="AQ155" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AR155" s="2" t="n">
+        <v>-0.0008688097306688878</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -20831,6 +21767,12 @@
       <c r="AP156" s="2" t="n">
         <v>-0.0009847365829641877</v>
       </c>
+      <c r="AQ156" s="1" t="n">
+        <v>0.08094999999999999</v>
+      </c>
+      <c r="AR156" s="2" t="n">
+        <v>-0.00258748151798918</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -20961,6 +21903,12 @@
       <c r="AP157" s="3" t="n">
         <v>0.005876506935142376</v>
       </c>
+      <c r="AQ157" s="1" t="n">
+        <v>0.23493</v>
+      </c>
+      <c r="AR157" s="3" t="n">
+        <v>0.009192834743760484</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -21091,6 +22039,12 @@
       <c r="AP158" s="3" t="n">
         <v>0.0007846214201646841</v>
       </c>
+      <c r="AQ158" s="1" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AR158" s="3" t="n">
+        <v>0.001568012544100398</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -21221,6 +22175,12 @@
       <c r="AP159" s="3" t="n">
         <v>0.001028453890983927</v>
       </c>
+      <c r="AQ159" s="1" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="AR159" s="3" t="n">
+        <v>0.0006849315068493917</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -21351,6 +22311,12 @@
       <c r="AP160" s="2" t="n">
         <v>-0.001011122345803871</v>
       </c>
+      <c r="AQ160" s="1" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="AR160" s="3" t="n">
+        <v>0.005060728744939276</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -21481,6 +22447,12 @@
       <c r="AP161" s="3" t="n">
         <v>0.005115961800818558</v>
       </c>
+      <c r="AQ161" s="1" t="n">
+        <v>0.14714</v>
+      </c>
+      <c r="AR161" s="2" t="n">
+        <v>-0.001425178147268515</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -21611,6 +22583,12 @@
       <c r="AP162" s="2" t="n">
         <v>-0.005754088431253762</v>
       </c>
+      <c r="AQ162" s="1" t="n">
+        <v>0.003285</v>
+      </c>
+      <c r="AR162" s="3" t="n">
+        <v>0.0006091989034420547</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -21741,6 +22719,12 @@
       <c r="AP163" s="2" t="n">
         <v>-0.00239473159050087</v>
       </c>
+      <c r="AQ163" s="1" t="n">
+        <v>0.005007</v>
+      </c>
+      <c r="AR163" s="3" t="n">
+        <v>0.001600320064012841</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -21871,6 +22855,12 @@
       <c r="AP164" s="2" t="n">
         <v>-0.001037344398340279</v>
       </c>
+      <c r="AQ164" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="AR164" s="2" t="n">
+        <v>-0.001038421599169292</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -22001,6 +22991,12 @@
       <c r="AP165" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ165" s="1" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AR165" s="3" t="n">
+        <v>0.005891980360065545</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -22131,6 +23127,12 @@
       <c r="AP166" s="2" t="n">
         <v>-0.0008621309002082534</v>
       </c>
+      <c r="AQ166" s="1" t="n">
+        <v>1.3935</v>
+      </c>
+      <c r="AR166" s="3" t="n">
+        <v>0.002013374559574253</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -22261,6 +23263,12 @@
       <c r="AP167" s="3" t="n">
         <v>0.000719683339330815</v>
       </c>
+      <c r="AQ167" s="1" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="AR167" s="2" t="n">
+        <v>-0.0007191657677095774</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -22391,6 +23399,12 @@
       <c r="AP168" s="2" t="n">
         <v>-0.003215434083601289</v>
       </c>
+      <c r="AQ168" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AR168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -22521,6 +23535,12 @@
       <c r="AP169" s="2" t="n">
         <v>-0.004012036108324927</v>
       </c>
+      <c r="AQ169" s="1" t="n">
+        <v>0.02984</v>
+      </c>
+      <c r="AR169" s="3" t="n">
+        <v>0.001678415575696474</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -22651,6 +23671,12 @@
       <c r="AP170" s="2" t="n">
         <v>-0.0002308935580698005</v>
       </c>
+      <c r="AQ170" s="1" t="n">
+        <v>0.04329</v>
+      </c>
+      <c r="AR170" s="2" t="n">
+        <v>-0.0002309468822170005</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -22781,6 +23807,12 @@
       <c r="AP171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ171" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="AR171" s="2" t="n">
+        <v>-0.006060606060606023</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -22911,6 +23943,12 @@
       <c r="AP172" s="2" t="n">
         <v>-0.007751937984496181</v>
       </c>
+      <c r="AQ172" s="1" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="AR172" s="3" t="n">
+        <v>0.01562499999999998</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -23041,6 +24079,12 @@
       <c r="AP173" s="2" t="n">
         <v>-0.0009483167377905478</v>
       </c>
+      <c r="AQ173" s="1" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="AR173" s="3" t="n">
+        <v>0.0004746084480305203</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -23171,6 +24215,12 @@
       <c r="AP174" s="2" t="n">
         <v>-0.001903695408734641</v>
       </c>
+      <c r="AQ174" s="1" t="n">
+        <v>0.08896</v>
+      </c>
+      <c r="AR174" s="2" t="n">
+        <v>-0.001907326377201879</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -23301,6 +24351,12 @@
       <c r="AP175" s="2" t="n">
         <v>-0.002218524681086987</v>
       </c>
+      <c r="AQ175" s="1" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="AR175" s="2" t="n">
+        <v>-0.003057254030016648</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -23431,6 +24487,12 @@
       <c r="AP176" s="2" t="n">
         <v>-0.004233301975540912</v>
       </c>
+      <c r="AQ176" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="AR176" s="3" t="n">
+        <v>0.005668398677373575</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -23561,6 +24623,12 @@
       <c r="AP177" s="2" t="n">
         <v>-0.002547770700636839</v>
       </c>
+      <c r="AQ177" s="1" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="AR177" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -23691,6 +24759,12 @@
       <c r="AP178" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ178" s="1" t="n">
+        <v>0.000952</v>
+      </c>
+      <c r="AR178" s="3" t="n">
+        <v>0.003161222339304608</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -23821,6 +24895,12 @@
       <c r="AP179" s="2" t="n">
         <v>-0.003582506881034503</v>
       </c>
+      <c r="AQ179" s="1" t="n">
+        <v>0.022863</v>
+      </c>
+      <c r="AR179" s="3" t="n">
+        <v>0.002455386504143486</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -23951,6 +25031,12 @@
       <c r="AP180" s="2" t="n">
         <v>-0.001959823615874573</v>
       </c>
+      <c r="AQ180" s="1" t="n">
+        <v>4.096</v>
+      </c>
+      <c r="AR180" s="3" t="n">
+        <v>0.005400098183603398</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -24081,6 +25167,12 @@
       <c r="AP181" s="2" t="n">
         <v>-0.0001761493746697005</v>
       </c>
+      <c r="AQ181" s="1" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="AR181" s="3" t="n">
+        <v>0.004404510218463808</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -24211,6 +25303,12 @@
       <c r="AP182" s="2" t="n">
         <v>-0.004371150407311702</v>
       </c>
+      <c r="AQ182" s="1" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="AR182" s="3" t="n">
+        <v>0.00419078028337647</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -24341,6 +25439,12 @@
       <c r="AP183" s="3" t="n">
         <v>0.0007377351530801269</v>
       </c>
+      <c r="AQ183" s="1" t="n">
+        <v>5.431</v>
+      </c>
+      <c r="AR183" s="3" t="n">
+        <v>0.0009214891264282885</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -24471,6 +25575,12 @@
       <c r="AP184" s="3" t="n">
         <v>0.00104602510460255</v>
       </c>
+      <c r="AQ184" s="1" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="AR184" s="3" t="n">
+        <v>0.003483106931382719</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -24601,6 +25711,12 @@
       <c r="AP185" s="3" t="n">
         <v>0.002168021680216714</v>
       </c>
+      <c r="AQ185" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="AR185" s="2" t="n">
+        <v>-0.001622498647917727</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -24731,6 +25847,12 @@
       <c r="AP186" s="2" t="n">
         <v>-0.006514657980456074</v>
       </c>
+      <c r="AQ186" s="1" t="n">
+        <v>3.06e-05</v>
+      </c>
+      <c r="AR186" s="3" t="n">
+        <v>0.003278688524590133</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -24861,6 +25983,12 @@
       <c r="AP187" s="2" t="n">
         <v>-0.001919385796545249</v>
       </c>
+      <c r="AQ187" s="1" t="n">
+        <v>0.01568</v>
+      </c>
+      <c r="AR187" s="3" t="n">
+        <v>0.005128205128205142</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -24991,6 +26119,12 @@
       <c r="AP188" s="2" t="n">
         <v>-0.001718634912840673</v>
       </c>
+      <c r="AQ188" s="1" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="AR188" s="3" t="n">
+        <v>0.001229709788489952</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -25121,6 +26255,12 @@
       <c r="AP189" s="2" t="n">
         <v>-0.003385240352064956</v>
       </c>
+      <c r="AQ189" s="1" t="n">
+        <v>0.0004417</v>
+      </c>
+      <c r="AR189" s="3" t="n">
+        <v>0.0002264492753623243</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -25251,6 +26391,12 @@
       <c r="AP190" s="2" t="n">
         <v>-0.0008680555555556708</v>
       </c>
+      <c r="AQ190" s="1" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="AR190" s="3" t="n">
+        <v>0.003040834057341469</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -25381,6 +26527,12 @@
       <c r="AP191" s="2" t="n">
         <v>-0.003824091778202521</v>
       </c>
+      <c r="AQ191" s="1" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="AR191" s="3" t="n">
+        <v>0.000639795265515009</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -25511,6 +26663,12 @@
       <c r="AP192" s="2" t="n">
         <v>-0.003586157432311257</v>
       </c>
+      <c r="AQ192" s="1" t="n">
+        <v>0.05574</v>
+      </c>
+      <c r="AR192" s="3" t="n">
+        <v>0.003059204606802169</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -25641,6 +26799,12 @@
       <c r="AP193" s="2" t="n">
         <v>-0.001071811361200311</v>
       </c>
+      <c r="AQ193" s="1" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="AR193" s="3" t="n">
+        <v>0.001609442060085808</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -25771,6 +26935,12 @@
       <c r="AP194" s="2" t="n">
         <v>-0.001558441558441495</v>
       </c>
+      <c r="AQ194" s="1" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="AR194" s="2" t="n">
+        <v>-0.0005202913631633503</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -25901,6 +27071,12 @@
       <c r="AP195" s="3" t="n">
         <v>0.0002347969006808852</v>
       </c>
+      <c r="AQ195" s="1" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="AR195" s="3" t="n">
+        <v>0.003051643192488318</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -26031,6 +27207,12 @@
       <c r="AP196" s="2" t="n">
         <v>-0.004885993485341962</v>
       </c>
+      <c r="AQ196" s="1" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="AR196" s="2" t="n">
+        <v>-0.00163666121112923</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -26161,6 +27343,12 @@
       <c r="AP197" s="2" t="n">
         <v>-0.01150173611111117</v>
       </c>
+      <c r="AQ197" s="1" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="AR197" s="3" t="n">
+        <v>0.01273326015367722</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -26291,6 +27479,12 @@
       <c r="AP198" s="2" t="n">
         <v>-0.001170731707316944</v>
       </c>
+      <c r="AQ198" s="1" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="AR198" s="3" t="n">
+        <v>0.004493065051767862</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -26421,6 +27615,12 @@
       <c r="AP199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AR199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -26551,6 +27751,12 @@
       <c r="AP200" s="2" t="n">
         <v>-0.0006752194463200396</v>
       </c>
+      <c r="AQ200" s="1" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="AR200" s="2" t="n">
+        <v>-0.0006756756756757813</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -26681,6 +27887,12 @@
       <c r="AP201" s="2" t="n">
         <v>-0.003021148036253715</v>
       </c>
+      <c r="AQ201" s="1" t="n">
+        <v>0.005607</v>
+      </c>
+      <c r="AR201" s="2" t="n">
+        <v>-0.000534759358288841</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -26811,6 +28023,12 @@
       <c r="AP202" s="3" t="n">
         <v>0.002176562772070409</v>
       </c>
+      <c r="AQ202" s="1" t="n">
+        <v>0.023006</v>
+      </c>
+      <c r="AR202" s="2" t="n">
+        <v>-0.0006949874033534064</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -26941,6 +28159,12 @@
       <c r="AP203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AR203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -27071,6 +28295,12 @@
       <c r="AP204" s="2" t="n">
         <v>-0.0006015037593984717</v>
       </c>
+      <c r="AQ204" s="1" t="n">
+        <v>0.03347</v>
+      </c>
+      <c r="AR204" s="3" t="n">
+        <v>0.007222389407162117</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -27201,6 +28431,12 @@
       <c r="AP205" s="3" t="n">
         <v>0.0004797313504439117</v>
       </c>
+      <c r="AQ205" s="1" t="n">
+        <v>4.143</v>
+      </c>
+      <c r="AR205" s="2" t="n">
+        <v>-0.00671301846080088</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -27331,6 +28567,12 @@
       <c r="AP206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ206" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -27461,6 +28703,12 @@
       <c r="AP207" s="2" t="n">
         <v>-0.03645007923930272</v>
       </c>
+      <c r="AQ207" s="1" t="n">
+        <v>0.0012201</v>
+      </c>
+      <c r="AR207" s="3" t="n">
+        <v>0.003371710526315738</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -27591,6 +28839,12 @@
       <c r="AP208" s="3" t="n">
         <v>0.004485562097000268</v>
       </c>
+      <c r="AQ208" s="1" t="n">
+        <v>0.007169</v>
+      </c>
+      <c r="AR208" s="3" t="n">
+        <v>0.0004186435947530558</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -27721,6 +28975,12 @@
       <c r="AP209" s="2" t="n">
         <v>-0.003344481605351151</v>
       </c>
+      <c r="AQ209" s="1" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="AR209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -27851,6 +29111,12 @@
       <c r="AP210" s="3" t="n">
         <v>0.001554001554001383</v>
       </c>
+      <c r="AQ210" s="1" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="AR210" s="2" t="n">
+        <v>-0.0007757951900697362</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -27981,6 +29247,12 @@
       <c r="AP211" s="2" t="n">
         <v>-0.001684919966301581</v>
       </c>
+      <c r="AQ211" s="1" t="n">
+        <v>0.007125</v>
+      </c>
+      <c r="AR211" s="3" t="n">
+        <v>0.002109704641350247</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -28111,6 +29383,12 @@
       <c r="AP212" s="3" t="n">
         <v>0.01363791339924993</v>
       </c>
+      <c r="AQ212" s="1" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="AR212" s="2" t="n">
+        <v>-0.003699966363942112</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -28241,6 +29519,12 @@
       <c r="AP213" s="3" t="n">
         <v>0.005142332415059733</v>
       </c>
+      <c r="AQ213" s="1" t="n">
+        <v>0.05465</v>
+      </c>
+      <c r="AR213" s="2" t="n">
+        <v>-0.001461721176685615</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -28371,6 +29655,12 @@
       <c r="AP214" s="2" t="n">
         <v>-0.001595744680851036</v>
       </c>
+      <c r="AQ214" s="1" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AR214" s="2" t="n">
+        <v>-0.00106553010122539</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -28501,6 +29791,12 @@
       <c r="AP215" s="3" t="n">
         <v>0.0001877581674802126</v>
       </c>
+      <c r="AQ215" s="1" t="n">
+        <v>0.05308</v>
+      </c>
+      <c r="AR215" s="2" t="n">
+        <v>-0.003566735498404275</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -28631,6 +29927,12 @@
       <c r="AP216" s="2" t="n">
         <v>-0.0009925558312654252</v>
       </c>
+      <c r="AQ216" s="1" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="AR216" s="3" t="n">
+        <v>0.003974167908594019</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -28761,6 +30063,12 @@
       <c r="AP217" s="2" t="n">
         <v>-0.002164502164502148</v>
       </c>
+      <c r="AQ217" s="1" t="n">
+        <v>6.005</v>
+      </c>
+      <c r="AR217" s="3" t="n">
+        <v>0.002002336058735119</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -28891,6 +30199,12 @@
       <c r="AP218" s="2" t="n">
         <v>-0.002596176540004749</v>
       </c>
+      <c r="AQ218" s="1" t="n">
+        <v>4.225</v>
+      </c>
+      <c r="AR218" s="2" t="n">
+        <v>-0.0002366303833413</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -29021,6 +30335,12 @@
       <c r="AP219" s="2" t="n">
         <v>-0.003182924545965273</v>
       </c>
+      <c r="AQ219" s="1" t="n">
+        <v>0.005364</v>
+      </c>
+      <c r="AR219" s="3" t="n">
+        <v>0.007513148009015798</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -29151,6 +30471,12 @@
       <c r="AP220" s="3" t="n">
         <v>0.001958384332925427</v>
       </c>
+      <c r="AQ220" s="1" t="n">
+        <v>0.04103</v>
+      </c>
+      <c r="AR220" s="3" t="n">
+        <v>0.002443195699975468</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -29281,6 +30607,12 @@
       <c r="AP221" s="3" t="n">
         <v>0.001916042501306496</v>
       </c>
+      <c r="AQ221" s="1" t="n">
+        <v>0.005784</v>
+      </c>
+      <c r="AR221" s="3" t="n">
+        <v>0.005563282336578565</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -29411,6 +30743,12 @@
       <c r="AP222" s="2" t="n">
         <v>-0.005428881650380027</v>
       </c>
+      <c r="AQ222" s="1" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="AR222" s="3" t="n">
+        <v>0.00218340611353718</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -29541,6 +30879,12 @@
       <c r="AP223" s="2" t="n">
         <v>-0.0002985074626867</v>
       </c>
+      <c r="AQ223" s="1" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AR223" s="3" t="n">
+        <v>0.00358315915198577</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -29671,6 +31015,12 @@
       <c r="AP224" s="2" t="n">
         <v>-0.00115821172110249</v>
       </c>
+      <c r="AQ224" s="1" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="AR224" s="3" t="n">
+        <v>0.002087198515769843</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -29801,6 +31151,12 @@
       <c r="AP225" s="2" t="n">
         <v>-0.001083684527393051</v>
       </c>
+      <c r="AQ225" s="1" t="n">
+        <v>0.08322</v>
+      </c>
+      <c r="AR225" s="3" t="n">
+        <v>0.003134040501446436</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -29931,6 +31287,12 @@
       <c r="AP226" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ226" s="1" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="AR226" s="2" t="n">
+        <v>-0.0005399568034557016</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -30061,6 +31423,12 @@
       <c r="AP227" s="2" t="n">
         <v>-0.001916116670215027</v>
       </c>
+      <c r="AQ227" s="1" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="AR227" s="3" t="n">
+        <v>0.000426621160409539</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -30191,6 +31559,12 @@
       <c r="AP228" s="2" t="n">
         <v>-0.0008620689655172063</v>
       </c>
+      <c r="AQ228" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="AR228" s="3" t="n">
+        <v>0.002588438308887016</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -30321,6 +31695,12 @@
       <c r="AP229" s="2" t="n">
         <v>-0.003683241252302003</v>
       </c>
+      <c r="AQ229" s="1" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="AR229" s="3" t="n">
+        <v>0.004621072088724588</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -30451,6 +31831,12 @@
       <c r="AP230" s="2" t="n">
         <v>-0.002406738868832634</v>
       </c>
+      <c r="AQ230" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AR230" s="3" t="n">
+        <v>0.001206272617611615</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -30581,6 +31967,12 @@
       <c r="AP231" s="3" t="n">
         <v>0.001321003963011835</v>
       </c>
+      <c r="AQ231" s="1" t="n">
+        <v>0.03041</v>
+      </c>
+      <c r="AR231" s="3" t="n">
+        <v>0.002968337730870706</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -30711,6 +32103,12 @@
       <c r="AP232" s="2" t="n">
         <v>-0.007637017070979336</v>
       </c>
+      <c r="AQ232" s="1" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="AR232" s="3" t="n">
+        <v>0.004979628791308396</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -30841,6 +32239,12 @@
       <c r="AP233" s="2" t="n">
         <v>-0.04184066159010893</v>
       </c>
+      <c r="AQ233" s="1" t="n">
+        <v>0.11836</v>
+      </c>
+      <c r="AR233" s="3" t="n">
+        <v>0.01145103401128019</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -30971,6 +32375,12 @@
       <c r="AP234" s="2" t="n">
         <v>-0.001185302252074149</v>
       </c>
+      <c r="AQ234" s="1" t="n">
+        <v>0.2534</v>
+      </c>
+      <c r="AR234" s="3" t="n">
+        <v>0.002373417721518945</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -31101,6 +32511,12 @@
       <c r="AP235" s="3" t="n">
         <v>0.0001456239988351537</v>
       </c>
+      <c r="AQ235" s="1" t="n">
+        <v>0.06876</v>
+      </c>
+      <c r="AR235" s="3" t="n">
+        <v>0.001164822364589353</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -31231,6 +32647,12 @@
       <c r="AP236" s="2" t="n">
         <v>-0.001033961663883075</v>
       </c>
+      <c r="AQ236" s="1" t="n">
+        <v>0.12575</v>
+      </c>
+      <c r="AR236" s="3" t="n">
+        <v>0.001194267515923656</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -31361,6 +32783,12 @@
       <c r="AP237" s="2" t="n">
         <v>-0.004183006535947723</v>
       </c>
+      <c r="AQ237" s="1" t="n">
+        <v>0.03819</v>
+      </c>
+      <c r="AR237" s="3" t="n">
+        <v>0.002625360987135806</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -31491,6 +32919,12 @@
       <c r="AP238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AR238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -31621,6 +33055,12 @@
       <c r="AP239" s="2" t="n">
         <v>-0.01738035264483618</v>
       </c>
+      <c r="AQ239" s="1" t="n">
+        <v>0.003919</v>
+      </c>
+      <c r="AR239" s="3" t="n">
+        <v>0.004614201486798203</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -31751,6 +33191,12 @@
       <c r="AP240" s="2" t="n">
         <v>-0.0007288629737609032</v>
       </c>
+      <c r="AQ240" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="AR240" s="3" t="n">
+        <v>0.002188183807439862</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -31881,6 +33327,12 @@
       <c r="AP241" s="2" t="n">
         <v>-0.003820224719101077</v>
       </c>
+      <c r="AQ241" s="1" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AR241" s="3" t="n">
+        <v>0.003834874802616691</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -32011,6 +33463,12 @@
       <c r="AP242" s="2" t="n">
         <v>-0.004026845637583845</v>
       </c>
+      <c r="AQ242" s="1" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="AR242" s="3" t="n">
+        <v>0.002695417789757419</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -32141,6 +33599,12 @@
       <c r="AP243" s="2" t="n">
         <v>-0.005754758742806471</v>
       </c>
+      <c r="AQ243" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="AR243" s="3" t="n">
+        <v>0.006233303650934896</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -32271,6 +33735,12 @@
       <c r="AP244" s="3" t="n">
         <v>0.002378121284185551</v>
       </c>
+      <c r="AQ244" s="1" t="n">
+        <v>0.001692</v>
+      </c>
+      <c r="AR244" s="3" t="n">
+        <v>0.003558718861209922</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -32401,6 +33871,12 @@
       <c r="AP245" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ245" s="1" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="AR245" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -32531,6 +34007,12 @@
       <c r="AP246" s="2" t="n">
         <v>-0.005106926268751898</v>
       </c>
+      <c r="AQ246" s="1" t="n">
+        <v>0.03103</v>
+      </c>
+      <c r="AR246" s="2" t="n">
+        <v>-0.004491498235482875</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -32661,6 +34143,12 @@
       <c r="AP247" s="2" t="n">
         <v>-0.001126760563380158</v>
       </c>
+      <c r="AQ247" s="1" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="AR247" s="3" t="n">
+        <v>0.001128031584884252</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -32791,6 +34279,12 @@
       <c r="AP248" s="2" t="n">
         <v>-0.002968337730870706</v>
       </c>
+      <c r="AQ248" s="1" t="n">
+        <v>0.03016</v>
+      </c>
+      <c r="AR248" s="2" t="n">
+        <v>-0.002315580549123408</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -32921,6 +34415,12 @@
       <c r="AP249" s="3" t="n">
         <v>0.003055114261273459</v>
       </c>
+      <c r="AQ249" s="1" t="n">
+        <v>0.008263</v>
+      </c>
+      <c r="AR249" s="3" t="n">
+        <v>0.006700779727095455</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -33051,6 +34551,12 @@
       <c r="AP250" s="3" t="n">
         <v>0.003033367037411579</v>
       </c>
+      <c r="AQ250" s="1" t="n">
+        <v>0.01996</v>
+      </c>
+      <c r="AR250" s="3" t="n">
+        <v>0.006048387096774122</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -33181,6 +34687,12 @@
       <c r="AP251" s="2" t="n">
         <v>-0.00215889464594134</v>
       </c>
+      <c r="AQ251" s="1" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="AR251" s="2" t="n">
+        <v>-0.000865426222414504</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -33311,6 +34823,12 @@
       <c r="AP252" s="3" t="n">
         <v>0.0001170548987474266</v>
       </c>
+      <c r="AQ252" s="1" t="n">
+        <v>0.008536999999999999</v>
+      </c>
+      <c r="AR252" s="2" t="n">
+        <v>-0.0008192883895131159</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -33441,6 +34959,12 @@
       <c r="AP253" s="2" t="n">
         <v>-0.007268951194184723</v>
       </c>
+      <c r="AQ253" s="1" t="n">
+        <v>0.03789</v>
+      </c>
+      <c r="AR253" s="2" t="n">
+        <v>-0.009152719665272046</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -33571,6 +35095,12 @@
       <c r="AP254" s="2" t="n">
         <v>-0.001147540983606568</v>
       </c>
+      <c r="AQ254" s="1" t="n">
+        <v>0.06094</v>
+      </c>
+      <c r="AR254" s="3" t="n">
+        <v>0.0001641227638273931</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -33701,6 +35231,12 @@
       <c r="AP255" s="2" t="n">
         <v>-0.0005668934240362335</v>
       </c>
+      <c r="AQ255" s="1" t="n">
+        <v>0.003519</v>
+      </c>
+      <c r="AR255" s="2" t="n">
+        <v>-0.001985252410663659</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -33831,6 +35367,12 @@
       <c r="AP256" s="3" t="n">
         <v>0.002323141486810535</v>
       </c>
+      <c r="AQ256" s="1" t="n">
+        <v>0.013303</v>
+      </c>
+      <c r="AR256" s="2" t="n">
+        <v>-0.005383177570093395</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -33961,6 +35503,12 @@
       <c r="AP257" s="2" t="n">
         <v>-1.000556309336747e-06</v>
       </c>
+      <c r="AQ257" s="1" t="n">
+        <v>0.999443</v>
+      </c>
+      <c r="AR257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -34091,6 +35639,12 @@
       <c r="AP258" s="2" t="n">
         <v>-0.003396739130434723</v>
       </c>
+      <c r="AQ258" s="1" t="n">
+        <v>0.08773</v>
+      </c>
+      <c r="AR258" s="2" t="n">
+        <v>-0.003294705748693463</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -34221,6 +35775,12 @@
       <c r="AP259" s="2" t="n">
         <v>-0.000784313725490203</v>
       </c>
+      <c r="AQ259" s="1" t="n">
+        <v>0.08926000000000001</v>
+      </c>
+      <c r="AR259" s="3" t="n">
+        <v>0.0008970621215520366</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -34351,6 +35911,12 @@
       <c r="AP260" s="2" t="n">
         <v>-0.003826688063202132</v>
       </c>
+      <c r="AQ260" s="1" t="n">
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="AR260" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -34481,6 +36047,12 @@
       <c r="AP261" s="2" t="n">
         <v>-0.001754385964912282</v>
       </c>
+      <c r="AQ261" s="1" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="AR261" s="3" t="n">
+        <v>0.008787346221441132</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -34611,6 +36183,12 @@
       <c r="AP262" s="3" t="n">
         <v>0.003340184994861251</v>
       </c>
+      <c r="AQ262" s="1" t="n">
+        <v>0.003925</v>
+      </c>
+      <c r="AR262" s="3" t="n">
+        <v>0.005121638924455729</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -34741,6 +36319,12 @@
       <c r="AP263" s="2" t="n">
         <v>-0.008818342151675493</v>
       </c>
+      <c r="AQ263" s="1" t="n">
+        <v>0.1124</v>
+      </c>
+      <c r="AR263" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -34871,6 +36455,12 @@
       <c r="AP264" s="2" t="n">
         <v>-0.007619974059662873</v>
       </c>
+      <c r="AQ264" s="1" t="n">
+        <v>0.0006169</v>
+      </c>
+      <c r="AR264" s="3" t="n">
+        <v>0.007841855905897742</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -35001,6 +36591,12 @@
       <c r="AP265" s="2" t="n">
         <v>-0.001374570446735458</v>
       </c>
+      <c r="AQ265" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="AR265" s="3" t="n">
+        <v>0.0006882312456986461</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -35131,6 +36727,12 @@
       <c r="AP266" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ266" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="AR266" s="3" t="n">
+        <v>0.001584786053882771</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -35261,6 +36863,12 @@
       <c r="AP267" s="2" t="n">
         <v>-0.003080714725816477</v>
       </c>
+      <c r="AQ267" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AR267" s="3" t="n">
+        <v>0.003090234857849285</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -35391,6 +36999,12 @@
       <c r="AP268" s="2" t="n">
         <v>-0.003945230912044528</v>
       </c>
+      <c r="AQ268" s="1" t="n">
+        <v>0.0004306</v>
+      </c>
+      <c r="AR268" s="3" t="n">
+        <v>0.003261882572227353</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -35521,6 +37135,12 @@
       <c r="AP269" s="3" t="n">
         <v>0.0004821600771455927</v>
       </c>
+      <c r="AQ269" s="1" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="AR269" s="2" t="n">
+        <v>-0.0009638554216868749</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -35651,6 +37271,12 @@
       <c r="AP270" s="2" t="n">
         <v>-0.0005488474204170636</v>
       </c>
+      <c r="AQ270" s="1" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="AR270" s="3" t="n">
+        <v>0.007138934651290475</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -35781,6 +37407,12 @@
       <c r="AP271" s="2" t="n">
         <v>-0.003387533875338756</v>
       </c>
+      <c r="AQ271" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="AR271" s="3" t="n">
+        <v>0.001359619306594004</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -35911,6 +37543,12 @@
       <c r="AP272" s="2" t="n">
         <v>-0.002540650406503962</v>
       </c>
+      <c r="AQ272" s="1" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="AR272" s="3" t="n">
+        <v>0.001273560876209743</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -36041,6 +37679,12 @@
       <c r="AP273" s="2" t="n">
         <v>-0.002166847237269774</v>
       </c>
+      <c r="AQ273" s="1" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="AR273" s="3" t="n">
+        <v>0.003257328990228016</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -36171,6 +37815,12 @@
       <c r="AP274" s="2" t="n">
         <v>-0.0007888923950773787</v>
       </c>
+      <c r="AQ274" s="1" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="AR274" s="3" t="n">
+        <v>0.0007895152376441539</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -36301,6 +37951,12 @@
       <c r="AP275" s="2" t="n">
         <v>-0.004436557231588261</v>
       </c>
+      <c r="AQ275" s="1" t="n">
+        <v>0.01124</v>
+      </c>
+      <c r="AR275" s="3" t="n">
+        <v>0.001782531194295827</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -36431,6 +38087,12 @@
       <c r="AP276" s="3" t="n">
         <v>0.001148985063194052</v>
       </c>
+      <c r="AQ276" s="1" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="AR276" s="3" t="n">
+        <v>0.001912777352716273</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -36561,6 +38223,12 @@
       <c r="AP277" s="2" t="n">
         <v>-0.0002394062724444113</v>
       </c>
+      <c r="AQ277" s="1" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="AR277" s="3" t="n">
+        <v>0.003113026819923328</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -36691,6 +38359,12 @@
       <c r="AP278" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ278" s="1" t="n">
+        <v>0.01949</v>
+      </c>
+      <c r="AR278" s="2" t="n">
+        <v>-0.001025115325474074</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -36821,6 +38495,12 @@
       <c r="AP279" s="2" t="n">
         <v>-0.002108592514496549</v>
       </c>
+      <c r="AQ279" s="1" t="n">
+        <v>0.00569</v>
+      </c>
+      <c r="AR279" s="3" t="n">
+        <v>0.001936960732523283</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -36951,6 +38631,12 @@
       <c r="AP280" s="3" t="n">
         <v>0.004113110539845769</v>
       </c>
+      <c r="AQ280" s="1" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="AR280" s="2" t="n">
+        <v>-0.002304147465437783</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -37081,6 +38767,12 @@
       <c r="AP281" s="3" t="n">
         <v>0.001107419712070876</v>
       </c>
+      <c r="AQ281" s="1" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="AR281" s="3" t="n">
+        <v>0.002212389380530975</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -37211,6 +38903,12 @@
       <c r="AP282" s="2" t="n">
         <v>-0.002888086642599348</v>
       </c>
+      <c r="AQ282" s="1" t="n">
+        <v>0.0004176</v>
+      </c>
+      <c r="AR282" s="3" t="n">
+        <v>0.007965242577842207</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -37341,6 +39039,12 @@
       <c r="AP283" s="2" t="n">
         <v>-0.0002439024390244649</v>
       </c>
+      <c r="AQ283" s="1" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="AR283" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -37471,6 +39175,12 @@
       <c r="AP284" s="2" t="n">
         <v>-0.001189626457292279</v>
       </c>
+      <c r="AQ284" s="1" t="n">
+        <v>0.04211</v>
+      </c>
+      <c r="AR284" s="3" t="n">
+        <v>0.003096712720342977</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -37601,6 +39311,12 @@
       <c r="AP285" s="2" t="n">
         <v>-0.0006590716505037249</v>
       </c>
+      <c r="AQ285" s="1" t="n">
+        <v>0.10595</v>
+      </c>
+      <c r="AR285" s="2" t="n">
+        <v>-0.001790088562276199</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -37731,6 +39447,12 @@
       <c r="AP286" s="3" t="n">
         <v>0.002392344497607766</v>
       </c>
+      <c r="AQ286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="AR286" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -37861,6 +39583,12 @@
       <c r="AP287" s="3" t="n">
         <v>0.002997640155622158</v>
       </c>
+      <c r="AQ287" s="1" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="AR287" s="2" t="n">
+        <v>-0.006422485056594244</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -37991,6 +39719,12 @@
       <c r="AP288" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ288" s="1" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="AR288" s="2" t="n">
+        <v>-0.0005537098560355301</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -38121,6 +39855,12 @@
       <c r="AP289" s="2" t="n">
         <v>-0.002662149080348314</v>
       </c>
+      <c r="AQ289" s="1" t="n">
+        <v>4.132</v>
+      </c>
+      <c r="AR289" s="3" t="n">
+        <v>0.002669255035185448</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -38251,6 +39991,12 @@
       <c r="AP290" s="2" t="n">
         <v>-0.0003521540086864919</v>
       </c>
+      <c r="AQ290" s="1" t="n">
+        <v>0.08518000000000001</v>
+      </c>
+      <c r="AR290" s="3" t="n">
+        <v>0.0002348520432128479</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -38381,6 +40127,12 @@
       <c r="AP291" s="3" t="n">
         <v>0.00226052557219564</v>
       </c>
+      <c r="AQ291" s="1" t="n">
+        <v>0.03553</v>
+      </c>
+      <c r="AR291" s="3" t="n">
+        <v>0.001691570341133283</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -38511,6 +40263,12 @@
       <c r="AP292" s="2" t="n">
         <v>-0.001358695652173914</v>
       </c>
+      <c r="AQ292" s="1" t="n">
+        <v>1.4665</v>
+      </c>
+      <c r="AR292" s="2" t="n">
+        <v>-0.002380952380952421</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -38641,6 +40399,12 @@
       <c r="AP293" s="2" t="n">
         <v>-0.00205444273240881</v>
       </c>
+      <c r="AQ293" s="1" t="n">
+        <v>0.005837</v>
+      </c>
+      <c r="AR293" s="3" t="n">
+        <v>0.001372448104306089</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -38771,6 +40535,12 @@
       <c r="AP294" s="2" t="n">
         <v>-0.001464986815118604</v>
       </c>
+      <c r="AQ294" s="1" t="n">
+        <v>0.003426</v>
+      </c>
+      <c r="AR294" s="3" t="n">
+        <v>0.005281690140845008</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -38901,6 +40671,12 @@
       <c r="AP295" s="2" t="n">
         <v>-0.0003726476616358822</v>
       </c>
+      <c r="AQ295" s="1" t="n">
+        <v>0.5362</v>
+      </c>
+      <c r="AR295" s="2" t="n">
+        <v>-0.0005591798695246356</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -39031,6 +40807,12 @@
       <c r="AP296" s="3" t="n">
         <v>0.0004448398576511965</v>
       </c>
+      <c r="AQ296" s="1" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="AR296" s="3" t="n">
+        <v>0.002667852378834941</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -39161,6 +40943,12 @@
       <c r="AP297" s="2" t="n">
         <v>-0.004184100418409871</v>
       </c>
+      <c r="AQ297" s="1" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="AR297" s="3" t="n">
+        <v>0.001800720288115173</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -39291,6 +41079,12 @@
       <c r="AP298" s="3" t="n">
         <v>0.00300792999726549</v>
       </c>
+      <c r="AQ298" s="1" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AR298" s="2" t="n">
+        <v>-0.002998909487459078</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -39421,6 +41215,12 @@
       <c r="AP299" s="2" t="n">
         <v>-0.002705139765554444</v>
       </c>
+      <c r="AQ299" s="1" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AR299" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -39551,6 +41351,12 @@
       <c r="AP300" s="2" t="n">
         <v>-0.0004885197850512747</v>
       </c>
+      <c r="AQ300" s="1" t="n">
+        <v>0.02057</v>
+      </c>
+      <c r="AR300" s="3" t="n">
+        <v>0.005376344086021626</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -39681,6 +41487,12 @@
       <c r="AP301" s="3" t="n">
         <v>0.002613524991832809</v>
       </c>
+      <c r="AQ301" s="1" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AR301" s="2" t="n">
+        <v>-0.000325839035516419</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -39811,6 +41623,12 @@
       <c r="AP302" s="3" t="n">
         <v>0.001450326323422711</v>
       </c>
+      <c r="AQ302" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="AR302" s="3" t="n">
+        <v>0.002172338884866076</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -39941,6 +41759,12 @@
       <c r="AP303" s="3" t="n">
         <v>0.0006799020940985637</v>
       </c>
+      <c r="AQ303" s="1" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="AR303" s="3" t="n">
+        <v>0.001630656339176452</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -40071,6 +41895,12 @@
       <c r="AP304" s="2" t="n">
         <v>-0.001263423878711256</v>
       </c>
+      <c r="AQ304" s="1" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="AR304" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -40201,6 +42031,12 @@
       <c r="AP305" s="2" t="n">
         <v>-0.0003134796238243299</v>
       </c>
+      <c r="AQ305" s="1" t="n">
+        <v>0.06393</v>
+      </c>
+      <c r="AR305" s="3" t="n">
+        <v>0.002351834430856026</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -40331,6 +42167,12 @@
       <c r="AP306" s="2" t="n">
         <v>-0.002034587995930741</v>
       </c>
+      <c r="AQ306" s="1" t="n">
+        <v>0.04915</v>
+      </c>
+      <c r="AR306" s="3" t="n">
+        <v>0.002038735983690029</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -40461,6 +42303,12 @@
       <c r="AP307" s="2" t="n">
         <v>-0.003253796095444688</v>
       </c>
+      <c r="AQ307" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="AR307" s="3" t="n">
+        <v>0.003264417845484225</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -40591,6 +42439,12 @@
       <c r="AP308" s="2" t="n">
         <v>-0.002014605892722329</v>
       </c>
+      <c r="AQ308" s="1" t="n">
+        <v>0.03962</v>
+      </c>
+      <c r="AR308" s="2" t="n">
+        <v>-0.0002523340903355065</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -40721,6 +42575,12 @@
       <c r="AP309" s="2" t="n">
         <v>-0.005184705119896207</v>
       </c>
+      <c r="AQ309" s="1" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="AR309" s="3" t="n">
+        <v>0.001954397394136728</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -40851,6 +42711,12 @@
       <c r="AP310" s="2" t="n">
         <v>-0.000183891136447152</v>
       </c>
+      <c r="AQ310" s="1" t="n">
+        <v>0.05456</v>
+      </c>
+      <c r="AR310" s="3" t="n">
+        <v>0.003494574213720723</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -40981,6 +42847,12 @@
       <c r="AP311" s="3" t="n">
         <v>0.002468027821404471</v>
       </c>
+      <c r="AQ311" s="1" t="n">
+        <v>0.004469</v>
+      </c>
+      <c r="AR311" s="3" t="n">
+        <v>0.0002238137869293045</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -41111,6 +42983,12 @@
       <c r="AP312" s="2" t="n">
         <v>-0.001537369914853255</v>
       </c>
+      <c r="AQ312" s="1" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="AR312" s="2" t="n">
+        <v>-0.002724150183584128</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -41241,6 +43119,12 @@
       <c r="AP313" s="2" t="n">
         <v>-0.001752021563342387</v>
       </c>
+      <c r="AQ313" s="1" t="n">
+        <v>0.07425</v>
+      </c>
+      <c r="AR313" s="3" t="n">
+        <v>0.002430133657351149</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -41371,6 +43255,12 @@
       <c r="AP314" s="2" t="n">
         <v>-0.0006561679790027345</v>
       </c>
+      <c r="AQ314" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="AR314" s="3" t="n">
+        <v>0.00196979645436653</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -41501,6 +43391,12 @@
       <c r="AP315" s="3" t="n">
         <v>0.0006297229219144632</v>
       </c>
+      <c r="AQ315" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="AR315" s="3" t="n">
+        <v>0.00188797986154811</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -41631,6 +43527,12 @@
       <c r="AP316" s="2" t="n">
         <v>-0.003904071388733845</v>
       </c>
+      <c r="AQ316" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="AR316" s="3" t="n">
+        <v>0.002239641657334735</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -41761,6 +43663,12 @@
       <c r="AP317" s="2" t="n">
         <v>-0.001472951258703766</v>
       </c>
+      <c r="AQ317" s="1" t="n">
+        <v>0.007479</v>
+      </c>
+      <c r="AR317" s="3" t="n">
+        <v>0.002950248089043894</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -41891,6 +43799,12 @@
       <c r="AP318" s="2" t="n">
         <v>-0.001763668430335093</v>
       </c>
+      <c r="AQ318" s="1" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="AR318" s="3" t="n">
+        <v>0.003729878288182227</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -42021,6 +43935,12 @@
       <c r="AP319" s="3" t="n">
         <v>0.0007153331664221824</v>
       </c>
+      <c r="AQ319" s="1" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="AR319" s="3" t="n">
+        <v>0.002108724400443315</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -42151,6 +44071,12 @@
       <c r="AP320" s="2" t="n">
         <v>-0.001596351197263349</v>
       </c>
+      <c r="AQ320" s="1" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="AR320" s="3" t="n">
+        <v>0.002284148012791231</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -42281,6 +44207,12 @@
       <c r="AP321" s="2" t="n">
         <v>-0.002063185041908362</v>
       </c>
+      <c r="AQ321" s="1" t="n">
+        <v>0.07778</v>
+      </c>
+      <c r="AR321" s="3" t="n">
+        <v>0.005039410776586141</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -42411,6 +44343,12 @@
       <c r="AP322" s="3" t="n">
         <v>0.003103662321539419</v>
       </c>
+      <c r="AQ322" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="AR322" s="3" t="n">
+        <v>0.0006188118811882225</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -42541,6 +44479,12 @@
       <c r="AP323" s="2" t="n">
         <v>-0.00658227848101272</v>
       </c>
+      <c r="AQ323" s="1" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="AR323" s="3" t="n">
+        <v>0.002548419979612699</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -42671,6 +44615,12 @@
       <c r="AP324" s="2" t="n">
         <v>-0.002149037645861143</v>
       </c>
+      <c r="AQ324" s="1" t="n">
+        <v>0.053044</v>
+      </c>
+      <c r="AR324" s="3" t="n">
+        <v>0.002096990535204881</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -42801,6 +44751,12 @@
       <c r="AP325" s="2" t="n">
         <v>-0.002825786948807163</v>
       </c>
+      <c r="AQ325" s="1" t="n">
+        <v>0.15152</v>
+      </c>
+      <c r="AR325" s="2" t="n">
+        <v>-0.001449848424937562</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -42931,6 +44887,12 @@
       <c r="AP326" s="3" t="n">
         <v>0.0007751937984495808</v>
       </c>
+      <c r="AQ326" s="1" t="n">
+        <v>0.006476</v>
+      </c>
+      <c r="AR326" s="3" t="n">
+        <v>0.003253292021688642</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -43061,6 +45023,12 @@
       <c r="AP327" s="2" t="n">
         <v>-0.001714022018590545</v>
       </c>
+      <c r="AQ327" s="1" t="n">
+        <v>0.015182</v>
+      </c>
+      <c r="AR327" s="3" t="n">
+        <v>0.00257544740143955</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -43191,6 +45159,12 @@
       <c r="AP328" s="2" t="n">
         <v>-0.005230125523012556</v>
       </c>
+      <c r="AQ328" s="1" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="AR328" s="3" t="n">
+        <v>0.002103049421661323</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -43321,6 +45295,12 @@
       <c r="AP329" s="2" t="n">
         <v>-0.000229357798165168</v>
       </c>
+      <c r="AQ329" s="1" t="n">
+        <v>0.004365</v>
+      </c>
+      <c r="AR329" s="3" t="n">
+        <v>0.001376462491397093</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -43451,6 +45431,12 @@
       <c r="AP330" s="3" t="n">
         <v>0.0007729468599034843</v>
       </c>
+      <c r="AQ330" s="1" t="n">
+        <v>0.05207</v>
+      </c>
+      <c r="AR330" s="3" t="n">
+        <v>0.005406449121451931</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -43581,6 +45567,12 @@
       <c r="AP331" s="2" t="n">
         <v>-0.0002809778027534736</v>
       </c>
+      <c r="AQ331" s="1" t="n">
+        <v>0.03549</v>
+      </c>
+      <c r="AR331" s="2" t="n">
+        <v>-0.002529510961214159</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -43711,6 +45703,12 @@
       <c r="AP332" s="3" t="n">
         <v>0.0006802721088436513</v>
       </c>
+      <c r="AQ332" s="1" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="AR332" s="2" t="n">
+        <v>-0.004078857919782577</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -43841,6 +45839,12 @@
       <c r="AP333" s="2" t="n">
         <v>-0.00104384133611694</v>
       </c>
+      <c r="AQ333" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AR333" s="2" t="n">
+        <v>-0.001044932079414723</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -43971,6 +45975,12 @@
       <c r="AP334" s="3" t="n">
         <v>0.0006807351940095813</v>
       </c>
+      <c r="AQ334" s="1" t="n">
+        <v>0.04416</v>
+      </c>
+      <c r="AR334" s="3" t="n">
+        <v>0.001360544217687019</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -44101,6 +46111,12 @@
       <c r="AP335" s="2" t="n">
         <v>-0.0007384615384615937</v>
       </c>
+      <c r="AQ335" s="1" t="n">
+        <v>0.08142000000000001</v>
+      </c>
+      <c r="AR335" s="3" t="n">
+        <v>0.002832861189801798</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -44231,6 +46247,12 @@
       <c r="AP336" s="2" t="n">
         <v>-0.00048402710551799</v>
       </c>
+      <c r="AQ336" s="1" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="AR336" s="3" t="n">
+        <v>0.00145278450363207</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -44361,6 +46383,12 @@
       <c r="AP337" s="2" t="n">
         <v>-0.0009950248756218499</v>
       </c>
+      <c r="AQ337" s="1" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="AR337" s="3" t="n">
+        <v>0.0009960159362549395</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -44491,6 +46519,12 @@
       <c r="AP338" s="2" t="n">
         <v>-0.002645502645502599</v>
       </c>
+      <c r="AQ338" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AR338" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -44621,6 +46655,12 @@
       <c r="AP339" s="2" t="n">
         <v>-0.001651982378854558</v>
       </c>
+      <c r="AQ339" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="AR339" s="3" t="n">
+        <v>0.001654715940430159</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -44751,6 +46791,12 @@
       <c r="AP340" s="3" t="n">
         <v>0.01050328227571114</v>
       </c>
+      <c r="AQ340" s="1" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="AR340" s="2" t="n">
+        <v>-0.007109859968240118</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -44881,6 +46927,12 @@
       <c r="AP341" s="2" t="n">
         <v>-0.003277920861624941</v>
       </c>
+      <c r="AQ341" s="1" t="n">
+        <v>0.04258</v>
+      </c>
+      <c r="AR341" s="3" t="n">
+        <v>0.0002349072116514696</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -45011,6 +47063,12 @@
       <c r="AP342" s="2" t="n">
         <v>-0.004184100418410003</v>
       </c>
+      <c r="AQ342" s="1" t="n">
+        <v>0.07837</v>
+      </c>
+      <c r="AR342" s="2" t="n">
+        <v>-0.002164502164502209</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -45141,6 +47199,12 @@
       <c r="AP343" s="2" t="n">
         <v>-0.001577909270217022</v>
       </c>
+      <c r="AQ343" s="1" t="n">
+        <v>7.599</v>
+      </c>
+      <c r="AR343" s="3" t="n">
+        <v>0.0007902015013828826</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -45271,6 +47335,12 @@
       <c r="AP344" s="2" t="n">
         <v>-0.001330450690171149</v>
       </c>
+      <c r="AQ344" s="1" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="AR344" s="3" t="n">
+        <v>0.001665278934221483</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -45401,6 +47471,12 @@
       <c r="AP345" s="2" t="n">
         <v>-0.002148227712137585</v>
       </c>
+      <c r="AQ345" s="1" t="n">
+        <v>0.03725</v>
+      </c>
+      <c r="AR345" s="3" t="n">
+        <v>0.002421959095801932</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -45531,6 +47607,12 @@
       <c r="AP346" s="2" t="n">
         <v>-0.002403846153846056</v>
       </c>
+      <c r="AQ346" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="AR346" s="2" t="n">
+        <v>-0.002409638554216936</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -45661,6 +47743,12 @@
       <c r="AP347" s="2" t="n">
         <v>-0.002855511136493435</v>
       </c>
+      <c r="AQ347" s="1" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="AR347" s="3" t="n">
+        <v>0.004009163802978271</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -45791,6 +47879,12 @@
       <c r="AP348" s="2" t="n">
         <v>-9.626121443148127e-05</v>
       </c>
+      <c r="AQ348" s="1" t="n">
+        <v>5198.7</v>
+      </c>
+      <c r="AR348" s="3" t="n">
+        <v>0.0009627048154494869</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -45921,6 +48015,12 @@
       <c r="AP349" s="3" t="n">
         <v>0.0153958944281525</v>
       </c>
+      <c r="AQ349" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="AR349" s="3" t="n">
+        <v>0.0007220216606499154</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -46051,6 +48151,12 @@
       <c r="AP350" s="2" t="n">
         <v>-0.01027617212588314</v>
       </c>
+      <c r="AQ350" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="AR350" s="3" t="n">
+        <v>0.006489292667099247</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -46181,6 +48287,12 @@
       <c r="AP351" s="2" t="n">
         <v>-0.005044751830756747</v>
       </c>
+      <c r="AQ351" s="1" t="n">
+        <v>0.0006127</v>
+      </c>
+      <c r="AR351" s="3" t="n">
+        <v>0.002126267582597281</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -46311,6 +48423,12 @@
       <c r="AP352" s="2" t="n">
         <v>-0.001519756838905889</v>
       </c>
+      <c r="AQ352" s="1" t="n">
+        <v>0.01973</v>
+      </c>
+      <c r="AR352" s="3" t="n">
+        <v>0.001014713343480602</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -46441,6 +48559,12 @@
       <c r="AP353" s="3" t="n">
         <v>0.0005347593582887112</v>
       </c>
+      <c r="AQ353" s="1" t="n">
+        <v>0.09345000000000001</v>
+      </c>
+      <c r="AR353" s="2" t="n">
+        <v>-0.00106894708711907</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -46571,6 +48695,12 @@
       <c r="AP354" s="2" t="n">
         <v>-0.001111111111111143</v>
       </c>
+      <c r="AQ354" s="1" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="AR354" s="3" t="n">
+        <v>0.00333704115684103</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -46701,6 +48831,12 @@
       <c r="AP355" s="2" t="n">
         <v>-0.002133245815556248</v>
       </c>
+      <c r="AQ355" s="1" t="n">
+        <v>0.0006085</v>
+      </c>
+      <c r="AR355" s="3" t="n">
+        <v>0.0006577865482651039</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -46831,6 +48967,12 @@
       <c r="AP356" s="2" t="n">
         <v>-0.0004975124378108905</v>
       </c>
+      <c r="AQ356" s="1" t="n">
+        <v>2.013</v>
+      </c>
+      <c r="AR356" s="3" t="n">
+        <v>0.001991040318566453</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -46961,6 +49103,12 @@
       <c r="AP357" s="2" t="n">
         <v>-0.004768097095795361</v>
       </c>
+      <c r="AQ357" s="1" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="AR357" s="3" t="n">
+        <v>0.004355400696864085</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -47091,6 +49239,12 @@
       <c r="AP358" s="2" t="n">
         <v>-0.002457002457002516</v>
       </c>
+      <c r="AQ358" s="1" t="n">
+        <v>0.000407</v>
+      </c>
+      <c r="AR358" s="3" t="n">
+        <v>0.002463054187192178</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -47221,6 +49375,12 @@
       <c r="AP359" s="3" t="n">
         <v>0.001360544217687137</v>
       </c>
+      <c r="AQ359" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="AR359" s="3" t="n">
+        <v>0.006793478260869524</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -47351,6 +49511,12 @@
       <c r="AP360" s="2" t="n">
         <v>-0.002408912978018728</v>
       </c>
+      <c r="AQ360" s="1" t="n">
+        <v>0.003307</v>
+      </c>
+      <c r="AR360" s="2" t="n">
+        <v>-0.001811047389073326</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -47481,6 +49647,12 @@
       <c r="AP361" s="2" t="n">
         <v>-0.001425855513308004</v>
       </c>
+      <c r="AQ361" s="1" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="AR361" s="3" t="n">
+        <v>0.007456766619070344</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -47611,6 +49783,12 @@
       <c r="AP362" s="2" t="n">
         <v>-0.00423190859077456</v>
       </c>
+      <c r="AQ362" s="1" t="n">
+        <v>0.02365</v>
+      </c>
+      <c r="AR362" s="3" t="n">
+        <v>0.005099872503187507</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -47741,6 +49919,12 @@
       <c r="AP363" s="2" t="n">
         <v>-0.01414731662309709</v>
       </c>
+      <c r="AQ363" s="1" t="n">
+        <v>0.06461</v>
+      </c>
+      <c r="AR363" s="3" t="n">
+        <v>0.007799095304944634</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -47871,6 +50055,12 @@
       <c r="AP364" s="2" t="n">
         <v>-0.001277955271565544</v>
       </c>
+      <c r="AQ364" s="1" t="n">
+        <v>4.704</v>
+      </c>
+      <c r="AR364" s="3" t="n">
+        <v>0.003198976327575108</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -48001,6 +50191,12 @@
       <c r="AP365" s="3" t="n">
         <v>0.001391982182628102</v>
       </c>
+      <c r="AQ365" s="1" t="n">
+        <v>0.07191</v>
+      </c>
+      <c r="AR365" s="2" t="n">
+        <v>-0.0004170141784820996</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -48131,6 +50327,12 @@
       <c r="AP366" s="2" t="n">
         <v>-0.00287562904385335</v>
       </c>
+      <c r="AQ366" s="1" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="AR366" s="2" t="n">
+        <v>-0.0001802451333814539</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -48261,6 +50463,12 @@
       <c r="AP367" s="2" t="n">
         <v>-0.001898515705902641</v>
       </c>
+      <c r="AQ367" s="1" t="n">
+        <v>0.05793</v>
+      </c>
+      <c r="AR367" s="3" t="n">
+        <v>0.001729206294310961</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -48391,6 +50599,12 @@
       <c r="AP368" s="2" t="n">
         <v>-0.002987172728870207</v>
       </c>
+      <c r="AQ368" s="1" t="n">
+        <v>0.05677</v>
+      </c>
+      <c r="AR368" s="3" t="n">
+        <v>0.0005287275290800537</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -48521,6 +50735,12 @@
       <c r="AP369" s="2" t="n">
         <v>-0.001611863313990908</v>
       </c>
+      <c r="AQ369" s="1" t="n">
+        <v>0.03088</v>
+      </c>
+      <c r="AR369" s="2" t="n">
+        <v>-0.002906038101388434</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -48651,6 +50871,12 @@
       <c r="AP370" s="2" t="n">
         <v>-0.003107520198881368</v>
       </c>
+      <c r="AQ370" s="1" t="n">
+        <v>0.0001607</v>
+      </c>
+      <c r="AR370" s="3" t="n">
+        <v>0.00187032418952623</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -48781,6 +51007,12 @@
       <c r="AP371" s="2" t="n">
         <v>-0.0002950722927117535</v>
       </c>
+      <c r="AQ371" s="1" t="n">
+        <v>0.00678</v>
+      </c>
+      <c r="AR371" s="3" t="n">
+        <v>0.0005903187721369043</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -48911,6 +51143,12 @@
       <c r="AP372" s="2" t="n">
         <v>-0.001302271740703149</v>
       </c>
+      <c r="AQ372" s="1" t="n">
+        <v>0.006924</v>
+      </c>
+      <c r="AR372" s="3" t="n">
+        <v>0.003187481889307368</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -49041,6 +51279,12 @@
       <c r="AP373" s="3" t="n">
         <v>0.0007826767545003051</v>
       </c>
+      <c r="AQ373" s="1" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="AR373" s="3" t="n">
+        <v>0.01955161626694478</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -49171,6 +51415,12 @@
       <c r="AP374" s="3" t="n">
         <v>0.0001435132032146401</v>
       </c>
+      <c r="AQ374" s="1" t="n">
+        <v>0.06966</v>
+      </c>
+      <c r="AR374" s="2" t="n">
+        <v>-0.000430477830391767</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -49301,6 +51551,12 @@
       <c r="AP375" s="2" t="n">
         <v>-0.0003794106487922379</v>
       </c>
+      <c r="AQ375" s="1" t="n">
+        <v>0.07938000000000001</v>
+      </c>
+      <c r="AR375" s="3" t="n">
+        <v>0.004301619433198469</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -49431,6 +51687,12 @@
       <c r="AP376" s="2" t="n">
         <v>-0.0006356268870172949</v>
       </c>
+      <c r="AQ376" s="1" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="AR376" s="3" t="n">
+        <v>0.003180155827635425</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -49561,6 +51823,12 @@
       <c r="AP377" s="2" t="n">
         <v>-0.00208224882873513</v>
       </c>
+      <c r="AQ377" s="1" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="AR377" s="3" t="n">
+        <v>0.001564945226916994</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -49691,6 +51959,12 @@
       <c r="AP378" s="2" t="n">
         <v>-0.001734390485629378</v>
       </c>
+      <c r="AQ378" s="1" t="n">
+        <v>0.0004053</v>
+      </c>
+      <c r="AR378" s="3" t="n">
+        <v>0.005956813104988841</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -49821,6 +52095,12 @@
       <c r="AP379" s="2" t="n">
         <v>-0.0005446623093681694</v>
       </c>
+      <c r="AQ379" s="1" t="n">
+        <v>0.07345</v>
+      </c>
+      <c r="AR379" s="3" t="n">
+        <v>0.0006811989100816688</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -49951,6 +52231,12 @@
       <c r="AP380" s="3" t="n">
         <v>0.006574141709276925</v>
       </c>
+      <c r="AQ380" s="1" t="n">
+        <v>0.001378</v>
+      </c>
+      <c r="AR380" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -50081,6 +52367,12 @@
       <c r="AP381" s="3" t="n">
         <v>0.0003151591553734289</v>
       </c>
+      <c r="AQ381" s="1" t="n">
+        <v>6.357</v>
+      </c>
+      <c r="AR381" s="3" t="n">
+        <v>0.001417769376181528</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -50211,6 +52503,12 @@
       <c r="AP382" s="2" t="n">
         <v>-0.004282655246252626</v>
       </c>
+      <c r="AQ382" s="1" t="n">
+        <v>0.01396</v>
+      </c>
+      <c r="AR382" s="3" t="n">
+        <v>0.0007168458781361714</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -50341,6 +52639,12 @@
       <c r="AP383" s="2" t="n">
         <v>-0.001147446930579613</v>
       </c>
+      <c r="AQ383" s="1" t="n">
+        <v>0.01738</v>
+      </c>
+      <c r="AR383" s="2" t="n">
+        <v>-0.001723147616312394</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -50471,6 +52775,12 @@
       <c r="AP384" s="2" t="n">
         <v>-0.002958579881656889</v>
       </c>
+      <c r="AQ384" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="AR384" s="3" t="n">
+        <v>0.0009891196834817297</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -50601,6 +52911,12 @@
       <c r="AP385" s="2" t="n">
         <v>-0.001564245810055793</v>
       </c>
+      <c r="AQ385" s="1" t="n">
+        <v>4.478</v>
+      </c>
+      <c r="AR385" s="3" t="n">
+        <v>0.002238137869292701</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -50731,6 +53047,12 @@
       <c r="AP386" s="3" t="n">
         <v>0.006923076923077008</v>
       </c>
+      <c r="AQ386" s="1" t="n">
+        <v>0.001304</v>
+      </c>
+      <c r="AR386" s="2" t="n">
+        <v>-0.003819709702062653</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -50861,6 +53183,12 @@
       <c r="AP387" s="2" t="n">
         <v>-0.002721551284232078</v>
       </c>
+      <c r="AQ387" s="1" t="n">
+        <v>0.0005878</v>
+      </c>
+      <c r="AR387" s="3" t="n">
+        <v>0.002558417192563504</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -50991,6 +53319,12 @@
       <c r="AP388" s="2" t="n">
         <v>-0.004405286343612461</v>
       </c>
+      <c r="AQ388" s="1" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="AR388" s="3" t="n">
+        <v>0.00176991150442486</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -51121,6 +53455,12 @@
       <c r="AP389" s="2" t="n">
         <v>-0.003325942350332651</v>
       </c>
+      <c r="AQ389" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AR389" s="3" t="n">
+        <v>0.001112347052280266</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -51251,6 +53591,12 @@
       <c r="AP390" s="2" t="n">
         <v>-0.002803619217535338</v>
       </c>
+      <c r="AQ390" s="1" t="n">
+        <v>0.07835</v>
+      </c>
+      <c r="AR390" s="3" t="n">
+        <v>0.001277955271565532</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -51381,6 +53727,12 @@
       <c r="AP391" s="2" t="n">
         <v>-0.002318840579710051</v>
       </c>
+      <c r="AQ391" s="1" t="n">
+        <v>0.05187</v>
+      </c>
+      <c r="AR391" s="3" t="n">
+        <v>0.004648460197559504</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -51511,6 +53863,12 @@
       <c r="AP392" s="2" t="n">
         <v>-0.008438818565400866</v>
       </c>
+      <c r="AQ392" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="AR392" s="3" t="n">
+        <v>0.004255319148936182</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -51641,6 +53999,12 @@
       <c r="AP393" s="2" t="n">
         <v>-0.0009442870632671947</v>
       </c>
+      <c r="AQ393" s="1" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="AR393" s="3" t="n">
+        <v>0.004253308128544414</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -51771,6 +54135,12 @@
       <c r="AP394" s="3" t="n">
         <v>0.001497753369945056</v>
       </c>
+      <c r="AQ394" s="1" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="AR394" s="3" t="n">
+        <v>0.002492522432701897</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -51901,6 +54271,12 @@
       <c r="AP395" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ395" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="AR395" s="3" t="n">
+        <v>0.001027749229188108</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -52031,6 +54407,12 @@
       <c r="AP396" s="3" t="n">
         <v>0.0007296607077708062</v>
       </c>
+      <c r="AQ396" s="1" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="AR396" s="3" t="n">
+        <v>0.009114108640174959</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -52161,6 +54543,12 @@
       <c r="AP397" s="2" t="n">
         <v>-0.0007892659826360615</v>
       </c>
+      <c r="AQ397" s="1" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR397" s="3" t="n">
+        <v>0.003159557661927333</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -52291,6 +54679,12 @@
       <c r="AP398" s="2" t="n">
         <v>-0.005536514632217177</v>
       </c>
+      <c r="AQ398" s="1" t="n">
+        <v>0.007563</v>
+      </c>
+      <c r="AR398" s="3" t="n">
+        <v>0.002518557794273584</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -52421,6 +54815,12 @@
       <c r="AP399" s="2" t="n">
         <v>-0.0007809449433814057</v>
       </c>
+      <c r="AQ399" s="1" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="AR399" s="2" t="n">
+        <v>-0.001953888237592811</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -52551,6 +54951,12 @@
       <c r="AP400" s="2" t="n">
         <v>-0.0009436929852155472</v>
       </c>
+      <c r="AQ400" s="1" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AR400" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -52681,6 +55087,12 @@
       <c r="AP401" s="2" t="n">
         <v>-0.001381406271584417</v>
       </c>
+      <c r="AQ401" s="1" t="n">
+        <v>0.007236</v>
+      </c>
+      <c r="AR401" s="3" t="n">
+        <v>0.000968322036242919</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -52811,6 +55223,12 @@
       <c r="AP402" s="2" t="n">
         <v>-0.0008764241893077411</v>
       </c>
+      <c r="AQ402" s="1" t="n">
+        <v>0.004569</v>
+      </c>
+      <c r="AR402" s="3" t="n">
+        <v>0.001973684210526387</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -52941,6 +55359,12 @@
       <c r="AP403" s="3" t="n">
         <v>0.0003789314134141303</v>
       </c>
+      <c r="AQ403" s="1" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="AR403" s="2" t="n">
+        <v>-0.002272727272727233</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -53071,6 +55495,12 @@
       <c r="AP404" s="2" t="n">
         <v>-0.008871989860582978</v>
       </c>
+      <c r="AQ404" s="1" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="AR404" s="3" t="n">
+        <v>0.002557544757033203</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -53201,6 +55631,12 @@
       <c r="AP405" s="3" t="n">
         <v>0.001169180404536448</v>
       </c>
+      <c r="AQ405" s="1" t="n">
+        <v>0.0008536</v>
+      </c>
+      <c r="AR405" s="2" t="n">
+        <v>-0.003153100548873072</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -53331,6 +55767,12 @@
       <c r="AP406" s="2" t="n">
         <v>-0.002978554408260403</v>
       </c>
+      <c r="AQ406" s="1" t="n">
+        <v>0.005024</v>
+      </c>
+      <c r="AR406" s="3" t="n">
+        <v>0.0005974905397330274</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -53461,6 +55903,12 @@
       <c r="AP407" s="3" t="n">
         <v>0.003358522250209916</v>
       </c>
+      <c r="AQ407" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="AR407" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -53591,6 +56039,12 @@
       <c r="AP408" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ408" s="1" t="n">
+        <v>0.001501</v>
+      </c>
+      <c r="AR408" s="3" t="n">
+        <v>0.004013377926421357</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -53721,6 +56175,12 @@
       <c r="AP409" s="2" t="n">
         <v>-0.006152268649064447</v>
       </c>
+      <c r="AQ409" s="1" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="AR409" s="3" t="n">
+        <v>0.0007737941707506383</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -53851,6 +56311,12 @@
       <c r="AP410" s="2" t="n">
         <v>-0.001231527093596222</v>
       </c>
+      <c r="AQ410" s="1" t="n">
+        <v>0.01617</v>
+      </c>
+      <c r="AR410" s="2" t="n">
+        <v>-0.003082614056719973</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -53981,6 +56447,12 @@
       <c r="AP411" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ411" s="1" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="AR411" s="3" t="n">
+        <v>0.001054296257248317</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -54111,6 +56583,12 @@
       <c r="AP412" s="3" t="n">
         <v>0.0002961208172933409</v>
       </c>
+      <c r="AQ412" s="1" t="n">
+        <v>0.06748</v>
+      </c>
+      <c r="AR412" s="2" t="n">
+        <v>-0.001184132622853711</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -54241,6 +56719,12 @@
       <c r="AP413" s="2" t="n">
         <v>-0.0003955696202531646</v>
       </c>
+      <c r="AQ413" s="1" t="n">
+        <v>2519</v>
+      </c>
+      <c r="AR413" s="2" t="n">
+        <v>-0.003165809259992085</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -54371,6 +56855,12 @@
       <c r="AP414" s="3" t="n">
         <v>0.0003807348181991088</v>
       </c>
+      <c r="AQ414" s="1" t="n">
+        <v>0.05295</v>
+      </c>
+      <c r="AR414" s="3" t="n">
+        <v>0.00761179828734534</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -54501,6 +56991,12 @@
       <c r="AP415" s="2" t="n">
         <v>-0.003426613363791995</v>
       </c>
+      <c r="AQ415" s="1" t="n">
+        <v>1.743</v>
+      </c>
+      <c r="AR415" s="2" t="n">
+        <v>-0.001146131805157594</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -54631,6 +57127,12 @@
       <c r="AP416" s="2" t="n">
         <v>-0.001167542323409176</v>
       </c>
+      <c r="AQ416" s="1" t="n">
+        <v>0.06852999999999999</v>
+      </c>
+      <c r="AR416" s="3" t="n">
+        <v>0.001315020455873654</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -54761,6 +57263,12 @@
       <c r="AP417" s="2" t="n">
         <v>-0.01351351351351353</v>
       </c>
+      <c r="AQ417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AR417" s="3" t="n">
+        <v>0.01369863013698631</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -54891,6 +57399,12 @@
       <c r="AP418" s="2" t="n">
         <v>-0.001988071570576506</v>
       </c>
+      <c r="AQ418" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="AR418" s="3" t="n">
+        <v>0.0006640106241699135</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -55021,6 +57535,12 @@
       <c r="AP419" s="2" t="n">
         <v>-0.008064516129032209</v>
       </c>
+      <c r="AQ419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AR419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -55151,6 +57671,12 @@
       <c r="AP420" s="3" t="n">
         <v>0.001048218029350062</v>
       </c>
+      <c r="AQ420" s="1" t="n">
+        <v>0.01907</v>
+      </c>
+      <c r="AR420" s="2" t="n">
+        <v>-0.001570680628272187</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -55281,6 +57807,12 @@
       <c r="AP421" s="3" t="n">
         <v>0.0009298961615953582</v>
       </c>
+      <c r="AQ421" s="1" t="n">
+        <v>0.1933</v>
+      </c>
+      <c r="AR421" s="2" t="n">
+        <v>-0.002322580645161321</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -55411,6 +57943,12 @@
       <c r="AP422" s="2" t="n">
         <v>-0.000588581518540498</v>
       </c>
+      <c r="AQ422" s="1" t="n">
+        <v>0.03407</v>
+      </c>
+      <c r="AR422" s="3" t="n">
+        <v>0.003239104829211011</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -55541,6 +58079,12 @@
       <c r="AP423" s="2" t="n">
         <v>-0.002832861189801584</v>
       </c>
+      <c r="AQ423" s="1" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="AR423" s="3" t="n">
+        <v>0.001420454545454389</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -55671,6 +58215,12 @@
       <c r="AP424" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AR424" s="3" t="n">
+        <v>0.003795066413662249</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -55801,6 +58351,12 @@
       <c r="AP425" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ425" s="1" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="AR425" s="3" t="n">
+        <v>0.002890173410404573</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -55931,6 +58487,12 @@
       <c r="AP426" s="2" t="n">
         <v>-0.003819493563446048</v>
       </c>
+      <c r="AQ426" s="1" t="n">
+        <v>0.00705</v>
+      </c>
+      <c r="AR426" s="3" t="n">
+        <v>0.001136040897472337</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -56061,6 +58623,12 @@
       <c r="AP427" s="3" t="n">
         <v>0.005084082909659822</v>
       </c>
+      <c r="AQ427" s="1" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="AR427" s="2" t="n">
+        <v>-0.001167315175097364</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -56191,6 +58759,12 @@
       <c r="AP428" s="3" t="n">
         <v>0.0008714054525084105</v>
       </c>
+      <c r="AQ428" s="1" t="n">
+        <v>0.008033999999999999</v>
+      </c>
+      <c r="AR428" s="2" t="n">
+        <v>-0.0007462686567165169</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -56321,6 +58895,12 @@
       <c r="AP429" s="2" t="n">
         <v>-0.001631321370310026</v>
       </c>
+      <c r="AQ429" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="AR429" s="2" t="n">
+        <v>-0.001633986928104509</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -56451,6 +59031,12 @@
       <c r="AP430" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ430" s="1" t="n">
+        <v>0.06659</v>
+      </c>
+      <c r="AR430" s="3" t="n">
+        <v>0.002106847253574135</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -56581,6 +59167,12 @@
       <c r="AP431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ431" s="1" t="n">
+        <v>0.00547</v>
+      </c>
+      <c r="AR431" s="3" t="n">
+        <v>0.003669724770642212</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -56711,6 +59303,12 @@
       <c r="AP432" s="2" t="n">
         <v>-0.001573976915005364</v>
       </c>
+      <c r="AQ432" s="1" t="n">
+        <v>0.009495</v>
+      </c>
+      <c r="AR432" s="2" t="n">
+        <v>-0.002101944298476005</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -56841,6 +59439,12 @@
       <c r="AP433" s="2" t="n">
         <v>-0.001952648279228624</v>
       </c>
+      <c r="AQ433" s="1" t="n">
+        <v>0.04105</v>
+      </c>
+      <c r="AR433" s="3" t="n">
+        <v>0.003912937148447063</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -56971,6 +59575,12 @@
       <c r="AP434" s="2" t="n">
         <v>-0.006976744186046389</v>
       </c>
+      <c r="AQ434" s="1" t="n">
+        <v>0.04285</v>
+      </c>
+      <c r="AR434" s="3" t="n">
+        <v>0.003512880562060828</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -57101,6 +59711,12 @@
       <c r="AP435" s="2" t="n">
         <v>-0.001293661060802101</v>
       </c>
+      <c r="AQ435" s="1" t="n">
+        <v>0.001546</v>
+      </c>
+      <c r="AR435" s="3" t="n">
+        <v>0.001295336787564798</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -57231,6 +59847,12 @@
       <c r="AP436" s="3" t="n">
         <v>0.001463057790782803</v>
       </c>
+      <c r="AQ436" s="1" t="n">
+        <v>0.02763</v>
+      </c>
+      <c r="AR436" s="3" t="n">
+        <v>0.009130752373995498</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -57361,6 +59983,12 @@
       <c r="AP437" s="3" t="n">
         <v>0.004011182691139065</v>
       </c>
+      <c r="AQ437" s="1" t="n">
+        <v>0.08251</v>
+      </c>
+      <c r="AR437" s="2" t="n">
+        <v>-0.001089588377724052</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -57491,6 +60119,12 @@
       <c r="AP438" s="2" t="n">
         <v>-0.001743679163033931</v>
       </c>
+      <c r="AQ438" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="AR438" s="3" t="n">
+        <v>0.0008733624454147509</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -57621,6 +60255,12 @@
       <c r="AP439" s="3" t="n">
         <v>0.0006455777921240232</v>
       </c>
+      <c r="AQ439" s="1" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="AR439" s="2" t="n">
+        <v>-0.001290322580645162</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -57751,6 +60391,12 @@
       <c r="AP440" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ440" s="1" t="n">
+        <v>0.001821</v>
+      </c>
+      <c r="AR440" s="3" t="n">
+        <v>0.003858875413450852</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -57881,6 +60527,12 @@
       <c r="AP441" s="2" t="n">
         <v>-0.001361285053090156</v>
       </c>
+      <c r="AQ441" s="1" t="n">
+        <v>0.03667</v>
+      </c>
+      <c r="AR441" s="2" t="n">
+        <v>-0.0002726281352234494</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -58011,6 +60663,12 @@
       <c r="AP442" s="3" t="n">
         <v>0.000549450549450527</v>
       </c>
+      <c r="AQ442" s="1" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="AR442" s="3" t="n">
+        <v>0.00274574409665008</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -58141,6 +60799,12 @@
       <c r="AP443" s="2" t="n">
         <v>-0.00149818640592963</v>
       </c>
+      <c r="AQ443" s="1" t="n">
+        <v>0.12682</v>
+      </c>
+      <c r="AR443" s="3" t="n">
+        <v>0.001500434336255198</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -58271,6 +60935,12 @@
       <c r="AP444" s="2" t="n">
         <v>-0.00477099236641217</v>
       </c>
+      <c r="AQ444" s="1" t="n">
+        <v>0.011431</v>
+      </c>
+      <c r="AR444" s="2" t="n">
+        <v>-0.003660768761439935</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -58401,6 +61071,12 @@
       <c r="AP445" s="2" t="n">
         <v>-0.00087108013937283</v>
       </c>
+      <c r="AQ445" s="1" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="AR445" s="3" t="n">
+        <v>0.001370033628098132</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -58531,6 +61207,12 @@
       <c r="AP446" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ446" s="1" t="n">
+        <v>0.0002135</v>
+      </c>
+      <c r="AR446" s="3" t="n">
+        <v>0.0004686035613870779</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -58661,6 +61343,12 @@
       <c r="AP447" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ447" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="AR447" s="3" t="n">
+        <v>0.003021148036253784</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -58791,6 +61479,12 @@
       <c r="AP448" s="2" t="n">
         <v>-0.004113162118780172</v>
       </c>
+      <c r="AQ448" s="1" t="n">
+        <v>0.10037</v>
+      </c>
+      <c r="AR448" s="3" t="n">
+        <v>0.01108089050065482</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -58921,6 +61615,12 @@
       <c r="AP449" s="2" t="n">
         <v>-0.002979737783075097</v>
       </c>
+      <c r="AQ449" s="1" t="n">
+        <v>0.001674</v>
+      </c>
+      <c r="AR449" s="3" t="n">
+        <v>0.0005977286312013843</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -59051,6 +61751,12 @@
       <c r="AP450" s="2" t="n">
         <v>-0.001447178002894391</v>
       </c>
+      <c r="AQ450" s="1" t="n">
+        <v>0.0002069</v>
+      </c>
+      <c r="AR450" s="2" t="n">
+        <v>-0.0004830917874396253</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -59181,6 +61887,12 @@
       <c r="AP451" s="2" t="n">
         <v>-0.005727376861397561</v>
       </c>
+      <c r="AQ451" s="1" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AR451" s="2" t="n">
+        <v>-0.001152073732718801</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -59311,6 +62023,12 @@
       <c r="AP452" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ452" s="1" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="AR452" s="3" t="n">
+        <v>0.002233804914370772</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -59441,6 +62159,12 @@
       <c r="AP453" s="3" t="n">
         <v>0.001731102135025852</v>
       </c>
+      <c r="AQ453" s="1" t="n">
+        <v>0.0001738</v>
+      </c>
+      <c r="AR453" s="3" t="n">
+        <v>0.001152073732718922</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -59571,6 +62295,12 @@
       <c r="AP454" s="3" t="n">
         <v>8.913450396645088e-05</v>
       </c>
+      <c r="AQ454" s="1" t="n">
+        <v>0.11371</v>
+      </c>
+      <c r="AR454" s="3" t="n">
+        <v>0.01345811051693415</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -59701,6 +62431,12 @@
       <c r="AP455" s="2" t="n">
         <v>-0.0004003202562049199</v>
       </c>
+      <c r="AQ455" s="1" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="AR455" s="3" t="n">
+        <v>0.002402883460152252</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -59831,6 +62567,12 @@
       <c r="AP456" s="2" t="n">
         <v>-6.258605582660725e-05</v>
       </c>
+      <c r="AQ456" s="1" t="n">
+        <v>0.015978</v>
+      </c>
+      <c r="AR456" s="3" t="n">
+        <v>6.258997308615701e-05</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -59961,6 +62703,12 @@
       <c r="AP457" s="2" t="n">
         <v>-0.0005991611743558513</v>
       </c>
+      <c r="AQ457" s="1" t="n">
+        <v>0.006696</v>
+      </c>
+      <c r="AR457" s="3" t="n">
+        <v>0.003597122302158231</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -60091,6 +62839,12 @@
       <c r="AP458" s="3" t="n">
         <v>0.0004158868787690445</v>
       </c>
+      <c r="AQ458" s="1" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="AR458" s="3" t="n">
+        <v>0.001039284971939191</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -60221,6 +62975,12 @@
       <c r="AP459" s="2" t="n">
         <v>-0.001260438002205797</v>
       </c>
+      <c r="AQ459" s="1" t="n">
+        <v>0.006349</v>
+      </c>
+      <c r="AR459" s="3" t="n">
+        <v>0.001577535888941409</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -60351,6 +63111,12 @@
       <c r="AP460" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ460" s="1" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="AR460" s="2" t="n">
+        <v>-0.0007315288953912874</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -60481,6 +63247,12 @@
       <c r="AP461" s="2" t="n">
         <v>-0.002996337809344051</v>
       </c>
+      <c r="AQ461" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="AR461" s="3" t="n">
+        <v>0.0006678539626000736</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -60611,6 +63383,12 @@
       <c r="AP462" s="2" t="n">
         <v>-0.000887902330743582</v>
       </c>
+      <c r="AQ462" s="1" t="n">
+        <v>0.04491</v>
+      </c>
+      <c r="AR462" s="2" t="n">
+        <v>-0.00222172850477678</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -60741,6 +63519,12 @@
       <c r="AP463" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="AR463" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -60871,6 +63655,12 @@
       <c r="AP464" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ464" s="1" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="AR464" s="3" t="n">
+        <v>0.0007710100231303871</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -61001,6 +63791,12 @@
       <c r="AP465" s="3" t="n">
         <v>0.0003614022406938525</v>
       </c>
+      <c r="AQ465" s="1" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AR465" s="3" t="n">
+        <v>0.000722543352601277</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -61131,6 +63927,12 @@
       <c r="AP466" s="2" t="n">
         <v>-0.0007072135785006294</v>
       </c>
+      <c r="AQ466" s="1" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="AR466" s="3" t="n">
+        <v>0.002123142250530709</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -61261,6 +64063,12 @@
       <c r="AP467" s="2" t="n">
         <v>-0.00157150340492398</v>
       </c>
+      <c r="AQ467" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="AR467" s="3" t="n">
+        <v>0.001573976915005182</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -61391,6 +64199,12 @@
       <c r="AP468" s="2" t="n">
         <v>-0.00498007968127487</v>
       </c>
+      <c r="AQ468" s="1" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="AR468" s="3" t="n">
+        <v>0.004004004004004014</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -61521,6 +64335,12 @@
       <c r="AP469" s="2" t="n">
         <v>-0.002026855839878447</v>
       </c>
+      <c r="AQ469" s="1" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="AR469" s="3" t="n">
+        <v>0.001269357705001271</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -61651,6 +64471,12 @@
       <c r="AP470" s="2" t="n">
         <v>-0.002283105022831052</v>
       </c>
+      <c r="AQ470" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="AR470" s="3" t="n">
+        <v>0.003432494279176205</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -61781,6 +64607,12 @@
       <c r="AP471" s="2" t="n">
         <v>-0.00404606286959225</v>
       </c>
+      <c r="AQ471" s="1" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="AR471" s="3" t="n">
+        <v>0.002187499999999898</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -61911,6 +64743,12 @@
       <c r="AP472" s="2" t="n">
         <v>-0.001192179303767321</v>
       </c>
+      <c r="AQ472" s="1" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="AR472" s="3" t="n">
+        <v>0.00716161375029844</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -62041,6 +64879,12 @@
       <c r="AP473" s="2" t="n">
         <v>-0.001601281024819857</v>
       </c>
+      <c r="AQ473" s="1" t="n">
+        <v>1.253</v>
+      </c>
+      <c r="AR473" s="3" t="n">
+        <v>0.004811547714514661</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -62171,6 +65015,12 @@
       <c r="AP474" s="2" t="n">
         <v>-0.0002345490793948945</v>
       </c>
+      <c r="AQ474" s="1" t="n">
+        <v>0.008554000000000001</v>
+      </c>
+      <c r="AR474" s="3" t="n">
+        <v>0.003401759530791935</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -62301,6 +65151,12 @@
       <c r="AP475" s="3" t="n">
         <v>0.002147458840372222</v>
       </c>
+      <c r="AQ475" s="1" t="n">
+        <v>0.04236</v>
+      </c>
+      <c r="AR475" s="3" t="n">
+        <v>0.008571428571428553</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -62431,6 +65287,12 @@
       <c r="AP476" s="2" t="n">
         <v>-0.002421307506053214</v>
       </c>
+      <c r="AQ476" s="1" t="n">
+        <v>0.07858</v>
+      </c>
+      <c r="AR476" s="3" t="n">
+        <v>0.00383239652529375</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -62561,6 +65423,12 @@
       <c r="AP477" s="3" t="n">
         <v>0.001687206572770012</v>
       </c>
+      <c r="AQ477" s="1" t="n">
+        <v>0.13624</v>
+      </c>
+      <c r="AR477" s="2" t="n">
+        <v>-0.002270230684730902</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -62691,6 +65559,12 @@
       <c r="AP478" s="2" t="n">
         <v>-0.002541296060991002</v>
       </c>
+      <c r="AQ478" s="1" t="n">
+        <v>0.04716</v>
+      </c>
+      <c r="AR478" s="3" t="n">
+        <v>0.001273885350318419</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -62821,6 +65695,12 @@
       <c r="AP479" s="3" t="n">
         <v>0.0003765769158351093</v>
       </c>
+      <c r="AQ479" s="1" t="n">
+        <v>0.005323</v>
+      </c>
+      <c r="AR479" s="3" t="n">
+        <v>0.001882175795219197</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -62951,6 +65831,12 @@
       <c r="AP480" s="2" t="n">
         <v>-0.0007147962830592494</v>
       </c>
+      <c r="AQ480" s="1" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AR480" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -63081,6 +65967,12 @@
       <c r="AP481" s="2" t="n">
         <v>-0.0006605019815060551</v>
       </c>
+      <c r="AQ481" s="1" t="n">
+        <v>0.07571</v>
+      </c>
+      <c r="AR481" s="3" t="n">
+        <v>0.0007931262392598083</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -63211,6 +66103,12 @@
       <c r="AP482" s="2" t="n">
         <v>-0.0006720430107527773</v>
       </c>
+      <c r="AQ482" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="AR482" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -63341,6 +66239,12 @@
       <c r="AP483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ483" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="AR483" s="2" t="n">
+        <v>-0.004000000000000115</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -63471,6 +66375,12 @@
       <c r="AP484" s="2" t="n">
         <v>-0.0009306654257793944</v>
       </c>
+      <c r="AQ484" s="1" t="n">
+        <v>0.02158</v>
+      </c>
+      <c r="AR484" s="3" t="n">
+        <v>0.005123428039124312</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -63601,6 +66511,12 @@
       <c r="AP485" s="2" t="n">
         <v>-0.004650608156451122</v>
       </c>
+      <c r="AQ485" s="1" t="n">
+        <v>0.008366999999999999</v>
+      </c>
+      <c r="AR485" s="3" t="n">
+        <v>0.00239607044447097</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -63731,6 +66647,12 @@
       <c r="AP486" s="2" t="n">
         <v>-0.001469213303058598</v>
       </c>
+      <c r="AQ486" s="1" t="n">
+        <v>0.007472</v>
+      </c>
+      <c r="AR486" s="2" t="n">
+        <v>-0.0005350454788656585</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -63861,6 +66783,12 @@
       <c r="AP487" s="3" t="n">
         <v>0.00179051029543425</v>
       </c>
+      <c r="AQ487" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="AR487" s="3" t="n">
+        <v>0.0008936550491510533</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -63991,6 +66919,12 @@
       <c r="AP488" s="3" t="n">
         <v>0.004411922952760262</v>
       </c>
+      <c r="AQ488" s="1" t="n">
+        <v>0.009316</v>
+      </c>
+      <c r="AR488" s="2" t="n">
+        <v>-0.001928433683308405</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -64121,6 +67055,12 @@
       <c r="AP489" s="3" t="n">
         <v>0.0005151983513652546</v>
       </c>
+      <c r="AQ489" s="1" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="AR489" s="3" t="n">
+        <v>0.007981462409886658</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -64251,6 +67191,12 @@
       <c r="AP490" s="3" t="n">
         <v>0.001216545012165461</v>
       </c>
+      <c r="AQ490" s="1" t="n">
+        <v>0.05777</v>
+      </c>
+      <c r="AR490" s="3" t="n">
+        <v>0.002777295608401326</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -64381,6 +67327,12 @@
       <c r="AP491" s="2" t="n">
         <v>-0.002055498458376073</v>
       </c>
+      <c r="AQ491" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="AR491" s="3" t="n">
+        <v>0.002059732234809391</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -64511,6 +67463,12 @@
       <c r="AP492" s="3" t="n">
         <v>0.0007593014426728261</v>
       </c>
+      <c r="AQ492" s="1" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="AR492" s="3" t="n">
+        <v>0.0007587253414263201</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -64641,6 +67599,12 @@
       <c r="AP493" s="2" t="n">
         <v>-0.001710376282782142</v>
       </c>
+      <c r="AQ493" s="1" t="n">
+        <v>0.03503</v>
+      </c>
+      <c r="AR493" s="3" t="n">
+        <v>0.0002855511136492325</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -64771,6 +67735,12 @@
       <c r="AP494" s="3" t="n">
         <v>0.0005931198102016366</v>
       </c>
+      <c r="AQ494" s="1" t="n">
+        <v>0.01688</v>
+      </c>
+      <c r="AR494" s="3" t="n">
+        <v>0.0005927682276229753</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -64901,6 +67871,12 @@
       <c r="AP495" s="2" t="n">
         <v>-0.0004267121826327968</v>
       </c>
+      <c r="AQ495" s="1" t="n">
+        <v>0.04684</v>
+      </c>
+      <c r="AR495" s="2" t="n">
+        <v>-0.0002134471718250387</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -65031,6 +68007,12 @@
       <c r="AP496" s="2" t="n">
         <v>-0.001453790238836981</v>
       </c>
+      <c r="AQ496" s="1" t="n">
+        <v>0.04811</v>
+      </c>
+      <c r="AR496" s="3" t="n">
+        <v>0.0006239600665557871</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -65161,6 +68143,12 @@
       <c r="AP497" s="2" t="n">
         <v>-0.0008080808080809153</v>
       </c>
+      <c r="AQ497" s="1" t="n">
+        <v>0.04974</v>
+      </c>
+      <c r="AR497" s="3" t="n">
+        <v>0.005661140315406439</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -65291,6 +68279,12 @@
       <c r="AP498" s="2" t="n">
         <v>-0.0006887052341597037</v>
       </c>
+      <c r="AQ498" s="1" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AR498" s="3" t="n">
+        <v>0.0003445899379737732</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -65421,6 +68415,12 @@
       <c r="AP499" s="3" t="n">
         <v>0.002209131075110417</v>
       </c>
+      <c r="AQ499" s="1" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="AR499" s="3" t="n">
+        <v>0.0003673769287288354</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -65551,6 +68551,12 @@
       <c r="AP500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AR500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -65681,6 +68687,12 @@
       <c r="AP501" s="3" t="n">
         <v>0.001408054069276301</v>
       </c>
+      <c r="AQ501" s="1" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="AR501" s="2" t="n">
+        <v>-0.003093363329583773</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -65811,6 +68823,12 @@
       <c r="AP502" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ502" s="1" t="n">
+        <v>0.03185</v>
+      </c>
+      <c r="AR502" s="2" t="n">
+        <v>-0.003441802252815988</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -65941,6 +68959,12 @@
       <c r="AP503" s="2" t="n">
         <v>-0.0002596391016486301</v>
       </c>
+      <c r="AQ503" s="1" t="n">
+        <v>0.007716</v>
+      </c>
+      <c r="AR503" s="3" t="n">
+        <v>0.001947798987144447</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -66071,6 +69095,12 @@
       <c r="AP504" s="2" t="n">
         <v>-0.0009956853634251954</v>
       </c>
+      <c r="AQ504" s="1" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="AR504" s="3" t="n">
+        <v>0.0009966777408638252</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -66201,6 +69231,12 @@
       <c r="AP505" s="2" t="n">
         <v>-0.0004043126684636947</v>
       </c>
+      <c r="AQ505" s="1" t="n">
+        <v>0.0007404999999999999</v>
+      </c>
+      <c r="AR505" s="2" t="n">
+        <v>-0.001617904813266859</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -66331,6 +69367,12 @@
       <c r="AP506" s="3" t="n">
         <v>0.001721170395869193</v>
       </c>
+      <c r="AQ506" s="1" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AR506" s="3" t="n">
+        <v>0.001374570446735435</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -66461,6 +69503,12 @@
       <c r="AP507" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ507" s="1" t="n">
+        <v>0.002846</v>
+      </c>
+      <c r="AR507" s="3" t="n">
+        <v>0.0003514938488576916</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -66591,6 +69639,12 @@
       <c r="AP508" s="3" t="n">
         <v>0.0009490667510282267</v>
       </c>
+      <c r="AQ508" s="1" t="n">
+        <v>0.06319</v>
+      </c>
+      <c r="AR508" s="2" t="n">
+        <v>-0.001422250316055732</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -66721,6 +69775,12 @@
       <c r="AP509" s="3" t="n">
         <v>0.001808318264014468</v>
       </c>
+      <c r="AQ509" s="1" t="n">
+        <v>2.224</v>
+      </c>
+      <c r="AR509" s="3" t="n">
+        <v>0.0036101083032491</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -66851,6 +69911,12 @@
       <c r="AP510" s="2" t="n">
         <v>-0.001368738023542327</v>
       </c>
+      <c r="AQ510" s="1" t="n">
+        <v>0.0007299</v>
+      </c>
+      <c r="AR510" s="3" t="n">
+        <v>0.0004111842105264001</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -66981,6 +70047,12 @@
       <c r="AP511" s="2" t="n">
         <v>-0.000729128691213919</v>
       </c>
+      <c r="AQ511" s="1" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="AR511" s="3" t="n">
+        <v>0.0007296607077708062</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -67111,6 +70183,12 @@
       <c r="AP512" s="3" t="n">
         <v>0.0006233118637024877</v>
       </c>
+      <c r="AQ512" s="1" t="n">
+        <v>0.0004812</v>
+      </c>
+      <c r="AR512" s="2" t="n">
+        <v>-0.0008305647840531763</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -67241,6 +70319,12 @@
       <c r="AP513" s="2" t="n">
         <v>-0.0001820498816676327</v>
       </c>
+      <c r="AQ513" s="1" t="n">
+        <v>0.05506</v>
+      </c>
+      <c r="AR513" s="3" t="n">
+        <v>0.002549162418062659</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -67371,6 +70455,12 @@
       <c r="AP514" s="2" t="n">
         <v>-0.001326259946949548</v>
       </c>
+      <c r="AQ514" s="1" t="n">
+        <v>0.03014</v>
+      </c>
+      <c r="AR514" s="3" t="n">
+        <v>0.0006640106241699597</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -67501,6 +70591,12 @@
       <c r="AP515" s="2" t="n">
         <v>-0.0008787346221440386</v>
       </c>
+      <c r="AQ515" s="1" t="n">
+        <v>0.001139</v>
+      </c>
+      <c r="AR515" s="3" t="n">
+        <v>0.001759014951627132</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -67631,6 +70727,12 @@
       <c r="AP516" s="3" t="n">
         <v>0.0004562043795619724</v>
       </c>
+      <c r="AQ516" s="1" t="n">
+        <v>0.006576</v>
+      </c>
+      <c r="AR516" s="2" t="n">
+        <v>-0.0004559963520291125</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -67761,6 +70863,12 @@
       <c r="AP517" s="3" t="n">
         <v>0.0007522567703109891</v>
       </c>
+      <c r="AQ517" s="1" t="n">
+        <v>0.03991</v>
+      </c>
+      <c r="AR517" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -67891,6 +70999,12 @@
       <c r="AP518" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ518" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="AR518" s="3" t="n">
+        <v>0.001937984496124086</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -68021,6 +71135,12 @@
       <c r="AP519" s="2" t="n">
         <v>-0.001150747986190977</v>
       </c>
+      <c r="AQ519" s="1" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="AR519" s="2" t="n">
+        <v>-0.001152073732718847</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -68151,6 +71271,12 @@
       <c r="AP520" s="3" t="n">
         <v>0.0006253908692934131</v>
       </c>
+      <c r="AQ520" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="AR520" s="3" t="n">
+        <v>0.002499999999999898</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -68281,6 +71407,12 @@
       <c r="AP521" s="2" t="n">
         <v>-0.001122334455667743</v>
       </c>
+      <c r="AQ521" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="AR521" s="3" t="n">
+        <v>0.002808988764045024</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -68411,6 +71543,12 @@
       <c r="AP522" s="2" t="n">
         <v>-0.0006116207951070088</v>
       </c>
+      <c r="AQ522" s="1" t="n">
+        <v>0.01637</v>
+      </c>
+      <c r="AR522" s="3" t="n">
+        <v>0.001835985312117428</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -68541,6 +71679,12 @@
       <c r="AP523" s="3" t="n">
         <v>0.002427184466019318</v>
       </c>
+      <c r="AQ523" s="1" t="n">
+        <v>0.004132</v>
+      </c>
+      <c r="AR523" s="3" t="n">
+        <v>0.000484261501210718</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -68671,6 +71815,12 @@
       <c r="AP524" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ524" s="1" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="AR524" s="3" t="n">
+        <v>0.0007037297677691479</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -68801,6 +71951,12 @@
       <c r="AP525" s="3" t="n">
         <v>0.001216051884880372</v>
       </c>
+      <c r="AQ525" s="1" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="AR525" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -68931,6 +72087,12 @@
       <c r="AP526" s="2" t="n">
         <v>-0.0008368200836819163</v>
       </c>
+      <c r="AQ526" s="1" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="AR526" s="3" t="n">
+        <v>0.0008375209380233583</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -69061,6 +72223,12 @@
       <c r="AP527" s="3" t="n">
         <v>0.001823537663066226</v>
       </c>
+      <c r="AQ527" s="1" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="AR527" s="3" t="n">
+        <v>0.01092131055726691</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -69191,6 +72359,12 @@
       <c r="AP528" s="2" t="n">
         <v>-0.001161440185830463</v>
       </c>
+      <c r="AQ528" s="1" t="n">
+        <v>0.04303</v>
+      </c>
+      <c r="AR528" s="3" t="n">
+        <v>0.0006976744186047034</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -69321,6 +72495,12 @@
       <c r="AP529" s="2" t="n">
         <v>-0.001270244522070447</v>
       </c>
+      <c r="AQ529" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="AR529" s="3" t="n">
+        <v>0.004769475357710789</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -69451,6 +72631,12 @@
       <c r="AP530" s="3" t="n">
         <v>0.003998400639744113</v>
       </c>
+      <c r="AQ530" s="1" t="n">
+        <v>0.005022</v>
+      </c>
+      <c r="AR530" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -69581,6 +72767,12 @@
       <c r="AP531" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ531" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="AR531" s="3" t="n">
+        <v>0.003088803088802963</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -69711,6 +72903,12 @@
       <c r="AP532" s="2" t="n">
         <v>-0.001310615989515084</v>
       </c>
+      <c r="AQ532" s="1" t="n">
+        <v>0.05339</v>
+      </c>
+      <c r="AR532" s="3" t="n">
+        <v>0.0009373828271466336</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -69841,6 +73039,12 @@
       <c r="AP533" s="3" t="n">
         <v>0.001610305958132026</v>
       </c>
+      <c r="AQ533" s="1" t="n">
+        <v>0.003749</v>
+      </c>
+      <c r="AR533" s="3" t="n">
+        <v>0.004555198285101846</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -69971,6 +73175,12 @@
       <c r="AP534" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AQ534" s="1" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="AR534" s="3" t="n">
+        <v>0.00117164616285885</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -70101,6 +73311,12 @@
       <c r="AP535" s="2" t="n">
         <v>-0.00884955752212396</v>
       </c>
+      <c r="AQ535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AR535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -70231,6 +73447,12 @@
       <c r="AP536" s="3" t="n">
         <v>0.0002275830678197597</v>
       </c>
+      <c r="AQ536" s="1" t="n">
+        <v>0.0004418</v>
+      </c>
+      <c r="AR536" s="3" t="n">
+        <v>0.005233219567690561</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -70361,6 +73583,12 @@
       <c r="AP537" s="2" t="n">
         <v>-0.002085505735140687</v>
       </c>
+      <c r="AQ537" s="1" t="n">
+        <v>0.00958</v>
+      </c>
+      <c r="AR537" s="3" t="n">
+        <v>0.001044932079414795</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -70491,6 +73719,12 @@
       <c r="AP538" s="2" t="n">
         <v>-0.0007340796476417393</v>
       </c>
+      <c r="AQ538" s="1" t="n">
+        <v>0.05451</v>
+      </c>
+      <c r="AR538" s="3" t="n">
+        <v>0.00110192837465573</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -70621,6 +73855,12 @@
       <c r="AP539" s="3" t="n">
         <v>0.001616458486407039</v>
       </c>
+      <c r="AQ539" s="1" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="AR539" s="2" t="n">
+        <v>-0.001907276995305117</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -70751,6 +73991,12 @@
       <c r="AP540" s="2" t="n">
         <v>-0.000663570006635627</v>
       </c>
+      <c r="AQ540" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AR540" s="3" t="n">
+        <v>0.002656042496679838</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -70881,6 +74127,12 @@
       <c r="AP541" s="2" t="n">
         <v>-0.0007704160246532814</v>
       </c>
+      <c r="AQ541" s="1" t="n">
+        <v>0.01297</v>
+      </c>
+      <c r="AR541" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -71011,6 +74263,12 @@
       <c r="AP542" s="3" t="n">
         <v>0.002158273381295001</v>
       </c>
+      <c r="AQ542" s="1" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="AR542" s="2" t="n">
+        <v>-0.00358937544867191</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -71141,6 +74399,12 @@
       <c r="AP543" s="2" t="n">
         <v>-0.0007027406886858463</v>
       </c>
+      <c r="AQ543" s="1" t="n">
+        <v>0.05698</v>
+      </c>
+      <c r="AR543" s="3" t="n">
+        <v>0.001758087201125226</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR543"/>
+  <dimension ref="A1:AT543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,8 @@
     <col width="18" customWidth="1" min="42" max="42"/>
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -693,6 +695,16 @@
           <t>change_05:15</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>price_05:30</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>change_05:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -829,6 +841,12 @@
       <c r="AR2" s="3" t="n">
         <v>0.003244114249860966</v>
       </c>
+      <c r="AS2" s="1" t="n">
+        <v>70252.7</v>
+      </c>
+      <c r="AT2" s="2" t="n">
+        <v>-0.00144695790603306</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -965,6 +983,12 @@
       <c r="AR3" s="3" t="n">
         <v>0.001819116733933561</v>
       </c>
+      <c r="AS3" s="1" t="n">
+        <v>2060.29</v>
+      </c>
+      <c r="AT3" s="2" t="n">
+        <v>-0.002372663047952048</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1101,6 +1125,12 @@
       <c r="AR4" s="3" t="n">
         <v>0.001273000810091418</v>
       </c>
+      <c r="AS4" s="1" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="AT4" s="2" t="n">
+        <v>-0.002427184466019345</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1237,6 +1267,12 @@
       <c r="AR5" s="3" t="n">
         <v>0.008905971688384863</v>
       </c>
+      <c r="AS5" s="1" t="n">
+        <v>0.01082</v>
+      </c>
+      <c r="AT5" s="3" t="n">
+        <v>0.005389332837762406</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1373,6 +1409,12 @@
       <c r="AR6" s="3" t="n">
         <v>0.001969221792721118</v>
       </c>
+      <c r="AS6" s="1" t="n">
+        <v>1.3723</v>
+      </c>
+      <c r="AT6" s="2" t="n">
+        <v>-0.001091861988644515</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1509,6 +1551,12 @@
       <c r="AR7" s="3" t="n">
         <v>0.002551291591368174</v>
       </c>
+      <c r="AS7" s="1" t="n">
+        <v>0.09417</v>
+      </c>
+      <c r="AT7" s="2" t="n">
+        <v>-0.001484466122362435</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1645,6 +1693,12 @@
       <c r="AR8" s="3" t="n">
         <v>0.005882511670579442</v>
       </c>
+      <c r="AS8" s="1" t="n">
+        <v>37.266</v>
+      </c>
+      <c r="AT8" s="2" t="n">
+        <v>-0.0002950881240443916</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1781,6 +1835,12 @@
       <c r="AR9" s="3" t="n">
         <v>0.003278016799836108</v>
       </c>
+      <c r="AS9" s="1" t="n">
+        <v>0.04907</v>
+      </c>
+      <c r="AT9" s="3" t="n">
+        <v>0.002042066571370285</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1917,6 +1977,12 @@
       <c r="AR10" s="3" t="n">
         <v>0.006448439805453965</v>
       </c>
+      <c r="AS10" s="1" t="n">
+        <v>18.492</v>
+      </c>
+      <c r="AT10" s="3" t="n">
+        <v>0.004072324482814752</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2053,6 +2119,12 @@
       <c r="AR11" s="3" t="n">
         <v>0.002292801526482641</v>
       </c>
+      <c r="AS11" s="1" t="n">
+        <v>650.8099999999999</v>
+      </c>
+      <c r="AT11" s="2" t="n">
+        <v>-0.0008290473631689219</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2189,6 +2261,12 @@
       <c r="AR12" s="2" t="n">
         <v>-0.02482789752849568</v>
       </c>
+      <c r="AS12" s="1" t="n">
+        <v>0.8557</v>
+      </c>
+      <c r="AT12" s="2" t="n">
+        <v>-0.009721097095243563</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2325,6 +2403,12 @@
       <c r="AR13" s="3" t="n">
         <v>0.00405014464802316</v>
       </c>
+      <c r="AS13" s="1" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="AT13" s="2" t="n">
+        <v>-0.0001920860545525378</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2461,6 +2545,12 @@
       <c r="AR14" s="3" t="n">
         <v>0.003590285110876457</v>
       </c>
+      <c r="AS14" s="1" t="n">
+        <v>0.0033351</v>
+      </c>
+      <c r="AT14" s="3" t="n">
+        <v>0.002615440115440097</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2597,6 +2687,12 @@
       <c r="AR15" s="2" t="n">
         <v>-0.05989088457058788</v>
       </c>
+      <c r="AS15" s="1" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>0.01026995305164315</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2733,6 +2829,12 @@
       <c r="AR16" s="3" t="n">
         <v>0.003806976026340196</v>
       </c>
+      <c r="AS16" s="1" t="n">
+        <v>0.9737</v>
+      </c>
+      <c r="AT16" s="2" t="n">
+        <v>-0.001947519475194765</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2869,6 +2971,12 @@
       <c r="AR17" s="3" t="n">
         <v>0.0156249999999999</v>
       </c>
+      <c r="AS17" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>0.007692307692307779</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3005,6 +3113,12 @@
       <c r="AR18" s="3" t="n">
         <v>0.00103690436913795</v>
       </c>
+      <c r="AS18" s="1" t="n">
+        <v>213.11</v>
+      </c>
+      <c r="AT18" s="3" t="n">
+        <v>0.003389990112528967</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3141,6 +3255,12 @@
       <c r="AR19" s="3" t="n">
         <v>0.002674818494459434</v>
       </c>
+      <c r="AS19" s="1" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="AT19" s="2" t="n">
+        <v>-0.001143292682926915</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3277,6 +3397,12 @@
       <c r="AR20" s="3" t="n">
         <v>0.000533712862480108</v>
       </c>
+      <c r="AS20" s="1" t="n">
+        <v>0.016976</v>
+      </c>
+      <c r="AT20" s="3" t="n">
+        <v>0.006164058795637738</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3413,6 +3539,12 @@
       <c r="AR21" s="3" t="n">
         <v>0.004269054560599789</v>
       </c>
+      <c r="AS21" s="1" t="n">
+        <v>9.621</v>
+      </c>
+      <c r="AT21" s="2" t="n">
+        <v>-0.002488335925349832</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3549,6 +3681,12 @@
       <c r="AR22" s="3" t="n">
         <v>0.0006049606775558922</v>
       </c>
+      <c r="AS22" s="1" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="AT22" s="2" t="n">
+        <v>-0.001813784764207949</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3685,6 +3823,12 @@
       <c r="AR23" s="2" t="n">
         <v>-0.004952053814226447</v>
       </c>
+      <c r="AS23" s="1" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AT23" s="3" t="n">
+        <v>0.002128761291065009</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3821,6 +3965,12 @@
       <c r="AR24" s="3" t="n">
         <v>0.001157407407407408</v>
       </c>
+      <c r="AS24" s="1" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="AT24" s="2" t="n">
+        <v>-0.004624277456647403</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3957,6 +4107,12 @@
       <c r="AR25" s="3" t="n">
         <v>0.004460800713728019</v>
       </c>
+      <c r="AS25" s="1" t="n">
+        <v>8.997999999999999</v>
+      </c>
+      <c r="AT25" s="2" t="n">
+        <v>-0.0009992228266903899</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4093,6 +4249,12 @@
       <c r="AR26" s="3" t="n">
         <v>0.006001500375093779</v>
       </c>
+      <c r="AS26" s="1" t="n">
+        <v>1.347</v>
+      </c>
+      <c r="AT26" s="3" t="n">
+        <v>0.004474272930648774</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4229,6 +4391,12 @@
       <c r="AR27" s="3" t="n">
         <v>0.001009979937947211</v>
       </c>
+      <c r="AS27" s="1" t="n">
+        <v>5096.65</v>
+      </c>
+      <c r="AT27" s="3" t="n">
+        <v>0.0004514805617987127</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4365,6 +4533,12 @@
       <c r="AR28" s="3" t="n">
         <v>0.001682085786375075</v>
       </c>
+      <c r="AS28" s="1" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AT28" s="2" t="n">
+        <v>-0.0008396305625525398</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4501,6 +4675,12 @@
       <c r="AR29" s="3" t="n">
         <v>0.0003786444528587239</v>
       </c>
+      <c r="AS29" s="1" t="n">
+        <v>2.648</v>
+      </c>
+      <c r="AT29" s="3" t="n">
+        <v>0.002271006813020525</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4637,6 +4817,12 @@
       <c r="AR30" s="3" t="n">
         <v>0.009651939935769481</v>
       </c>
+      <c r="AS30" s="1" t="n">
+        <v>0.57979</v>
+      </c>
+      <c r="AT30" s="2" t="n">
+        <v>-0.003129244682862972</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4773,6 +4959,12 @@
       <c r="AR31" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS31" s="1" t="n">
+        <v>0.002077</v>
+      </c>
+      <c r="AT31" s="3" t="n">
+        <v>0.0004816955684006257</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4909,6 +5101,12 @@
       <c r="AR32" s="3" t="n">
         <v>0.00403852127990049</v>
       </c>
+      <c r="AS32" s="1" t="n">
+        <v>1.2973</v>
+      </c>
+      <c r="AT32" s="3" t="n">
+        <v>0.003480816831683128</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5045,6 +5243,12 @@
       <c r="AR33" s="3" t="n">
         <v>0.006308200660859256</v>
       </c>
+      <c r="AS33" s="1" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AT33" s="3" t="n">
+        <v>0.0152238805970149</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5181,6 +5385,12 @@
       <c r="AR34" s="3" t="n">
         <v>0.0006635700066357743</v>
       </c>
+      <c r="AS34" s="1" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="AT34" s="2" t="n">
+        <v>-0.0006631299734748753</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5317,6 +5527,12 @@
       <c r="AR35" s="3" t="n">
         <v>0.001564531411824287</v>
       </c>
+      <c r="AS35" s="1" t="n">
+        <v>454.25</v>
+      </c>
+      <c r="AT35" s="2" t="n">
+        <v>-0.0005940332658628483</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5453,6 +5669,12 @@
       <c r="AR36" s="3" t="n">
         <v>0.005497991118629801</v>
       </c>
+      <c r="AS36" s="1" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="AT36" s="3" t="n">
+        <v>0.001261829652996794</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5589,6 +5811,12 @@
       <c r="AR37" s="3" t="n">
         <v>0.002711574140145587</v>
       </c>
+      <c r="AS37" s="1" t="n">
+        <v>0.7020999999999999</v>
+      </c>
+      <c r="AT37" s="2" t="n">
+        <v>-0.0007116424708227383</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5725,6 +5953,12 @@
       <c r="AR38" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS38" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="AT38" s="3" t="n">
+        <v>0.001901140684410569</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5861,6 +6095,12 @@
       <c r="AR39" s="3" t="n">
         <v>0.0007238508867173208</v>
       </c>
+      <c r="AS39" s="1" t="n">
+        <v>110.71</v>
+      </c>
+      <c r="AT39" s="3" t="n">
+        <v>0.0009945750452079515</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5997,6 +6237,12 @@
       <c r="AR40" s="3" t="n">
         <v>0.00616073928871459</v>
       </c>
+      <c r="AS40" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="AT40" s="2" t="n">
+        <v>-0.009184525466184163</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6133,6 +6379,12 @@
       <c r="AR41" s="3" t="n">
         <v>0.00110619469026557</v>
       </c>
+      <c r="AS41" s="1" t="n">
+        <v>0.05439</v>
+      </c>
+      <c r="AT41" s="3" t="n">
+        <v>0.001657458563535908</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6269,6 +6521,12 @@
       <c r="AR42" s="3" t="n">
         <v>0.00351006835396264</v>
       </c>
+      <c r="AS42" s="1" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AT42" s="3" t="n">
+        <v>0.0001840942562591681</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6405,6 +6663,12 @@
       <c r="AR43" s="2" t="n">
         <v>-0.003793626707132021</v>
       </c>
+      <c r="AS43" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="AT43" s="3" t="n">
+        <v>0.004569687738004489</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6541,6 +6805,12 @@
       <c r="AR44" s="3" t="n">
         <v>0.002389078498293536</v>
       </c>
+      <c r="AS44" s="1" t="n">
+        <v>0.005877</v>
+      </c>
+      <c r="AT44" s="3" t="n">
+        <v>0.0005107252298264212</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6677,6 +6947,12 @@
       <c r="AR45" s="2" t="n">
         <v>-0.002926041771768727</v>
       </c>
+      <c r="AS45" s="1" t="n">
+        <v>0.09865</v>
+      </c>
+      <c r="AT45" s="2" t="n">
+        <v>-0.00172029953450722</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6813,6 +7089,12 @@
       <c r="AR46" s="3" t="n">
         <v>0.00721153846153843</v>
       </c>
+      <c r="AS46" s="1" t="n">
+        <v>2.902</v>
+      </c>
+      <c r="AT46" s="2" t="n">
+        <v>-0.01056938288441858</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6949,6 +7231,12 @@
       <c r="AR47" s="3" t="n">
         <v>0.0004503412200783559</v>
       </c>
+      <c r="AS47" s="1" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AT47" s="3" t="n">
+        <v>0.0004501385041551904</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7085,6 +7373,12 @@
       <c r="AR48" s="3" t="n">
         <v>0.002830188679245364</v>
       </c>
+      <c r="AS48" s="1" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="AT48" s="3" t="n">
+        <v>0.004703668861712139</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7221,6 +7515,12 @@
       <c r="AR49" s="2" t="n">
         <v>-0.001360936984493554</v>
       </c>
+      <c r="AS49" s="1" t="n">
+        <v>0.24171</v>
+      </c>
+      <c r="AT49" s="2" t="n">
+        <v>-0.001817055544084229</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7357,6 +7657,12 @@
       <c r="AR50" s="3" t="n">
         <v>0.006948702227672185</v>
       </c>
+      <c r="AS50" s="1" t="n">
+        <v>0.04891</v>
+      </c>
+      <c r="AT50" s="2" t="n">
+        <v>-0.007306677491374045</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7493,6 +7799,12 @@
       <c r="AR51" s="3" t="n">
         <v>0.001800411522633775</v>
       </c>
+      <c r="AS51" s="1" t="n">
+        <v>3.887</v>
+      </c>
+      <c r="AT51" s="2" t="n">
+        <v>-0.002053915275994867</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7629,6 +7941,12 @@
       <c r="AR52" s="3" t="n">
         <v>0.03070175438596482</v>
       </c>
+      <c r="AS52" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="AT52" s="2" t="n">
+        <v>-0.01702127659574463</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7765,6 +8083,12 @@
       <c r="AR53" s="3" t="n">
         <v>0.001191185229303191</v>
       </c>
+      <c r="AS53" s="1" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="AT53" s="3" t="n">
+        <v>0.002379535990481924</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7901,6 +8225,12 @@
       <c r="AR54" s="2" t="n">
         <v>-0.006517016654598103</v>
       </c>
+      <c r="AS54" s="1" t="n">
+        <v>0.04136</v>
+      </c>
+      <c r="AT54" s="3" t="n">
+        <v>0.004859086491739524</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8037,6 +8367,12 @@
       <c r="AR55" s="2" t="n">
         <v>-0.004181072605933848</v>
       </c>
+      <c r="AS55" s="1" t="n">
+        <v>0.12315</v>
+      </c>
+      <c r="AT55" s="2" t="n">
+        <v>-0.005651998385143369</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8173,6 +8509,12 @@
       <c r="AR56" s="3" t="n">
         <v>0.003827751196172181</v>
       </c>
+      <c r="AS56" s="1" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AT56" s="3" t="n">
+        <v>0.00603749602796318</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8309,6 +8651,12 @@
       <c r="AR57" s="3" t="n">
         <v>0.008748906386701762</v>
       </c>
+      <c r="AS57" s="1" t="n">
+        <v>0.01156</v>
+      </c>
+      <c r="AT57" s="3" t="n">
+        <v>0.002601908065915049</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8445,6 +8793,12 @@
       <c r="AR58" s="3" t="n">
         <v>0.004024144869215267</v>
       </c>
+      <c r="AS58" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT58" s="3" t="n">
+        <v>0.002004008016032122</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8581,6 +8935,12 @@
       <c r="AR59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS59" s="1" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="AT59" s="3" t="n">
+        <v>0.006024096385542185</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8717,6 +9077,12 @@
       <c r="AR60" s="3" t="n">
         <v>0.004530744336569619</v>
       </c>
+      <c r="AS60" s="1" t="n">
+        <v>0.1551</v>
+      </c>
+      <c r="AT60" s="2" t="n">
+        <v>-0.0006443298969073244</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8853,6 +9219,12 @@
       <c r="AR61" s="3" t="n">
         <v>0.004273772861542242</v>
       </c>
+      <c r="AS61" s="1" t="n">
+        <v>0.15955</v>
+      </c>
+      <c r="AT61" s="2" t="n">
+        <v>-0.001501971337380251</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8989,6 +9361,12 @@
       <c r="AR62" s="3" t="n">
         <v>0.004813137032842523</v>
       </c>
+      <c r="AS62" s="1" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="AT62" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9125,6 +9503,12 @@
       <c r="AR63" s="2" t="n">
         <v>-0.002815035601920758</v>
       </c>
+      <c r="AS63" s="1" t="n">
+        <v>5.978</v>
+      </c>
+      <c r="AT63" s="2" t="n">
+        <v>-0.007306542676851624</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9261,6 +9645,12 @@
       <c r="AR64" s="3" t="n">
         <v>0.002102017937219767</v>
       </c>
+      <c r="AS64" s="1" t="n">
+        <v>0.007149</v>
+      </c>
+      <c r="AT64" s="2" t="n">
+        <v>-0.0002796811634736772</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9397,6 +9787,12 @@
       <c r="AR65" s="3" t="n">
         <v>0.0006112469437652562</v>
       </c>
+      <c r="AS65" s="1" t="n">
+        <v>0.03342</v>
+      </c>
+      <c r="AT65" s="3" t="n">
+        <v>0.02076970067196091</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9533,6 +9929,12 @@
       <c r="AR66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS66" s="1" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AT66" s="3" t="n">
+        <v>0.00431034482758621</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9669,6 +10071,12 @@
       <c r="AR67" s="3" t="n">
         <v>0.003080714725816324</v>
       </c>
+      <c r="AS67" s="1" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="AT67" s="3" t="n">
+        <v>0.003071253071253142</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9805,6 +10213,12 @@
       <c r="AR68" s="3" t="n">
         <v>0.007868207523973452</v>
       </c>
+      <c r="AS68" s="1" t="n">
+        <v>2.0438</v>
+      </c>
+      <c r="AT68" s="2" t="n">
+        <v>-0.002781166138082478</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9941,6 +10355,12 @@
       <c r="AR69" s="3" t="n">
         <v>0.0006763611768683732</v>
       </c>
+      <c r="AS69" s="1" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="AT69" s="3" t="n">
+        <v>0.003379520108144646</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10077,6 +10497,12 @@
       <c r="AR70" s="3" t="n">
         <v>0.009708737864077679</v>
       </c>
+      <c r="AS70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AT70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10213,6 +10639,12 @@
       <c r="AR71" s="3" t="n">
         <v>0.00320690036492316</v>
       </c>
+      <c r="AS71" s="1" t="n">
+        <v>0.9073</v>
+      </c>
+      <c r="AT71" s="3" t="n">
+        <v>0.0001102292768959314</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10349,6 +10781,12 @@
       <c r="AR72" s="3" t="n">
         <v>0.01086453999075367</v>
       </c>
+      <c r="AS72" s="1" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="AT72" s="3" t="n">
+        <v>0.0006860278984677955</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10485,6 +10923,12 @@
       <c r="AR73" s="3" t="n">
         <v>0.001597444089456841</v>
       </c>
+      <c r="AS73" s="1" t="n">
+        <v>0.09385</v>
+      </c>
+      <c r="AT73" s="2" t="n">
+        <v>-0.002126528442317829</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10621,6 +11065,12 @@
       <c r="AR74" s="3" t="n">
         <v>0.001994969208083935</v>
       </c>
+      <c r="AS74" s="1" t="n">
+        <v>1.1522</v>
+      </c>
+      <c r="AT74" s="2" t="n">
+        <v>-0.002596952908587356</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10757,6 +11207,12 @@
       <c r="AR75" s="3" t="n">
         <v>0.001873828856964321</v>
       </c>
+      <c r="AS75" s="1" t="n">
+        <v>0.01609</v>
+      </c>
+      <c r="AT75" s="3" t="n">
+        <v>0.00311720698254373</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10893,6 +11349,12 @@
       <c r="AR76" s="3" t="n">
         <v>0.002714932126696807</v>
       </c>
+      <c r="AS76" s="1" t="n">
+        <v>0.1219</v>
+      </c>
+      <c r="AT76" s="3" t="n">
+        <v>0.0001640958319658044</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11029,6 +11491,12 @@
       <c r="AR77" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS77" s="1" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="AT77" s="3" t="n">
+        <v>0.005097706032285499</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11165,6 +11633,12 @@
       <c r="AR78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS78" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AT78" s="3" t="n">
+        <v>0.0009910802775025061</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11301,6 +11775,12 @@
       <c r="AR79" s="3" t="n">
         <v>0.001832111925383177</v>
       </c>
+      <c r="AS79" s="1" t="n">
+        <v>0.006015</v>
+      </c>
+      <c r="AT79" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11437,6 +11917,12 @@
       <c r="AR80" s="3" t="n">
         <v>0.00164974619289351</v>
       </c>
+      <c r="AS80" s="1" t="n">
+        <v>0.007963</v>
+      </c>
+      <c r="AT80" s="3" t="n">
+        <v>0.008868617762574291</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -11573,6 +12059,12 @@
       <c r="AR81" s="3" t="n">
         <v>0.00281214848143966</v>
       </c>
+      <c r="AS81" s="1" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AT81" s="2" t="n">
+        <v>-0.005047672462142449</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -11709,6 +12201,12 @@
       <c r="AR82" s="2" t="n">
         <v>-0.004186602870813268</v>
       </c>
+      <c r="AS82" s="1" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="AT82" s="3" t="n">
+        <v>0.0198198198198198</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11845,6 +12343,12 @@
       <c r="AR83" s="2" t="n">
         <v>-0.0003651856360316633</v>
       </c>
+      <c r="AS83" s="1" t="n">
+        <v>8.215999999999999</v>
+      </c>
+      <c r="AT83" s="3" t="n">
+        <v>0.0004870920603993618</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11981,6 +12485,12 @@
       <c r="AR84" s="3" t="n">
         <v>0.002497374918409613</v>
       </c>
+      <c r="AS84" s="1" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="AT84" s="3" t="n">
+        <v>0.001755130927105462</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12117,6 +12627,12 @@
       <c r="AR85" s="2" t="n">
         <v>-0.004237288135593134</v>
       </c>
+      <c r="AS85" s="1" t="n">
+        <v>0.004015</v>
+      </c>
+      <c r="AT85" s="3" t="n">
+        <v>0.00500625782227786</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12253,6 +12769,12 @@
       <c r="AR86" s="2" t="n">
         <v>-0.001143902997025726</v>
       </c>
+      <c r="AS86" s="1" t="n">
+        <v>0.13132</v>
+      </c>
+      <c r="AT86" s="3" t="n">
+        <v>0.00259581615513803</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -12389,6 +12911,12 @@
       <c r="AR87" s="3" t="n">
         <v>0.01044529961517313</v>
       </c>
+      <c r="AS87" s="1" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="AT87" s="3" t="n">
+        <v>0.002176278563656059</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -12525,6 +13053,12 @@
       <c r="AR88" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS88" s="1" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="AT88" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -12661,6 +13195,12 @@
       <c r="AR89" s="3" t="n">
         <v>0.001718213058419246</v>
       </c>
+      <c r="AS89" s="1" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AT89" s="3" t="n">
+        <v>0.001715265866209264</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12797,6 +13337,12 @@
       <c r="AR90" s="3" t="n">
         <v>0.003504672897196308</v>
       </c>
+      <c r="AS90" s="1" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="AT90" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12933,6 +13479,12 @@
       <c r="AR91" s="3" t="n">
         <v>0.0247948626471638</v>
       </c>
+      <c r="AS91" s="1" t="n">
+        <v>0.05746</v>
+      </c>
+      <c r="AT91" s="3" t="n">
+        <v>0.0001740644038293494</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -13069,6 +13621,12 @@
       <c r="AR92" s="3" t="n">
         <v>0.0001533389557616944</v>
       </c>
+      <c r="AS92" s="1" t="n">
+        <v>1.3055</v>
+      </c>
+      <c r="AT92" s="3" t="n">
+        <v>0.0007665772326562759</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13205,6 +13763,12 @@
       <c r="AR93" s="3" t="n">
         <v>0.004548306148055186</v>
       </c>
+      <c r="AS93" s="1" t="n">
+        <v>0.06415</v>
+      </c>
+      <c r="AT93" s="3" t="n">
+        <v>0.001561280249804885</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13341,6 +13905,12 @@
       <c r="AR94" s="2" t="n">
         <v>-0.01609195402298845</v>
       </c>
+      <c r="AS94" s="1" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="AT94" s="2" t="n">
+        <v>-0.01051401869158876</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -13477,6 +14047,12 @@
       <c r="AR95" s="3" t="n">
         <v>0.002680166765932138</v>
       </c>
+      <c r="AS95" s="1" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AT95" s="3" t="n">
+        <v>0.003267003267003237</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13613,6 +14189,12 @@
       <c r="AR96" s="3" t="n">
         <v>0.003109729009329215</v>
       </c>
+      <c r="AS96" s="1" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="AT96" s="2" t="n">
+        <v>-0.005314437555358662</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13749,6 +14331,12 @@
       <c r="AR97" s="3" t="n">
         <v>0.002770935960591238</v>
       </c>
+      <c r="AS97" s="1" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="AT97" s="3" t="n">
+        <v>0.001535155050660029</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13885,6 +14473,12 @@
       <c r="AR98" s="3" t="n">
         <v>0.005305039787798413</v>
       </c>
+      <c r="AS98" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="AT98" s="3" t="n">
+        <v>0.008795074758135452</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14021,6 +14615,12 @@
       <c r="AR99" s="3" t="n">
         <v>0.003309066843150308</v>
       </c>
+      <c r="AS99" s="1" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="AT99" s="3" t="n">
+        <v>0.001649076517150361</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -14157,6 +14757,12 @@
       <c r="AR100" s="3" t="n">
         <v>0.008539458186101459</v>
       </c>
+      <c r="AS100" s="1" t="n">
+        <v>0.03433</v>
+      </c>
+      <c r="AT100" s="3" t="n">
+        <v>0.002335766423357569</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -14293,6 +14899,12 @@
       <c r="AR101" s="2" t="n">
         <v>-0.001643835616438297</v>
       </c>
+      <c r="AS101" s="1" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="AT101" s="3" t="n">
+        <v>0.001097694840834249</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -14429,6 +15041,12 @@
       <c r="AR102" s="3" t="n">
         <v>0.004946297343131756</v>
       </c>
+      <c r="AS102" s="1" t="n">
+        <v>0.00725</v>
+      </c>
+      <c r="AT102" s="3" t="n">
+        <v>0.01954718042469417</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -14565,6 +15183,12 @@
       <c r="AR103" s="2" t="n">
         <v>-0.001077586206896561</v>
       </c>
+      <c r="AS103" s="1" t="n">
+        <v>0.06517000000000001</v>
+      </c>
+      <c r="AT103" s="3" t="n">
+        <v>0.00431499460625678</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -14701,6 +15325,12 @@
       <c r="AR104" s="2" t="n">
         <v>-0.004846135207172284</v>
       </c>
+      <c r="AS104" s="1" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="AT104" s="3" t="n">
+        <v>0.009495982468955477</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14837,6 +15467,12 @@
       <c r="AR105" s="3" t="n">
         <v>0.002745744096650256</v>
       </c>
+      <c r="AS105" s="1" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="AT105" s="3" t="n">
+        <v>0.007119386637458872</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14973,6 +15609,12 @@
       <c r="AR106" s="3" t="n">
         <v>0.004099378881987583</v>
       </c>
+      <c r="AS106" s="1" t="n">
+        <v>0.008012</v>
+      </c>
+      <c r="AT106" s="2" t="n">
+        <v>-0.008783867375974252</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -15109,6 +15751,12 @@
       <c r="AR107" s="3" t="n">
         <v>0.001103752759381853</v>
       </c>
+      <c r="AS107" s="1" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AT107" s="3" t="n">
+        <v>0.003307607497243717</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -15245,6 +15893,12 @@
       <c r="AR108" s="2" t="n">
         <v>-0.0004627487274409807</v>
       </c>
+      <c r="AS108" s="1" t="n">
+        <v>0.02164</v>
+      </c>
+      <c r="AT108" s="3" t="n">
+        <v>0.001851851851851776</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -15381,6 +16035,12 @@
       <c r="AR109" s="2" t="n">
         <v>-0.001970972943916843</v>
       </c>
+      <c r="AS109" s="1" t="n">
+        <v>0.05577</v>
+      </c>
+      <c r="AT109" s="3" t="n">
+        <v>0.001256732495511681</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -15517,6 +16177,12 @@
       <c r="AR110" s="2" t="n">
         <v>-0.004245732605493496</v>
       </c>
+      <c r="AS110" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="AT110" s="2" t="n">
+        <v>-0.0001740341106856269</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -15653,6 +16319,12 @@
       <c r="AR111" s="3" t="n">
         <v>0.0003125000000000234</v>
       </c>
+      <c r="AS111" s="1" t="n">
+        <v>0.09599000000000001</v>
+      </c>
+      <c r="AT111" s="2" t="n">
+        <v>-0.0004165364990107089</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -15789,6 +16461,12 @@
       <c r="AR112" s="3" t="n">
         <v>0.002695417789757302</v>
       </c>
+      <c r="AS112" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="AT112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -15925,6 +16603,12 @@
       <c r="AR113" s="3" t="n">
         <v>0.002752293577981574</v>
       </c>
+      <c r="AS113" s="1" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="AT113" s="3" t="n">
+        <v>0.001118227101758656</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -16061,6 +16745,12 @@
       <c r="AR114" s="3" t="n">
         <v>0.008460236886632848</v>
       </c>
+      <c r="AS114" s="1" t="n">
+        <v>0.001801</v>
+      </c>
+      <c r="AT114" s="3" t="n">
+        <v>0.007270693512304245</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -16197,6 +16887,12 @@
       <c r="AR115" s="3" t="n">
         <v>0.005569700827498502</v>
       </c>
+      <c r="AS115" s="1" t="n">
+        <v>1.2635</v>
+      </c>
+      <c r="AT115" s="2" t="n">
+        <v>-0.000237379332172786</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -16333,6 +17029,12 @@
       <c r="AR116" s="2" t="n">
         <v>-0.0004251700680271641</v>
       </c>
+      <c r="AS116" s="1" t="n">
+        <v>0.2356</v>
+      </c>
+      <c r="AT116" s="3" t="n">
+        <v>0.002126754572522333</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -16469,6 +17171,12 @@
       <c r="AR117" s="3" t="n">
         <v>0.001157981803143104</v>
       </c>
+      <c r="AS117" s="1" t="n">
+        <v>0.06065</v>
+      </c>
+      <c r="AT117" s="3" t="n">
+        <v>0.002148050231328571</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -16605,6 +17313,12 @@
       <c r="AR118" s="2" t="n">
         <v>-0.01204281891168597</v>
       </c>
+      <c r="AS118" s="1" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AT118" s="2" t="n">
+        <v>-0.002031602708803607</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -16741,6 +17455,12 @@
       <c r="AR119" s="2" t="n">
         <v>-0.004107338444687794</v>
       </c>
+      <c r="AS119" s="1" t="n">
+        <v>0.003642</v>
+      </c>
+      <c r="AT119" s="3" t="n">
+        <v>0.001374759417101951</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -16877,6 +17597,12 @@
       <c r="AR120" s="3" t="n">
         <v>0.001270648030495554</v>
       </c>
+      <c r="AS120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AT120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -17013,6 +17739,12 @@
       <c r="AR121" s="3" t="n">
         <v>0.005398110661268524</v>
       </c>
+      <c r="AS121" s="1" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AT121" s="3" t="n">
+        <v>0.0003355704697986208</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -17149,6 +17881,12 @@
       <c r="AR122" s="3" t="n">
         <v>0.00459526334393787</v>
       </c>
+      <c r="AS122" s="1" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="AT122" s="2" t="n">
+        <v>-0.0003518648838845496</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -17285,6 +18023,12 @@
       <c r="AR123" s="3" t="n">
         <v>0.001577231782972903</v>
       </c>
+      <c r="AS123" s="1" t="n">
+        <v>0.028658</v>
+      </c>
+      <c r="AT123" s="3" t="n">
+        <v>0.002869540873460202</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -17421,6 +18165,12 @@
       <c r="AR124" s="3" t="n">
         <v>0.002687140115163172</v>
       </c>
+      <c r="AS124" s="1" t="n">
+        <v>0.07826</v>
+      </c>
+      <c r="AT124" s="2" t="n">
+        <v>-0.001276161306789215</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -17557,6 +18307,12 @@
       <c r="AR125" s="2" t="n">
         <v>-0.0006627532664268189</v>
       </c>
+      <c r="AS125" s="1" t="n">
+        <v>0.10542</v>
+      </c>
+      <c r="AT125" s="2" t="n">
+        <v>-0.001231643770724823</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -17693,6 +18449,12 @@
       <c r="AR126" s="2" t="n">
         <v>-0.001521491061240085</v>
       </c>
+      <c r="AS126" s="1" t="n">
+        <v>0.02624</v>
+      </c>
+      <c r="AT126" s="2" t="n">
+        <v>-0.0003809523809523655</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -17829,6 +18591,12 @@
       <c r="AR127" s="2" t="n">
         <v>-0.0009191176470589455</v>
       </c>
+      <c r="AS127" s="1" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="AT127" s="3" t="n">
+        <v>0.0004599816007359519</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -17965,6 +18733,12 @@
       <c r="AR128" s="3" t="n">
         <v>0.004972032318210211</v>
       </c>
+      <c r="AS128" s="1" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="AT128" s="2" t="n">
+        <v>-0.001236858379715558</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -18101,6 +18875,12 @@
       <c r="AR129" s="3" t="n">
         <v>0.001613468958260121</v>
       </c>
+      <c r="AS129" s="1" t="n">
+        <v>0.14262</v>
+      </c>
+      <c r="AT129" s="2" t="n">
+        <v>-0.001120605126768409</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -18237,6 +19017,12 @@
       <c r="AR130" s="3" t="n">
         <v>0.007903760097634657</v>
       </c>
+      <c r="AS130" s="1" t="n">
+        <v>0.052202</v>
+      </c>
+      <c r="AT130" s="3" t="n">
+        <v>0.003325068711680016</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -18373,6 +19159,12 @@
       <c r="AR131" s="3" t="n">
         <v>0.002808988764045041</v>
       </c>
+      <c r="AS131" s="1" t="n">
+        <v>0.08219</v>
+      </c>
+      <c r="AT131" s="3" t="n">
+        <v>0.0009743027645840547</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -18509,6 +19301,12 @@
       <c r="AR132" s="3" t="n">
         <v>0.002280501710376348</v>
       </c>
+      <c r="AS132" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="AT132" s="3" t="n">
+        <v>0.002275312855517541</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -18645,6 +19443,12 @@
       <c r="AR133" s="3" t="n">
         <v>0.003967569432465014</v>
       </c>
+      <c r="AS133" s="1" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="AT133" s="3" t="n">
+        <v>0.0005154639175259072</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -18781,6 +19585,12 @@
       <c r="AR134" s="3" t="n">
         <v>0.00304981362250084</v>
       </c>
+      <c r="AS134" s="1" t="n">
+        <v>0.02964</v>
+      </c>
+      <c r="AT134" s="3" t="n">
+        <v>0.001351351351351296</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -18917,6 +19727,12 @@
       <c r="AR135" s="3" t="n">
         <v>0.001146131805157546</v>
       </c>
+      <c r="AS135" s="1" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="AT135" s="3" t="n">
+        <v>0.002862049227246791</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -19053,6 +19869,12 @@
       <c r="AR136" s="3" t="n">
         <v>0.005398110661268524</v>
       </c>
+      <c r="AS136" s="1" t="n">
+        <v>0.03721</v>
+      </c>
+      <c r="AT136" s="2" t="n">
+        <v>-0.001073825503355661</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -19189,6 +20011,12 @@
       <c r="AR137" s="3" t="n">
         <v>0.0007429420505200291</v>
       </c>
+      <c r="AS137" s="1" t="n">
+        <v>0.02693</v>
+      </c>
+      <c r="AT137" s="2" t="n">
+        <v>-0.0003711952487008015</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -19325,6 +20153,12 @@
       <c r="AR138" s="2" t="n">
         <v>-0.0116686114352393</v>
       </c>
+      <c r="AS138" s="1" t="n">
+        <v>2.557</v>
+      </c>
+      <c r="AT138" s="3" t="n">
+        <v>0.006296733569460848</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -19461,6 +20295,12 @@
       <c r="AR139" s="2" t="n">
         <v>-0.0008488964346350872</v>
       </c>
+      <c r="AS139" s="1" t="n">
+        <v>0.01179</v>
+      </c>
+      <c r="AT139" s="3" t="n">
+        <v>0.001699235344095235</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -19597,6 +20437,12 @@
       <c r="AR140" s="2" t="n">
         <v>-0.004765146358066754</v>
       </c>
+      <c r="AS140" s="1" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="AT140" s="3" t="n">
+        <v>0.0006839945280438665</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -19733,6 +20579,12 @@
       <c r="AR141" s="2" t="n">
         <v>-0.0005569996286669353</v>
       </c>
+      <c r="AS141" s="1" t="n">
+        <v>16.228</v>
+      </c>
+      <c r="AT141" s="3" t="n">
+        <v>0.004891943773608311</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -19869,6 +20721,12 @@
       <c r="AR142" s="3" t="n">
         <v>0.002411575562701006</v>
       </c>
+      <c r="AS142" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="AT142" s="3" t="n">
+        <v>0.001603849238171547</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -20005,6 +20863,12 @@
       <c r="AR143" s="3" t="n">
         <v>0.01030927835051554</v>
       </c>
+      <c r="AS143" s="1" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="AT143" s="2" t="n">
+        <v>-0.004222378606615132</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -20141,6 +21005,12 @@
       <c r="AR144" s="3" t="n">
         <v>0.005081515985602495</v>
       </c>
+      <c r="AS144" s="1" t="n">
+        <v>0.004773</v>
+      </c>
+      <c r="AT144" s="3" t="n">
+        <v>0.005477143459026749</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -20277,6 +21147,12 @@
       <c r="AR145" s="3" t="n">
         <v>0.002022960602842261</v>
       </c>
+      <c r="AS145" s="1" t="n">
+        <v>1.9771</v>
+      </c>
+      <c r="AT145" s="2" t="n">
+        <v>-0.002119820319991915</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -20413,6 +21289,12 @@
       <c r="AR146" s="2" t="n">
         <v>-0.002558635394456186</v>
       </c>
+      <c r="AS146" s="1" t="n">
+        <v>0.02339</v>
+      </c>
+      <c r="AT146" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -20549,6 +21431,12 @@
       <c r="AR147" s="3" t="n">
         <v>0.001448629373746435</v>
       </c>
+      <c r="AS147" s="1" t="n">
+        <v>0.08971</v>
+      </c>
+      <c r="AT147" s="2" t="n">
+        <v>-0.00178034939356857</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -20685,6 +21573,12 @@
       <c r="AR148" s="3" t="n">
         <v>0.01177394034536871</v>
       </c>
+      <c r="AS148" s="1" t="n">
+        <v>0.06398</v>
+      </c>
+      <c r="AT148" s="2" t="n">
+        <v>-0.007292474786656296</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -20821,6 +21715,12 @@
       <c r="AR149" s="2" t="n">
         <v>-0.0001694915254236631</v>
       </c>
+      <c r="AS149" s="1" t="n">
+        <v>0.05905</v>
+      </c>
+      <c r="AT149" s="3" t="n">
+        <v>0.001017121546024708</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -20957,6 +21857,12 @@
       <c r="AR150" s="3" t="n">
         <v>0.006913580246913641</v>
       </c>
+      <c r="AS150" s="1" t="n">
+        <v>0.24473</v>
+      </c>
+      <c r="AT150" s="3" t="n">
+        <v>0.0002043485368644535</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -21093,6 +21999,12 @@
       <c r="AR151" s="3" t="n">
         <v>0.004434272636246633</v>
       </c>
+      <c r="AS151" s="1" t="n">
+        <v>7.059e-05</v>
+      </c>
+      <c r="AT151" s="3" t="n">
+        <v>0.005269154087154631</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -21229,6 +22141,12 @@
       <c r="AR152" s="2" t="n">
         <v>-0.002252759630547422</v>
       </c>
+      <c r="AS152" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="AT152" s="2" t="n">
+        <v>-0.001354707608941046</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -21365,6 +22283,12 @@
       <c r="AR153" s="3" t="n">
         <v>0.003216468317787072</v>
       </c>
+      <c r="AS153" s="1" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AT153" s="3" t="n">
+        <v>0.003206155819172815</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -21501,6 +22425,12 @@
       <c r="AR154" s="3" t="n">
         <v>0.01242064587358544</v>
       </c>
+      <c r="AS154" s="1" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AT154" s="2" t="n">
+        <v>-0.005725190839694631</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -21637,6 +22567,12 @@
       <c r="AR155" s="2" t="n">
         <v>-0.0008688097306688878</v>
       </c>
+      <c r="AS155" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AT155" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -21773,6 +22709,12 @@
       <c r="AR156" s="2" t="n">
         <v>-0.00258748151798918</v>
       </c>
+      <c r="AS156" s="1" t="n">
+        <v>0.08081000000000001</v>
+      </c>
+      <c r="AT156" s="2" t="n">
+        <v>-0.001729462631253704</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -21909,6 +22851,12 @@
       <c r="AR157" s="3" t="n">
         <v>0.009192834743760484</v>
       </c>
+      <c r="AS157" s="1" t="n">
+        <v>0.23755</v>
+      </c>
+      <c r="AT157" s="3" t="n">
+        <v>0.01115225811943988</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -22045,6 +22993,12 @@
       <c r="AR158" s="3" t="n">
         <v>0.001568012544100398</v>
       </c>
+      <c r="AS158" s="1" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="AT158" s="2" t="n">
+        <v>-0.004305283757338512</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -22181,6 +23135,12 @@
       <c r="AR159" s="3" t="n">
         <v>0.0006849315068493917</v>
       </c>
+      <c r="AS159" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT159" s="2" t="n">
+        <v>-0.0006844626967831019</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -22317,6 +23277,12 @@
       <c r="AR160" s="3" t="n">
         <v>0.005060728744939276</v>
       </c>
+      <c r="AS160" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="AT160" s="3" t="n">
+        <v>0.005035246727089632</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -22453,6 +23419,12 @@
       <c r="AR161" s="2" t="n">
         <v>-0.001425178147268515</v>
       </c>
+      <c r="AS161" s="1" t="n">
+        <v>0.14656</v>
+      </c>
+      <c r="AT161" s="2" t="n">
+        <v>-0.003941824113089556</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -22589,6 +23561,12 @@
       <c r="AR162" s="3" t="n">
         <v>0.0006091989034420547</v>
       </c>
+      <c r="AS162" s="1" t="n">
+        <v>0.003301</v>
+      </c>
+      <c r="AT162" s="3" t="n">
+        <v>0.004870624048706227</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -22725,6 +23703,12 @@
       <c r="AR163" s="3" t="n">
         <v>0.001600320064012841</v>
       </c>
+      <c r="AS163" s="1" t="n">
+        <v>0.004994</v>
+      </c>
+      <c r="AT163" s="2" t="n">
+        <v>-0.002596365088875572</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -22861,6 +23845,12 @@
       <c r="AR164" s="2" t="n">
         <v>-0.001038421599169292</v>
       </c>
+      <c r="AS164" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="AT164" s="3" t="n">
+        <v>0.005197505197505202</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -22997,6 +23987,12 @@
       <c r="AR165" s="3" t="n">
         <v>0.005891980360065545</v>
       </c>
+      <c r="AS165" s="1" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AT165" s="3" t="n">
+        <v>0.00130165961601027</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -23133,6 +24129,12 @@
       <c r="AR166" s="3" t="n">
         <v>0.002013374559574253</v>
       </c>
+      <c r="AS166" s="1" t="n">
+        <v>1.3921</v>
+      </c>
+      <c r="AT166" s="2" t="n">
+        <v>-0.001004664513814186</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -23269,6 +24271,12 @@
       <c r="AR167" s="2" t="n">
         <v>-0.0007191657677095774</v>
       </c>
+      <c r="AS167" s="1" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AT167" s="3" t="n">
+        <v>0.001799208348326738</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -23405,6 +24413,12 @@
       <c r="AR168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS168" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AT168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -23541,6 +24555,12 @@
       <c r="AR169" s="3" t="n">
         <v>0.001678415575696474</v>
       </c>
+      <c r="AS169" s="1" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="AT169" s="3" t="n">
+        <v>0.002010723860589847</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -23677,6 +24697,12 @@
       <c r="AR170" s="2" t="n">
         <v>-0.0002309468822170005</v>
       </c>
+      <c r="AS170" s="1" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="AT170" s="3" t="n">
+        <v>0.002310002310002216</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -23813,6 +24839,12 @@
       <c r="AR171" s="2" t="n">
         <v>-0.006060606060606023</v>
       </c>
+      <c r="AS171" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="AT171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -23949,6 +24981,12 @@
       <c r="AR172" s="3" t="n">
         <v>0.01562499999999998</v>
       </c>
+      <c r="AS172" s="1" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="AT172" s="2" t="n">
+        <v>-0.007692307692307619</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -24085,6 +25123,12 @@
       <c r="AR173" s="3" t="n">
         <v>0.0004746084480305203</v>
       </c>
+      <c r="AS173" s="1" t="n">
+        <v>0.02099</v>
+      </c>
+      <c r="AT173" s="2" t="n">
+        <v>-0.00426944971537001</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -24221,6 +25265,12 @@
       <c r="AR174" s="2" t="n">
         <v>-0.001907326377201879</v>
       </c>
+      <c r="AS174" s="1" t="n">
+        <v>0.08905</v>
+      </c>
+      <c r="AT174" s="3" t="n">
+        <v>0.00101169064748209</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -24357,6 +25407,12 @@
       <c r="AR175" s="2" t="n">
         <v>-0.003057254030016648</v>
       </c>
+      <c r="AS175" s="1" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AT175" s="3" t="n">
+        <v>0.00111513799832717</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -24493,6 +25549,12 @@
       <c r="AR176" s="3" t="n">
         <v>0.005668398677373575</v>
       </c>
+      <c r="AS176" s="1" t="n">
+        <v>0.02124</v>
+      </c>
+      <c r="AT176" s="2" t="n">
+        <v>-0.002348520432127827</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -24629,6 +25691,12 @@
       <c r="AR177" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS177" s="1" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="AT177" s="3" t="n">
+        <v>0.001277139208173639</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -24765,6 +25833,12 @@
       <c r="AR178" s="3" t="n">
         <v>0.003161222339304608</v>
       </c>
+      <c r="AS178" s="1" t="n">
+        <v>0.000954</v>
+      </c>
+      <c r="AT178" s="3" t="n">
+        <v>0.002100840336134391</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -24901,6 +25975,12 @@
       <c r="AR179" s="3" t="n">
         <v>0.002455386504143486</v>
       </c>
+      <c r="AS179" s="1" t="n">
+        <v>0.022971</v>
+      </c>
+      <c r="AT179" s="3" t="n">
+        <v>0.004723789528933079</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -25037,6 +26117,12 @@
       <c r="AR180" s="3" t="n">
         <v>0.005400098183603398</v>
       </c>
+      <c r="AS180" s="1" t="n">
+        <v>4.109</v>
+      </c>
+      <c r="AT180" s="3" t="n">
+        <v>0.003173828124999976</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -25173,6 +26259,12 @@
       <c r="AR181" s="3" t="n">
         <v>0.004404510218463808</v>
       </c>
+      <c r="AS181" s="1" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="AT181" s="3" t="n">
+        <v>0.002806525171022513</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -25309,6 +26401,12 @@
       <c r="AR182" s="3" t="n">
         <v>0.00419078028337647</v>
       </c>
+      <c r="AS182" s="1" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="AT182" s="3" t="n">
+        <v>0.003775834658187652</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -25445,6 +26543,12 @@
       <c r="AR183" s="3" t="n">
         <v>0.0009214891264282885</v>
       </c>
+      <c r="AS183" s="1" t="n">
+        <v>5.428</v>
+      </c>
+      <c r="AT183" s="2" t="n">
+        <v>-0.0005523844595838913</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -25581,6 +26685,12 @@
       <c r="AR184" s="3" t="n">
         <v>0.003483106931382719</v>
       </c>
+      <c r="AS184" s="1" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="AT184" s="2" t="n">
+        <v>-0.001735508503991571</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -25717,6 +26827,12 @@
       <c r="AR185" s="2" t="n">
         <v>-0.001622498647917727</v>
       </c>
+      <c r="AS185" s="1" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="AT185" s="3" t="n">
+        <v>0.005417118093174398</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -25853,6 +26969,12 @@
       <c r="AR186" s="3" t="n">
         <v>0.003278688524590133</v>
       </c>
+      <c r="AS186" s="1" t="n">
+        <v>3.06e-05</v>
+      </c>
+      <c r="AT186" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -25989,6 +27111,12 @@
       <c r="AR187" s="3" t="n">
         <v>0.005128205128205142</v>
       </c>
+      <c r="AS187" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="AT187" s="3" t="n">
+        <v>0.002551020408163383</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -26125,6 +27253,12 @@
       <c r="AR188" s="3" t="n">
         <v>0.001229709788489952</v>
       </c>
+      <c r="AS188" s="1" t="n">
+        <v>0.04081</v>
+      </c>
+      <c r="AT188" s="3" t="n">
+        <v>0.002456398919184375</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -26261,6 +27395,12 @@
       <c r="AR189" s="3" t="n">
         <v>0.0002264492753623243</v>
       </c>
+      <c r="AS189" s="1" t="n">
+        <v>0.0004423</v>
+      </c>
+      <c r="AT189" s="3" t="n">
+        <v>0.001358388046185227</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -26397,6 +27537,12 @@
       <c r="AR190" s="3" t="n">
         <v>0.003040834057341469</v>
       </c>
+      <c r="AS190" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="AT190" s="3" t="n">
+        <v>0.001299263750541457</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -26533,6 +27679,12 @@
       <c r="AR191" s="3" t="n">
         <v>0.000639795265515009</v>
       </c>
+      <c r="AS191" s="1" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="AT191" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -26669,6 +27821,12 @@
       <c r="AR192" s="3" t="n">
         <v>0.003059204606802169</v>
       </c>
+      <c r="AS192" s="1" t="n">
+        <v>0.05562</v>
+      </c>
+      <c r="AT192" s="2" t="n">
+        <v>-0.002152852529601634</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -26805,6 +27963,12 @@
       <c r="AR193" s="3" t="n">
         <v>0.001609442060085808</v>
       </c>
+      <c r="AS193" s="1" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="AT193" s="3" t="n">
+        <v>0.001071237279057342</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -26941,6 +28105,12 @@
       <c r="AR194" s="2" t="n">
         <v>-0.0005202913631633503</v>
       </c>
+      <c r="AS194" s="1" t="n">
+        <v>0.01919</v>
+      </c>
+      <c r="AT194" s="2" t="n">
+        <v>-0.001041124414367655</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -27077,6 +28247,12 @@
       <c r="AR195" s="3" t="n">
         <v>0.003051643192488318</v>
       </c>
+      <c r="AS195" s="1" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="AT195" s="3" t="n">
+        <v>0.003276386613620436</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -27213,6 +28389,12 @@
       <c r="AR196" s="2" t="n">
         <v>-0.00163666121112923</v>
       </c>
+      <c r="AS196" s="1" t="n">
+        <v>0.01226</v>
+      </c>
+      <c r="AT196" s="3" t="n">
+        <v>0.004918032786885187</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -27349,6 +28531,12 @@
       <c r="AR197" s="3" t="n">
         <v>0.01273326015367722</v>
       </c>
+      <c r="AS197" s="1" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="AT197" s="3" t="n">
+        <v>0.001517450682852821</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -27485,6 +28673,12 @@
       <c r="AR198" s="3" t="n">
         <v>0.004493065051767862</v>
       </c>
+      <c r="AS198" s="1" t="n">
+        <v>0.5127</v>
+      </c>
+      <c r="AT198" s="2" t="n">
+        <v>-0.002917152858809696</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -27621,6 +28815,12 @@
       <c r="AR199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AT199" s="2" t="n">
+        <v>-0.01123595505617979</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -27757,6 +28957,12 @@
       <c r="AR200" s="2" t="n">
         <v>-0.0006756756756757813</v>
       </c>
+      <c r="AS200" s="1" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="AT200" s="2" t="n">
+        <v>-0.002028397565922878</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -27893,6 +29099,12 @@
       <c r="AR201" s="2" t="n">
         <v>-0.000534759358288841</v>
       </c>
+      <c r="AS201" s="1" t="n">
+        <v>0.005604</v>
+      </c>
+      <c r="AT201" s="2" t="n">
+        <v>-0.0005350454788657746</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -28029,6 +29241,12 @@
       <c r="AR202" s="2" t="n">
         <v>-0.0006949874033534064</v>
       </c>
+      <c r="AS202" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AT202" s="2" t="n">
+        <v>-0.0002608015300356021</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -28165,6 +29383,12 @@
       <c r="AR203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS203" s="1" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="AT203" s="3" t="n">
+        <v>0.003676470588235399</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -28301,6 +29525,12 @@
       <c r="AR204" s="3" t="n">
         <v>0.007222389407162117</v>
       </c>
+      <c r="AS204" s="1" t="n">
+        <v>0.03372</v>
+      </c>
+      <c r="AT204" s="3" t="n">
+        <v>0.007469375560203174</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -28437,6 +29667,12 @@
       <c r="AR205" s="2" t="n">
         <v>-0.00671301846080088</v>
       </c>
+      <c r="AS205" s="1" t="n">
+        <v>4.169</v>
+      </c>
+      <c r="AT205" s="3" t="n">
+        <v>0.006275645667390732</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -28573,6 +29809,12 @@
       <c r="AR206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS206" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AT206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -28709,6 +29951,12 @@
       <c r="AR207" s="3" t="n">
         <v>0.003371710526315738</v>
       </c>
+      <c r="AS207" s="1" t="n">
+        <v>0.0012142</v>
+      </c>
+      <c r="AT207" s="2" t="n">
+        <v>-0.004835669207442086</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -28845,6 +30093,12 @@
       <c r="AR208" s="3" t="n">
         <v>0.0004186435947530558</v>
       </c>
+      <c r="AS208" s="1" t="n">
+        <v>0.007177</v>
+      </c>
+      <c r="AT208" s="3" t="n">
+        <v>0.001115915748361026</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -28981,6 +30235,12 @@
       <c r="AR209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="AT209" s="3" t="n">
+        <v>0.003355704697986557</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -29117,6 +30377,12 @@
       <c r="AR210" s="2" t="n">
         <v>-0.0007757951900697362</v>
       </c>
+      <c r="AS210" s="1" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="AT210" s="2" t="n">
+        <v>-0.0007763975155278648</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -29253,6 +30519,12 @@
       <c r="AR211" s="3" t="n">
         <v>0.002109704641350247</v>
       </c>
+      <c r="AS211" s="1" t="n">
+        <v>0.007119</v>
+      </c>
+      <c r="AT211" s="2" t="n">
+        <v>-0.0008421052631578847</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -29389,6 +30661,12 @@
       <c r="AR212" s="2" t="n">
         <v>-0.003699966363942112</v>
       </c>
+      <c r="AS212" s="1" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AT212" s="3" t="n">
+        <v>0.008440243079000683</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -29525,6 +30803,12 @@
       <c r="AR213" s="2" t="n">
         <v>-0.001461721176685615</v>
       </c>
+      <c r="AS213" s="1" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="AT213" s="2" t="n">
+        <v>-0.01372369624885625</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -29661,6 +30945,12 @@
       <c r="AR214" s="2" t="n">
         <v>-0.00106553010122539</v>
       </c>
+      <c r="AS214" s="1" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="AT214" s="3" t="n">
+        <v>0.001599999999999972</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -29797,6 +31087,12 @@
       <c r="AR215" s="2" t="n">
         <v>-0.003566735498404275</v>
       </c>
+      <c r="AS215" s="1" t="n">
+        <v>0.05325</v>
+      </c>
+      <c r="AT215" s="3" t="n">
+        <v>0.00320271288620943</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -29933,6 +31229,12 @@
       <c r="AR216" s="3" t="n">
         <v>0.003974167908594019</v>
       </c>
+      <c r="AS216" s="1" t="n">
+        <v>0.002013</v>
+      </c>
+      <c r="AT216" s="2" t="n">
+        <v>-0.003958436417614924</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -30069,6 +31371,12 @@
       <c r="AR217" s="3" t="n">
         <v>0.002002336058735119</v>
       </c>
+      <c r="AS217" s="1" t="n">
+        <v>6.002</v>
+      </c>
+      <c r="AT217" s="2" t="n">
+        <v>-0.0004995836802664636</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -30205,6 +31513,12 @@
       <c r="AR218" s="2" t="n">
         <v>-0.0002366303833413</v>
       </c>
+      <c r="AS218" s="1" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AT218" s="3" t="n">
+        <v>0.0035502958579883</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -30341,6 +31655,12 @@
       <c r="AR219" s="3" t="n">
         <v>0.007513148009015798</v>
       </c>
+      <c r="AS219" s="1" t="n">
+        <v>0.005344</v>
+      </c>
+      <c r="AT219" s="2" t="n">
+        <v>-0.003728560775540651</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -30477,6 +31797,12 @@
       <c r="AR220" s="3" t="n">
         <v>0.002443195699975468</v>
       </c>
+      <c r="AS220" s="1" t="n">
+        <v>0.04106</v>
+      </c>
+      <c r="AT220" s="3" t="n">
+        <v>0.0007311723129418047</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -30613,6 +31939,12 @@
       <c r="AR221" s="3" t="n">
         <v>0.005563282336578565</v>
       </c>
+      <c r="AS221" s="1" t="n">
+        <v>0.005785</v>
+      </c>
+      <c r="AT221" s="3" t="n">
+        <v>0.0001728907330567311</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -30749,6 +32081,12 @@
       <c r="AR222" s="3" t="n">
         <v>0.00218340611353718</v>
       </c>
+      <c r="AS222" s="1" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="AT222" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -30885,6 +32223,12 @@
       <c r="AR223" s="3" t="n">
         <v>0.00358315915198577</v>
       </c>
+      <c r="AS223" s="1" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AT223" s="2" t="n">
+        <v>-0.0005950609937519592</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -31021,6 +32365,12 @@
       <c r="AR224" s="3" t="n">
         <v>0.002087198515769843</v>
       </c>
+      <c r="AS224" s="1" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AT224" s="2" t="n">
+        <v>-0.0002314279102059454</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -31157,6 +32507,12 @@
       <c r="AR225" s="3" t="n">
         <v>0.003134040501446436</v>
       </c>
+      <c r="AS225" s="1" t="n">
+        <v>0.08316</v>
+      </c>
+      <c r="AT225" s="2" t="n">
+        <v>-0.0007209805335256488</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -31293,6 +32649,12 @@
       <c r="AR226" s="2" t="n">
         <v>-0.0005399568034557016</v>
       </c>
+      <c r="AS226" s="1" t="n">
+        <v>0.01857</v>
+      </c>
+      <c r="AT226" s="3" t="n">
+        <v>0.00324149108589957</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -31429,6 +32791,12 @@
       <c r="AR227" s="3" t="n">
         <v>0.000426621160409539</v>
       </c>
+      <c r="AS227" s="1" t="n">
+        <v>0.04695</v>
+      </c>
+      <c r="AT227" s="3" t="n">
+        <v>0.001066098081023485</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -31565,6 +32933,12 @@
       <c r="AR228" s="3" t="n">
         <v>0.002588438308887016</v>
       </c>
+      <c r="AS228" s="1" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="AT228" s="2" t="n">
+        <v>-0.001290877796901841</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -31701,6 +33075,12 @@
       <c r="AR229" s="3" t="n">
         <v>0.004621072088724588</v>
       </c>
+      <c r="AS229" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="AT229" s="3" t="n">
+        <v>0.0009199632014718397</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -31837,6 +33217,12 @@
       <c r="AR230" s="3" t="n">
         <v>0.001206272617611615</v>
       </c>
+      <c r="AS230" s="1" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="AT230" s="3" t="n">
+        <v>0.004819277108433706</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -31973,6 +33359,12 @@
       <c r="AR231" s="3" t="n">
         <v>0.002968337730870706</v>
       </c>
+      <c r="AS231" s="1" t="n">
+        <v>0.03038</v>
+      </c>
+      <c r="AT231" s="2" t="n">
+        <v>-0.0009865175928970332</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -32109,6 +33501,12 @@
       <c r="AR232" s="3" t="n">
         <v>0.004979628791308396</v>
       </c>
+      <c r="AS232" s="1" t="n">
+        <v>0.02233</v>
+      </c>
+      <c r="AT232" s="3" t="n">
+        <v>0.005855855855855773</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -32245,6 +33643,12 @@
       <c r="AR233" s="3" t="n">
         <v>0.01145103401128019</v>
       </c>
+      <c r="AS233" s="1" t="n">
+        <v>0.11943</v>
+      </c>
+      <c r="AT233" s="3" t="n">
+        <v>0.009040216289286817</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -32381,6 +33785,12 @@
       <c r="AR234" s="3" t="n">
         <v>0.002373417721518945</v>
       </c>
+      <c r="AS234" s="1" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="AT234" s="3" t="n">
+        <v>0.001973164956590373</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -32517,6 +33927,12 @@
       <c r="AR235" s="3" t="n">
         <v>0.001164822364589353</v>
       </c>
+      <c r="AS235" s="1" t="n">
+        <v>0.06888</v>
+      </c>
+      <c r="AT235" s="3" t="n">
+        <v>0.001745200698080208</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -32653,6 +34069,12 @@
       <c r="AR236" s="3" t="n">
         <v>0.001194267515923656</v>
       </c>
+      <c r="AS236" s="1" t="n">
+        <v>0.12613</v>
+      </c>
+      <c r="AT236" s="3" t="n">
+        <v>0.003021868787276274</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -32789,6 +34211,12 @@
       <c r="AR237" s="3" t="n">
         <v>0.002625360987135806</v>
       </c>
+      <c r="AS237" s="1" t="n">
+        <v>0.03802</v>
+      </c>
+      <c r="AT237" s="2" t="n">
+        <v>-0.004451427075150654</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -32925,6 +34353,12 @@
       <c r="AR238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS238" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AT238" s="2" t="n">
+        <v>-0.008403361344537823</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -33061,6 +34495,12 @@
       <c r="AR239" s="3" t="n">
         <v>0.004614201486798203</v>
       </c>
+      <c r="AS239" s="1" t="n">
+        <v>0.003888</v>
+      </c>
+      <c r="AT239" s="2" t="n">
+        <v>-0.007910181168665419</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -33197,6 +34637,12 @@
       <c r="AR240" s="3" t="n">
         <v>0.002188183807439862</v>
       </c>
+      <c r="AS240" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="AT240" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -33333,6 +34779,12 @@
       <c r="AR241" s="3" t="n">
         <v>0.003834874802616691</v>
       </c>
+      <c r="AS241" s="1" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AT241" s="2" t="n">
+        <v>-0.002471910112359528</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -33469,6 +34921,12 @@
       <c r="AR242" s="3" t="n">
         <v>0.002695417789757419</v>
       </c>
+      <c r="AS242" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="AT242" s="3" t="n">
+        <v>0.001344086021505322</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -33605,6 +35063,12 @@
       <c r="AR243" s="3" t="n">
         <v>0.006233303650934896</v>
       </c>
+      <c r="AS243" s="1" t="n">
+        <v>0.02255</v>
+      </c>
+      <c r="AT243" s="2" t="n">
+        <v>-0.002212389380530884</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -33741,6 +35205,12 @@
       <c r="AR244" s="3" t="n">
         <v>0.003558718861209922</v>
       </c>
+      <c r="AS244" s="1" t="n">
+        <v>0.001692</v>
+      </c>
+      <c r="AT244" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -33877,6 +35347,12 @@
       <c r="AR245" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS245" s="1" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="AT245" s="3" t="n">
+        <v>0.001531393568147058</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -34013,6 +35489,12 @@
       <c r="AR246" s="2" t="n">
         <v>-0.004491498235482875</v>
       </c>
+      <c r="AS246" s="1" t="n">
+        <v>0.03135</v>
+      </c>
+      <c r="AT246" s="3" t="n">
+        <v>0.01031260070899144</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -34149,6 +35631,12 @@
       <c r="AR247" s="3" t="n">
         <v>0.001128031584884252</v>
       </c>
+      <c r="AS247" s="1" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="AT247" s="3" t="n">
+        <v>0.002253521126760628</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -34285,6 +35773,12 @@
       <c r="AR248" s="2" t="n">
         <v>-0.002315580549123408</v>
       </c>
+      <c r="AS248" s="1" t="n">
+        <v>0.03011</v>
+      </c>
+      <c r="AT248" s="2" t="n">
+        <v>-0.001657824933686935</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -34421,6 +35915,12 @@
       <c r="AR249" s="3" t="n">
         <v>0.006700779727095455</v>
       </c>
+      <c r="AS249" s="1" t="n">
+        <v>0.008244</v>
+      </c>
+      <c r="AT249" s="2" t="n">
+        <v>-0.002299406995038112</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -34557,6 +36057,12 @@
       <c r="AR250" s="3" t="n">
         <v>0.006048387096774122</v>
       </c>
+      <c r="AS250" s="1" t="n">
+        <v>0.02012</v>
+      </c>
+      <c r="AT250" s="3" t="n">
+        <v>0.008016032064128278</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -34693,6 +36199,12 @@
       <c r="AR251" s="2" t="n">
         <v>-0.000865426222414504</v>
       </c>
+      <c r="AS251" s="1" t="n">
+        <v>0.04619</v>
+      </c>
+      <c r="AT251" s="3" t="n">
+        <v>0.0002165439584236263</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -34829,6 +36341,12 @@
       <c r="AR252" s="2" t="n">
         <v>-0.0008192883895131159</v>
       </c>
+      <c r="AS252" s="1" t="n">
+        <v>0.00852</v>
+      </c>
+      <c r="AT252" s="2" t="n">
+        <v>-0.001991331849595836</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -34965,6 +36483,12 @@
       <c r="AR253" s="2" t="n">
         <v>-0.009152719665272046</v>
       </c>
+      <c r="AS253" s="1" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="AT253" s="2" t="n">
+        <v>-0.0005278437582475372</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -35101,6 +36625,12 @@
       <c r="AR254" s="3" t="n">
         <v>0.0001641227638273931</v>
       </c>
+      <c r="AS254" s="1" t="n">
+        <v>0.06102</v>
+      </c>
+      <c r="AT254" s="3" t="n">
+        <v>0.001312766655726891</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -35237,6 +36767,12 @@
       <c r="AR255" s="2" t="n">
         <v>-0.001985252410663659</v>
       </c>
+      <c r="AS255" s="1" t="n">
+        <v>0.003525</v>
+      </c>
+      <c r="AT255" s="3" t="n">
+        <v>0.001705029838022145</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -35373,6 +36909,12 @@
       <c r="AR256" s="2" t="n">
         <v>-0.005383177570093395</v>
       </c>
+      <c r="AS256" s="1" t="n">
+        <v>0.013214</v>
+      </c>
+      <c r="AT256" s="2" t="n">
+        <v>-0.006690220251071227</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -35509,6 +37051,12 @@
       <c r="AR257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS257" s="1" t="n">
+        <v>0.999443</v>
+      </c>
+      <c r="AT257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -35645,6 +37193,12 @@
       <c r="AR258" s="2" t="n">
         <v>-0.003294705748693463</v>
       </c>
+      <c r="AS258" s="1" t="n">
+        <v>0.08797000000000001</v>
+      </c>
+      <c r="AT258" s="3" t="n">
+        <v>0.002735666248717703</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -35781,6 +37335,12 @@
       <c r="AR259" s="3" t="n">
         <v>0.0008970621215520366</v>
       </c>
+      <c r="AS259" s="1" t="n">
+        <v>0.08917</v>
+      </c>
+      <c r="AT259" s="2" t="n">
+        <v>-0.001008290387631713</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -35917,6 +37477,12 @@
       <c r="AR260" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS260" s="1" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="AT260" s="2" t="n">
+        <v>-0.004956629491945448</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -36053,6 +37619,12 @@
       <c r="AR261" s="3" t="n">
         <v>0.008787346221441132</v>
       </c>
+      <c r="AS261" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT261" s="3" t="n">
+        <v>0.001742160278745646</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -36189,6 +37761,12 @@
       <c r="AR262" s="3" t="n">
         <v>0.005121638924455729</v>
       </c>
+      <c r="AS262" s="1" t="n">
+        <v>0.003915</v>
+      </c>
+      <c r="AT262" s="2" t="n">
+        <v>-0.002547770700636839</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -36325,6 +37903,12 @@
       <c r="AR263" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS263" s="1" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="AT263" s="3" t="n">
+        <v>0.0008896797153025165</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -36461,6 +38045,12 @@
       <c r="AR264" s="3" t="n">
         <v>0.007841855905897742</v>
       </c>
+      <c r="AS264" s="1" t="n">
+        <v>0.0006195</v>
+      </c>
+      <c r="AT264" s="3" t="n">
+        <v>0.004214621494569725</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -36597,6 +38187,12 @@
       <c r="AR265" s="3" t="n">
         <v>0.0006882312456986461</v>
       </c>
+      <c r="AS265" s="1" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="AT265" s="3" t="n">
+        <v>0.001375515818431856</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -36733,6 +38329,12 @@
       <c r="AR266" s="3" t="n">
         <v>0.001584786053882771</v>
       </c>
+      <c r="AS266" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AT266" s="2" t="n">
+        <v>-0.001582278481012703</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -36869,6 +38471,12 @@
       <c r="AR267" s="3" t="n">
         <v>0.003090234857849285</v>
       </c>
+      <c r="AS267" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="AT267" s="3" t="n">
+        <v>0.002464571780653011</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -37005,6 +38613,12 @@
       <c r="AR268" s="3" t="n">
         <v>0.003261882572227353</v>
       </c>
+      <c r="AS268" s="1" t="n">
+        <v>0.0004323</v>
+      </c>
+      <c r="AT268" s="3" t="n">
+        <v>0.003947979563399877</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -37141,6 +38755,12 @@
       <c r="AR269" s="2" t="n">
         <v>-0.0009638554216868749</v>
       </c>
+      <c r="AS269" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="AT269" s="3" t="n">
+        <v>0.007718282682103253</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -37277,6 +38897,12 @@
       <c r="AR270" s="3" t="n">
         <v>0.007138934651290475</v>
       </c>
+      <c r="AS270" s="1" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="AT270" s="2" t="n">
+        <v>-0.0005452562704472015</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -37413,6 +39039,12 @@
       <c r="AR271" s="3" t="n">
         <v>0.001359619306594004</v>
       </c>
+      <c r="AS271" s="1" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="AT271" s="3" t="n">
+        <v>0.0006788866259335828</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -37549,6 +39181,12 @@
       <c r="AR272" s="3" t="n">
         <v>0.001273560876209743</v>
       </c>
+      <c r="AS272" s="1" t="n">
+        <v>0.03933</v>
+      </c>
+      <c r="AT272" s="3" t="n">
+        <v>0.0005087763927753545</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -37685,6 +39323,12 @@
       <c r="AR273" s="3" t="n">
         <v>0.003257328990228016</v>
       </c>
+      <c r="AS273" s="1" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="AT273" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -37821,6 +39465,12 @@
       <c r="AR274" s="3" t="n">
         <v>0.0007895152376441539</v>
       </c>
+      <c r="AS274" s="1" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="AT274" s="3" t="n">
+        <v>0.0006311139160618356</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -37957,6 +39607,12 @@
       <c r="AR275" s="3" t="n">
         <v>0.001782531194295827</v>
       </c>
+      <c r="AS275" s="1" t="n">
+        <v>0.01124</v>
+      </c>
+      <c r="AT275" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -38093,6 +39749,12 @@
       <c r="AR276" s="3" t="n">
         <v>0.001912777352716273</v>
       </c>
+      <c r="AS276" s="1" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT276" s="3" t="n">
+        <v>0.004200076365024695</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -38229,6 +39891,12 @@
       <c r="AR277" s="3" t="n">
         <v>0.003113026819923328</v>
       </c>
+      <c r="AS277" s="1" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="AT277" s="3" t="n">
+        <v>0.0002387204583433531</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -38365,6 +40033,12 @@
       <c r="AR278" s="2" t="n">
         <v>-0.001025115325474074</v>
       </c>
+      <c r="AS278" s="1" t="n">
+        <v>0.01954</v>
+      </c>
+      <c r="AT278" s="3" t="n">
+        <v>0.002565418163160491</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -38501,6 +40175,12 @@
       <c r="AR279" s="3" t="n">
         <v>0.001936960732523283</v>
       </c>
+      <c r="AS279" s="1" t="n">
+        <v>0.005652</v>
+      </c>
+      <c r="AT279" s="2" t="n">
+        <v>-0.006678383128295227</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -38637,6 +40317,12 @@
       <c r="AR280" s="2" t="n">
         <v>-0.002304147465437783</v>
       </c>
+      <c r="AS280" s="1" t="n">
+        <v>0.03886</v>
+      </c>
+      <c r="AT280" s="2" t="n">
+        <v>-0.002822684115986631</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -38773,6 +40459,12 @@
       <c r="AR281" s="3" t="n">
         <v>0.002212389380530975</v>
       </c>
+      <c r="AS281" s="1" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="AT281" s="3" t="n">
+        <v>0.001103752759381899</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -38909,6 +40601,12 @@
       <c r="AR282" s="3" t="n">
         <v>0.007965242577842207</v>
       </c>
+      <c r="AS282" s="1" t="n">
+        <v>0.0004181</v>
+      </c>
+      <c r="AT282" s="3" t="n">
+        <v>0.001197318007662864</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -39045,6 +40743,12 @@
       <c r="AR283" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AT283" s="3" t="n">
+        <v>0.0002439619419371325</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -39181,6 +40885,12 @@
       <c r="AR284" s="3" t="n">
         <v>0.003096712720342977</v>
       </c>
+      <c r="AS284" s="1" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="AT284" s="2" t="n">
+        <v>-0.000237473284255594</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -39317,6 +41027,12 @@
       <c r="AR285" s="2" t="n">
         <v>-0.001790088562276199</v>
       </c>
+      <c r="AS285" s="1" t="n">
+        <v>0.10615</v>
+      </c>
+      <c r="AT285" s="3" t="n">
+        <v>0.001887682869277884</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -39453,6 +41169,12 @@
       <c r="AR286" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="AT286" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -39589,6 +41311,12 @@
       <c r="AR287" s="2" t="n">
         <v>-0.006422485056594244</v>
       </c>
+      <c r="AS287" s="1" t="n">
+        <v>0.15755</v>
+      </c>
+      <c r="AT287" s="3" t="n">
+        <v>0.008319999999999972</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -39725,6 +41453,12 @@
       <c r="AR288" s="2" t="n">
         <v>-0.0005537098560355301</v>
       </c>
+      <c r="AS288" s="1" t="n">
+        <v>0.1797</v>
+      </c>
+      <c r="AT288" s="2" t="n">
+        <v>-0.004432132963988893</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -39861,6 +41595,12 @@
       <c r="AR289" s="3" t="n">
         <v>0.002669255035185448</v>
       </c>
+      <c r="AS289" s="1" t="n">
+        <v>4.131</v>
+      </c>
+      <c r="AT289" s="2" t="n">
+        <v>-0.0002420135527588204</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -39997,6 +41737,12 @@
       <c r="AR290" s="3" t="n">
         <v>0.0002348520432128479</v>
       </c>
+      <c r="AS290" s="1" t="n">
+        <v>0.08488999999999999</v>
+      </c>
+      <c r="AT290" s="2" t="n">
+        <v>-0.003404555059873356</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -40133,6 +41879,12 @@
       <c r="AR291" s="3" t="n">
         <v>0.001691570341133283</v>
       </c>
+      <c r="AS291" s="1" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="AT291" s="3" t="n">
+        <v>0.000281452293836281</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -40269,6 +42021,12 @@
       <c r="AR292" s="2" t="n">
         <v>-0.002380952380952421</v>
       </c>
+      <c r="AS292" s="1" t="n">
+        <v>1.4726</v>
+      </c>
+      <c r="AT292" s="3" t="n">
+        <v>0.00415956358677122</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -40405,6 +42163,12 @@
       <c r="AR293" s="3" t="n">
         <v>0.001372448104306089</v>
       </c>
+      <c r="AS293" s="1" t="n">
+        <v>0.005834</v>
+      </c>
+      <c r="AT293" s="2" t="n">
+        <v>-0.0005139626520473527</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -40541,6 +42305,12 @@
       <c r="AR294" s="3" t="n">
         <v>0.005281690140845008</v>
       </c>
+      <c r="AS294" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="AT294" s="2" t="n">
+        <v>-0.001751313485113815</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -40677,6 +42447,12 @@
       <c r="AR295" s="2" t="n">
         <v>-0.0005591798695246356</v>
       </c>
+      <c r="AS295" s="1" t="n">
+        <v>0.5359</v>
+      </c>
+      <c r="AT295" s="2" t="n">
+        <v>-0.0005594927265944927</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -40813,6 +42589,12 @@
       <c r="AR296" s="3" t="n">
         <v>0.002667852378834941</v>
       </c>
+      <c r="AS296" s="1" t="n">
+        <v>2.252</v>
+      </c>
+      <c r="AT296" s="2" t="n">
+        <v>-0.001330376940133088</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -40949,6 +42731,12 @@
       <c r="AR297" s="3" t="n">
         <v>0.001800720288115173</v>
       </c>
+      <c r="AS297" s="1" t="n">
+        <v>0.01661</v>
+      </c>
+      <c r="AT297" s="2" t="n">
+        <v>-0.004793289394847226</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -41085,6 +42873,12 @@
       <c r="AR298" s="2" t="n">
         <v>-0.002998909487459078</v>
       </c>
+      <c r="AS298" s="1" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="AT298" s="3" t="n">
+        <v>0.003281378178835053</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -41221,6 +43015,12 @@
       <c r="AR299" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS299" s="1" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="AT299" s="3" t="n">
+        <v>0.001808318264014393</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -41357,6 +43157,12 @@
       <c r="AR300" s="3" t="n">
         <v>0.005376344086021626</v>
       </c>
+      <c r="AS300" s="1" t="n">
+        <v>0.02048</v>
+      </c>
+      <c r="AT300" s="2" t="n">
+        <v>-0.004375303840544472</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -41493,6 +43299,12 @@
       <c r="AR301" s="2" t="n">
         <v>-0.000325839035516419</v>
       </c>
+      <c r="AS301" s="1" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="AT301" s="2" t="n">
+        <v>-0.000651890482399066</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -41629,6 +43441,12 @@
       <c r="AR302" s="3" t="n">
         <v>0.002172338884866076</v>
       </c>
+      <c r="AS302" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="AT302" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -41765,6 +43583,12 @@
       <c r="AR303" s="3" t="n">
         <v>0.001630656339176452</v>
       </c>
+      <c r="AS303" s="1" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="AT303" s="3" t="n">
+        <v>0.0002713336046670211</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -41901,6 +43725,12 @@
       <c r="AR304" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS304" s="1" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="AT304" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -42037,6 +43867,12 @@
       <c r="AR305" s="3" t="n">
         <v>0.002351834430856026</v>
       </c>
+      <c r="AS305" s="1" t="n">
+        <v>0.06403</v>
+      </c>
+      <c r="AT305" s="3" t="n">
+        <v>0.001564210855623383</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -42173,6 +44009,12 @@
       <c r="AR306" s="3" t="n">
         <v>0.002038735983690029</v>
       </c>
+      <c r="AS306" s="1" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="AT306" s="2" t="n">
+        <v>-0.005086469989827065</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -42309,6 +44151,12 @@
       <c r="AR307" s="3" t="n">
         <v>0.003264417845484225</v>
       </c>
+      <c r="AS307" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT307" s="2" t="n">
+        <v>-0.002169197396963125</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -42445,6 +44293,12 @@
       <c r="AR308" s="2" t="n">
         <v>-0.0002523340903355065</v>
       </c>
+      <c r="AS308" s="1" t="n">
+        <v>0.03968</v>
+      </c>
+      <c r="AT308" s="3" t="n">
+        <v>0.001514386673397212</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -42581,6 +44435,12 @@
       <c r="AR309" s="3" t="n">
         <v>0.001954397394136728</v>
       </c>
+      <c r="AS309" s="1" t="n">
+        <v>0.01537</v>
+      </c>
+      <c r="AT309" s="2" t="n">
+        <v>-0.0006501950585175288</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -42717,6 +44577,12 @@
       <c r="AR310" s="3" t="n">
         <v>0.003494574213720723</v>
       </c>
+      <c r="AS310" s="1" t="n">
+        <v>0.05458</v>
+      </c>
+      <c r="AT310" s="3" t="n">
+        <v>0.0003665689149559968</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -42853,6 +44719,12 @@
       <c r="AR311" s="3" t="n">
         <v>0.0002238137869293045</v>
       </c>
+      <c r="AS311" s="1" t="n">
+        <v>0.004459</v>
+      </c>
+      <c r="AT311" s="2" t="n">
+        <v>-0.002237637055269544</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -42989,6 +44861,12 @@
       <c r="AR312" s="2" t="n">
         <v>-0.002724150183584128</v>
       </c>
+      <c r="AS312" s="1" t="n">
+        <v>0.08436</v>
+      </c>
+      <c r="AT312" s="3" t="n">
+        <v>0.001900237529691299</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -43125,6 +45003,12 @@
       <c r="AR313" s="3" t="n">
         <v>0.002430133657351149</v>
       </c>
+      <c r="AS313" s="1" t="n">
+        <v>0.07426000000000001</v>
+      </c>
+      <c r="AT313" s="3" t="n">
+        <v>0.0001346801346802694</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -43261,6 +45145,12 @@
       <c r="AR314" s="3" t="n">
         <v>0.00196979645436653</v>
       </c>
+      <c r="AS314" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="AT314" s="3" t="n">
+        <v>0.001310615989514928</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -43397,6 +45287,12 @@
       <c r="AR315" s="3" t="n">
         <v>0.00188797986154811</v>
       </c>
+      <c r="AS315" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="AT315" s="2" t="n">
+        <v>-0.0006281407035176931</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -43533,6 +45429,12 @@
       <c r="AR316" s="3" t="n">
         <v>0.002239641657334735</v>
       </c>
+      <c r="AS316" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="AT316" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -43669,6 +45571,12 @@
       <c r="AR317" s="3" t="n">
         <v>0.002950248089043894</v>
       </c>
+      <c r="AS317" s="1" t="n">
+        <v>0.007479</v>
+      </c>
+      <c r="AT317" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -43805,6 +45713,12 @@
       <c r="AR318" s="3" t="n">
         <v>0.003729878288182227</v>
       </c>
+      <c r="AS318" s="1" t="n">
+        <v>0.05104</v>
+      </c>
+      <c r="AT318" s="2" t="n">
+        <v>-0.001760219049481709</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -43941,6 +45855,12 @@
       <c r="AR319" s="3" t="n">
         <v>0.002108724400443315</v>
       </c>
+      <c r="AS319" s="1" t="n">
+        <v>0.28078</v>
+      </c>
+      <c r="AT319" s="3" t="n">
+        <v>0.001426635280690334</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -44077,6 +45997,12 @@
       <c r="AR320" s="3" t="n">
         <v>0.002284148012791231</v>
       </c>
+      <c r="AS320" s="1" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="AT320" s="3" t="n">
+        <v>0.0004557885141293937</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -44213,6 +46139,12 @@
       <c r="AR321" s="3" t="n">
         <v>0.005039410776586141</v>
       </c>
+      <c r="AS321" s="1" t="n">
+        <v>0.07797</v>
+      </c>
+      <c r="AT321" s="3" t="n">
+        <v>0.002442787348932833</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -44349,6 +46281,12 @@
       <c r="AR322" s="3" t="n">
         <v>0.0006188118811882225</v>
       </c>
+      <c r="AS322" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="AT322" s="2" t="n">
+        <v>-0.001855287569573423</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -44485,6 +46423,12 @@
       <c r="AR323" s="3" t="n">
         <v>0.002548419979612699</v>
       </c>
+      <c r="AS323" s="1" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT323" s="3" t="n">
+        <v>0.001525165226232787</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -44621,6 +46565,12 @@
       <c r="AR324" s="3" t="n">
         <v>0.002096990535204881</v>
       </c>
+      <c r="AS324" s="1" t="n">
+        <v>0.053045</v>
+      </c>
+      <c r="AT324" s="3" t="n">
+        <v>1.885227358421311e-05</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -44757,6 +46707,12 @@
       <c r="AR325" s="2" t="n">
         <v>-0.001449848424937562</v>
       </c>
+      <c r="AS325" s="1" t="n">
+        <v>0.15106</v>
+      </c>
+      <c r="AT325" s="2" t="n">
+        <v>-0.003035902851108687</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -44893,6 +46849,12 @@
       <c r="AR326" s="3" t="n">
         <v>0.003253292021688642</v>
       </c>
+      <c r="AS326" s="1" t="n">
+        <v>0.006396</v>
+      </c>
+      <c r="AT326" s="2" t="n">
+        <v>-0.01235330450895618</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -45029,6 +46991,12 @@
       <c r="AR327" s="3" t="n">
         <v>0.00257544740143955</v>
       </c>
+      <c r="AS327" s="1" t="n">
+        <v>0.015189</v>
+      </c>
+      <c r="AT327" s="3" t="n">
+        <v>0.0004610723224871599</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -45165,6 +47133,12 @@
       <c r="AR328" s="3" t="n">
         <v>0.002103049421661323</v>
       </c>
+      <c r="AS328" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="AT328" s="2" t="n">
+        <v>-0.002098635886673577</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -45301,6 +47275,12 @@
       <c r="AR329" s="3" t="n">
         <v>0.001376462491397093</v>
       </c>
+      <c r="AS329" s="1" t="n">
+        <v>0.004373</v>
+      </c>
+      <c r="AT329" s="3" t="n">
+        <v>0.001832760595647238</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -45437,6 +47417,12 @@
       <c r="AR330" s="3" t="n">
         <v>0.005406449121451931</v>
       </c>
+      <c r="AS330" s="1" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="AT330" s="3" t="n">
+        <v>0.001152294987516891</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -45573,6 +47559,12 @@
       <c r="AR331" s="2" t="n">
         <v>-0.002529510961214159</v>
       </c>
+      <c r="AS331" s="1" t="n">
+        <v>0.03546</v>
+      </c>
+      <c r="AT331" s="2" t="n">
+        <v>-0.0008453085376162932</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -45709,6 +47701,12 @@
       <c r="AR332" s="2" t="n">
         <v>-0.004078857919782577</v>
       </c>
+      <c r="AS332" s="1" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="AT332" s="3" t="n">
+        <v>0.004778156996587073</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -45845,6 +47843,12 @@
       <c r="AR333" s="2" t="n">
         <v>-0.001044932079414723</v>
       </c>
+      <c r="AS333" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="AT333" s="3" t="n">
+        <v>0.001046025104602395</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -45981,6 +47985,12 @@
       <c r="AR334" s="3" t="n">
         <v>0.001360544217687019</v>
       </c>
+      <c r="AS334" s="1" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="AT334" s="2" t="n">
+        <v>-0.0006793478260868504</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -46117,6 +48127,12 @@
       <c r="AR335" s="3" t="n">
         <v>0.002832861189801798</v>
       </c>
+      <c r="AS335" s="1" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="AT335" s="3" t="n">
+        <v>0.002210759027266023</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -46253,6 +48269,12 @@
       <c r="AR336" s="3" t="n">
         <v>0.00145278450363207</v>
       </c>
+      <c r="AS336" s="1" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AT336" s="3" t="n">
+        <v>0.0009671179883944776</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -46389,6 +48411,12 @@
       <c r="AR337" s="3" t="n">
         <v>0.0009960159362549395</v>
       </c>
+      <c r="AS337" s="1" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="AT337" s="3" t="n">
+        <v>0.001990049751243872</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -46525,6 +48553,12 @@
       <c r="AR338" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS338" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AT338" s="2" t="n">
+        <v>-0.0008841732979664267</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -46661,6 +48695,12 @@
       <c r="AR339" s="3" t="n">
         <v>0.001654715940430159</v>
       </c>
+      <c r="AS339" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="AT339" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -46797,6 +48837,12 @@
       <c r="AR340" s="2" t="n">
         <v>-0.007109859968240118</v>
       </c>
+      <c r="AS340" s="1" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="AT340" s="3" t="n">
+        <v>0.005779506379266403</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -46933,6 +48979,12 @@
       <c r="AR341" s="3" t="n">
         <v>0.0002349072116514696</v>
       </c>
+      <c r="AS341" s="1" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="AT341" s="3" t="n">
+        <v>0.0004697040864255328</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -47069,6 +49121,12 @@
       <c r="AR342" s="2" t="n">
         <v>-0.002164502164502209</v>
       </c>
+      <c r="AS342" s="1" t="n">
+        <v>0.07804999999999999</v>
+      </c>
+      <c r="AT342" s="2" t="n">
+        <v>-0.004083195100165891</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -47205,6 +49263,12 @@
       <c r="AR343" s="3" t="n">
         <v>0.0007902015013828826</v>
       </c>
+      <c r="AS343" s="1" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT343" s="3" t="n">
+        <v>0.0001315962626660674</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -47341,6 +49405,12 @@
       <c r="AR344" s="3" t="n">
         <v>0.001665278934221483</v>
       </c>
+      <c r="AS344" s="1" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="AT344" s="2" t="n">
+        <v>-0.001496259351620967</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -47477,6 +49547,12 @@
       <c r="AR345" s="3" t="n">
         <v>0.002421959095801932</v>
       </c>
+      <c r="AS345" s="1" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AT345" s="3" t="n">
+        <v>0.003221476510067169</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -47613,6 +49689,12 @@
       <c r="AR346" s="2" t="n">
         <v>-0.002409638554216936</v>
       </c>
+      <c r="AS346" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="AT346" s="3" t="n">
+        <v>0.002415458937198137</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -47749,6 +49831,12 @@
       <c r="AR347" s="3" t="n">
         <v>0.004009163802978271</v>
       </c>
+      <c r="AS347" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="AT347" s="3" t="n">
+        <v>0.001711351968054733</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -47885,6 +49973,12 @@
       <c r="AR348" s="3" t="n">
         <v>0.0009627048154494869</v>
       </c>
+      <c r="AS348" s="1" t="n">
+        <v>5199</v>
+      </c>
+      <c r="AT348" s="3" t="n">
+        <v>5.770673437593666e-05</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -48021,6 +50115,12 @@
       <c r="AR349" s="3" t="n">
         <v>0.0007220216606499154</v>
       </c>
+      <c r="AS349" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AT349" s="3" t="n">
+        <v>0.002164502164502076</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -48157,6 +50257,12 @@
       <c r="AR350" s="3" t="n">
         <v>0.006489292667099247</v>
       </c>
+      <c r="AS350" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="AT350" s="3" t="n">
+        <v>0.003223726627981928</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -48293,6 +50399,12 @@
       <c r="AR351" s="3" t="n">
         <v>0.002126267582597281</v>
       </c>
+      <c r="AS351" s="1" t="n">
+        <v>0.0006114</v>
+      </c>
+      <c r="AT351" s="2" t="n">
+        <v>-0.002121756161253431</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -48429,6 +50541,12 @@
       <c r="AR352" s="3" t="n">
         <v>0.001014713343480602</v>
       </c>
+      <c r="AS352" s="1" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="AT352" s="2" t="n">
+        <v>-0.001013684744044737</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -48565,6 +50683,12 @@
       <c r="AR353" s="2" t="n">
         <v>-0.00106894708711907</v>
       </c>
+      <c r="AS353" s="1" t="n">
+        <v>0.09368</v>
+      </c>
+      <c r="AT353" s="3" t="n">
+        <v>0.002461209202782173</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -48701,6 +50825,12 @@
       <c r="AR354" s="3" t="n">
         <v>0.00333704115684103</v>
       </c>
+      <c r="AS354" s="1" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="AT354" s="3" t="n">
+        <v>0.002217294900221639</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -48837,6 +50967,12 @@
       <c r="AR355" s="3" t="n">
         <v>0.0006577865482651039</v>
       </c>
+      <c r="AS355" s="1" t="n">
+        <v>0.0006074</v>
+      </c>
+      <c r="AT355" s="2" t="n">
+        <v>-0.001807723911257145</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -48973,6 +51109,12 @@
       <c r="AR356" s="3" t="n">
         <v>0.001991040318566453</v>
       </c>
+      <c r="AS356" s="1" t="n">
+        <v>2.003</v>
+      </c>
+      <c r="AT356" s="2" t="n">
+        <v>-0.004967709885742567</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -49109,6 +51251,12 @@
       <c r="AR357" s="3" t="n">
         <v>0.004355400696864085</v>
       </c>
+      <c r="AS357" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="AT357" s="2" t="n">
+        <v>-0.0008673026886382994</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -49245,6 +51393,12 @@
       <c r="AR358" s="3" t="n">
         <v>0.002463054187192178</v>
       </c>
+      <c r="AS358" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="AT358" s="3" t="n">
+        <v>0.002457002457002383</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -49381,6 +51535,12 @@
       <c r="AR359" s="3" t="n">
         <v>0.006793478260869524</v>
       </c>
+      <c r="AS359" s="1" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="AT359" s="3" t="n">
+        <v>0.001349527665317201</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -49517,6 +51677,12 @@
       <c r="AR360" s="2" t="n">
         <v>-0.001811047389073326</v>
       </c>
+      <c r="AS360" s="1" t="n">
+        <v>0.003308</v>
+      </c>
+      <c r="AT360" s="3" t="n">
+        <v>0.0003023888720895472</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -49653,6 +51819,12 @@
       <c r="AR361" s="3" t="n">
         <v>0.007456766619070344</v>
       </c>
+      <c r="AS361" s="1" t="n">
+        <v>0.6334</v>
+      </c>
+      <c r="AT361" s="2" t="n">
+        <v>-0.002519685039370151</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -49789,6 +51961,12 @@
       <c r="AR362" s="3" t="n">
         <v>0.005099872503187507</v>
       </c>
+      <c r="AS362" s="1" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="AT362" s="3" t="n">
+        <v>0.002114164904862493</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -49925,6 +52103,12 @@
       <c r="AR363" s="3" t="n">
         <v>0.007799095304944634</v>
       </c>
+      <c r="AS363" s="1" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="AT363" s="3" t="n">
+        <v>0.002166847237269791</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -50061,6 +52245,12 @@
       <c r="AR364" s="3" t="n">
         <v>0.003198976327575108</v>
       </c>
+      <c r="AS364" s="1" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT364" s="2" t="n">
+        <v>-0.0008503401360543282</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -50197,6 +52387,12 @@
       <c r="AR365" s="2" t="n">
         <v>-0.0004170141784820996</v>
       </c>
+      <c r="AS365" s="1" t="n">
+        <v>0.07192999999999999</v>
+      </c>
+      <c r="AT365" s="3" t="n">
+        <v>0.0002781254345708837</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -50333,6 +52529,12 @@
       <c r="AR366" s="2" t="n">
         <v>-0.0001802451333814539</v>
       </c>
+      <c r="AS366" s="1" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AT366" s="3" t="n">
+        <v>0.00162249864791779</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -50469,6 +52671,12 @@
       <c r="AR367" s="3" t="n">
         <v>0.001729206294310961</v>
       </c>
+      <c r="AS367" s="1" t="n">
+        <v>0.05788</v>
+      </c>
+      <c r="AT367" s="2" t="n">
+        <v>-0.0008631106507854554</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -50605,6 +52813,12 @@
       <c r="AR368" s="3" t="n">
         <v>0.0005287275290800537</v>
       </c>
+      <c r="AS368" s="1" t="n">
+        <v>0.05686</v>
+      </c>
+      <c r="AT368" s="3" t="n">
+        <v>0.001585344372027476</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -50741,6 +52955,12 @@
       <c r="AR369" s="2" t="n">
         <v>-0.002906038101388434</v>
       </c>
+      <c r="AS369" s="1" t="n">
+        <v>0.03083</v>
+      </c>
+      <c r="AT369" s="2" t="n">
+        <v>-0.001619170984456005</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -50877,6 +53097,12 @@
       <c r="AR370" s="3" t="n">
         <v>0.00187032418952623</v>
       </c>
+      <c r="AS370" s="1" t="n">
+        <v>0.0001609</v>
+      </c>
+      <c r="AT370" s="3" t="n">
+        <v>0.001244555071561947</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -51013,6 +53239,12 @@
       <c r="AR371" s="3" t="n">
         <v>0.0005903187721369043</v>
       </c>
+      <c r="AS371" s="1" t="n">
+        <v>0.006774</v>
+      </c>
+      <c r="AT371" s="2" t="n">
+        <v>-0.000884955752212379</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -51149,6 +53381,12 @@
       <c r="AR372" s="3" t="n">
         <v>0.003187481889307368</v>
       </c>
+      <c r="AS372" s="1" t="n">
+        <v>0.006925</v>
+      </c>
+      <c r="AT372" s="3" t="n">
+        <v>0.0001444251877527633</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -51285,6 +53523,12 @@
       <c r="AR373" s="3" t="n">
         <v>0.01955161626694478</v>
       </c>
+      <c r="AS373" s="1" t="n">
+        <v>3.863</v>
+      </c>
+      <c r="AT373" s="2" t="n">
+        <v>-0.01227307593965739</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -51421,6 +53665,12 @@
       <c r="AR374" s="2" t="n">
         <v>-0.000430477830391767</v>
       </c>
+      <c r="AS374" s="1" t="n">
+        <v>0.06967</v>
+      </c>
+      <c r="AT374" s="3" t="n">
+        <v>0.0001435544071202429</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -51557,6 +53807,12 @@
       <c r="AR375" s="3" t="n">
         <v>0.004301619433198469</v>
       </c>
+      <c r="AS375" s="1" t="n">
+        <v>0.07992</v>
+      </c>
+      <c r="AT375" s="3" t="n">
+        <v>0.006802721088435358</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -51693,6 +53949,12 @@
       <c r="AR376" s="3" t="n">
         <v>0.003180155827635425</v>
       </c>
+      <c r="AS376" s="1" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="AT376" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -51829,6 +54091,12 @@
       <c r="AR377" s="3" t="n">
         <v>0.001564945226916994</v>
       </c>
+      <c r="AS377" s="1" t="n">
+        <v>0.07666000000000001</v>
+      </c>
+      <c r="AT377" s="2" t="n">
+        <v>-0.001822916666666502</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -51965,6 +54233,12 @@
       <c r="AR378" s="3" t="n">
         <v>0.005956813104988841</v>
       </c>
+      <c r="AS378" s="1" t="n">
+        <v>0.0004047</v>
+      </c>
+      <c r="AT378" s="2" t="n">
+        <v>-0.001480384900073922</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -52101,6 +54375,12 @@
       <c r="AR379" s="3" t="n">
         <v>0.0006811989100816688</v>
       </c>
+      <c r="AS379" s="1" t="n">
+        <v>0.07335</v>
+      </c>
+      <c r="AT379" s="2" t="n">
+        <v>-0.0013614703880191</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -52237,6 +54517,12 @@
       <c r="AR380" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS380" s="1" t="n">
+        <v>0.00138</v>
+      </c>
+      <c r="AT380" s="3" t="n">
+        <v>0.001451378809869254</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -52373,6 +54659,12 @@
       <c r="AR381" s="3" t="n">
         <v>0.001417769376181528</v>
       </c>
+      <c r="AS381" s="1" t="n">
+        <v>6.357</v>
+      </c>
+      <c r="AT381" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -52509,6 +54801,12 @@
       <c r="AR382" s="3" t="n">
         <v>0.0007168458781361714</v>
       </c>
+      <c r="AS382" s="1" t="n">
+        <v>0.01396</v>
+      </c>
+      <c r="AT382" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -52645,6 +54943,12 @@
       <c r="AR383" s="2" t="n">
         <v>-0.001723147616312394</v>
       </c>
+      <c r="AS383" s="1" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="AT383" s="3" t="n">
+        <v>0.001150747986190977</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -52781,6 +55085,12 @@
       <c r="AR384" s="3" t="n">
         <v>0.0009891196834817297</v>
       </c>
+      <c r="AS384" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="AT384" s="3" t="n">
+        <v>0.003952569169960451</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -52917,6 +55227,12 @@
       <c r="AR385" s="3" t="n">
         <v>0.002238137869292701</v>
       </c>
+      <c r="AS385" s="1" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="AT385" s="3" t="n">
+        <v>0.00223313979455129</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -53053,6 +55369,12 @@
       <c r="AR386" s="2" t="n">
         <v>-0.003819709702062653</v>
       </c>
+      <c r="AS386" s="1" t="n">
+        <v>0.001313</v>
+      </c>
+      <c r="AT386" s="3" t="n">
+        <v>0.006901840490797465</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -53189,6 +55511,12 @@
       <c r="AR387" s="3" t="n">
         <v>0.002558417192563504</v>
       </c>
+      <c r="AS387" s="1" t="n">
+        <v>0.0005876</v>
+      </c>
+      <c r="AT387" s="2" t="n">
+        <v>-0.0003402517863218865</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -53325,6 +55653,12 @@
       <c r="AR388" s="3" t="n">
         <v>0.00176991150442486</v>
       </c>
+      <c r="AS388" s="1" t="n">
+        <v>0.01129</v>
+      </c>
+      <c r="AT388" s="2" t="n">
+        <v>-0.002650176678445275</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -53461,6 +55795,12 @@
       <c r="AR389" s="3" t="n">
         <v>0.001112347052280266</v>
       </c>
+      <c r="AS389" s="1" t="n">
+        <v>0.00899</v>
+      </c>
+      <c r="AT389" s="2" t="n">
+        <v>-0.001111111111111066</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -53597,6 +55937,12 @@
       <c r="AR390" s="3" t="n">
         <v>0.001277955271565532</v>
       </c>
+      <c r="AS390" s="1" t="n">
+        <v>0.07832</v>
+      </c>
+      <c r="AT390" s="2" t="n">
+        <v>-0.000382897255903028</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -53733,6 +56079,12 @@
       <c r="AR391" s="3" t="n">
         <v>0.004648460197559504</v>
       </c>
+      <c r="AS391" s="1" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="AT391" s="3" t="n">
+        <v>0.0005783689994216743</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -53869,6 +56221,12 @@
       <c r="AR392" s="3" t="n">
         <v>0.004255319148936182</v>
       </c>
+      <c r="AS392" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="AT392" s="2" t="n">
+        <v>-0.004237288135593232</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -54005,6 +56363,12 @@
       <c r="AR393" s="3" t="n">
         <v>0.004253308128544414</v>
       </c>
+      <c r="AS393" s="1" t="n">
+        <v>0.02139</v>
+      </c>
+      <c r="AT393" s="3" t="n">
+        <v>0.006588235294117542</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -54141,6 +56505,12 @@
       <c r="AR394" s="3" t="n">
         <v>0.002492522432701897</v>
       </c>
+      <c r="AS394" s="1" t="n">
+        <v>0.2017</v>
+      </c>
+      <c r="AT394" s="3" t="n">
+        <v>0.002983590253605119</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -54277,6 +56647,12 @@
       <c r="AR395" s="3" t="n">
         <v>0.001027749229188108</v>
       </c>
+      <c r="AS395" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="AT395" s="2" t="n">
+        <v>-0.001026694045174567</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -54413,6 +56789,12 @@
       <c r="AR396" s="3" t="n">
         <v>0.009114108640174959</v>
       </c>
+      <c r="AS396" s="1" t="n">
+        <v>2.771</v>
+      </c>
+      <c r="AT396" s="3" t="n">
+        <v>0.001083815028901775</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -54549,6 +56931,12 @@
       <c r="AR397" s="3" t="n">
         <v>0.003159557661927333</v>
       </c>
+      <c r="AS397" s="1" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="AT397" s="3" t="n">
+        <v>0.0015748031496063</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -54685,6 +57073,12 @@
       <c r="AR398" s="3" t="n">
         <v>0.002518557794273584</v>
       </c>
+      <c r="AS398" s="1" t="n">
+        <v>0.007516</v>
+      </c>
+      <c r="AT398" s="2" t="n">
+        <v>-0.006214465159328331</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -54821,6 +57215,12 @@
       <c r="AR399" s="2" t="n">
         <v>-0.001953888237592811</v>
       </c>
+      <c r="AS399" s="1" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="AT399" s="3" t="n">
+        <v>0.001566170712607719</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -54957,6 +57357,12 @@
       <c r="AR400" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS400" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AT400" s="2" t="n">
+        <v>-0.00188916876574304</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -55093,6 +57499,12 @@
       <c r="AR401" s="3" t="n">
         <v>0.000968322036242919</v>
       </c>
+      <c r="AS401" s="1" t="n">
+        <v>0.007209</v>
+      </c>
+      <c r="AT401" s="2" t="n">
+        <v>-0.003731343283582105</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -55229,6 +57641,12 @@
       <c r="AR402" s="3" t="n">
         <v>0.001973684210526387</v>
       </c>
+      <c r="AS402" s="1" t="n">
+        <v>0.004568</v>
+      </c>
+      <c r="AT402" s="2" t="n">
+        <v>-0.0002188662727074048</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -55365,6 +57783,12 @@
       <c r="AR403" s="2" t="n">
         <v>-0.002272727272727233</v>
       </c>
+      <c r="AS403" s="1" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="AT403" s="3" t="n">
+        <v>0.001518602885345315</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -55501,6 +57925,12 @@
       <c r="AR404" s="3" t="n">
         <v>0.002557544757033203</v>
       </c>
+      <c r="AS404" s="1" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="AT404" s="2" t="n">
+        <v>-0.006377551020408169</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -55637,6 +58067,12 @@
       <c r="AR405" s="2" t="n">
         <v>-0.003153100548873072</v>
       </c>
+      <c r="AS405" s="1" t="n">
+        <v>0.0008592</v>
+      </c>
+      <c r="AT405" s="3" t="n">
+        <v>0.006560449859418837</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -55773,6 +58209,12 @@
       <c r="AR406" s="3" t="n">
         <v>0.0005974905397330274</v>
       </c>
+      <c r="AS406" s="1" t="n">
+        <v>0.005022</v>
+      </c>
+      <c r="AT406" s="2" t="n">
+        <v>-0.0003980891719744025</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -55909,6 +58351,12 @@
       <c r="AR407" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS407" s="1" t="n">
+        <v>0.01193</v>
+      </c>
+      <c r="AT407" s="2" t="n">
+        <v>-0.001673640167364094</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -56045,6 +58493,12 @@
       <c r="AR408" s="3" t="n">
         <v>0.004013377926421357</v>
       </c>
+      <c r="AS408" s="1" t="n">
+        <v>0.001527</v>
+      </c>
+      <c r="AT408" s="3" t="n">
+        <v>0.01732178547634909</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -56181,6 +58635,12 @@
       <c r="AR409" s="3" t="n">
         <v>0.0007737941707506383</v>
       </c>
+      <c r="AS409" s="1" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="AT409" s="2" t="n">
+        <v>-0.00128865979381447</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -56317,6 +58777,12 @@
       <c r="AR410" s="2" t="n">
         <v>-0.003082614056719973</v>
       </c>
+      <c r="AS410" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AT410" s="3" t="n">
+        <v>0.001855287569573208</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -56453,6 +58919,12 @@
       <c r="AR411" s="3" t="n">
         <v>0.001054296257248317</v>
       </c>
+      <c r="AS411" s="1" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="AT411" s="3" t="n">
+        <v>0.002632964718272777</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -56589,6 +59061,12 @@
       <c r="AR412" s="2" t="n">
         <v>-0.001184132622853711</v>
       </c>
+      <c r="AS412" s="1" t="n">
+        <v>0.06734999999999999</v>
+      </c>
+      <c r="AT412" s="2" t="n">
+        <v>-0.001926496739774824</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -56725,6 +59203,12 @@
       <c r="AR413" s="2" t="n">
         <v>-0.003165809259992085</v>
       </c>
+      <c r="AS413" s="1" t="n">
+        <v>2519</v>
+      </c>
+      <c r="AT413" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -56861,6 +59345,12 @@
       <c r="AR414" s="3" t="n">
         <v>0.00761179828734534</v>
       </c>
+      <c r="AS414" s="1" t="n">
+        <v>0.05271</v>
+      </c>
+      <c r="AT414" s="2" t="n">
+        <v>-0.004532577903682666</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -56997,6 +59487,12 @@
       <c r="AR415" s="2" t="n">
         <v>-0.001146131805157594</v>
       </c>
+      <c r="AS415" s="1" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="AT415" s="3" t="n">
+        <v>0.002294893861158923</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -57133,6 +59629,12 @@
       <c r="AR416" s="3" t="n">
         <v>0.001315020455873654</v>
       </c>
+      <c r="AS416" s="1" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="AT416" s="3" t="n">
+        <v>0.001021450459652716</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -57269,6 +59771,12 @@
       <c r="AR417" s="3" t="n">
         <v>0.01369863013698631</v>
       </c>
+      <c r="AS417" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AT417" s="2" t="n">
+        <v>-0.01351351351351353</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -57405,6 +59913,12 @@
       <c r="AR418" s="3" t="n">
         <v>0.0006640106241699135</v>
       </c>
+      <c r="AS418" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="AT418" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -57541,6 +60055,12 @@
       <c r="AR419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AT419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -57677,6 +60197,12 @@
       <c r="AR420" s="2" t="n">
         <v>-0.001570680628272187</v>
       </c>
+      <c r="AS420" s="1" t="n">
+        <v>0.01911</v>
+      </c>
+      <c r="AT420" s="3" t="n">
+        <v>0.002097535395909721</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -57813,6 +60339,12 @@
       <c r="AR421" s="2" t="n">
         <v>-0.002322580645161321</v>
       </c>
+      <c r="AS421" s="1" t="n">
+        <v>0.19437</v>
+      </c>
+      <c r="AT421" s="3" t="n">
+        <v>0.005535437144335166</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -57949,6 +60481,12 @@
       <c r="AR422" s="3" t="n">
         <v>0.003239104829211011</v>
       </c>
+      <c r="AS422" s="1" t="n">
+        <v>0.03412</v>
+      </c>
+      <c r="AT422" s="3" t="n">
+        <v>0.001467566774288068</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -58085,6 +60623,12 @@
       <c r="AR423" s="3" t="n">
         <v>0.001420454545454389</v>
       </c>
+      <c r="AS423" s="1" t="n">
+        <v>0.1414</v>
+      </c>
+      <c r="AT423" s="3" t="n">
+        <v>0.002836879432624195</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -58221,6 +60765,12 @@
       <c r="AR424" s="3" t="n">
         <v>0.003795066413662249</v>
       </c>
+      <c r="AS424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AT424" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -58357,6 +60907,12 @@
       <c r="AR425" s="3" t="n">
         <v>0.002890173410404573</v>
       </c>
+      <c r="AS425" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AT425" s="2" t="n">
+        <v>-0.0009606147934678469</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -58493,6 +61049,12 @@
       <c r="AR426" s="3" t="n">
         <v>0.001136040897472337</v>
       </c>
+      <c r="AS426" s="1" t="n">
+        <v>0.007039</v>
+      </c>
+      <c r="AT426" s="2" t="n">
+        <v>-0.001560283687943223</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -58629,6 +61191,12 @@
       <c r="AR427" s="2" t="n">
         <v>-0.001167315175097364</v>
       </c>
+      <c r="AS427" s="1" t="n">
+        <v>0.02568</v>
+      </c>
+      <c r="AT427" s="3" t="n">
+        <v>0.0003895597974290247</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -58765,6 +61333,12 @@
       <c r="AR428" s="2" t="n">
         <v>-0.0007462686567165169</v>
       </c>
+      <c r="AS428" s="1" t="n">
+        <v>0.008042000000000001</v>
+      </c>
+      <c r="AT428" s="3" t="n">
+        <v>0.0009957679860593805</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -58901,6 +61475,12 @@
       <c r="AR429" s="2" t="n">
         <v>-0.001633986928104509</v>
       </c>
+      <c r="AS429" s="1" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="AT429" s="3" t="n">
+        <v>0.004091653027823216</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -59037,6 +61617,12 @@
       <c r="AR430" s="3" t="n">
         <v>0.002106847253574135</v>
       </c>
+      <c r="AS430" s="1" t="n">
+        <v>0.06654</v>
+      </c>
+      <c r="AT430" s="2" t="n">
+        <v>-0.0007508634930168868</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -59173,6 +61759,12 @@
       <c r="AR431" s="3" t="n">
         <v>0.003669724770642212</v>
       </c>
+      <c r="AS431" s="1" t="n">
+        <v>0.00547</v>
+      </c>
+      <c r="AT431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -59309,6 +61901,12 @@
       <c r="AR432" s="2" t="n">
         <v>-0.002101944298476005</v>
       </c>
+      <c r="AS432" s="1" t="n">
+        <v>0.009516999999999999</v>
+      </c>
+      <c r="AT432" s="3" t="n">
+        <v>0.002317008952079984</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -59445,6 +62043,12 @@
       <c r="AR433" s="3" t="n">
         <v>0.003912937148447063</v>
       </c>
+      <c r="AS433" s="1" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="AT433" s="3" t="n">
+        <v>0.001218026796589391</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -59581,6 +62185,12 @@
       <c r="AR434" s="3" t="n">
         <v>0.003512880562060828</v>
       </c>
+      <c r="AS434" s="1" t="n">
+        <v>0.04262</v>
+      </c>
+      <c r="AT434" s="2" t="n">
+        <v>-0.005367561260210059</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -59717,6 +62327,12 @@
       <c r="AR435" s="3" t="n">
         <v>0.001295336787564798</v>
       </c>
+      <c r="AS435" s="1" t="n">
+        <v>0.001547</v>
+      </c>
+      <c r="AT435" s="3" t="n">
+        <v>0.0006468305304009804</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -59853,6 +62469,12 @@
       <c r="AR436" s="3" t="n">
         <v>0.009130752373995498</v>
       </c>
+      <c r="AS436" s="1" t="n">
+        <v>0.02758</v>
+      </c>
+      <c r="AT436" s="2" t="n">
+        <v>-0.001809627216793267</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -59989,6 +62611,12 @@
       <c r="AR437" s="2" t="n">
         <v>-0.001089588377724052</v>
       </c>
+      <c r="AS437" s="1" t="n">
+        <v>0.08225</v>
+      </c>
+      <c r="AT437" s="2" t="n">
+        <v>-0.003151133195976201</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -60125,6 +62753,12 @@
       <c r="AR438" s="3" t="n">
         <v>0.0008733624454147509</v>
       </c>
+      <c r="AS438" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="AT438" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -60261,6 +62895,12 @@
       <c r="AR439" s="2" t="n">
         <v>-0.001290322580645162</v>
       </c>
+      <c r="AS439" s="1" t="n">
+        <v>1.549</v>
+      </c>
+      <c r="AT439" s="3" t="n">
+        <v>0.0006459948320412725</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -60397,6 +63037,12 @@
       <c r="AR440" s="3" t="n">
         <v>0.003858875413450852</v>
       </c>
+      <c r="AS440" s="1" t="n">
+        <v>0.00182</v>
+      </c>
+      <c r="AT440" s="2" t="n">
+        <v>-0.0005491488193299923</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -60533,6 +63179,12 @@
       <c r="AR441" s="2" t="n">
         <v>-0.0002726281352234494</v>
       </c>
+      <c r="AS441" s="1" t="n">
+        <v>0.03671</v>
+      </c>
+      <c r="AT441" s="3" t="n">
+        <v>0.001090809926370285</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -60669,6 +63321,12 @@
       <c r="AR442" s="3" t="n">
         <v>0.00274574409665008</v>
       </c>
+      <c r="AS442" s="1" t="n">
+        <v>0.01829</v>
+      </c>
+      <c r="AT442" s="3" t="n">
+        <v>0.00164293537787526</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -60805,6 +63463,12 @@
       <c r="AR443" s="3" t="n">
         <v>0.001500434336255198</v>
       </c>
+      <c r="AS443" s="1" t="n">
+        <v>0.12685</v>
+      </c>
+      <c r="AT443" s="3" t="n">
+        <v>0.0002365557483047015</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -60941,6 +63605,12 @@
       <c r="AR444" s="2" t="n">
         <v>-0.003660768761439935</v>
       </c>
+      <c r="AS444" s="1" t="n">
+        <v>0.011428</v>
+      </c>
+      <c r="AT444" s="2" t="n">
+        <v>-0.0002624442306009562</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -61077,6 +63747,12 @@
       <c r="AR445" s="3" t="n">
         <v>0.001370033628098132</v>
       </c>
+      <c r="AS445" s="1" t="n">
+        <v>0.08031000000000001</v>
+      </c>
+      <c r="AT445" s="2" t="n">
+        <v>-0.001119402985074538</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -61213,6 +63889,12 @@
       <c r="AR446" s="3" t="n">
         <v>0.0004686035613870779</v>
       </c>
+      <c r="AS446" s="1" t="n">
+        <v>0.0002138</v>
+      </c>
+      <c r="AT446" s="3" t="n">
+        <v>0.001405152224824263</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -61349,6 +64031,12 @@
       <c r="AR447" s="3" t="n">
         <v>0.003021148036253784</v>
       </c>
+      <c r="AS447" s="1" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="AT447" s="3" t="n">
+        <v>0.003012048192771092</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -61485,6 +64173,12 @@
       <c r="AR448" s="3" t="n">
         <v>0.01108089050065482</v>
       </c>
+      <c r="AS448" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="AT448" s="2" t="n">
+        <v>-0.004682674105808491</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -61621,6 +64315,12 @@
       <c r="AR449" s="3" t="n">
         <v>0.0005977286312013843</v>
       </c>
+      <c r="AS449" s="1" t="n">
+        <v>0.001678</v>
+      </c>
+      <c r="AT449" s="3" t="n">
+        <v>0.002389486260454061</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -61757,6 +64457,12 @@
       <c r="AR450" s="2" t="n">
         <v>-0.0004830917874396253</v>
       </c>
+      <c r="AS450" s="1" t="n">
+        <v>0.0002067</v>
+      </c>
+      <c r="AT450" s="2" t="n">
+        <v>-0.0009666505558239622</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -61893,6 +64599,12 @@
       <c r="AR451" s="2" t="n">
         <v>-0.001152073732718801</v>
       </c>
+      <c r="AS451" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT451" s="2" t="n">
+        <v>-0.0003844675124952542</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -62029,6 +64741,12 @@
       <c r="AR452" s="3" t="n">
         <v>0.002233804914370772</v>
       </c>
+      <c r="AS452" s="1" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="AT452" s="3" t="n">
+        <v>0.002228826151560139</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -62165,6 +64883,12 @@
       <c r="AR453" s="3" t="n">
         <v>0.001152073732718922</v>
       </c>
+      <c r="AS453" s="1" t="n">
+        <v>0.0001736</v>
+      </c>
+      <c r="AT453" s="2" t="n">
+        <v>-0.001150747986191052</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -62301,6 +65025,12 @@
       <c r="AR454" s="3" t="n">
         <v>0.01345811051693415</v>
       </c>
+      <c r="AS454" s="1" t="n">
+        <v>0.11298</v>
+      </c>
+      <c r="AT454" s="2" t="n">
+        <v>-0.006419839943716545</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -62437,6 +65167,12 @@
       <c r="AR455" s="3" t="n">
         <v>0.002402883460152252</v>
       </c>
+      <c r="AS455" s="1" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="AT455" s="3" t="n">
+        <v>0.0001997602876547922</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -62573,6 +65309,12 @@
       <c r="AR456" s="3" t="n">
         <v>6.258997308615701e-05</v>
       </c>
+      <c r="AS456" s="1" t="n">
+        <v>0.016003</v>
+      </c>
+      <c r="AT456" s="3" t="n">
+        <v>0.00156465139566909</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -62709,6 +65451,12 @@
       <c r="AR457" s="3" t="n">
         <v>0.003597122302158231</v>
       </c>
+      <c r="AS457" s="1" t="n">
+        <v>0.006696</v>
+      </c>
+      <c r="AT457" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -62845,6 +65593,12 @@
       <c r="AR458" s="3" t="n">
         <v>0.001039284971939191</v>
       </c>
+      <c r="AS458" s="1" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="AT458" s="2" t="n">
+        <v>-0.0008305647840530648</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -62981,6 +65735,12 @@
       <c r="AR459" s="3" t="n">
         <v>0.001577535888941409</v>
       </c>
+      <c r="AS459" s="1" t="n">
+        <v>0.006365</v>
+      </c>
+      <c r="AT459" s="3" t="n">
+        <v>0.002520081902661898</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -63117,6 +65877,12 @@
       <c r="AR460" s="2" t="n">
         <v>-0.0007315288953912874</v>
       </c>
+      <c r="AS460" s="1" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="AT460" s="3" t="n">
+        <v>0.002196193265007282</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -63253,6 +66019,12 @@
       <c r="AR461" s="3" t="n">
         <v>0.0006678539626000736</v>
       </c>
+      <c r="AS461" s="1" t="n">
+        <v>0.09026000000000001</v>
+      </c>
+      <c r="AT461" s="3" t="n">
+        <v>0.004004449388209267</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -63389,6 +66161,12 @@
       <c r="AR462" s="2" t="n">
         <v>-0.00222172850477678</v>
       </c>
+      <c r="AS462" s="1" t="n">
+        <v>0.04478</v>
+      </c>
+      <c r="AT462" s="2" t="n">
+        <v>-0.002894678245379608</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -63525,6 +66303,12 @@
       <c r="AR463" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="AT463" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -63661,6 +66445,12 @@
       <c r="AR464" s="3" t="n">
         <v>0.0007710100231303871</v>
       </c>
+      <c r="AS464" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT464" s="3" t="n">
+        <v>0.001540832049306627</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -63797,6 +66587,12 @@
       <c r="AR465" s="3" t="n">
         <v>0.000722543352601277</v>
       </c>
+      <c r="AS465" s="1" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="AT465" s="2" t="n">
+        <v>-0.0007220216606499403</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -63933,6 +66729,12 @@
       <c r="AR466" s="3" t="n">
         <v>0.002123142250530709</v>
       </c>
+      <c r="AS466" s="1" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="AT466" s="2" t="n">
+        <v>-0.000706214689265459</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -64069,6 +66871,12 @@
       <c r="AR467" s="3" t="n">
         <v>0.001573976915005182</v>
       </c>
+      <c r="AS467" s="1" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="AT467" s="3" t="n">
+        <v>0.0005238344683079933</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -64205,6 +67013,12 @@
       <c r="AR468" s="3" t="n">
         <v>0.004004004004004014</v>
       </c>
+      <c r="AS468" s="1" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="AT468" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -64341,6 +67155,12 @@
       <c r="AR469" s="3" t="n">
         <v>0.001269357705001271</v>
       </c>
+      <c r="AS469" s="1" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="AT469" s="2" t="n">
+        <v>-0.0002535496957403372</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -64477,6 +67297,12 @@
       <c r="AR470" s="3" t="n">
         <v>0.003432494279176205</v>
       </c>
+      <c r="AS470" s="1" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="AT470" s="3" t="n">
+        <v>0.001140250855188142</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -64613,6 +67439,12 @@
       <c r="AR471" s="3" t="n">
         <v>0.002187499999999898</v>
       </c>
+      <c r="AS471" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT471" s="2" t="n">
+        <v>-0.002182725288431454</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -64749,6 +67581,12 @@
       <c r="AR472" s="3" t="n">
         <v>0.00716161375029844</v>
       </c>
+      <c r="AS472" s="1" t="n">
+        <v>0.04205</v>
+      </c>
+      <c r="AT472" s="2" t="n">
+        <v>-0.00331832187722212</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -64885,6 +67723,12 @@
       <c r="AR473" s="3" t="n">
         <v>0.004811547714514661</v>
       </c>
+      <c r="AS473" s="1" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="AT473" s="2" t="n">
+        <v>-0.0007980845969671908</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -65021,6 +67865,12 @@
       <c r="AR474" s="3" t="n">
         <v>0.003401759530791935</v>
       </c>
+      <c r="AS474" s="1" t="n">
+        <v>0.008566000000000001</v>
+      </c>
+      <c r="AT474" s="3" t="n">
+        <v>0.001402852466682237</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -65157,6 +68007,12 @@
       <c r="AR475" s="3" t="n">
         <v>0.008571428571428553</v>
       </c>
+      <c r="AS475" s="1" t="n">
+        <v>0.04243</v>
+      </c>
+      <c r="AT475" s="3" t="n">
+        <v>0.001652502360717673</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -65293,6 +68149,12 @@
       <c r="AR476" s="3" t="n">
         <v>0.00383239652529375</v>
       </c>
+      <c r="AS476" s="1" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="AT476" s="2" t="n">
+        <v>-0.003563247645711409</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -65429,6 +68291,12 @@
       <c r="AR477" s="2" t="n">
         <v>-0.002270230684730902</v>
       </c>
+      <c r="AS477" s="1" t="n">
+        <v>0.13617</v>
+      </c>
+      <c r="AT477" s="2" t="n">
+        <v>-0.000513799177921218</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -65565,6 +68433,12 @@
       <c r="AR478" s="3" t="n">
         <v>0.001273885350318419</v>
       </c>
+      <c r="AS478" s="1" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="AT478" s="3" t="n">
+        <v>0.0008481764206954701</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -65701,6 +68575,12 @@
       <c r="AR479" s="3" t="n">
         <v>0.001882175795219197</v>
       </c>
+      <c r="AS479" s="1" t="n">
+        <v>0.005319</v>
+      </c>
+      <c r="AT479" s="2" t="n">
+        <v>-0.0007514559458951087</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -65837,6 +68717,12 @@
       <c r="AR480" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS480" s="1" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AT480" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -65973,6 +68859,12 @@
       <c r="AR481" s="3" t="n">
         <v>0.0007931262392598083</v>
       </c>
+      <c r="AS481" s="1" t="n">
+        <v>0.07573000000000001</v>
+      </c>
+      <c r="AT481" s="3" t="n">
+        <v>0.0002641658961828837</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -66109,6 +69001,12 @@
       <c r="AR482" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS482" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="AT482" s="3" t="n">
+        <v>0.001344989912575718</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -66245,6 +69143,12 @@
       <c r="AR483" s="2" t="n">
         <v>-0.004000000000000115</v>
       </c>
+      <c r="AS483" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AT483" s="3" t="n">
+        <v>0.004016064257028227</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -66381,6 +69285,12 @@
       <c r="AR484" s="3" t="n">
         <v>0.005123428039124312</v>
       </c>
+      <c r="AS484" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="AT484" s="2" t="n">
+        <v>-0.001853568118628284</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -66517,6 +69427,12 @@
       <c r="AR485" s="3" t="n">
         <v>0.00239607044447097</v>
       </c>
+      <c r="AS485" s="1" t="n">
+        <v>0.008378</v>
+      </c>
+      <c r="AT485" s="3" t="n">
+        <v>0.001314688657822468</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -66653,6 +69569,12 @@
       <c r="AR486" s="2" t="n">
         <v>-0.0005350454788656585</v>
       </c>
+      <c r="AS486" s="1" t="n">
+        <v>0.007475</v>
+      </c>
+      <c r="AT486" s="3" t="n">
+        <v>0.0004014989293361256</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -66789,6 +69711,12 @@
       <c r="AR487" s="3" t="n">
         <v>0.0008936550491510533</v>
       </c>
+      <c r="AS487" s="1" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="AT487" s="2" t="n">
+        <v>-0.006250000000000055</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -66925,6 +69853,12 @@
       <c r="AR488" s="2" t="n">
         <v>-0.001928433683308405</v>
       </c>
+      <c r="AS488" s="1" t="n">
+        <v>0.009315</v>
+      </c>
+      <c r="AT488" s="2" t="n">
+        <v>-0.0001073422069556962</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -67061,6 +69995,12 @@
       <c r="AR489" s="3" t="n">
         <v>0.007981462409886658</v>
       </c>
+      <c r="AS489" s="1" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="AT489" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -67197,6 +70137,12 @@
       <c r="AR490" s="3" t="n">
         <v>0.002777295608401326</v>
       </c>
+      <c r="AS490" s="1" t="n">
+        <v>0.05785</v>
+      </c>
+      <c r="AT490" s="3" t="n">
+        <v>0.001384801800242284</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -67333,6 +70279,12 @@
       <c r="AR491" s="3" t="n">
         <v>0.002059732234809391</v>
       </c>
+      <c r="AS491" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="AT491" s="2" t="n">
+        <v>-0.002055498458376073</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -67469,6 +70421,12 @@
       <c r="AR492" s="3" t="n">
         <v>0.0007587253414263201</v>
       </c>
+      <c r="AS492" s="1" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="AT492" s="3" t="n">
+        <v>0.002274450341167637</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -67605,6 +70563,12 @@
       <c r="AR493" s="3" t="n">
         <v>0.0002855511136492325</v>
       </c>
+      <c r="AS493" s="1" t="n">
+        <v>0.03509</v>
+      </c>
+      <c r="AT493" s="3" t="n">
+        <v>0.001712817584927334</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -67741,6 +70705,12 @@
       <c r="AR494" s="3" t="n">
         <v>0.0005927682276229753</v>
       </c>
+      <c r="AS494" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="AT494" s="2" t="n">
+        <v>-0.001184834123222701</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -67877,6 +70847,12 @@
       <c r="AR495" s="2" t="n">
         <v>-0.0002134471718250387</v>
       </c>
+      <c r="AS495" s="1" t="n">
+        <v>0.04684</v>
+      </c>
+      <c r="AT495" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -68013,6 +70989,12 @@
       <c r="AR496" s="3" t="n">
         <v>0.0006239600665557871</v>
       </c>
+      <c r="AS496" s="1" t="n">
+        <v>0.04816</v>
+      </c>
+      <c r="AT496" s="3" t="n">
+        <v>0.001039284971939336</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -68149,6 +71131,12 @@
       <c r="AR497" s="3" t="n">
         <v>0.005661140315406439</v>
       </c>
+      <c r="AS497" s="1" t="n">
+        <v>0.04971</v>
+      </c>
+      <c r="AT497" s="2" t="n">
+        <v>-0.0006031363088058353</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -68285,6 +71273,12 @@
       <c r="AR498" s="3" t="n">
         <v>0.0003445899379737732</v>
       </c>
+      <c r="AS498" s="1" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AT498" s="3" t="n">
+        <v>0.0037891836031691</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -68421,6 +71415,12 @@
       <c r="AR499" s="3" t="n">
         <v>0.0003673769287288354</v>
       </c>
+      <c r="AS499" s="1" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="AT499" s="2" t="n">
+        <v>-0.001468968049944956</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -68557,6 +71557,12 @@
       <c r="AR500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS500" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="AT500" s="3" t="n">
+        <v>0.003759398496240611</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -68693,6 +71699,12 @@
       <c r="AR501" s="2" t="n">
         <v>-0.003093363329583773</v>
       </c>
+      <c r="AS501" s="1" t="n">
+        <v>0.03568</v>
+      </c>
+      <c r="AT501" s="3" t="n">
+        <v>0.006488011283497913</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -68829,6 +71841,12 @@
       <c r="AR502" s="2" t="n">
         <v>-0.003441802252815988</v>
       </c>
+      <c r="AS502" s="1" t="n">
+        <v>0.03188</v>
+      </c>
+      <c r="AT502" s="3" t="n">
+        <v>0.000941915227629366</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -68965,6 +71983,12 @@
       <c r="AR503" s="3" t="n">
         <v>0.001947798987144447</v>
       </c>
+      <c r="AS503" s="1" t="n">
+        <v>0.007707</v>
+      </c>
+      <c r="AT503" s="2" t="n">
+        <v>-0.001166407465007706</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -69101,6 +72125,12 @@
       <c r="AR504" s="3" t="n">
         <v>0.0009966777408638252</v>
       </c>
+      <c r="AS504" s="1" t="n">
+        <v>3.011</v>
+      </c>
+      <c r="AT504" s="2" t="n">
+        <v>-0.0006637902422833654</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -69237,6 +72267,12 @@
       <c r="AR505" s="2" t="n">
         <v>-0.001617904813266859</v>
       </c>
+      <c r="AS505" s="1" t="n">
+        <v>0.0007412</v>
+      </c>
+      <c r="AT505" s="3" t="n">
+        <v>0.0009453072248481719</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -69373,6 +72409,12 @@
       <c r="AR506" s="3" t="n">
         <v>0.001374570446735435</v>
       </c>
+      <c r="AS506" s="1" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AT506" s="3" t="n">
+        <v>0.001029512697323344</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -69509,6 +72551,12 @@
       <c r="AR507" s="3" t="n">
         <v>0.0003514938488576916</v>
       </c>
+      <c r="AS507" s="1" t="n">
+        <v>0.002858</v>
+      </c>
+      <c r="AT507" s="3" t="n">
+        <v>0.0042164441321152</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -69645,6 +72693,12 @@
       <c r="AR508" s="2" t="n">
         <v>-0.001422250316055732</v>
       </c>
+      <c r="AS508" s="1" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="AT508" s="2" t="n">
+        <v>-0.001582528881152126</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -69781,6 +72835,12 @@
       <c r="AR509" s="3" t="n">
         <v>0.0036101083032491</v>
       </c>
+      <c r="AS509" s="1" t="n">
+        <v>2.221</v>
+      </c>
+      <c r="AT509" s="2" t="n">
+        <v>-0.001348920863309404</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -69917,6 +72977,12 @@
       <c r="AR510" s="3" t="n">
         <v>0.0004111842105264001</v>
       </c>
+      <c r="AS510" s="1" t="n">
+        <v>0.0007291</v>
+      </c>
+      <c r="AT510" s="2" t="n">
+        <v>-0.001096040553500506</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -70053,6 +73119,12 @@
       <c r="AR511" s="3" t="n">
         <v>0.0007296607077708062</v>
       </c>
+      <c r="AS511" s="1" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="AT511" s="2" t="n">
+        <v>-0.001093693036820879</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -70189,6 +73261,12 @@
       <c r="AR512" s="2" t="n">
         <v>-0.0008305647840531763</v>
       </c>
+      <c r="AS512" s="1" t="n">
+        <v>0.0004822</v>
+      </c>
+      <c r="AT512" s="3" t="n">
+        <v>0.002078137988362478</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -70325,6 +73403,12 @@
       <c r="AR513" s="3" t="n">
         <v>0.002549162418062659</v>
       </c>
+      <c r="AS513" s="1" t="n">
+        <v>0.05494</v>
+      </c>
+      <c r="AT513" s="2" t="n">
+        <v>-0.002179440610243282</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -70461,6 +73545,12 @@
       <c r="AR514" s="3" t="n">
         <v>0.0006640106241699597</v>
       </c>
+      <c r="AS514" s="1" t="n">
+        <v>0.03017</v>
+      </c>
+      <c r="AT514" s="3" t="n">
+        <v>0.0009953550099535094</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -70597,6 +73687,12 @@
       <c r="AR515" s="3" t="n">
         <v>0.001759014951627132</v>
       </c>
+      <c r="AS515" s="1" t="n">
+        <v>0.001138</v>
+      </c>
+      <c r="AT515" s="2" t="n">
+        <v>-0.0008779631255488435</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -70733,6 +73829,12 @@
       <c r="AR516" s="2" t="n">
         <v>-0.0004559963520291125</v>
       </c>
+      <c r="AS516" s="1" t="n">
+        <v>0.006583</v>
+      </c>
+      <c r="AT516" s="3" t="n">
+        <v>0.001064476885644778</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -70869,6 +73971,12 @@
       <c r="AR517" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS517" s="1" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="AT517" s="3" t="n">
+        <v>0.00075169130543729</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -71005,6 +74113,12 @@
       <c r="AR518" s="3" t="n">
         <v>0.001937984496124086</v>
       </c>
+      <c r="AS518" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="AT518" s="2" t="n">
+        <v>-0.0009671179883946118</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -71141,6 +74255,12 @@
       <c r="AR519" s="2" t="n">
         <v>-0.001152073732718847</v>
       </c>
+      <c r="AS519" s="1" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="AT519" s="2" t="n">
+        <v>-0.003460207612456806</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -71277,6 +74397,12 @@
       <c r="AR520" s="3" t="n">
         <v>0.002499999999999898</v>
       </c>
+      <c r="AS520" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="AT520" s="2" t="n">
+        <v>-0.005610972568578455</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -71413,6 +74539,12 @@
       <c r="AR521" s="3" t="n">
         <v>0.002808988764045024</v>
       </c>
+      <c r="AS521" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="AT521" s="2" t="n">
+        <v>-0.0005602240896358314</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -71549,6 +74681,12 @@
       <c r="AR522" s="3" t="n">
         <v>0.001835985312117428</v>
       </c>
+      <c r="AS522" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="AT522" s="2" t="n">
+        <v>-0.001832620647525888</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -71685,6 +74823,12 @@
       <c r="AR523" s="3" t="n">
         <v>0.000484261501210718</v>
       </c>
+      <c r="AS523" s="1" t="n">
+        <v>0.004133</v>
+      </c>
+      <c r="AT523" s="3" t="n">
+        <v>0.0002420135527589866</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -71821,6 +74965,12 @@
       <c r="AR524" s="3" t="n">
         <v>0.0007037297677691479</v>
       </c>
+      <c r="AS524" s="1" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="AT524" s="2" t="n">
+        <v>-0.0007032348804500417</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -71957,6 +75107,12 @@
       <c r="AR525" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS525" s="1" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="AT525" s="2" t="n">
+        <v>-0.004048582995951393</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -72093,6 +75249,12 @@
       <c r="AR526" s="3" t="n">
         <v>0.0008375209380233583</v>
       </c>
+      <c r="AS526" s="1" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="AT526" s="2" t="n">
+        <v>-0.0008368200836819163</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -72229,6 +75391,12 @@
       <c r="AR527" s="3" t="n">
         <v>0.01092131055726691</v>
       </c>
+      <c r="AS527" s="1" t="n">
+        <v>0.07235999999999999</v>
+      </c>
+      <c r="AT527" s="3" t="n">
+        <v>0.002216066481994369</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -72365,6 +75533,12 @@
       <c r="AR528" s="3" t="n">
         <v>0.0006976744186047034</v>
       </c>
+      <c r="AS528" s="1" t="n">
+        <v>0.04303</v>
+      </c>
+      <c r="AT528" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -72501,6 +75675,12 @@
       <c r="AR529" s="3" t="n">
         <v>0.004769475357710789</v>
       </c>
+      <c r="AS529" s="1" t="n">
+        <v>0.06332</v>
+      </c>
+      <c r="AT529" s="3" t="n">
+        <v>0.001898734177215112</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -72637,6 +75817,12 @@
       <c r="AR530" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS530" s="1" t="n">
+        <v>0.005015</v>
+      </c>
+      <c r="AT530" s="2" t="n">
+        <v>-0.001393866985264847</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -72773,6 +75959,12 @@
       <c r="AR531" s="3" t="n">
         <v>0.003088803088802963</v>
       </c>
+      <c r="AS531" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="AT531" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -72909,6 +76101,12 @@
       <c r="AR532" s="3" t="n">
         <v>0.0009373828271466336</v>
       </c>
+      <c r="AS532" s="1" t="n">
+        <v>0.05346</v>
+      </c>
+      <c r="AT532" s="3" t="n">
+        <v>0.001311106948866841</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -73045,6 +76243,12 @@
       <c r="AR533" s="3" t="n">
         <v>0.004555198285101846</v>
       </c>
+      <c r="AS533" s="1" t="n">
+        <v>0.003756</v>
+      </c>
+      <c r="AT533" s="3" t="n">
+        <v>0.001867164577220493</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -73181,6 +76385,12 @@
       <c r="AR534" s="3" t="n">
         <v>0.00117164616285885</v>
       </c>
+      <c r="AS534" s="1" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="AT534" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -73317,6 +76527,12 @@
       <c r="AR535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AT535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -73453,6 +76669,12 @@
       <c r="AR536" s="3" t="n">
         <v>0.005233219567690561</v>
       </c>
+      <c r="AS536" s="1" t="n">
+        <v>0.0004403</v>
+      </c>
+      <c r="AT536" s="2" t="n">
+        <v>-0.003395201448619245</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -73589,6 +76811,12 @@
       <c r="AR537" s="3" t="n">
         <v>0.001044932079414795</v>
       </c>
+      <c r="AS537" s="1" t="n">
+        <v>0.00958</v>
+      </c>
+      <c r="AT537" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -73725,6 +76953,12 @@
       <c r="AR538" s="3" t="n">
         <v>0.00110192837465573</v>
       </c>
+      <c r="AS538" s="1" t="n">
+        <v>0.05451</v>
+      </c>
+      <c r="AT538" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -73861,6 +77095,12 @@
       <c r="AR539" s="2" t="n">
         <v>-0.001907276995305117</v>
       </c>
+      <c r="AS539" s="1" t="n">
+        <v>0.6807</v>
+      </c>
+      <c r="AT539" s="3" t="n">
+        <v>0.0005879758929883227</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -73997,6 +77237,12 @@
       <c r="AR540" s="3" t="n">
         <v>0.002656042496679838</v>
       </c>
+      <c r="AS540" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="AT540" s="2" t="n">
+        <v>-0.001324503311258316</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -74133,6 +77379,12 @@
       <c r="AR541" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AS541" s="1" t="n">
+        <v>0.01296</v>
+      </c>
+      <c r="AT541" s="2" t="n">
+        <v>-0.000771010023130403</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -74269,6 +77521,12 @@
       <c r="AR542" s="2" t="n">
         <v>-0.00358937544867191</v>
       </c>
+      <c r="AS542" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="AT542" s="2" t="n">
+        <v>-0.002881844380403466</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -74405,6 +77663,12 @@
       <c r="AR543" s="3" t="n">
         <v>0.001758087201125226</v>
       </c>
+      <c r="AS543" s="1" t="n">
+        <v>0.05707</v>
+      </c>
+      <c r="AT543" s="3" t="n">
+        <v>0.001579501579501576</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT543"/>
+  <dimension ref="A1:AV543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,8 @@
     <col width="18" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
     <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,6 +707,16 @@
           <t>change_05:30</t>
         </is>
       </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>price_05:45</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>change_05:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -847,6 +859,12 @@
       <c r="AT2" s="2" t="n">
         <v>-0.00144695790603306</v>
       </c>
+      <c r="AU2" s="1" t="n">
+        <v>70247.7</v>
+      </c>
+      <c r="AV2" s="2" t="n">
+        <v>-7.117164180166741e-05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -989,6 +1007,12 @@
       <c r="AT3" s="2" t="n">
         <v>-0.002372663047952048</v>
       </c>
+      <c r="AU3" s="1" t="n">
+        <v>2059.64</v>
+      </c>
+      <c r="AV3" s="2" t="n">
+        <v>-0.0003154895670027477</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1131,6 +1155,12 @@
       <c r="AT4" s="2" t="n">
         <v>-0.002427184466019345</v>
       </c>
+      <c r="AU4" s="1" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="AV4" s="2" t="n">
+        <v>-0.0009268914378403231</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1273,6 +1303,12 @@
       <c r="AT5" s="3" t="n">
         <v>0.005389332837762406</v>
       </c>
+      <c r="AU5" s="1" t="n">
+        <v>0.010724</v>
+      </c>
+      <c r="AV5" s="2" t="n">
+        <v>-0.008872458410351256</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1415,6 +1451,12 @@
       <c r="AT6" s="2" t="n">
         <v>-0.001091861988644515</v>
       </c>
+      <c r="AU6" s="1" t="n">
+        <v>1.3729</v>
+      </c>
+      <c r="AV6" s="3" t="n">
+        <v>0.0004372221817386387</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1557,6 +1599,12 @@
       <c r="AT7" s="2" t="n">
         <v>-0.001484466122362435</v>
       </c>
+      <c r="AU7" s="1" t="n">
+        <v>0.09417</v>
+      </c>
+      <c r="AV7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1699,6 +1747,12 @@
       <c r="AT8" s="2" t="n">
         <v>-0.0002950881240443916</v>
       </c>
+      <c r="AU8" s="1" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="AV8" s="2" t="n">
+        <v>-0.000161004669135411</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1841,6 +1895,12 @@
       <c r="AT9" s="3" t="n">
         <v>0.002042066571370285</v>
       </c>
+      <c r="AU9" s="1" t="n">
+        <v>0.04841</v>
+      </c>
+      <c r="AV9" s="2" t="n">
+        <v>-0.01345017322192787</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1983,6 +2043,12 @@
       <c r="AT10" s="3" t="n">
         <v>0.004072324482814752</v>
       </c>
+      <c r="AU10" s="1" t="n">
+        <v>18.415</v>
+      </c>
+      <c r="AV10" s="2" t="n">
+        <v>-0.004163962794722136</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2125,6 +2191,12 @@
       <c r="AT11" s="2" t="n">
         <v>-0.0008290473631689219</v>
       </c>
+      <c r="AU11" s="1" t="n">
+        <v>651.29</v>
+      </c>
+      <c r="AV11" s="3" t="n">
+        <v>0.0007375424471044057</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2267,6 +2339,12 @@
       <c r="AT12" s="2" t="n">
         <v>-0.009721097095243563</v>
       </c>
+      <c r="AU12" s="1" t="n">
+        <v>0.8653</v>
+      </c>
+      <c r="AV12" s="3" t="n">
+        <v>0.0112188851232908</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2409,6 +2487,12 @@
       <c r="AT13" s="2" t="n">
         <v>-0.0001920860545525378</v>
       </c>
+      <c r="AU13" s="1" t="n">
+        <v>208.32</v>
+      </c>
+      <c r="AV13" s="3" t="n">
+        <v>0.0005763688760807135</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2551,6 +2635,12 @@
       <c r="AT14" s="3" t="n">
         <v>0.002615440115440097</v>
       </c>
+      <c r="AU14" s="1" t="n">
+        <v>0.0033351</v>
+      </c>
+      <c r="AV14" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2693,6 +2783,12 @@
       <c r="AT15" s="3" t="n">
         <v>0.01026995305164315</v>
       </c>
+      <c r="AU15" s="1" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AV15" s="2" t="n">
+        <v>-0.01732984800077447</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2835,6 +2931,12 @@
       <c r="AT16" s="2" t="n">
         <v>-0.001947519475194765</v>
       </c>
+      <c r="AU16" s="1" t="n">
+        <v>0.9756</v>
+      </c>
+      <c r="AV16" s="3" t="n">
+        <v>0.001951319708329067</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2977,6 +3079,12 @@
       <c r="AT17" s="3" t="n">
         <v>0.007692307692307779</v>
       </c>
+      <c r="AU17" s="1" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="AV17" s="2" t="n">
+        <v>-0.003816793893129748</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3119,6 +3227,12 @@
       <c r="AT18" s="3" t="n">
         <v>0.003389990112528967</v>
       </c>
+      <c r="AU18" s="1" t="n">
+        <v>213.64</v>
+      </c>
+      <c r="AV18" s="3" t="n">
+        <v>0.002486978555675345</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3261,6 +3375,12 @@
       <c r="AT19" s="2" t="n">
         <v>-0.001143292682926915</v>
       </c>
+      <c r="AU19" s="1" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="AV19" s="3" t="n">
+        <v>0.001526135062953115</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3403,6 +3523,12 @@
       <c r="AT20" s="3" t="n">
         <v>0.006164058795637738</v>
       </c>
+      <c r="AU20" s="1" t="n">
+        <v>0.016922</v>
+      </c>
+      <c r="AV20" s="2" t="n">
+        <v>-0.003180961357210294</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3545,6 +3671,12 @@
       <c r="AT21" s="2" t="n">
         <v>-0.002488335925349832</v>
       </c>
+      <c r="AU21" s="1" t="n">
+        <v>9.622999999999999</v>
+      </c>
+      <c r="AV21" s="3" t="n">
+        <v>0.0002078785988981282</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3687,6 +3819,12 @@
       <c r="AT22" s="2" t="n">
         <v>-0.001813784764207949</v>
       </c>
+      <c r="AU22" s="1" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="AV22" s="3" t="n">
+        <v>0.001817080557238006</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3829,6 +3967,12 @@
       <c r="AT23" s="3" t="n">
         <v>0.002128761291065009</v>
       </c>
+      <c r="AU23" s="1" t="n">
+        <v>0.34553</v>
+      </c>
+      <c r="AV23" s="2" t="n">
+        <v>-0.008123779997703523</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3971,6 +4115,12 @@
       <c r="AT24" s="2" t="n">
         <v>-0.004624277456647403</v>
       </c>
+      <c r="AU24" s="1" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="AV24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4113,6 +4263,12 @@
       <c r="AT25" s="2" t="n">
         <v>-0.0009992228266903899</v>
       </c>
+      <c r="AU25" s="1" t="n">
+        <v>8.994999999999999</v>
+      </c>
+      <c r="AV25" s="2" t="n">
+        <v>-0.0003334074238719842</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4255,6 +4411,12 @@
       <c r="AT26" s="3" t="n">
         <v>0.004474272930648774</v>
       </c>
+      <c r="AU26" s="1" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="AV26" s="3" t="n">
+        <v>0.001484780994803268</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4397,6 +4559,12 @@
       <c r="AT27" s="3" t="n">
         <v>0.0004514805617987127</v>
       </c>
+      <c r="AU27" s="1" t="n">
+        <v>5102.71</v>
+      </c>
+      <c r="AV27" s="3" t="n">
+        <v>0.001189016314638125</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4539,6 +4707,12 @@
       <c r="AT28" s="2" t="n">
         <v>-0.0008396305625525398</v>
       </c>
+      <c r="AU28" s="1" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="AV28" s="3" t="n">
+        <v>0.002240896358543482</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4681,6 +4855,12 @@
       <c r="AT29" s="3" t="n">
         <v>0.002271006813020525</v>
       </c>
+      <c r="AU29" s="1" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="AV29" s="3" t="n">
+        <v>0.007552870090634448</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4823,6 +5003,12 @@
       <c r="AT30" s="2" t="n">
         <v>-0.003129244682862972</v>
       </c>
+      <c r="AU30" s="1" t="n">
+        <v>0.57602</v>
+      </c>
+      <c r="AV30" s="2" t="n">
+        <v>-0.006502354300695167</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4965,6 +5151,12 @@
       <c r="AT31" s="3" t="n">
         <v>0.0004816955684006257</v>
       </c>
+      <c r="AU31" s="1" t="n">
+        <v>0.002079</v>
+      </c>
+      <c r="AV31" s="3" t="n">
+        <v>0.0009629272989890543</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5107,6 +5299,12 @@
       <c r="AT32" s="3" t="n">
         <v>0.003480816831683128</v>
       </c>
+      <c r="AU32" s="1" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="AV32" s="3" t="n">
+        <v>0.0005395822092038425</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5249,6 +5447,12 @@
       <c r="AT33" s="3" t="n">
         <v>0.0152238805970149</v>
       </c>
+      <c r="AU33" s="1" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AV33" s="2" t="n">
+        <v>-0.001764187003822374</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5391,6 +5595,12 @@
       <c r="AT34" s="2" t="n">
         <v>-0.0006631299734748753</v>
       </c>
+      <c r="AU34" s="1" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="AV34" s="3" t="n">
+        <v>0.0006635700066357743</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5533,6 +5743,12 @@
       <c r="AT35" s="2" t="n">
         <v>-0.0005940332658628483</v>
       </c>
+      <c r="AU35" s="1" t="n">
+        <v>454.27</v>
+      </c>
+      <c r="AV35" s="3" t="n">
+        <v>4.402861860205132e-05</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5675,6 +5891,12 @@
       <c r="AT36" s="3" t="n">
         <v>0.001261829652996794</v>
       </c>
+      <c r="AU36" s="1" t="n">
+        <v>0.04768</v>
+      </c>
+      <c r="AV36" s="3" t="n">
+        <v>0.001470279353077098</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5817,6 +6039,12 @@
       <c r="AT37" s="2" t="n">
         <v>-0.0007116424708227383</v>
       </c>
+      <c r="AU37" s="1" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="AV37" s="2" t="n">
+        <v>-0.0001424298532972354</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5959,6 +6187,12 @@
       <c r="AT38" s="3" t="n">
         <v>0.001901140684410569</v>
       </c>
+      <c r="AU38" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="AV38" s="2" t="n">
+        <v>-0.0009487666034154554</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6101,6 +6335,12 @@
       <c r="AT39" s="3" t="n">
         <v>0.0009945750452079515</v>
       </c>
+      <c r="AU39" s="1" t="n">
+        <v>110.91</v>
+      </c>
+      <c r="AV39" s="3" t="n">
+        <v>0.001806521542769423</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6243,6 +6483,12 @@
       <c r="AT40" s="2" t="n">
         <v>-0.009184525466184163</v>
       </c>
+      <c r="AU40" s="1" t="n">
+        <v>0.03558</v>
+      </c>
+      <c r="AV40" s="2" t="n">
+        <v>-0.0005617977528089658</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6385,6 +6631,12 @@
       <c r="AT41" s="3" t="n">
         <v>0.001657458563535908</v>
       </c>
+      <c r="AU41" s="1" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="AV41" s="2" t="n">
+        <v>-0.01268615554329846</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6527,6 +6779,12 @@
       <c r="AT42" s="3" t="n">
         <v>0.0001840942562591681</v>
       </c>
+      <c r="AU42" s="1" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="AV42" s="3" t="n">
+        <v>0.001104362230811748</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6669,6 +6927,12 @@
       <c r="AT43" s="3" t="n">
         <v>0.004569687738004489</v>
       </c>
+      <c r="AU43" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="AV43" s="3" t="n">
+        <v>0.003032600454890155</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6811,6 +7075,12 @@
       <c r="AT44" s="3" t="n">
         <v>0.0005107252298264212</v>
       </c>
+      <c r="AU44" s="1" t="n">
+        <v>0.005883</v>
+      </c>
+      <c r="AV44" s="3" t="n">
+        <v>0.00102092904543133</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6953,6 +7223,12 @@
       <c r="AT45" s="2" t="n">
         <v>-0.00172029953450722</v>
       </c>
+      <c r="AU45" s="1" t="n">
+        <v>0.09787999999999999</v>
+      </c>
+      <c r="AV45" s="2" t="n">
+        <v>-0.007805372529143505</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7095,6 +7371,12 @@
       <c r="AT46" s="2" t="n">
         <v>-0.01056938288441858</v>
       </c>
+      <c r="AU46" s="1" t="n">
+        <v>2.904</v>
+      </c>
+      <c r="AV46" s="3" t="n">
+        <v>0.0006891798759475464</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7237,6 +7519,12 @@
       <c r="AT47" s="3" t="n">
         <v>0.0004501385041551904</v>
       </c>
+      <c r="AU47" s="1" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AV47" s="3" t="n">
+        <v>0.0005883778077735212</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7379,6 +7667,12 @@
       <c r="AT48" s="3" t="n">
         <v>0.004703668861712139</v>
       </c>
+      <c r="AU48" s="1" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="AV48" s="2" t="n">
+        <v>-0.003745318352060032</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7521,6 +7815,12 @@
       <c r="AT49" s="2" t="n">
         <v>-0.001817055544084229</v>
       </c>
+      <c r="AU49" s="1" t="n">
+        <v>0.24351</v>
+      </c>
+      <c r="AV49" s="3" t="n">
+        <v>0.00744694054859127</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7663,6 +7963,12 @@
       <c r="AT50" s="2" t="n">
         <v>-0.007306677491374045</v>
       </c>
+      <c r="AU50" s="1" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="AV50" s="3" t="n">
+        <v>0.01001840114496008</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7805,6 +8111,12 @@
       <c r="AT51" s="2" t="n">
         <v>-0.002053915275994867</v>
       </c>
+      <c r="AU51" s="1" t="n">
+        <v>3.885</v>
+      </c>
+      <c r="AV51" s="2" t="n">
+        <v>-0.0005145356315925454</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7947,6 +8259,12 @@
       <c r="AT52" s="2" t="n">
         <v>-0.01702127659574463</v>
       </c>
+      <c r="AU52" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="AV52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8089,6 +8407,12 @@
       <c r="AT53" s="3" t="n">
         <v>0.002379535990481924</v>
       </c>
+      <c r="AU53" s="1" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="AV53" s="3" t="n">
+        <v>0.003560830860534062</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8231,6 +8555,12 @@
       <c r="AT54" s="3" t="n">
         <v>0.004859086491739524</v>
       </c>
+      <c r="AU54" s="1" t="n">
+        <v>0.04153</v>
+      </c>
+      <c r="AV54" s="3" t="n">
+        <v>0.004110251450676899</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8373,6 +8703,12 @@
       <c r="AT55" s="2" t="n">
         <v>-0.005651998385143369</v>
       </c>
+      <c r="AU55" s="1" t="n">
+        <v>0.12289</v>
+      </c>
+      <c r="AV55" s="2" t="n">
+        <v>-0.002111246447421814</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8515,6 +8851,12 @@
       <c r="AT56" s="3" t="n">
         <v>0.00603749602796318</v>
       </c>
+      <c r="AU56" s="1" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="AV56" s="2" t="n">
+        <v>-0.007580543272267888</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8657,6 +8999,12 @@
       <c r="AT57" s="3" t="n">
         <v>0.002601908065915049</v>
       </c>
+      <c r="AU57" s="1" t="n">
+        <v>0.01159</v>
+      </c>
+      <c r="AV57" s="3" t="n">
+        <v>0.002595155709342455</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8799,6 +9147,12 @@
       <c r="AT58" s="3" t="n">
         <v>0.002004008016032122</v>
       </c>
+      <c r="AU58" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="AV58" s="3" t="n">
+        <v>0.0009999999999998899</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8941,6 +9295,12 @@
       <c r="AT59" s="3" t="n">
         <v>0.006024096385542185</v>
       </c>
+      <c r="AU59" s="1" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="AV59" s="3" t="n">
+        <v>0.002994011976047912</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9083,6 +9443,12 @@
       <c r="AT60" s="2" t="n">
         <v>-0.0006443298969073244</v>
       </c>
+      <c r="AU60" s="1" t="n">
+        <v>0.1551</v>
+      </c>
+      <c r="AV60" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9225,6 +9591,12 @@
       <c r="AT61" s="2" t="n">
         <v>-0.001501971337380251</v>
       </c>
+      <c r="AU61" s="1" t="n">
+        <v>0.15976</v>
+      </c>
+      <c r="AV61" s="3" t="n">
+        <v>0.001316201817612132</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9367,6 +9739,12 @@
       <c r="AT62" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU62" s="1" t="n">
+        <v>0.7122000000000001</v>
+      </c>
+      <c r="AV62" s="3" t="n">
+        <v>0.003381234150465017</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9509,6 +9887,12 @@
       <c r="AT63" s="2" t="n">
         <v>-0.007306542676851624</v>
       </c>
+      <c r="AU63" s="1" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AV63" s="2" t="n">
+        <v>-0.003011040481766443</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9651,6 +10035,12 @@
       <c r="AT64" s="2" t="n">
         <v>-0.0002796811634736772</v>
       </c>
+      <c r="AU64" s="1" t="n">
+        <v>0.007156</v>
+      </c>
+      <c r="AV64" s="3" t="n">
+        <v>0.0009791579241852093</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9793,6 +10183,12 @@
       <c r="AT65" s="3" t="n">
         <v>0.02076970067196091</v>
       </c>
+      <c r="AU65" s="1" t="n">
+        <v>0.03358</v>
+      </c>
+      <c r="AV65" s="3" t="n">
+        <v>0.004787552363853993</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9935,6 +10331,12 @@
       <c r="AT66" s="3" t="n">
         <v>0.00431034482758621</v>
       </c>
+      <c r="AU66" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AV66" s="3" t="n">
+        <v>0.004291845493562235</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10077,6 +10479,12 @@
       <c r="AT67" s="3" t="n">
         <v>0.003071253071253142</v>
       </c>
+      <c r="AU67" s="1" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="AV67" s="3" t="n">
+        <v>0.01408450704225347</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10219,6 +10627,12 @@
       <c r="AT68" s="2" t="n">
         <v>-0.002781166138082478</v>
       </c>
+      <c r="AU68" s="1" t="n">
+        <v>2.0653</v>
+      </c>
+      <c r="AV68" s="3" t="n">
+        <v>0.01051962031509936</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10361,6 +10775,12 @@
       <c r="AT69" s="3" t="n">
         <v>0.003379520108144646</v>
       </c>
+      <c r="AU69" s="1" t="n">
+        <v>0.5943000000000001</v>
+      </c>
+      <c r="AV69" s="3" t="n">
+        <v>0.0008420343550017783</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10503,6 +10923,12 @@
       <c r="AT70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AV70" s="3" t="n">
+        <v>0.04807692307692312</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10645,6 +11071,12 @@
       <c r="AT71" s="3" t="n">
         <v>0.0001102292768959314</v>
       </c>
+      <c r="AU71" s="1" t="n">
+        <v>0.9089</v>
+      </c>
+      <c r="AV71" s="3" t="n">
+        <v>0.001763474043866467</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10787,6 +11219,12 @@
       <c r="AT72" s="3" t="n">
         <v>0.0006860278984677955</v>
       </c>
+      <c r="AU72" s="1" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="AV72" s="3" t="n">
+        <v>0.005255941499085978</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10929,6 +11367,12 @@
       <c r="AT73" s="2" t="n">
         <v>-0.002126528442317829</v>
       </c>
+      <c r="AU73" s="1" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="AV73" s="3" t="n">
+        <v>0.0005327650506126211</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11071,6 +11515,12 @@
       <c r="AT74" s="2" t="n">
         <v>-0.002596952908587356</v>
       </c>
+      <c r="AU74" s="1" t="n">
+        <v>1.1439</v>
+      </c>
+      <c r="AV74" s="2" t="n">
+        <v>-0.0072036104842909</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11213,6 +11663,12 @@
       <c r="AT75" s="3" t="n">
         <v>0.00311720698254373</v>
       </c>
+      <c r="AU75" s="1" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="AV75" s="3" t="n">
+        <v>0.001243008079552466</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11355,6 +11811,12 @@
       <c r="AT76" s="3" t="n">
         <v>0.0001640958319658044</v>
       </c>
+      <c r="AU76" s="1" t="n">
+        <v>0.12277</v>
+      </c>
+      <c r="AV76" s="3" t="n">
+        <v>0.007136997538966445</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11497,6 +11959,12 @@
       <c r="AT77" s="3" t="n">
         <v>0.005097706032285499</v>
       </c>
+      <c r="AU77" s="1" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="AV77" s="3" t="n">
+        <v>0.001690617075232391</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11639,6 +12107,12 @@
       <c r="AT78" s="3" t="n">
         <v>0.0009910802775025061</v>
       </c>
+      <c r="AU78" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AV78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11781,6 +12255,12 @@
       <c r="AT79" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" s="1" t="n">
+        <v>0.006024</v>
+      </c>
+      <c r="AV79" s="3" t="n">
+        <v>0.001496259351620858</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11923,6 +12403,12 @@
       <c r="AT80" s="3" t="n">
         <v>0.008868617762574291</v>
       </c>
+      <c r="AU80" s="1" t="n">
+        <v>0.007927999999999999</v>
+      </c>
+      <c r="AV80" s="2" t="n">
+        <v>-0.004395328393821463</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12065,6 +12551,12 @@
       <c r="AT81" s="2" t="n">
         <v>-0.005047672462142449</v>
       </c>
+      <c r="AU81" s="1" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AV81" s="3" t="n">
+        <v>0.003382187147688967</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -12207,6 +12699,12 @@
       <c r="AT82" s="3" t="n">
         <v>0.0198198198198198</v>
       </c>
+      <c r="AU82" s="1" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="AV82" s="3" t="n">
+        <v>0.006478209658421613</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -12349,6 +12847,12 @@
       <c r="AT83" s="3" t="n">
         <v>0.0004870920603993618</v>
       </c>
+      <c r="AU83" s="1" t="n">
+        <v>8.228999999999999</v>
+      </c>
+      <c r="AV83" s="3" t="n">
+        <v>0.001582278481012646</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -12491,6 +12995,12 @@
       <c r="AT84" s="3" t="n">
         <v>0.001755130927105462</v>
       </c>
+      <c r="AU84" s="1" t="n">
+        <v>353.21</v>
+      </c>
+      <c r="AV84" s="2" t="n">
+        <v>-0.001865091700342004</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12633,6 +13143,12 @@
       <c r="AT85" s="3" t="n">
         <v>0.00500625782227786</v>
       </c>
+      <c r="AU85" s="1" t="n">
+        <v>0.004029</v>
+      </c>
+      <c r="AV85" s="3" t="n">
+        <v>0.003486924034869055</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12775,6 +13291,12 @@
       <c r="AT86" s="3" t="n">
         <v>0.00259581615513803</v>
       </c>
+      <c r="AU86" s="1" t="n">
+        <v>0.13189</v>
+      </c>
+      <c r="AV86" s="3" t="n">
+        <v>0.004340542187024178</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -12917,6 +13439,12 @@
       <c r="AT87" s="3" t="n">
         <v>0.002176278563656059</v>
       </c>
+      <c r="AU87" s="1" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="AV87" s="3" t="n">
+        <v>0.0005428881650379801</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13059,6 +13587,12 @@
       <c r="AT88" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU88" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="AV88" s="2" t="n">
+        <v>-0.0008873114463177568</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13201,6 +13735,12 @@
       <c r="AT89" s="3" t="n">
         <v>0.001715265866209264</v>
       </c>
+      <c r="AU89" s="1" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="AV89" s="3" t="n">
+        <v>0.003082191780821959</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13343,6 +13883,12 @@
       <c r="AT90" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU90" s="1" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="AV90" s="3" t="n">
+        <v>0.0007760962359333857</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -13485,6 +14031,12 @@
       <c r="AT91" s="3" t="n">
         <v>0.0001740644038293494</v>
       </c>
+      <c r="AU91" s="1" t="n">
+        <v>0.05721</v>
+      </c>
+      <c r="AV91" s="2" t="n">
+        <v>-0.004350852767142364</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -13627,6 +14179,12 @@
       <c r="AT92" s="3" t="n">
         <v>0.0007665772326562759</v>
       </c>
+      <c r="AU92" s="1" t="n">
+        <v>1.3063</v>
+      </c>
+      <c r="AV92" s="3" t="n">
+        <v>0.0006127920337034943</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13769,6 +14327,12 @@
       <c r="AT93" s="3" t="n">
         <v>0.001561280249804885</v>
       </c>
+      <c r="AU93" s="1" t="n">
+        <v>0.06431000000000001</v>
+      </c>
+      <c r="AV93" s="3" t="n">
+        <v>0.002494154325799024</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13911,6 +14475,12 @@
       <c r="AT94" s="2" t="n">
         <v>-0.01051401869158876</v>
       </c>
+      <c r="AU94" s="1" t="n">
+        <v>0.008410000000000001</v>
+      </c>
+      <c r="AV94" s="2" t="n">
+        <v>-0.007083825265643363</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -14053,6 +14623,12 @@
       <c r="AT95" s="3" t="n">
         <v>0.003267003267003237</v>
       </c>
+      <c r="AU95" s="1" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AV95" s="2" t="n">
+        <v>-0.001184132622853794</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -14195,6 +14771,12 @@
       <c r="AT96" s="2" t="n">
         <v>-0.005314437555358662</v>
       </c>
+      <c r="AU96" s="1" t="n">
+        <v>0.02257</v>
+      </c>
+      <c r="AV96" s="3" t="n">
+        <v>0.004897595725734594</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -14337,6 +14919,12 @@
       <c r="AT97" s="3" t="n">
         <v>0.001535155050660029</v>
       </c>
+      <c r="AU97" s="1" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AV97" s="2" t="n">
+        <v>-0.001839362354383666</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -14479,6 +15067,12 @@
       <c r="AT98" s="3" t="n">
         <v>0.008795074758135452</v>
       </c>
+      <c r="AU98" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="AV98" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14621,6 +15215,12 @@
       <c r="AT99" s="3" t="n">
         <v>0.001649076517150361</v>
       </c>
+      <c r="AU99" s="1" t="n">
+        <v>3.029</v>
+      </c>
+      <c r="AV99" s="2" t="n">
+        <v>-0.002634178465591046</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -14763,6 +15363,12 @@
       <c r="AT100" s="3" t="n">
         <v>0.002335766423357569</v>
       </c>
+      <c r="AU100" s="1" t="n">
+        <v>0.03443</v>
+      </c>
+      <c r="AV100" s="3" t="n">
+        <v>0.00291290416545304</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -14905,6 +15511,12 @@
       <c r="AT101" s="3" t="n">
         <v>0.001097694840834249</v>
       </c>
+      <c r="AU101" s="1" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="AV101" s="3" t="n">
+        <v>0.0005482456140350273</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -15047,6 +15659,12 @@
       <c r="AT102" s="3" t="n">
         <v>0.01954718042469417</v>
       </c>
+      <c r="AU102" s="1" t="n">
+        <v>0.007252</v>
+      </c>
+      <c r="AV102" s="3" t="n">
+        <v>0.0002758620689654342</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -15189,6 +15807,12 @@
       <c r="AT103" s="3" t="n">
         <v>0.00431499460625678</v>
       </c>
+      <c r="AU103" s="1" t="n">
+        <v>0.06542000000000001</v>
+      </c>
+      <c r="AV103" s="3" t="n">
+        <v>0.003836120914531229</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -15331,6 +15955,12 @@
       <c r="AT104" s="3" t="n">
         <v>0.009495982468955477</v>
       </c>
+      <c r="AU104" s="1" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="AV104" s="3" t="n">
+        <v>0.007718282682103185</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -15473,6 +16103,12 @@
       <c r="AT105" s="3" t="n">
         <v>0.007119386637458872</v>
       </c>
+      <c r="AU105" s="1" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="AV105" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -15615,6 +16251,12 @@
       <c r="AT106" s="2" t="n">
         <v>-0.008783867375974252</v>
       </c>
+      <c r="AU106" s="1" t="n">
+        <v>0.008029</v>
+      </c>
+      <c r="AV106" s="3" t="n">
+        <v>0.002121817274088823</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -15757,6 +16399,12 @@
       <c r="AT107" s="3" t="n">
         <v>0.003307607497243717</v>
       </c>
+      <c r="AU107" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="AV107" s="2" t="n">
+        <v>-0.003296703296703353</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -15899,6 +16547,12 @@
       <c r="AT108" s="3" t="n">
         <v>0.001851851851851776</v>
       </c>
+      <c r="AU108" s="1" t="n">
+        <v>0.02162</v>
+      </c>
+      <c r="AV108" s="2" t="n">
+        <v>-0.0009242144177448792</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -16041,6 +16695,12 @@
       <c r="AT109" s="3" t="n">
         <v>0.001256732495511681</v>
       </c>
+      <c r="AU109" s="1" t="n">
+        <v>0.05596</v>
+      </c>
+      <c r="AV109" s="3" t="n">
+        <v>0.003406849560695762</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -16183,6 +16843,12 @@
       <c r="AT110" s="2" t="n">
         <v>-0.0001740341106856269</v>
       </c>
+      <c r="AU110" s="1" t="n">
+        <v>0.11526</v>
+      </c>
+      <c r="AV110" s="3" t="n">
+        <v>0.003133159268929497</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -16325,6 +16991,12 @@
       <c r="AT111" s="2" t="n">
         <v>-0.0004165364990107089</v>
       </c>
+      <c r="AU111" s="1" t="n">
+        <v>0.09624000000000001</v>
+      </c>
+      <c r="AV111" s="3" t="n">
+        <v>0.002604437962287741</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -16467,6 +17139,12 @@
       <c r="AT112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU112" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="AV112" s="3" t="n">
+        <v>0.00537634408602166</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -16609,6 +17287,12 @@
       <c r="AT113" s="3" t="n">
         <v>0.001118227101758656</v>
       </c>
+      <c r="AU113" s="1" t="n">
+        <v>0.09852</v>
+      </c>
+      <c r="AV113" s="3" t="n">
+        <v>0.0004061738424045326</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -16751,6 +17435,12 @@
       <c r="AT114" s="3" t="n">
         <v>0.007270693512304245</v>
       </c>
+      <c r="AU114" s="1" t="n">
+        <v>0.00179</v>
+      </c>
+      <c r="AV114" s="2" t="n">
+        <v>-0.006107717934480932</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -16893,6 +17583,12 @@
       <c r="AT115" s="2" t="n">
         <v>-0.000237379332172786</v>
       </c>
+      <c r="AU115" s="1" t="n">
+        <v>1.2636</v>
+      </c>
+      <c r="AV115" s="3" t="n">
+        <v>7.914523149979342e-05</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -17035,6 +17731,12 @@
       <c r="AT116" s="3" t="n">
         <v>0.002126754572522333</v>
       </c>
+      <c r="AU116" s="1" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="AV116" s="2" t="n">
+        <v>-0.0008488964346349988</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -17177,6 +17879,12 @@
       <c r="AT117" s="3" t="n">
         <v>0.002148050231328571</v>
       </c>
+      <c r="AU117" s="1" t="n">
+        <v>0.06053</v>
+      </c>
+      <c r="AV117" s="2" t="n">
+        <v>-0.001978565539983546</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -17319,6 +18027,12 @@
       <c r="AT118" s="2" t="n">
         <v>-0.002031602708803607</v>
       </c>
+      <c r="AU118" s="1" t="n">
+        <v>0.04414</v>
+      </c>
+      <c r="AV118" s="2" t="n">
+        <v>-0.001583352182764095</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -17461,6 +18175,12 @@
       <c r="AT119" s="3" t="n">
         <v>0.001374759417101951</v>
       </c>
+      <c r="AU119" s="1" t="n">
+        <v>0.003646</v>
+      </c>
+      <c r="AV119" s="3" t="n">
+        <v>0.001098297638660104</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -17603,6 +18323,12 @@
       <c r="AT120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AV120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -17745,6 +18471,12 @@
       <c r="AT121" s="3" t="n">
         <v>0.0003355704697986208</v>
       </c>
+      <c r="AU121" s="1" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AV121" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -17887,6 +18619,12 @@
       <c r="AT122" s="2" t="n">
         <v>-0.0003518648838845496</v>
       </c>
+      <c r="AU122" s="1" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="AV122" s="3" t="n">
+        <v>0.002991904259063576</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -18029,6 +18767,12 @@
       <c r="AT123" s="3" t="n">
         <v>0.002869540873460202</v>
       </c>
+      <c r="AU123" s="1" t="n">
+        <v>0.028761</v>
+      </c>
+      <c r="AV123" s="3" t="n">
+        <v>0.003594109847163058</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -18171,6 +18915,12 @@
       <c r="AT124" s="2" t="n">
         <v>-0.001276161306789215</v>
       </c>
+      <c r="AU124" s="1" t="n">
+        <v>0.07819</v>
+      </c>
+      <c r="AV124" s="2" t="n">
+        <v>-0.0008944543828264838</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -18313,6 +19063,12 @@
       <c r="AT125" s="2" t="n">
         <v>-0.001231643770724823</v>
       </c>
+      <c r="AU125" s="1" t="n">
+        <v>0.10493</v>
+      </c>
+      <c r="AV125" s="2" t="n">
+        <v>-0.004648074369189948</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -18455,6 +19211,12 @@
       <c r="AT126" s="2" t="n">
         <v>-0.0003809523809523655</v>
       </c>
+      <c r="AU126" s="1" t="n">
+        <v>0.02642</v>
+      </c>
+      <c r="AV126" s="3" t="n">
+        <v>0.006859756097560961</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -18597,6 +19359,12 @@
       <c r="AT127" s="3" t="n">
         <v>0.0004599816007359519</v>
       </c>
+      <c r="AU127" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="AV127" s="3" t="n">
+        <v>0.00137931034482769</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -18739,6 +19507,12 @@
       <c r="AT128" s="2" t="n">
         <v>-0.001236858379715558</v>
       </c>
+      <c r="AU128" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="AV128" s="2" t="n">
+        <v>-0.0006191950464397322</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -18881,6 +19655,12 @@
       <c r="AT129" s="2" t="n">
         <v>-0.001120605126768409</v>
       </c>
+      <c r="AU129" s="1" t="n">
+        <v>0.14429</v>
+      </c>
+      <c r="AV129" s="3" t="n">
+        <v>0.01170943766652647</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -19023,6 +19803,12 @@
       <c r="AT130" s="3" t="n">
         <v>0.003325068711680016</v>
       </c>
+      <c r="AU130" s="1" t="n">
+        <v>0.052461</v>
+      </c>
+      <c r="AV130" s="3" t="n">
+        <v>0.004961495728133066</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -19165,6 +19951,12 @@
       <c r="AT131" s="3" t="n">
         <v>0.0009743027645840547</v>
       </c>
+      <c r="AU131" s="1" t="n">
+        <v>0.08222</v>
+      </c>
+      <c r="AV131" s="3" t="n">
+        <v>0.0003650079085047116</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -19307,6 +20099,12 @@
       <c r="AT132" s="3" t="n">
         <v>0.002275312855517541</v>
       </c>
+      <c r="AU132" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AV132" s="2" t="n">
+        <v>-0.001135073779795719</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -19449,6 +20247,12 @@
       <c r="AT133" s="3" t="n">
         <v>0.0005154639175259072</v>
       </c>
+      <c r="AU133" s="1" t="n">
+        <v>0.5815</v>
+      </c>
+      <c r="AV133" s="2" t="n">
+        <v>-0.001373862270307441</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -19591,6 +20395,12 @@
       <c r="AT134" s="3" t="n">
         <v>0.001351351351351296</v>
       </c>
+      <c r="AU134" s="1" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="AV134" s="2" t="n">
+        <v>-0.001349527665317084</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -19733,6 +20543,12 @@
       <c r="AT135" s="3" t="n">
         <v>0.002862049227246791</v>
       </c>
+      <c r="AU135" s="1" t="n">
+        <v>0.01747</v>
+      </c>
+      <c r="AV135" s="2" t="n">
+        <v>-0.002853881278538895</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -19875,6 +20691,12 @@
       <c r="AT136" s="2" t="n">
         <v>-0.001073825503355661</v>
       </c>
+      <c r="AU136" s="1" t="n">
+        <v>0.03726</v>
+      </c>
+      <c r="AV136" s="3" t="n">
+        <v>0.001343724805159942</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -20017,6 +20839,12 @@
       <c r="AT137" s="2" t="n">
         <v>-0.0003711952487008015</v>
       </c>
+      <c r="AU137" s="1" t="n">
+        <v>0.02702</v>
+      </c>
+      <c r="AV137" s="3" t="n">
+        <v>0.003341997772001478</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -20159,6 +20987,12 @@
       <c r="AT138" s="3" t="n">
         <v>0.006296733569460848</v>
       </c>
+      <c r="AU138" s="1" t="n">
+        <v>2.556</v>
+      </c>
+      <c r="AV138" s="2" t="n">
+        <v>-0.0003910833007430152</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -20301,6 +21135,12 @@
       <c r="AT139" s="3" t="n">
         <v>0.001699235344095235</v>
       </c>
+      <c r="AU139" s="1" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="AV139" s="3" t="n">
+        <v>0.00169635284139094</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -20443,6 +21283,12 @@
       <c r="AT140" s="3" t="n">
         <v>0.0006839945280438665</v>
       </c>
+      <c r="AU140" s="1" t="n">
+        <v>0.01461</v>
+      </c>
+      <c r="AV140" s="2" t="n">
+        <v>-0.001367053998633009</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -20585,6 +21431,12 @@
       <c r="AT141" s="3" t="n">
         <v>0.004891943773608311</v>
       </c>
+      <c r="AU141" s="1" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AV141" s="3" t="n">
+        <v>0.005052994823761226</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -20727,6 +21579,12 @@
       <c r="AT142" s="3" t="n">
         <v>0.001603849238171547</v>
       </c>
+      <c r="AU142" s="1" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="AV142" s="2" t="n">
+        <v>-0.0008006405124098954</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -20869,6 +21727,12 @@
       <c r="AT143" s="2" t="n">
         <v>-0.004222378606615132</v>
       </c>
+      <c r="AU143" s="1" t="n">
+        <v>0.02771</v>
+      </c>
+      <c r="AV143" s="2" t="n">
+        <v>-0.02084805653710248</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -21011,6 +21875,12 @@
       <c r="AT144" s="3" t="n">
         <v>0.005477143459026749</v>
       </c>
+      <c r="AU144" s="1" t="n">
+        <v>0.004782</v>
+      </c>
+      <c r="AV144" s="3" t="n">
+        <v>0.001885606536769214</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -21153,6 +22023,12 @@
       <c r="AT145" s="2" t="n">
         <v>-0.002119820319991915</v>
       </c>
+      <c r="AU145" s="1" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="AV145" s="2" t="n">
+        <v>-5.057913105052298e-05</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -21295,6 +22171,12 @@
       <c r="AT146" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU146" s="1" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="AV146" s="2" t="n">
+        <v>-0.001710132535271562</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -21437,6 +22319,12 @@
       <c r="AT147" s="2" t="n">
         <v>-0.00178034939356857</v>
       </c>
+      <c r="AU147" s="1" t="n">
+        <v>0.08961</v>
+      </c>
+      <c r="AV147" s="2" t="n">
+        <v>-0.001114702931668742</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -21579,6 +22467,12 @@
       <c r="AT148" s="2" t="n">
         <v>-0.007292474786656296</v>
       </c>
+      <c r="AU148" s="1" t="n">
+        <v>0.06375</v>
+      </c>
+      <c r="AV148" s="2" t="n">
+        <v>-0.003594873397936763</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -21721,6 +22615,12 @@
       <c r="AT149" s="3" t="n">
         <v>0.001017121546024708</v>
       </c>
+      <c r="AU149" s="1" t="n">
+        <v>0.05925</v>
+      </c>
+      <c r="AV149" s="3" t="n">
+        <v>0.003386960203217592</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -21863,6 +22763,12 @@
       <c r="AT150" s="3" t="n">
         <v>0.0002043485368644535</v>
       </c>
+      <c r="AU150" s="1" t="n">
+        <v>0.24394</v>
+      </c>
+      <c r="AV150" s="2" t="n">
+        <v>-0.003228047235729224</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -22005,6 +22911,12 @@
       <c r="AT151" s="3" t="n">
         <v>0.005269154087154631</v>
       </c>
+      <c r="AU151" s="1" t="n">
+        <v>7.038e-05</v>
+      </c>
+      <c r="AV151" s="2" t="n">
+        <v>-0.002974925626859324</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -22147,6 +23059,12 @@
       <c r="AT152" s="2" t="n">
         <v>-0.001354707608941046</v>
       </c>
+      <c r="AU152" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AV152" s="2" t="n">
+        <v>-0.005200090436355469</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -22289,6 +23207,12 @@
       <c r="AT153" s="3" t="n">
         <v>0.003206155819172815</v>
       </c>
+      <c r="AU153" s="1" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AV153" s="3" t="n">
+        <v>0.009268136784915351</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -22431,6 +23355,12 @@
       <c r="AT154" s="2" t="n">
         <v>-0.005725190839694631</v>
       </c>
+      <c r="AU154" s="1" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AV154" s="3" t="n">
+        <v>0.002741979709350153</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -22573,6 +23503,12 @@
       <c r="AT155" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" s="1" t="n">
+        <v>0.2297</v>
+      </c>
+      <c r="AV155" s="2" t="n">
+        <v>-0.001304347826087054</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -22715,6 +23651,12 @@
       <c r="AT156" s="2" t="n">
         <v>-0.001729462631253704</v>
       </c>
+      <c r="AU156" s="1" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="AV156" s="3" t="n">
+        <v>0.005444870684321197</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -22857,6 +23799,12 @@
       <c r="AT157" s="3" t="n">
         <v>0.01115225811943988</v>
       </c>
+      <c r="AU157" s="1" t="n">
+        <v>0.23575</v>
+      </c>
+      <c r="AV157" s="2" t="n">
+        <v>-0.007577352136392438</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -22999,6 +23947,12 @@
       <c r="AT158" s="2" t="n">
         <v>-0.004305283757338512</v>
       </c>
+      <c r="AU158" s="1" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="AV158" s="3" t="n">
+        <v>0.009040880503144531</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -23141,6 +24095,12 @@
       <c r="AT159" s="2" t="n">
         <v>-0.0006844626967831019</v>
       </c>
+      <c r="AU159" s="1" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="AV159" s="3" t="n">
+        <v>0.004794520547945286</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -23283,6 +24243,12 @@
       <c r="AT160" s="3" t="n">
         <v>0.005035246727089632</v>
       </c>
+      <c r="AU160" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="AV160" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -23425,6 +24391,12 @@
       <c r="AT161" s="2" t="n">
         <v>-0.003941824113089556</v>
       </c>
+      <c r="AU161" s="1" t="n">
+        <v>0.14644</v>
+      </c>
+      <c r="AV161" s="2" t="n">
+        <v>-0.0008187772925764805</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -23567,6 +24539,12 @@
       <c r="AT162" s="3" t="n">
         <v>0.004870624048706227</v>
       </c>
+      <c r="AU162" s="1" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="AV162" s="2" t="n">
+        <v>-0.000302938503483833</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -23709,6 +24687,12 @@
       <c r="AT163" s="2" t="n">
         <v>-0.002596365088875572</v>
       </c>
+      <c r="AU163" s="1" t="n">
+        <v>0.005035</v>
+      </c>
+      <c r="AV163" s="3" t="n">
+        <v>0.008209851822186672</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -23851,6 +24835,12 @@
       <c r="AT164" s="3" t="n">
         <v>0.005197505197505202</v>
       </c>
+      <c r="AU164" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="AV164" s="2" t="n">
+        <v>-0.00103412616339182</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -23993,6 +24983,12 @@
       <c r="AT165" s="3" t="n">
         <v>0.00130165961601027</v>
       </c>
+      <c r="AU165" s="1" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AV165" s="2" t="n">
+        <v>-0.0003249918752030842</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -24135,6 +25131,12 @@
       <c r="AT166" s="2" t="n">
         <v>-0.001004664513814186</v>
       </c>
+      <c r="AU166" s="1" t="n">
+        <v>1.3918</v>
+      </c>
+      <c r="AV166" s="2" t="n">
+        <v>-0.0002155017599310157</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -24277,6 +25279,12 @@
       <c r="AT167" s="3" t="n">
         <v>0.001799208348326738</v>
       </c>
+      <c r="AU167" s="1" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AV167" s="3" t="n">
+        <v>0.005028735632183953</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -24419,6 +25427,12 @@
       <c r="AT168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU168" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AV168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -24561,6 +25575,12 @@
       <c r="AT169" s="3" t="n">
         <v>0.002010723860589847</v>
       </c>
+      <c r="AU169" s="1" t="n">
+        <v>0.02993</v>
+      </c>
+      <c r="AV169" s="3" t="n">
+        <v>0.00100334448160531</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -24703,6 +25723,12 @@
       <c r="AT170" s="3" t="n">
         <v>0.002310002310002216</v>
       </c>
+      <c r="AU170" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="AV170" s="3" t="n">
+        <v>0.009910117538603361</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -24845,6 +25871,12 @@
       <c r="AT171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU171" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="AV171" s="3" t="n">
+        <v>0.006097560975609719</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -24987,6 +26019,12 @@
       <c r="AT172" s="2" t="n">
         <v>-0.007692307692307619</v>
       </c>
+      <c r="AU172" s="1" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="AV172" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -25129,6 +26167,12 @@
       <c r="AT173" s="2" t="n">
         <v>-0.00426944971537001</v>
       </c>
+      <c r="AU173" s="1" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="AV173" s="3" t="n">
+        <v>0.000952834683182429</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -25271,6 +26315,12 @@
       <c r="AT174" s="3" t="n">
         <v>0.00101169064748209</v>
       </c>
+      <c r="AU174" s="1" t="n">
+        <v>0.08928</v>
+      </c>
+      <c r="AV174" s="3" t="n">
+        <v>0.002582818641212735</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -25413,6 +26463,12 @@
       <c r="AT175" s="3" t="n">
         <v>0.00111513799832717</v>
       </c>
+      <c r="AU175" s="1" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AV175" s="3" t="n">
+        <v>0.001949317738791518</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -25555,6 +26611,12 @@
       <c r="AT176" s="2" t="n">
         <v>-0.002348520432127827</v>
       </c>
+      <c r="AU176" s="1" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="AV176" s="3" t="n">
+        <v>0.0004708097928438353</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -25697,6 +26759,12 @@
       <c r="AT177" s="3" t="n">
         <v>0.001277139208173639</v>
       </c>
+      <c r="AU177" s="1" t="n">
+        <v>0.00793</v>
+      </c>
+      <c r="AV177" s="3" t="n">
+        <v>0.01147959183673467</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -25839,6 +26907,12 @@
       <c r="AT178" s="3" t="n">
         <v>0.002100840336134391</v>
       </c>
+      <c r="AU178" s="1" t="n">
+        <v>0.000955</v>
+      </c>
+      <c r="AV178" s="3" t="n">
+        <v>0.00104821802935013</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -25981,6 +27055,12 @@
       <c r="AT179" s="3" t="n">
         <v>0.004723789528933079</v>
       </c>
+      <c r="AU179" s="1" t="n">
+        <v>0.022938</v>
+      </c>
+      <c r="AV179" s="2" t="n">
+        <v>-0.001436593966305268</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -26123,6 +27203,12 @@
       <c r="AT180" s="3" t="n">
         <v>0.003173828124999976</v>
       </c>
+      <c r="AU180" s="1" t="n">
+        <v>4.124</v>
+      </c>
+      <c r="AV180" s="3" t="n">
+        <v>0.003650523241664561</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -26265,6 +27351,12 @@
       <c r="AT181" s="3" t="n">
         <v>0.002806525171022513</v>
       </c>
+      <c r="AU181" s="1" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="AV181" s="3" t="n">
+        <v>0.002973587545915751</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -26407,6 +27499,12 @@
       <c r="AT182" s="3" t="n">
         <v>0.003775834658187652</v>
       </c>
+      <c r="AU182" s="1" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="AV182" s="3" t="n">
+        <v>0.004751534349633818</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -26549,6 +27647,12 @@
       <c r="AT183" s="2" t="n">
         <v>-0.0005523844595838913</v>
       </c>
+      <c r="AU183" s="1" t="n">
+        <v>5.431</v>
+      </c>
+      <c r="AV183" s="3" t="n">
+        <v>0.0005526897568165279</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -26691,6 +27795,12 @@
       <c r="AT184" s="2" t="n">
         <v>-0.001735508503991571</v>
       </c>
+      <c r="AU184" s="1" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="AV184" s="2" t="n">
+        <v>-0.001043115438108523</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -26833,6 +27943,12 @@
       <c r="AT185" s="3" t="n">
         <v>0.005417118093174398</v>
       </c>
+      <c r="AU185" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="AV185" s="2" t="n">
+        <v>-0.003771551724137964</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -26975,6 +28091,12 @@
       <c r="AT186" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU186" s="1" t="n">
+        <v>3.07e-05</v>
+      </c>
+      <c r="AV186" s="3" t="n">
+        <v>0.00326797385620923</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -27117,6 +28239,12 @@
       <c r="AT187" s="3" t="n">
         <v>0.002551020408163383</v>
       </c>
+      <c r="AU187" s="1" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="AV187" s="3" t="n">
+        <v>0.006361323155216246</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -27259,6 +28387,12 @@
       <c r="AT188" s="3" t="n">
         <v>0.002456398919184375</v>
       </c>
+      <c r="AU188" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="AV188" s="3" t="n">
+        <v>0.002205341827983332</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -27401,6 +28535,12 @@
       <c r="AT189" s="3" t="n">
         <v>0.001358388046185227</v>
       </c>
+      <c r="AU189" s="1" t="n">
+        <v>0.0004426</v>
+      </c>
+      <c r="AV189" s="3" t="n">
+        <v>0.0006782726656115923</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -27543,6 +28683,12 @@
       <c r="AT190" s="3" t="n">
         <v>0.001299263750541457</v>
       </c>
+      <c r="AU190" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="AV190" s="2" t="n">
+        <v>-0.004757785467128134</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -27685,6 +28831,12 @@
       <c r="AT191" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU191" s="1" t="n">
+        <v>0.01567</v>
+      </c>
+      <c r="AV191" s="3" t="n">
+        <v>0.001918158567774858</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -27827,6 +28979,12 @@
       <c r="AT192" s="2" t="n">
         <v>-0.002152852529601634</v>
       </c>
+      <c r="AU192" s="1" t="n">
+        <v>0.05571</v>
+      </c>
+      <c r="AV192" s="3" t="n">
+        <v>0.001618122977346275</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -27969,6 +29127,12 @@
       <c r="AT193" s="3" t="n">
         <v>0.001071237279057342</v>
       </c>
+      <c r="AU193" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="AV193" s="3" t="n">
+        <v>0.0005350454788656447</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -28111,6 +29275,12 @@
       <c r="AT194" s="2" t="n">
         <v>-0.001041124414367655</v>
       </c>
+      <c r="AU194" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AV194" s="3" t="n">
+        <v>0.0005211047420531315</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -28253,6 +29423,12 @@
       <c r="AT195" s="3" t="n">
         <v>0.003276386613620436</v>
       </c>
+      <c r="AU195" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AV195" s="3" t="n">
+        <v>0.003032423606251383</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -28395,6 +29571,12 @@
       <c r="AT196" s="3" t="n">
         <v>0.004918032786885187</v>
       </c>
+      <c r="AU196" s="1" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="AV196" s="3" t="n">
+        <v>0.008156606851549706</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -28537,6 +29719,12 @@
       <c r="AT197" s="3" t="n">
         <v>0.001517450682852821</v>
       </c>
+      <c r="AU197" s="1" t="n">
+        <v>0.04646</v>
+      </c>
+      <c r="AV197" s="3" t="n">
+        <v>0.005627705627705699</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -28679,6 +29867,12 @@
       <c r="AT198" s="2" t="n">
         <v>-0.002917152858809696</v>
       </c>
+      <c r="AU198" s="1" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="AV198" s="3" t="n">
+        <v>0.0005851375073141543</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -28821,6 +30015,12 @@
       <c r="AT199" s="2" t="n">
         <v>-0.01123595505617979</v>
       </c>
+      <c r="AU199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AV199" s="3" t="n">
+        <v>0.01136363636363637</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -28963,6 +30163,12 @@
       <c r="AT200" s="2" t="n">
         <v>-0.002028397565922878</v>
       </c>
+      <c r="AU200" s="1" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AV200" s="3" t="n">
+        <v>0.0006775067750677363</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -29105,6 +30311,12 @@
       <c r="AT201" s="2" t="n">
         <v>-0.0005350454788657746</v>
       </c>
+      <c r="AU201" s="1" t="n">
+        <v>0.005607</v>
+      </c>
+      <c r="AV201" s="3" t="n">
+        <v>0.0005353319057816556</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -29247,6 +30459,12 @@
       <c r="AT202" s="2" t="n">
         <v>-0.0002608015300356021</v>
       </c>
+      <c r="AU202" s="1" t="n">
+        <v>0.023034</v>
+      </c>
+      <c r="AV202" s="3" t="n">
+        <v>0.001478260869565187</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -29389,6 +30607,12 @@
       <c r="AT203" s="3" t="n">
         <v>0.003676470588235399</v>
       </c>
+      <c r="AU203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AV203" s="2" t="n">
+        <v>-0.003663003663003768</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -29531,6 +30755,12 @@
       <c r="AT204" s="3" t="n">
         <v>0.007469375560203174</v>
       </c>
+      <c r="AU204" s="1" t="n">
+        <v>0.03375</v>
+      </c>
+      <c r="AV204" s="3" t="n">
+        <v>0.0008896797153025577</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -29673,6 +30903,12 @@
       <c r="AT205" s="3" t="n">
         <v>0.006275645667390732</v>
       </c>
+      <c r="AU205" s="1" t="n">
+        <v>4.166</v>
+      </c>
+      <c r="AV205" s="2" t="n">
+        <v>-0.0007195970256654415</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -29815,6 +31051,12 @@
       <c r="AT206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU206" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AV206" s="3" t="n">
+        <v>0.00277777777777778</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -29957,6 +31199,12 @@
       <c r="AT207" s="2" t="n">
         <v>-0.004835669207442086</v>
       </c>
+      <c r="AU207" s="1" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="AV207" s="2" t="n">
+        <v>-0.01169494317245925</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -30099,6 +31347,12 @@
       <c r="AT208" s="3" t="n">
         <v>0.001115915748361026</v>
       </c>
+      <c r="AU208" s="1" t="n">
+        <v>0.007146</v>
+      </c>
+      <c r="AV208" s="2" t="n">
+        <v>-0.004319353490316378</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -30241,6 +31495,12 @@
       <c r="AT209" s="3" t="n">
         <v>0.003355704697986557</v>
       </c>
+      <c r="AU209" s="1" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="AV209" s="2" t="n">
+        <v>-0.001672240802675517</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -30383,6 +31643,12 @@
       <c r="AT210" s="2" t="n">
         <v>-0.0007763975155278648</v>
       </c>
+      <c r="AU210" s="1" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="AV210" s="3" t="n">
+        <v>0.001554001554001383</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -30525,6 +31791,12 @@
       <c r="AT211" s="2" t="n">
         <v>-0.0008421052631578847</v>
       </c>
+      <c r="AU211" s="1" t="n">
+        <v>0.007134</v>
+      </c>
+      <c r="AV211" s="3" t="n">
+        <v>0.002107037505267508</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -30667,6 +31939,12 @@
       <c r="AT212" s="3" t="n">
         <v>0.008440243079000683</v>
       </c>
+      <c r="AU212" s="1" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AV212" s="3" t="n">
+        <v>0.03649146300636078</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -30809,6 +32087,12 @@
       <c r="AT213" s="2" t="n">
         <v>-0.01372369624885625</v>
       </c>
+      <c r="AU213" s="1" t="n">
+        <v>0.05374</v>
+      </c>
+      <c r="AV213" s="2" t="n">
+        <v>-0.002968460111317262</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -30951,6 +32235,12 @@
       <c r="AT214" s="3" t="n">
         <v>0.001599999999999972</v>
       </c>
+      <c r="AU214" s="1" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="AV214" s="2" t="n">
+        <v>-0.00106496272630461</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -31093,6 +32383,12 @@
       <c r="AT215" s="3" t="n">
         <v>0.00320271288620943</v>
       </c>
+      <c r="AU215" s="1" t="n">
+        <v>0.05352</v>
+      </c>
+      <c r="AV215" s="3" t="n">
+        <v>0.005070422535211256</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -31235,6 +32531,12 @@
       <c r="AT216" s="2" t="n">
         <v>-0.003958436417614924</v>
       </c>
+      <c r="AU216" s="1" t="n">
+        <v>0.002009</v>
+      </c>
+      <c r="AV216" s="2" t="n">
+        <v>-0.001987083954297117</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -31377,6 +32679,12 @@
       <c r="AT217" s="2" t="n">
         <v>-0.0004995836802664636</v>
       </c>
+      <c r="AU217" s="1" t="n">
+        <v>6.002</v>
+      </c>
+      <c r="AV217" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -31519,6 +32827,12 @@
       <c r="AT218" s="3" t="n">
         <v>0.0035502958579883</v>
       </c>
+      <c r="AU218" s="1" t="n">
+        <v>4.258</v>
+      </c>
+      <c r="AV218" s="3" t="n">
+        <v>0.004245283018867876</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -31661,6 +32975,12 @@
       <c r="AT219" s="2" t="n">
         <v>-0.003728560775540651</v>
       </c>
+      <c r="AU219" s="1" t="n">
+        <v>0.005347</v>
+      </c>
+      <c r="AV219" s="3" t="n">
+        <v>0.0005613772455090566</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -31803,6 +33123,12 @@
       <c r="AT220" s="3" t="n">
         <v>0.0007311723129418047</v>
       </c>
+      <c r="AU220" s="1" t="n">
+        <v>0.04104</v>
+      </c>
+      <c r="AV220" s="2" t="n">
+        <v>-0.0004870920603993957</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -31945,6 +33271,12 @@
       <c r="AT221" s="3" t="n">
         <v>0.0001728907330567311</v>
       </c>
+      <c r="AU221" s="1" t="n">
+        <v>0.00581</v>
+      </c>
+      <c r="AV221" s="3" t="n">
+        <v>0.004321521175453733</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -32087,6 +33419,12 @@
       <c r="AT222" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU222" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="AV222" s="2" t="n">
+        <v>-0.001089324618736415</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -32229,6 +33567,12 @@
       <c r="AT223" s="2" t="n">
         <v>-0.0005950609937519592</v>
       </c>
+      <c r="AU223" s="1" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AV223" s="2" t="n">
+        <v>-0.0005954153021732003</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -32371,6 +33715,12 @@
       <c r="AT224" s="2" t="n">
         <v>-0.0002314279102059454</v>
       </c>
+      <c r="AU224" s="1" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="AV224" s="3" t="n">
+        <v>0.001157407407407408</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -32513,6 +33863,12 @@
       <c r="AT225" s="2" t="n">
         <v>-0.0007209805335256488</v>
       </c>
+      <c r="AU225" s="1" t="n">
+        <v>0.08322</v>
+      </c>
+      <c r="AV225" s="3" t="n">
+        <v>0.0007215007215007756</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -32655,6 +34011,12 @@
       <c r="AT226" s="3" t="n">
         <v>0.00324149108589957</v>
       </c>
+      <c r="AU226" s="1" t="n">
+        <v>0.01857</v>
+      </c>
+      <c r="AV226" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -32797,6 +34159,12 @@
       <c r="AT227" s="3" t="n">
         <v>0.001066098081023485</v>
       </c>
+      <c r="AU227" s="1" t="n">
+        <v>0.04705</v>
+      </c>
+      <c r="AV227" s="3" t="n">
+        <v>0.00212992545260922</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -32939,6 +34307,12 @@
       <c r="AT228" s="2" t="n">
         <v>-0.001290877796901841</v>
       </c>
+      <c r="AU228" s="1" t="n">
+        <v>0.02328</v>
+      </c>
+      <c r="AV228" s="3" t="n">
+        <v>0.003015941404566874</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -33081,6 +34455,12 @@
       <c r="AT229" s="3" t="n">
         <v>0.0009199632014718397</v>
       </c>
+      <c r="AU229" s="1" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="AV229" s="3" t="n">
+        <v>0.0009191176470588499</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -33223,6 +34603,12 @@
       <c r="AT230" s="3" t="n">
         <v>0.004819277108433706</v>
       </c>
+      <c r="AU230" s="1" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="AV230" s="3" t="n">
+        <v>0.0005995203836929795</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -33365,6 +34751,12 @@
       <c r="AT231" s="2" t="n">
         <v>-0.0009865175928970332</v>
       </c>
+      <c r="AU231" s="1" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="AV231" s="3" t="n">
+        <v>0.0006583278472679126</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -33507,6 +34899,12 @@
       <c r="AT232" s="3" t="n">
         <v>0.005855855855855773</v>
       </c>
+      <c r="AU232" s="1" t="n">
+        <v>0.02231</v>
+      </c>
+      <c r="AV232" s="2" t="n">
+        <v>-0.0008956560680698247</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -33649,6 +35047,12 @@
       <c r="AT233" s="3" t="n">
         <v>0.009040216289286817</v>
       </c>
+      <c r="AU233" s="1" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="AV233" s="3" t="n">
+        <v>0.005944904965251631</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -33791,6 +35195,12 @@
       <c r="AT234" s="3" t="n">
         <v>0.001973164956590373</v>
       </c>
+      <c r="AU234" s="1" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="AV234" s="3" t="n">
+        <v>0.0003938558487593107</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -33933,6 +35343,12 @@
       <c r="AT235" s="3" t="n">
         <v>0.001745200698080208</v>
       </c>
+      <c r="AU235" s="1" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="AV235" s="3" t="n">
+        <v>0.0002903600464576963</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -34075,6 +35491,12 @@
       <c r="AT236" s="3" t="n">
         <v>0.003021868787276274</v>
       </c>
+      <c r="AU236" s="1" t="n">
+        <v>0.12692</v>
+      </c>
+      <c r="AV236" s="3" t="n">
+        <v>0.00626337905335775</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -34217,6 +35639,12 @@
       <c r="AT237" s="2" t="n">
         <v>-0.004451427075150654</v>
       </c>
+      <c r="AU237" s="1" t="n">
+        <v>0.03807</v>
+      </c>
+      <c r="AV237" s="3" t="n">
+        <v>0.001315097317201511</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -34359,6 +35787,12 @@
       <c r="AT238" s="2" t="n">
         <v>-0.008403361344537823</v>
       </c>
+      <c r="AU238" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AV238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -34501,6 +35935,12 @@
       <c r="AT239" s="2" t="n">
         <v>-0.007910181168665419</v>
       </c>
+      <c r="AU239" s="1" t="n">
+        <v>0.003828</v>
+      </c>
+      <c r="AV239" s="2" t="n">
+        <v>-0.01543209876543214</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -34643,6 +36083,12 @@
       <c r="AT240" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU240" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="AV240" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -34785,6 +36231,12 @@
       <c r="AT241" s="2" t="n">
         <v>-0.002471910112359528</v>
       </c>
+      <c r="AU241" s="1" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="AV241" s="2" t="n">
+        <v>-0.0101374183374634</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -34927,6 +36379,12 @@
       <c r="AT242" s="3" t="n">
         <v>0.001344086021505322</v>
       </c>
+      <c r="AU242" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="AV242" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -35069,6 +36527,12 @@
       <c r="AT243" s="2" t="n">
         <v>-0.002212389380530884</v>
       </c>
+      <c r="AU243" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="AV243" s="3" t="n">
+        <v>0.0004434589800443278</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -35211,6 +36675,12 @@
       <c r="AT244" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU244" s="1" t="n">
+        <v>0.001699</v>
+      </c>
+      <c r="AV244" s="3" t="n">
+        <v>0.004137115839243535</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -35353,6 +36823,12 @@
       <c r="AT245" s="3" t="n">
         <v>0.001531393568147058</v>
       </c>
+      <c r="AU245" s="1" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="AV245" s="2" t="n">
+        <v>-0.0007645259938837078</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -35495,6 +36971,12 @@
       <c r="AT246" s="3" t="n">
         <v>0.01031260070899144</v>
       </c>
+      <c r="AU246" s="1" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="AV246" s="2" t="n">
+        <v>-0.007974481658692302</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -35637,6 +37119,12 @@
       <c r="AT247" s="3" t="n">
         <v>0.002253521126760628</v>
       </c>
+      <c r="AU247" s="1" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="AV247" s="3" t="n">
+        <v>0.002248454187745833</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -35779,6 +37267,12 @@
       <c r="AT248" s="2" t="n">
         <v>-0.001657824933686935</v>
       </c>
+      <c r="AU248" s="1" t="n">
+        <v>0.03024</v>
+      </c>
+      <c r="AV248" s="3" t="n">
+        <v>0.00431750249086676</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -35921,6 +37415,12 @@
       <c r="AT249" s="2" t="n">
         <v>-0.002299406995038112</v>
       </c>
+      <c r="AU249" s="1" t="n">
+        <v>0.00822</v>
+      </c>
+      <c r="AV249" s="2" t="n">
+        <v>-0.00291120815138279</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -36063,6 +37563,12 @@
       <c r="AT250" s="3" t="n">
         <v>0.008016032064128278</v>
       </c>
+      <c r="AU250" s="1" t="n">
+        <v>0.02023</v>
+      </c>
+      <c r="AV250" s="3" t="n">
+        <v>0.00546719681908561</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -36205,6 +37711,12 @@
       <c r="AT251" s="3" t="n">
         <v>0.0002165439584236263</v>
       </c>
+      <c r="AU251" s="1" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="AV251" s="3" t="n">
+        <v>0.001298982463736687</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -36347,6 +37859,12 @@
       <c r="AT252" s="2" t="n">
         <v>-0.001991331849595836</v>
       </c>
+      <c r="AU252" s="1" t="n">
+        <v>0.008515</v>
+      </c>
+      <c r="AV252" s="2" t="n">
+        <v>-0.0005868544600938728</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -36489,6 +38007,12 @@
       <c r="AT253" s="2" t="n">
         <v>-0.0005278437582475372</v>
       </c>
+      <c r="AU253" s="1" t="n">
+        <v>0.03805</v>
+      </c>
+      <c r="AV253" s="3" t="n">
+        <v>0.00475310271983099</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -36631,6 +38155,12 @@
       <c r="AT254" s="3" t="n">
         <v>0.001312766655726891</v>
       </c>
+      <c r="AU254" s="1" t="n">
+        <v>0.06106</v>
+      </c>
+      <c r="AV254" s="3" t="n">
+        <v>0.0006555227794166718</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -36773,6 +38303,12 @@
       <c r="AT255" s="3" t="n">
         <v>0.001705029838022145</v>
       </c>
+      <c r="AU255" s="1" t="n">
+        <v>0.003524</v>
+      </c>
+      <c r="AV255" s="2" t="n">
+        <v>-0.000283687943262449</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -36915,6 +38451,12 @@
       <c r="AT256" s="2" t="n">
         <v>-0.006690220251071227</v>
       </c>
+      <c r="AU256" s="1" t="n">
+        <v>0.013332</v>
+      </c>
+      <c r="AV256" s="3" t="n">
+        <v>0.008929922809141823</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -37057,6 +38599,12 @@
       <c r="AT257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU257" s="1" t="n">
+        <v>0.999443</v>
+      </c>
+      <c r="AV257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -37199,6 +38747,12 @@
       <c r="AT258" s="3" t="n">
         <v>0.002735666248717703</v>
       </c>
+      <c r="AU258" s="1" t="n">
+        <v>0.08774999999999999</v>
+      </c>
+      <c r="AV258" s="2" t="n">
+        <v>-0.002500852563374012</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -37341,6 +38895,12 @@
       <c r="AT259" s="2" t="n">
         <v>-0.001008290387631713</v>
       </c>
+      <c r="AU259" s="1" t="n">
+        <v>0.08946999999999999</v>
+      </c>
+      <c r="AV259" s="3" t="n">
+        <v>0.003364360210833181</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -37483,6 +39043,12 @@
       <c r="AT260" s="2" t="n">
         <v>-0.004956629491945448</v>
       </c>
+      <c r="AU260" s="1" t="n">
+        <v>0.08005</v>
+      </c>
+      <c r="AV260" s="2" t="n">
+        <v>-0.003113325031133253</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -37625,6 +39191,12 @@
       <c r="AT261" s="3" t="n">
         <v>0.001742160278745646</v>
       </c>
+      <c r="AU261" s="1" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="AV261" s="2" t="n">
+        <v>-0.0008695652173912086</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -37767,6 +39339,12 @@
       <c r="AT262" s="2" t="n">
         <v>-0.002547770700636839</v>
       </c>
+      <c r="AU262" s="1" t="n">
+        <v>0.003943</v>
+      </c>
+      <c r="AV262" s="3" t="n">
+        <v>0.007151979565772732</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -37909,6 +39487,12 @@
       <c r="AT263" s="3" t="n">
         <v>0.0008896797153025165</v>
       </c>
+      <c r="AU263" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="AV263" s="3" t="n">
+        <v>0.003555555555555534</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -38051,6 +39635,12 @@
       <c r="AT264" s="3" t="n">
         <v>0.004214621494569725</v>
       </c>
+      <c r="AU264" s="1" t="n">
+        <v>0.0006185</v>
+      </c>
+      <c r="AV264" s="2" t="n">
+        <v>-0.001614205004035552</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -38193,6 +39783,12 @@
       <c r="AT265" s="3" t="n">
         <v>0.001375515818431856</v>
       </c>
+      <c r="AU265" s="1" t="n">
+        <v>0.01459</v>
+      </c>
+      <c r="AV265" s="3" t="n">
+        <v>0.002060439560439596</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -38335,6 +39931,12 @@
       <c r="AT266" s="2" t="n">
         <v>-0.001582278481012703</v>
       </c>
+      <c r="AU266" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="AV266" s="3" t="n">
+        <v>0.003169572107765323</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -38477,6 +40079,12 @@
       <c r="AT267" s="3" t="n">
         <v>0.002464571780653011</v>
       </c>
+      <c r="AU267" s="1" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="AV267" s="3" t="n">
+        <v>0.007375537799631136</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -38619,6 +40227,12 @@
       <c r="AT268" s="3" t="n">
         <v>0.003947979563399877</v>
       </c>
+      <c r="AU268" s="1" t="n">
+        <v>0.0004312</v>
+      </c>
+      <c r="AV268" s="2" t="n">
+        <v>-0.00254452926208645</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -38761,6 +40375,12 @@
       <c r="AT269" s="3" t="n">
         <v>0.007718282682103253</v>
       </c>
+      <c r="AU269" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AV269" s="3" t="n">
+        <v>0.0004786979415988317</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -38903,6 +40523,12 @@
       <c r="AT270" s="2" t="n">
         <v>-0.0005452562704472015</v>
       </c>
+      <c r="AU270" s="1" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="AV270" s="3" t="n">
+        <v>0.00763775231860345</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -39045,6 +40671,12 @@
       <c r="AT271" s="3" t="n">
         <v>0.0006788866259335828</v>
       </c>
+      <c r="AU271" s="1" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="AV271" s="3" t="n">
+        <v>0.001356852103120799</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -39187,6 +40819,12 @@
       <c r="AT272" s="3" t="n">
         <v>0.0005087763927753545</v>
       </c>
+      <c r="AU272" s="1" t="n">
+        <v>0.03938</v>
+      </c>
+      <c r="AV272" s="3" t="n">
+        <v>0.001271294177472704</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -39329,6 +40967,12 @@
       <c r="AT273" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU273" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="AV273" s="2" t="n">
+        <v>-0.002164502164502166</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -39471,6 +41115,12 @@
       <c r="AT274" s="3" t="n">
         <v>0.0006311139160618356</v>
       </c>
+      <c r="AU274" s="1" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="AV274" s="3" t="n">
+        <v>0.0001576789656259541</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -39613,6 +41263,12 @@
       <c r="AT275" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU275" s="1" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="AV275" s="3" t="n">
+        <v>0.0008896797153024548</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -39755,6 +41411,12 @@
       <c r="AT276" s="3" t="n">
         <v>0.004200076365024695</v>
       </c>
+      <c r="AU276" s="1" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="AV276" s="3" t="n">
+        <v>0.0003802281368820874</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -39897,6 +41559,12 @@
       <c r="AT277" s="3" t="n">
         <v>0.0002387204583433531</v>
       </c>
+      <c r="AU277" s="1" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="AV277" s="3" t="n">
+        <v>0.0009546539379474551</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -40039,6 +41707,12 @@
       <c r="AT278" s="3" t="n">
         <v>0.002565418163160491</v>
       </c>
+      <c r="AU278" s="1" t="n">
+        <v>0.01961</v>
+      </c>
+      <c r="AV278" s="3" t="n">
+        <v>0.003582395087001056</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -40181,6 +41855,12 @@
       <c r="AT279" s="2" t="n">
         <v>-0.006678383128295227</v>
       </c>
+      <c r="AU279" s="1" t="n">
+        <v>0.005635</v>
+      </c>
+      <c r="AV279" s="2" t="n">
+        <v>-0.003007784854918552</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -40323,6 +42003,12 @@
       <c r="AT280" s="2" t="n">
         <v>-0.002822684115986631</v>
       </c>
+      <c r="AU280" s="1" t="n">
+        <v>0.03903</v>
+      </c>
+      <c r="AV280" s="3" t="n">
+        <v>0.004374678332475643</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -40465,6 +42151,12 @@
       <c r="AT281" s="3" t="n">
         <v>0.001103752759381899</v>
       </c>
+      <c r="AU281" s="1" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="AV281" s="2" t="n">
+        <v>-0.001102535832414554</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -40607,6 +42299,12 @@
       <c r="AT282" s="3" t="n">
         <v>0.001197318007662864</v>
       </c>
+      <c r="AU282" s="1" t="n">
+        <v>0.0004162</v>
+      </c>
+      <c r="AV282" s="2" t="n">
+        <v>-0.004544367376225894</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -40749,6 +42447,12 @@
       <c r="AT283" s="3" t="n">
         <v>0.0002439619419371325</v>
       </c>
+      <c r="AU283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AV283" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -40891,6 +42595,12 @@
       <c r="AT284" s="2" t="n">
         <v>-0.000237473284255594</v>
       </c>
+      <c r="AU284" s="1" t="n">
+        <v>0.04207</v>
+      </c>
+      <c r="AV284" s="2" t="n">
+        <v>-0.0007125890736340929</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -41033,6 +42743,12 @@
       <c r="AT285" s="3" t="n">
         <v>0.001887682869277884</v>
       </c>
+      <c r="AU285" s="1" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="AV285" s="3" t="n">
+        <v>0.002355157795572306</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -41175,6 +42891,12 @@
       <c r="AT286" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AU286" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="AV286" s="3" t="n">
+        <v>0.004773269689737483</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -41317,6 +43039,12 @@
       <c r="AT287" s="3" t="n">
         <v>0.008319999999999972</v>
       </c>
+      <c r="AU287" s="1" t="n">
+        <v>0.15907</v>
+      </c>
+      <c r="AV287" s="3" t="n">
+        <v>0.009647730879085964</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -41459,6 +43187,12 @@
       <c r="AT288" s="2" t="n">
         <v>-0.004432132963988893</v>
       </c>
+      <c r="AU288" s="1" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="AV288" s="3" t="n">
+        <v>0.003338898163605951</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -41601,6 +43335,12 @@
       <c r="AT289" s="2" t="n">
         <v>-0.0002420135527588204</v>
       </c>
+      <c r="AU289" s="1" t="n">
+        <v>4.126</v>
+      </c>
+      <c r="AV289" s="2" t="n">
+        <v>-0.001210360687484845</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -41743,6 +43483,12 @@
       <c r="AT290" s="2" t="n">
         <v>-0.003404555059873356</v>
       </c>
+      <c r="AU290" s="1" t="n">
+        <v>0.08492</v>
+      </c>
+      <c r="AV290" s="3" t="n">
+        <v>0.0003533985157262605</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -41885,6 +43631,12 @@
       <c r="AT291" s="3" t="n">
         <v>0.000281452293836281</v>
       </c>
+      <c r="AU291" s="1" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="AV291" s="2" t="n">
+        <v>-0.001125492402926429</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -42027,6 +43779,12 @@
       <c r="AT292" s="3" t="n">
         <v>0.00415956358677122</v>
       </c>
+      <c r="AU292" s="1" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="AV292" s="2" t="n">
+        <v>-0.0010865136493276</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -42169,6 +43927,12 @@
       <c r="AT293" s="2" t="n">
         <v>-0.0005139626520473527</v>
       </c>
+      <c r="AU293" s="1" t="n">
+        <v>0.005843</v>
+      </c>
+      <c r="AV293" s="3" t="n">
+        <v>0.001542680836475888</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -42311,6 +44075,12 @@
       <c r="AT294" s="2" t="n">
         <v>-0.001751313485113815</v>
       </c>
+      <c r="AU294" s="1" t="n">
+        <v>0.003436</v>
+      </c>
+      <c r="AV294" s="3" t="n">
+        <v>0.004678362573099402</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -42453,6 +44223,12 @@
       <c r="AT295" s="2" t="n">
         <v>-0.0005594927265944927</v>
       </c>
+      <c r="AU295" s="1" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="AV295" s="3" t="n">
+        <v>0.002799029669714398</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -42595,6 +44371,12 @@
       <c r="AT296" s="2" t="n">
         <v>-0.001330376940133088</v>
       </c>
+      <c r="AU296" s="1" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="AV29